--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -772,7 +772,13 @@
     <t>Cours-Identifiation et diagnostique des machines électriques</t>
   </si>
   <si>
-    <t>TP-conception assistée par ordinateur des machines électriques-SG12</t>
+    <t>TP-Conception assistée par ordinateur des machines électriques-SG11</t>
+  </si>
+  <si>
+    <t>TP-Machines électriques spéciales-SG12</t>
+  </si>
+  <si>
+    <t>TP-Conception assistée par ordinateur des machines électriques-SG12</t>
   </si>
   <si>
     <t>TP-Machines électriques spéciales-SG11</t>
@@ -1453,9 +1459,6 @@
     <t>TP-Cap-3ELT</t>
   </si>
   <si>
-    <t>Cours-RE-L3ELT</t>
-  </si>
-  <si>
     <t>Cours-SA-3ELT</t>
   </si>
   <si>
@@ -1463,9 +1466,6 @@
   </si>
   <si>
     <t>TD-TC-3ELT</t>
-  </si>
-  <si>
-    <t>Cours-RE-3ELT</t>
   </si>
   <si>
     <t>Cours-C &amp;M-3ELT</t>
@@ -3556,7 +3556,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C2" t="s">
         <v>674</v>
@@ -3579,7 +3579,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C3" t="s">
         <v>674</v>
@@ -3602,7 +3602,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C4" t="s">
         <v>675</v>
@@ -3625,7 +3625,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C5" t="s">
         <v>675</v>
@@ -3648,7 +3648,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C6" t="s">
         <v>674</v>
@@ -3671,7 +3671,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C7" t="s">
         <v>674</v>
@@ -3694,7 +3694,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C8" t="s">
         <v>674</v>
@@ -3717,7 +3717,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C9" t="s">
         <v>674</v>
@@ -3740,7 +3740,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C10" t="s">
         <v>676</v>
@@ -3763,7 +3763,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C11" t="s">
         <v>676</v>
@@ -3786,7 +3786,7 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C12" t="s">
         <v>676</v>
@@ -3809,7 +3809,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C13" t="s">
         <v>676</v>
@@ -3832,7 +3832,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C14" t="s">
         <v>676</v>
@@ -3855,7 +3855,7 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C15" t="s">
         <v>676</v>
@@ -3878,7 +3878,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C16" t="s">
         <v>674</v>
@@ -3901,7 +3901,7 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C17" t="s">
         <v>674</v>
@@ -3924,7 +3924,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C18" t="s">
         <v>677</v>
@@ -3947,7 +3947,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C19" t="s">
         <v>675</v>
@@ -3970,7 +3970,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C20" t="s">
         <v>678</v>
@@ -3993,7 +3993,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C21" t="s">
         <v>678</v>
@@ -4016,7 +4016,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C22" t="s">
         <v>677</v>
@@ -4039,7 +4039,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C23" t="s">
         <v>679</v>
@@ -4062,7 +4062,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C24" t="s">
         <v>676</v>
@@ -4085,7 +4085,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C25" t="s">
         <v>680</v>
@@ -4108,7 +4108,7 @@
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C26" t="s">
         <v>675</v>
@@ -4131,7 +4131,7 @@
         <v>15</v>
       </c>
       <c r="B27" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C27" t="s">
         <v>675</v>
@@ -4154,7 +4154,7 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C28" t="s">
         <v>675</v>
@@ -4177,7 +4177,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C29" t="s">
         <v>675</v>
@@ -4200,7 +4200,7 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C30" t="s">
         <v>675</v>
@@ -4223,7 +4223,7 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C31" t="s">
         <v>678</v>
@@ -4246,7 +4246,7 @@
         <v>26</v>
       </c>
       <c r="B32" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C32" t="s">
         <v>681</v>
@@ -4269,7 +4269,7 @@
         <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C33" t="s">
         <v>682</v>
@@ -4292,7 +4292,7 @@
         <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C34" t="s">
         <v>683</v>
@@ -4315,7 +4315,7 @@
         <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C35" t="s">
         <v>683</v>
@@ -4338,7 +4338,7 @@
         <v>30</v>
       </c>
       <c r="B36" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C36" t="s">
         <v>684</v>
@@ -4361,7 +4361,7 @@
         <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C37" t="s">
         <v>685</v>
@@ -4384,7 +4384,7 @@
         <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C38" t="s">
         <v>686</v>
@@ -4407,7 +4407,7 @@
         <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C39" t="s">
         <v>687</v>
@@ -4430,7 +4430,7 @@
         <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C40" t="s">
         <v>685</v>
@@ -4453,7 +4453,7 @@
         <v>35</v>
       </c>
       <c r="B41" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C41" t="s">
         <v>688</v>
@@ -4476,7 +4476,7 @@
         <v>36</v>
       </c>
       <c r="B42" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C42" t="s">
         <v>689</v>
@@ -4499,7 +4499,7 @@
         <v>37</v>
       </c>
       <c r="B43" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C43" t="s">
         <v>690</v>
@@ -4522,7 +4522,7 @@
         <v>38</v>
       </c>
       <c r="B44" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C44" t="s">
         <v>690</v>
@@ -4545,7 +4545,7 @@
         <v>39</v>
       </c>
       <c r="B45" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C45" t="s">
         <v>691</v>
@@ -4568,7 +4568,7 @@
         <v>39</v>
       </c>
       <c r="B46" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C46" t="s">
         <v>691</v>
@@ -4591,7 +4591,7 @@
         <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C47" t="s">
         <v>692</v>
@@ -4614,7 +4614,7 @@
         <v>41</v>
       </c>
       <c r="B48" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C48" t="s">
         <v>693</v>
@@ -4637,7 +4637,7 @@
         <v>42</v>
       </c>
       <c r="B49" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C49" t="s">
         <v>694</v>
@@ -4660,7 +4660,7 @@
         <v>43</v>
       </c>
       <c r="B50" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C50" t="s">
         <v>695</v>
@@ -4683,7 +4683,7 @@
         <v>44</v>
       </c>
       <c r="B51" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C51" t="s">
         <v>685</v>
@@ -4706,7 +4706,7 @@
         <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C52" t="s">
         <v>686</v>
@@ -4729,7 +4729,7 @@
         <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C53" t="s">
         <v>685</v>
@@ -4752,7 +4752,7 @@
         <v>47</v>
       </c>
       <c r="B54" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C54" t="s">
         <v>696</v>
@@ -4775,7 +4775,7 @@
         <v>30</v>
       </c>
       <c r="B55" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C55" t="s">
         <v>684</v>
@@ -4798,7 +4798,7 @@
         <v>31</v>
       </c>
       <c r="B56" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C56" t="s">
         <v>685</v>
@@ -4821,7 +4821,7 @@
         <v>32</v>
       </c>
       <c r="B57" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C57" t="s">
         <v>686</v>
@@ -4844,7 +4844,7 @@
         <v>33</v>
       </c>
       <c r="B58" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C58" t="s">
         <v>687</v>
@@ -4867,7 +4867,7 @@
         <v>34</v>
       </c>
       <c r="B59" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C59" t="s">
         <v>685</v>
@@ -4890,7 +4890,7 @@
         <v>35</v>
       </c>
       <c r="B60" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C60" t="s">
         <v>688</v>
@@ -4913,7 +4913,7 @@
         <v>36</v>
       </c>
       <c r="B61" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C61" t="s">
         <v>689</v>
@@ -4936,7 +4936,7 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C62" t="s">
         <v>690</v>
@@ -4959,7 +4959,7 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C63" t="s">
         <v>690</v>
@@ -4982,7 +4982,7 @@
         <v>39</v>
       </c>
       <c r="B64" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C64" t="s">
         <v>691</v>
@@ -5005,7 +5005,7 @@
         <v>39</v>
       </c>
       <c r="B65" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C65" t="s">
         <v>691</v>
@@ -5028,7 +5028,7 @@
         <v>40</v>
       </c>
       <c r="B66" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C66" t="s">
         <v>692</v>
@@ -5051,7 +5051,7 @@
         <v>41</v>
       </c>
       <c r="B67" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C67" t="s">
         <v>693</v>
@@ -5074,7 +5074,7 @@
         <v>42</v>
       </c>
       <c r="B68" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C68" t="s">
         <v>694</v>
@@ -5097,7 +5097,7 @@
         <v>43</v>
       </c>
       <c r="B69" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C69" t="s">
         <v>695</v>
@@ -5120,7 +5120,7 @@
         <v>44</v>
       </c>
       <c r="B70" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C70" t="s">
         <v>685</v>
@@ -5143,7 +5143,7 @@
         <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C71" t="s">
         <v>686</v>
@@ -5166,7 +5166,7 @@
         <v>46</v>
       </c>
       <c r="B72" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C72" t="s">
         <v>685</v>
@@ -5189,7 +5189,7 @@
         <v>47</v>
       </c>
       <c r="B73" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C73" t="s">
         <v>696</v>
@@ -5212,7 +5212,7 @@
         <v>48</v>
       </c>
       <c r="B74" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C74" t="s">
         <v>697</v>
@@ -5235,7 +5235,7 @@
         <v>48</v>
       </c>
       <c r="B75" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C75" t="s">
         <v>697</v>
@@ -5258,7 +5258,7 @@
         <v>49</v>
       </c>
       <c r="B76" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C76" t="s">
         <v>698</v>
@@ -5281,7 +5281,7 @@
         <v>50</v>
       </c>
       <c r="B77" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C77" t="s">
         <v>699</v>
@@ -5304,7 +5304,7 @@
         <v>51</v>
       </c>
       <c r="B78" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C78" t="s">
         <v>674</v>
@@ -5327,7 +5327,7 @@
         <v>52</v>
       </c>
       <c r="B79" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C79" t="s">
         <v>700</v>
@@ -5350,7 +5350,7 @@
         <v>51</v>
       </c>
       <c r="B80" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C80" t="s">
         <v>674</v>
@@ -5373,7 +5373,7 @@
         <v>52</v>
       </c>
       <c r="B81" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C81" t="s">
         <v>700</v>
@@ -5396,7 +5396,7 @@
         <v>53</v>
       </c>
       <c r="B82" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C82" t="s">
         <v>674</v>
@@ -5419,7 +5419,7 @@
         <v>54</v>
       </c>
       <c r="B83" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C83" t="s">
         <v>699</v>
@@ -5442,7 +5442,7 @@
         <v>55</v>
       </c>
       <c r="B84" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C84" t="s">
         <v>701</v>
@@ -5465,7 +5465,7 @@
         <v>56</v>
       </c>
       <c r="B85" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C85" t="s">
         <v>702</v>
@@ -5488,7 +5488,7 @@
         <v>57</v>
       </c>
       <c r="B86" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C86" t="s">
         <v>703</v>
@@ -5511,7 +5511,7 @@
         <v>58</v>
       </c>
       <c r="B87" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C87" t="s">
         <v>697</v>
@@ -5534,7 +5534,7 @@
         <v>59</v>
       </c>
       <c r="B88" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C88" t="s">
         <v>697</v>
@@ -5557,7 +5557,7 @@
         <v>60</v>
       </c>
       <c r="B89" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C89" t="s">
         <v>704</v>
@@ -5580,7 +5580,7 @@
         <v>61</v>
       </c>
       <c r="B90" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C90" t="s">
         <v>705</v>
@@ -5603,7 +5603,7 @@
         <v>61</v>
       </c>
       <c r="B91" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C91" t="s">
         <v>704</v>
@@ -5626,7 +5626,7 @@
         <v>61</v>
       </c>
       <c r="B92" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C92" t="s">
         <v>705</v>
@@ -5649,7 +5649,7 @@
         <v>61</v>
       </c>
       <c r="B93" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C93" t="s">
         <v>704</v>
@@ -5672,7 +5672,7 @@
         <v>62</v>
       </c>
       <c r="B94" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C94" t="s">
         <v>706</v>
@@ -5695,7 +5695,7 @@
         <v>63</v>
       </c>
       <c r="B95" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C95" t="s">
         <v>706</v>
@@ -5718,7 +5718,7 @@
         <v>64</v>
       </c>
       <c r="B96" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C96" t="s">
         <v>707</v>
@@ -5741,7 +5741,7 @@
         <v>65</v>
       </c>
       <c r="B97" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C97" t="s">
         <v>707</v>
@@ -5764,7 +5764,7 @@
         <v>66</v>
       </c>
       <c r="B98" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C98" t="s">
         <v>708</v>
@@ -5787,7 +5787,7 @@
         <v>67</v>
       </c>
       <c r="B99" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C99" t="s">
         <v>709</v>
@@ -5810,7 +5810,7 @@
         <v>68</v>
       </c>
       <c r="B100" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C100" t="s">
         <v>708</v>
@@ -5833,7 +5833,7 @@
         <v>67</v>
       </c>
       <c r="B101" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C101" t="s">
         <v>709</v>
@@ -5856,7 +5856,7 @@
         <v>68</v>
       </c>
       <c r="B102" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C102" t="s">
         <v>708</v>
@@ -5879,7 +5879,7 @@
         <v>69</v>
       </c>
       <c r="B103" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C103" t="s">
         <v>710</v>
@@ -5902,7 +5902,7 @@
         <v>70</v>
       </c>
       <c r="B104" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C104" t="s">
         <v>709</v>
@@ -5925,7 +5925,7 @@
         <v>71</v>
       </c>
       <c r="B105" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C105" t="s">
         <v>701</v>
@@ -5948,7 +5948,7 @@
         <v>72</v>
       </c>
       <c r="B106" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C106" t="s">
         <v>711</v>
@@ -5971,7 +5971,7 @@
         <v>72</v>
       </c>
       <c r="B107" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C107" t="s">
         <v>711</v>
@@ -5994,7 +5994,7 @@
         <v>73</v>
       </c>
       <c r="B108" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C108" t="s">
         <v>698</v>
@@ -6017,7 +6017,7 @@
         <v>74</v>
       </c>
       <c r="B109" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C109" t="s">
         <v>711</v>
@@ -6040,7 +6040,7 @@
         <v>75</v>
       </c>
       <c r="B110" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C110" t="s">
         <v>712</v>
@@ -6063,7 +6063,7 @@
         <v>76</v>
       </c>
       <c r="B111" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C111" t="s">
         <v>712</v>
@@ -6086,7 +6086,7 @@
         <v>76</v>
       </c>
       <c r="B112" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C112" t="s">
         <v>712</v>
@@ -6109,7 +6109,7 @@
         <v>77</v>
       </c>
       <c r="B113" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C113" t="s">
         <v>700</v>
@@ -6132,7 +6132,7 @@
         <v>78</v>
       </c>
       <c r="B114" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C114" t="s">
         <v>712</v>
@@ -6155,7 +6155,7 @@
         <v>77</v>
       </c>
       <c r="B115" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C115" t="s">
         <v>700</v>
@@ -6178,7 +6178,7 @@
         <v>78</v>
       </c>
       <c r="B116" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C116" t="s">
         <v>712</v>
@@ -6201,7 +6201,7 @@
         <v>79</v>
       </c>
       <c r="B117" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C117" t="s">
         <v>706</v>
@@ -6224,7 +6224,7 @@
         <v>80</v>
       </c>
       <c r="B118" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C118" t="s">
         <v>713</v>
@@ -6247,7 +6247,7 @@
         <v>81</v>
       </c>
       <c r="B119" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C119" t="s">
         <v>703</v>
@@ -6270,7 +6270,7 @@
         <v>82</v>
       </c>
       <c r="B120" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C120" t="s">
         <v>706</v>
@@ -6293,7 +6293,7 @@
         <v>79</v>
       </c>
       <c r="B121" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C121" t="s">
         <v>706</v>
@@ -6316,7 +6316,7 @@
         <v>83</v>
       </c>
       <c r="B122" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C122" t="s">
         <v>702</v>
@@ -6339,7 +6339,7 @@
         <v>84</v>
       </c>
       <c r="B123" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C123" t="s">
         <v>714</v>
@@ -6362,7 +6362,7 @@
         <v>85</v>
       </c>
       <c r="B124" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C124" t="s">
         <v>714</v>
@@ -6385,7 +6385,7 @@
         <v>86</v>
       </c>
       <c r="B125" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C125" t="s">
         <v>712</v>
@@ -6408,7 +6408,7 @@
         <v>87</v>
       </c>
       <c r="B126" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C126" t="s">
         <v>712</v>
@@ -6431,7 +6431,7 @@
         <v>88</v>
       </c>
       <c r="B127" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C127" t="s">
         <v>715</v>
@@ -6454,7 +6454,7 @@
         <v>89</v>
       </c>
       <c r="B128" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C128" t="s">
         <v>715</v>
@@ -6477,7 +6477,7 @@
         <v>90</v>
       </c>
       <c r="B129" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C129" t="s">
         <v>715</v>
@@ -6500,7 +6500,7 @@
         <v>91</v>
       </c>
       <c r="B130" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C130" t="s">
         <v>716</v>
@@ -6523,7 +6523,7 @@
         <v>92</v>
       </c>
       <c r="B131" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C131" t="s">
         <v>716</v>
@@ -6546,7 +6546,7 @@
         <v>93</v>
       </c>
       <c r="B132" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C132" t="s">
         <v>717</v>
@@ -6569,7 +6569,7 @@
         <v>94</v>
       </c>
       <c r="B133" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C133" t="s">
         <v>702</v>
@@ -6592,7 +6592,7 @@
         <v>95</v>
       </c>
       <c r="B134" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C134" t="s">
         <v>712</v>
@@ -6615,7 +6615,7 @@
         <v>96</v>
       </c>
       <c r="B135" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C135" t="s">
         <v>718</v>
@@ -6638,7 +6638,7 @@
         <v>97</v>
       </c>
       <c r="B136" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C136" t="s">
         <v>718</v>
@@ -6661,7 +6661,7 @@
         <v>98</v>
       </c>
       <c r="B137" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C137" t="s">
         <v>685</v>
@@ -6684,7 +6684,7 @@
         <v>99</v>
       </c>
       <c r="B138" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C138" t="s">
         <v>702</v>
@@ -6707,7 +6707,7 @@
         <v>100</v>
       </c>
       <c r="B139" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C139" t="s">
         <v>717</v>
@@ -6730,7 +6730,7 @@
         <v>101</v>
       </c>
       <c r="B140" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C140" t="s">
         <v>719</v>
@@ -6753,7 +6753,7 @@
         <v>102</v>
       </c>
       <c r="B141" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C141" t="s">
         <v>720</v>
@@ -6776,7 +6776,7 @@
         <v>103</v>
       </c>
       <c r="B142" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C142" t="s">
         <v>720</v>
@@ -6799,7 +6799,7 @@
         <v>104</v>
       </c>
       <c r="B143" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C143" t="s">
         <v>721</v>
@@ -6822,7 +6822,7 @@
         <v>105</v>
       </c>
       <c r="B144" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C144" t="s">
         <v>719</v>
@@ -6845,7 +6845,7 @@
         <v>106</v>
       </c>
       <c r="B145" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C145" t="s">
         <v>722</v>
@@ -6868,7 +6868,7 @@
         <v>107</v>
       </c>
       <c r="B146" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C146" t="s">
         <v>721</v>
@@ -6891,7 +6891,7 @@
         <v>108</v>
       </c>
       <c r="B147" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C147" t="s">
         <v>723</v>
@@ -6914,7 +6914,7 @@
         <v>107</v>
       </c>
       <c r="B148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C148" t="s">
         <v>721</v>
@@ -6937,7 +6937,7 @@
         <v>108</v>
       </c>
       <c r="B149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C149" t="s">
         <v>723</v>
@@ -6960,7 +6960,7 @@
         <v>109</v>
       </c>
       <c r="B150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C150" t="s">
         <v>724</v>
@@ -6983,7 +6983,7 @@
         <v>110</v>
       </c>
       <c r="B151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C151" t="s">
         <v>714</v>
@@ -7006,7 +7006,7 @@
         <v>111</v>
       </c>
       <c r="B152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C152" t="s">
         <v>721</v>
@@ -7029,7 +7029,7 @@
         <v>112</v>
       </c>
       <c r="B153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C153" t="s">
         <v>724</v>
@@ -7052,7 +7052,7 @@
         <v>113</v>
       </c>
       <c r="B154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C154" t="s">
         <v>723</v>
@@ -7075,7 +7075,7 @@
         <v>114</v>
       </c>
       <c r="B155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C155" t="s">
         <v>725</v>
@@ -7098,7 +7098,7 @@
         <v>114</v>
       </c>
       <c r="B156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C156" t="s">
         <v>725</v>
@@ -7121,7 +7121,7 @@
         <v>115</v>
       </c>
       <c r="B157" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C157" t="s">
         <v>726</v>
@@ -7144,7 +7144,7 @@
         <v>116</v>
       </c>
       <c r="B158" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C158" t="s">
         <v>723</v>
@@ -7167,7 +7167,7 @@
         <v>117</v>
       </c>
       <c r="B159" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C159" t="s">
         <v>685</v>
@@ -7190,7 +7190,7 @@
         <v>118</v>
       </c>
       <c r="B160" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C160" t="s">
         <v>724</v>
@@ -7213,7 +7213,7 @@
         <v>117</v>
       </c>
       <c r="B161" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C161" t="s">
         <v>724</v>
@@ -7236,7 +7236,7 @@
         <v>119</v>
       </c>
       <c r="B162" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C162" t="s">
         <v>714</v>
@@ -7259,7 +7259,7 @@
         <v>117</v>
       </c>
       <c r="B163" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C163" t="s">
         <v>685</v>
@@ -7282,7 +7282,7 @@
         <v>120</v>
       </c>
       <c r="B164" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C164" t="s">
         <v>727</v>
@@ -7305,7 +7305,7 @@
         <v>121</v>
       </c>
       <c r="B165" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C165" t="s">
         <v>725</v>
@@ -7328,7 +7328,7 @@
         <v>122</v>
       </c>
       <c r="B166" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C166" t="s">
         <v>728</v>
@@ -7351,7 +7351,7 @@
         <v>123</v>
       </c>
       <c r="B167" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C167" t="s">
         <v>729</v>
@@ -7374,7 +7374,7 @@
         <v>124</v>
       </c>
       <c r="B168" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C168" t="s">
         <v>725</v>
@@ -7397,7 +7397,7 @@
         <v>125</v>
       </c>
       <c r="B169" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C169" t="s">
         <v>725</v>
@@ -7420,7 +7420,7 @@
         <v>126</v>
       </c>
       <c r="B170" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C170" t="s">
         <v>730</v>
@@ -7443,7 +7443,7 @@
         <v>127</v>
       </c>
       <c r="B171" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C171" t="s">
         <v>731</v>
@@ -7466,7 +7466,7 @@
         <v>128</v>
       </c>
       <c r="B172" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C172" t="s">
         <v>732</v>
@@ -7489,7 +7489,7 @@
         <v>129</v>
       </c>
       <c r="B173" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C173" t="s">
         <v>731</v>
@@ -7512,7 +7512,7 @@
         <v>130</v>
       </c>
       <c r="B174" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C174" t="s">
         <v>726</v>
@@ -7535,7 +7535,7 @@
         <v>131</v>
       </c>
       <c r="B175" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C175" t="s">
         <v>730</v>
@@ -7558,7 +7558,7 @@
         <v>132</v>
       </c>
       <c r="B176" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C176" t="s">
         <v>726</v>
@@ -7581,7 +7581,7 @@
         <v>133</v>
       </c>
       <c r="B177" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C177" t="s">
         <v>685</v>
@@ -7604,7 +7604,7 @@
         <v>134</v>
       </c>
       <c r="B178" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C178" t="s">
         <v>724</v>
@@ -7627,7 +7627,7 @@
         <v>135</v>
       </c>
       <c r="B179" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C179" t="s">
         <v>699</v>
@@ -7650,7 +7650,7 @@
         <v>136</v>
       </c>
       <c r="B180" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C180" t="s">
         <v>733</v>
@@ -7673,7 +7673,7 @@
         <v>20</v>
       </c>
       <c r="B181" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C181" t="s">
         <v>734</v>
@@ -7696,7 +7696,7 @@
         <v>137</v>
       </c>
       <c r="B182" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C182" t="s">
         <v>735</v>
@@ -7719,7 +7719,7 @@
         <v>138</v>
       </c>
       <c r="B183" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C183" t="s">
         <v>736</v>
@@ -7742,7 +7742,7 @@
         <v>9</v>
       </c>
       <c r="B184" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C184" t="s">
         <v>737</v>
@@ -7765,7 +7765,7 @@
         <v>20</v>
       </c>
       <c r="B185" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C185" t="s">
         <v>734</v>
@@ -7788,7 +7788,7 @@
         <v>139</v>
       </c>
       <c r="B186" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C186" t="s">
         <v>676</v>
@@ -7811,7 +7811,7 @@
         <v>140</v>
       </c>
       <c r="B187" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C187" t="s">
         <v>738</v>
@@ -7834,7 +7834,7 @@
         <v>138</v>
       </c>
       <c r="B188" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C188" t="s">
         <v>736</v>
@@ -7857,7 +7857,7 @@
         <v>9</v>
       </c>
       <c r="B189" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C189" t="s">
         <v>737</v>
@@ -7880,7 +7880,7 @@
         <v>20</v>
       </c>
       <c r="B190" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C190" t="s">
         <v>734</v>
@@ -7903,7 +7903,7 @@
         <v>140</v>
       </c>
       <c r="B191" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C191" t="s">
         <v>738</v>
@@ -7926,7 +7926,7 @@
         <v>139</v>
       </c>
       <c r="B192" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C192" t="s">
         <v>675</v>
@@ -7949,7 +7949,7 @@
         <v>138</v>
       </c>
       <c r="B193" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C193" t="s">
         <v>736</v>
@@ -7972,7 +7972,7 @@
         <v>9</v>
       </c>
       <c r="B194" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C194" t="s">
         <v>737</v>
@@ -7995,7 +7995,7 @@
         <v>20</v>
       </c>
       <c r="B195" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C195" t="s">
         <v>734</v>
@@ -8018,7 +8018,7 @@
         <v>138</v>
       </c>
       <c r="B196" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C196" t="s">
         <v>736</v>
@@ -8041,7 +8041,7 @@
         <v>9</v>
       </c>
       <c r="B197" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C197" t="s">
         <v>737</v>
@@ -8064,7 +8064,7 @@
         <v>28</v>
       </c>
       <c r="B198" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C198" t="s">
         <v>734</v>
@@ -8087,7 +8087,7 @@
         <v>25</v>
       </c>
       <c r="B199" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C199" t="s">
         <v>734</v>
@@ -8110,7 +8110,7 @@
         <v>20</v>
       </c>
       <c r="B200" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C200" t="s">
         <v>683</v>
@@ -8133,7 +8133,7 @@
         <v>138</v>
       </c>
       <c r="B201" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C201" t="s">
         <v>739</v>
@@ -8156,7 +8156,7 @@
         <v>9</v>
       </c>
       <c r="B202" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C202" t="s">
         <v>740</v>
@@ -8179,7 +8179,7 @@
         <v>20</v>
       </c>
       <c r="B203" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C203" t="s">
         <v>683</v>
@@ -8202,7 +8202,7 @@
         <v>138</v>
       </c>
       <c r="B204" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C204" t="s">
         <v>739</v>
@@ -8225,7 +8225,7 @@
         <v>9</v>
       </c>
       <c r="B205" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C205" t="s">
         <v>740</v>
@@ -8248,7 +8248,7 @@
         <v>20</v>
       </c>
       <c r="B206" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C206" t="s">
         <v>683</v>
@@ -8271,7 +8271,7 @@
         <v>139</v>
       </c>
       <c r="B207" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C207" t="s">
         <v>741</v>
@@ -8294,7 +8294,7 @@
         <v>140</v>
       </c>
       <c r="B208" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C208" t="s">
         <v>742</v>
@@ -8317,7 +8317,7 @@
         <v>138</v>
       </c>
       <c r="B209" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C209" t="s">
         <v>739</v>
@@ -8340,7 +8340,7 @@
         <v>9</v>
       </c>
       <c r="B210" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C210" t="s">
         <v>740</v>
@@ -8363,7 +8363,7 @@
         <v>20</v>
       </c>
       <c r="B211" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C211" t="s">
         <v>683</v>
@@ -8386,7 +8386,7 @@
         <v>140</v>
       </c>
       <c r="B212" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C212" t="s">
         <v>742</v>
@@ -8409,7 +8409,7 @@
         <v>138</v>
       </c>
       <c r="B213" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C213" t="s">
         <v>739</v>
@@ -8432,7 +8432,7 @@
         <v>9</v>
       </c>
       <c r="B214" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C214" t="s">
         <v>740</v>
@@ -8455,7 +8455,7 @@
         <v>137</v>
       </c>
       <c r="B215" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C215" t="s">
         <v>735</v>
@@ -8478,7 +8478,7 @@
         <v>141</v>
       </c>
       <c r="B216" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C216" t="s">
         <v>706</v>
@@ -8501,7 +8501,7 @@
         <v>142</v>
       </c>
       <c r="B217" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C217" t="s">
         <v>743</v>
@@ -8524,7 +8524,7 @@
         <v>141</v>
       </c>
       <c r="B218" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C218" t="s">
         <v>706</v>
@@ -8547,7 +8547,7 @@
         <v>29</v>
       </c>
       <c r="B219" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C219" t="s">
         <v>734</v>
@@ -8570,7 +8570,7 @@
         <v>143</v>
       </c>
       <c r="B220" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C220" t="s">
         <v>744</v>
@@ -8593,7 +8593,7 @@
         <v>143</v>
       </c>
       <c r="B221" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C221" t="s">
         <v>745</v>
@@ -8616,7 +8616,7 @@
         <v>29</v>
       </c>
       <c r="B222" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C222" t="s">
         <v>734</v>
@@ -8639,7 +8639,7 @@
         <v>140</v>
       </c>
       <c r="B223" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C223" t="s">
         <v>746</v>
@@ -8662,7 +8662,7 @@
         <v>139</v>
       </c>
       <c r="B224" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C224" t="s">
         <v>747</v>
@@ -8685,7 +8685,7 @@
         <v>138</v>
       </c>
       <c r="B225" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C225" t="s">
         <v>747</v>
@@ -8708,7 +8708,7 @@
         <v>9</v>
       </c>
       <c r="B226" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C226" t="s">
         <v>742</v>
@@ -8731,7 +8731,7 @@
         <v>20</v>
       </c>
       <c r="B227" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C227" t="s">
         <v>748</v>
@@ -8754,7 +8754,7 @@
         <v>139</v>
       </c>
       <c r="B228" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C228" t="s">
         <v>747</v>
@@ -8777,7 +8777,7 @@
         <v>140</v>
       </c>
       <c r="B229" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C229" t="s">
         <v>740</v>
@@ -8800,7 +8800,7 @@
         <v>138</v>
       </c>
       <c r="B230" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C230" t="s">
         <v>747</v>
@@ -8823,7 +8823,7 @@
         <v>9</v>
       </c>
       <c r="B231" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C231" t="s">
         <v>742</v>
@@ -8846,7 +8846,7 @@
         <v>143</v>
       </c>
       <c r="B232" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C232" t="s">
         <v>744</v>
@@ -8869,7 +8869,7 @@
         <v>144</v>
       </c>
       <c r="B233" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C233" t="s">
         <v>703</v>
@@ -8892,7 +8892,7 @@
         <v>29</v>
       </c>
       <c r="B234" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C234" t="s">
         <v>734</v>
@@ -8915,7 +8915,7 @@
         <v>143</v>
       </c>
       <c r="B235" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C235" t="s">
         <v>743</v>
@@ -8938,7 +8938,7 @@
         <v>143</v>
       </c>
       <c r="B236" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C236" t="s">
         <v>744</v>
@@ -8961,7 +8961,7 @@
         <v>20</v>
       </c>
       <c r="B237" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C237" t="s">
         <v>734</v>
@@ -8984,7 +8984,7 @@
         <v>143</v>
       </c>
       <c r="B238" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C238" t="s">
         <v>744</v>
@@ -9007,7 +9007,7 @@
         <v>143</v>
       </c>
       <c r="B239" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C239" t="s">
         <v>745</v>
@@ -9030,7 +9030,7 @@
         <v>138</v>
       </c>
       <c r="B240" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C240" t="s">
         <v>736</v>
@@ -9053,7 +9053,7 @@
         <v>20</v>
       </c>
       <c r="B241" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C241" t="s">
         <v>734</v>
@@ -9076,7 +9076,7 @@
         <v>138</v>
       </c>
       <c r="B242" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C242" t="s">
         <v>736</v>
@@ -9099,7 +9099,7 @@
         <v>20</v>
       </c>
       <c r="B243" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C243" t="s">
         <v>734</v>
@@ -9122,7 +9122,7 @@
         <v>139</v>
       </c>
       <c r="B244" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C244" t="s">
         <v>747</v>
@@ -9145,7 +9145,7 @@
         <v>140</v>
       </c>
       <c r="B245" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C245" t="s">
         <v>742</v>
@@ -9168,7 +9168,7 @@
         <v>138</v>
       </c>
       <c r="B246" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C246" t="s">
         <v>736</v>
@@ -9191,7 +9191,7 @@
         <v>9</v>
       </c>
       <c r="B247" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C247" t="s">
         <v>738</v>
@@ -9214,7 +9214,7 @@
         <v>20</v>
       </c>
       <c r="B248" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C248" t="s">
         <v>734</v>
@@ -9237,7 +9237,7 @@
         <v>138</v>
       </c>
       <c r="B249" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C249" t="s">
         <v>736</v>
@@ -9260,7 +9260,7 @@
         <v>9</v>
       </c>
       <c r="B250" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C250" t="s">
         <v>738</v>
@@ -9283,7 +9283,7 @@
         <v>10</v>
       </c>
       <c r="B251" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C251" t="s">
         <v>746</v>
@@ -9306,7 +9306,7 @@
         <v>28</v>
       </c>
       <c r="B252" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C252" t="s">
         <v>734</v>
@@ -9329,7 +9329,7 @@
         <v>25</v>
       </c>
       <c r="B253" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C253" t="s">
         <v>734</v>
@@ -9352,7 +9352,7 @@
         <v>142</v>
       </c>
       <c r="B254" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C254" t="s">
         <v>743</v>
@@ -9375,7 +9375,7 @@
         <v>20</v>
       </c>
       <c r="B255" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C255" t="s">
         <v>742</v>
@@ -9398,7 +9398,7 @@
         <v>10</v>
       </c>
       <c r="B256" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C256" t="s">
         <v>746</v>
@@ -9421,7 +9421,7 @@
         <v>138</v>
       </c>
       <c r="B257" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C257" t="s">
         <v>749</v>
@@ -9444,7 +9444,7 @@
         <v>9</v>
       </c>
       <c r="B258" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C258" t="s">
         <v>742</v>
@@ -9467,7 +9467,7 @@
         <v>29</v>
       </c>
       <c r="B259" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C259" t="s">
         <v>742</v>
@@ -9490,7 +9490,7 @@
         <v>9</v>
       </c>
       <c r="B260" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C260" t="s">
         <v>742</v>
@@ -9513,7 +9513,7 @@
         <v>29</v>
       </c>
       <c r="B261" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C261" t="s">
         <v>683</v>
@@ -9536,7 +9536,7 @@
         <v>140</v>
       </c>
       <c r="B262" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C262" t="s">
         <v>746</v>
@@ -9559,7 +9559,7 @@
         <v>139</v>
       </c>
       <c r="B263" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C263" t="s">
         <v>676</v>
@@ -9582,7 +9582,7 @@
         <v>29</v>
       </c>
       <c r="B264" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C264" t="s">
         <v>678</v>
@@ -9605,7 +9605,7 @@
         <v>29</v>
       </c>
       <c r="B265" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C265" t="s">
         <v>678</v>
@@ -9628,7 +9628,7 @@
         <v>29</v>
       </c>
       <c r="B266" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C266" t="s">
         <v>742</v>
@@ -9651,7 +9651,7 @@
         <v>22</v>
       </c>
       <c r="B267" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C267" t="s">
         <v>679</v>
@@ -9674,7 +9674,7 @@
         <v>9</v>
       </c>
       <c r="B268" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C268" t="s">
         <v>742</v>
@@ -9697,7 +9697,7 @@
         <v>140</v>
       </c>
       <c r="B269" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C269" t="s">
         <v>746</v>
@@ -9720,7 +9720,7 @@
         <v>139</v>
       </c>
       <c r="B270" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C270" t="s">
         <v>675</v>
@@ -9743,7 +9743,7 @@
         <v>20</v>
       </c>
       <c r="B271" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C271" t="s">
         <v>742</v>
@@ -9766,7 +9766,7 @@
         <v>138</v>
       </c>
       <c r="B272" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C272" t="s">
         <v>749</v>
@@ -9789,7 +9789,7 @@
         <v>9</v>
       </c>
       <c r="B273" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C273" t="s">
         <v>742</v>
@@ -9812,7 +9812,7 @@
         <v>145</v>
       </c>
       <c r="B274" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C274" t="s">
         <v>742</v>
@@ -9835,7 +9835,7 @@
         <v>146</v>
       </c>
       <c r="B275" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C275" t="s">
         <v>750</v>
@@ -9858,7 +9858,7 @@
         <v>40</v>
       </c>
       <c r="B276" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C276" t="s">
         <v>685</v>
@@ -9881,7 +9881,7 @@
         <v>146</v>
       </c>
       <c r="B277" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C277" t="s">
         <v>750</v>
@@ -9904,7 +9904,7 @@
         <v>40</v>
       </c>
       <c r="B278" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C278" t="s">
         <v>685</v>
@@ -9927,7 +9927,7 @@
         <v>30</v>
       </c>
       <c r="B279" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C279" t="s">
         <v>675</v>
@@ -9950,7 +9950,7 @@
         <v>147</v>
       </c>
       <c r="B280" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C280" t="s">
         <v>751</v>
@@ -9973,7 +9973,7 @@
         <v>148</v>
       </c>
       <c r="B281" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C281" t="s">
         <v>752</v>
@@ -9996,7 +9996,7 @@
         <v>46</v>
       </c>
       <c r="B282" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C282" t="s">
         <v>753</v>
@@ -10019,7 +10019,7 @@
         <v>149</v>
       </c>
       <c r="B283" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C283" t="s">
         <v>712</v>
@@ -10042,7 +10042,7 @@
         <v>46</v>
       </c>
       <c r="B284" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C284" t="s">
         <v>753</v>
@@ -10065,7 +10065,7 @@
         <v>149</v>
       </c>
       <c r="B285" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C285" t="s">
         <v>712</v>
@@ -10088,7 +10088,7 @@
         <v>46</v>
       </c>
       <c r="B286" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C286" t="s">
         <v>675</v>
@@ -10111,7 +10111,7 @@
         <v>149</v>
       </c>
       <c r="B287" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C287" t="s">
         <v>754</v>
@@ -10134,7 +10134,7 @@
         <v>150</v>
       </c>
       <c r="B288" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C288" t="s">
         <v>755</v>
@@ -10157,7 +10157,7 @@
         <v>151</v>
       </c>
       <c r="B289" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C289" t="s">
         <v>685</v>
@@ -10180,7 +10180,7 @@
         <v>43</v>
       </c>
       <c r="B290" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C290" t="s">
         <v>721</v>
@@ -10203,7 +10203,7 @@
         <v>46</v>
       </c>
       <c r="B291" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C291" t="s">
         <v>675</v>
@@ -10226,7 +10226,7 @@
         <v>149</v>
       </c>
       <c r="B292" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C292" t="s">
         <v>754</v>
@@ -10249,7 +10249,7 @@
         <v>150</v>
       </c>
       <c r="B293" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C293" t="s">
         <v>755</v>
@@ -10272,7 +10272,7 @@
         <v>41</v>
       </c>
       <c r="B294" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C294" t="s">
         <v>756</v>
@@ -10295,7 +10295,7 @@
         <v>39</v>
       </c>
       <c r="B295" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C295" t="s">
         <v>756</v>
@@ -10318,7 +10318,7 @@
         <v>152</v>
       </c>
       <c r="B296" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C296" t="s">
         <v>685</v>
@@ -10341,7 +10341,7 @@
         <v>152</v>
       </c>
       <c r="B297" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C297" t="s">
         <v>685</v>
@@ -10364,7 +10364,7 @@
         <v>153</v>
       </c>
       <c r="B298" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C298" t="s">
         <v>757</v>
@@ -10387,7 +10387,7 @@
         <v>39</v>
       </c>
       <c r="B299" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C299" t="s">
         <v>756</v>
@@ -10410,7 +10410,7 @@
         <v>150</v>
       </c>
       <c r="B300" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C300" t="s">
         <v>757</v>
@@ -10433,7 +10433,7 @@
         <v>150</v>
       </c>
       <c r="B301" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C301" t="s">
         <v>708</v>
@@ -10456,7 +10456,7 @@
         <v>154</v>
       </c>
       <c r="B302" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C302" t="s">
         <v>742</v>
@@ -10479,7 +10479,7 @@
         <v>155</v>
       </c>
       <c r="B303" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C303" t="s">
         <v>742</v>
@@ -10502,7 +10502,7 @@
         <v>156</v>
       </c>
       <c r="B304" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C304" t="s">
         <v>706</v>
@@ -10525,7 +10525,7 @@
         <v>39</v>
       </c>
       <c r="B305" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C305" t="s">
         <v>758</v>
@@ -10548,7 +10548,7 @@
         <v>156</v>
       </c>
       <c r="B306" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C306" t="s">
         <v>706</v>
@@ -10571,7 +10571,7 @@
         <v>157</v>
       </c>
       <c r="B307" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C307" t="s">
         <v>759</v>
@@ -10594,7 +10594,7 @@
         <v>158</v>
       </c>
       <c r="B308" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C308" t="s">
         <v>742</v>
@@ -10617,7 +10617,7 @@
         <v>39</v>
       </c>
       <c r="B309" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C309" t="s">
         <v>758</v>
@@ -10640,7 +10640,7 @@
         <v>50</v>
       </c>
       <c r="B310" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C310" t="s">
         <v>717</v>
@@ -10663,7 +10663,7 @@
         <v>159</v>
       </c>
       <c r="B311" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C311" t="s">
         <v>760</v>
@@ -10686,7 +10686,7 @@
         <v>160</v>
       </c>
       <c r="B312" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C312" t="s">
         <v>761</v>
@@ -10709,7 +10709,7 @@
         <v>161</v>
       </c>
       <c r="B313" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C313" t="s">
         <v>761</v>
@@ -10732,7 +10732,7 @@
         <v>162</v>
       </c>
       <c r="B314" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C314" t="s">
         <v>751</v>
@@ -10755,7 +10755,7 @@
         <v>163</v>
       </c>
       <c r="B315" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C315" t="s">
         <v>762</v>
@@ -10778,7 +10778,7 @@
         <v>164</v>
       </c>
       <c r="B316" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C316" t="s">
         <v>763</v>
@@ -10801,7 +10801,7 @@
         <v>165</v>
       </c>
       <c r="B317" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C317" t="s">
         <v>755</v>
@@ -10824,7 +10824,7 @@
         <v>161</v>
       </c>
       <c r="B318" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C318" t="s">
         <v>761</v>
@@ -10847,7 +10847,7 @@
         <v>162</v>
       </c>
       <c r="B319" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C319" t="s">
         <v>751</v>
@@ -10870,7 +10870,7 @@
         <v>163</v>
       </c>
       <c r="B320" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C320" t="s">
         <v>762</v>
@@ -10893,7 +10893,7 @@
         <v>164</v>
       </c>
       <c r="B321" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C321" t="s">
         <v>763</v>
@@ -10916,7 +10916,7 @@
         <v>165</v>
       </c>
       <c r="B322" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C322" t="s">
         <v>755</v>
@@ -10939,13 +10939,13 @@
         <v>166</v>
       </c>
       <c r="B323" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="C323" t="s">
-        <v>711</v>
+        <v>760</v>
       </c>
       <c r="D323" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E323" t="s">
         <v>796</v>
@@ -10962,7 +10962,7 @@
         <v>167</v>
       </c>
       <c r="B324" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C324" t="s">
         <v>761</v>
@@ -10985,7 +10985,7 @@
         <v>168</v>
       </c>
       <c r="B325" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C325" t="s">
         <v>764</v>
@@ -11008,7 +11008,7 @@
         <v>159</v>
       </c>
       <c r="B326" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C326" t="s">
         <v>760</v>
@@ -11031,7 +11031,7 @@
         <v>160</v>
       </c>
       <c r="B327" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C327" t="s">
         <v>702</v>
@@ -11054,7 +11054,7 @@
         <v>81</v>
       </c>
       <c r="B328" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C328" t="s">
         <v>703</v>
@@ -11077,7 +11077,7 @@
         <v>162</v>
       </c>
       <c r="B329" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C329" t="s">
         <v>760</v>
@@ -11100,7 +11100,7 @@
         <v>81</v>
       </c>
       <c r="B330" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C330" t="s">
         <v>703</v>
@@ -11123,7 +11123,7 @@
         <v>162</v>
       </c>
       <c r="B331" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C331" t="s">
         <v>760</v>
@@ -11146,13 +11146,13 @@
         <v>166</v>
       </c>
       <c r="B332" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="C332" t="s">
-        <v>711</v>
+        <v>760</v>
       </c>
       <c r="D332" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E332" t="s">
         <v>798</v>
@@ -11169,7 +11169,7 @@
         <v>159</v>
       </c>
       <c r="B333" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C333" t="s">
         <v>760</v>
@@ -11192,7 +11192,7 @@
         <v>160</v>
       </c>
       <c r="B334" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C334" t="s">
         <v>723</v>
@@ -11215,7 +11215,7 @@
         <v>169</v>
       </c>
       <c r="B335" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C335" t="s">
         <v>703</v>
@@ -11261,7 +11261,7 @@
         <v>162</v>
       </c>
       <c r="B337" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C337" t="s">
         <v>760</v>
@@ -11307,7 +11307,7 @@
         <v>162</v>
       </c>
       <c r="B339" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C339" t="s">
         <v>760</v>
@@ -11399,7 +11399,7 @@
         <v>50</v>
       </c>
       <c r="B343" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C343" t="s">
         <v>762</v>
@@ -11445,7 +11445,7 @@
         <v>161</v>
       </c>
       <c r="B345" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C345" t="s">
         <v>761</v>
@@ -11468,7 +11468,7 @@
         <v>165</v>
       </c>
       <c r="B346" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C346" t="s">
         <v>755</v>
@@ -11491,7 +11491,7 @@
         <v>164</v>
       </c>
       <c r="B347" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C347" t="s">
         <v>711</v>
@@ -11514,7 +11514,7 @@
         <v>161</v>
       </c>
       <c r="B348" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C348" t="s">
         <v>761</v>
@@ -11537,7 +11537,7 @@
         <v>165</v>
       </c>
       <c r="B349" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C349" t="s">
         <v>755</v>
@@ -11560,7 +11560,7 @@
         <v>164</v>
       </c>
       <c r="B350" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C350" t="s">
         <v>711</v>
@@ -11606,7 +11606,7 @@
         <v>50</v>
       </c>
       <c r="B352" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C352" t="s">
         <v>762</v>
@@ -11629,7 +11629,7 @@
         <v>50</v>
       </c>
       <c r="B353" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C353" t="s">
         <v>699</v>
@@ -14435,7 +14435,7 @@
         <v>208</v>
       </c>
       <c r="B475" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C475" t="s">
         <v>729</v>
@@ -14458,7 +14458,7 @@
         <v>209</v>
       </c>
       <c r="B476" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C476" t="s">
         <v>729</v>
@@ -14504,7 +14504,7 @@
         <v>211</v>
       </c>
       <c r="B478" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C478" t="s">
         <v>718</v>
@@ -14550,7 +14550,7 @@
         <v>213</v>
       </c>
       <c r="B480" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C480" t="s">
         <v>712</v>
@@ -14573,7 +14573,7 @@
         <v>213</v>
       </c>
       <c r="B481" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C481" t="s">
         <v>712</v>
@@ -14596,7 +14596,7 @@
         <v>211</v>
       </c>
       <c r="B482" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C482" t="s">
         <v>718</v>
@@ -14711,7 +14711,7 @@
         <v>216</v>
       </c>
       <c r="B487" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C487" t="s">
         <v>718</v>
@@ -14734,7 +14734,7 @@
         <v>217</v>
       </c>
       <c r="B488" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C488" t="s">
         <v>742</v>
@@ -14757,7 +14757,7 @@
         <v>217</v>
       </c>
       <c r="B489" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C489" t="s">
         <v>742</v>
@@ -14849,7 +14849,7 @@
         <v>219</v>
       </c>
       <c r="B493" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C493" t="s">
         <v>731</v>
@@ -14872,7 +14872,7 @@
         <v>220</v>
       </c>
       <c r="B494" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C494" t="s">
         <v>727</v>
@@ -14895,7 +14895,7 @@
         <v>221</v>
       </c>
       <c r="B495" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C495" t="s">
         <v>731</v>
@@ -14918,7 +14918,7 @@
         <v>222</v>
       </c>
       <c r="B496" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C496" t="s">
         <v>727</v>
@@ -14964,7 +14964,7 @@
         <v>208</v>
       </c>
       <c r="B498" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C498" t="s">
         <v>729</v>
@@ -14987,7 +14987,7 @@
         <v>209</v>
       </c>
       <c r="B499" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C499" t="s">
         <v>729</v>
@@ -15056,7 +15056,7 @@
         <v>224</v>
       </c>
       <c r="B502" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C502" t="s">
         <v>727</v>
@@ -15079,7 +15079,7 @@
         <v>225</v>
       </c>
       <c r="B503" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C503" t="s">
         <v>732</v>
@@ -15102,7 +15102,7 @@
         <v>226</v>
       </c>
       <c r="B504" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C504" t="s">
         <v>727</v>
@@ -15125,7 +15125,7 @@
         <v>227</v>
       </c>
       <c r="B505" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C505" t="s">
         <v>732</v>
@@ -15355,7 +15355,7 @@
         <v>119</v>
       </c>
       <c r="B515" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C515" t="s">
         <v>714</v>
@@ -15835,7 +15835,7 @@
     </row>
     <row r="536" spans="1:7">
       <c r="A536" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B536" t="s">
         <v>615</v>
@@ -15858,7 +15858,7 @@
     </row>
     <row r="537" spans="1:7">
       <c r="A537" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B537" t="s">
         <v>616</v>
@@ -15881,7 +15881,7 @@
     </row>
     <row r="538" spans="1:7">
       <c r="A538" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B538" t="s">
         <v>617</v>
@@ -15904,7 +15904,7 @@
     </row>
     <row r="539" spans="1:7">
       <c r="A539" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B539" t="s">
         <v>618</v>
@@ -15973,7 +15973,7 @@
     </row>
     <row r="542" spans="1:7">
       <c r="A542" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B542" t="s">
         <v>621</v>
@@ -15996,7 +15996,7 @@
     </row>
     <row r="543" spans="1:7">
       <c r="A543" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B543" t="s">
         <v>622</v>
@@ -16019,7 +16019,7 @@
     </row>
     <row r="544" spans="1:7">
       <c r="A544" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B544" t="s">
         <v>623</v>
@@ -16042,7 +16042,7 @@
     </row>
     <row r="545" spans="1:7">
       <c r="A545" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B545" t="s">
         <v>624</v>
@@ -16065,7 +16065,7 @@
     </row>
     <row r="546" spans="1:7">
       <c r="A546" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B546" t="s">
         <v>625</v>
@@ -16088,7 +16088,7 @@
     </row>
     <row r="547" spans="1:7">
       <c r="A547" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B547" t="s">
         <v>626</v>
@@ -16111,7 +16111,7 @@
     </row>
     <row r="548" spans="1:7">
       <c r="A548" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B548" t="s">
         <v>622</v>
@@ -16134,7 +16134,7 @@
     </row>
     <row r="549" spans="1:7">
       <c r="A549" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B549" t="s">
         <v>623</v>
@@ -16157,7 +16157,7 @@
     </row>
     <row r="550" spans="1:7">
       <c r="A550" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B550" t="s">
         <v>627</v>
@@ -16180,7 +16180,7 @@
     </row>
     <row r="551" spans="1:7">
       <c r="A551" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B551" t="s">
         <v>628</v>
@@ -16203,7 +16203,7 @@
     </row>
     <row r="552" spans="1:7">
       <c r="A552" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B552" t="s">
         <v>629</v>
@@ -16226,10 +16226,10 @@
     </row>
     <row r="553" spans="1:7">
       <c r="A553" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B553" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C553" t="s">
         <v>767</v>
@@ -16249,7 +16249,7 @@
     </row>
     <row r="554" spans="1:7">
       <c r="A554" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B554" t="s">
         <v>630</v>
@@ -16272,7 +16272,7 @@
     </row>
     <row r="555" spans="1:7">
       <c r="A555" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B555" t="s">
         <v>631</v>
@@ -16295,7 +16295,7 @@
     </row>
     <row r="556" spans="1:7">
       <c r="A556" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B556" t="s">
         <v>631</v>
@@ -16321,7 +16321,7 @@
         <v>119</v>
       </c>
       <c r="B557" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C557" t="s">
         <v>714</v>
@@ -16367,7 +16367,7 @@
         <v>208</v>
       </c>
       <c r="B559" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C559" t="s">
         <v>729</v>
@@ -16390,7 +16390,7 @@
         <v>209</v>
       </c>
       <c r="B560" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C560" t="s">
         <v>729</v>
@@ -16433,7 +16433,7 @@
     </row>
     <row r="562" spans="1:7">
       <c r="A562" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B562" t="s">
         <v>634</v>
@@ -16456,7 +16456,7 @@
     </row>
     <row r="563" spans="1:7">
       <c r="A563" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B563" t="s">
         <v>635</v>
@@ -16479,10 +16479,10 @@
     </row>
     <row r="564" spans="1:7">
       <c r="A564" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B564" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C564" t="s">
         <v>768</v>
@@ -16502,10 +16502,10 @@
     </row>
     <row r="565" spans="1:7">
       <c r="A565" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B565" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C565" t="s">
         <v>768</v>
@@ -16525,7 +16525,7 @@
     </row>
     <row r="566" spans="1:7">
       <c r="A566" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B566" t="s">
         <v>636</v>
@@ -16548,7 +16548,7 @@
     </row>
     <row r="567" spans="1:7">
       <c r="A567" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B567" t="s">
         <v>636</v>
@@ -16571,7 +16571,7 @@
     </row>
     <row r="568" spans="1:7">
       <c r="A568" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B568" t="s">
         <v>577</v>
@@ -16594,7 +16594,7 @@
     </row>
     <row r="569" spans="1:7">
       <c r="A569" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B569" t="s">
         <v>577</v>
@@ -16617,10 +16617,10 @@
     </row>
     <row r="570" spans="1:7">
       <c r="A570" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B570" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C570" t="s">
         <v>728</v>
@@ -16640,7 +16640,7 @@
     </row>
     <row r="571" spans="1:7">
       <c r="A571" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B571" t="s">
         <v>637</v>
@@ -16686,7 +16686,7 @@
     </row>
     <row r="573" spans="1:7">
       <c r="A573" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B573" t="s">
         <v>639</v>
@@ -16709,7 +16709,7 @@
     </row>
     <row r="574" spans="1:7">
       <c r="A574" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B574" t="s">
         <v>640</v>
@@ -16732,7 +16732,7 @@
     </row>
     <row r="575" spans="1:7">
       <c r="A575" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B575" t="s">
         <v>641</v>
@@ -16847,7 +16847,7 @@
     </row>
     <row r="580" spans="1:7">
       <c r="A580" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B580" t="s">
         <v>644</v>
@@ -16962,7 +16962,7 @@
     </row>
     <row r="585" spans="1:7">
       <c r="A585" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B585" t="s">
         <v>646</v>
@@ -16985,7 +16985,7 @@
     </row>
     <row r="586" spans="1:7">
       <c r="A586" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B586" t="s">
         <v>647</v>
@@ -17008,7 +17008,7 @@
     </row>
     <row r="587" spans="1:7">
       <c r="A587" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B587" t="s">
         <v>646</v>
@@ -17031,7 +17031,7 @@
     </row>
     <row r="588" spans="1:7">
       <c r="A588" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B588" t="s">
         <v>647</v>
@@ -17054,7 +17054,7 @@
     </row>
     <row r="589" spans="1:7">
       <c r="A589" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B589" t="s">
         <v>648</v>
@@ -17100,7 +17100,7 @@
     </row>
     <row r="591" spans="1:7">
       <c r="A591" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B591" t="s">
         <v>648</v>
@@ -17123,7 +17123,7 @@
     </row>
     <row r="592" spans="1:7">
       <c r="A592" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B592" t="s">
         <v>646</v>
@@ -17146,7 +17146,7 @@
     </row>
     <row r="593" spans="1:7">
       <c r="A593" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B593" t="s">
         <v>647</v>
@@ -17169,7 +17169,7 @@
     </row>
     <row r="594" spans="1:7">
       <c r="A594" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B594" t="s">
         <v>648</v>
@@ -17192,7 +17192,7 @@
     </row>
     <row r="595" spans="1:7">
       <c r="A595" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B595" t="s">
         <v>646</v>
@@ -17215,7 +17215,7 @@
     </row>
     <row r="596" spans="1:7">
       <c r="A596" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B596" t="s">
         <v>647</v>
@@ -17238,7 +17238,7 @@
     </row>
     <row r="597" spans="1:7">
       <c r="A597" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B597" t="s">
         <v>648</v>
@@ -17307,7 +17307,7 @@
     </row>
     <row r="600" spans="1:7">
       <c r="A600" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B600" t="s">
         <v>651</v>
@@ -17330,7 +17330,7 @@
     </row>
     <row r="601" spans="1:7">
       <c r="A601" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B601" t="s">
         <v>648</v>
@@ -17353,7 +17353,7 @@
     </row>
     <row r="602" spans="1:7">
       <c r="A602" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B602" t="s">
         <v>646</v>
@@ -17376,7 +17376,7 @@
     </row>
     <row r="603" spans="1:7">
       <c r="A603" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B603" t="s">
         <v>651</v>
@@ -17399,7 +17399,7 @@
     </row>
     <row r="604" spans="1:7">
       <c r="A604" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B604" t="s">
         <v>648</v>
@@ -17422,7 +17422,7 @@
     </row>
     <row r="605" spans="1:7">
       <c r="A605" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B605" t="s">
         <v>646</v>
@@ -17468,7 +17468,7 @@
     </row>
     <row r="607" spans="1:7">
       <c r="A607" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B607" t="s">
         <v>651</v>
@@ -17514,7 +17514,7 @@
     </row>
     <row r="609" spans="1:7">
       <c r="A609" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B609" t="s">
         <v>653</v>
@@ -17560,7 +17560,7 @@
     </row>
     <row r="611" spans="1:7">
       <c r="A611" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B611" t="s">
         <v>644</v>
@@ -17629,7 +17629,7 @@
     </row>
     <row r="614" spans="1:7">
       <c r="A614" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B614" t="s">
         <v>644</v>
@@ -17744,7 +17744,7 @@
     </row>
     <row r="619" spans="1:7">
       <c r="A619" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B619" t="s">
         <v>651</v>
@@ -17951,7 +17951,7 @@
     </row>
     <row r="628" spans="1:7">
       <c r="A628" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B628" t="s">
         <v>657</v>
@@ -17974,7 +17974,7 @@
     </row>
     <row r="629" spans="1:7">
       <c r="A629" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B629" t="s">
         <v>658</v>
@@ -17997,7 +17997,7 @@
     </row>
     <row r="630" spans="1:7">
       <c r="A630" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B630" t="s">
         <v>659</v>
@@ -18020,7 +18020,7 @@
     </row>
     <row r="631" spans="1:7">
       <c r="A631" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B631" t="s">
         <v>660</v>
@@ -18089,7 +18089,7 @@
     </row>
     <row r="634" spans="1:7">
       <c r="A634" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B634" t="s">
         <v>663</v>
@@ -18112,7 +18112,7 @@
     </row>
     <row r="635" spans="1:7">
       <c r="A635" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B635" t="s">
         <v>664</v>
@@ -18135,7 +18135,7 @@
     </row>
     <row r="636" spans="1:7">
       <c r="A636" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B636" t="s">
         <v>665</v>
@@ -18158,7 +18158,7 @@
     </row>
     <row r="637" spans="1:7">
       <c r="A637" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B637" t="s">
         <v>665</v>
@@ -18181,7 +18181,7 @@
     </row>
     <row r="638" spans="1:7">
       <c r="A638" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B638" t="s">
         <v>666</v>
@@ -18227,7 +18227,7 @@
     </row>
     <row r="640" spans="1:7">
       <c r="A640" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B640" t="s">
         <v>668</v>
@@ -18273,7 +18273,7 @@
     </row>
     <row r="642" spans="1:7">
       <c r="A642" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B642" t="s">
         <v>669</v>
@@ -18319,7 +18319,7 @@
     </row>
     <row r="644" spans="1:7">
       <c r="A644" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B644" t="s">
         <v>669</v>
@@ -18365,7 +18365,7 @@
     </row>
     <row r="646" spans="1:7">
       <c r="A646" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B646" t="s">
         <v>671</v>
@@ -18434,7 +18434,7 @@
     </row>
     <row r="649" spans="1:7">
       <c r="A649" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B649" t="s">
         <v>671</v>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15780" windowHeight="7620"/>
+    <workbookView windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$636</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -14195,7 +14198,7 @@
         <v>48</v>
       </c>
       <c r="F441" t="s">
-        <v>57</v>
+        <v>460</v>
       </c>
       <c r="G441" t="s">
         <v>742</v>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -4,14 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView windowWidth="15780" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$640</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -2876,22 +2873,22 @@
     <t>Cours-ENF1-MCIL2</t>
   </si>
   <si>
+    <t>TD-Électronique de puissance-G1</t>
+  </si>
+  <si>
     <t>MCIL3</t>
   </si>
   <si>
-    <t>TD-Électronique de puissance-G1</t>
-  </si>
-  <si>
     <t>Cours-Métrologie en haute tension</t>
   </si>
   <si>
     <t>Cours-MHT-MCIL3</t>
   </si>
   <si>
+    <t>TD-Électronique de puissance-G2</t>
+  </si>
+  <si>
     <t>TD-Systèmes Asservis-G3</t>
-  </si>
-  <si>
-    <t>TD-Électronique de puissance-G2</t>
   </si>
   <si>
     <t>Cours-EAD-Outils de simulation numérique 1</t>
@@ -17996,13 +17993,13 @@
     </row>
     <row r="612" spans="1:7">
       <c r="A612" t="s">
-        <v>568</v>
+        <v>948</v>
       </c>
       <c r="B612" t="s">
         <v>16</v>
       </c>
       <c r="C612" t="s">
-        <v>219</v>
+        <v>356</v>
       </c>
       <c r="D612" t="s">
         <v>10</v>
@@ -18011,21 +18008,21 @@
         <v>11</v>
       </c>
       <c r="F612" t="s">
-        <v>476</v>
+        <v>46</v>
       </c>
       <c r="G612" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="613" spans="1:7">
       <c r="A613" t="s">
-        <v>949</v>
+        <v>568</v>
       </c>
       <c r="B613" t="s">
         <v>16</v>
       </c>
       <c r="C613" t="s">
-        <v>356</v>
+        <v>219</v>
       </c>
       <c r="D613" t="s">
         <v>10</v>
@@ -18034,10 +18031,10 @@
         <v>11</v>
       </c>
       <c r="F613" t="s">
-        <v>46</v>
+        <v>476</v>
       </c>
       <c r="G613" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="614" spans="1:7">
@@ -18060,7 +18057,7 @@
         <v>46</v>
       </c>
       <c r="G614" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="615" spans="1:7">
@@ -18083,7 +18080,7 @@
         <v>46</v>
       </c>
       <c r="G615" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="616" spans="1:7">
@@ -18103,10 +18100,10 @@
         <v>11</v>
       </c>
       <c r="F616" t="s">
-        <v>46</v>
+        <v>476</v>
       </c>
       <c r="G616" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="617" spans="1:7">
@@ -18117,7 +18114,7 @@
         <v>16</v>
       </c>
       <c r="C617" t="s">
-        <v>219</v>
+        <v>356</v>
       </c>
       <c r="D617" t="s">
         <v>26</v>
@@ -18126,10 +18123,10 @@
         <v>11</v>
       </c>
       <c r="F617" t="s">
-        <v>476</v>
+        <v>46</v>
       </c>
       <c r="G617" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="618" spans="1:7">
@@ -18140,7 +18137,7 @@
         <v>16</v>
       </c>
       <c r="C618" t="s">
-        <v>356</v>
+        <v>219</v>
       </c>
       <c r="D618" t="s">
         <v>26</v>
@@ -18149,10 +18146,10 @@
         <v>11</v>
       </c>
       <c r="F618" t="s">
-        <v>46</v>
+        <v>476</v>
       </c>
       <c r="G618" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="619" spans="1:7">
@@ -18175,18 +18172,18 @@
         <v>409</v>
       </c>
       <c r="G619" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="620" spans="1:7">
       <c r="A620" t="s">
-        <v>557</v>
+        <v>956</v>
       </c>
       <c r="B620" t="s">
         <v>16</v>
       </c>
       <c r="C620" t="s">
-        <v>219</v>
+        <v>356</v>
       </c>
       <c r="D620" t="s">
         <v>10</v>
@@ -18195,21 +18192,21 @@
         <v>51</v>
       </c>
       <c r="F620" t="s">
-        <v>476</v>
+        <v>46</v>
       </c>
       <c r="G620" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="621" spans="1:7">
       <c r="A621" t="s">
-        <v>956</v>
+        <v>557</v>
       </c>
       <c r="B621" t="s">
         <v>16</v>
       </c>
       <c r="C621" t="s">
-        <v>356</v>
+        <v>219</v>
       </c>
       <c r="D621" t="s">
         <v>10</v>
@@ -18218,10 +18215,10 @@
         <v>51</v>
       </c>
       <c r="F621" t="s">
-        <v>46</v>
+        <v>476</v>
       </c>
       <c r="G621" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="622" spans="1:7">
@@ -18244,7 +18241,7 @@
         <v>46</v>
       </c>
       <c r="G622" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="623" spans="1:7">
@@ -18267,7 +18264,7 @@
         <v>46</v>
       </c>
       <c r="G623" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="624" spans="1:7">
@@ -18290,7 +18287,7 @@
         <v>46</v>
       </c>
       <c r="G624" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="625" spans="1:7">
@@ -18313,7 +18310,7 @@
         <v>46</v>
       </c>
       <c r="G625" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="626" spans="1:7">
@@ -18336,7 +18333,7 @@
         <v>185</v>
       </c>
       <c r="G626" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="627" spans="1:7">
@@ -18359,7 +18356,7 @@
         <v>963</v>
       </c>
       <c r="G627" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="628" spans="1:7">
@@ -18382,7 +18379,7 @@
         <v>963</v>
       </c>
       <c r="G628" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="629" spans="1:7">
@@ -18405,7 +18402,7 @@
         <v>46</v>
       </c>
       <c r="G629" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="630" spans="1:7">
@@ -18428,7 +18425,7 @@
         <v>46</v>
       </c>
       <c r="G630" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="631" spans="1:7">
@@ -18451,7 +18448,7 @@
         <v>185</v>
       </c>
       <c r="G631" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="632" spans="1:7">
@@ -18474,7 +18471,7 @@
         <v>970</v>
       </c>
       <c r="G632" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="633" spans="1:7">
@@ -18497,7 +18494,7 @@
         <v>185</v>
       </c>
       <c r="G633" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="634" spans="1:7">
@@ -18520,7 +18517,7 @@
         <v>973</v>
       </c>
       <c r="G634" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="635" spans="1:7">
@@ -18543,7 +18540,7 @@
         <v>46</v>
       </c>
       <c r="G635" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="636" spans="1:7">
@@ -18566,7 +18563,7 @@
         <v>973</v>
       </c>
       <c r="G636" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="637" spans="1:7">
@@ -18589,7 +18586,7 @@
         <v>46</v>
       </c>
       <c r="G637" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="638" spans="1:7">
@@ -18612,7 +18609,7 @@
         <v>185</v>
       </c>
       <c r="G638" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="639" spans="1:7">
@@ -18635,7 +18632,7 @@
         <v>978</v>
       </c>
       <c r="G639" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="640" spans="1:7">
@@ -18658,13 +18655,10 @@
         <v>185</v>
       </c>
       <c r="G640" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G640" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7020"/>
+    <workbookView windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4487" uniqueCount="971">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4487" uniqueCount="968">
   <si>
     <t>Enseignements</t>
   </si>
@@ -563,7 +563,7 @@
     <t>TD-Automates programmables industriels PLC</t>
   </si>
   <si>
-    <t>Cours-Théorie de champ Electromagnétique</t>
+    <t>Cours-Théorie de champ électromagnétique</t>
   </si>
   <si>
     <t>TILMATINE AMAR</t>
@@ -629,7 +629,7 @@
     <t>Cours- Production de l'énergie électrique</t>
   </si>
   <si>
-    <t>TD-Théorie de champ</t>
+    <t>TD-Théorie de champ Electromagnétique</t>
   </si>
   <si>
     <t>ZIANI DJAMEL</t>
@@ -1682,15 +1682,15 @@
     <t>Cours-Réseaux électriques</t>
   </si>
   <si>
+    <t>Cours-Systèmes Asservis</t>
+  </si>
+  <si>
+    <t>Cours-SA-3ELT</t>
+  </si>
+  <si>
     <t>A12</t>
   </si>
   <si>
-    <t>Cours-Systèmes Asservis</t>
-  </si>
-  <si>
-    <t>Cours-SA-3ELT</t>
-  </si>
-  <si>
     <t>Cours-EAD-Logiciels de Simulation</t>
   </si>
   <si>
@@ -1706,6 +1706,12 @@
     <t>Salle 08</t>
   </si>
   <si>
+    <t>Cours-Théorie du champ électromagnétique</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
     <t>TD-Théorie du champ électromagnétique-G1</t>
   </si>
   <si>
@@ -1745,9 +1751,6 @@
     <t>Cours-C &amp;M-3ELT</t>
   </si>
   <si>
-    <t>A1</t>
-  </si>
-  <si>
     <t>Labo Réseaux SG11</t>
   </si>
   <si>
@@ -1766,18 +1769,12 @@
     <t>Labo ELN-P SG11</t>
   </si>
   <si>
-    <t>Cours-Shémas et Appareillage électrique</t>
+    <t>Cours-Schémas et Appareillage électrique</t>
   </si>
   <si>
     <t>Cours-S &amp; A</t>
   </si>
   <si>
-    <t>Cours-Théorie du champ Électromagnétique</t>
-  </si>
-  <si>
-    <t>Cours-Tc-3ELT</t>
-  </si>
-  <si>
     <t>Cours-Conception des Systèmes électriques</t>
   </si>
   <si>
@@ -1796,9 +1793,6 @@
     <t>Labo Mesures N°10 ELN SG22 &amp; SG31 &amp; SG32</t>
   </si>
   <si>
-    <t>TP-Shémas et Appareillage électrique</t>
-  </si>
-  <si>
     <t>Labo Shémas SG32 &amp; SG22/SG31</t>
   </si>
   <si>
@@ -2885,16 +2879,13 @@
     <t>Cours-Introdution à la haute tension</t>
   </si>
   <si>
-    <t>Cours-Shémas électriques</t>
-  </si>
-  <si>
-    <t>Cours-Théorie du champ électromagnétique</t>
+    <t>Cours-Schémas électriques</t>
+  </si>
+  <si>
+    <t>TD-Modélisation des Réseaux électriques-G1</t>
   </si>
   <si>
     <t>TD-Théorie du champ électromagnétique-G3</t>
-  </si>
-  <si>
-    <t>TD-Modélisation des Réseaux électriques-G1</t>
   </si>
   <si>
     <t>TP-Schémas électriques-SG11/SG21/SG31</t>
@@ -3913,12 +3904,6 @@
   <sheetPr/>
   <dimension ref="A1:G641"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
-  <cols>
-    <col min="1" max="1" width="60.8571428571429" customWidth="1"/>
-    <col min="3" max="3" width="19.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="14.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="14.1428571428571" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
@@ -11397,13 +11382,13 @@
     </row>
     <row r="326" spans="1:7">
       <c r="A326" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="B326" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="C326" t="s">
-        <v>184</v>
+        <v>498</v>
       </c>
       <c r="D326" t="s">
         <v>40</v>
@@ -11412,7 +11397,7 @@
         <v>11</v>
       </c>
       <c r="F326" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="G326" t="s">
         <v>528</v>
@@ -11420,13 +11405,13 @@
     </row>
     <row r="327" spans="1:7">
       <c r="A327" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="B327" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="C327" t="s">
-        <v>498</v>
+        <v>184</v>
       </c>
       <c r="D327" t="s">
         <v>40</v>
@@ -11435,7 +11420,7 @@
         <v>11</v>
       </c>
       <c r="F327" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="G327" t="s">
         <v>528</v>
@@ -11458,7 +11443,7 @@
         <v>11</v>
       </c>
       <c r="F328" t="s">
-        <v>550</v>
+        <v>471</v>
       </c>
       <c r="G328" t="s">
         <v>528</v>
@@ -11466,10 +11451,10 @@
     </row>
     <row r="329" spans="1:7">
       <c r="A329" t="s">
+        <v>550</v>
+      </c>
+      <c r="B329" t="s">
         <v>551</v>
-      </c>
-      <c r="B329" t="s">
-        <v>552</v>
       </c>
       <c r="C329" t="s">
         <v>532</v>
@@ -11481,7 +11466,7 @@
         <v>11</v>
       </c>
       <c r="F329" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G329" t="s">
         <v>528</v>
@@ -11504,7 +11489,7 @@
         <v>28</v>
       </c>
       <c r="F330" t="s">
-        <v>528</v>
+        <v>335</v>
       </c>
       <c r="G330" t="s">
         <v>528</v>
@@ -11527,7 +11512,7 @@
         <v>28</v>
       </c>
       <c r="F331" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G331" t="s">
         <v>528</v>
@@ -11561,13 +11546,13 @@
         <v>558</v>
       </c>
       <c r="B333" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C333" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="D333" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E333" t="s">
         <v>51</v>
@@ -11584,19 +11569,19 @@
         <v>560</v>
       </c>
       <c r="B334" t="s">
-        <v>561</v>
+        <v>16</v>
       </c>
       <c r="C334" t="s">
-        <v>319</v>
+        <v>200</v>
       </c>
       <c r="D334" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E334" t="s">
         <v>51</v>
       </c>
       <c r="F334" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G334" t="s">
         <v>528</v>
@@ -11604,22 +11589,22 @@
     </row>
     <row r="335" spans="1:7">
       <c r="A335" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B335" t="s">
-        <v>16</v>
+        <v>563</v>
       </c>
       <c r="C335" t="s">
-        <v>200</v>
+        <v>319</v>
       </c>
       <c r="D335" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E335" t="s">
         <v>51</v>
       </c>
       <c r="F335" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="G335" t="s">
         <v>528</v>
@@ -11630,19 +11615,19 @@
         <v>560</v>
       </c>
       <c r="B336" t="s">
-        <v>561</v>
+        <v>16</v>
       </c>
       <c r="C336" t="s">
-        <v>319</v>
+        <v>200</v>
       </c>
       <c r="D336" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E336" t="s">
         <v>51</v>
       </c>
       <c r="F336" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G336" t="s">
         <v>528</v>
@@ -11650,22 +11635,22 @@
     </row>
     <row r="337" spans="1:7">
       <c r="A337" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B337" t="s">
-        <v>16</v>
+        <v>563</v>
       </c>
       <c r="C337" t="s">
         <v>319</v>
       </c>
       <c r="D337" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E337" t="s">
         <v>51</v>
       </c>
       <c r="F337" t="s">
-        <v>530</v>
+        <v>566</v>
       </c>
       <c r="G337" t="s">
         <v>528</v>
@@ -11673,13 +11658,13 @@
     </row>
     <row r="338" spans="1:7">
       <c r="A338" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B338" t="s">
         <v>16</v>
       </c>
       <c r="C338" t="s">
-        <v>200</v>
+        <v>319</v>
       </c>
       <c r="D338" t="s">
         <v>43</v>
@@ -11688,7 +11673,7 @@
         <v>51</v>
       </c>
       <c r="F338" t="s">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="G338" t="s">
         <v>528</v>
@@ -11696,22 +11681,22 @@
     </row>
     <row r="339" spans="1:7">
       <c r="A339" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B339" t="s">
         <v>16</v>
       </c>
       <c r="C339" t="s">
-        <v>319</v>
+        <v>200</v>
       </c>
       <c r="D339" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E339" t="s">
         <v>51</v>
       </c>
       <c r="F339" t="s">
-        <v>251</v>
+        <v>552</v>
       </c>
       <c r="G339" t="s">
         <v>528</v>
@@ -11725,7 +11710,7 @@
         <v>16</v>
       </c>
       <c r="C340" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="D340" t="s">
         <v>26</v>
@@ -11734,7 +11719,7 @@
         <v>51</v>
       </c>
       <c r="F340" t="s">
-        <v>568</v>
+        <v>251</v>
       </c>
       <c r="G340" t="s">
         <v>528</v>
@@ -11745,19 +11730,19 @@
         <v>569</v>
       </c>
       <c r="B341" t="s">
+        <v>16</v>
+      </c>
+      <c r="C341" t="s">
+        <v>296</v>
+      </c>
+      <c r="D341" t="s">
+        <v>26</v>
+      </c>
+      <c r="E341" t="s">
+        <v>51</v>
+      </c>
+      <c r="F341" t="s">
         <v>570</v>
-      </c>
-      <c r="C341" t="s">
-        <v>192</v>
-      </c>
-      <c r="D341" t="s">
-        <v>50</v>
-      </c>
-      <c r="E341" t="s">
-        <v>65</v>
-      </c>
-      <c r="F341" t="s">
-        <v>571</v>
       </c>
       <c r="G341" t="s">
         <v>528</v>
@@ -11765,22 +11750,22 @@
     </row>
     <row r="342" spans="1:7">
       <c r="A342" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="B342" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="C342" t="s">
-        <v>319</v>
+        <v>192</v>
       </c>
       <c r="D342" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E342" t="s">
         <v>65</v>
       </c>
       <c r="F342" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="G342" t="s">
         <v>528</v>
@@ -11788,13 +11773,13 @@
     </row>
     <row r="343" spans="1:7">
       <c r="A343" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="B343" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="C343" t="s">
-        <v>192</v>
+        <v>319</v>
       </c>
       <c r="D343" t="s">
         <v>33</v>
@@ -11803,7 +11788,7 @@
         <v>65</v>
       </c>
       <c r="F343" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="G343" t="s">
         <v>528</v>
@@ -11811,16 +11796,16 @@
     </row>
     <row r="344" spans="1:7">
       <c r="A344" t="s">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="B344" t="s">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="C344" t="s">
-        <v>319</v>
+        <v>192</v>
       </c>
       <c r="D344" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E344" t="s">
         <v>65</v>
@@ -11834,13 +11819,13 @@
     </row>
     <row r="345" spans="1:7">
       <c r="A345" t="s">
-        <v>216</v>
+        <v>562</v>
       </c>
       <c r="B345" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="C345" t="s">
-        <v>192</v>
+        <v>319</v>
       </c>
       <c r="D345" t="s">
         <v>40</v>
@@ -11857,22 +11842,22 @@
     </row>
     <row r="346" spans="1:7">
       <c r="A346" t="s">
-        <v>578</v>
+        <v>216</v>
       </c>
       <c r="B346" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C346" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="D346" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E346" t="s">
         <v>65</v>
       </c>
       <c r="F346" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="G346" t="s">
         <v>528</v>
@@ -11880,22 +11865,22 @@
     </row>
     <row r="347" spans="1:7">
       <c r="A347" t="s">
+        <v>579</v>
+      </c>
+      <c r="B347" t="s">
         <v>580</v>
       </c>
-      <c r="B347" t="s">
-        <v>581</v>
-      </c>
       <c r="C347" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D347" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="E347" t="s">
         <v>65</v>
       </c>
       <c r="F347" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="G347" t="s">
         <v>528</v>
@@ -11903,10 +11888,10 @@
     </row>
     <row r="348" spans="1:7">
       <c r="A348" t="s">
+        <v>581</v>
+      </c>
+      <c r="B348" t="s">
         <v>582</v>
-      </c>
-      <c r="B348" t="s">
-        <v>583</v>
       </c>
       <c r="C348" t="s">
         <v>354</v>
@@ -11918,7 +11903,7 @@
         <v>72</v>
       </c>
       <c r="F348" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G348" t="s">
         <v>528</v>
@@ -11926,10 +11911,10 @@
     </row>
     <row r="349" spans="1:7">
       <c r="A349" t="s">
+        <v>583</v>
+      </c>
+      <c r="B349" t="s">
         <v>584</v>
-      </c>
-      <c r="B349" t="s">
-        <v>585</v>
       </c>
       <c r="C349" t="s">
         <v>532</v>
@@ -11941,7 +11926,7 @@
         <v>72</v>
       </c>
       <c r="F349" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G349" t="s">
         <v>528</v>
@@ -11964,7 +11949,7 @@
         <v>72</v>
       </c>
       <c r="F350" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G350" t="s">
         <v>528</v>
@@ -11972,7 +11957,7 @@
     </row>
     <row r="351" spans="1:7">
       <c r="A351" t="s">
-        <v>588</v>
+        <v>547</v>
       </c>
       <c r="B351" t="s">
         <v>548</v>
@@ -11987,7 +11972,7 @@
         <v>72</v>
       </c>
       <c r="F351" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G351" t="s">
         <v>528</v>
@@ -11995,10 +11980,10 @@
     </row>
     <row r="352" spans="1:7">
       <c r="A352" t="s">
+        <v>583</v>
+      </c>
+      <c r="B352" t="s">
         <v>584</v>
-      </c>
-      <c r="B352" t="s">
-        <v>585</v>
       </c>
       <c r="C352" t="s">
         <v>532</v>
@@ -12010,7 +11995,7 @@
         <v>72</v>
       </c>
       <c r="F352" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G352" t="s">
         <v>528</v>
@@ -12033,7 +12018,7 @@
         <v>72</v>
       </c>
       <c r="F353" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G353" t="s">
         <v>528</v>
@@ -12056,7 +12041,7 @@
         <v>72</v>
       </c>
       <c r="F354" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G354" t="s">
         <v>528</v>
@@ -12067,7 +12052,7 @@
         <v>204</v>
       </c>
       <c r="B355" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C355" t="s">
         <v>537</v>
@@ -12079,7 +12064,7 @@
         <v>72</v>
       </c>
       <c r="F355" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G355" t="s">
         <v>528</v>
@@ -12087,7 +12072,7 @@
     </row>
     <row r="356" spans="1:7">
       <c r="A356" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B356" t="s">
         <v>16</v>
@@ -12113,7 +12098,7 @@
         <v>304</v>
       </c>
       <c r="B357" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C357" t="s">
         <v>234</v>
@@ -12125,18 +12110,18 @@
         <v>11</v>
       </c>
       <c r="F357" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G357" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="358" spans="1:7">
       <c r="A358" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B358" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C358" t="s">
         <v>268</v>
@@ -12148,18 +12133,18 @@
         <v>11</v>
       </c>
       <c r="F358" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G358" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="359" spans="1:7">
       <c r="A359" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B359" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C359" t="s">
         <v>285</v>
@@ -12171,10 +12156,10 @@
         <v>11</v>
       </c>
       <c r="F359" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G359" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="360" spans="1:7">
@@ -12182,10 +12167,10 @@
         <v>283</v>
       </c>
       <c r="B360" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C360" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D360" t="s">
         <v>25</v>
@@ -12194,18 +12179,18 @@
         <v>11</v>
       </c>
       <c r="F360" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G360" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="361" spans="1:7">
       <c r="A361" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B361" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C361" t="s">
         <v>209</v>
@@ -12217,18 +12202,18 @@
         <v>11</v>
       </c>
       <c r="F361" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G361" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="362" spans="1:7">
       <c r="A362" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B362" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C362" t="s">
         <v>9</v>
@@ -12240,10 +12225,10 @@
         <v>28</v>
       </c>
       <c r="F362" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G362" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="363" spans="1:7">
@@ -12251,7 +12236,7 @@
         <v>249</v>
       </c>
       <c r="B363" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C363" t="s">
         <v>248</v>
@@ -12263,18 +12248,18 @@
         <v>28</v>
       </c>
       <c r="F363" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G363" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="364" spans="1:7">
       <c r="A364" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B364" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C364" t="s">
         <v>9</v>
@@ -12286,21 +12271,21 @@
         <v>28</v>
       </c>
       <c r="F364" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G364" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="365" spans="1:7">
       <c r="A365" t="s">
+        <v>606</v>
+      </c>
+      <c r="B365" t="s">
+        <v>607</v>
+      </c>
+      <c r="C365" t="s">
         <v>608</v>
-      </c>
-      <c r="B365" t="s">
-        <v>609</v>
-      </c>
-      <c r="C365" t="s">
-        <v>610</v>
       </c>
       <c r="D365" t="s">
         <v>50</v>
@@ -12309,18 +12294,18 @@
         <v>51</v>
       </c>
       <c r="F365" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G365" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="366" spans="1:7">
       <c r="A366" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B366" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C366" t="s">
         <v>285</v>
@@ -12332,18 +12317,18 @@
         <v>51</v>
       </c>
       <c r="F366" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G366" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="367" spans="1:7">
       <c r="A367" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B367" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C367" t="s">
         <v>285</v>
@@ -12355,21 +12340,21 @@
         <v>51</v>
       </c>
       <c r="F367" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G367" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="368" spans="1:7">
       <c r="A368" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B368" t="s">
         <v>21</v>
       </c>
       <c r="C368" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D368" t="s">
         <v>26</v>
@@ -12381,15 +12366,15 @@
         <v>46</v>
       </c>
       <c r="G368" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="369" spans="1:7">
       <c r="A369" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B369" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C369" t="s">
         <v>45</v>
@@ -12401,10 +12386,10 @@
         <v>65</v>
       </c>
       <c r="F369" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G369" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="370" spans="1:7">
@@ -12412,7 +12397,7 @@
         <v>246</v>
       </c>
       <c r="B370" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C370" t="s">
         <v>248</v>
@@ -12424,21 +12409,21 @@
         <v>65</v>
       </c>
       <c r="F370" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G370" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="371" spans="1:7">
       <c r="A371" t="s">
+        <v>618</v>
+      </c>
+      <c r="B371" t="s">
+        <v>619</v>
+      </c>
+      <c r="C371" t="s">
         <v>620</v>
-      </c>
-      <c r="B371" t="s">
-        <v>621</v>
-      </c>
-      <c r="C371" t="s">
-        <v>622</v>
       </c>
       <c r="D371" t="s">
         <v>50</v>
@@ -12447,21 +12432,21 @@
         <v>72</v>
       </c>
       <c r="F371" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G371" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="372" spans="1:7">
       <c r="A372" t="s">
+        <v>622</v>
+      </c>
+      <c r="B372" t="s">
+        <v>623</v>
+      </c>
+      <c r="C372" t="s">
         <v>624</v>
-      </c>
-      <c r="B372" t="s">
-        <v>625</v>
-      </c>
-      <c r="C372" t="s">
-        <v>626</v>
       </c>
       <c r="D372" t="s">
         <v>50</v>
@@ -12470,18 +12455,18 @@
         <v>72</v>
       </c>
       <c r="F372" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G372" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="373" spans="1:7">
       <c r="A373" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B373" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C373" t="s">
         <v>234</v>
@@ -12493,18 +12478,18 @@
         <v>72</v>
       </c>
       <c r="F373" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G373" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="374" spans="1:7">
       <c r="A374" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B374" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C374" t="s">
         <v>45</v>
@@ -12516,18 +12501,18 @@
         <v>72</v>
       </c>
       <c r="F374" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G374" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="375" spans="1:7">
       <c r="A375" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B375" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C375" t="s">
         <v>234</v>
@@ -12539,18 +12524,18 @@
         <v>72</v>
       </c>
       <c r="F375" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G375" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="376" spans="1:7">
       <c r="A376" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B376" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C376" t="s">
         <v>45</v>
@@ -12562,21 +12547,21 @@
         <v>72</v>
       </c>
       <c r="F376" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G376" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="377" spans="1:7">
       <c r="A377" t="s">
+        <v>634</v>
+      </c>
+      <c r="B377" t="s">
+        <v>635</v>
+      </c>
+      <c r="C377" t="s">
         <v>636</v>
-      </c>
-      <c r="B377" t="s">
-        <v>637</v>
-      </c>
-      <c r="C377" t="s">
-        <v>638</v>
       </c>
       <c r="D377" t="s">
         <v>25</v>
@@ -12585,21 +12570,21 @@
         <v>72</v>
       </c>
       <c r="F377" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G377" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="378" spans="1:7">
       <c r="A378" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B378" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C378" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D378" t="s">
         <v>63</v>
@@ -12608,21 +12593,21 @@
         <v>72</v>
       </c>
       <c r="F378" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G378" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="379" spans="1:7">
       <c r="A379" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B379" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C379" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D379" t="s">
         <v>63</v>
@@ -12631,10 +12616,10 @@
         <v>72</v>
       </c>
       <c r="F379" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G379" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="380" spans="1:7">
@@ -12642,7 +12627,7 @@
         <v>304</v>
       </c>
       <c r="B380" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C380" t="s">
         <v>234</v>
@@ -12654,18 +12639,18 @@
         <v>11</v>
       </c>
       <c r="F380" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G380" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="381" spans="1:7">
       <c r="A381" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B381" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C381" t="s">
         <v>268</v>
@@ -12677,18 +12662,18 @@
         <v>11</v>
       </c>
       <c r="F381" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G381" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="382" spans="1:7">
       <c r="A382" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B382" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C382" t="s">
         <v>285</v>
@@ -12700,10 +12685,10 @@
         <v>11</v>
       </c>
       <c r="F382" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G382" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="383" spans="1:7">
@@ -12711,10 +12696,10 @@
         <v>283</v>
       </c>
       <c r="B383" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C383" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D383" t="s">
         <v>25</v>
@@ -12723,18 +12708,18 @@
         <v>11</v>
       </c>
       <c r="F383" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G383" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="384" spans="1:7">
       <c r="A384" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B384" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C384" t="s">
         <v>209</v>
@@ -12746,18 +12731,18 @@
         <v>11</v>
       </c>
       <c r="F384" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G384" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="385" spans="1:7">
       <c r="A385" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B385" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C385" t="s">
         <v>92</v>
@@ -12769,21 +12754,21 @@
         <v>28</v>
       </c>
       <c r="F385" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="G385" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="386" spans="1:7">
       <c r="A386" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B386" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C386" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D386" t="s">
         <v>33</v>
@@ -12792,18 +12777,18 @@
         <v>28</v>
       </c>
       <c r="F386" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G386" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="387" spans="1:7">
       <c r="A387" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B387" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C387" t="s">
         <v>92</v>
@@ -12815,21 +12800,21 @@
         <v>28</v>
       </c>
       <c r="F387" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="G387" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="388" spans="1:7">
       <c r="A388" t="s">
+        <v>622</v>
+      </c>
+      <c r="B388" t="s">
+        <v>647</v>
+      </c>
+      <c r="C388" t="s">
         <v>624</v>
-      </c>
-      <c r="B388" t="s">
-        <v>649</v>
-      </c>
-      <c r="C388" t="s">
-        <v>626</v>
       </c>
       <c r="D388" t="s">
         <v>40</v>
@@ -12838,10 +12823,10 @@
         <v>28</v>
       </c>
       <c r="F388" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G388" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="389" spans="1:7">
@@ -12849,7 +12834,7 @@
         <v>249</v>
       </c>
       <c r="B389" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C389" t="s">
         <v>248</v>
@@ -12861,21 +12846,21 @@
         <v>28</v>
       </c>
       <c r="F389" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G389" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="390" spans="1:7">
       <c r="A390" t="s">
+        <v>606</v>
+      </c>
+      <c r="B390" t="s">
+        <v>649</v>
+      </c>
+      <c r="C390" t="s">
         <v>608</v>
-      </c>
-      <c r="B390" t="s">
-        <v>651</v>
-      </c>
-      <c r="C390" t="s">
-        <v>610</v>
       </c>
       <c r="D390" t="s">
         <v>50</v>
@@ -12884,18 +12869,18 @@
         <v>51</v>
       </c>
       <c r="F390" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G390" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="391" spans="1:7">
       <c r="A391" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B391" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C391" t="s">
         <v>45</v>
@@ -12907,18 +12892,18 @@
         <v>65</v>
       </c>
       <c r="F391" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G391" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="392" spans="1:7">
       <c r="A392" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B392" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C392" t="s">
         <v>285</v>
@@ -12930,18 +12915,18 @@
         <v>65</v>
       </c>
       <c r="F392" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G392" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="393" spans="1:7">
       <c r="A393" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B393" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C393" t="s">
         <v>45</v>
@@ -12953,18 +12938,18 @@
         <v>65</v>
       </c>
       <c r="F393" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G393" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="394" spans="1:7">
       <c r="A394" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B394" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C394" t="s">
         <v>285</v>
@@ -12976,18 +12961,18 @@
         <v>65</v>
       </c>
       <c r="F394" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G394" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="395" spans="1:7">
       <c r="A395" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B395" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C395" t="s">
         <v>45</v>
@@ -12999,10 +12984,10 @@
         <v>65</v>
       </c>
       <c r="F395" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G395" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="396" spans="1:7">
@@ -13010,7 +12995,7 @@
         <v>246</v>
       </c>
       <c r="B396" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C396" t="s">
         <v>248</v>
@@ -13022,18 +13007,18 @@
         <v>65</v>
       </c>
       <c r="F396" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G396" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="397" spans="1:7">
       <c r="A397" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B397" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C397" t="s">
         <v>234</v>
@@ -13045,18 +13030,18 @@
         <v>72</v>
       </c>
       <c r="F397" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G397" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="398" spans="1:7">
       <c r="A398" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B398" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C398" t="s">
         <v>104</v>
@@ -13068,18 +13053,18 @@
         <v>72</v>
       </c>
       <c r="F398" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G398" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="399" spans="1:7">
       <c r="A399" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B399" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C399" t="s">
         <v>234</v>
@@ -13091,18 +13076,18 @@
         <v>72</v>
       </c>
       <c r="F399" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G399" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="400" spans="1:7">
       <c r="A400" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B400" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C400" t="s">
         <v>104</v>
@@ -13114,21 +13099,21 @@
         <v>72</v>
       </c>
       <c r="F400" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G400" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="401" spans="1:7">
       <c r="A401" t="s">
+        <v>634</v>
+      </c>
+      <c r="B401" t="s">
+        <v>657</v>
+      </c>
+      <c r="C401" t="s">
         <v>636</v>
-      </c>
-      <c r="B401" t="s">
-        <v>659</v>
-      </c>
-      <c r="C401" t="s">
-        <v>638</v>
       </c>
       <c r="D401" t="s">
         <v>25</v>
@@ -13137,21 +13122,21 @@
         <v>72</v>
       </c>
       <c r="F401" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G401" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="402" spans="1:7">
       <c r="A402" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B402" t="s">
         <v>21</v>
       </c>
       <c r="C402" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D402" t="s">
         <v>26</v>
@@ -13163,18 +13148,18 @@
         <v>46</v>
       </c>
       <c r="G402" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="403" spans="1:7">
       <c r="A403" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B403" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C403" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D403" t="s">
         <v>50</v>
@@ -13183,41 +13168,41 @@
         <v>11</v>
       </c>
       <c r="F403" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G403" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="404" spans="1:7">
       <c r="A404" t="s">
+        <v>622</v>
+      </c>
+      <c r="B404" t="s">
+        <v>661</v>
+      </c>
+      <c r="C404" t="s">
         <v>624</v>
       </c>
-      <c r="B404" t="s">
-        <v>663</v>
-      </c>
-      <c r="C404" t="s">
-        <v>626</v>
-      </c>
       <c r="D404" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E404" t="s">
         <v>11</v>
       </c>
       <c r="F404" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G404" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="405" spans="1:7">
       <c r="A405" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B405" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C405" t="s">
         <v>302</v>
@@ -13229,33 +13214,33 @@
         <v>11</v>
       </c>
       <c r="F405" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G405" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="406" spans="1:7">
       <c r="A406" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B406" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C406" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D406" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E406" t="s">
         <v>11</v>
       </c>
       <c r="F406" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G406" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="407" spans="1:7">
@@ -13263,7 +13248,7 @@
         <v>246</v>
       </c>
       <c r="B407" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C407" t="s">
         <v>164</v>
@@ -13275,18 +13260,18 @@
         <v>11</v>
       </c>
       <c r="F407" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G407" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="408" spans="1:7">
       <c r="A408" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B408" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C408" t="s">
         <v>302</v>
@@ -13298,18 +13283,18 @@
         <v>11</v>
       </c>
       <c r="F408" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G408" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="409" spans="1:7">
       <c r="A409" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B409" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C409" t="s">
         <v>197</v>
@@ -13321,18 +13306,18 @@
         <v>51</v>
       </c>
       <c r="F409" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G409" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="410" spans="1:7">
       <c r="A410" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B410" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C410" t="s">
         <v>334</v>
@@ -13344,18 +13329,18 @@
         <v>51</v>
       </c>
       <c r="F410" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="G410" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="411" spans="1:7">
       <c r="A411" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B411" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C411" t="s">
         <v>334</v>
@@ -13367,21 +13352,21 @@
         <v>51</v>
       </c>
       <c r="F411" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="G411" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="412" spans="1:7">
       <c r="A412" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B412" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C412" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D412" t="s">
         <v>25</v>
@@ -13390,18 +13375,18 @@
         <v>51</v>
       </c>
       <c r="F412" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="G412" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="413" spans="1:7">
       <c r="A413" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B413" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C413" t="s">
         <v>104</v>
@@ -13413,10 +13398,10 @@
         <v>51</v>
       </c>
       <c r="F413" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="G413" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="414" spans="1:7">
@@ -13424,7 +13409,7 @@
         <v>249</v>
       </c>
       <c r="B414" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C414" t="s">
         <v>248</v>
@@ -13436,10 +13421,10 @@
         <v>65</v>
       </c>
       <c r="F414" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G414" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="415" spans="1:7">
@@ -13447,10 +13432,10 @@
         <v>304</v>
       </c>
       <c r="B415" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C415" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D415" t="s">
         <v>33</v>
@@ -13459,15 +13444,15 @@
         <v>65</v>
       </c>
       <c r="F415" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G415" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="416" spans="1:7">
       <c r="A416" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B416" t="s">
         <v>21</v>
@@ -13485,15 +13470,15 @@
         <v>335</v>
       </c>
       <c r="G416" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="417" spans="1:7">
       <c r="A417" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B417" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C417" t="s">
         <v>285</v>
@@ -13505,18 +13490,18 @@
         <v>65</v>
       </c>
       <c r="F417" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G417" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="418" spans="1:7">
       <c r="A418" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B418" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C418" t="s">
         <v>285</v>
@@ -13528,10 +13513,10 @@
         <v>65</v>
       </c>
       <c r="F418" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G418" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="419" spans="1:7">
@@ -13539,10 +13524,10 @@
         <v>283</v>
       </c>
       <c r="B419" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C419" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D419" t="s">
         <v>50</v>
@@ -13551,18 +13536,18 @@
         <v>72</v>
       </c>
       <c r="F419" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G419" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="420" spans="1:7">
       <c r="A420" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B420" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C420" t="s">
         <v>494</v>
@@ -13574,18 +13559,18 @@
         <v>72</v>
       </c>
       <c r="F420" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="G420" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="421" spans="1:7">
       <c r="A421" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B421" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C421" t="s">
         <v>9</v>
@@ -13597,18 +13582,18 @@
         <v>72</v>
       </c>
       <c r="F421" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G421" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="422" spans="1:7">
       <c r="A422" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B422" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C422" t="s">
         <v>494</v>
@@ -13620,18 +13605,18 @@
         <v>72</v>
       </c>
       <c r="F422" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="G422" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="423" spans="1:7">
       <c r="A423" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B423" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C423" t="s">
         <v>9</v>
@@ -13643,18 +13628,18 @@
         <v>72</v>
       </c>
       <c r="F423" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G423" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="424" spans="1:7">
       <c r="A424" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B424" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C424" t="s">
         <v>49</v>
@@ -13666,10 +13651,10 @@
         <v>72</v>
       </c>
       <c r="F424" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G424" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="425" spans="1:7">
@@ -13677,10 +13662,10 @@
         <v>304</v>
       </c>
       <c r="B425" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C425" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D425" t="s">
         <v>50</v>
@@ -13692,15 +13677,15 @@
         <v>471</v>
       </c>
       <c r="G425" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="426" spans="1:7">
       <c r="A426" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B426" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C426" t="s">
         <v>268</v>
@@ -13712,10 +13697,10 @@
         <v>11</v>
       </c>
       <c r="F426" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G426" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="427" spans="1:7">
@@ -13723,7 +13708,7 @@
         <v>249</v>
       </c>
       <c r="B427" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C427" t="s">
         <v>248</v>
@@ -13738,7 +13723,7 @@
         <v>471</v>
       </c>
       <c r="G427" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="428" spans="1:7">
@@ -13746,10 +13731,10 @@
         <v>283</v>
       </c>
       <c r="B428" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C428" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D428" t="s">
         <v>25</v>
@@ -13758,18 +13743,18 @@
         <v>11</v>
       </c>
       <c r="F428" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G428" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="429" spans="1:7">
       <c r="A429" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B429" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C429" t="s">
         <v>209</v>
@@ -13781,18 +13766,18 @@
         <v>11</v>
       </c>
       <c r="F429" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G429" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="430" spans="1:7">
       <c r="A430" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B430" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C430" t="s">
         <v>334</v>
@@ -13804,21 +13789,21 @@
         <v>28</v>
       </c>
       <c r="F430" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="G430" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="431" spans="1:7">
       <c r="A431" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B431" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C431" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D431" t="s">
         <v>50</v>
@@ -13827,18 +13812,18 @@
         <v>28</v>
       </c>
       <c r="F431" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G431" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="432" spans="1:7">
       <c r="A432" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B432" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C432" t="s">
         <v>268</v>
@@ -13853,15 +13838,15 @@
         <v>471</v>
       </c>
       <c r="G432" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="433" spans="1:7">
       <c r="A433" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B433" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C433" t="s">
         <v>334</v>
@@ -13873,21 +13858,21 @@
         <v>28</v>
       </c>
       <c r="F433" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="G433" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="434" spans="1:7">
       <c r="A434" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B434" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C434" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D434" t="s">
         <v>63</v>
@@ -13896,21 +13881,21 @@
         <v>28</v>
       </c>
       <c r="F434" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G434" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="435" spans="1:7">
       <c r="A435" t="s">
+        <v>606</v>
+      </c>
+      <c r="B435" t="s">
+        <v>703</v>
+      </c>
+      <c r="C435" t="s">
         <v>608</v>
-      </c>
-      <c r="B435" t="s">
-        <v>705</v>
-      </c>
-      <c r="C435" t="s">
-        <v>610</v>
       </c>
       <c r="D435" t="s">
         <v>50</v>
@@ -13919,21 +13904,21 @@
         <v>51</v>
       </c>
       <c r="F435" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G435" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="436" spans="1:7">
       <c r="A436" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B436" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C436" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D436" t="s">
         <v>33</v>
@@ -13942,18 +13927,18 @@
         <v>51</v>
       </c>
       <c r="F436" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G436" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="437" spans="1:7">
       <c r="A437" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B437" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C437" t="s">
         <v>209</v>
@@ -13965,21 +13950,21 @@
         <v>51</v>
       </c>
       <c r="F437" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G437" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="438" spans="1:7">
       <c r="A438" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B438" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C438" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D438" t="s">
         <v>40</v>
@@ -13988,18 +13973,18 @@
         <v>51</v>
       </c>
       <c r="F438" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G438" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="439" spans="1:7">
       <c r="A439" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B439" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C439" t="s">
         <v>209</v>
@@ -14011,21 +13996,21 @@
         <v>51</v>
       </c>
       <c r="F439" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G439" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="440" spans="1:7">
       <c r="A440" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B440" t="s">
         <v>21</v>
       </c>
       <c r="C440" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D440" t="s">
         <v>26</v>
@@ -14037,18 +14022,18 @@
         <v>335</v>
       </c>
       <c r="G440" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="441" spans="1:7">
       <c r="A441" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B441" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C441" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D441" t="s">
         <v>50</v>
@@ -14060,15 +14045,15 @@
         <v>471</v>
       </c>
       <c r="G441" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="442" spans="1:7">
       <c r="A442" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B442" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C442" t="s">
         <v>494</v>
@@ -14080,21 +14065,21 @@
         <v>65</v>
       </c>
       <c r="F442" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G442" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="443" spans="1:7">
       <c r="A443" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B443" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C443" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D443" t="s">
         <v>33</v>
@@ -14103,18 +14088,18 @@
         <v>65</v>
       </c>
       <c r="F443" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G443" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="444" spans="1:7">
       <c r="A444" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B444" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C444" t="s">
         <v>494</v>
@@ -14126,21 +14111,21 @@
         <v>65</v>
       </c>
       <c r="F444" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G444" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="445" spans="1:7">
       <c r="A445" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B445" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C445" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D445" t="s">
         <v>40</v>
@@ -14149,10 +14134,10 @@
         <v>65</v>
       </c>
       <c r="F445" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G445" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="446" spans="1:7">
@@ -14160,7 +14145,7 @@
         <v>246</v>
       </c>
       <c r="B446" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C446" t="s">
         <v>248</v>
@@ -14172,21 +14157,21 @@
         <v>65</v>
       </c>
       <c r="F446" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G446" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="447" spans="1:7">
       <c r="A447" t="s">
+        <v>634</v>
+      </c>
+      <c r="B447" t="s">
+        <v>710</v>
+      </c>
+      <c r="C447" t="s">
         <v>636</v>
-      </c>
-      <c r="B447" t="s">
-        <v>712</v>
-      </c>
-      <c r="C447" t="s">
-        <v>638</v>
       </c>
       <c r="D447" t="s">
         <v>25</v>
@@ -14195,10 +14180,10 @@
         <v>72</v>
       </c>
       <c r="F447" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G447" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="448" spans="1:7">
@@ -14206,10 +14191,10 @@
         <v>304</v>
       </c>
       <c r="B448" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C448" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D448" t="s">
         <v>50</v>
@@ -14221,15 +14206,15 @@
         <v>471</v>
       </c>
       <c r="G448" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="449" spans="1:7">
       <c r="A449" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B449" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C449" t="s">
         <v>268</v>
@@ -14241,10 +14226,10 @@
         <v>11</v>
       </c>
       <c r="F449" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G449" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="450" spans="1:7">
@@ -14252,7 +14237,7 @@
         <v>249</v>
       </c>
       <c r="B450" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C450" t="s">
         <v>248</v>
@@ -14267,7 +14252,7 @@
         <v>471</v>
       </c>
       <c r="G450" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="451" spans="1:7">
@@ -14275,10 +14260,10 @@
         <v>283</v>
       </c>
       <c r="B451" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C451" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D451" t="s">
         <v>25</v>
@@ -14287,18 +14272,18 @@
         <v>11</v>
       </c>
       <c r="F451" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G451" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="452" spans="1:7">
       <c r="A452" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B452" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C452" t="s">
         <v>209</v>
@@ -14310,18 +14295,18 @@
         <v>11</v>
       </c>
       <c r="F452" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G452" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="453" spans="1:7">
       <c r="A453" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B453" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C453" t="s">
         <v>494</v>
@@ -14333,18 +14318,18 @@
         <v>28</v>
       </c>
       <c r="F453" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G453" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="454" spans="1:7">
       <c r="A454" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B454" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C454" t="s">
         <v>209</v>
@@ -14356,18 +14341,18 @@
         <v>28</v>
       </c>
       <c r="F454" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G454" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="455" spans="1:7">
       <c r="A455" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B455" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C455" t="s">
         <v>268</v>
@@ -14382,15 +14367,15 @@
         <v>471</v>
       </c>
       <c r="G455" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="456" spans="1:7">
       <c r="A456" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B456" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C456" t="s">
         <v>494</v>
@@ -14402,18 +14387,18 @@
         <v>28</v>
       </c>
       <c r="F456" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G456" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="457" spans="1:7">
       <c r="A457" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B457" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C457" t="s">
         <v>209</v>
@@ -14425,21 +14410,21 @@
         <v>28</v>
       </c>
       <c r="F457" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G457" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="458" spans="1:7">
       <c r="A458" t="s">
+        <v>606</v>
+      </c>
+      <c r="B458" t="s">
+        <v>720</v>
+      </c>
+      <c r="C458" t="s">
         <v>608</v>
-      </c>
-      <c r="B458" t="s">
-        <v>722</v>
-      </c>
-      <c r="C458" t="s">
-        <v>610</v>
       </c>
       <c r="D458" t="s">
         <v>50</v>
@@ -14448,21 +14433,21 @@
         <v>51</v>
       </c>
       <c r="F458" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G458" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="459" spans="1:7">
       <c r="A459" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B459" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C459" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D459" t="s">
         <v>33</v>
@@ -14471,21 +14456,21 @@
         <v>51</v>
       </c>
       <c r="F459" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="G459" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="460" spans="1:7">
       <c r="A460" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B460" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C460" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D460" t="s">
         <v>33</v>
@@ -14494,21 +14479,21 @@
         <v>51</v>
       </c>
       <c r="F460" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G460" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="461" spans="1:7">
       <c r="A461" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B461" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C461" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D461" t="s">
         <v>40</v>
@@ -14517,21 +14502,21 @@
         <v>51</v>
       </c>
       <c r="F461" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="G461" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="462" spans="1:7">
       <c r="A462" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B462" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C462" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D462" t="s">
         <v>40</v>
@@ -14540,21 +14525,21 @@
         <v>51</v>
       </c>
       <c r="F462" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G462" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="463" spans="1:7">
       <c r="A463" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B463" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C463" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D463" t="s">
         <v>25</v>
@@ -14563,18 +14548,18 @@
         <v>51</v>
       </c>
       <c r="F463" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G463" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="464" spans="1:7">
       <c r="A464" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B464" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C464" t="s">
         <v>268</v>
@@ -14586,21 +14571,21 @@
         <v>51</v>
       </c>
       <c r="F464" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G464" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="465" spans="1:7">
       <c r="A465" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B465" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C465" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D465" t="s">
         <v>63</v>
@@ -14609,18 +14594,18 @@
         <v>51</v>
       </c>
       <c r="F465" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G465" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="466" spans="1:7">
       <c r="A466" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B466" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C466" t="s">
         <v>268</v>
@@ -14632,21 +14617,21 @@
         <v>51</v>
       </c>
       <c r="F466" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G466" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="467" spans="1:7">
       <c r="A467" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B467" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C467" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D467" t="s">
         <v>50</v>
@@ -14658,7 +14643,7 @@
         <v>471</v>
       </c>
       <c r="G467" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="468" spans="1:7">
@@ -14666,7 +14651,7 @@
         <v>246</v>
       </c>
       <c r="B468" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C468" t="s">
         <v>248</v>
@@ -14678,21 +14663,21 @@
         <v>65</v>
       </c>
       <c r="F468" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G468" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="469" spans="1:7">
       <c r="A469" t="s">
+        <v>634</v>
+      </c>
+      <c r="B469" t="s">
+        <v>729</v>
+      </c>
+      <c r="C469" t="s">
         <v>636</v>
-      </c>
-      <c r="B469" t="s">
-        <v>731</v>
-      </c>
-      <c r="C469" t="s">
-        <v>638</v>
       </c>
       <c r="D469" t="s">
         <v>25</v>
@@ -14701,21 +14686,21 @@
         <v>72</v>
       </c>
       <c r="F469" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G469" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="470" spans="1:7">
       <c r="A470" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B470" t="s">
         <v>21</v>
       </c>
       <c r="C470" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D470" t="s">
         <v>26</v>
@@ -14727,12 +14712,12 @@
         <v>46</v>
       </c>
       <c r="G470" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="471" spans="1:7">
       <c r="A471" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B471" t="s">
         <v>16</v>
@@ -14747,18 +14732,18 @@
         <v>11</v>
       </c>
       <c r="F471" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G471" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="472" spans="1:7">
       <c r="A472" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B472" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C472" t="s">
         <v>351</v>
@@ -14770,21 +14755,21 @@
         <v>11</v>
       </c>
       <c r="F472" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="G472" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="473" spans="1:7">
       <c r="A473" t="s">
+        <v>736</v>
+      </c>
+      <c r="B473" t="s">
+        <v>737</v>
+      </c>
+      <c r="C473" t="s">
         <v>738</v>
-      </c>
-      <c r="B473" t="s">
-        <v>739</v>
-      </c>
-      <c r="C473" t="s">
-        <v>740</v>
       </c>
       <c r="D473" t="s">
         <v>40</v>
@@ -14793,21 +14778,21 @@
         <v>11</v>
       </c>
       <c r="F473" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="G473" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="474" spans="1:7">
       <c r="A474" t="s">
+        <v>740</v>
+      </c>
+      <c r="B474" t="s">
+        <v>741</v>
+      </c>
+      <c r="C474" t="s">
         <v>742</v>
-      </c>
-      <c r="B474" t="s">
-        <v>743</v>
-      </c>
-      <c r="C474" t="s">
-        <v>744</v>
       </c>
       <c r="D474" t="s">
         <v>25</v>
@@ -14816,18 +14801,18 @@
         <v>11</v>
       </c>
       <c r="F474" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="G474" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="475" spans="1:7">
       <c r="A475" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B475" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C475" t="s">
         <v>164</v>
@@ -14839,15 +14824,15 @@
         <v>11</v>
       </c>
       <c r="F475" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="G475" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="476" spans="1:7">
       <c r="A476" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B476" t="s">
         <v>8</v>
@@ -14862,15 +14847,15 @@
         <v>28</v>
       </c>
       <c r="F476" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G476" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="477" spans="1:7">
       <c r="A477" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B477" t="s">
         <v>21</v>
@@ -14885,18 +14870,18 @@
         <v>28</v>
       </c>
       <c r="F477" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G477" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="478" spans="1:7">
       <c r="A478" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B478" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C478" t="s">
         <v>334</v>
@@ -14908,18 +14893,18 @@
         <v>28</v>
       </c>
       <c r="F478" t="s">
-        <v>92</v>
+        <v>335</v>
       </c>
       <c r="G478" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="479" spans="1:7">
       <c r="A479" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B479" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C479" t="s">
         <v>310</v>
@@ -14934,12 +14919,12 @@
         <v>92</v>
       </c>
       <c r="G479" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="480" spans="1:7">
       <c r="A480" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B480" t="s">
         <v>21</v>
@@ -14954,15 +14939,15 @@
         <v>51</v>
       </c>
       <c r="F480" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G480" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="481" spans="1:7">
       <c r="A481" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B481" t="s">
         <v>21</v>
@@ -14977,15 +14962,15 @@
         <v>51</v>
       </c>
       <c r="F481" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G481" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="482" spans="1:7">
       <c r="A482" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B482" t="s">
         <v>8</v>
@@ -15003,18 +14988,18 @@
         <v>92</v>
       </c>
       <c r="G482" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="483" spans="1:7">
       <c r="A483" t="s">
+        <v>754</v>
+      </c>
+      <c r="B483" t="s">
+        <v>755</v>
+      </c>
+      <c r="C483" t="s">
         <v>756</v>
-      </c>
-      <c r="B483" t="s">
-        <v>757</v>
-      </c>
-      <c r="C483" t="s">
-        <v>758</v>
       </c>
       <c r="D483" t="s">
         <v>33</v>
@@ -15023,21 +15008,21 @@
         <v>65</v>
       </c>
       <c r="F483" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G483" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="484" spans="1:7">
       <c r="A484" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B484" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C484" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D484" t="s">
         <v>40</v>
@@ -15046,21 +15031,21 @@
         <v>65</v>
       </c>
       <c r="F484" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G484" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="485" spans="1:7">
       <c r="A485" t="s">
+        <v>740</v>
+      </c>
+      <c r="B485" t="s">
+        <v>741</v>
+      </c>
+      <c r="C485" t="s">
         <v>742</v>
-      </c>
-      <c r="B485" t="s">
-        <v>743</v>
-      </c>
-      <c r="C485" t="s">
-        <v>744</v>
       </c>
       <c r="D485" t="s">
         <v>25</v>
@@ -15069,15 +15054,15 @@
         <v>65</v>
       </c>
       <c r="F485" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G485" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="486" spans="1:7">
       <c r="A486" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B486" t="s">
         <v>21</v>
@@ -15092,21 +15077,21 @@
         <v>65</v>
       </c>
       <c r="F486" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G486" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="487" spans="1:7">
       <c r="A487" t="s">
+        <v>760</v>
+      </c>
+      <c r="B487" t="s">
+        <v>761</v>
+      </c>
+      <c r="C487" t="s">
         <v>762</v>
-      </c>
-      <c r="B487" t="s">
-        <v>763</v>
-      </c>
-      <c r="C487" t="s">
-        <v>764</v>
       </c>
       <c r="D487" t="s">
         <v>25</v>
@@ -15118,18 +15103,18 @@
         <v>92</v>
       </c>
       <c r="G487" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="488" spans="1:7">
       <c r="A488" t="s">
+        <v>760</v>
+      </c>
+      <c r="B488" t="s">
+        <v>761</v>
+      </c>
+      <c r="C488" t="s">
         <v>762</v>
-      </c>
-      <c r="B488" t="s">
-        <v>763</v>
-      </c>
-      <c r="C488" t="s">
-        <v>764</v>
       </c>
       <c r="D488" t="s">
         <v>63</v>
@@ -15141,15 +15126,15 @@
         <v>92</v>
       </c>
       <c r="G488" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="489" spans="1:7">
       <c r="A489" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B489" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C489" t="s">
         <v>310</v>
@@ -15161,15 +15146,15 @@
         <v>11</v>
       </c>
       <c r="F489" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G489" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="490" spans="1:7">
       <c r="A490" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B490" t="s">
         <v>8</v>
@@ -15184,21 +15169,21 @@
         <v>11</v>
       </c>
       <c r="F490" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G490" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="491" spans="1:7">
       <c r="A491" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B491" t="s">
         <v>8</v>
       </c>
       <c r="C491" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D491" t="s">
         <v>22</v>
@@ -15207,18 +15192,18 @@
         <v>11</v>
       </c>
       <c r="F491" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G491" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="492" spans="1:7">
       <c r="A492" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B492" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C492" t="s">
         <v>310</v>
@@ -15230,15 +15215,15 @@
         <v>11</v>
       </c>
       <c r="F492" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G492" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="493" spans="1:7">
       <c r="A493" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B493" t="s">
         <v>8</v>
@@ -15253,15 +15238,15 @@
         <v>28</v>
       </c>
       <c r="F493" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G493" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="494" spans="1:7">
       <c r="A494" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B494" t="s">
         <v>21</v>
@@ -15276,18 +15261,18 @@
         <v>28</v>
       </c>
       <c r="F494" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G494" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="495" spans="1:7">
       <c r="A495" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B495" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C495" t="s">
         <v>334</v>
@@ -15302,7 +15287,7 @@
         <v>335</v>
       </c>
       <c r="G495" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="496" spans="1:7">
@@ -15310,7 +15295,7 @@
         <v>336</v>
       </c>
       <c r="B496" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C496" t="s">
         <v>338</v>
@@ -15325,18 +15310,18 @@
         <v>329</v>
       </c>
       <c r="G496" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="497" spans="1:7">
       <c r="A497" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B497" t="s">
         <v>8</v>
       </c>
       <c r="C497" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D497" t="s">
         <v>18</v>
@@ -15345,15 +15330,15 @@
         <v>51</v>
       </c>
       <c r="F497" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G497" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="498" spans="1:7">
       <c r="A498" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B498" t="s">
         <v>8</v>
@@ -15368,18 +15353,18 @@
         <v>51</v>
       </c>
       <c r="F498" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G498" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="499" spans="1:7">
       <c r="A499" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B499" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C499" t="s">
         <v>340</v>
@@ -15391,10 +15376,10 @@
         <v>51</v>
       </c>
       <c r="F499" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G499" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="500" spans="1:7">
@@ -15402,7 +15387,7 @@
         <v>344</v>
       </c>
       <c r="B500" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C500" t="s">
         <v>338</v>
@@ -15417,15 +15402,15 @@
         <v>346</v>
       </c>
       <c r="G500" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="501" spans="1:7">
       <c r="A501" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B501" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C501" t="s">
         <v>363</v>
@@ -15437,18 +15422,18 @@
         <v>65</v>
       </c>
       <c r="F501" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G501" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="502" spans="1:7">
       <c r="A502" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B502" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C502" t="s">
         <v>351</v>
@@ -15460,18 +15445,18 @@
         <v>65</v>
       </c>
       <c r="F502" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G502" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="503" spans="1:7">
       <c r="A503" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B503" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C503" t="s">
         <v>351</v>
@@ -15483,18 +15468,18 @@
         <v>65</v>
       </c>
       <c r="F503" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G503" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="504" spans="1:7">
       <c r="A504" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B504" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C504" t="s">
         <v>277</v>
@@ -15506,18 +15491,18 @@
         <v>72</v>
       </c>
       <c r="F504" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G504" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="505" spans="1:7">
       <c r="A505" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B505" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C505" t="s">
         <v>277</v>
@@ -15529,15 +15514,15 @@
         <v>72</v>
       </c>
       <c r="F505" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G505" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="506" spans="1:7">
       <c r="A506" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B506" t="s">
         <v>16</v>
@@ -15552,10 +15537,10 @@
         <v>11</v>
       </c>
       <c r="F506" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G506" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="507" spans="1:7">
@@ -15575,18 +15560,18 @@
         <v>11</v>
       </c>
       <c r="F507" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G507" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="508" spans="1:7">
       <c r="A508" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B508" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C508" t="s">
         <v>302</v>
@@ -15598,15 +15583,15 @@
         <v>11</v>
       </c>
       <c r="F508" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G508" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="509" spans="1:7">
       <c r="A509" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B509" t="s">
         <v>8</v>
@@ -15621,15 +15606,15 @@
         <v>28</v>
       </c>
       <c r="F509" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="G509" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="510" spans="1:7">
       <c r="A510" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B510" t="s">
         <v>21</v>
@@ -15644,18 +15629,18 @@
         <v>28</v>
       </c>
       <c r="F510" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G510" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="511" spans="1:7">
       <c r="A511" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B511" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C511" t="s">
         <v>334</v>
@@ -15670,15 +15655,15 @@
         <v>335</v>
       </c>
       <c r="G511" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="512" spans="1:7">
       <c r="A512" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B512" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C512" t="s">
         <v>322</v>
@@ -15690,18 +15675,18 @@
         <v>51</v>
       </c>
       <c r="F512" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G512" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="513" spans="1:7">
       <c r="A513" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B513" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C513" t="s">
         <v>348</v>
@@ -15713,18 +15698,18 @@
         <v>51</v>
       </c>
       <c r="F513" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G513" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="514" spans="1:7">
       <c r="A514" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B514" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C514" t="s">
         <v>348</v>
@@ -15736,18 +15721,18 @@
         <v>51</v>
       </c>
       <c r="F514" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G514" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="515" spans="1:7">
       <c r="A515" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B515" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C515" t="s">
         <v>475</v>
@@ -15759,18 +15744,18 @@
         <v>51</v>
       </c>
       <c r="F515" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G515" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="516" spans="1:7">
       <c r="A516" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B516" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C516" t="s">
         <v>354</v>
@@ -15782,18 +15767,18 @@
         <v>65</v>
       </c>
       <c r="F516" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G516" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="517" spans="1:7">
       <c r="A517" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B517" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C517" t="s">
         <v>354</v>
@@ -15805,15 +15790,15 @@
         <v>65</v>
       </c>
       <c r="F517" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G517" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="518" spans="1:7">
       <c r="A518" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B518" t="s">
         <v>8</v>
@@ -15822,21 +15807,21 @@
         <v>322</v>
       </c>
       <c r="D518" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="E518" t="s">
         <v>72</v>
       </c>
       <c r="F518" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="G518" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="519" spans="1:7">
       <c r="A519" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B519" t="s">
         <v>8</v>
@@ -15851,18 +15836,18 @@
         <v>72</v>
       </c>
       <c r="F519" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="G519" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="520" spans="1:7">
       <c r="A520" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B520" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C520" t="s">
         <v>325</v>
@@ -15874,15 +15859,15 @@
         <v>72</v>
       </c>
       <c r="F520" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="G520" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="521" spans="1:7">
       <c r="A521" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B521" t="s">
         <v>8</v>
@@ -15897,18 +15882,18 @@
         <v>72</v>
       </c>
       <c r="F521" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="G521" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="522" spans="1:7">
       <c r="A522" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B522" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C522" t="s">
         <v>325</v>
@@ -15920,15 +15905,15 @@
         <v>72</v>
       </c>
       <c r="F522" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="G522" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="523" spans="1:7">
       <c r="A523" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B523" t="s">
         <v>8</v>
@@ -15937,27 +15922,27 @@
         <v>322</v>
       </c>
       <c r="D523" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="E523" t="s">
         <v>72</v>
       </c>
       <c r="F523" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="G523" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="524" spans="1:7">
       <c r="A524" t="s">
+        <v>820</v>
+      </c>
+      <c r="B524" t="s">
+        <v>821</v>
+      </c>
+      <c r="C524" t="s">
         <v>822</v>
-      </c>
-      <c r="B524" t="s">
-        <v>823</v>
-      </c>
-      <c r="C524" t="s">
-        <v>824</v>
       </c>
       <c r="D524" t="s">
         <v>50</v>
@@ -15966,21 +15951,21 @@
         <v>11</v>
       </c>
       <c r="F524" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G524" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="525" spans="1:7">
       <c r="A525" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B525" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C525" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D525" t="s">
         <v>18</v>
@@ -15989,21 +15974,21 @@
         <v>11</v>
       </c>
       <c r="F525" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="G525" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="526" spans="1:7">
       <c r="A526" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B526" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C526" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D526" t="s">
         <v>40</v>
@@ -16012,21 +15997,21 @@
         <v>11</v>
       </c>
       <c r="F526" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="G526" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="527" spans="1:7">
       <c r="A527" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B527" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C527" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D527" t="s">
         <v>25</v>
@@ -16035,21 +16020,21 @@
         <v>11</v>
       </c>
       <c r="F527" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G527" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="528" spans="1:7">
       <c r="A528" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B528" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C528" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D528" t="s">
         <v>63</v>
@@ -16058,18 +16043,18 @@
         <v>11</v>
       </c>
       <c r="F528" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G528" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="529" spans="1:7">
       <c r="A529" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B529" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C529" t="s">
         <v>325</v>
@@ -16081,18 +16066,18 @@
         <v>28</v>
       </c>
       <c r="F529" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G529" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="530" spans="1:7">
       <c r="A530" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B530" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C530" t="s">
         <v>325</v>
@@ -16104,18 +16089,18 @@
         <v>28</v>
       </c>
       <c r="F530" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G530" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="531" spans="1:7">
       <c r="A531" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B531" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C531" t="s">
         <v>334</v>
@@ -16127,18 +16112,18 @@
         <v>28</v>
       </c>
       <c r="F531" t="s">
-        <v>825</v>
+        <v>335</v>
       </c>
       <c r="G531" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="532" spans="1:7">
       <c r="A532" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B532" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C532" t="s">
         <v>532</v>
@@ -16150,21 +16135,21 @@
         <v>51</v>
       </c>
       <c r="F532" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="G532" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="533" spans="1:7">
       <c r="A533" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B533" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C533" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D533" t="s">
         <v>33</v>
@@ -16173,21 +16158,21 @@
         <v>51</v>
       </c>
       <c r="F533" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G533" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="534" spans="1:7">
       <c r="A534" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B534" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C534" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D534" t="s">
         <v>40</v>
@@ -16196,21 +16181,21 @@
         <v>51</v>
       </c>
       <c r="F534" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G534" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="535" spans="1:7">
       <c r="A535" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B535" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C535" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D535" t="s">
         <v>25</v>
@@ -16219,21 +16204,21 @@
         <v>51</v>
       </c>
       <c r="F535" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G535" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="536" spans="1:7">
       <c r="A536" t="s">
+        <v>848</v>
+      </c>
+      <c r="B536" t="s">
+        <v>849</v>
+      </c>
+      <c r="C536" t="s">
         <v>850</v>
-      </c>
-      <c r="B536" t="s">
-        <v>851</v>
-      </c>
-      <c r="C536" t="s">
-        <v>852</v>
       </c>
       <c r="D536" t="s">
         <v>63</v>
@@ -16242,21 +16227,21 @@
         <v>51</v>
       </c>
       <c r="F536" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="G536" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="537" spans="1:7">
       <c r="A537" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B537" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C537" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D537" t="s">
         <v>25</v>
@@ -16265,21 +16250,21 @@
         <v>65</v>
       </c>
       <c r="F537" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G537" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="538" spans="1:7">
       <c r="A538" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B538" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="C538" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D538" t="s">
         <v>63</v>
@@ -16288,21 +16273,21 @@
         <v>65</v>
       </c>
       <c r="F538" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G538" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="539" spans="1:7">
       <c r="A539" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B539" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C539" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D539" t="s">
         <v>33</v>
@@ -16311,21 +16296,21 @@
         <v>72</v>
       </c>
       <c r="F539" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="G539" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="540" spans="1:7">
       <c r="A540" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B540" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="C540" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D540" t="s">
         <v>63</v>
@@ -16334,18 +16319,18 @@
         <v>72</v>
       </c>
       <c r="F540" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G540" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="541" spans="1:7">
       <c r="A541" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B541" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="C541" t="s">
         <v>325</v>
@@ -16357,10 +16342,10 @@
         <v>11</v>
       </c>
       <c r="F541" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="G541" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="542" spans="1:7">
@@ -16383,15 +16368,15 @@
         <v>522</v>
       </c>
       <c r="G542" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="543" spans="1:7">
       <c r="A543" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B543" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C543" t="s">
         <v>322</v>
@@ -16406,12 +16391,12 @@
         <v>522</v>
       </c>
       <c r="G543" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="544" spans="1:7">
       <c r="A544" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B544" t="s">
         <v>8</v>
@@ -16426,15 +16411,15 @@
         <v>28</v>
       </c>
       <c r="F544" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="G544" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="545" spans="1:7">
       <c r="A545" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B545" t="s">
         <v>21</v>
@@ -16452,15 +16437,15 @@
         <v>522</v>
       </c>
       <c r="G545" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="546" spans="1:7">
       <c r="A546" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B546" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C546" t="s">
         <v>334</v>
@@ -16475,15 +16460,15 @@
         <v>335</v>
       </c>
       <c r="G546" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="547" spans="1:7">
       <c r="A547" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B547" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="C547" t="s">
         <v>45</v>
@@ -16498,15 +16483,15 @@
         <v>522</v>
       </c>
       <c r="G547" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="548" spans="1:7">
       <c r="A548" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B548" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C548" t="s">
         <v>45</v>
@@ -16521,12 +16506,12 @@
         <v>522</v>
       </c>
       <c r="G548" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="549" spans="1:7">
       <c r="A549" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B549" t="s">
         <v>8</v>
@@ -16541,18 +16526,18 @@
         <v>51</v>
       </c>
       <c r="F549" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="G549" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="550" spans="1:7">
       <c r="A550" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B550" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C550" t="s">
         <v>322</v>
@@ -16564,15 +16549,15 @@
         <v>51</v>
       </c>
       <c r="F550" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G550" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="551" spans="1:7">
       <c r="A551" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B551" t="s">
         <v>16</v>
@@ -16590,12 +16575,12 @@
         <v>522</v>
       </c>
       <c r="G551" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="552" spans="1:7">
       <c r="A552" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B552" t="s">
         <v>16</v>
@@ -16613,12 +16598,12 @@
         <v>522</v>
       </c>
       <c r="G552" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="553" spans="1:7">
       <c r="A553" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B553" t="s">
         <v>21</v>
@@ -16636,15 +16621,15 @@
         <v>522</v>
       </c>
       <c r="G553" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="554" spans="1:7">
       <c r="A554" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B554" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C554" t="s">
         <v>348</v>
@@ -16659,7 +16644,7 @@
         <v>522</v>
       </c>
       <c r="G554" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="555" spans="1:7">
@@ -16667,7 +16652,7 @@
         <v>356</v>
       </c>
       <c r="B555" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C555" t="s">
         <v>357</v>
@@ -16682,15 +16667,15 @@
         <v>522</v>
       </c>
       <c r="G555" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="556" spans="1:7">
       <c r="A556" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B556" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C556" t="s">
         <v>45</v>
@@ -16705,15 +16690,15 @@
         <v>522</v>
       </c>
       <c r="G556" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="557" spans="1:7">
       <c r="A557" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B557" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="C557" t="s">
         <v>45</v>
@@ -16728,18 +16713,18 @@
         <v>522</v>
       </c>
       <c r="G557" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="558" spans="1:7">
       <c r="A558" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B558" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C558" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D558" t="s">
         <v>50</v>
@@ -16748,10 +16733,10 @@
         <v>11</v>
       </c>
       <c r="F558" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G558" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="559" spans="1:7">
@@ -16759,7 +16744,7 @@
         <v>511</v>
       </c>
       <c r="B559" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C559" t="s">
         <v>521</v>
@@ -16771,10 +16756,10 @@
         <v>11</v>
       </c>
       <c r="F559" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="G559" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="560" spans="1:7">
@@ -16782,7 +16767,7 @@
         <v>518</v>
       </c>
       <c r="B560" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C560" t="s">
         <v>78</v>
@@ -16794,10 +16779,10 @@
         <v>11</v>
       </c>
       <c r="F560" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G560" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="561" spans="1:7">
@@ -16805,7 +16790,7 @@
         <v>502</v>
       </c>
       <c r="B561" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C561" t="s">
         <v>92</v>
@@ -16817,18 +16802,18 @@
         <v>11</v>
       </c>
       <c r="F561" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="G561" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="562" spans="1:7">
       <c r="A562" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B562" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C562" t="s">
         <v>78</v>
@@ -16840,18 +16825,18 @@
         <v>11</v>
       </c>
       <c r="F562" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G562" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="563" spans="1:7">
       <c r="A563" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B563" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C563" t="s">
         <v>53</v>
@@ -16863,10 +16848,10 @@
         <v>11</v>
       </c>
       <c r="F563" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="G563" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="564" spans="1:7">
@@ -16874,7 +16859,7 @@
         <v>124</v>
       </c>
       <c r="B564" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C564" t="s">
         <v>78</v>
@@ -16886,18 +16871,18 @@
         <v>11</v>
       </c>
       <c r="F564" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G564" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="565" spans="1:7">
       <c r="A565" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B565" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C565" t="s">
         <v>53</v>
@@ -16909,18 +16894,18 @@
         <v>11</v>
       </c>
       <c r="F565" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G565" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="566" spans="1:7">
       <c r="A566" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B566" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C566" t="s">
         <v>78</v>
@@ -16932,18 +16917,18 @@
         <v>11</v>
       </c>
       <c r="F566" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="G566" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="567" spans="1:7">
       <c r="A567" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B567" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C567" t="s">
         <v>187</v>
@@ -16955,18 +16940,18 @@
         <v>28</v>
       </c>
       <c r="F567" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="G567" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="568" spans="1:7">
       <c r="A568" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B568" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C568" t="s">
         <v>289</v>
@@ -16978,18 +16963,18 @@
         <v>28</v>
       </c>
       <c r="F568" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="G568" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="569" spans="1:7">
       <c r="A569" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B569" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C569" t="s">
         <v>187</v>
@@ -17001,18 +16986,18 @@
         <v>28</v>
       </c>
       <c r="F569" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="G569" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="570" spans="1:7">
       <c r="A570" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B570" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C570" t="s">
         <v>289</v>
@@ -17024,18 +17009,18 @@
         <v>28</v>
       </c>
       <c r="F570" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="G570" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="571" spans="1:7">
       <c r="A571" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B571" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C571" t="s">
         <v>92</v>
@@ -17047,10 +17032,10 @@
         <v>28</v>
       </c>
       <c r="F571" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="G571" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="572" spans="1:7">
@@ -17058,7 +17043,7 @@
         <v>484</v>
       </c>
       <c r="B572" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C572" t="s">
         <v>485</v>
@@ -17070,18 +17055,18 @@
         <v>28</v>
       </c>
       <c r="F572" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="G572" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="573" spans="1:7">
       <c r="A573" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B573" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C573" t="s">
         <v>92</v>
@@ -17093,21 +17078,21 @@
         <v>28</v>
       </c>
       <c r="F573" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="G573" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="574" spans="1:7">
       <c r="A574" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B574" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C574" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D574" t="s">
         <v>25</v>
@@ -17116,18 +17101,18 @@
         <v>28</v>
       </c>
       <c r="F574" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G574" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="575" spans="1:7">
       <c r="A575" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B575" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C575" t="s">
         <v>175</v>
@@ -17139,18 +17124,18 @@
         <v>28</v>
       </c>
       <c r="F575" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="G575" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="576" spans="1:7">
       <c r="A576" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B576" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C576" t="s">
         <v>92</v>
@@ -17162,21 +17147,21 @@
         <v>28</v>
       </c>
       <c r="F576" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="G576" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="577" spans="1:7">
       <c r="A577" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B577" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C577" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D577" t="s">
         <v>63</v>
@@ -17185,18 +17170,18 @@
         <v>28</v>
       </c>
       <c r="F577" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="G577" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="578" spans="1:7">
       <c r="A578" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B578" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C578" t="s">
         <v>175</v>
@@ -17208,18 +17193,18 @@
         <v>28</v>
       </c>
       <c r="F578" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="G578" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="579" spans="1:7">
       <c r="A579" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B579" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C579" t="s">
         <v>92</v>
@@ -17231,10 +17216,10 @@
         <v>28</v>
       </c>
       <c r="F579" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="G579" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="580" spans="1:7">
@@ -17254,10 +17239,10 @@
         <v>51</v>
       </c>
       <c r="F580" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G580" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="581" spans="1:7">
@@ -17265,7 +17250,7 @@
         <v>511</v>
       </c>
       <c r="B581" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C581" t="s">
         <v>78</v>
@@ -17277,10 +17262,10 @@
         <v>51</v>
       </c>
       <c r="F581" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="G581" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="582" spans="1:7">
@@ -17288,7 +17273,7 @@
         <v>519</v>
       </c>
       <c r="B582" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C582" t="s">
         <v>526</v>
@@ -17300,18 +17285,18 @@
         <v>51</v>
       </c>
       <c r="F582" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="G582" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="583" spans="1:7">
       <c r="A583" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B583" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C583" t="s">
         <v>498</v>
@@ -17323,18 +17308,18 @@
         <v>51</v>
       </c>
       <c r="F583" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="G583" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="584" spans="1:7">
       <c r="A584" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B584" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C584" t="s">
         <v>92</v>
@@ -17346,10 +17331,10 @@
         <v>51</v>
       </c>
       <c r="F584" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="G584" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="585" spans="1:7">
@@ -17357,7 +17342,7 @@
         <v>523</v>
       </c>
       <c r="B585" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C585" t="s">
         <v>526</v>
@@ -17369,18 +17354,18 @@
         <v>51</v>
       </c>
       <c r="F585" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G585" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="586" spans="1:7">
       <c r="A586" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B586" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C586" t="s">
         <v>498</v>
@@ -17392,18 +17377,18 @@
         <v>51</v>
       </c>
       <c r="F586" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="G586" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="587" spans="1:7">
       <c r="A587" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B587" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C587" t="s">
         <v>92</v>
@@ -17415,10 +17400,10 @@
         <v>51</v>
       </c>
       <c r="F587" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="G587" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="588" spans="1:7">
@@ -17426,7 +17411,7 @@
         <v>130</v>
       </c>
       <c r="B588" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C588" t="s">
         <v>285</v>
@@ -17438,18 +17423,18 @@
         <v>51</v>
       </c>
       <c r="F588" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G588" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="589" spans="1:7">
       <c r="A589" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B589" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C589" t="s">
         <v>92</v>
@@ -17461,18 +17446,18 @@
         <v>51</v>
       </c>
       <c r="F589" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G589" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="590" spans="1:7">
       <c r="A590" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B590" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C590" t="s">
         <v>92</v>
@@ -17484,18 +17469,18 @@
         <v>51</v>
       </c>
       <c r="F590" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="G590" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="591" spans="1:7">
       <c r="A591" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B591" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C591" t="s">
         <v>515</v>
@@ -17507,10 +17492,10 @@
         <v>65</v>
       </c>
       <c r="F591" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G591" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="592" spans="1:7">
@@ -17518,7 +17503,7 @@
         <v>518</v>
       </c>
       <c r="B592" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C592" t="s">
         <v>78</v>
@@ -17530,21 +17515,21 @@
         <v>65</v>
       </c>
       <c r="F592" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G592" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="593" spans="1:7">
       <c r="A593" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B593" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C593" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D593" t="s">
         <v>33</v>
@@ -17553,21 +17538,21 @@
         <v>65</v>
       </c>
       <c r="F593" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G593" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="594" spans="1:7">
       <c r="A594" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B594" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C594" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D594" t="s">
         <v>33</v>
@@ -17576,21 +17561,21 @@
         <v>65</v>
       </c>
       <c r="F594" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="G594" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="595" spans="1:7">
       <c r="A595" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B595" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C595" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D595" t="s">
         <v>33</v>
@@ -17599,10 +17584,10 @@
         <v>65</v>
       </c>
       <c r="F595" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G595" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="596" spans="1:7">
@@ -17610,7 +17595,7 @@
         <v>509</v>
       </c>
       <c r="B596" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C596" t="s">
         <v>92</v>
@@ -17622,18 +17607,18 @@
         <v>65</v>
       </c>
       <c r="F596" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G596" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="597" spans="1:7">
       <c r="A597" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B597" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C597" t="s">
         <v>482</v>
@@ -17645,21 +17630,21 @@
         <v>65</v>
       </c>
       <c r="F597" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="G597" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="598" spans="1:7">
       <c r="A598" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B598" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C598" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D598" t="s">
         <v>40</v>
@@ -17668,10 +17653,10 @@
         <v>65</v>
       </c>
       <c r="F598" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G598" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="599" spans="1:7">
@@ -17679,7 +17664,7 @@
         <v>500</v>
       </c>
       <c r="B599" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C599" t="s">
         <v>75</v>
@@ -17691,10 +17676,10 @@
         <v>65</v>
       </c>
       <c r="F599" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G599" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="600" spans="1:7">
@@ -17702,7 +17687,7 @@
         <v>86</v>
       </c>
       <c r="B600" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C600" t="s">
         <v>53</v>
@@ -17714,18 +17699,18 @@
         <v>65</v>
       </c>
       <c r="F600" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G600" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="601" spans="1:7">
       <c r="A601" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B601" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C601" t="s">
         <v>92</v>
@@ -17737,10 +17722,10 @@
         <v>72</v>
       </c>
       <c r="F601" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G601" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="602" spans="1:7">
@@ -17748,10 +17733,10 @@
         <v>484</v>
       </c>
       <c r="B602" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C602" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D602" t="s">
         <v>50</v>
@@ -17760,10 +17745,10 @@
         <v>72</v>
       </c>
       <c r="F602" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="G602" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="603" spans="1:7">
@@ -17771,7 +17756,7 @@
         <v>484</v>
       </c>
       <c r="B603" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C603" t="s">
         <v>485</v>
@@ -17783,10 +17768,10 @@
         <v>72</v>
       </c>
       <c r="F603" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="G603" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="604" spans="1:7">
@@ -17794,10 +17779,10 @@
         <v>484</v>
       </c>
       <c r="B604" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C604" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D604" t="s">
         <v>29</v>
@@ -17806,10 +17791,10 @@
         <v>72</v>
       </c>
       <c r="F604" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="G604" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="605" spans="1:7">
@@ -17817,7 +17802,7 @@
         <v>484</v>
       </c>
       <c r="B605" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C605" t="s">
         <v>485</v>
@@ -17829,18 +17814,18 @@
         <v>72</v>
       </c>
       <c r="F605" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="G605" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="606" spans="1:7">
       <c r="A606" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B606" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C606" t="s">
         <v>521</v>
@@ -17852,18 +17837,18 @@
         <v>72</v>
       </c>
       <c r="F606" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="G606" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="607" spans="1:7">
       <c r="A607" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B607" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C607" t="s">
         <v>92</v>
@@ -17875,10 +17860,10 @@
         <v>72</v>
       </c>
       <c r="F607" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G607" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="608" spans="1:7">
@@ -17898,18 +17883,18 @@
         <v>72</v>
       </c>
       <c r="F608" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G608" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="609" spans="1:7">
       <c r="A609" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B609" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C609" t="s">
         <v>92</v>
@@ -17921,10 +17906,10 @@
         <v>72</v>
       </c>
       <c r="F609" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="G609" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="610" spans="1:7">
@@ -17944,18 +17929,18 @@
         <v>72</v>
       </c>
       <c r="F610" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="G610" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="611" spans="1:7">
       <c r="A611" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B611" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C611" t="s">
         <v>78</v>
@@ -17967,18 +17952,18 @@
         <v>72</v>
       </c>
       <c r="F611" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G611" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="612" spans="1:7">
       <c r="A612" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B612" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C612" t="s">
         <v>526</v>
@@ -17990,15 +17975,15 @@
         <v>72</v>
       </c>
       <c r="F612" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G612" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="613" spans="1:7">
       <c r="A613" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B613" t="s">
         <v>16</v>
@@ -18016,12 +18001,12 @@
         <v>329</v>
       </c>
       <c r="G613" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="614" spans="1:7">
       <c r="A614" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B614" t="s">
         <v>16</v>
@@ -18039,12 +18024,12 @@
         <v>346</v>
       </c>
       <c r="G614" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="615" spans="1:7">
       <c r="A615" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B615" t="s">
         <v>21</v>
@@ -18062,12 +18047,12 @@
         <v>522</v>
       </c>
       <c r="G615" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="616" spans="1:7">
       <c r="A616" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B616" t="s">
         <v>16</v>
@@ -18085,12 +18070,12 @@
         <v>522</v>
       </c>
       <c r="G616" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="617" spans="1:7">
       <c r="A617" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B617" t="s">
         <v>21</v>
@@ -18108,12 +18093,12 @@
         <v>346</v>
       </c>
       <c r="G617" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="618" spans="1:7">
       <c r="A618" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B618" t="s">
         <v>16</v>
@@ -18131,12 +18116,12 @@
         <v>471</v>
       </c>
       <c r="G618" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="619" spans="1:7">
       <c r="A619" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B619" t="s">
         <v>16</v>
@@ -18154,15 +18139,15 @@
         <v>346</v>
       </c>
       <c r="G619" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="620" spans="1:7">
       <c r="A620" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B620" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="C620" t="s">
         <v>555</v>
@@ -18177,12 +18162,12 @@
         <v>335</v>
       </c>
       <c r="G620" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="621" spans="1:7">
       <c r="A621" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B621" t="s">
         <v>16</v>
@@ -18200,7 +18185,7 @@
         <v>471</v>
       </c>
       <c r="G621" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="622" spans="1:7">
@@ -18223,110 +18208,110 @@
         <v>346</v>
       </c>
       <c r="G622" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="623" spans="1:7">
       <c r="A623" t="s">
-        <v>950</v>
+        <v>558</v>
       </c>
       <c r="B623" t="s">
         <v>21</v>
       </c>
       <c r="C623" t="s">
-        <v>740</v>
+        <v>178</v>
       </c>
       <c r="D623" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E623" t="s">
         <v>51</v>
       </c>
       <c r="F623" t="s">
-        <v>346</v>
+        <v>591</v>
       </c>
       <c r="G623" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="624" spans="1:7">
       <c r="A624" t="s">
-        <v>566</v>
+        <v>948</v>
       </c>
       <c r="B624" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C624" t="s">
-        <v>200</v>
+        <v>738</v>
       </c>
       <c r="D624" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E624" t="s">
         <v>51</v>
       </c>
       <c r="F624" t="s">
-        <v>471</v>
+        <v>346</v>
       </c>
       <c r="G624" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="625" spans="1:7">
       <c r="A625" t="s">
-        <v>951</v>
+        <v>568</v>
       </c>
       <c r="B625" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C625" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D625" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="E625" t="s">
         <v>51</v>
       </c>
       <c r="F625" t="s">
-        <v>346</v>
+        <v>471</v>
       </c>
       <c r="G625" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="626" spans="1:7">
       <c r="A626" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="B626" t="s">
         <v>21</v>
       </c>
       <c r="C626" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D626" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E626" t="s">
         <v>51</v>
       </c>
       <c r="F626" t="s">
-        <v>593</v>
+        <v>346</v>
       </c>
       <c r="G626" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="627" spans="1:7">
       <c r="A627" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="B627" t="s">
         <v>16</v>
       </c>
       <c r="C627" t="s">
-        <v>200</v>
+        <v>338</v>
       </c>
       <c r="D627" t="s">
         <v>10</v>
@@ -18335,21 +18320,21 @@
         <v>65</v>
       </c>
       <c r="F627" t="s">
-        <v>733</v>
+        <v>346</v>
       </c>
       <c r="G627" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="628" spans="1:7">
       <c r="A628" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="B628" t="s">
         <v>16</v>
       </c>
       <c r="C628" t="s">
-        <v>338</v>
+        <v>200</v>
       </c>
       <c r="D628" t="s">
         <v>10</v>
@@ -18358,15 +18343,15 @@
         <v>65</v>
       </c>
       <c r="F628" t="s">
-        <v>346</v>
+        <v>731</v>
       </c>
       <c r="G628" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="629" spans="1:7">
       <c r="A629" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="B629" t="s">
         <v>8</v>
@@ -18381,15 +18366,15 @@
         <v>65</v>
       </c>
       <c r="F629" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="G629" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="630" spans="1:7">
       <c r="A630" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="B630" t="s">
         <v>8</v>
@@ -18404,15 +18389,15 @@
         <v>65</v>
       </c>
       <c r="F630" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="G630" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="631" spans="1:7">
       <c r="A631" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="B631" t="s">
         <v>21</v>
@@ -18430,12 +18415,12 @@
         <v>346</v>
       </c>
       <c r="G631" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="632" spans="1:7">
       <c r="A632" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B632" t="s">
         <v>21</v>
@@ -18453,12 +18438,12 @@
         <v>346</v>
       </c>
       <c r="G632" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="633" spans="1:7">
       <c r="A633" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="B633" t="s">
         <v>8</v>
@@ -18473,15 +18458,15 @@
         <v>72</v>
       </c>
       <c r="F633" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="G633" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="634" spans="1:7">
       <c r="A634" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B634" t="s">
         <v>16</v>
@@ -18499,12 +18484,12 @@
         <v>471</v>
       </c>
       <c r="G634" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="635" spans="1:7">
       <c r="A635" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="B635" t="s">
         <v>8</v>
@@ -18519,15 +18504,15 @@
         <v>72</v>
       </c>
       <c r="F635" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G635" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="636" spans="1:7">
       <c r="A636" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B636" t="s">
         <v>8</v>
@@ -18545,12 +18530,12 @@
         <v>46</v>
       </c>
       <c r="G636" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="637" spans="1:7">
       <c r="A637" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="B637" t="s">
         <v>8</v>
@@ -18565,15 +18550,15 @@
         <v>72</v>
       </c>
       <c r="F637" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="G637" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="638" spans="1:7">
       <c r="A638" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="B638" t="s">
         <v>8</v>
@@ -18591,12 +18576,12 @@
         <v>46</v>
       </c>
       <c r="G638" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="639" spans="1:7">
       <c r="A639" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B639" t="s">
         <v>21</v>
@@ -18614,12 +18599,12 @@
         <v>346</v>
       </c>
       <c r="G639" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="640" spans="1:7">
       <c r="A640" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B640" t="s">
         <v>8</v>
@@ -18634,15 +18619,15 @@
         <v>72</v>
       </c>
       <c r="F640" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="G640" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="641" spans="1:7">
       <c r="A641" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="B641" t="s">
         <v>16</v>
@@ -18660,7 +18645,7 @@
         <v>471</v>
       </c>
       <c r="G641" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
   </sheetData>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -4,14 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView windowWidth="20490" windowHeight="7020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$641</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -9,9 +9,6 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$673</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -30,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4711" uniqueCount="948">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4697" uniqueCount="948">
   <si>
     <t>Enseignements</t>
   </si>
@@ -752,10 +749,13 @@
     <t>Cours-Protection des réseaux électriques</t>
   </si>
   <si>
-    <t>Cours-système de concersion d'énergie photovoltaique</t>
-  </si>
-  <si>
-    <t>ABBOU MAJDA</t>
+    <t>Cours-système de conversion d'énergie photovoltaique</t>
+  </si>
+  <si>
+    <t>JBILOU MOKHTARIA</t>
+  </si>
+  <si>
+    <t>S12</t>
   </si>
   <si>
     <t>TD-Réseaux de transport et distribution</t>
@@ -845,9 +845,6 @@
     <t>TD-SCEP-ING4RSE</t>
   </si>
   <si>
-    <t>S12</t>
-  </si>
-  <si>
     <t>ING4RSE</t>
   </si>
   <si>
@@ -2630,151 +2627,151 @@
     <t>TD-CdRE-M2RE</t>
   </si>
   <si>
+    <t>TD-Electronique fondamentale 1-G4</t>
+  </si>
+  <si>
+    <t>AS20</t>
+  </si>
+  <si>
+    <t>MCIL2</t>
+  </si>
+  <si>
+    <t>labo physique/G21/G22</t>
+  </si>
+  <si>
+    <t>labo physique/G31/G32</t>
+  </si>
+  <si>
+    <t>TD-Anly3-MCIL2</t>
+  </si>
+  <si>
+    <t>AS19</t>
+  </si>
+  <si>
+    <t>TD-OV-MCIL2</t>
+  </si>
+  <si>
+    <t>TD-Analyse 3-G3</t>
+  </si>
+  <si>
+    <t>TD-Electrotechnique fondamentale 1-G1</t>
+  </si>
+  <si>
+    <t>TD-EF1-MCIL2</t>
+  </si>
+  <si>
+    <t>Cours-Analy3-MCIL2</t>
+  </si>
+  <si>
+    <t>TD-Analyse 3-G4</t>
+  </si>
+  <si>
+    <t>TD-Ondes et vibrations-G3</t>
+  </si>
+  <si>
+    <t>TP-Programmation Python</t>
+  </si>
+  <si>
+    <t>TP-Ppython-MCIL2</t>
+  </si>
+  <si>
+    <t>salle micro 3/G41/G42</t>
+  </si>
+  <si>
+    <t>TP-Electrotechnique fondamentale 1</t>
+  </si>
+  <si>
+    <t>TP-EF1-MCIL2</t>
+  </si>
+  <si>
+    <t>labo ETT 1/G11/G12</t>
+  </si>
+  <si>
+    <t>labo ETT 1/G21/G22</t>
+  </si>
+  <si>
+    <t>TP-Electronique fondamentale 1</t>
+  </si>
+  <si>
+    <t>TP-ENF1-MCIL2</t>
+  </si>
+  <si>
+    <t>labo eˊlectronique/G21/G22</t>
+  </si>
+  <si>
+    <t>TP-OV-MCIL2</t>
+  </si>
+  <si>
+    <t>labo physique/G11/G12</t>
+  </si>
+  <si>
+    <t>MESLEM MEHADJIA</t>
+  </si>
+  <si>
+    <t>salle micro BIS/G21/G22</t>
+  </si>
+  <si>
+    <t>labo ETT 1/G31/G32</t>
+  </si>
+  <si>
+    <t>labo eˊlectronique/G31/G32</t>
+  </si>
+  <si>
+    <t>salle micro BIS/G31/G32</t>
+  </si>
+  <si>
+    <t>labo eˊlectronique/G11/G12</t>
+  </si>
+  <si>
+    <t>TD-ENF1-MCIL2</t>
+  </si>
+  <si>
+    <t>labo eˊlectronique/G41/G42</t>
+  </si>
+  <si>
+    <t>labo ETT 1/G41/G42</t>
+  </si>
+  <si>
+    <t>TD-Electronique fondamentale 1-G3</t>
+  </si>
+  <si>
+    <t>TD-Ondes et vibrations-G4</t>
+  </si>
+  <si>
+    <t>Cours-Etat de l'art du génie électrique</t>
+  </si>
+  <si>
+    <t>Cours-EGE-MCIL2</t>
+  </si>
+  <si>
+    <t>TD-Electrotechnique fondamentale 1-G2</t>
+  </si>
+  <si>
+    <t>TD-Electrotechnique fondamentale 1-G3</t>
+  </si>
+  <si>
+    <t>TP-Programmation python</t>
+  </si>
+  <si>
+    <t>CHIKHI NAWEL</t>
+  </si>
+  <si>
+    <t>salle micro BIS/G11/G12</t>
+  </si>
+  <si>
+    <t>TD-PS-MCIL2</t>
+  </si>
+  <si>
+    <t>TD-Electrotechnique fondamentale 1-G4</t>
+  </si>
+  <si>
+    <t>Cours-PS-MCIL2</t>
+  </si>
+  <si>
+    <t>Cours-OV-MCIL2</t>
+  </si>
+  <si>
     <t>Cours-Energies et environnement</t>
-  </si>
-  <si>
-    <t>MCIL2</t>
-  </si>
-  <si>
-    <t>TD-Anly3-MCIL2</t>
-  </si>
-  <si>
-    <t>AS19</t>
-  </si>
-  <si>
-    <t>AS20</t>
-  </si>
-  <si>
-    <t>TD-OV-MCIL2</t>
-  </si>
-  <si>
-    <t>TD-Analyse 3-G3</t>
-  </si>
-  <si>
-    <t>TD-Electrotechnique fondamentale 1-G1</t>
-  </si>
-  <si>
-    <t>TD-EF1-MCIL2</t>
-  </si>
-  <si>
-    <t>Cours-Analy3-MCIL2</t>
-  </si>
-  <si>
-    <t>TD-Analyse 3-G4</t>
-  </si>
-  <si>
-    <t>TD-Ondes et vibrations-G3</t>
-  </si>
-  <si>
-    <t>TP-Programmation Python</t>
-  </si>
-  <si>
-    <t>TP-Ppython-MCIL2</t>
-  </si>
-  <si>
-    <t>salle micro 3/G41/G42</t>
-  </si>
-  <si>
-    <t>TP-Electrotechnique fondamentale 1</t>
-  </si>
-  <si>
-    <t>TP-EF1-MCIL2</t>
-  </si>
-  <si>
-    <t>labo ETT 1/G11/G12</t>
-  </si>
-  <si>
-    <t>labo ETT 1/G21/G22</t>
-  </si>
-  <si>
-    <t>TP-Electronique fondamentale 1</t>
-  </si>
-  <si>
-    <t>TP-ENF1-MCIL2</t>
-  </si>
-  <si>
-    <t>labo eˊlectronique/G21/G22</t>
-  </si>
-  <si>
-    <t>TP-OV-MCIL2</t>
-  </si>
-  <si>
-    <t>labo physique/G11/G12</t>
-  </si>
-  <si>
-    <t>MESLEM MEHADJIA</t>
-  </si>
-  <si>
-    <t>salle micro BIS/G21/G22</t>
-  </si>
-  <si>
-    <t>labo ETT 1/G31/G32</t>
-  </si>
-  <si>
-    <t>labo eˊlectronique/G31/G32</t>
-  </si>
-  <si>
-    <t>salle micro BIS/G31/G32</t>
-  </si>
-  <si>
-    <t>labo eˊlectronique/G11/G12</t>
-  </si>
-  <si>
-    <t>TD-ENF1-MCIL2</t>
-  </si>
-  <si>
-    <t>labo eˊlectronique/G41/G42</t>
-  </si>
-  <si>
-    <t>labo ETT 1/G41/G42</t>
-  </si>
-  <si>
-    <t>TD-Electronique fondamentale 1-G3</t>
-  </si>
-  <si>
-    <t>TD-Ondes et vibrations-G4</t>
-  </si>
-  <si>
-    <t>Cours-Etat de l'art du génie électrique</t>
-  </si>
-  <si>
-    <t>Cours-EGE-MCIL2</t>
-  </si>
-  <si>
-    <t>TD-Electrotechnique fondamentale 1-G2</t>
-  </si>
-  <si>
-    <t>TD-Electrotechnique fondamentale 1-G3</t>
-  </si>
-  <si>
-    <t>TP-Programmation python</t>
-  </si>
-  <si>
-    <t>CHIKHI NAWEL</t>
-  </si>
-  <si>
-    <t>salle micro BIS/G11/G12</t>
-  </si>
-  <si>
-    <t>TD-PS-MCIL2</t>
-  </si>
-  <si>
-    <t>TD-Electrotechnique fondamentale 1-G4</t>
-  </si>
-  <si>
-    <t>Cours-PS-MCIL2</t>
-  </si>
-  <si>
-    <t>Cours-OV-MCIL2</t>
-  </si>
-  <si>
-    <t>TD-Electronique fondamentale 1-G4</t>
-  </si>
-  <si>
-    <t>labo physique/G21/G22</t>
-  </si>
-  <si>
-    <t>labo physique/G31/G32</t>
   </si>
   <si>
     <t>labo physique/G41/G42</t>
@@ -3842,13 +3839,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G673"/>
+  <dimension ref="A1:G671"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
-  <cols>
-    <col min="1" max="1" width="26.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="19.2857142857143" customWidth="1"/>
-    <col min="5" max="5" width="17.4285714285714" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
@@ -7294,7 +7286,7 @@
         <v>11</v>
       </c>
       <c r="F150" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="G150" t="s">
         <v>235</v>
@@ -7302,7 +7294,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B151" t="s">
         <v>16</v>
@@ -7317,7 +7309,7 @@
         <v>51</v>
       </c>
       <c r="F151" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G151" t="s">
         <v>235</v>
@@ -7325,13 +7317,13 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B152" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C152" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D152" t="s">
         <v>33</v>
@@ -7340,7 +7332,7 @@
         <v>51</v>
       </c>
       <c r="F152" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G152" t="s">
         <v>235</v>
@@ -7348,13 +7340,13 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B153" t="s">
         <v>21</v>
       </c>
       <c r="C153" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D153" t="s">
         <v>22</v>
@@ -7371,7 +7363,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B154" t="s">
         <v>16</v>
@@ -7394,7 +7386,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B155" t="s">
         <v>16</v>
@@ -7417,7 +7409,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B156" t="s">
         <v>8</v>
@@ -7440,10 +7432,10 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B157" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C157" t="s">
         <v>233</v>
@@ -7455,7 +7447,7 @@
         <v>66</v>
       </c>
       <c r="F157" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G157" t="s">
         <v>235</v>
@@ -7463,10 +7455,10 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B158" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C158" t="s">
         <v>186</v>
@@ -7478,7 +7470,7 @@
         <v>66</v>
       </c>
       <c r="F158" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G158" t="s">
         <v>235</v>
@@ -7486,7 +7478,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B159" t="s">
         <v>21</v>
@@ -7509,13 +7501,13 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B160" t="s">
         <v>21</v>
       </c>
       <c r="C160" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D160" t="s">
         <v>26</v>
@@ -7532,7 +7524,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B161" t="s">
         <v>8</v>
@@ -7547,7 +7539,7 @@
         <v>73</v>
       </c>
       <c r="F161" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G161" t="s">
         <v>235</v>
@@ -7555,10 +7547,10 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B162" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C162" t="s">
         <v>233</v>
@@ -7570,7 +7562,7 @@
         <v>73</v>
       </c>
       <c r="F162" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G162" t="s">
         <v>235</v>
@@ -7578,13 +7570,13 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B163" t="s">
         <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D163" t="s">
         <v>22</v>
@@ -7593,7 +7585,7 @@
         <v>73</v>
       </c>
       <c r="F163" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G163" t="s">
         <v>235</v>
@@ -7601,13 +7593,13 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B164" t="s">
         <v>21</v>
       </c>
       <c r="C164" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D164" t="s">
         <v>43</v>
@@ -7624,7 +7616,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B165" t="s">
         <v>8</v>
@@ -7647,10 +7639,10 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B166" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C166" t="s">
         <v>241</v>
@@ -7662,7 +7654,7 @@
         <v>11</v>
       </c>
       <c r="F166" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="G166" t="s">
         <v>272</v>
@@ -7685,7 +7677,7 @@
         <v>11</v>
       </c>
       <c r="F167" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="G167" t="s">
         <v>272</v>
@@ -7731,7 +7723,7 @@
         <v>11</v>
       </c>
       <c r="F169" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="G169" t="s">
         <v>272</v>
@@ -7754,7 +7746,7 @@
         <v>11</v>
       </c>
       <c r="F170" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="G170" t="s">
         <v>272</v>
@@ -7869,7 +7861,7 @@
         <v>51</v>
       </c>
       <c r="F175" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="G175" t="s">
         <v>272</v>
@@ -7906,7 +7898,7 @@
         <v>21</v>
       </c>
       <c r="C177" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D177" t="s">
         <v>22</v>
@@ -7938,7 +7930,7 @@
         <v>51</v>
       </c>
       <c r="F178" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="G178" t="s">
         <v>272</v>
@@ -7961,7 +7953,7 @@
         <v>51</v>
       </c>
       <c r="F179" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="G179" t="s">
         <v>272</v>
@@ -8053,7 +8045,7 @@
         <v>66</v>
       </c>
       <c r="F183" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="G183" t="s">
         <v>272</v>
@@ -8076,7 +8068,7 @@
         <v>66</v>
       </c>
       <c r="F184" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="G184" t="s">
         <v>272</v>
@@ -8136,7 +8128,7 @@
         <v>8</v>
       </c>
       <c r="C187" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D187" t="s">
         <v>22</v>
@@ -8168,7 +8160,7 @@
         <v>73</v>
       </c>
       <c r="F188" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="G188" t="s">
         <v>272</v>
@@ -10008,7 +10000,7 @@
         <v>66</v>
       </c>
       <c r="F268" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="G268" t="s">
         <v>359</v>
@@ -10123,7 +10115,7 @@
         <v>66</v>
       </c>
       <c r="F273" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="G273" t="s">
         <v>359</v>
@@ -10399,7 +10391,7 @@
         <v>66</v>
       </c>
       <c r="F285" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="G285" t="s">
         <v>359</v>
@@ -11724,7 +11716,7 @@
         <v>16</v>
       </c>
       <c r="C343" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D343" t="s">
         <v>10</v>
@@ -11977,7 +11969,7 @@
         <v>21</v>
       </c>
       <c r="C354" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D354" t="s">
         <v>43</v>
@@ -12046,7 +12038,7 @@
         <v>21</v>
       </c>
       <c r="C357" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D357" t="s">
         <v>26</v>
@@ -12138,7 +12130,7 @@
         <v>551</v>
       </c>
       <c r="C361" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D361" t="s">
         <v>33</v>
@@ -12184,7 +12176,7 @@
         <v>551</v>
       </c>
       <c r="C363" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D363" t="s">
         <v>40</v>
@@ -12207,7 +12199,7 @@
         <v>16</v>
       </c>
       <c r="C364" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D364" t="s">
         <v>43</v>
@@ -12253,7 +12245,7 @@
         <v>16</v>
       </c>
       <c r="C366" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D366" t="s">
         <v>26</v>
@@ -12262,7 +12254,7 @@
         <v>51</v>
       </c>
       <c r="F366" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G366" t="s">
         <v>516</v>
@@ -12322,7 +12314,7 @@
         <v>551</v>
       </c>
       <c r="C369" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D369" t="s">
         <v>33</v>
@@ -12368,7 +12360,7 @@
         <v>551</v>
       </c>
       <c r="C371" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D371" t="s">
         <v>40</v>
@@ -12630,7 +12622,7 @@
         <v>73</v>
       </c>
       <c r="F382" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="G382" t="s">
         <v>516</v>
@@ -12776,13 +12768,13 @@
     </row>
     <row r="389" spans="1:7">
       <c r="A389" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B389" t="s">
         <v>591</v>
       </c>
       <c r="C389" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D389" t="s">
         <v>25</v>
@@ -12937,13 +12929,13 @@
     </row>
     <row r="396" spans="1:7">
       <c r="A396" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B396" t="s">
         <v>603</v>
       </c>
       <c r="C396" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D396" t="s">
         <v>64</v>
@@ -13098,13 +13090,13 @@
     </row>
     <row r="403" spans="1:7">
       <c r="A403" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B403" t="s">
         <v>620</v>
       </c>
       <c r="C403" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D403" t="s">
         <v>25</v>
@@ -13374,13 +13366,13 @@
     </row>
     <row r="415" spans="1:7">
       <c r="A415" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B415" t="s">
         <v>631</v>
       </c>
       <c r="C415" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D415" t="s">
         <v>25</v>
@@ -13535,13 +13527,13 @@
     </row>
     <row r="422" spans="1:7">
       <c r="A422" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B422" t="s">
         <v>635</v>
       </c>
       <c r="C422" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D422" t="s">
         <v>64</v>
@@ -13650,13 +13642,13 @@
     </row>
     <row r="427" spans="1:7">
       <c r="A427" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B427" t="s">
         <v>639</v>
       </c>
       <c r="C427" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D427" t="s">
         <v>25</v>
@@ -13788,7 +13780,7 @@
     </row>
     <row r="433" spans="1:7">
       <c r="A433" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B433" t="s">
         <v>649</v>
@@ -13949,13 +13941,13 @@
     </row>
     <row r="440" spans="1:7">
       <c r="A440" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B440" t="s">
         <v>661</v>
       </c>
       <c r="C440" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D440" t="s">
         <v>10</v>
@@ -14248,13 +14240,13 @@
     </row>
     <row r="453" spans="1:7">
       <c r="A453" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B453" t="s">
         <v>678</v>
       </c>
       <c r="C453" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D453" t="s">
         <v>40</v>
@@ -14576,7 +14568,7 @@
         <v>688</v>
       </c>
       <c r="C467" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D467" t="s">
         <v>50</v>
@@ -14622,7 +14614,7 @@
         <v>690</v>
       </c>
       <c r="C469" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D469" t="s">
         <v>33</v>
@@ -14668,7 +14660,7 @@
         <v>690</v>
       </c>
       <c r="C471" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D471" t="s">
         <v>40</v>
@@ -14685,13 +14677,13 @@
     </row>
     <row r="472" spans="1:7">
       <c r="A472" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B472" t="s">
         <v>691</v>
       </c>
       <c r="C472" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D472" t="s">
         <v>64</v>
@@ -14708,13 +14700,13 @@
     </row>
     <row r="473" spans="1:7">
       <c r="A473" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B473" t="s">
         <v>692</v>
       </c>
       <c r="C473" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D473" t="s">
         <v>25</v>
@@ -14777,13 +14769,13 @@
     </row>
     <row r="476" spans="1:7">
       <c r="A476" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B476" t="s">
         <v>696</v>
       </c>
       <c r="C476" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D476" t="s">
         <v>40</v>
@@ -15013,7 +15005,7 @@
         <v>705</v>
       </c>
       <c r="C486" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D486" t="s">
         <v>33</v>
@@ -15059,7 +15051,7 @@
         <v>705</v>
       </c>
       <c r="C488" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D488" t="s">
         <v>40</v>
@@ -15174,7 +15166,7 @@
         <v>709</v>
       </c>
       <c r="C493" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D493" t="s">
         <v>50</v>
@@ -15191,13 +15183,13 @@
     </row>
     <row r="494" spans="1:7">
       <c r="A494" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B494" t="s">
         <v>710</v>
       </c>
       <c r="C494" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D494" t="s">
         <v>64</v>
@@ -15214,13 +15206,13 @@
     </row>
     <row r="495" spans="1:7">
       <c r="A495" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B495" t="s">
         <v>711</v>
       </c>
       <c r="C495" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D495" t="s">
         <v>25</v>
@@ -16738,7 +16730,7 @@
         <v>829</v>
       </c>
       <c r="C561" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D561" t="s">
         <v>25</v>
@@ -17264,36 +17256,36 @@
         <v>866</v>
       </c>
       <c r="B584" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C584" t="s">
-        <v>431</v>
+        <v>45</v>
       </c>
       <c r="D584" t="s">
         <v>10</v>
       </c>
       <c r="E584" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="F584" t="s">
-        <v>540</v>
+        <v>867</v>
       </c>
       <c r="G584" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="585" spans="1:7">
       <c r="A585" t="s">
-        <v>500</v>
+        <v>474</v>
       </c>
       <c r="B585" t="s">
-        <v>868</v>
+        <v>8</v>
       </c>
       <c r="C585" t="s">
-        <v>510</v>
+        <v>600</v>
       </c>
       <c r="D585" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E585" t="s">
         <v>11</v>
@@ -17302,21 +17294,21 @@
         <v>869</v>
       </c>
       <c r="G585" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="586" spans="1:7">
       <c r="A586" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="B586" t="s">
-        <v>868</v>
+        <v>8</v>
       </c>
       <c r="C586" t="s">
-        <v>79</v>
+        <v>475</v>
       </c>
       <c r="D586" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E586" t="s">
         <v>11</v>
@@ -17325,21 +17317,21 @@
         <v>870</v>
       </c>
       <c r="G586" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="587" spans="1:7">
       <c r="A587" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
       <c r="B587" t="s">
-        <v>871</v>
+        <v>8</v>
       </c>
       <c r="C587" t="s">
-        <v>45</v>
+        <v>600</v>
       </c>
       <c r="D587" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E587" t="s">
         <v>11</v>
@@ -17348,87 +17340,87 @@
         <v>869</v>
       </c>
       <c r="G587" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="588" spans="1:7">
       <c r="A588" t="s">
-        <v>872</v>
+        <v>500</v>
       </c>
       <c r="B588" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C588" t="s">
-        <v>79</v>
+        <v>510</v>
       </c>
       <c r="D588" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E588" t="s">
         <v>11</v>
       </c>
       <c r="F588" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="G588" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="589" spans="1:7">
       <c r="A589" t="s">
-        <v>873</v>
+        <v>507</v>
       </c>
       <c r="B589" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C589" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="D589" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E589" t="s">
         <v>11</v>
       </c>
       <c r="F589" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="G589" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="590" spans="1:7">
       <c r="A590" t="s">
+        <v>490</v>
+      </c>
+      <c r="B590" t="s">
         <v>873</v>
-      </c>
-      <c r="B590" t="s">
-        <v>874</v>
       </c>
       <c r="C590" t="s">
         <v>45</v>
       </c>
       <c r="D590" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E590" t="s">
         <v>11</v>
       </c>
       <c r="F590" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="G590" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="591" spans="1:7">
       <c r="A591" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B591" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C591" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="D591" t="s">
         <v>40</v>
@@ -17437,113 +17429,113 @@
         <v>11</v>
       </c>
       <c r="F591" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="G591" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="592" spans="1:7">
       <c r="A592" t="s">
-        <v>123</v>
+        <v>875</v>
       </c>
       <c r="B592" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C592" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="D592" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E592" t="s">
         <v>11</v>
       </c>
       <c r="F592" t="s">
-        <v>540</v>
+        <v>872</v>
       </c>
       <c r="G592" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="593" spans="1:7">
       <c r="A593" t="s">
+        <v>875</v>
+      </c>
+      <c r="B593" t="s">
         <v>876</v>
       </c>
-      <c r="B593" t="s">
-        <v>868</v>
-      </c>
       <c r="C593" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="D593" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E593" t="s">
         <v>11</v>
       </c>
       <c r="F593" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="G593" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="594" spans="1:7">
       <c r="A594" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B594" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="C594" t="s">
         <v>45</v>
       </c>
       <c r="D594" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E594" t="s">
         <v>11</v>
       </c>
       <c r="F594" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="G594" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="595" spans="1:7">
       <c r="A595" t="s">
+        <v>123</v>
+      </c>
+      <c r="B595" t="s">
         <v>877</v>
       </c>
-      <c r="B595" t="s">
-        <v>871</v>
-      </c>
       <c r="C595" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="D595" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E595" t="s">
         <v>11</v>
       </c>
       <c r="F595" t="s">
-        <v>870</v>
+        <v>540</v>
       </c>
       <c r="G595" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="596" spans="1:7">
       <c r="A596" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B596" t="s">
         <v>871</v>
       </c>
       <c r="C596" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D596" t="s">
         <v>64</v>
@@ -17552,300 +17544,300 @@
         <v>11</v>
       </c>
       <c r="F596" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="G596" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="597" spans="1:7">
       <c r="A597" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B597" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="C597" t="s">
-        <v>186</v>
+        <v>45</v>
       </c>
       <c r="D597" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E597" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F597" t="s">
-        <v>880</v>
+        <v>867</v>
       </c>
       <c r="G597" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="598" spans="1:7">
       <c r="A598" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B598" t="s">
-        <v>882</v>
+        <v>873</v>
       </c>
       <c r="C598" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D598" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E598" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F598" t="s">
-        <v>883</v>
+        <v>867</v>
       </c>
       <c r="G598" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="599" spans="1:7">
       <c r="A599" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B599" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="C599" t="s">
-        <v>186</v>
+        <v>53</v>
       </c>
       <c r="D599" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="E599" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F599" t="s">
-        <v>880</v>
+        <v>867</v>
       </c>
       <c r="G599" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="600" spans="1:7">
       <c r="A600" t="s">
+        <v>880</v>
+      </c>
+      <c r="B600" t="s">
         <v>881</v>
       </c>
-      <c r="B600" t="s">
-        <v>882</v>
-      </c>
       <c r="C600" t="s">
-        <v>248</v>
+        <v>186</v>
       </c>
       <c r="D600" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E600" t="s">
         <v>28</v>
       </c>
       <c r="F600" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="G600" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="601" spans="1:7">
       <c r="A601" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B601" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C601" t="s">
-        <v>45</v>
+        <v>249</v>
       </c>
       <c r="D601" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E601" t="s">
         <v>28</v>
       </c>
       <c r="F601" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="G601" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="602" spans="1:7">
       <c r="A602" t="s">
-        <v>474</v>
+        <v>880</v>
       </c>
       <c r="B602" t="s">
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="C602" t="s">
-        <v>475</v>
+        <v>186</v>
       </c>
       <c r="D602" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E602" t="s">
         <v>28</v>
       </c>
       <c r="F602" t="s">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="G602" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="603" spans="1:7">
       <c r="A603" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B603" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C603" t="s">
-        <v>45</v>
+        <v>249</v>
       </c>
       <c r="D603" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E603" t="s">
         <v>28</v>
       </c>
       <c r="F603" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="G603" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="604" spans="1:7">
       <c r="A604" t="s">
-        <v>878</v>
+        <v>887</v>
       </c>
       <c r="B604" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="C604" t="s">
-        <v>890</v>
+        <v>45</v>
       </c>
       <c r="D604" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E604" t="s">
         <v>28</v>
       </c>
       <c r="F604" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G604" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="605" spans="1:7">
       <c r="A605" t="s">
-        <v>881</v>
+        <v>474</v>
       </c>
       <c r="B605" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="C605" t="s">
-        <v>174</v>
+        <v>475</v>
       </c>
       <c r="D605" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E605" t="s">
         <v>28</v>
       </c>
       <c r="F605" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G605" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="606" spans="1:7">
       <c r="A606" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B606" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C606" t="s">
         <v>45</v>
       </c>
       <c r="D606" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E606" t="s">
         <v>28</v>
       </c>
       <c r="F606" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="G606" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="607" spans="1:7">
       <c r="A607" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B607" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C607" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="D607" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E607" t="s">
         <v>28</v>
       </c>
       <c r="F607" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="G607" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="608" spans="1:7">
       <c r="A608" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B608" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="C608" t="s">
         <v>174</v>
       </c>
       <c r="D608" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E608" t="s">
         <v>28</v>
       </c>
       <c r="F608" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="G608" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="609" spans="1:7">
       <c r="A609" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B609" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C609" t="s">
         <v>45</v>
       </c>
       <c r="D609" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E609" t="s">
         <v>28</v>
@@ -17854,527 +17846,527 @@
         <v>895</v>
       </c>
       <c r="G609" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="610" spans="1:7">
       <c r="A610" t="s">
-        <v>468</v>
+        <v>880</v>
       </c>
       <c r="B610" t="s">
-        <v>21</v>
+        <v>881</v>
       </c>
       <c r="C610" t="s">
-        <v>338</v>
+        <v>892</v>
       </c>
       <c r="D610" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="E610" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F610" t="s">
-        <v>540</v>
+        <v>896</v>
       </c>
       <c r="G610" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="611" spans="1:7">
       <c r="A611" t="s">
-        <v>500</v>
+        <v>883</v>
       </c>
       <c r="B611" t="s">
+        <v>884</v>
+      </c>
+      <c r="C611" t="s">
+        <v>174</v>
+      </c>
+      <c r="D611" t="s">
+        <v>64</v>
+      </c>
+      <c r="E611" t="s">
+        <v>28</v>
+      </c>
+      <c r="F611" t="s">
+        <v>894</v>
+      </c>
+      <c r="G611" t="s">
         <v>868</v>
-      </c>
-      <c r="C611" t="s">
-        <v>79</v>
-      </c>
-      <c r="D611" t="s">
-        <v>29</v>
-      </c>
-      <c r="E611" t="s">
-        <v>51</v>
-      </c>
-      <c r="F611" t="s">
-        <v>869</v>
-      </c>
-      <c r="G611" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="612" spans="1:7">
       <c r="A612" t="s">
-        <v>508</v>
+        <v>887</v>
       </c>
       <c r="B612" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="C612" t="s">
-        <v>514</v>
+        <v>45</v>
       </c>
       <c r="D612" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="E612" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F612" t="s">
-        <v>869</v>
+        <v>897</v>
       </c>
       <c r="G612" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="613" spans="1:7">
       <c r="A613" t="s">
-        <v>885</v>
+        <v>468</v>
       </c>
       <c r="B613" t="s">
-        <v>886</v>
+        <v>21</v>
       </c>
       <c r="C613" t="s">
-        <v>486</v>
+        <v>338</v>
       </c>
       <c r="D613" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="E613" t="s">
         <v>51</v>
       </c>
       <c r="F613" t="s">
-        <v>897</v>
+        <v>540</v>
       </c>
       <c r="G613" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="614" spans="1:7">
       <c r="A614" t="s">
-        <v>881</v>
+        <v>500</v>
       </c>
       <c r="B614" t="s">
-        <v>882</v>
+        <v>871</v>
       </c>
       <c r="C614" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="D614" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E614" t="s">
         <v>51</v>
       </c>
       <c r="F614" t="s">
-        <v>898</v>
+        <v>872</v>
       </c>
       <c r="G614" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="615" spans="1:7">
       <c r="A615" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B615" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C615" t="s">
         <v>514</v>
       </c>
       <c r="D615" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E615" t="s">
         <v>51</v>
       </c>
       <c r="F615" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="G615" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="616" spans="1:7">
       <c r="A616" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B616" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C616" t="s">
         <v>486</v>
       </c>
       <c r="D616" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E616" t="s">
         <v>51</v>
       </c>
       <c r="F616" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="G616" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="617" spans="1:7">
       <c r="A617" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B617" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="C617" t="s">
         <v>45</v>
       </c>
       <c r="D617" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E617" t="s">
         <v>51</v>
       </c>
       <c r="F617" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="G617" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="618" spans="1:7">
       <c r="A618" t="s">
-        <v>129</v>
+        <v>511</v>
       </c>
       <c r="B618" t="s">
-        <v>21</v>
+        <v>898</v>
       </c>
       <c r="C618" t="s">
-        <v>428</v>
+        <v>514</v>
       </c>
       <c r="D618" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E618" t="s">
         <v>51</v>
       </c>
       <c r="F618" t="s">
-        <v>540</v>
+        <v>867</v>
       </c>
       <c r="G618" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="619" spans="1:7">
       <c r="A619" t="s">
-        <v>899</v>
+        <v>887</v>
       </c>
       <c r="B619" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="C619" t="s">
-        <v>45</v>
+        <v>486</v>
       </c>
       <c r="D619" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E619" t="s">
         <v>51</v>
       </c>
       <c r="F619" t="s">
-        <v>870</v>
+        <v>899</v>
       </c>
       <c r="G619" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="620" spans="1:7">
       <c r="A620" t="s">
-        <v>900</v>
+        <v>883</v>
       </c>
       <c r="B620" t="s">
-        <v>871</v>
+        <v>884</v>
       </c>
       <c r="C620" t="s">
         <v>45</v>
       </c>
       <c r="D620" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E620" t="s">
         <v>51</v>
       </c>
       <c r="F620" t="s">
-        <v>869</v>
+        <v>900</v>
       </c>
       <c r="G620" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="621" spans="1:7">
       <c r="A621" t="s">
-        <v>901</v>
+        <v>129</v>
       </c>
       <c r="B621" t="s">
-        <v>902</v>
+        <v>21</v>
       </c>
       <c r="C621" t="s">
-        <v>504</v>
+        <v>428</v>
       </c>
       <c r="D621" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E621" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F621" t="s">
         <v>540</v>
       </c>
       <c r="G621" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="622" spans="1:7">
       <c r="A622" t="s">
-        <v>507</v>
+        <v>901</v>
       </c>
       <c r="B622" t="s">
+        <v>898</v>
+      </c>
+      <c r="C622" t="s">
+        <v>45</v>
+      </c>
+      <c r="D622" t="s">
+        <v>64</v>
+      </c>
+      <c r="E622" t="s">
+        <v>51</v>
+      </c>
+      <c r="F622" t="s">
+        <v>867</v>
+      </c>
+      <c r="G622" t="s">
         <v>868</v>
-      </c>
-      <c r="C622" t="s">
-        <v>79</v>
-      </c>
-      <c r="D622" t="s">
-        <v>29</v>
-      </c>
-      <c r="E622" t="s">
-        <v>66</v>
-      </c>
-      <c r="F622" t="s">
-        <v>870</v>
-      </c>
-      <c r="G622" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="623" spans="1:7">
       <c r="A623" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B623" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C623" t="s">
-        <v>890</v>
+        <v>45</v>
       </c>
       <c r="D623" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="E623" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F623" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="G623" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="624" spans="1:7">
       <c r="A624" t="s">
+        <v>903</v>
+      </c>
+      <c r="B624" t="s">
         <v>904</v>
       </c>
-      <c r="B624" t="s">
-        <v>874</v>
-      </c>
       <c r="C624" t="s">
-        <v>890</v>
+        <v>504</v>
       </c>
       <c r="D624" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E624" t="s">
         <v>66</v>
       </c>
       <c r="F624" t="s">
-        <v>869</v>
+        <v>540</v>
       </c>
       <c r="G624" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="625" spans="1:7">
       <c r="A625" t="s">
-        <v>905</v>
+        <v>507</v>
       </c>
       <c r="B625" t="s">
-        <v>879</v>
+        <v>871</v>
       </c>
       <c r="C625" t="s">
-        <v>906</v>
+        <v>79</v>
       </c>
       <c r="D625" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E625" t="s">
         <v>66</v>
       </c>
       <c r="F625" t="s">
-        <v>907</v>
+        <v>867</v>
       </c>
       <c r="G625" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="626" spans="1:7">
       <c r="A626" t="s">
-        <v>498</v>
+        <v>905</v>
       </c>
       <c r="B626" t="s">
-        <v>908</v>
+        <v>876</v>
       </c>
       <c r="C626" t="s">
-        <v>45</v>
+        <v>892</v>
       </c>
       <c r="D626" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E626" t="s">
         <v>66</v>
       </c>
       <c r="F626" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="G626" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="627" spans="1:7">
       <c r="A627" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="B627" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C627" t="s">
-        <v>472</v>
+        <v>892</v>
       </c>
       <c r="D627" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E627" t="s">
         <v>66</v>
       </c>
       <c r="F627" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="G627" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="628" spans="1:7">
       <c r="A628" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B628" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C628" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="D628" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E628" t="s">
         <v>66</v>
       </c>
       <c r="F628" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="G628" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="629" spans="1:7">
       <c r="A629" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="B629" t="s">
         <v>910</v>
       </c>
       <c r="C629" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="D629" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E629" t="s">
         <v>66</v>
       </c>
       <c r="F629" t="s">
-        <v>540</v>
+        <v>867</v>
       </c>
       <c r="G629" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="630" spans="1:7">
       <c r="A630" t="s">
-        <v>85</v>
+        <v>911</v>
       </c>
       <c r="B630" t="s">
-        <v>911</v>
+        <v>876</v>
       </c>
       <c r="C630" t="s">
-        <v>45</v>
+        <v>472</v>
       </c>
       <c r="D630" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E630" t="s">
         <v>66</v>
       </c>
       <c r="F630" t="s">
-        <v>540</v>
+        <v>872</v>
       </c>
       <c r="G630" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="631" spans="1:7">
       <c r="A631" t="s">
-        <v>85</v>
+        <v>907</v>
       </c>
       <c r="B631" t="s">
-        <v>911</v>
+        <v>881</v>
       </c>
       <c r="C631" t="s">
-        <v>45</v>
+        <v>908</v>
       </c>
       <c r="D631" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E631" t="s">
         <v>66</v>
       </c>
       <c r="F631" t="s">
-        <v>540</v>
+        <v>909</v>
       </c>
       <c r="G631" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="632" spans="1:7">
       <c r="A632" t="s">
-        <v>85</v>
+        <v>488</v>
       </c>
       <c r="B632" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C632" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="D632" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E632" t="s">
         <v>66</v>
@@ -18383,53 +18375,53 @@
         <v>540</v>
       </c>
       <c r="G632" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="633" spans="1:7">
       <c r="A633" t="s">
-        <v>912</v>
+        <v>85</v>
       </c>
       <c r="B633" t="s">
-        <v>16</v>
+        <v>913</v>
       </c>
       <c r="C633" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D633" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="E633" t="s">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="F633" t="s">
-        <v>870</v>
+        <v>540</v>
       </c>
       <c r="G633" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="634" spans="1:7">
       <c r="A634" t="s">
-        <v>474</v>
+        <v>914</v>
       </c>
       <c r="B634" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C634" t="s">
-        <v>600</v>
+        <v>431</v>
       </c>
       <c r="D634" t="s">
         <v>10</v>
       </c>
       <c r="E634" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="F634" t="s">
-        <v>913</v>
+        <v>540</v>
       </c>
       <c r="G634" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="635" spans="1:7">
@@ -18437,56 +18429,56 @@
         <v>474</v>
       </c>
       <c r="B635" t="s">
-        <v>8</v>
+        <v>890</v>
       </c>
       <c r="C635" t="s">
         <v>475</v>
       </c>
       <c r="D635" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="E635" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="F635" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="G635" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="636" spans="1:7">
       <c r="A636" t="s">
-        <v>474</v>
+        <v>874</v>
       </c>
       <c r="B636" t="s">
-        <v>8</v>
+        <v>871</v>
       </c>
       <c r="C636" t="s">
-        <v>600</v>
+        <v>510</v>
       </c>
       <c r="D636" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="E636" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="F636" t="s">
-        <v>913</v>
+        <v>872</v>
       </c>
       <c r="G636" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="637" spans="1:7">
       <c r="A637" t="s">
-        <v>474</v>
+        <v>916</v>
       </c>
       <c r="B637" t="s">
-        <v>888</v>
+        <v>910</v>
       </c>
       <c r="C637" t="s">
-        <v>475</v>
+        <v>45</v>
       </c>
       <c r="D637" t="s">
         <v>33</v>
@@ -18495,61 +18487,61 @@
         <v>73</v>
       </c>
       <c r="F637" t="s">
-        <v>915</v>
+        <v>867</v>
       </c>
       <c r="G637" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="638" spans="1:7">
       <c r="A638" t="s">
-        <v>872</v>
+        <v>459</v>
       </c>
       <c r="B638" t="s">
-        <v>868</v>
+        <v>16</v>
       </c>
       <c r="C638" t="s">
-        <v>510</v>
+        <v>45</v>
       </c>
       <c r="D638" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E638" t="s">
         <v>73</v>
       </c>
       <c r="F638" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="G638" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="639" spans="1:7">
       <c r="A639" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B639" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="C639" t="s">
         <v>45</v>
       </c>
       <c r="D639" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E639" t="s">
         <v>73</v>
       </c>
       <c r="F639" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="G639" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="640" spans="1:7">
       <c r="A640" t="s">
-        <v>459</v>
+        <v>502</v>
       </c>
       <c r="B640" t="s">
         <v>16</v>
@@ -18558,128 +18550,128 @@
         <v>45</v>
       </c>
       <c r="D640" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="E640" t="s">
         <v>73</v>
       </c>
       <c r="F640" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="G640" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="641" spans="1:7">
       <c r="A641" t="s">
-        <v>917</v>
+        <v>878</v>
       </c>
       <c r="B641" t="s">
-        <v>908</v>
+        <v>871</v>
       </c>
       <c r="C641" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="D641" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E641" t="s">
         <v>73</v>
       </c>
       <c r="F641" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="G641" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="642" spans="1:7">
       <c r="A642" t="s">
-        <v>502</v>
+        <v>918</v>
       </c>
       <c r="B642" t="s">
-        <v>16</v>
+        <v>919</v>
       </c>
       <c r="C642" t="s">
-        <v>45</v>
+        <v>514</v>
       </c>
       <c r="D642" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="E642" t="s">
         <v>73</v>
       </c>
       <c r="F642" t="s">
-        <v>869</v>
+        <v>540</v>
       </c>
       <c r="G642" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="643" spans="1:7">
       <c r="A643" t="s">
-        <v>876</v>
+        <v>920</v>
       </c>
       <c r="B643" t="s">
-        <v>868</v>
+        <v>16</v>
       </c>
       <c r="C643" t="s">
-        <v>79</v>
+        <v>347</v>
       </c>
       <c r="D643" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E643" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="F643" t="s">
-        <v>870</v>
+        <v>320</v>
       </c>
       <c r="G643" t="s">
-        <v>867</v>
+        <v>921</v>
       </c>
     </row>
     <row r="644" spans="1:7">
       <c r="A644" t="s">
-        <v>918</v>
+        <v>557</v>
       </c>
       <c r="B644" t="s">
-        <v>919</v>
+        <v>16</v>
       </c>
       <c r="C644" t="s">
-        <v>514</v>
+        <v>218</v>
       </c>
       <c r="D644" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="E644" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="F644" t="s">
-        <v>540</v>
+        <v>336</v>
       </c>
       <c r="G644" t="s">
-        <v>867</v>
+        <v>921</v>
       </c>
     </row>
     <row r="645" spans="1:7">
       <c r="A645" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B645" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C645" t="s">
-        <v>347</v>
+        <v>199</v>
       </c>
       <c r="D645" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E645" t="s">
         <v>11</v>
       </c>
       <c r="F645" t="s">
-        <v>320</v>
+        <v>60</v>
       </c>
       <c r="G645" t="s">
         <v>921</v>
@@ -18687,22 +18679,22 @@
     </row>
     <row r="646" spans="1:7">
       <c r="A646" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="B646" t="s">
         <v>16</v>
       </c>
       <c r="C646" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="D646" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E646" t="s">
         <v>11</v>
       </c>
       <c r="F646" t="s">
-        <v>336</v>
+        <v>60</v>
       </c>
       <c r="G646" t="s">
         <v>921</v>
@@ -18710,22 +18702,22 @@
     </row>
     <row r="647" spans="1:7">
       <c r="A647" t="s">
-        <v>922</v>
+        <v>538</v>
       </c>
       <c r="B647" t="s">
         <v>21</v>
       </c>
       <c r="C647" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="D647" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E647" t="s">
         <v>11</v>
       </c>
       <c r="F647" t="s">
-        <v>60</v>
+        <v>336</v>
       </c>
       <c r="G647" t="s">
         <v>921</v>
@@ -18733,22 +18725,22 @@
     </row>
     <row r="648" spans="1:7">
       <c r="A648" t="s">
-        <v>548</v>
+        <v>923</v>
       </c>
       <c r="B648" t="s">
         <v>16</v>
       </c>
       <c r="C648" t="s">
-        <v>199</v>
+        <v>347</v>
       </c>
       <c r="D648" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E648" t="s">
         <v>11</v>
       </c>
       <c r="F648" t="s">
-        <v>60</v>
+        <v>461</v>
       </c>
       <c r="G648" t="s">
         <v>921</v>
@@ -18756,16 +18748,16 @@
     </row>
     <row r="649" spans="1:7">
       <c r="A649" t="s">
-        <v>538</v>
+        <v>924</v>
       </c>
       <c r="B649" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C649" t="s">
         <v>218</v>
       </c>
       <c r="D649" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E649" t="s">
         <v>11</v>
@@ -18779,22 +18771,22 @@
     </row>
     <row r="650" spans="1:7">
       <c r="A650" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B650" t="s">
-        <v>16</v>
+        <v>926</v>
       </c>
       <c r="C650" t="s">
-        <v>347</v>
+        <v>543</v>
       </c>
       <c r="D650" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E650" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F650" t="s">
-        <v>461</v>
+        <v>46</v>
       </c>
       <c r="G650" t="s">
         <v>921</v>
@@ -18802,22 +18794,22 @@
     </row>
     <row r="651" spans="1:7">
       <c r="A651" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B651" t="s">
         <v>16</v>
       </c>
       <c r="C651" t="s">
-        <v>218</v>
+        <v>347</v>
       </c>
       <c r="D651" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E651" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="F651" t="s">
-        <v>336</v>
+        <v>461</v>
       </c>
       <c r="G651" t="s">
         <v>921</v>
@@ -18825,22 +18817,22 @@
     </row>
     <row r="652" spans="1:7">
       <c r="A652" t="s">
-        <v>925</v>
+        <v>544</v>
       </c>
       <c r="B652" t="s">
-        <v>926</v>
+        <v>16</v>
       </c>
       <c r="C652" t="s">
-        <v>543</v>
+        <v>218</v>
       </c>
       <c r="D652" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E652" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F652" t="s">
-        <v>46</v>
+        <v>336</v>
       </c>
       <c r="G652" t="s">
         <v>921</v>
@@ -18848,13 +18840,13 @@
     </row>
     <row r="653" spans="1:7">
       <c r="A653" t="s">
-        <v>927</v>
+        <v>546</v>
       </c>
       <c r="B653" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C653" t="s">
-        <v>347</v>
+        <v>177</v>
       </c>
       <c r="D653" t="s">
         <v>10</v>
@@ -18863,7 +18855,7 @@
         <v>51</v>
       </c>
       <c r="F653" t="s">
-        <v>461</v>
+        <v>579</v>
       </c>
       <c r="G653" t="s">
         <v>921</v>
@@ -18871,16 +18863,16 @@
     </row>
     <row r="654" spans="1:7">
       <c r="A654" t="s">
-        <v>544</v>
+        <v>928</v>
       </c>
       <c r="B654" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C654" t="s">
-        <v>218</v>
+        <v>719</v>
       </c>
       <c r="D654" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E654" t="s">
         <v>51</v>
@@ -18894,22 +18886,22 @@
     </row>
     <row r="655" spans="1:7">
       <c r="A655" t="s">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="B655" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C655" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="D655" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E655" t="s">
         <v>51</v>
       </c>
       <c r="F655" t="s">
-        <v>579</v>
+        <v>461</v>
       </c>
       <c r="G655" t="s">
         <v>921</v>
@@ -18917,16 +18909,16 @@
     </row>
     <row r="656" spans="1:7">
       <c r="A656" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B656" t="s">
         <v>21</v>
       </c>
       <c r="C656" t="s">
-        <v>719</v>
+        <v>179</v>
       </c>
       <c r="D656" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E656" t="s">
         <v>51</v>
@@ -18940,22 +18932,22 @@
     </row>
     <row r="657" spans="1:7">
       <c r="A657" t="s">
-        <v>556</v>
+        <v>930</v>
       </c>
       <c r="B657" t="s">
         <v>16</v>
       </c>
       <c r="C657" t="s">
-        <v>199</v>
+        <v>328</v>
       </c>
       <c r="D657" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E657" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F657" t="s">
-        <v>461</v>
+        <v>336</v>
       </c>
       <c r="G657" t="s">
         <v>921</v>
@@ -18963,22 +18955,22 @@
     </row>
     <row r="658" spans="1:7">
       <c r="A658" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B658" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C658" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="D658" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="E658" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F658" t="s">
-        <v>336</v>
+        <v>19</v>
       </c>
       <c r="G658" t="s">
         <v>921</v>
@@ -18986,22 +18978,22 @@
     </row>
     <row r="659" spans="1:7">
       <c r="A659" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B659" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C659" t="s">
-        <v>328</v>
+        <v>179</v>
       </c>
       <c r="D659" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E659" t="s">
         <v>66</v>
       </c>
       <c r="F659" t="s">
-        <v>336</v>
+        <v>933</v>
       </c>
       <c r="G659" t="s">
         <v>921</v>
@@ -19009,22 +19001,22 @@
     </row>
     <row r="660" spans="1:7">
       <c r="A660" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="B660" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C660" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="D660" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E660" t="s">
         <v>66</v>
       </c>
       <c r="F660" t="s">
-        <v>19</v>
+        <v>933</v>
       </c>
       <c r="G660" t="s">
         <v>921</v>
@@ -19032,22 +19024,22 @@
     </row>
     <row r="661" spans="1:7">
       <c r="A661" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B661" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C661" t="s">
-        <v>179</v>
+        <v>347</v>
       </c>
       <c r="D661" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E661" t="s">
         <v>66</v>
       </c>
       <c r="F661" t="s">
-        <v>933</v>
+        <v>336</v>
       </c>
       <c r="G661" t="s">
         <v>921</v>
@@ -19055,22 +19047,22 @@
     </row>
     <row r="662" spans="1:7">
       <c r="A662" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B662" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C662" t="s">
-        <v>179</v>
+        <v>328</v>
       </c>
       <c r="D662" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E662" t="s">
         <v>66</v>
       </c>
       <c r="F662" t="s">
-        <v>933</v>
+        <v>336</v>
       </c>
       <c r="G662" t="s">
         <v>921</v>
@@ -19078,22 +19070,22 @@
     </row>
     <row r="663" spans="1:7">
       <c r="A663" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="B663" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C663" t="s">
-        <v>347</v>
+        <v>191</v>
       </c>
       <c r="D663" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="E663" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F663" t="s">
-        <v>336</v>
+        <v>938</v>
       </c>
       <c r="G663" t="s">
         <v>921</v>
@@ -19101,22 +19093,22 @@
     </row>
     <row r="664" spans="1:7">
       <c r="A664" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="B664" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C664" t="s">
         <v>328</v>
       </c>
       <c r="D664" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E664" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F664" t="s">
-        <v>336</v>
+        <v>461</v>
       </c>
       <c r="G664" t="s">
         <v>921</v>
@@ -19124,22 +19116,22 @@
     </row>
     <row r="665" spans="1:7">
       <c r="A665" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="B665" t="s">
         <v>8</v>
       </c>
       <c r="C665" t="s">
-        <v>191</v>
+        <v>486</v>
       </c>
       <c r="D665" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E665" t="s">
         <v>73</v>
       </c>
       <c r="F665" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="G665" t="s">
         <v>921</v>
@@ -19147,22 +19139,22 @@
     </row>
     <row r="666" spans="1:7">
       <c r="A666" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="B666" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C666" t="s">
-        <v>328</v>
+        <v>45</v>
       </c>
       <c r="D666" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E666" t="s">
         <v>73</v>
       </c>
       <c r="F666" t="s">
-        <v>461</v>
+        <v>99</v>
       </c>
       <c r="G666" t="s">
         <v>921</v>
@@ -19170,7 +19162,7 @@
     </row>
     <row r="667" spans="1:7">
       <c r="A667" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="B667" t="s">
         <v>8</v>
@@ -19179,7 +19171,7 @@
         <v>486</v>
       </c>
       <c r="D667" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E667" t="s">
         <v>73</v>
@@ -19193,7 +19185,7 @@
     </row>
     <row r="668" spans="1:7">
       <c r="A668" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="B668" t="s">
         <v>8</v>
@@ -19202,7 +19194,7 @@
         <v>45</v>
       </c>
       <c r="D668" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E668" t="s">
         <v>73</v>
@@ -19216,22 +19208,22 @@
     </row>
     <row r="669" spans="1:7">
       <c r="A669" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
       <c r="B669" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C669" t="s">
-        <v>486</v>
+        <v>328</v>
       </c>
       <c r="D669" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="E669" t="s">
         <v>73</v>
       </c>
       <c r="F669" t="s">
-        <v>941</v>
+        <v>336</v>
       </c>
       <c r="G669" t="s">
         <v>921</v>
@@ -19239,22 +19231,22 @@
     </row>
     <row r="670" spans="1:7">
       <c r="A670" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B670" t="s">
         <v>8</v>
       </c>
       <c r="C670" t="s">
-        <v>45</v>
+        <v>191</v>
       </c>
       <c r="D670" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E670" t="s">
         <v>73</v>
       </c>
       <c r="F670" t="s">
-        <v>99</v>
+        <v>946</v>
       </c>
       <c r="G670" t="s">
         <v>921</v>
@@ -19262,77 +19254,28 @@
     </row>
     <row r="671" spans="1:7">
       <c r="A671" t="s">
-        <v>936</v>
+        <v>947</v>
       </c>
       <c r="B671" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C671" t="s">
         <v>328</v>
       </c>
       <c r="D671" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E671" t="s">
         <v>73</v>
       </c>
       <c r="F671" t="s">
-        <v>336</v>
+        <v>461</v>
       </c>
       <c r="G671" t="s">
         <v>921</v>
       </c>
     </row>
-    <row r="672" spans="1:7">
-      <c r="A672" t="s">
-        <v>945</v>
-      </c>
-      <c r="B672" t="s">
-        <v>8</v>
-      </c>
-      <c r="C672" t="s">
-        <v>191</v>
-      </c>
-      <c r="D672" t="s">
-        <v>26</v>
-      </c>
-      <c r="E672" t="s">
-        <v>73</v>
-      </c>
-      <c r="F672" t="s">
-        <v>946</v>
-      </c>
-      <c r="G672" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="673" spans="1:7">
-      <c r="A673" t="s">
-        <v>947</v>
-      </c>
-      <c r="B673" t="s">
-        <v>16</v>
-      </c>
-      <c r="C673" t="s">
-        <v>328</v>
-      </c>
-      <c r="D673" t="s">
-        <v>26</v>
-      </c>
-      <c r="E673" t="s">
-        <v>73</v>
-      </c>
-      <c r="F673" t="s">
-        <v>461</v>
-      </c>
-      <c r="G673" t="s">
-        <v>921</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G673" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -9,9 +9,6 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$669</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -6248,7 +6245,7 @@
         <v>10</v>
       </c>
       <c r="E105" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="F105" t="s">
         <v>164</v>
@@ -12021,7 +12018,7 @@
         <v>10</v>
       </c>
       <c r="E356" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F356" t="s">
         <v>547</v>
@@ -12041,7 +12038,7 @@
         <v>177</v>
       </c>
       <c r="D357" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E357" t="s">
         <v>44</v>
@@ -12205,7 +12202,7 @@
         <v>18</v>
       </c>
       <c r="E364" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F364" t="s">
         <v>249</v>
@@ -12228,7 +12225,7 @@
         <v>18</v>
       </c>
       <c r="E365" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F365" t="s">
         <v>560</v>
@@ -18803,7 +18800,7 @@
         <v>177</v>
       </c>
       <c r="D651" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E651" t="s">
         <v>44</v>
@@ -19230,9 +19227,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G669" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$669</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4683" uniqueCount="947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4683" uniqueCount="946">
   <si>
     <t>Enseignements</t>
   </si>
@@ -203,7 +206,7 @@
     <t>Cours-DEDF-ING1</t>
   </si>
   <si>
-    <t>OUARI KHERIA</t>
+    <t>OUARI KHEIRA</t>
   </si>
   <si>
     <t>9h30 -11h</t>
@@ -821,7 +824,7 @@
     <t>Cours-CE-ING4EI</t>
   </si>
   <si>
-    <t>SALAH HANAFI</t>
+    <t>HANAFI SALAH</t>
   </si>
   <si>
     <t>Cours-Machines électriques approfondies</t>
@@ -2283,9 +2286,6 @@
   </si>
   <si>
     <t>TP-Stockage de l'énergie-SG1</t>
-  </si>
-  <si>
-    <t>KOUIDRI</t>
   </si>
   <si>
     <t>Cours-Applications et dimensionnement des systèmes à énergies renouvelables</t>
@@ -3835,9 +3835,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G669"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="68.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
@@ -3862,7 +3866,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" hidden="1" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -3885,7 +3889,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" hidden="1" spans="1:7">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -3908,7 +3912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" hidden="1" spans="1:7">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -3931,7 +3935,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" hidden="1" spans="1:7">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -3954,7 +3958,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" hidden="1" spans="1:7">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -3977,7 +3981,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" hidden="1" spans="1:7">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -4000,7 +4004,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" hidden="1" spans="1:7">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -4023,7 +4027,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" hidden="1" spans="1:7">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -4046,7 +4050,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" hidden="1" spans="1:7">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -4069,7 +4073,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" hidden="1" spans="1:7">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -4092,7 +4096,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" hidden="1" spans="1:7">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -4115,7 +4119,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" hidden="1" spans="1:7">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -4138,7 +4142,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" hidden="1" spans="1:7">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -4161,7 +4165,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" hidden="1" spans="1:7">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -4184,7 +4188,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" hidden="1" spans="1:7">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -4207,7 +4211,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" hidden="1" spans="1:7">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -4230,7 +4234,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" hidden="1" spans="1:7">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -4253,7 +4257,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" hidden="1" spans="1:7">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -4276,7 +4280,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" hidden="1" spans="1:7">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -4299,7 +4303,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" hidden="1" spans="1:7">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -4322,7 +4326,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" hidden="1" spans="1:7">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -4345,7 +4349,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" hidden="1" spans="1:7">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -4368,7 +4372,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" hidden="1" spans="1:7">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -4391,7 +4395,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" hidden="1" spans="1:7">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -4414,7 +4418,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" hidden="1" spans="1:7">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -4437,7 +4441,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" hidden="1" spans="1:7">
       <c r="A27" t="s">
         <v>56</v>
       </c>
@@ -4460,7 +4464,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" hidden="1" spans="1:7">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -4483,7 +4487,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" hidden="1" spans="1:7">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -4506,7 +4510,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" hidden="1" spans="1:7">
       <c r="A30" t="s">
         <v>22</v>
       </c>
@@ -4529,7 +4533,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" hidden="1" spans="1:7">
       <c r="A31" t="s">
         <v>28</v>
       </c>
@@ -4552,7 +4556,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" hidden="1" spans="1:7">
       <c r="A32" t="s">
         <v>22</v>
       </c>
@@ -4575,7 +4579,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" hidden="1" spans="1:7">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -4598,7 +4602,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" hidden="1" spans="1:7">
       <c r="A34" t="s">
         <v>22</v>
       </c>
@@ -4621,7 +4625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" hidden="1" spans="1:7">
       <c r="A35" t="s">
         <v>28</v>
       </c>
@@ -4644,7 +4648,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" hidden="1" spans="1:7">
       <c r="A36" t="s">
         <v>65</v>
       </c>
@@ -4667,7 +4671,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" hidden="1" spans="1:7">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -4690,7 +4694,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" hidden="1" spans="1:7">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -4713,7 +4717,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" hidden="1" spans="1:7">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -4736,7 +4740,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" hidden="1" spans="1:7">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -4759,7 +4763,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" hidden="1" spans="1:7">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -4782,7 +4786,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" hidden="1" spans="1:7">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -4805,7 +4809,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" hidden="1" spans="1:7">
       <c r="A43" t="s">
         <v>69</v>
       </c>
@@ -4828,7 +4832,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" hidden="1" spans="1:7">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -4851,7 +4855,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" hidden="1" spans="1:7">
       <c r="A45" t="s">
         <v>75</v>
       </c>
@@ -4874,7 +4878,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" hidden="1" spans="1:7">
       <c r="A46" t="s">
         <v>78</v>
       </c>
@@ -4897,7 +4901,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" hidden="1" spans="1:7">
       <c r="A47" t="s">
         <v>79</v>
       </c>
@@ -4920,7 +4924,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" hidden="1" spans="1:7">
       <c r="A48" t="s">
         <v>65</v>
       </c>
@@ -4943,7 +4947,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" hidden="1" spans="1:7">
       <c r="A49" t="s">
         <v>82</v>
       </c>
@@ -4966,7 +4970,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" hidden="1" spans="1:7">
       <c r="A50" t="s">
         <v>84</v>
       </c>
@@ -4989,7 +4993,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" hidden="1" spans="1:7">
       <c r="A51" t="s">
         <v>88</v>
       </c>
@@ -5012,7 +5016,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" hidden="1" spans="1:7">
       <c r="A52" t="s">
         <v>92</v>
       </c>
@@ -5035,7 +5039,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" hidden="1" spans="1:7">
       <c r="A53" t="s">
         <v>95</v>
       </c>
@@ -5058,7 +5062,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" hidden="1" spans="1:7">
       <c r="A54" t="s">
         <v>97</v>
       </c>
@@ -5081,7 +5085,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" hidden="1" spans="1:7">
       <c r="A55" t="s">
         <v>100</v>
       </c>
@@ -5104,7 +5108,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" hidden="1" spans="1:7">
       <c r="A56" t="s">
         <v>102</v>
       </c>
@@ -5127,7 +5131,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" hidden="1" spans="1:7">
       <c r="A57" t="s">
         <v>104</v>
       </c>
@@ -5150,7 +5154,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" hidden="1" spans="1:7">
       <c r="A58" t="s">
         <v>107</v>
       </c>
@@ -5173,7 +5177,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" hidden="1" spans="1:7">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -5196,7 +5200,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" hidden="1" spans="1:7">
       <c r="A60" t="s">
         <v>113</v>
       </c>
@@ -5219,7 +5223,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" hidden="1" spans="1:7">
       <c r="A61" t="s">
         <v>117</v>
       </c>
@@ -5242,7 +5246,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" hidden="1" spans="1:7">
       <c r="A62" t="s">
         <v>117</v>
       </c>
@@ -5265,7 +5269,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" hidden="1" spans="1:7">
       <c r="A63" t="s">
         <v>120</v>
       </c>
@@ -5288,7 +5292,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" hidden="1" spans="1:7">
       <c r="A64" t="s">
         <v>124</v>
       </c>
@@ -5311,7 +5315,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" hidden="1" spans="1:7">
       <c r="A65" t="s">
         <v>126</v>
       </c>
@@ -5334,7 +5338,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" hidden="1" spans="1:7">
       <c r="A66" t="s">
         <v>128</v>
       </c>
@@ -5357,7 +5361,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" hidden="1" spans="1:7">
       <c r="A67" t="s">
         <v>130</v>
       </c>
@@ -5380,7 +5384,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" hidden="1" spans="1:7">
       <c r="A68" t="s">
         <v>132</v>
       </c>
@@ -5403,7 +5407,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" hidden="1" spans="1:7">
       <c r="A69" t="s">
         <v>134</v>
       </c>
@@ -5426,7 +5430,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" hidden="1" spans="1:7">
       <c r="A70" t="s">
         <v>136</v>
       </c>
@@ -5449,7 +5453,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" hidden="1" spans="1:7">
       <c r="A71" t="s">
         <v>138</v>
       </c>
@@ -5472,7 +5476,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" hidden="1" spans="1:7">
       <c r="A72" t="s">
         <v>139</v>
       </c>
@@ -5495,7 +5499,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" hidden="1" spans="1:7">
       <c r="A73" t="s">
         <v>140</v>
       </c>
@@ -5518,7 +5522,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" hidden="1" spans="1:7">
       <c r="A74" t="s">
         <v>84</v>
       </c>
@@ -5541,7 +5545,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" hidden="1" spans="1:7">
       <c r="A75" t="s">
         <v>88</v>
       </c>
@@ -5564,7 +5568,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" hidden="1" spans="1:7">
       <c r="A76" t="s">
         <v>92</v>
       </c>
@@ -5587,7 +5591,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" hidden="1" spans="1:7">
       <c r="A77" t="s">
         <v>144</v>
       </c>
@@ -5610,7 +5614,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" hidden="1" spans="1:7">
       <c r="A78" t="s">
         <v>145</v>
       </c>
@@ -5633,7 +5637,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" hidden="1" spans="1:7">
       <c r="A79" t="s">
         <v>146</v>
       </c>
@@ -5656,7 +5660,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" hidden="1" spans="1:7">
       <c r="A80" t="s">
         <v>147</v>
       </c>
@@ -5679,7 +5683,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" hidden="1" spans="1:7">
       <c r="A81" t="s">
         <v>107</v>
       </c>
@@ -5702,7 +5706,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" hidden="1" spans="1:7">
       <c r="A82" t="s">
         <v>149</v>
       </c>
@@ -5725,7 +5729,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" hidden="1" spans="1:7">
       <c r="A83" t="s">
         <v>150</v>
       </c>
@@ -5748,7 +5752,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" hidden="1" spans="1:7">
       <c r="A84" t="s">
         <v>113</v>
       </c>
@@ -5771,7 +5775,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" hidden="1" spans="1:7">
       <c r="A85" t="s">
         <v>117</v>
       </c>
@@ -5794,7 +5798,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" hidden="1" spans="1:7">
       <c r="A86" t="s">
         <v>117</v>
       </c>
@@ -5817,7 +5821,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" hidden="1" spans="1:7">
       <c r="A87" t="s">
         <v>120</v>
       </c>
@@ -5840,7 +5844,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" hidden="1" spans="1:7">
       <c r="A88" t="s">
         <v>124</v>
       </c>
@@ -5863,7 +5867,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" hidden="1" spans="1:7">
       <c r="A89" t="s">
         <v>126</v>
       </c>
@@ -5886,7 +5890,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" hidden="1" spans="1:7">
       <c r="A90" t="s">
         <v>128</v>
       </c>
@@ -5909,7 +5913,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" hidden="1" spans="1:7">
       <c r="A91" t="s">
         <v>130</v>
       </c>
@@ -5932,7 +5936,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" hidden="1" spans="1:7">
       <c r="A92" t="s">
         <v>132</v>
       </c>
@@ -5955,7 +5959,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" hidden="1" spans="1:7">
       <c r="A93" t="s">
         <v>134</v>
       </c>
@@ -5978,7 +5982,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" hidden="1" spans="1:7">
       <c r="A94" t="s">
         <v>156</v>
       </c>
@@ -6001,7 +6005,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" hidden="1" spans="1:7">
       <c r="A95" t="s">
         <v>157</v>
       </c>
@@ -6024,7 +6028,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" hidden="1" spans="1:7">
       <c r="A96" t="s">
         <v>159</v>
       </c>
@@ -6047,7 +6051,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" hidden="1" spans="1:7">
       <c r="A97" t="s">
         <v>160</v>
       </c>
@@ -6070,7 +6074,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" hidden="1" spans="1:7">
       <c r="A98" t="s">
         <v>162</v>
       </c>
@@ -6093,7 +6097,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" hidden="1" spans="1:7">
       <c r="A99" t="s">
         <v>166</v>
       </c>
@@ -6116,7 +6120,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" hidden="1" spans="1:7">
       <c r="A100" t="s">
         <v>168</v>
       </c>
@@ -6139,7 +6143,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" hidden="1" spans="1:7">
       <c r="A101" t="s">
         <v>170</v>
       </c>
@@ -6162,7 +6166,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" hidden="1" spans="1:7">
       <c r="A102" t="s">
         <v>172</v>
       </c>
@@ -6185,7 +6189,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" hidden="1" spans="1:7">
       <c r="A103" t="s">
         <v>173</v>
       </c>
@@ -6208,7 +6212,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" hidden="1" spans="1:7">
       <c r="A104" t="s">
         <v>175</v>
       </c>
@@ -6231,7 +6235,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" hidden="1" spans="1:7">
       <c r="A105" t="s">
         <v>176</v>
       </c>
@@ -6254,7 +6258,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" hidden="1" spans="1:7">
       <c r="A106" t="s">
         <v>178</v>
       </c>
@@ -6277,7 +6281,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" hidden="1" spans="1:7">
       <c r="A107" t="s">
         <v>178</v>
       </c>
@@ -6300,7 +6304,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" hidden="1" spans="1:7">
       <c r="A108" t="s">
         <v>180</v>
       </c>
@@ -6323,7 +6327,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" hidden="1" spans="1:7">
       <c r="A109" t="s">
         <v>182</v>
       </c>
@@ -6346,7 +6350,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" hidden="1" spans="1:7">
       <c r="A110" t="s">
         <v>185</v>
       </c>
@@ -6369,7 +6373,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" hidden="1" spans="1:7">
       <c r="A111" t="s">
         <v>187</v>
       </c>
@@ -6392,7 +6396,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" hidden="1" spans="1:7">
       <c r="A112" t="s">
         <v>187</v>
       </c>
@@ -6415,7 +6419,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" hidden="1" spans="1:7">
       <c r="A113" t="s">
         <v>189</v>
       </c>
@@ -6438,7 +6442,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" hidden="1" spans="1:7">
       <c r="A114" t="s">
         <v>191</v>
       </c>
@@ -6461,7 +6465,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" hidden="1" spans="1:7">
       <c r="A115" t="s">
         <v>194</v>
       </c>
@@ -6484,7 +6488,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" hidden="1" spans="1:7">
       <c r="A116" t="s">
         <v>189</v>
       </c>
@@ -6507,7 +6511,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" hidden="1" spans="1:7">
       <c r="A117" t="s">
         <v>196</v>
       </c>
@@ -6530,7 +6534,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" hidden="1" spans="1:7">
       <c r="A118" t="s">
         <v>198</v>
       </c>
@@ -6538,7 +6542,7 @@
         <v>37</v>
       </c>
       <c r="C118" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="D118" t="s">
         <v>90</v>
@@ -6553,7 +6557,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" hidden="1" spans="1:7">
       <c r="A119" t="s">
         <v>199</v>
       </c>
@@ -6576,7 +6580,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" hidden="1" spans="1:7">
       <c r="A120" t="s">
         <v>201</v>
       </c>
@@ -6599,7 +6603,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" hidden="1" spans="1:7">
       <c r="A121" t="s">
         <v>196</v>
       </c>
@@ -6622,7 +6626,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" hidden="1" spans="1:7">
       <c r="A122" t="s">
         <v>202</v>
       </c>
@@ -6645,7 +6649,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" hidden="1" spans="1:7">
       <c r="A123" t="s">
         <v>205</v>
       </c>
@@ -6668,7 +6672,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" hidden="1" spans="1:7">
       <c r="A124" t="s">
         <v>208</v>
       </c>
@@ -6691,7 +6695,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" hidden="1" spans="1:7">
       <c r="A125" t="s">
         <v>210</v>
       </c>
@@ -6714,7 +6718,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" hidden="1" spans="1:7">
       <c r="A126" t="s">
         <v>212</v>
       </c>
@@ -6737,7 +6741,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" hidden="1" spans="1:7">
       <c r="A127" t="s">
         <v>214</v>
       </c>
@@ -6760,7 +6764,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" hidden="1" spans="1:7">
       <c r="A128" t="s">
         <v>212</v>
       </c>
@@ -6783,7 +6787,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" hidden="1" spans="1:7">
       <c r="A129" t="s">
         <v>214</v>
       </c>
@@ -6806,7 +6810,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" hidden="1" spans="1:7">
       <c r="A130" t="s">
         <v>215</v>
       </c>
@@ -6829,7 +6833,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" hidden="1" spans="1:7">
       <c r="A131" t="s">
         <v>216</v>
       </c>
@@ -6852,7 +6856,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" hidden="1" spans="1:7">
       <c r="A132" t="s">
         <v>218</v>
       </c>
@@ -6860,7 +6864,7 @@
         <v>8</v>
       </c>
       <c r="C132" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="D132" t="s">
         <v>90</v>
@@ -6875,7 +6879,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" hidden="1" spans="1:7">
       <c r="A133" t="s">
         <v>218</v>
       </c>
@@ -6883,7 +6887,7 @@
         <v>8</v>
       </c>
       <c r="C133" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="D133" t="s">
         <v>143</v>
@@ -6898,7 +6902,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" hidden="1" spans="1:7">
       <c r="A134" t="s">
         <v>220</v>
       </c>
@@ -6921,7 +6925,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" hidden="1" spans="1:7">
       <c r="A135" t="s">
         <v>222</v>
       </c>
@@ -6944,7 +6948,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" hidden="1" spans="1:7">
       <c r="A136" t="s">
         <v>223</v>
       </c>
@@ -6967,7 +6971,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" hidden="1" spans="1:7">
       <c r="A137" t="s">
         <v>226</v>
       </c>
@@ -6990,7 +6994,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" hidden="1" spans="1:7">
       <c r="A138" t="s">
         <v>228</v>
       </c>
@@ -7013,7 +7017,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" hidden="1" spans="1:7">
       <c r="A139" t="s">
         <v>230</v>
       </c>
@@ -7036,7 +7040,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" hidden="1" spans="1:7">
       <c r="A140" t="s">
         <v>232</v>
       </c>
@@ -7059,7 +7063,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" hidden="1" spans="1:7">
       <c r="A141" t="s">
         <v>228</v>
       </c>
@@ -7082,7 +7086,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" hidden="1" spans="1:7">
       <c r="A142" t="s">
         <v>230</v>
       </c>
@@ -7105,7 +7109,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" hidden="1" spans="1:7">
       <c r="A143" t="s">
         <v>234</v>
       </c>
@@ -7128,7 +7132,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" hidden="1" spans="1:7">
       <c r="A144" t="s">
         <v>202</v>
       </c>
@@ -7151,7 +7155,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" hidden="1" spans="1:7">
       <c r="A145" t="s">
         <v>235</v>
       </c>
@@ -7174,7 +7178,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" hidden="1" spans="1:7">
       <c r="A146" t="s">
         <v>236</v>
       </c>
@@ -7197,7 +7201,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" hidden="1" spans="1:7">
       <c r="A147" t="s">
         <v>241</v>
       </c>
@@ -7220,7 +7224,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" hidden="1" spans="1:7">
       <c r="A148" t="s">
         <v>243</v>
       </c>
@@ -7243,7 +7247,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" hidden="1" spans="1:7">
       <c r="A149" t="s">
         <v>244</v>
       </c>
@@ -7266,7 +7270,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" hidden="1" spans="1:7">
       <c r="A150" t="s">
         <v>245</v>
       </c>
@@ -7289,7 +7293,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" hidden="1" spans="1:7">
       <c r="A151" t="s">
         <v>248</v>
       </c>
@@ -7312,7 +7316,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" hidden="1" spans="1:7">
       <c r="A152" t="s">
         <v>250</v>
       </c>
@@ -7335,7 +7339,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" hidden="1" spans="1:7">
       <c r="A153" t="s">
         <v>253</v>
       </c>
@@ -7358,7 +7362,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" hidden="1" spans="1:7">
       <c r="A154" t="s">
         <v>255</v>
       </c>
@@ -7381,7 +7385,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" hidden="1" spans="1:7">
       <c r="A155" t="s">
         <v>255</v>
       </c>
@@ -7404,7 +7408,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" hidden="1" spans="1:7">
       <c r="A156" t="s">
         <v>256</v>
       </c>
@@ -7427,7 +7431,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" hidden="1" spans="1:7">
       <c r="A157" t="s">
         <v>257</v>
       </c>
@@ -7450,7 +7454,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" hidden="1" spans="1:7">
       <c r="A158" t="s">
         <v>260</v>
       </c>
@@ -7496,7 +7500,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="160" spans="1:7">
+    <row r="160" hidden="1" spans="1:7">
       <c r="A160" t="s">
         <v>265</v>
       </c>
@@ -7519,7 +7523,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="161" spans="1:7">
+    <row r="161" hidden="1" spans="1:7">
       <c r="A161" t="s">
         <v>266</v>
       </c>
@@ -7542,7 +7546,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="162" spans="1:7">
+    <row r="162" hidden="1" spans="1:7">
       <c r="A162" t="s">
         <v>268</v>
       </c>
@@ -7565,7 +7569,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="163" spans="1:7">
+    <row r="163" hidden="1" spans="1:7">
       <c r="A163" t="s">
         <v>270</v>
       </c>
@@ -7588,7 +7592,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" hidden="1" spans="1:7">
       <c r="A164" t="s">
         <v>273</v>
       </c>
@@ -7611,7 +7615,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="165" spans="1:7">
+    <row r="165" hidden="1" spans="1:7">
       <c r="A165" t="s">
         <v>275</v>
       </c>
@@ -7634,7 +7638,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" hidden="1" spans="1:7">
       <c r="A166" t="s">
         <v>276</v>
       </c>
@@ -7657,7 +7661,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" hidden="1" spans="1:7">
       <c r="A167" t="s">
         <v>279</v>
       </c>
@@ -7680,7 +7684,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="168" spans="1:7">
+    <row r="168" hidden="1" spans="1:7">
       <c r="A168" t="s">
         <v>281</v>
       </c>
@@ -7703,7 +7707,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" hidden="1" spans="1:7">
       <c r="A169" t="s">
         <v>282</v>
       </c>
@@ -7726,7 +7730,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" hidden="1" spans="1:7">
       <c r="A170" t="s">
         <v>285</v>
       </c>
@@ -7749,7 +7753,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" hidden="1" spans="1:7">
       <c r="A171" t="s">
         <v>287</v>
       </c>
@@ -7772,7 +7776,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" hidden="1" spans="1:7">
       <c r="A172" t="s">
         <v>290</v>
       </c>
@@ -7795,7 +7799,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" hidden="1" spans="1:7">
       <c r="A173" t="s">
         <v>287</v>
       </c>
@@ -7818,7 +7822,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" hidden="1" spans="1:7">
       <c r="A174" t="s">
         <v>290</v>
       </c>
@@ -7841,7 +7845,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" hidden="1" spans="1:7">
       <c r="A175" t="s">
         <v>296</v>
       </c>
@@ -7864,7 +7868,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" hidden="1" spans="1:7">
       <c r="A176" t="s">
         <v>299</v>
       </c>
@@ -7887,7 +7891,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" hidden="1" spans="1:7">
       <c r="A177" t="s">
         <v>300</v>
       </c>
@@ -7910,7 +7914,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" hidden="1" spans="1:7">
       <c r="A178" t="s">
         <v>302</v>
       </c>
@@ -7933,7 +7937,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" hidden="1" spans="1:7">
       <c r="A179" t="s">
         <v>304</v>
       </c>
@@ -7956,7 +7960,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" hidden="1" spans="1:7">
       <c r="A180" t="s">
         <v>306</v>
       </c>
@@ -7979,7 +7983,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" hidden="1" spans="1:7">
       <c r="A181" t="s">
         <v>307</v>
       </c>
@@ -8002,7 +8006,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" hidden="1" spans="1:7">
       <c r="A182" t="s">
         <v>307</v>
       </c>
@@ -8025,7 +8029,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" hidden="1" spans="1:7">
       <c r="A183" t="s">
         <v>310</v>
       </c>
@@ -8048,7 +8052,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" hidden="1" spans="1:7">
       <c r="A184" t="s">
         <v>312</v>
       </c>
@@ -8071,7 +8075,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" hidden="1" spans="1:7">
       <c r="A185" t="s">
         <v>314</v>
       </c>
@@ -8094,7 +8098,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" hidden="1" spans="1:7">
       <c r="A186" t="s">
         <v>314</v>
       </c>
@@ -8117,7 +8121,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" hidden="1" spans="1:7">
       <c r="A187" t="s">
         <v>317</v>
       </c>
@@ -8140,7 +8144,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" hidden="1" spans="1:7">
       <c r="A188" t="s">
         <v>318</v>
       </c>
@@ -8163,7 +8167,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" hidden="1" spans="1:7">
       <c r="A189" t="s">
         <v>321</v>
       </c>
@@ -8186,7 +8190,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" hidden="1" spans="1:7">
       <c r="A190" t="s">
         <v>322</v>
       </c>
@@ -8209,7 +8213,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" hidden="1" spans="1:7">
       <c r="A191" t="s">
         <v>326</v>
       </c>
@@ -8232,7 +8236,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="192" spans="1:7">
+    <row r="192" hidden="1" spans="1:7">
       <c r="A192" t="s">
         <v>328</v>
       </c>
@@ -8255,7 +8259,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="193" spans="1:7">
+    <row r="193" hidden="1" spans="1:7">
       <c r="A193" t="s">
         <v>329</v>
       </c>
@@ -8278,7 +8282,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" hidden="1" spans="1:7">
       <c r="A194" t="s">
         <v>330</v>
       </c>
@@ -8301,7 +8305,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="195" spans="1:7">
+    <row r="195" hidden="1" spans="1:7">
       <c r="A195" t="s">
         <v>331</v>
       </c>
@@ -8324,7 +8328,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="196" spans="1:7">
+    <row r="196" hidden="1" spans="1:7">
       <c r="A196" t="s">
         <v>333</v>
       </c>
@@ -8347,7 +8351,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="197" spans="1:7">
+    <row r="197" hidden="1" spans="1:7">
       <c r="A197" t="s">
         <v>336</v>
       </c>
@@ -8370,7 +8374,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="198" spans="1:7">
+    <row r="198" hidden="1" spans="1:7">
       <c r="A198" t="s">
         <v>338</v>
       </c>
@@ -8393,7 +8397,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="199" spans="1:7">
+    <row r="199" hidden="1" spans="1:7">
       <c r="A199" t="s">
         <v>339</v>
       </c>
@@ -8416,7 +8420,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="200" spans="1:7">
+    <row r="200" hidden="1" spans="1:7">
       <c r="A200" t="s">
         <v>341</v>
       </c>
@@ -8439,7 +8443,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="201" spans="1:7">
+    <row r="201" hidden="1" spans="1:7">
       <c r="A201" t="s">
         <v>344</v>
       </c>
@@ -8462,7 +8466,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="202" spans="1:7">
+    <row r="202" hidden="1" spans="1:7">
       <c r="A202" t="s">
         <v>346</v>
       </c>
@@ -8485,7 +8489,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="203" spans="1:7">
+    <row r="203" hidden="1" spans="1:7">
       <c r="A203" t="s">
         <v>350</v>
       </c>
@@ -8508,7 +8512,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="204" spans="1:7">
+    <row r="204" hidden="1" spans="1:7">
       <c r="A204" t="s">
         <v>352</v>
       </c>
@@ -8531,7 +8535,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="205" spans="1:7">
+    <row r="205" hidden="1" spans="1:7">
       <c r="A205" t="s">
         <v>353</v>
       </c>
@@ -8554,7 +8558,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="206" spans="1:7">
+    <row r="206" hidden="1" spans="1:7">
       <c r="A206" t="s">
         <v>354</v>
       </c>
@@ -8577,7 +8581,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="207" spans="1:7">
+    <row r="207" hidden="1" spans="1:7">
       <c r="A207" t="s">
         <v>356</v>
       </c>
@@ -8600,7 +8604,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="208" spans="1:7">
+    <row r="208" hidden="1" spans="1:7">
       <c r="A208" t="s">
         <v>357</v>
       </c>
@@ -8623,7 +8627,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="209" spans="1:7">
+    <row r="209" hidden="1" spans="1:7">
       <c r="A209" t="s">
         <v>361</v>
       </c>
@@ -8646,7 +8650,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="210" spans="1:7">
+    <row r="210" hidden="1" spans="1:7">
       <c r="A210" t="s">
         <v>366</v>
       </c>
@@ -8669,7 +8673,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="211" spans="1:7">
+    <row r="211" hidden="1" spans="1:7">
       <c r="A211" t="s">
         <v>370</v>
       </c>
@@ -8692,7 +8696,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="212" spans="1:7">
+    <row r="212" hidden="1" spans="1:7">
       <c r="A212" t="s">
         <v>372</v>
       </c>
@@ -8715,7 +8719,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="213" spans="1:7">
+    <row r="213" hidden="1" spans="1:7">
       <c r="A213" t="s">
         <v>376</v>
       </c>
@@ -8738,7 +8742,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="214" spans="1:7">
+    <row r="214" hidden="1" spans="1:7">
       <c r="A214" t="s">
         <v>380</v>
       </c>
@@ -8761,7 +8765,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="215" spans="1:7">
+    <row r="215" hidden="1" spans="1:7">
       <c r="A215" t="s">
         <v>366</v>
       </c>
@@ -8784,7 +8788,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="216" spans="1:7">
+    <row r="216" hidden="1" spans="1:7">
       <c r="A216" t="s">
         <v>372</v>
       </c>
@@ -8807,7 +8811,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="217" spans="1:7">
+    <row r="217" hidden="1" spans="1:7">
       <c r="A217" t="s">
         <v>383</v>
       </c>
@@ -8830,7 +8834,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="218" spans="1:7">
+    <row r="218" hidden="1" spans="1:7">
       <c r="A218" t="s">
         <v>385</v>
       </c>
@@ -8853,7 +8857,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="219" spans="1:7">
+    <row r="219" hidden="1" spans="1:7">
       <c r="A219" t="s">
         <v>386</v>
       </c>
@@ -8876,7 +8880,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="220" spans="1:7">
+    <row r="220" hidden="1" spans="1:7">
       <c r="A220" t="s">
         <v>387</v>
       </c>
@@ -8899,7 +8903,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="221" spans="1:7">
+    <row r="221" hidden="1" spans="1:7">
       <c r="A221" t="s">
         <v>387</v>
       </c>
@@ -8922,7 +8926,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="222" spans="1:7">
+    <row r="222" hidden="1" spans="1:7">
       <c r="A222" t="s">
         <v>387</v>
       </c>
@@ -8945,7 +8949,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="223" spans="1:7">
+    <row r="223" hidden="1" spans="1:7">
       <c r="A223" t="s">
         <v>388</v>
       </c>
@@ -8968,7 +8972,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="224" spans="1:7">
+    <row r="224" hidden="1" spans="1:7">
       <c r="A224" t="s">
         <v>385</v>
       </c>
@@ -8991,7 +8995,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="225" spans="1:7">
+    <row r="225" hidden="1" spans="1:7">
       <c r="A225" t="s">
         <v>386</v>
       </c>
@@ -9014,7 +9018,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="226" spans="1:7">
+    <row r="226" hidden="1" spans="1:7">
       <c r="A226" t="s">
         <v>388</v>
       </c>
@@ -9037,7 +9041,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="227" spans="1:7">
+    <row r="227" hidden="1" spans="1:7">
       <c r="A227" t="s">
         <v>389</v>
       </c>
@@ -9060,7 +9064,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="228" spans="1:7">
+    <row r="228" hidden="1" spans="1:7">
       <c r="A228" t="s">
         <v>390</v>
       </c>
@@ -9083,7 +9087,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="229" spans="1:7">
+    <row r="229" hidden="1" spans="1:7">
       <c r="A229" t="s">
         <v>391</v>
       </c>
@@ -9106,7 +9110,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="230" spans="1:7">
+    <row r="230" hidden="1" spans="1:7">
       <c r="A230" t="s">
         <v>393</v>
       </c>
@@ -9129,7 +9133,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="231" spans="1:7">
+    <row r="231" hidden="1" spans="1:7">
       <c r="A231" t="s">
         <v>395</v>
       </c>
@@ -9152,7 +9156,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="232" spans="1:7">
+    <row r="232" hidden="1" spans="1:7">
       <c r="A232" t="s">
         <v>397</v>
       </c>
@@ -9175,7 +9179,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="233" spans="1:7">
+    <row r="233" hidden="1" spans="1:7">
       <c r="A233" t="s">
         <v>398</v>
       </c>
@@ -9198,7 +9202,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="234" spans="1:7">
+    <row r="234" hidden="1" spans="1:7">
       <c r="A234" t="s">
         <v>393</v>
       </c>
@@ -9221,7 +9225,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="235" spans="1:7">
+    <row r="235" hidden="1" spans="1:7">
       <c r="A235" t="s">
         <v>395</v>
       </c>
@@ -9244,7 +9248,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="236" spans="1:7">
+    <row r="236" hidden="1" spans="1:7">
       <c r="A236" t="s">
         <v>398</v>
       </c>
@@ -9267,7 +9271,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="237" spans="1:7">
+    <row r="237" hidden="1" spans="1:7">
       <c r="A237" t="s">
         <v>399</v>
       </c>
@@ -9290,7 +9294,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="238" spans="1:7">
+    <row r="238" hidden="1" spans="1:7">
       <c r="A238" t="s">
         <v>401</v>
       </c>
@@ -9313,7 +9317,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="239" spans="1:7">
+    <row r="239" hidden="1" spans="1:7">
       <c r="A239" t="s">
         <v>403</v>
       </c>
@@ -9336,7 +9340,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="240" spans="1:7">
+    <row r="240" hidden="1" spans="1:7">
       <c r="A240" t="s">
         <v>404</v>
       </c>
@@ -9359,7 +9363,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="241" spans="1:7">
+    <row r="241" hidden="1" spans="1:7">
       <c r="A241" t="s">
         <v>405</v>
       </c>
@@ -9382,7 +9386,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="242" spans="1:7">
+    <row r="242" hidden="1" spans="1:7">
       <c r="A242" t="s">
         <v>406</v>
       </c>
@@ -9405,7 +9409,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="243" spans="1:7">
+    <row r="243" hidden="1" spans="1:7">
       <c r="A243" t="s">
         <v>403</v>
       </c>
@@ -9428,7 +9432,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="244" spans="1:7">
+    <row r="244" hidden="1" spans="1:7">
       <c r="A244" t="s">
         <v>404</v>
       </c>
@@ -9451,7 +9455,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="245" spans="1:7">
+    <row r="245" hidden="1" spans="1:7">
       <c r="A245" t="s">
         <v>405</v>
       </c>
@@ -9474,7 +9478,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="246" spans="1:7">
+    <row r="246" hidden="1" spans="1:7">
       <c r="A246" t="s">
         <v>407</v>
       </c>
@@ -9497,7 +9501,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="247" spans="1:7">
+    <row r="247" hidden="1" spans="1:7">
       <c r="A247" t="s">
         <v>408</v>
       </c>
@@ -9520,7 +9524,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="248" spans="1:7">
+    <row r="248" hidden="1" spans="1:7">
       <c r="A248" t="s">
         <v>409</v>
       </c>
@@ -9543,7 +9547,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="249" spans="1:7">
+    <row r="249" hidden="1" spans="1:7">
       <c r="A249" t="s">
         <v>413</v>
       </c>
@@ -9566,7 +9570,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="250" spans="1:7">
+    <row r="250" hidden="1" spans="1:7">
       <c r="A250" t="s">
         <v>414</v>
       </c>
@@ -9589,7 +9593,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="251" spans="1:7">
+    <row r="251" hidden="1" spans="1:7">
       <c r="A251" t="s">
         <v>416</v>
       </c>
@@ -9612,7 +9616,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="252" spans="1:7">
+    <row r="252" hidden="1" spans="1:7">
       <c r="A252" t="s">
         <v>418</v>
       </c>
@@ -9635,7 +9639,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="253" spans="1:7">
+    <row r="253" hidden="1" spans="1:7">
       <c r="A253" t="s">
         <v>361</v>
       </c>
@@ -9658,7 +9662,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="254" spans="1:7">
+    <row r="254" hidden="1" spans="1:7">
       <c r="A254" t="s">
         <v>420</v>
       </c>
@@ -9681,7 +9685,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="255" spans="1:7">
+    <row r="255" hidden="1" spans="1:7">
       <c r="A255" t="s">
         <v>421</v>
       </c>
@@ -9704,7 +9708,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="256" spans="1:7">
+    <row r="256" hidden="1" spans="1:7">
       <c r="A256" t="s">
         <v>422</v>
       </c>
@@ -9727,7 +9731,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="257" spans="1:7">
+    <row r="257" hidden="1" spans="1:7">
       <c r="A257" t="s">
         <v>424</v>
       </c>
@@ -9750,7 +9754,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="258" spans="1:7">
+    <row r="258" hidden="1" spans="1:7">
       <c r="A258" t="s">
         <v>425</v>
       </c>
@@ -9773,7 +9777,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="259" spans="1:7">
+    <row r="259" hidden="1" spans="1:7">
       <c r="A259" t="s">
         <v>426</v>
       </c>
@@ -9796,7 +9800,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="260" spans="1:7">
+    <row r="260" hidden="1" spans="1:7">
       <c r="A260" t="s">
         <v>428</v>
       </c>
@@ -9819,7 +9823,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="261" spans="1:7">
+    <row r="261" hidden="1" spans="1:7">
       <c r="A261" t="s">
         <v>424</v>
       </c>
@@ -9842,7 +9846,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="262" spans="1:7">
+    <row r="262" hidden="1" spans="1:7">
       <c r="A262" t="s">
         <v>425</v>
       </c>
@@ -9865,7 +9869,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="263" spans="1:7">
+    <row r="263" hidden="1" spans="1:7">
       <c r="A263" t="s">
         <v>429</v>
       </c>
@@ -9888,7 +9892,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="264" spans="1:7">
+    <row r="264" hidden="1" spans="1:7">
       <c r="A264" t="s">
         <v>430</v>
       </c>
@@ -9911,7 +9915,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="265" spans="1:7">
+    <row r="265" hidden="1" spans="1:7">
       <c r="A265" t="s">
         <v>431</v>
       </c>
@@ -9934,7 +9938,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="266" spans="1:7">
+    <row r="266" hidden="1" spans="1:7">
       <c r="A266" t="s">
         <v>432</v>
       </c>
@@ -9957,7 +9961,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="267" spans="1:7">
+    <row r="267" hidden="1" spans="1:7">
       <c r="A267" t="s">
         <v>433</v>
       </c>
@@ -9980,7 +9984,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="268" spans="1:7">
+    <row r="268" hidden="1" spans="1:7">
       <c r="A268" t="s">
         <v>435</v>
       </c>
@@ -10003,7 +10007,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="269" spans="1:7">
+    <row r="269" hidden="1" spans="1:7">
       <c r="A269" t="s">
         <v>436</v>
       </c>
@@ -10026,7 +10030,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="270" spans="1:7">
+    <row r="270" hidden="1" spans="1:7">
       <c r="A270" t="s">
         <v>437</v>
       </c>
@@ -10049,7 +10053,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="271" spans="1:7">
+    <row r="271" hidden="1" spans="1:7">
       <c r="A271" t="s">
         <v>438</v>
       </c>
@@ -10072,7 +10076,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="272" spans="1:7">
+    <row r="272" hidden="1" spans="1:7">
       <c r="A272" t="s">
         <v>439</v>
       </c>
@@ -10095,7 +10099,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="273" spans="1:7">
+    <row r="273" hidden="1" spans="1:7">
       <c r="A273" t="s">
         <v>440</v>
       </c>
@@ -10118,7 +10122,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="274" spans="1:7">
+    <row r="274" hidden="1" spans="1:7">
       <c r="A274" t="s">
         <v>441</v>
       </c>
@@ -10141,7 +10145,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="275" spans="1:7">
+    <row r="275" hidden="1" spans="1:7">
       <c r="A275" t="s">
         <v>438</v>
       </c>
@@ -10164,7 +10168,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="276" spans="1:7">
+    <row r="276" hidden="1" spans="1:7">
       <c r="A276" t="s">
         <v>442</v>
       </c>
@@ -10187,7 +10191,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="277" spans="1:7">
+    <row r="277" hidden="1" spans="1:7">
       <c r="A277" t="s">
         <v>440</v>
       </c>
@@ -10210,7 +10214,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="278" spans="1:7">
+    <row r="278" hidden="1" spans="1:7">
       <c r="A278" t="s">
         <v>443</v>
       </c>
@@ -10233,7 +10237,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="279" spans="1:7">
+    <row r="279" hidden="1" spans="1:7">
       <c r="A279" t="s">
         <v>444</v>
       </c>
@@ -10256,7 +10260,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="280" spans="1:7">
+    <row r="280" hidden="1" spans="1:7">
       <c r="A280" t="s">
         <v>445</v>
       </c>
@@ -10279,7 +10283,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="281" spans="1:7">
+    <row r="281" hidden="1" spans="1:7">
       <c r="A281" t="s">
         <v>446</v>
       </c>
@@ -10302,7 +10306,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="282" spans="1:7">
+    <row r="282" hidden="1" spans="1:7">
       <c r="A282" t="s">
         <v>447</v>
       </c>
@@ -10325,7 +10329,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="283" spans="1:7">
+    <row r="283" hidden="1" spans="1:7">
       <c r="A283" t="s">
         <v>445</v>
       </c>
@@ -10348,7 +10352,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="284" spans="1:7">
+    <row r="284" hidden="1" spans="1:7">
       <c r="A284" t="s">
         <v>446</v>
       </c>
@@ -10371,7 +10375,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="285" spans="1:7">
+    <row r="285" hidden="1" spans="1:7">
       <c r="A285" t="s">
         <v>447</v>
       </c>
@@ -10394,7 +10398,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="286" spans="1:7">
+    <row r="286" hidden="1" spans="1:7">
       <c r="A286" t="s">
         <v>448</v>
       </c>
@@ -10417,7 +10421,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="287" spans="1:7">
+    <row r="287" hidden="1" spans="1:7">
       <c r="A287" t="s">
         <v>449</v>
       </c>
@@ -10440,7 +10444,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="288" spans="1:7">
+    <row r="288" hidden="1" spans="1:7">
       <c r="A288" t="s">
         <v>450</v>
       </c>
@@ -10463,7 +10467,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="289" spans="1:7">
+    <row r="289" hidden="1" spans="1:7">
       <c r="A289" t="s">
         <v>452</v>
       </c>
@@ -10486,7 +10490,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="290" spans="1:7">
+    <row r="290" hidden="1" spans="1:7">
       <c r="A290" t="s">
         <v>453</v>
       </c>
@@ -10509,7 +10513,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="291" spans="1:7">
+    <row r="291" hidden="1" spans="1:7">
       <c r="A291" t="s">
         <v>441</v>
       </c>
@@ -10532,7 +10536,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="292" spans="1:7">
+    <row r="292" hidden="1" spans="1:7">
       <c r="A292" t="s">
         <v>454</v>
       </c>
@@ -10555,7 +10559,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="293" spans="1:7">
+    <row r="293" hidden="1" spans="1:7">
       <c r="A293" t="s">
         <v>455</v>
       </c>
@@ -10578,7 +10582,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="294" spans="1:7">
+    <row r="294" hidden="1" spans="1:7">
       <c r="A294" t="s">
         <v>456</v>
       </c>
@@ -10601,7 +10605,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="295" spans="1:7">
+    <row r="295" hidden="1" spans="1:7">
       <c r="A295" t="s">
         <v>457</v>
       </c>
@@ -10624,7 +10628,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="296" spans="1:7">
+    <row r="296" hidden="1" spans="1:7">
       <c r="A296" t="s">
         <v>458</v>
       </c>
@@ -10647,7 +10651,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="297" spans="1:7">
+    <row r="297" hidden="1" spans="1:7">
       <c r="A297" t="s">
         <v>460</v>
       </c>
@@ -10670,7 +10674,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="298" spans="1:7">
+    <row r="298" hidden="1" spans="1:7">
       <c r="A298" t="s">
         <v>461</v>
       </c>
@@ -10693,7 +10697,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="299" spans="1:7">
+    <row r="299" hidden="1" spans="1:7">
       <c r="A299" t="s">
         <v>461</v>
       </c>
@@ -10716,7 +10720,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="300" spans="1:7">
+    <row r="300" hidden="1" spans="1:7">
       <c r="A300" t="s">
         <v>461</v>
       </c>
@@ -10739,7 +10743,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="301" spans="1:7">
+    <row r="301" hidden="1" spans="1:7">
       <c r="A301" t="s">
         <v>436</v>
       </c>
@@ -10762,7 +10766,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="302" spans="1:7">
+    <row r="302" hidden="1" spans="1:7">
       <c r="A302" t="s">
         <v>413</v>
       </c>
@@ -10785,7 +10789,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="303" spans="1:7">
+    <row r="303" hidden="1" spans="1:7">
       <c r="A303" t="s">
         <v>418</v>
       </c>
@@ -10808,7 +10812,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="304" spans="1:7">
+    <row r="304" hidden="1" spans="1:7">
       <c r="A304" t="s">
         <v>462</v>
       </c>
@@ -10831,7 +10835,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="305" spans="1:7">
+    <row r="305" hidden="1" spans="1:7">
       <c r="A305" t="s">
         <v>466</v>
       </c>
@@ -10854,7 +10858,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="306" spans="1:7">
+    <row r="306" hidden="1" spans="1:7">
       <c r="A306" t="s">
         <v>469</v>
       </c>
@@ -10877,7 +10881,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="307" spans="1:7">
+    <row r="307" hidden="1" spans="1:7">
       <c r="A307" t="s">
         <v>84</v>
       </c>
@@ -10900,7 +10904,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="308" spans="1:7">
+    <row r="308" hidden="1" spans="1:7">
       <c r="A308" t="s">
         <v>471</v>
       </c>
@@ -10923,7 +10927,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="309" spans="1:7">
+    <row r="309" hidden="1" spans="1:7">
       <c r="A309" t="s">
         <v>474</v>
       </c>
@@ -10946,7 +10950,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="310" spans="1:7">
+    <row r="310" hidden="1" spans="1:7">
       <c r="A310" t="s">
         <v>477</v>
       </c>
@@ -10969,7 +10973,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="311" spans="1:7">
+    <row r="311" hidden="1" spans="1:7">
       <c r="A311" t="s">
         <v>479</v>
       </c>
@@ -10992,7 +10996,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="312" spans="1:7">
+    <row r="312" hidden="1" spans="1:7">
       <c r="A312" t="s">
         <v>477</v>
       </c>
@@ -11015,7 +11019,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="313" spans="1:7">
+    <row r="313" hidden="1" spans="1:7">
       <c r="A313" t="s">
         <v>479</v>
       </c>
@@ -11038,7 +11042,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="314" spans="1:7">
+    <row r="314" hidden="1" spans="1:7">
       <c r="A314" t="s">
         <v>479</v>
       </c>
@@ -11061,7 +11065,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="315" spans="1:7">
+    <row r="315" hidden="1" spans="1:7">
       <c r="A315" t="s">
         <v>486</v>
       </c>
@@ -11084,7 +11088,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="316" spans="1:7">
+    <row r="316" hidden="1" spans="1:7">
       <c r="A316" t="s">
         <v>490</v>
       </c>
@@ -11107,7 +11111,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="317" spans="1:7">
+    <row r="317" hidden="1" spans="1:7">
       <c r="A317" t="s">
         <v>492</v>
       </c>
@@ -11130,7 +11134,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="318" spans="1:7">
+    <row r="318" hidden="1" spans="1:7">
       <c r="A318" t="s">
         <v>130</v>
       </c>
@@ -11153,7 +11157,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="319" spans="1:7">
+    <row r="319" hidden="1" spans="1:7">
       <c r="A319" t="s">
         <v>477</v>
       </c>
@@ -11176,7 +11180,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="320" spans="1:7">
+    <row r="320" hidden="1" spans="1:7">
       <c r="A320" t="s">
         <v>477</v>
       </c>
@@ -11199,7 +11203,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="321" spans="1:7">
+    <row r="321" hidden="1" spans="1:7">
       <c r="A321" t="s">
         <v>477</v>
       </c>
@@ -11222,7 +11226,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="322" spans="1:7">
+    <row r="322" hidden="1" spans="1:7">
       <c r="A322" t="s">
         <v>479</v>
       </c>
@@ -11245,7 +11249,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="323" spans="1:7">
+    <row r="323" hidden="1" spans="1:7">
       <c r="A323" t="s">
         <v>486</v>
       </c>
@@ -11268,7 +11272,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="324" spans="1:7">
+    <row r="324" hidden="1" spans="1:7">
       <c r="A324" t="s">
         <v>477</v>
       </c>
@@ -11291,7 +11295,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="325" spans="1:7">
+    <row r="325" hidden="1" spans="1:7">
       <c r="A325" t="s">
         <v>477</v>
       </c>
@@ -11314,7 +11318,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="326" spans="1:7">
+    <row r="326" hidden="1" spans="1:7">
       <c r="A326" t="s">
         <v>477</v>
       </c>
@@ -11337,7 +11341,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="327" spans="1:7">
+    <row r="327" hidden="1" spans="1:7">
       <c r="A327" t="s">
         <v>126</v>
       </c>
@@ -11360,7 +11364,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="328" spans="1:7">
+    <row r="328" hidden="1" spans="1:7">
       <c r="A328" t="s">
         <v>500</v>
       </c>
@@ -11383,7 +11387,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="329" spans="1:7">
+    <row r="329" hidden="1" spans="1:7">
       <c r="A329" t="s">
         <v>502</v>
       </c>
@@ -11406,7 +11410,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="330" spans="1:7">
+    <row r="330" hidden="1" spans="1:7">
       <c r="A330" t="s">
         <v>504</v>
       </c>
@@ -11429,7 +11433,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="331" spans="1:7">
+    <row r="331" hidden="1" spans="1:7">
       <c r="A331" t="s">
         <v>505</v>
       </c>
@@ -11452,7 +11456,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="332" spans="1:7">
+    <row r="332" hidden="1" spans="1:7">
       <c r="A332" t="s">
         <v>486</v>
       </c>
@@ -11475,7 +11479,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="333" spans="1:7">
+    <row r="333" hidden="1" spans="1:7">
       <c r="A333" t="s">
         <v>486</v>
       </c>
@@ -11498,7 +11502,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="334" spans="1:7">
+    <row r="334" hidden="1" spans="1:7">
       <c r="A334" t="s">
         <v>509</v>
       </c>
@@ -11521,7 +11525,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="335" spans="1:7">
+    <row r="335" hidden="1" spans="1:7">
       <c r="A335" t="s">
         <v>510</v>
       </c>
@@ -11544,7 +11548,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="336" spans="1:7">
+    <row r="336" hidden="1" spans="1:7">
       <c r="A336" t="s">
         <v>512</v>
       </c>
@@ -11567,7 +11571,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="337" spans="1:7">
+    <row r="337" hidden="1" spans="1:7">
       <c r="A337" t="s">
         <v>502</v>
       </c>
@@ -11590,7 +11594,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="338" spans="1:7">
+    <row r="338" hidden="1" spans="1:7">
       <c r="A338" t="s">
         <v>514</v>
       </c>
@@ -11613,7 +11617,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="339" spans="1:7">
+    <row r="339" hidden="1" spans="1:7">
       <c r="A339" t="s">
         <v>509</v>
       </c>
@@ -11636,7 +11640,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="340" spans="1:7">
+    <row r="340" hidden="1" spans="1:7">
       <c r="A340" t="s">
         <v>517</v>
       </c>
@@ -11659,7 +11663,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="341" spans="1:7">
+    <row r="341" hidden="1" spans="1:7">
       <c r="A341" t="s">
         <v>519</v>
       </c>
@@ -11682,7 +11686,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="342" spans="1:7">
+    <row r="342" hidden="1" spans="1:7">
       <c r="A342" t="s">
         <v>521</v>
       </c>
@@ -11705,7 +11709,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="343" spans="1:7">
+    <row r="343" hidden="1" spans="1:7">
       <c r="A343" t="s">
         <v>524</v>
       </c>
@@ -11728,7 +11732,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="344" spans="1:7">
+    <row r="344" hidden="1" spans="1:7">
       <c r="A344" t="s">
         <v>526</v>
       </c>
@@ -11751,7 +11755,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="345" spans="1:7">
+    <row r="345" hidden="1" spans="1:7">
       <c r="A345" t="s">
         <v>529</v>
       </c>
@@ -11774,7 +11778,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="346" spans="1:7">
+    <row r="346" hidden="1" spans="1:7">
       <c r="A346" t="s">
         <v>531</v>
       </c>
@@ -11797,7 +11801,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="347" spans="1:7">
+    <row r="347" hidden="1" spans="1:7">
       <c r="A347" t="s">
         <v>534</v>
       </c>
@@ -11820,7 +11824,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="348" spans="1:7">
+    <row r="348" hidden="1" spans="1:7">
       <c r="A348" t="s">
         <v>535</v>
       </c>
@@ -11843,7 +11847,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="349" spans="1:7">
+    <row r="349" hidden="1" spans="1:7">
       <c r="A349" t="s">
         <v>218</v>
       </c>
@@ -11866,7 +11870,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="350" spans="1:7">
+    <row r="350" hidden="1" spans="1:7">
       <c r="A350" t="s">
         <v>531</v>
       </c>
@@ -11889,7 +11893,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="351" spans="1:7">
+    <row r="351" hidden="1" spans="1:7">
       <c r="A351" t="s">
         <v>537</v>
       </c>
@@ -11912,7 +11916,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="352" spans="1:7">
+    <row r="352" hidden="1" spans="1:7">
       <c r="A352" t="s">
         <v>539</v>
       </c>
@@ -11935,7 +11939,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="353" spans="1:7">
+    <row r="353" hidden="1" spans="1:7">
       <c r="A353" t="s">
         <v>540</v>
       </c>
@@ -11958,7 +11962,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="354" spans="1:7">
+    <row r="354" hidden="1" spans="1:7">
       <c r="A354" t="s">
         <v>543</v>
       </c>
@@ -11981,7 +11985,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="355" spans="1:7">
+    <row r="355" hidden="1" spans="1:7">
       <c r="A355" t="s">
         <v>539</v>
       </c>
@@ -12004,7 +12008,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="356" spans="1:7">
+    <row r="356" hidden="1" spans="1:7">
       <c r="A356" t="s">
         <v>546</v>
       </c>
@@ -12027,7 +12031,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="357" spans="1:7">
+    <row r="357" hidden="1" spans="1:7">
       <c r="A357" t="s">
         <v>548</v>
       </c>
@@ -12050,7 +12054,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="358" spans="1:7">
+    <row r="358" hidden="1" spans="1:7">
       <c r="A358" t="s">
         <v>550</v>
       </c>
@@ -12073,7 +12077,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="359" spans="1:7">
+    <row r="359" hidden="1" spans="1:7">
       <c r="A359" t="s">
         <v>552</v>
       </c>
@@ -12096,7 +12100,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="360" spans="1:7">
+    <row r="360" hidden="1" spans="1:7">
       <c r="A360" t="s">
         <v>550</v>
       </c>
@@ -12119,7 +12123,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="361" spans="1:7">
+    <row r="361" hidden="1" spans="1:7">
       <c r="A361" t="s">
         <v>552</v>
       </c>
@@ -12142,7 +12146,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="362" spans="1:7">
+    <row r="362" hidden="1" spans="1:7">
       <c r="A362" t="s">
         <v>557</v>
       </c>
@@ -12165,7 +12169,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="363" spans="1:7">
+    <row r="363" hidden="1" spans="1:7">
       <c r="A363" t="s">
         <v>558</v>
       </c>
@@ -12188,7 +12192,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="364" spans="1:7">
+    <row r="364" hidden="1" spans="1:7">
       <c r="A364" t="s">
         <v>557</v>
       </c>
@@ -12211,7 +12215,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="365" spans="1:7">
+    <row r="365" hidden="1" spans="1:7">
       <c r="A365" t="s">
         <v>559</v>
       </c>
@@ -12234,7 +12238,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="366" spans="1:7">
+    <row r="366" hidden="1" spans="1:7">
       <c r="A366" t="s">
         <v>561</v>
       </c>
@@ -12257,7 +12261,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="367" spans="1:7">
+    <row r="367" hidden="1" spans="1:7">
       <c r="A367" t="s">
         <v>552</v>
       </c>
@@ -12280,7 +12284,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="368" spans="1:7">
+    <row r="368" hidden="1" spans="1:7">
       <c r="A368" t="s">
         <v>564</v>
       </c>
@@ -12303,7 +12307,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="369" spans="1:7">
+    <row r="369" hidden="1" spans="1:7">
       <c r="A369" t="s">
         <v>552</v>
       </c>
@@ -12326,7 +12330,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="370" spans="1:7">
+    <row r="370" hidden="1" spans="1:7">
       <c r="A370" t="s">
         <v>218</v>
       </c>
@@ -12349,7 +12353,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="371" spans="1:7">
+    <row r="371" hidden="1" spans="1:7">
       <c r="A371" t="s">
         <v>569</v>
       </c>
@@ -12372,7 +12376,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="372" spans="1:7">
+    <row r="372" hidden="1" spans="1:7">
       <c r="A372" t="s">
         <v>571</v>
       </c>
@@ -12395,7 +12399,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="373" spans="1:7">
+    <row r="373" hidden="1" spans="1:7">
       <c r="A373" t="s">
         <v>573</v>
       </c>
@@ -12418,7 +12422,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="374" spans="1:7">
+    <row r="374" hidden="1" spans="1:7">
       <c r="A374" t="s">
         <v>531</v>
       </c>
@@ -12441,7 +12445,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="375" spans="1:7">
+    <row r="375" hidden="1" spans="1:7">
       <c r="A375" t="s">
         <v>537</v>
       </c>
@@ -12464,7 +12468,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="376" spans="1:7">
+    <row r="376" hidden="1" spans="1:7">
       <c r="A376" t="s">
         <v>573</v>
       </c>
@@ -12487,7 +12491,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="377" spans="1:7">
+    <row r="377" hidden="1" spans="1:7">
       <c r="A377" t="s">
         <v>531</v>
       </c>
@@ -12510,7 +12514,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="378" spans="1:7">
+    <row r="378" hidden="1" spans="1:7">
       <c r="A378" t="s">
         <v>537</v>
       </c>
@@ -12533,7 +12537,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="379" spans="1:7">
+    <row r="379" hidden="1" spans="1:7">
       <c r="A379" t="s">
         <v>205</v>
       </c>
@@ -12556,7 +12560,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="380" spans="1:7">
+    <row r="380" hidden="1" spans="1:7">
       <c r="A380" t="s">
         <v>579</v>
       </c>
@@ -12579,7 +12583,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="381" spans="1:7">
+    <row r="381" hidden="1" spans="1:7">
       <c r="A381" t="s">
         <v>302</v>
       </c>
@@ -12602,7 +12606,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="382" spans="1:7">
+    <row r="382" hidden="1" spans="1:7">
       <c r="A382" t="s">
         <v>583</v>
       </c>
@@ -12625,7 +12629,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="383" spans="1:7">
+    <row r="383" hidden="1" spans="1:7">
       <c r="A383" t="s">
         <v>585</v>
       </c>
@@ -12648,7 +12652,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="384" spans="1:7">
+    <row r="384" hidden="1" spans="1:7">
       <c r="A384" t="s">
         <v>282</v>
       </c>
@@ -12671,7 +12675,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="385" spans="1:7">
+    <row r="385" hidden="1" spans="1:7">
       <c r="A385" t="s">
         <v>588</v>
       </c>
@@ -12694,7 +12698,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="386" spans="1:7">
+    <row r="386" hidden="1" spans="1:7">
       <c r="A386" t="s">
         <v>590</v>
       </c>
@@ -12717,7 +12721,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="387" spans="1:7">
+    <row r="387" hidden="1" spans="1:7">
       <c r="A387" t="s">
         <v>250</v>
       </c>
@@ -12740,7 +12744,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="388" spans="1:7">
+    <row r="388" hidden="1" spans="1:7">
       <c r="A388" t="s">
         <v>594</v>
       </c>
@@ -12763,7 +12767,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="389" spans="1:7">
+    <row r="389" hidden="1" spans="1:7">
       <c r="A389" t="s">
         <v>595</v>
       </c>
@@ -12786,7 +12790,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="390" spans="1:7">
+    <row r="390" hidden="1" spans="1:7">
       <c r="A390" t="s">
         <v>598</v>
       </c>
@@ -12809,7 +12813,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="391" spans="1:7">
+    <row r="391" hidden="1" spans="1:7">
       <c r="A391" t="s">
         <v>601</v>
       </c>
@@ -12832,7 +12836,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="392" spans="1:7">
+    <row r="392" hidden="1" spans="1:7">
       <c r="A392" t="s">
         <v>602</v>
       </c>
@@ -12855,7 +12859,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="393" spans="1:7">
+    <row r="393" hidden="1" spans="1:7">
       <c r="A393" t="s">
         <v>604</v>
       </c>
@@ -12878,7 +12882,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="394" spans="1:7">
+    <row r="394" hidden="1" spans="1:7">
       <c r="A394" t="s">
         <v>265</v>
       </c>
@@ -12901,7 +12905,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="395" spans="1:7">
+    <row r="395" hidden="1" spans="1:7">
       <c r="A395" t="s">
         <v>607</v>
       </c>
@@ -12924,7 +12928,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="396" spans="1:7">
+    <row r="396" hidden="1" spans="1:7">
       <c r="A396" t="s">
         <v>611</v>
       </c>
@@ -12947,7 +12951,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="397" spans="1:7">
+    <row r="397" hidden="1" spans="1:7">
       <c r="A397" t="s">
         <v>615</v>
       </c>
@@ -12970,7 +12974,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="398" spans="1:7">
+    <row r="398" hidden="1" spans="1:7">
       <c r="A398" t="s">
         <v>617</v>
       </c>
@@ -12993,7 +12997,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="399" spans="1:7">
+    <row r="399" hidden="1" spans="1:7">
       <c r="A399" t="s">
         <v>620</v>
       </c>
@@ -13016,7 +13020,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="400" spans="1:7">
+    <row r="400" hidden="1" spans="1:7">
       <c r="A400" t="s">
         <v>622</v>
       </c>
@@ -13039,7 +13043,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="401" spans="1:7">
+    <row r="401" hidden="1" spans="1:7">
       <c r="A401" t="s">
         <v>273</v>
       </c>
@@ -13062,7 +13066,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="402" spans="1:7">
+    <row r="402" hidden="1" spans="1:7">
       <c r="A402" t="s">
         <v>624</v>
       </c>
@@ -13085,7 +13089,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="403" spans="1:7">
+    <row r="403" hidden="1" spans="1:7">
       <c r="A403" t="s">
         <v>625</v>
       </c>
@@ -13108,7 +13112,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="404" spans="1:7">
+    <row r="404" hidden="1" spans="1:7">
       <c r="A404" t="s">
         <v>302</v>
       </c>
@@ -13131,7 +13135,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="405" spans="1:7">
+    <row r="405" hidden="1" spans="1:7">
       <c r="A405" t="s">
         <v>583</v>
       </c>
@@ -13154,7 +13158,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="406" spans="1:7">
+    <row r="406" hidden="1" spans="1:7">
       <c r="A406" t="s">
         <v>585</v>
       </c>
@@ -13177,7 +13181,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="407" spans="1:7">
+    <row r="407" hidden="1" spans="1:7">
       <c r="A407" t="s">
         <v>282</v>
       </c>
@@ -13200,7 +13204,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="408" spans="1:7">
+    <row r="408" hidden="1" spans="1:7">
       <c r="A408" t="s">
         <v>588</v>
       </c>
@@ -13223,7 +13227,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="409" spans="1:7">
+    <row r="409" hidden="1" spans="1:7">
       <c r="A409" t="s">
         <v>594</v>
       </c>
@@ -13246,7 +13250,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="410" spans="1:7">
+    <row r="410" hidden="1" spans="1:7">
       <c r="A410" t="s">
         <v>625</v>
       </c>
@@ -13269,7 +13273,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="411" spans="1:7">
+    <row r="411" hidden="1" spans="1:7">
       <c r="A411" t="s">
         <v>590</v>
       </c>
@@ -13292,7 +13296,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="412" spans="1:7">
+    <row r="412" hidden="1" spans="1:7">
       <c r="A412" t="s">
         <v>611</v>
       </c>
@@ -13315,7 +13319,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="413" spans="1:7">
+    <row r="413" hidden="1" spans="1:7">
       <c r="A413" t="s">
         <v>250</v>
       </c>
@@ -13338,7 +13342,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="414" spans="1:7">
+    <row r="414" hidden="1" spans="1:7">
       <c r="A414" t="s">
         <v>595</v>
       </c>
@@ -13361,7 +13365,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="415" spans="1:7">
+    <row r="415" hidden="1" spans="1:7">
       <c r="A415" t="s">
         <v>604</v>
       </c>
@@ -13384,7 +13388,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="416" spans="1:7">
+    <row r="416" hidden="1" spans="1:7">
       <c r="A416" t="s">
         <v>598</v>
       </c>
@@ -13407,7 +13411,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="417" spans="1:7">
+    <row r="417" hidden="1" spans="1:7">
       <c r="A417" t="s">
         <v>622</v>
       </c>
@@ -13430,7 +13434,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="418" spans="1:7">
+    <row r="418" hidden="1" spans="1:7">
       <c r="A418" t="s">
         <v>601</v>
       </c>
@@ -13453,7 +13457,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="419" spans="1:7">
+    <row r="419" hidden="1" spans="1:7">
       <c r="A419" t="s">
         <v>617</v>
       </c>
@@ -13476,7 +13480,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="420" spans="1:7">
+    <row r="420" hidden="1" spans="1:7">
       <c r="A420" t="s">
         <v>265</v>
       </c>
@@ -13499,7 +13503,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="421" spans="1:7">
+    <row r="421" hidden="1" spans="1:7">
       <c r="A421" t="s">
         <v>620</v>
       </c>
@@ -13522,7 +13526,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="422" spans="1:7">
+    <row r="422" hidden="1" spans="1:7">
       <c r="A422" t="s">
         <v>607</v>
       </c>
@@ -13545,7 +13549,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="423" spans="1:7">
+    <row r="423" hidden="1" spans="1:7">
       <c r="A423" t="s">
         <v>615</v>
       </c>
@@ -13568,7 +13572,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="424" spans="1:7">
+    <row r="424" hidden="1" spans="1:7">
       <c r="A424" t="s">
         <v>624</v>
       </c>
@@ -13591,7 +13595,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="425" spans="1:7">
+    <row r="425" hidden="1" spans="1:7">
       <c r="A425" t="s">
         <v>273</v>
       </c>
@@ -13614,7 +13618,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="426" spans="1:7">
+    <row r="426" hidden="1" spans="1:7">
       <c r="A426" t="s">
         <v>602</v>
       </c>
@@ -13637,7 +13641,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="427" spans="1:7">
+    <row r="427" hidden="1" spans="1:7">
       <c r="A427" t="s">
         <v>595</v>
       </c>
@@ -13660,7 +13664,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="428" spans="1:7">
+    <row r="428" hidden="1" spans="1:7">
       <c r="A428" t="s">
         <v>611</v>
       </c>
@@ -13683,7 +13687,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="429" spans="1:7">
+    <row r="429" hidden="1" spans="1:7">
       <c r="A429" t="s">
         <v>649</v>
       </c>
@@ -13706,7 +13710,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="430" spans="1:7">
+    <row r="430" hidden="1" spans="1:7">
       <c r="A430" t="s">
         <v>625</v>
       </c>
@@ -13729,7 +13733,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="431" spans="1:7">
+    <row r="431" hidden="1" spans="1:7">
       <c r="A431" t="s">
         <v>265</v>
       </c>
@@ -13752,7 +13756,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="432" spans="1:7">
+    <row r="432" hidden="1" spans="1:7">
       <c r="A432" t="s">
         <v>653</v>
       </c>
@@ -13775,7 +13779,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="433" spans="1:7">
+    <row r="433" hidden="1" spans="1:7">
       <c r="A433" t="s">
         <v>655</v>
       </c>
@@ -13798,7 +13802,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="434" spans="1:7">
+    <row r="434" hidden="1" spans="1:7">
       <c r="A434" t="s">
         <v>657</v>
       </c>
@@ -13821,7 +13825,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="435" spans="1:7">
+    <row r="435" hidden="1" spans="1:7">
       <c r="A435" t="s">
         <v>660</v>
       </c>
@@ -13844,7 +13848,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="436" spans="1:7">
+    <row r="436" hidden="1" spans="1:7">
       <c r="A436" t="s">
         <v>661</v>
       </c>
@@ -13867,7 +13871,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="437" spans="1:7">
+    <row r="437" hidden="1" spans="1:7">
       <c r="A437" t="s">
         <v>607</v>
       </c>
@@ -13890,7 +13894,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="438" spans="1:7">
+    <row r="438" hidden="1" spans="1:7">
       <c r="A438" t="s">
         <v>250</v>
       </c>
@@ -13913,7 +13917,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="439" spans="1:7">
+    <row r="439" hidden="1" spans="1:7">
       <c r="A439" t="s">
         <v>302</v>
       </c>
@@ -13936,7 +13940,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="440" spans="1:7">
+    <row r="440" hidden="1" spans="1:7">
       <c r="A440" t="s">
         <v>666</v>
       </c>
@@ -13959,7 +13963,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="441" spans="1:7">
+    <row r="441" hidden="1" spans="1:7">
       <c r="A441" t="s">
         <v>667</v>
       </c>
@@ -13982,7 +13986,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="442" spans="1:7">
+    <row r="442" hidden="1" spans="1:7">
       <c r="A442" t="s">
         <v>669</v>
       </c>
@@ -14005,7 +14009,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="443" spans="1:7">
+    <row r="443" hidden="1" spans="1:7">
       <c r="A443" t="s">
         <v>282</v>
       </c>
@@ -14028,7 +14032,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="444" spans="1:7">
+    <row r="444" hidden="1" spans="1:7">
       <c r="A444" t="s">
         <v>620</v>
       </c>
@@ -14051,7 +14055,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="445" spans="1:7">
+    <row r="445" hidden="1" spans="1:7">
       <c r="A445" t="s">
         <v>673</v>
       </c>
@@ -14074,7 +14078,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="446" spans="1:7">
+    <row r="446" hidden="1" spans="1:7">
       <c r="A446" t="s">
         <v>615</v>
       </c>
@@ -14097,7 +14101,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="447" spans="1:7">
+    <row r="447" hidden="1" spans="1:7">
       <c r="A447" t="s">
         <v>675</v>
       </c>
@@ -14120,7 +14124,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="448" spans="1:7">
+    <row r="448" hidden="1" spans="1:7">
       <c r="A448" t="s">
         <v>676</v>
       </c>
@@ -14143,7 +14147,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="449" spans="1:7">
+    <row r="449" hidden="1" spans="1:7">
       <c r="A449" t="s">
         <v>302</v>
       </c>
@@ -14166,7 +14170,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="450" spans="1:7">
+    <row r="450" hidden="1" spans="1:7">
       <c r="A450" t="s">
         <v>583</v>
       </c>
@@ -14189,7 +14193,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="451" spans="1:7">
+    <row r="451" hidden="1" spans="1:7">
       <c r="A451" t="s">
         <v>250</v>
       </c>
@@ -14212,7 +14216,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="452" spans="1:7">
+    <row r="452" hidden="1" spans="1:7">
       <c r="A452" t="s">
         <v>282</v>
       </c>
@@ -14235,7 +14239,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="453" spans="1:7">
+    <row r="453" hidden="1" spans="1:7">
       <c r="A453" t="s">
         <v>588</v>
       </c>
@@ -14258,7 +14262,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="454" spans="1:7">
+    <row r="454" hidden="1" spans="1:7">
       <c r="A454" t="s">
         <v>617</v>
       </c>
@@ -14281,7 +14285,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="455" spans="1:7">
+    <row r="455" hidden="1" spans="1:7">
       <c r="A455" t="s">
         <v>625</v>
       </c>
@@ -14304,7 +14308,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="456" spans="1:7">
+    <row r="456" hidden="1" spans="1:7">
       <c r="A456" t="s">
         <v>604</v>
       </c>
@@ -14327,7 +14331,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="457" spans="1:7">
+    <row r="457" hidden="1" spans="1:7">
       <c r="A457" t="s">
         <v>622</v>
       </c>
@@ -14350,7 +14354,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="458" spans="1:7">
+    <row r="458" hidden="1" spans="1:7">
       <c r="A458" t="s">
         <v>611</v>
       </c>
@@ -14373,7 +14377,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="459" spans="1:7">
+    <row r="459" hidden="1" spans="1:7">
       <c r="A459" t="s">
         <v>595</v>
       </c>
@@ -14396,7 +14400,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="460" spans="1:7">
+    <row r="460" hidden="1" spans="1:7">
       <c r="A460" t="s">
         <v>624</v>
       </c>
@@ -14419,7 +14423,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="461" spans="1:7">
+    <row r="461" hidden="1" spans="1:7">
       <c r="A461" t="s">
         <v>590</v>
       </c>
@@ -14442,7 +14446,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="462" spans="1:7">
+    <row r="462" hidden="1" spans="1:7">
       <c r="A462" t="s">
         <v>607</v>
       </c>
@@ -14465,7 +14469,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="463" spans="1:7">
+    <row r="463" hidden="1" spans="1:7">
       <c r="A463" t="s">
         <v>594</v>
       </c>
@@ -14488,7 +14492,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="464" spans="1:7">
+    <row r="464" hidden="1" spans="1:7">
       <c r="A464" t="s">
         <v>602</v>
       </c>
@@ -14511,7 +14515,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="465" spans="1:7">
+    <row r="465" hidden="1" spans="1:7">
       <c r="A465" t="s">
         <v>585</v>
       </c>
@@ -14534,7 +14538,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="466" spans="1:7">
+    <row r="466" hidden="1" spans="1:7">
       <c r="A466" t="s">
         <v>620</v>
       </c>
@@ -14557,7 +14561,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="467" spans="1:7">
+    <row r="467" hidden="1" spans="1:7">
       <c r="A467" t="s">
         <v>601</v>
       </c>
@@ -14580,7 +14584,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="468" spans="1:7">
+    <row r="468" hidden="1" spans="1:7">
       <c r="A468" t="s">
         <v>615</v>
       </c>
@@ -14603,7 +14607,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="469" spans="1:7">
+    <row r="469" hidden="1" spans="1:7">
       <c r="A469" t="s">
         <v>598</v>
       </c>
@@ -14626,7 +14630,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="470" spans="1:7">
+    <row r="470" hidden="1" spans="1:7">
       <c r="A470" t="s">
         <v>265</v>
       </c>
@@ -14649,7 +14653,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="471" spans="1:7">
+    <row r="471" hidden="1" spans="1:7">
       <c r="A471" t="s">
         <v>273</v>
       </c>
@@ -14672,7 +14676,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="472" spans="1:7">
+    <row r="472" hidden="1" spans="1:7">
       <c r="A472" t="s">
         <v>302</v>
       </c>
@@ -14695,7 +14699,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="473" spans="1:7">
+    <row r="473" hidden="1" spans="1:7">
       <c r="A473" t="s">
         <v>583</v>
       </c>
@@ -14718,7 +14722,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="474" spans="1:7">
+    <row r="474" hidden="1" spans="1:7">
       <c r="A474" t="s">
         <v>250</v>
       </c>
@@ -14741,7 +14745,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="475" spans="1:7">
+    <row r="475" hidden="1" spans="1:7">
       <c r="A475" t="s">
         <v>282</v>
       </c>
@@ -14764,7 +14768,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="476" spans="1:7">
+    <row r="476" hidden="1" spans="1:7">
       <c r="A476" t="s">
         <v>588</v>
       </c>
@@ -14787,7 +14791,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="477" spans="1:7">
+    <row r="477" hidden="1" spans="1:7">
       <c r="A477" t="s">
         <v>620</v>
       </c>
@@ -14810,7 +14814,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="478" spans="1:7">
+    <row r="478" hidden="1" spans="1:7">
       <c r="A478" t="s">
         <v>590</v>
       </c>
@@ -14833,7 +14837,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="479" spans="1:7">
+    <row r="479" hidden="1" spans="1:7">
       <c r="A479" t="s">
         <v>604</v>
       </c>
@@ -14856,7 +14860,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="480" spans="1:7">
+    <row r="480" hidden="1" spans="1:7">
       <c r="A480" t="s">
         <v>615</v>
       </c>
@@ -14879,7 +14883,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="481" spans="1:7">
+    <row r="481" hidden="1" spans="1:7">
       <c r="A481" t="s">
         <v>594</v>
       </c>
@@ -14902,7 +14906,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="482" spans="1:7">
+    <row r="482" hidden="1" spans="1:7">
       <c r="A482" t="s">
         <v>595</v>
       </c>
@@ -14925,7 +14929,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="483" spans="1:7">
+    <row r="483" hidden="1" spans="1:7">
       <c r="A483" t="s">
         <v>624</v>
       </c>
@@ -14948,7 +14952,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="484" spans="1:7">
+    <row r="484" hidden="1" spans="1:7">
       <c r="A484" t="s">
         <v>601</v>
       </c>
@@ -14971,7 +14975,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="485" spans="1:7">
+    <row r="485" hidden="1" spans="1:7">
       <c r="A485" t="s">
         <v>607</v>
       </c>
@@ -14994,7 +14998,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="486" spans="1:7">
+    <row r="486" hidden="1" spans="1:7">
       <c r="A486" t="s">
         <v>598</v>
       </c>
@@ -15017,7 +15021,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="487" spans="1:7">
+    <row r="487" hidden="1" spans="1:7">
       <c r="A487" t="s">
         <v>611</v>
       </c>
@@ -15040,7 +15044,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="488" spans="1:7">
+    <row r="488" hidden="1" spans="1:7">
       <c r="A488" t="s">
         <v>617</v>
       </c>
@@ -15063,7 +15067,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="489" spans="1:7">
+    <row r="489" hidden="1" spans="1:7">
       <c r="A489" t="s">
         <v>625</v>
       </c>
@@ -15086,7 +15090,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="490" spans="1:7">
+    <row r="490" hidden="1" spans="1:7">
       <c r="A490" t="s">
         <v>622</v>
       </c>
@@ -15109,7 +15113,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="491" spans="1:7">
+    <row r="491" hidden="1" spans="1:7">
       <c r="A491" t="s">
         <v>585</v>
       </c>
@@ -15132,7 +15136,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="492" spans="1:7">
+    <row r="492" hidden="1" spans="1:7">
       <c r="A492" t="s">
         <v>265</v>
       </c>
@@ -15155,7 +15159,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="493" spans="1:7">
+    <row r="493" hidden="1" spans="1:7">
       <c r="A493" t="s">
         <v>273</v>
       </c>
@@ -15178,7 +15182,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="494" spans="1:7">
+    <row r="494" hidden="1" spans="1:7">
       <c r="A494" t="s">
         <v>602</v>
       </c>
@@ -15201,7 +15205,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="495" spans="1:7">
+    <row r="495" hidden="1" spans="1:7">
       <c r="A495" t="s">
         <v>716</v>
       </c>
@@ -15224,7 +15228,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="496" spans="1:7">
+    <row r="496" hidden="1" spans="1:7">
       <c r="A496" t="s">
         <v>720</v>
       </c>
@@ -15247,7 +15251,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="497" spans="1:7">
+    <row r="497" hidden="1" spans="1:7">
       <c r="A497" t="s">
         <v>724</v>
       </c>
@@ -15270,7 +15274,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="498" spans="1:7">
+    <row r="498" hidden="1" spans="1:7">
       <c r="A498" t="s">
         <v>728</v>
       </c>
@@ -15293,7 +15297,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="499" spans="1:7">
+    <row r="499" hidden="1" spans="1:7">
       <c r="A499" t="s">
         <v>730</v>
       </c>
@@ -15316,7 +15320,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="500" spans="1:7">
+    <row r="500" hidden="1" spans="1:7">
       <c r="A500" t="s">
         <v>731</v>
       </c>
@@ -15339,7 +15343,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="501" spans="1:7">
+    <row r="501" hidden="1" spans="1:7">
       <c r="A501" t="s">
         <v>732</v>
       </c>
@@ -15362,7 +15366,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="502" spans="1:7">
+    <row r="502" hidden="1" spans="1:7">
       <c r="A502" t="s">
         <v>734</v>
       </c>
@@ -15370,7 +15374,7 @@
         <v>8</v>
       </c>
       <c r="C502" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="D502" t="s">
         <v>10</v>
@@ -15385,7 +15389,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="503" spans="1:7">
+    <row r="503" hidden="1" spans="1:7">
       <c r="A503" t="s">
         <v>736</v>
       </c>
@@ -15408,7 +15412,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="504" spans="1:7">
+    <row r="504" hidden="1" spans="1:7">
       <c r="A504" t="s">
         <v>737</v>
       </c>
@@ -15431,7 +15435,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="505" spans="1:7">
+    <row r="505" hidden="1" spans="1:7">
       <c r="A505" t="s">
         <v>737</v>
       </c>
@@ -15454,7 +15458,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="506" spans="1:7">
+    <row r="506" hidden="1" spans="1:7">
       <c r="A506" t="s">
         <v>734</v>
       </c>
@@ -15462,7 +15466,7 @@
         <v>8</v>
       </c>
       <c r="C506" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="D506" t="s">
         <v>18</v>
@@ -15477,7 +15481,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="507" spans="1:7">
+    <row r="507" hidden="1" spans="1:7">
       <c r="A507" t="s">
         <v>738</v>
       </c>
@@ -15500,7 +15504,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="508" spans="1:7">
+    <row r="508" hidden="1" spans="1:7">
       <c r="A508" t="s">
         <v>741</v>
       </c>
@@ -15523,7 +15527,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="509" spans="1:7">
+    <row r="509" hidden="1" spans="1:7">
       <c r="A509" t="s">
         <v>724</v>
       </c>
@@ -15546,7 +15550,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="510" spans="1:7">
+    <row r="510" hidden="1" spans="1:7">
       <c r="A510" t="s">
         <v>743</v>
       </c>
@@ -15569,7 +15573,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="511" spans="1:7">
+    <row r="511" hidden="1" spans="1:7">
       <c r="A511" t="s">
         <v>745</v>
       </c>
@@ -15592,7 +15596,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="512" spans="1:7">
+    <row r="512" hidden="1" spans="1:7">
       <c r="A512" t="s">
         <v>746</v>
       </c>
@@ -15615,7 +15619,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="513" spans="1:7">
+    <row r="513" hidden="1" spans="1:7">
       <c r="A513" t="s">
         <v>747</v>
       </c>
@@ -15638,7 +15642,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="514" spans="1:7">
+    <row r="514" hidden="1" spans="1:7">
       <c r="A514" t="s">
         <v>750</v>
       </c>
@@ -15661,7 +15665,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="515" spans="1:7">
+    <row r="515" hidden="1" spans="1:7">
       <c r="A515" t="s">
         <v>751</v>
       </c>
@@ -15669,7 +15673,7 @@
         <v>8</v>
       </c>
       <c r="C515" t="s">
-        <v>752</v>
+        <v>47</v>
       </c>
       <c r="D515" t="s">
         <v>143</v>
@@ -15684,12 +15688,12 @@
         <v>749</v>
       </c>
     </row>
-    <row r="516" spans="1:7">
+    <row r="516" hidden="1" spans="1:7">
       <c r="A516" t="s">
+        <v>752</v>
+      </c>
+      <c r="B516" t="s">
         <v>753</v>
-      </c>
-      <c r="B516" t="s">
-        <v>754</v>
       </c>
       <c r="C516" t="s">
         <v>308</v>
@@ -15707,7 +15711,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="517" spans="1:7">
+    <row r="517" hidden="1" spans="1:7">
       <c r="A517" t="s">
         <v>730</v>
       </c>
@@ -15730,7 +15734,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="518" spans="1:7">
+    <row r="518" hidden="1" spans="1:7">
       <c r="A518" t="s">
         <v>731</v>
       </c>
@@ -15753,12 +15757,12 @@
         <v>749</v>
       </c>
     </row>
-    <row r="519" spans="1:7">
+    <row r="519" hidden="1" spans="1:7">
       <c r="A519" t="s">
         <v>732</v>
       </c>
       <c r="B519" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C519" t="s">
         <v>332</v>
@@ -15776,12 +15780,12 @@
         <v>749</v>
       </c>
     </row>
-    <row r="520" spans="1:7">
+    <row r="520" hidden="1" spans="1:7">
       <c r="A520" t="s">
         <v>333</v>
       </c>
       <c r="B520" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C520" t="s">
         <v>335</v>
@@ -15799,15 +15803,15 @@
         <v>749</v>
       </c>
     </row>
-    <row r="521" spans="1:7">
+    <row r="521" hidden="1" spans="1:7">
       <c r="A521" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B521" t="s">
         <v>8</v>
       </c>
       <c r="C521" t="s">
-        <v>752</v>
+        <v>47</v>
       </c>
       <c r="D521" t="s">
         <v>90</v>
@@ -15816,15 +15820,15 @@
         <v>44</v>
       </c>
       <c r="F521" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G521" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="522" spans="1:7">
+    <row r="522" hidden="1" spans="1:7">
       <c r="A522" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B522" t="s">
         <v>8</v>
@@ -15839,18 +15843,18 @@
         <v>44</v>
       </c>
       <c r="F522" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G522" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="523" spans="1:7">
+    <row r="523" hidden="1" spans="1:7">
       <c r="A523" t="s">
+        <v>759</v>
+      </c>
+      <c r="B523" t="s">
         <v>760</v>
-      </c>
-      <c r="B523" t="s">
-        <v>761</v>
       </c>
       <c r="C523" t="s">
         <v>337</v>
@@ -15868,12 +15872,12 @@
         <v>749</v>
       </c>
     </row>
-    <row r="524" spans="1:7">
+    <row r="524" hidden="1" spans="1:7">
       <c r="A524" t="s">
         <v>341</v>
       </c>
       <c r="B524" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C524" t="s">
         <v>335</v>
@@ -15891,12 +15895,12 @@
         <v>749</v>
       </c>
     </row>
-    <row r="525" spans="1:7">
+    <row r="525" hidden="1" spans="1:7">
       <c r="A525" t="s">
+        <v>762</v>
+      </c>
+      <c r="B525" t="s">
         <v>763</v>
-      </c>
-      <c r="B525" t="s">
-        <v>764</v>
       </c>
       <c r="C525" t="s">
         <v>359</v>
@@ -15914,12 +15918,12 @@
         <v>749</v>
       </c>
     </row>
-    <row r="526" spans="1:7">
+    <row r="526" hidden="1" spans="1:7">
       <c r="A526" t="s">
+        <v>764</v>
+      </c>
+      <c r="B526" t="s">
         <v>765</v>
-      </c>
-      <c r="B526" t="s">
-        <v>766</v>
       </c>
       <c r="C526" t="s">
         <v>348</v>
@@ -15937,12 +15941,12 @@
         <v>749</v>
       </c>
     </row>
-    <row r="527" spans="1:7">
+    <row r="527" hidden="1" spans="1:7">
       <c r="A527" t="s">
+        <v>766</v>
+      </c>
+      <c r="B527" t="s">
         <v>767</v>
-      </c>
-      <c r="B527" t="s">
-        <v>768</v>
       </c>
       <c r="C527" t="s">
         <v>348</v>
@@ -15960,12 +15964,12 @@
         <v>749</v>
       </c>
     </row>
-    <row r="528" spans="1:7">
+    <row r="528" hidden="1" spans="1:7">
       <c r="A528" t="s">
+        <v>768</v>
+      </c>
+      <c r="B528" t="s">
         <v>769</v>
-      </c>
-      <c r="B528" t="s">
-        <v>770</v>
       </c>
       <c r="C528" t="s">
         <v>246</v>
@@ -15983,12 +15987,12 @@
         <v>749</v>
       </c>
     </row>
-    <row r="529" spans="1:7">
+    <row r="529" hidden="1" spans="1:7">
       <c r="A529" t="s">
+        <v>770</v>
+      </c>
+      <c r="B529" t="s">
         <v>771</v>
-      </c>
-      <c r="B529" t="s">
-        <v>772</v>
       </c>
       <c r="C529" t="s">
         <v>246</v>
@@ -16006,9 +16010,9 @@
         <v>749</v>
       </c>
     </row>
-    <row r="530" spans="1:7">
+    <row r="530" hidden="1" spans="1:7">
       <c r="A530" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B530" t="s">
         <v>66</v>
@@ -16023,13 +16027,13 @@
         <v>11</v>
       </c>
       <c r="F530" t="s">
+        <v>773</v>
+      </c>
+      <c r="G530" t="s">
         <v>774</v>
       </c>
-      <c r="G530" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="531" spans="1:7">
+    </row>
+    <row r="531" hidden="1" spans="1:7">
       <c r="A531" t="s">
         <v>318</v>
       </c>
@@ -16046,18 +16050,18 @@
         <v>11</v>
       </c>
       <c r="F531" t="s">
+        <v>773</v>
+      </c>
+      <c r="G531" t="s">
         <v>774</v>
       </c>
-      <c r="G531" t="s">
+    </row>
+    <row r="532" hidden="1" spans="1:7">
+      <c r="A532" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="532" spans="1:7">
-      <c r="A532" t="s">
+      <c r="B532" t="s">
         <v>776</v>
-      </c>
-      <c r="B532" t="s">
-        <v>777</v>
       </c>
       <c r="C532" t="s">
         <v>298</v>
@@ -16069,13 +16073,13 @@
         <v>11</v>
       </c>
       <c r="F532" t="s">
+        <v>773</v>
+      </c>
+      <c r="G532" t="s">
         <v>774</v>
       </c>
-      <c r="G532" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="533" spans="1:7">
+    </row>
+    <row r="533" hidden="1" spans="1:7">
       <c r="A533" t="s">
         <v>730</v>
       </c>
@@ -16092,13 +16096,13 @@
         <v>20</v>
       </c>
       <c r="F533" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G533" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="534" spans="1:7">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="534" hidden="1" spans="1:7">
       <c r="A534" t="s">
         <v>731</v>
       </c>
@@ -16115,18 +16119,18 @@
         <v>20</v>
       </c>
       <c r="F534" t="s">
+        <v>773</v>
+      </c>
+      <c r="G534" t="s">
         <v>774</v>
       </c>
-      <c r="G534" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="535" spans="1:7">
+    </row>
+    <row r="535" hidden="1" spans="1:7">
       <c r="A535" t="s">
         <v>732</v>
       </c>
       <c r="B535" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C535" t="s">
         <v>332</v>
@@ -16141,15 +16145,15 @@
         <v>39</v>
       </c>
       <c r="G535" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="536" spans="1:7">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="536" hidden="1" spans="1:7">
       <c r="A536" t="s">
+        <v>779</v>
+      </c>
+      <c r="B536" t="s">
         <v>780</v>
-      </c>
-      <c r="B536" t="s">
-        <v>781</v>
       </c>
       <c r="C536" t="s">
         <v>320</v>
@@ -16161,18 +16165,18 @@
         <v>44</v>
       </c>
       <c r="F536" t="s">
+        <v>773</v>
+      </c>
+      <c r="G536" t="s">
         <v>774</v>
       </c>
-      <c r="G536" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="537" spans="1:7">
+    </row>
+    <row r="537" hidden="1" spans="1:7">
       <c r="A537" t="s">
+        <v>781</v>
+      </c>
+      <c r="B537" t="s">
         <v>782</v>
-      </c>
-      <c r="B537" t="s">
-        <v>783</v>
       </c>
       <c r="C537" t="s">
         <v>345</v>
@@ -16184,18 +16188,18 @@
         <v>44</v>
       </c>
       <c r="F537" t="s">
+        <v>773</v>
+      </c>
+      <c r="G537" t="s">
         <v>774</v>
       </c>
-      <c r="G537" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="538" spans="1:7">
+    </row>
+    <row r="538" hidden="1" spans="1:7">
       <c r="A538" t="s">
+        <v>783</v>
+      </c>
+      <c r="B538" t="s">
         <v>784</v>
-      </c>
-      <c r="B538" t="s">
-        <v>785</v>
       </c>
       <c r="C538" t="s">
         <v>345</v>
@@ -16207,18 +16211,18 @@
         <v>44</v>
       </c>
       <c r="F538" t="s">
+        <v>773</v>
+      </c>
+      <c r="G538" t="s">
         <v>774</v>
       </c>
-      <c r="G538" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="539" spans="1:7">
+    </row>
+    <row r="539" hidden="1" spans="1:7">
       <c r="A539" t="s">
+        <v>785</v>
+      </c>
+      <c r="B539" t="s">
         <v>786</v>
-      </c>
-      <c r="B539" t="s">
-        <v>787</v>
       </c>
       <c r="C539" t="s">
         <v>464</v>
@@ -16230,18 +16234,18 @@
         <v>44</v>
       </c>
       <c r="F539" t="s">
+        <v>773</v>
+      </c>
+      <c r="G539" t="s">
         <v>774</v>
       </c>
-      <c r="G539" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="540" spans="1:7">
+    </row>
+    <row r="540" hidden="1" spans="1:7">
       <c r="A540" t="s">
+        <v>787</v>
+      </c>
+      <c r="B540" t="s">
         <v>788</v>
-      </c>
-      <c r="B540" t="s">
-        <v>789</v>
       </c>
       <c r="C540" t="s">
         <v>351</v>
@@ -16253,18 +16257,18 @@
         <v>61</v>
       </c>
       <c r="F540" t="s">
+        <v>773</v>
+      </c>
+      <c r="G540" t="s">
         <v>774</v>
       </c>
-      <c r="G540" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="541" spans="1:7">
+    </row>
+    <row r="541" hidden="1" spans="1:7">
       <c r="A541" t="s">
+        <v>789</v>
+      </c>
+      <c r="B541" t="s">
         <v>790</v>
-      </c>
-      <c r="B541" t="s">
-        <v>791</v>
       </c>
       <c r="C541" t="s">
         <v>351</v>
@@ -16276,15 +16280,15 @@
         <v>61</v>
       </c>
       <c r="F541" t="s">
+        <v>773</v>
+      </c>
+      <c r="G541" t="s">
         <v>774</v>
       </c>
-      <c r="G541" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="542" spans="1:7">
+    </row>
+    <row r="542" hidden="1" spans="1:7">
       <c r="A542" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B542" t="s">
         <v>8</v>
@@ -16293,21 +16297,21 @@
         <v>320</v>
       </c>
       <c r="D542" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E542" t="s">
         <v>71</v>
       </c>
       <c r="F542" t="s">
+        <v>793</v>
+      </c>
+      <c r="G542" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="543" hidden="1" spans="1:7">
+      <c r="A543" t="s">
         <v>794</v>
-      </c>
-      <c r="G542" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="543" spans="1:7">
-      <c r="A543" t="s">
-        <v>795</v>
       </c>
       <c r="B543" t="s">
         <v>8</v>
@@ -16322,18 +16326,18 @@
         <v>71</v>
       </c>
       <c r="F543" t="s">
+        <v>795</v>
+      </c>
+      <c r="G543" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="544" hidden="1" spans="1:7">
+      <c r="A544" t="s">
         <v>796</v>
       </c>
-      <c r="G543" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="544" spans="1:7">
-      <c r="A544" t="s">
+      <c r="B544" t="s">
         <v>797</v>
-      </c>
-      <c r="B544" t="s">
-        <v>798</v>
       </c>
       <c r="C544" t="s">
         <v>323</v>
@@ -16345,15 +16349,15 @@
         <v>71</v>
       </c>
       <c r="F544" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="G544" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="545" spans="1:7">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="545" hidden="1" spans="1:7">
       <c r="A545" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B545" t="s">
         <v>8</v>
@@ -16368,18 +16372,18 @@
         <v>71</v>
       </c>
       <c r="F545" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G545" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="546" spans="1:7">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="546" hidden="1" spans="1:7">
       <c r="A546" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B546" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C546" t="s">
         <v>323</v>
@@ -16391,15 +16395,15 @@
         <v>71</v>
       </c>
       <c r="F546" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="G546" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="547" spans="1:7">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="547" hidden="1" spans="1:7">
       <c r="A547" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B547" t="s">
         <v>8</v>
@@ -16408,27 +16412,27 @@
         <v>320</v>
       </c>
       <c r="D547" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="E547" t="s">
         <v>71</v>
       </c>
       <c r="F547" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G547" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="548" spans="1:7">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="548" hidden="1" spans="1:7">
       <c r="A548" t="s">
+        <v>802</v>
+      </c>
+      <c r="B548" t="s">
         <v>803</v>
       </c>
-      <c r="B548" t="s">
+      <c r="C548" t="s">
         <v>804</v>
-      </c>
-      <c r="C548" t="s">
-        <v>805</v>
       </c>
       <c r="D548" t="s">
         <v>43</v>
@@ -16437,18 +16441,18 @@
         <v>11</v>
       </c>
       <c r="F548" t="s">
+        <v>805</v>
+      </c>
+      <c r="G548" t="s">
         <v>806</v>
       </c>
-      <c r="G548" t="s">
+    </row>
+    <row r="549" hidden="1" spans="1:7">
+      <c r="A549" t="s">
         <v>807</v>
       </c>
-    </row>
-    <row r="549" spans="1:7">
-      <c r="A549" t="s">
+      <c r="B549" t="s">
         <v>808</v>
-      </c>
-      <c r="B549" t="s">
-        <v>809</v>
       </c>
       <c r="C549" t="s">
         <v>597</v>
@@ -16460,21 +16464,21 @@
         <v>11</v>
       </c>
       <c r="F549" t="s">
+        <v>809</v>
+      </c>
+      <c r="G549" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="550" hidden="1" spans="1:7">
+      <c r="A550" t="s">
         <v>810</v>
       </c>
-      <c r="G549" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="550" spans="1:7">
-      <c r="A550" t="s">
+      <c r="B550" t="s">
         <v>811</v>
       </c>
-      <c r="B550" t="s">
-        <v>812</v>
-      </c>
       <c r="C550" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D550" t="s">
         <v>32</v>
@@ -16483,21 +16487,21 @@
         <v>11</v>
       </c>
       <c r="F550" t="s">
+        <v>812</v>
+      </c>
+      <c r="G550" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="551" hidden="1" spans="1:7">
+      <c r="A551" t="s">
         <v>813</v>
       </c>
-      <c r="G550" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="551" spans="1:7">
-      <c r="A551" t="s">
+      <c r="B551" t="s">
         <v>814</v>
       </c>
-      <c r="B551" t="s">
-        <v>815</v>
-      </c>
       <c r="C551" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D551" t="s">
         <v>17</v>
@@ -16506,21 +16510,21 @@
         <v>11</v>
       </c>
       <c r="F551" t="s">
+        <v>805</v>
+      </c>
+      <c r="G551" t="s">
         <v>806</v>
       </c>
-      <c r="G551" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="552" spans="1:7">
+    </row>
+    <row r="552" hidden="1" spans="1:7">
       <c r="A552" t="s">
+        <v>815</v>
+      </c>
+      <c r="B552" t="s">
         <v>816</v>
       </c>
-      <c r="B552" t="s">
-        <v>817</v>
-      </c>
       <c r="C552" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D552" t="s">
         <v>59</v>
@@ -16529,18 +16533,18 @@
         <v>11</v>
       </c>
       <c r="F552" t="s">
+        <v>805</v>
+      </c>
+      <c r="G552" t="s">
         <v>806</v>
       </c>
-      <c r="G552" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="553" spans="1:7">
+    </row>
+    <row r="553" hidden="1" spans="1:7">
       <c r="A553" t="s">
         <v>730</v>
       </c>
       <c r="B553" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C553" t="s">
         <v>323</v>
@@ -16552,18 +16556,18 @@
         <v>20</v>
       </c>
       <c r="F553" t="s">
+        <v>805</v>
+      </c>
+      <c r="G553" t="s">
         <v>806</v>
       </c>
-      <c r="G553" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="554" spans="1:7">
+    </row>
+    <row r="554" hidden="1" spans="1:7">
       <c r="A554" t="s">
         <v>731</v>
       </c>
       <c r="B554" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C554" t="s">
         <v>323</v>
@@ -16575,18 +16579,18 @@
         <v>20</v>
       </c>
       <c r="F554" t="s">
+        <v>805</v>
+      </c>
+      <c r="G554" t="s">
         <v>806</v>
       </c>
-      <c r="G554" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="555" spans="1:7">
+    </row>
+    <row r="555" hidden="1" spans="1:7">
       <c r="A555" t="s">
+        <v>819</v>
+      </c>
+      <c r="B555" t="s">
         <v>820</v>
-      </c>
-      <c r="B555" t="s">
-        <v>821</v>
       </c>
       <c r="C555" t="s">
         <v>332</v>
@@ -16601,15 +16605,15 @@
         <v>39</v>
       </c>
       <c r="G555" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="556" spans="1:7">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="556" hidden="1" spans="1:7">
       <c r="A556" t="s">
+        <v>821</v>
+      </c>
+      <c r="B556" t="s">
         <v>822</v>
-      </c>
-      <c r="B556" t="s">
-        <v>823</v>
       </c>
       <c r="C556" t="s">
         <v>522</v>
@@ -16621,18 +16625,18 @@
         <v>44</v>
       </c>
       <c r="F556" t="s">
+        <v>823</v>
+      </c>
+      <c r="G556" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="557" hidden="1" spans="1:7">
+      <c r="A557" t="s">
         <v>824</v>
       </c>
-      <c r="G556" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="557" spans="1:7">
-      <c r="A557" t="s">
+      <c r="B557" t="s">
         <v>825</v>
-      </c>
-      <c r="B557" t="s">
-        <v>826</v>
       </c>
       <c r="C557" t="s">
         <v>609</v>
@@ -16644,18 +16648,18 @@
         <v>44</v>
       </c>
       <c r="F557" t="s">
+        <v>805</v>
+      </c>
+      <c r="G557" t="s">
         <v>806</v>
       </c>
-      <c r="G557" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="558" spans="1:7">
+    </row>
+    <row r="558" hidden="1" spans="1:7">
       <c r="A558" t="s">
+        <v>826</v>
+      </c>
+      <c r="B558" t="s">
         <v>827</v>
-      </c>
-      <c r="B558" t="s">
-        <v>828</v>
       </c>
       <c r="C558" t="s">
         <v>609</v>
@@ -16667,18 +16671,18 @@
         <v>44</v>
       </c>
       <c r="F558" t="s">
+        <v>805</v>
+      </c>
+      <c r="G558" t="s">
         <v>806</v>
       </c>
-      <c r="G558" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="559" spans="1:7">
+    </row>
+    <row r="559" hidden="1" spans="1:7">
       <c r="A559" t="s">
+        <v>828</v>
+      </c>
+      <c r="B559" t="s">
         <v>829</v>
-      </c>
-      <c r="B559" t="s">
-        <v>830</v>
       </c>
       <c r="C559" t="s">
         <v>274</v>
@@ -16690,21 +16694,21 @@
         <v>44</v>
       </c>
       <c r="F559" t="s">
+        <v>805</v>
+      </c>
+      <c r="G559" t="s">
         <v>806</v>
       </c>
-      <c r="G559" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="560" spans="1:7">
+    </row>
+    <row r="560" hidden="1" spans="1:7">
       <c r="A560" t="s">
+        <v>830</v>
+      </c>
+      <c r="B560" t="s">
         <v>831</v>
       </c>
-      <c r="B560" t="s">
+      <c r="C560" t="s">
         <v>832</v>
-      </c>
-      <c r="C560" t="s">
-        <v>833</v>
       </c>
       <c r="D560" t="s">
         <v>59</v>
@@ -16713,21 +16717,21 @@
         <v>44</v>
       </c>
       <c r="F560" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="G560" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="561" spans="1:7">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="561" hidden="1" spans="1:7">
       <c r="A561" t="s">
+        <v>833</v>
+      </c>
+      <c r="B561" t="s">
         <v>834</v>
       </c>
-      <c r="B561" t="s">
-        <v>835</v>
-      </c>
       <c r="C561" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D561" t="s">
         <v>17</v>
@@ -16736,21 +16740,21 @@
         <v>61</v>
       </c>
       <c r="F561" t="s">
+        <v>805</v>
+      </c>
+      <c r="G561" t="s">
         <v>806</v>
       </c>
-      <c r="G561" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="562" spans="1:7">
+    </row>
+    <row r="562" hidden="1" spans="1:7">
       <c r="A562" t="s">
+        <v>835</v>
+      </c>
+      <c r="B562" t="s">
         <v>836</v>
       </c>
-      <c r="B562" t="s">
-        <v>837</v>
-      </c>
       <c r="C562" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D562" t="s">
         <v>59</v>
@@ -16759,18 +16763,18 @@
         <v>61</v>
       </c>
       <c r="F562" t="s">
+        <v>805</v>
+      </c>
+      <c r="G562" t="s">
         <v>806</v>
       </c>
-      <c r="G562" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="563" spans="1:7">
+    </row>
+    <row r="563" hidden="1" spans="1:7">
       <c r="A563" t="s">
+        <v>837</v>
+      </c>
+      <c r="B563" t="s">
         <v>838</v>
-      </c>
-      <c r="B563" t="s">
-        <v>839</v>
       </c>
       <c r="C563" t="s">
         <v>609</v>
@@ -16782,18 +16786,18 @@
         <v>71</v>
       </c>
       <c r="F563" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="G563" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="564" spans="1:7">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="564" hidden="1" spans="1:7">
       <c r="A564" t="s">
+        <v>839</v>
+      </c>
+      <c r="B564" t="s">
         <v>840</v>
-      </c>
-      <c r="B564" t="s">
-        <v>841</v>
       </c>
       <c r="C564" t="s">
         <v>597</v>
@@ -16805,18 +16809,18 @@
         <v>71</v>
       </c>
       <c r="F564" t="s">
+        <v>805</v>
+      </c>
+      <c r="G564" t="s">
         <v>806</v>
       </c>
-      <c r="G564" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="565" spans="1:7">
+    </row>
+    <row r="565" hidden="1" spans="1:7">
       <c r="A565" t="s">
+        <v>841</v>
+      </c>
+      <c r="B565" t="s">
         <v>842</v>
-      </c>
-      <c r="B565" t="s">
-        <v>843</v>
       </c>
       <c r="C565" t="s">
         <v>323</v>
@@ -16828,13 +16832,13 @@
         <v>11</v>
       </c>
       <c r="F565" t="s">
+        <v>843</v>
+      </c>
+      <c r="G565" t="s">
         <v>844</v>
       </c>
-      <c r="G565" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="566" spans="1:7">
+    </row>
+    <row r="566" hidden="1" spans="1:7">
       <c r="A566" t="s">
         <v>318</v>
       </c>
@@ -16854,15 +16858,15 @@
         <v>55</v>
       </c>
       <c r="G566" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="567" hidden="1" spans="1:7">
+      <c r="A567" t="s">
+        <v>779</v>
+      </c>
+      <c r="B567" t="s">
         <v>845</v>
-      </c>
-    </row>
-    <row r="567" spans="1:7">
-      <c r="A567" t="s">
-        <v>780</v>
-      </c>
-      <c r="B567" t="s">
-        <v>846</v>
       </c>
       <c r="C567" t="s">
         <v>320</v>
@@ -16877,10 +16881,10 @@
         <v>55</v>
       </c>
       <c r="G567" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="568" spans="1:7">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="568" hidden="1" spans="1:7">
       <c r="A568" t="s">
         <v>730</v>
       </c>
@@ -16897,13 +16901,13 @@
         <v>20</v>
       </c>
       <c r="F568" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G568" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="569" spans="1:7">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="569" hidden="1" spans="1:7">
       <c r="A569" t="s">
         <v>731</v>
       </c>
@@ -16923,15 +16927,15 @@
         <v>55</v>
       </c>
       <c r="G569" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="570" spans="1:7">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="570" hidden="1" spans="1:7">
       <c r="A570" t="s">
         <v>732</v>
       </c>
       <c r="B570" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C570" t="s">
         <v>332</v>
@@ -16946,15 +16950,15 @@
         <v>39</v>
       </c>
       <c r="G570" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="571" spans="1:7">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="571" hidden="1" spans="1:7">
       <c r="A571" t="s">
+        <v>848</v>
+      </c>
+      <c r="B571" t="s">
         <v>849</v>
-      </c>
-      <c r="B571" t="s">
-        <v>850</v>
       </c>
       <c r="C571" t="s">
         <v>246</v>
@@ -16969,15 +16973,15 @@
         <v>55</v>
       </c>
       <c r="G571" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="572" spans="1:7">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="572" hidden="1" spans="1:7">
       <c r="A572" t="s">
+        <v>850</v>
+      </c>
+      <c r="B572" t="s">
         <v>851</v>
-      </c>
-      <c r="B572" t="s">
-        <v>852</v>
       </c>
       <c r="C572" t="s">
         <v>47</v>
@@ -16992,12 +16996,12 @@
         <v>55</v>
       </c>
       <c r="G572" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="573" spans="1:7">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="573" hidden="1" spans="1:7">
       <c r="A573" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B573" t="s">
         <v>8</v>
@@ -17012,18 +17016,18 @@
         <v>44</v>
       </c>
       <c r="F573" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G573" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="574" spans="1:7">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="574" hidden="1" spans="1:7">
       <c r="A574" t="s">
+        <v>853</v>
+      </c>
+      <c r="B574" t="s">
         <v>854</v>
-      </c>
-      <c r="B574" t="s">
-        <v>855</v>
       </c>
       <c r="C574" t="s">
         <v>320</v>
@@ -17035,15 +17039,15 @@
         <v>44</v>
       </c>
       <c r="F574" t="s">
+        <v>855</v>
+      </c>
+      <c r="G574" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="575" hidden="1" spans="1:7">
+      <c r="A575" t="s">
         <v>856</v>
-      </c>
-      <c r="G574" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="575" spans="1:7">
-      <c r="A575" t="s">
-        <v>857</v>
       </c>
       <c r="B575" t="s">
         <v>66</v>
@@ -17061,12 +17065,12 @@
         <v>55</v>
       </c>
       <c r="G575" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="576" spans="1:7">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="576" hidden="1" spans="1:7">
       <c r="A576" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B576" t="s">
         <v>66</v>
@@ -17084,12 +17088,12 @@
         <v>55</v>
       </c>
       <c r="G576" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="577" spans="1:7">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="577" hidden="1" spans="1:7">
       <c r="A577" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B577" t="s">
         <v>37</v>
@@ -17107,15 +17111,15 @@
         <v>55</v>
       </c>
       <c r="G577" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="578" spans="1:7">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="578" hidden="1" spans="1:7">
       <c r="A578" t="s">
+        <v>859</v>
+      </c>
+      <c r="B578" t="s">
         <v>860</v>
-      </c>
-      <c r="B578" t="s">
-        <v>861</v>
       </c>
       <c r="C578" t="s">
         <v>345</v>
@@ -17130,15 +17134,15 @@
         <v>55</v>
       </c>
       <c r="G578" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="579" spans="1:7">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="579" hidden="1" spans="1:7">
       <c r="A579" t="s">
         <v>353</v>
       </c>
       <c r="B579" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C579" t="s">
         <v>206</v>
@@ -17153,15 +17157,15 @@
         <v>55</v>
       </c>
       <c r="G579" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="580" spans="1:7">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="580" hidden="1" spans="1:7">
       <c r="A580" t="s">
+        <v>862</v>
+      </c>
+      <c r="B580" t="s">
         <v>863</v>
-      </c>
-      <c r="B580" t="s">
-        <v>864</v>
       </c>
       <c r="C580" t="s">
         <v>119</v>
@@ -17176,15 +17180,15 @@
         <v>55</v>
       </c>
       <c r="G580" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="581" spans="1:7">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="581" hidden="1" spans="1:7">
       <c r="A581" t="s">
+        <v>864</v>
+      </c>
+      <c r="B581" t="s">
         <v>865</v>
-      </c>
-      <c r="B581" t="s">
-        <v>866</v>
       </c>
       <c r="C581" t="s">
         <v>47</v>
@@ -17199,12 +17203,12 @@
         <v>55</v>
       </c>
       <c r="G581" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="582" spans="1:7">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="582" hidden="1" spans="1:7">
       <c r="A582" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B582" t="s">
         <v>66</v>
@@ -17219,13 +17223,13 @@
         <v>11</v>
       </c>
       <c r="F582" t="s">
+        <v>867</v>
+      </c>
+      <c r="G582" t="s">
         <v>868</v>
       </c>
-      <c r="G582" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="583" spans="1:7">
+    </row>
+    <row r="583" hidden="1" spans="1:7">
       <c r="A583" t="s">
         <v>477</v>
       </c>
@@ -17242,13 +17246,13 @@
         <v>11</v>
       </c>
       <c r="F583" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="G583" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="584" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="584" hidden="1" spans="1:7">
       <c r="A584" t="s">
         <v>477</v>
       </c>
@@ -17265,13 +17269,13 @@
         <v>11</v>
       </c>
       <c r="F584" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="G584" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="585" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="585" hidden="1" spans="1:7">
       <c r="A585" t="s">
         <v>477</v>
       </c>
@@ -17288,18 +17292,18 @@
         <v>11</v>
       </c>
       <c r="F585" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="G585" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="586" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="586" hidden="1" spans="1:7">
       <c r="A586" t="s">
         <v>502</v>
       </c>
       <c r="B586" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C586" t="s">
         <v>513</v>
@@ -17311,18 +17315,18 @@
         <v>11</v>
       </c>
       <c r="F586" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G586" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="587" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="587" hidden="1" spans="1:7">
       <c r="A587" t="s">
         <v>509</v>
       </c>
       <c r="B587" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C587" t="s">
         <v>77</v>
@@ -17334,18 +17338,18 @@
         <v>11</v>
       </c>
       <c r="F587" t="s">
+        <v>867</v>
+      </c>
+      <c r="G587" t="s">
         <v>868</v>
       </c>
-      <c r="G587" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="588" spans="1:7">
+    </row>
+    <row r="588" hidden="1" spans="1:7">
       <c r="A588" t="s">
         <v>492</v>
       </c>
       <c r="B588" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C588" t="s">
         <v>122</v>
@@ -17357,18 +17361,18 @@
         <v>11</v>
       </c>
       <c r="F588" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G588" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="589" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="589" hidden="1" spans="1:7">
       <c r="A589" t="s">
+        <v>874</v>
+      </c>
+      <c r="B589" t="s">
         <v>875</v>
-      </c>
-      <c r="B589" t="s">
-        <v>876</v>
       </c>
       <c r="C589" t="s">
         <v>47</v>
@@ -17380,18 +17384,18 @@
         <v>11</v>
       </c>
       <c r="F589" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G589" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="590" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="590" hidden="1" spans="1:7">
       <c r="A590" t="s">
+        <v>874</v>
+      </c>
+      <c r="B590" t="s">
         <v>875</v>
-      </c>
-      <c r="B590" t="s">
-        <v>876</v>
       </c>
       <c r="C590" t="s">
         <v>47</v>
@@ -17403,18 +17407,18 @@
         <v>11</v>
       </c>
       <c r="F590" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G590" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="591" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="591" hidden="1" spans="1:7">
       <c r="A591" t="s">
+        <v>874</v>
+      </c>
+      <c r="B591" t="s">
         <v>875</v>
-      </c>
-      <c r="B591" t="s">
-        <v>876</v>
       </c>
       <c r="C591" t="s">
         <v>47</v>
@@ -17426,18 +17430,18 @@
         <v>11</v>
       </c>
       <c r="F591" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G591" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="592" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="592" hidden="1" spans="1:7">
       <c r="A592" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B592" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C592" t="s">
         <v>77</v>
@@ -17449,18 +17453,18 @@
         <v>11</v>
       </c>
       <c r="F592" t="s">
+        <v>867</v>
+      </c>
+      <c r="G592" t="s">
         <v>868</v>
       </c>
-      <c r="G592" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="593" spans="1:7">
+    </row>
+    <row r="593" hidden="1" spans="1:7">
       <c r="A593" t="s">
         <v>126</v>
       </c>
       <c r="B593" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C593" t="s">
         <v>77</v>
@@ -17475,15 +17479,15 @@
         <v>542</v>
       </c>
       <c r="G593" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="594" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="594" hidden="1" spans="1:7">
       <c r="A594" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B594" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C594" t="s">
         <v>77</v>
@@ -17495,18 +17499,18 @@
         <v>11</v>
       </c>
       <c r="F594" t="s">
+        <v>872</v>
+      </c>
+      <c r="G594" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="595" hidden="1" spans="1:7">
+      <c r="A595" t="s">
+        <v>879</v>
+      </c>
+      <c r="B595" t="s">
         <v>873</v>
-      </c>
-      <c r="G594" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="595" spans="1:7">
-      <c r="A595" t="s">
-        <v>880</v>
-      </c>
-      <c r="B595" t="s">
-        <v>874</v>
       </c>
       <c r="C595" t="s">
         <v>48</v>
@@ -17518,18 +17522,18 @@
         <v>11</v>
       </c>
       <c r="F595" t="s">
+        <v>867</v>
+      </c>
+      <c r="G595" t="s">
         <v>868</v>
       </c>
-      <c r="G595" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="596" spans="1:7">
+    </row>
+    <row r="596" hidden="1" spans="1:7">
       <c r="A596" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B596" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C596" t="s">
         <v>158</v>
@@ -17541,18 +17545,18 @@
         <v>11</v>
       </c>
       <c r="F596" t="s">
+        <v>867</v>
+      </c>
+      <c r="G596" t="s">
         <v>868</v>
       </c>
-      <c r="G596" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="597" spans="1:7">
+    </row>
+    <row r="597" hidden="1" spans="1:7">
       <c r="A597" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B597" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C597" t="s">
         <v>158</v>
@@ -17564,18 +17568,18 @@
         <v>11</v>
       </c>
       <c r="F597" t="s">
+        <v>867</v>
+      </c>
+      <c r="G597" t="s">
         <v>868</v>
       </c>
-      <c r="G597" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="598" spans="1:7">
+    </row>
+    <row r="598" hidden="1" spans="1:7">
       <c r="A598" t="s">
+        <v>880</v>
+      </c>
+      <c r="B598" t="s">
         <v>881</v>
-      </c>
-      <c r="B598" t="s">
-        <v>882</v>
       </c>
       <c r="C598" t="s">
         <v>254</v>
@@ -17587,18 +17591,18 @@
         <v>20</v>
       </c>
       <c r="F598" t="s">
+        <v>882</v>
+      </c>
+      <c r="G598" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="599" hidden="1" spans="1:7">
+      <c r="A599" t="s">
         <v>883</v>
       </c>
-      <c r="G598" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="599" spans="1:7">
-      <c r="A599" t="s">
+      <c r="B599" t="s">
         <v>884</v>
-      </c>
-      <c r="B599" t="s">
-        <v>885</v>
       </c>
       <c r="C599" t="s">
         <v>186</v>
@@ -17610,18 +17614,18 @@
         <v>20</v>
       </c>
       <c r="F599" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="G599" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="600" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="600" hidden="1" spans="1:7">
       <c r="A600" t="s">
+        <v>880</v>
+      </c>
+      <c r="B600" t="s">
         <v>881</v>
-      </c>
-      <c r="B600" t="s">
-        <v>882</v>
       </c>
       <c r="C600" t="s">
         <v>254</v>
@@ -17633,18 +17637,18 @@
         <v>20</v>
       </c>
       <c r="F600" t="s">
+        <v>886</v>
+      </c>
+      <c r="G600" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="601" hidden="1" spans="1:7">
+      <c r="A601" t="s">
         <v>887</v>
       </c>
-      <c r="G600" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="601" spans="1:7">
-      <c r="A601" t="s">
+      <c r="B601" t="s">
         <v>888</v>
-      </c>
-      <c r="B601" t="s">
-        <v>889</v>
       </c>
       <c r="C601" t="s">
         <v>47</v>
@@ -17656,18 +17660,18 @@
         <v>20</v>
       </c>
       <c r="F601" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="G601" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="602" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="602" hidden="1" spans="1:7">
       <c r="A602" t="s">
+        <v>883</v>
+      </c>
+      <c r="B602" t="s">
         <v>884</v>
-      </c>
-      <c r="B602" t="s">
-        <v>885</v>
       </c>
       <c r="C602" t="s">
         <v>186</v>
@@ -17679,18 +17683,18 @@
         <v>20</v>
       </c>
       <c r="F602" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="G602" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="603" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="603" hidden="1" spans="1:7">
       <c r="A603" t="s">
         <v>477</v>
       </c>
       <c r="B603" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C603" t="s">
         <v>42</v>
@@ -17702,18 +17706,18 @@
         <v>20</v>
       </c>
       <c r="F603" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G603" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="604" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="604" hidden="1" spans="1:7">
       <c r="A604" t="s">
+        <v>887</v>
+      </c>
+      <c r="B604" t="s">
         <v>888</v>
-      </c>
-      <c r="B604" t="s">
-        <v>889</v>
       </c>
       <c r="C604" t="s">
         <v>47</v>
@@ -17725,18 +17729,18 @@
         <v>20</v>
       </c>
       <c r="F604" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="G604" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="605" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="605" hidden="1" spans="1:7">
       <c r="A605" t="s">
+        <v>880</v>
+      </c>
+      <c r="B605" t="s">
         <v>881</v>
-      </c>
-      <c r="B605" t="s">
-        <v>882</v>
       </c>
       <c r="C605" t="s">
         <v>174</v>
@@ -17748,18 +17752,18 @@
         <v>20</v>
       </c>
       <c r="F605" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="G605" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="606" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="606" hidden="1" spans="1:7">
       <c r="A606" t="s">
+        <v>887</v>
+      </c>
+      <c r="B606" t="s">
         <v>888</v>
-      </c>
-      <c r="B606" t="s">
-        <v>889</v>
       </c>
       <c r="C606" t="s">
         <v>47</v>
@@ -17771,18 +17775,18 @@
         <v>20</v>
       </c>
       <c r="F606" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="G606" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="607" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="607" hidden="1" spans="1:7">
       <c r="A607" t="s">
+        <v>883</v>
+      </c>
+      <c r="B607" t="s">
         <v>884</v>
-      </c>
-      <c r="B607" t="s">
-        <v>885</v>
       </c>
       <c r="C607" t="s">
         <v>188</v>
@@ -17794,18 +17798,18 @@
         <v>20</v>
       </c>
       <c r="F607" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="G607" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="608" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="608" hidden="1" spans="1:7">
       <c r="A608" t="s">
+        <v>880</v>
+      </c>
+      <c r="B608" t="s">
         <v>881</v>
-      </c>
-      <c r="B608" t="s">
-        <v>882</v>
       </c>
       <c r="C608" t="s">
         <v>174</v>
@@ -17817,18 +17821,18 @@
         <v>20</v>
       </c>
       <c r="F608" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="G608" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="609" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="609" hidden="1" spans="1:7">
       <c r="A609" t="s">
+        <v>887</v>
+      </c>
+      <c r="B609" t="s">
         <v>888</v>
-      </c>
-      <c r="B609" t="s">
-        <v>889</v>
       </c>
       <c r="C609" t="s">
         <v>47</v>
@@ -17840,18 +17844,18 @@
         <v>20</v>
       </c>
       <c r="F609" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G609" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="610" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="610" hidden="1" spans="1:7">
       <c r="A610" t="s">
+        <v>883</v>
+      </c>
+      <c r="B610" t="s">
         <v>884</v>
-      </c>
-      <c r="B610" t="s">
-        <v>885</v>
       </c>
       <c r="C610" t="s">
         <v>188</v>
@@ -17863,13 +17867,13 @@
         <v>20</v>
       </c>
       <c r="F610" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="G610" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="611" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="611" hidden="1" spans="1:7">
       <c r="A611" t="s">
         <v>471</v>
       </c>
@@ -17889,15 +17893,15 @@
         <v>542</v>
       </c>
       <c r="G611" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="612" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="612" hidden="1" spans="1:7">
       <c r="A612" t="s">
         <v>502</v>
       </c>
       <c r="B612" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C612" t="s">
         <v>77</v>
@@ -17909,18 +17913,18 @@
         <v>44</v>
       </c>
       <c r="F612" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G612" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="613" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="613" hidden="1" spans="1:7">
       <c r="A613" t="s">
         <v>510</v>
       </c>
       <c r="B613" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C613" t="s">
         <v>516</v>
@@ -17932,18 +17936,18 @@
         <v>44</v>
       </c>
       <c r="F613" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G613" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="614" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="614" hidden="1" spans="1:7">
       <c r="A614" t="s">
+        <v>887</v>
+      </c>
+      <c r="B614" t="s">
         <v>888</v>
-      </c>
-      <c r="B614" t="s">
-        <v>889</v>
       </c>
       <c r="C614" t="s">
         <v>488</v>
@@ -17955,18 +17959,18 @@
         <v>44</v>
       </c>
       <c r="F614" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="G614" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="615" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="615" hidden="1" spans="1:7">
       <c r="A615" t="s">
+        <v>880</v>
+      </c>
+      <c r="B615" t="s">
         <v>881</v>
-      </c>
-      <c r="B615" t="s">
-        <v>882</v>
       </c>
       <c r="C615" t="s">
         <v>47</v>
@@ -17978,18 +17982,18 @@
         <v>44</v>
       </c>
       <c r="F615" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G615" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="616" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="616" hidden="1" spans="1:7">
       <c r="A616" t="s">
         <v>512</v>
       </c>
       <c r="B616" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C616" t="s">
         <v>516</v>
@@ -18001,18 +18005,18 @@
         <v>44</v>
       </c>
       <c r="F616" t="s">
+        <v>867</v>
+      </c>
+      <c r="G616" t="s">
         <v>868</v>
       </c>
-      <c r="G616" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="617" spans="1:7">
+    </row>
+    <row r="617" hidden="1" spans="1:7">
       <c r="A617" t="s">
+        <v>887</v>
+      </c>
+      <c r="B617" t="s">
         <v>888</v>
-      </c>
-      <c r="B617" t="s">
-        <v>889</v>
       </c>
       <c r="C617" t="s">
         <v>488</v>
@@ -18024,18 +18028,18 @@
         <v>44</v>
       </c>
       <c r="F617" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="G617" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="618" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="618" hidden="1" spans="1:7">
       <c r="A618" t="s">
+        <v>880</v>
+      </c>
+      <c r="B618" t="s">
         <v>881</v>
-      </c>
-      <c r="B618" t="s">
-        <v>882</v>
       </c>
       <c r="C618" t="s">
         <v>47</v>
@@ -18047,13 +18051,13 @@
         <v>44</v>
       </c>
       <c r="F618" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G618" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="619" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="619" hidden="1" spans="1:7">
       <c r="A619" t="s">
         <v>130</v>
       </c>
@@ -18073,15 +18077,15 @@
         <v>542</v>
       </c>
       <c r="G619" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="620" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="620" hidden="1" spans="1:7">
       <c r="A620" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B620" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C620" t="s">
         <v>47</v>
@@ -18093,18 +18097,18 @@
         <v>44</v>
       </c>
       <c r="F620" t="s">
+        <v>867</v>
+      </c>
+      <c r="G620" t="s">
         <v>868</v>
       </c>
-      <c r="G620" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="621" spans="1:7">
+    </row>
+    <row r="621" hidden="1" spans="1:7">
       <c r="A621" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B621" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C621" t="s">
         <v>158</v>
@@ -18116,18 +18120,18 @@
         <v>44</v>
       </c>
       <c r="F621" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G621" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="622" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="622" hidden="1" spans="1:7">
       <c r="A622" t="s">
+        <v>902</v>
+      </c>
+      <c r="B622" t="s">
         <v>903</v>
-      </c>
-      <c r="B622" t="s">
-        <v>904</v>
       </c>
       <c r="C622" t="s">
         <v>506</v>
@@ -18142,15 +18146,15 @@
         <v>542</v>
       </c>
       <c r="G622" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="623" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="623" hidden="1" spans="1:7">
       <c r="A623" t="s">
         <v>509</v>
       </c>
       <c r="B623" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C623" t="s">
         <v>77</v>
@@ -18162,18 +18166,18 @@
         <v>61</v>
       </c>
       <c r="F623" t="s">
+        <v>867</v>
+      </c>
+      <c r="G623" t="s">
         <v>868</v>
       </c>
-      <c r="G623" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="624" spans="1:7">
+    </row>
+    <row r="624" hidden="1" spans="1:7">
       <c r="A624" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B624" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C624" t="s">
         <v>188</v>
@@ -18185,18 +18189,18 @@
         <v>61</v>
       </c>
       <c r="F624" t="s">
+        <v>867</v>
+      </c>
+      <c r="G624" t="s">
         <v>868</v>
       </c>
-      <c r="G624" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="625" spans="1:7">
+    </row>
+    <row r="625" hidden="1" spans="1:7">
       <c r="A625" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B625" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C625" t="s">
         <v>188</v>
@@ -18208,18 +18212,18 @@
         <v>61</v>
       </c>
       <c r="F625" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G625" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="626" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="626" hidden="1" spans="1:7">
       <c r="A626" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B626" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C626" t="s">
         <v>98</v>
@@ -18231,18 +18235,18 @@
         <v>61</v>
       </c>
       <c r="F626" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="G626" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="627" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="627" hidden="1" spans="1:7">
       <c r="A627" t="s">
         <v>500</v>
       </c>
       <c r="B627" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C627" t="s">
         <v>47</v>
@@ -18254,18 +18258,18 @@
         <v>61</v>
       </c>
       <c r="F627" t="s">
+        <v>867</v>
+      </c>
+      <c r="G627" t="s">
         <v>868</v>
       </c>
-      <c r="G627" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="628" spans="1:7">
+    </row>
+    <row r="628" hidden="1" spans="1:7">
       <c r="A628" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B628" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C628" t="s">
         <v>475</v>
@@ -18277,18 +18281,18 @@
         <v>61</v>
       </c>
       <c r="F628" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G628" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="629" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="629" hidden="1" spans="1:7">
       <c r="A629" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B629" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C629" t="s">
         <v>98</v>
@@ -18300,18 +18304,18 @@
         <v>61</v>
       </c>
       <c r="F629" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="G629" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="630" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="630" hidden="1" spans="1:7">
       <c r="A630" t="s">
         <v>490</v>
       </c>
       <c r="B630" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C630" t="s">
         <v>74</v>
@@ -18326,15 +18330,15 @@
         <v>542</v>
       </c>
       <c r="G630" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="631" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="631" hidden="1" spans="1:7">
       <c r="A631" t="s">
         <v>84</v>
       </c>
       <c r="B631" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C631" t="s">
         <v>48</v>
@@ -18349,12 +18353,12 @@
         <v>542</v>
       </c>
       <c r="G631" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="632" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="632" hidden="1" spans="1:7">
       <c r="A632" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B632" t="s">
         <v>37</v>
@@ -18372,15 +18376,15 @@
         <v>542</v>
       </c>
       <c r="G632" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="633" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="633" hidden="1" spans="1:7">
       <c r="A633" t="s">
         <v>477</v>
       </c>
       <c r="B633" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C633" t="s">
         <v>42</v>
@@ -18392,18 +18396,18 @@
         <v>71</v>
       </c>
       <c r="F633" t="s">
+        <v>913</v>
+      </c>
+      <c r="G633" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="634" hidden="1" spans="1:7">
+      <c r="A634" t="s">
         <v>914</v>
       </c>
-      <c r="G633" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="634" spans="1:7">
-      <c r="A634" t="s">
-        <v>915</v>
-      </c>
       <c r="B634" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C634" t="s">
         <v>47</v>
@@ -18415,18 +18419,18 @@
         <v>71</v>
       </c>
       <c r="F634" t="s">
+        <v>867</v>
+      </c>
+      <c r="G634" t="s">
         <v>868</v>
       </c>
-      <c r="G634" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="635" spans="1:7">
+    </row>
+    <row r="635" hidden="1" spans="1:7">
       <c r="A635" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B635" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C635" t="s">
         <v>513</v>
@@ -18438,13 +18442,13 @@
         <v>71</v>
       </c>
       <c r="F635" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G635" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="636" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="636" hidden="1" spans="1:7">
       <c r="A636" t="s">
         <v>466</v>
       </c>
@@ -18461,18 +18465,18 @@
         <v>71</v>
       </c>
       <c r="F636" t="s">
+        <v>867</v>
+      </c>
+      <c r="G636" t="s">
         <v>868</v>
       </c>
-      <c r="G636" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="637" spans="1:7">
+    </row>
+    <row r="637" hidden="1" spans="1:7">
       <c r="A637" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B637" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C637" t="s">
         <v>47</v>
@@ -18484,13 +18488,13 @@
         <v>71</v>
       </c>
       <c r="F637" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G637" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="638" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="638" hidden="1" spans="1:7">
       <c r="A638" t="s">
         <v>504</v>
       </c>
@@ -18507,18 +18511,18 @@
         <v>71</v>
       </c>
       <c r="F638" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G638" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="639" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="639" hidden="1" spans="1:7">
       <c r="A639" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B639" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C639" t="s">
         <v>77</v>
@@ -18530,18 +18534,18 @@
         <v>71</v>
       </c>
       <c r="F639" t="s">
+        <v>867</v>
+      </c>
+      <c r="G639" t="s">
         <v>868</v>
       </c>
-      <c r="G639" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="640" spans="1:7">
+    </row>
+    <row r="640" hidden="1" spans="1:7">
       <c r="A640" t="s">
+        <v>916</v>
+      </c>
+      <c r="B640" t="s">
         <v>917</v>
-      </c>
-      <c r="B640" t="s">
-        <v>918</v>
       </c>
       <c r="C640" t="s">
         <v>516</v>
@@ -18556,12 +18560,12 @@
         <v>542</v>
       </c>
       <c r="G640" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="641" spans="1:7">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="641" hidden="1" spans="1:7">
       <c r="A641" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B641" t="s">
         <v>66</v>
@@ -18579,10 +18583,10 @@
         <v>327</v>
       </c>
       <c r="G641" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="642" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="642" hidden="1" spans="1:7">
       <c r="A642" t="s">
         <v>559</v>
       </c>
@@ -18602,12 +18606,12 @@
         <v>343</v>
       </c>
       <c r="G642" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="643" hidden="1" spans="1:7">
+      <c r="A643" t="s">
         <v>920</v>
-      </c>
-    </row>
-    <row r="643" spans="1:7">
-      <c r="A643" t="s">
-        <v>921</v>
       </c>
       <c r="B643" t="s">
         <v>37</v>
@@ -18625,10 +18629,10 @@
         <v>55</v>
       </c>
       <c r="G643" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="644" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="644" hidden="1" spans="1:7">
       <c r="A644" t="s">
         <v>550</v>
       </c>
@@ -18648,10 +18652,10 @@
         <v>55</v>
       </c>
       <c r="G644" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="645" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="645" hidden="1" spans="1:7">
       <c r="A645" t="s">
         <v>540</v>
       </c>
@@ -18671,12 +18675,12 @@
         <v>343</v>
       </c>
       <c r="G645" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="646" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="646" hidden="1" spans="1:7">
       <c r="A646" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B646" t="s">
         <v>66</v>
@@ -18694,12 +18698,12 @@
         <v>468</v>
       </c>
       <c r="G646" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="647" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="647" hidden="1" spans="1:7">
       <c r="A647" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B647" t="s">
         <v>66</v>
@@ -18717,15 +18721,15 @@
         <v>343</v>
       </c>
       <c r="G647" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="648" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="648" hidden="1" spans="1:7">
       <c r="A648" t="s">
+        <v>923</v>
+      </c>
+      <c r="B648" t="s">
         <v>924</v>
-      </c>
-      <c r="B648" t="s">
-        <v>925</v>
       </c>
       <c r="C648" t="s">
         <v>545</v>
@@ -18740,12 +18744,12 @@
         <v>39</v>
       </c>
       <c r="G648" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="649" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="649" hidden="1" spans="1:7">
       <c r="A649" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B649" t="s">
         <v>66</v>
@@ -18763,10 +18767,10 @@
         <v>468</v>
       </c>
       <c r="G649" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="650" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="650" hidden="1" spans="1:7">
       <c r="A650" t="s">
         <v>546</v>
       </c>
@@ -18786,10 +18790,10 @@
         <v>343</v>
       </c>
       <c r="G650" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="651" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="651" hidden="1" spans="1:7">
       <c r="A651" t="s">
         <v>548</v>
       </c>
@@ -18809,12 +18813,12 @@
         <v>581</v>
       </c>
       <c r="G651" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="652" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="652" hidden="1" spans="1:7">
       <c r="A652" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B652" t="s">
         <v>37</v>
@@ -18832,10 +18836,10 @@
         <v>343</v>
       </c>
       <c r="G652" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="653" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="653" hidden="1" spans="1:7">
       <c r="A653" t="s">
         <v>558</v>
       </c>
@@ -18855,12 +18859,12 @@
         <v>468</v>
       </c>
       <c r="G653" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="654" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="654" hidden="1" spans="1:7">
       <c r="A654" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B654" t="s">
         <v>37</v>
@@ -18878,12 +18882,12 @@
         <v>343</v>
       </c>
       <c r="G654" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="655" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="655" hidden="1" spans="1:7">
       <c r="A655" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B655" t="s">
         <v>66</v>
@@ -18901,12 +18905,12 @@
         <v>343</v>
       </c>
       <c r="G655" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="656" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="656" hidden="1" spans="1:7">
       <c r="A656" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B656" t="s">
         <v>66</v>
@@ -18924,12 +18928,12 @@
         <v>45</v>
       </c>
       <c r="G656" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="657" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="657" hidden="1" spans="1:7">
       <c r="A657" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B657" t="s">
         <v>8</v>
@@ -18944,15 +18948,15 @@
         <v>61</v>
       </c>
       <c r="F657" t="s">
+        <v>931</v>
+      </c>
+      <c r="G657" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="658" hidden="1" spans="1:7">
+      <c r="A658" t="s">
         <v>932</v>
-      </c>
-      <c r="G657" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="658" spans="1:7">
-      <c r="A658" t="s">
-        <v>933</v>
       </c>
       <c r="B658" t="s">
         <v>8</v>
@@ -18967,15 +18971,15 @@
         <v>61</v>
       </c>
       <c r="F658" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="G658" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="659" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="659" hidden="1" spans="1:7">
       <c r="A659" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B659" t="s">
         <v>37</v>
@@ -18993,12 +18997,12 @@
         <v>343</v>
       </c>
       <c r="G659" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="660" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="660" hidden="1" spans="1:7">
       <c r="A660" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B660" t="s">
         <v>37</v>
@@ -19016,12 +19020,12 @@
         <v>343</v>
       </c>
       <c r="G660" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="661" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="661" hidden="1" spans="1:7">
       <c r="A661" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B661" t="s">
         <v>8</v>
@@ -19036,15 +19040,15 @@
         <v>71</v>
       </c>
       <c r="F661" t="s">
+        <v>936</v>
+      </c>
+      <c r="G661" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="662" hidden="1" spans="1:7">
+      <c r="A662" t="s">
         <v>937</v>
-      </c>
-      <c r="G661" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="662" spans="1:7">
-      <c r="A662" t="s">
-        <v>938</v>
       </c>
       <c r="B662" t="s">
         <v>66</v>
@@ -19062,12 +19066,12 @@
         <v>468</v>
       </c>
       <c r="G662" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="663" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="663" hidden="1" spans="1:7">
       <c r="A663" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B663" t="s">
         <v>8</v>
@@ -19082,15 +19086,15 @@
         <v>71</v>
       </c>
       <c r="F663" t="s">
+        <v>939</v>
+      </c>
+      <c r="G663" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="664" hidden="1" spans="1:7">
+      <c r="A664" t="s">
         <v>940</v>
-      </c>
-      <c r="G663" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="664" spans="1:7">
-      <c r="A664" t="s">
-        <v>941</v>
       </c>
       <c r="B664" t="s">
         <v>8</v>
@@ -19108,12 +19112,12 @@
         <v>96</v>
       </c>
       <c r="G664" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="665" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="665" hidden="1" spans="1:7">
       <c r="A665" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B665" t="s">
         <v>8</v>
@@ -19128,15 +19132,15 @@
         <v>71</v>
       </c>
       <c r="F665" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="G665" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="666" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="666" hidden="1" spans="1:7">
       <c r="A666" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B666" t="s">
         <v>8</v>
@@ -19154,12 +19158,12 @@
         <v>96</v>
       </c>
       <c r="G666" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="667" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="667" hidden="1" spans="1:7">
       <c r="A667" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B667" t="s">
         <v>37</v>
@@ -19177,12 +19181,12 @@
         <v>343</v>
       </c>
       <c r="G667" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="668" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="668" hidden="1" spans="1:7">
       <c r="A668" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B668" t="s">
         <v>8</v>
@@ -19197,15 +19201,15 @@
         <v>71</v>
       </c>
       <c r="F668" t="s">
+        <v>944</v>
+      </c>
+      <c r="G668" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="669" hidden="1" spans="1:7">
+      <c r="A669" t="s">
         <v>945</v>
-      </c>
-      <c r="G668" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="669" spans="1:7">
-      <c r="A669" t="s">
-        <v>946</v>
       </c>
       <c r="B669" t="s">
         <v>66</v>
@@ -19223,10 +19227,18 @@
         <v>468</v>
       </c>
       <c r="G669" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G669" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="SALAH HANAFI"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4641" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4641" uniqueCount="916">
   <si>
     <t>Enseignements</t>
   </si>
@@ -1308,6 +1308,9 @@
   </si>
   <si>
     <t>TD-Élément de mécanique-G6</t>
+  </si>
+  <si>
+    <t>Amphi 02</t>
   </si>
   <si>
     <t>TD-Structure de la matière-G5</t>
@@ -3395,9 +3398,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3746,11 +3748,6 @@
   <sheetPr/>
   <dimension ref="A1:G663"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
-  <cols>
-    <col min="1" max="1" width="57" customWidth="1"/>
-    <col min="3" max="3" width="32.2857142857143" customWidth="1"/>
-    <col min="6" max="6" width="43.5714285714286" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
@@ -4150,7 +4147,7 @@
       <c r="B18" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>46</v>
       </c>
       <c r="D18" t="s">
@@ -4311,7 +4308,7 @@
       <c r="B25" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>46</v>
       </c>
       <c r="D25" t="s">
@@ -4334,7 +4331,7 @@
       <c r="B26" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>46</v>
       </c>
       <c r="D26" t="s">
@@ -4357,7 +4354,7 @@
       <c r="B27" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>46</v>
       </c>
       <c r="D27" t="s">
@@ -4380,7 +4377,7 @@
       <c r="B28" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>46</v>
       </c>
       <c r="D28" t="s">
@@ -4403,7 +4400,7 @@
       <c r="B29" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
         <v>46</v>
       </c>
       <c r="D29" t="s">
@@ -4426,7 +4423,7 @@
       <c r="B30" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s">
         <v>46</v>
       </c>
       <c r="D30" t="s">
@@ -4472,7 +4469,7 @@
       <c r="B32" t="s">
         <v>8</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s">
         <v>46</v>
       </c>
       <c r="D32" t="s">
@@ -4495,7 +4492,7 @@
       <c r="B33" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s">
         <v>46</v>
       </c>
       <c r="D33" t="s">
@@ -4518,7 +4515,7 @@
       <c r="B34" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" t="s">
         <v>46</v>
       </c>
       <c r="D34" t="s">
@@ -4541,7 +4538,7 @@
       <c r="B35" t="s">
         <v>23</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s">
         <v>46</v>
       </c>
       <c r="D35" t="s">
@@ -4564,7 +4561,7 @@
       <c r="B36" t="s">
         <v>23</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s">
         <v>46</v>
       </c>
       <c r="D36" t="s">
@@ -4587,7 +4584,7 @@
       <c r="B37" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" t="s">
         <v>46</v>
       </c>
       <c r="D37" t="s">
@@ -4863,7 +4860,7 @@
       <c r="B49" t="s">
         <v>8</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" t="s">
         <v>46</v>
       </c>
       <c r="D49" t="s">
@@ -4909,7 +4906,7 @@
       <c r="B51" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" t="s">
         <v>46</v>
       </c>
       <c r="D51" t="s">
@@ -5231,7 +5228,7 @@
       <c r="B65" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" t="s">
         <v>46</v>
       </c>
       <c r="D65" t="s">
@@ -5277,7 +5274,7 @@
       <c r="B67" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" t="s">
         <v>46</v>
       </c>
       <c r="D67" t="s">
@@ -5346,7 +5343,7 @@
       <c r="B70" t="s">
         <v>64</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" t="s">
         <v>46</v>
       </c>
       <c r="D70" t="s">
@@ -5369,7 +5366,7 @@
       <c r="B71" t="s">
         <v>64</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" t="s">
         <v>46</v>
       </c>
       <c r="D71" t="s">
@@ -5553,7 +5550,7 @@
       <c r="B79" t="s">
         <v>64</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" t="s">
         <v>46</v>
       </c>
       <c r="D79" t="s">
@@ -5576,7 +5573,7 @@
       <c r="B80" t="s">
         <v>64</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" t="s">
         <v>46</v>
       </c>
       <c r="D80" t="s">
@@ -5599,7 +5596,7 @@
       <c r="B81" t="s">
         <v>64</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" t="s">
         <v>46</v>
       </c>
       <c r="D81" t="s">
@@ -5622,7 +5619,7 @@
       <c r="B82" t="s">
         <v>64</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" t="s">
         <v>46</v>
       </c>
       <c r="D82" t="s">
@@ -5829,7 +5826,7 @@
       <c r="B91" t="s">
         <v>8</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" t="s">
         <v>46</v>
       </c>
       <c r="D91" t="s">
@@ -5967,7 +5964,7 @@
       <c r="B97" t="s">
         <v>8</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C97" t="s">
         <v>46</v>
       </c>
       <c r="D97" t="s">
@@ -6358,7 +6355,7 @@
       <c r="B114" t="s">
         <v>37</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C114" t="s">
         <v>46</v>
       </c>
       <c r="D114" t="s">
@@ -6611,7 +6608,7 @@
       <c r="B125" t="s">
         <v>8</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C125" t="s">
         <v>46</v>
       </c>
       <c r="D125" t="s">
@@ -6657,7 +6654,7 @@
       <c r="B127" t="s">
         <v>8</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C127" t="s">
         <v>46</v>
       </c>
       <c r="D127" t="s">
@@ -6749,7 +6746,7 @@
       <c r="B131" t="s">
         <v>8</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="C131" t="s">
         <v>46</v>
       </c>
       <c r="D131" t="s">
@@ -6772,7 +6769,7 @@
       <c r="B132" t="s">
         <v>8</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="C132" t="s">
         <v>46</v>
       </c>
       <c r="D132" t="s">
@@ -6956,7 +6953,7 @@
       <c r="B140" t="s">
         <v>64</v>
       </c>
-      <c r="C140" s="1" t="s">
+      <c r="C140" t="s">
         <v>46</v>
       </c>
       <c r="D140" t="s">
@@ -7002,7 +6999,7 @@
       <c r="B142" t="s">
         <v>8</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="C142" t="s">
         <v>46</v>
       </c>
       <c r="D142" t="s">
@@ -7071,7 +7068,7 @@
       <c r="B145" t="s">
         <v>8</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="C145" t="s">
         <v>46</v>
       </c>
       <c r="D145" t="s">
@@ -7186,7 +7183,7 @@
       <c r="B150" t="s">
         <v>64</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="C150" t="s">
         <v>46</v>
       </c>
       <c r="D150" t="s">
@@ -7209,7 +7206,7 @@
       <c r="B151" t="s">
         <v>64</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="C151" t="s">
         <v>46</v>
       </c>
       <c r="D151" t="s">
@@ -7278,7 +7275,7 @@
       <c r="B154" t="s">
         <v>8</v>
       </c>
-      <c r="C154" s="1" t="s">
+      <c r="C154" t="s">
         <v>46</v>
       </c>
       <c r="D154" t="s">
@@ -7347,7 +7344,7 @@
       <c r="B157" t="s">
         <v>8</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="C157" t="s">
         <v>46</v>
       </c>
       <c r="D157" t="s">
@@ -7370,7 +7367,7 @@
       <c r="B158" t="s">
         <v>8</v>
       </c>
-      <c r="C158" s="1" t="s">
+      <c r="C158" t="s">
         <v>46</v>
       </c>
       <c r="D158" t="s">
@@ -7416,7 +7413,7 @@
       <c r="B160" t="s">
         <v>8</v>
       </c>
-      <c r="C160" s="1" t="s">
+      <c r="C160" t="s">
         <v>46</v>
       </c>
       <c r="D160" t="s">
@@ -7669,7 +7666,7 @@
       <c r="B171" t="s">
         <v>8</v>
       </c>
-      <c r="C171" s="1" t="s">
+      <c r="C171" t="s">
         <v>46</v>
       </c>
       <c r="D171" t="s">
@@ -7876,7 +7873,7 @@
       <c r="B180" t="s">
         <v>304</v>
       </c>
-      <c r="C180" s="1" t="s">
+      <c r="C180" t="s">
         <v>46</v>
       </c>
       <c r="D180" t="s">
@@ -7899,7 +7896,7 @@
       <c r="B181" t="s">
         <v>8</v>
       </c>
-      <c r="C181" s="1" t="s">
+      <c r="C181" t="s">
         <v>46</v>
       </c>
       <c r="D181" t="s">
@@ -7922,7 +7919,7 @@
       <c r="B182" t="s">
         <v>8</v>
       </c>
-      <c r="C182" s="1" t="s">
+      <c r="C182" t="s">
         <v>46</v>
       </c>
       <c r="D182" t="s">
@@ -8060,7 +8057,7 @@
       <c r="B188" t="s">
         <v>64</v>
       </c>
-      <c r="C188" s="1" t="s">
+      <c r="C188" t="s">
         <v>46</v>
       </c>
       <c r="D188" t="s">
@@ -8359,7 +8356,7 @@
       <c r="B201" t="s">
         <v>8</v>
       </c>
-      <c r="C201" s="1" t="s">
+      <c r="C201" t="s">
         <v>46</v>
       </c>
       <c r="D201" t="s">
@@ -8405,7 +8402,7 @@
       <c r="B203" t="s">
         <v>37</v>
       </c>
-      <c r="C203" s="1" t="s">
+      <c r="C203" t="s">
         <v>46</v>
       </c>
       <c r="D203" t="s">
@@ -8635,7 +8632,7 @@
       <c r="B213" t="s">
         <v>365</v>
       </c>
-      <c r="C213" s="1" t="s">
+      <c r="C213" t="s">
         <v>46</v>
       </c>
       <c r="D213" t="s">
@@ -8658,7 +8655,7 @@
       <c r="B214" t="s">
         <v>365</v>
       </c>
-      <c r="C214" s="1" t="s">
+      <c r="C214" t="s">
         <v>46</v>
       </c>
       <c r="D214" t="s">
@@ -8852,7 +8849,7 @@
         <v>11</v>
       </c>
       <c r="F222" t="s">
-        <v>147</v>
+        <v>358</v>
       </c>
       <c r="G222" t="s">
         <v>350</v>
@@ -9072,7 +9069,7 @@
       <c r="B232" t="s">
         <v>361</v>
       </c>
-      <c r="C232" s="1" t="s">
+      <c r="C232" t="s">
         <v>46</v>
       </c>
       <c r="D232" t="s">
@@ -9187,7 +9184,7 @@
       <c r="B237" t="s">
         <v>361</v>
       </c>
-      <c r="C237" s="1" t="s">
+      <c r="C237" t="s">
         <v>46</v>
       </c>
       <c r="D237" t="s">
@@ -9312,7 +9309,7 @@
         <v>20</v>
       </c>
       <c r="F242" t="s">
-        <v>147</v>
+        <v>358</v>
       </c>
       <c r="G242" t="s">
         <v>350</v>
@@ -9348,7 +9345,7 @@
       <c r="B244" t="s">
         <v>395</v>
       </c>
-      <c r="C244" s="1" t="s">
+      <c r="C244" t="s">
         <v>46</v>
       </c>
       <c r="D244" t="s">
@@ -9417,7 +9414,7 @@
       <c r="B247" t="s">
         <v>64</v>
       </c>
-      <c r="C247" s="1" t="s">
+      <c r="C247" t="s">
         <v>46</v>
       </c>
       <c r="D247" t="s">
@@ -9555,7 +9552,7 @@
       <c r="B253" t="s">
         <v>64</v>
       </c>
-      <c r="C253" s="1" t="s">
+      <c r="C253" t="s">
         <v>46</v>
       </c>
       <c r="D253" t="s">
@@ -9670,7 +9667,7 @@
       <c r="B258" t="s">
         <v>64</v>
       </c>
-      <c r="C258" s="1" t="s">
+      <c r="C258" t="s">
         <v>46</v>
       </c>
       <c r="D258" t="s">
@@ -9693,7 +9690,7 @@
       <c r="B259" t="s">
         <v>8</v>
       </c>
-      <c r="C259" s="1" t="s">
+      <c r="C259" t="s">
         <v>46</v>
       </c>
       <c r="D259" t="s">
@@ -9739,7 +9736,7 @@
       <c r="B261" t="s">
         <v>64</v>
       </c>
-      <c r="C261" s="1" t="s">
+      <c r="C261" t="s">
         <v>46</v>
       </c>
       <c r="D261" t="s">
@@ -9831,7 +9828,7 @@
       <c r="B265" t="s">
         <v>395</v>
       </c>
-      <c r="C265" s="1" t="s">
+      <c r="C265" t="s">
         <v>46</v>
       </c>
       <c r="D265" t="s">
@@ -9910,7 +9907,7 @@
         <v>59</v>
       </c>
       <c r="F268" t="s">
-        <v>147</v>
+        <v>426</v>
       </c>
       <c r="G268" t="s">
         <v>350</v>
@@ -9964,12 +9961,12 @@
     </row>
     <row r="271" spans="1:7">
       <c r="A271" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B271" t="s">
         <v>64</v>
       </c>
-      <c r="C271" s="1" t="s">
+      <c r="C271" t="s">
         <v>46</v>
       </c>
       <c r="D271" t="s">
@@ -9987,7 +9984,7 @@
     </row>
     <row r="272" spans="1:7">
       <c r="A272" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B272" t="s">
         <v>64</v>
@@ -10010,12 +10007,12 @@
     </row>
     <row r="273" spans="1:7">
       <c r="A273" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B273" t="s">
         <v>361</v>
       </c>
-      <c r="C273" s="1" t="s">
+      <c r="C273" t="s">
         <v>46</v>
       </c>
       <c r="D273" t="s">
@@ -10033,7 +10030,7 @@
     </row>
     <row r="274" spans="1:7">
       <c r="A274" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B274" t="s">
         <v>365</v>
@@ -10056,7 +10053,7 @@
     </row>
     <row r="275" spans="1:7">
       <c r="A275" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B275" t="s">
         <v>348</v>
@@ -10079,7 +10076,7 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B276" t="s">
         <v>352</v>
@@ -10102,7 +10099,7 @@
     </row>
     <row r="277" spans="1:7">
       <c r="A277" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B277" t="s">
         <v>356</v>
@@ -10125,7 +10122,7 @@
     </row>
     <row r="278" spans="1:7">
       <c r="A278" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B278" t="s">
         <v>348</v>
@@ -10148,7 +10145,7 @@
     </row>
     <row r="279" spans="1:7">
       <c r="A279" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B279" t="s">
         <v>352</v>
@@ -10171,7 +10168,7 @@
     </row>
     <row r="280" spans="1:7">
       <c r="A280" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B280" t="s">
         <v>356</v>
@@ -10194,7 +10191,7 @@
     </row>
     <row r="281" spans="1:7">
       <c r="A281" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B281" t="s">
         <v>37</v>
@@ -10217,7 +10214,7 @@
     </row>
     <row r="282" spans="1:7">
       <c r="A282" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B282" t="s">
         <v>37</v>
@@ -10240,10 +10237,10 @@
     </row>
     <row r="283" spans="1:7">
       <c r="A283" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B283" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C283" t="s">
         <v>419</v>
@@ -10263,7 +10260,7 @@
     </row>
     <row r="284" spans="1:7">
       <c r="A284" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B284" t="s">
         <v>377</v>
@@ -10286,12 +10283,12 @@
     </row>
     <row r="285" spans="1:7">
       <c r="A285" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B285" t="s">
         <v>356</v>
       </c>
-      <c r="C285" s="1" t="s">
+      <c r="C285" t="s">
         <v>46</v>
       </c>
       <c r="D285" t="s">
@@ -10309,12 +10306,12 @@
     </row>
     <row r="286" spans="1:7">
       <c r="A286" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B286" t="s">
         <v>403</v>
       </c>
-      <c r="C286" s="1" t="s">
+      <c r="C286" t="s">
         <v>46</v>
       </c>
       <c r="D286" t="s">
@@ -10332,7 +10329,7 @@
     </row>
     <row r="287" spans="1:7">
       <c r="A287" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B287" t="s">
         <v>361</v>
@@ -10355,7 +10352,7 @@
     </row>
     <row r="288" spans="1:7">
       <c r="A288" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B288" t="s">
         <v>365</v>
@@ -10378,7 +10375,7 @@
     </row>
     <row r="289" spans="1:7">
       <c r="A289" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B289" t="s">
         <v>403</v>
@@ -10401,7 +10398,7 @@
     </row>
     <row r="290" spans="1:7">
       <c r="A290" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B290" t="s">
         <v>64</v>
@@ -10424,10 +10421,10 @@
     </row>
     <row r="291" spans="1:7">
       <c r="A291" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B291" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C291" t="s">
         <v>56</v>
@@ -10447,12 +10444,12 @@
     </row>
     <row r="292" spans="1:7">
       <c r="A292" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B292" t="s">
         <v>8</v>
       </c>
-      <c r="C292" s="1" t="s">
+      <c r="C292" t="s">
         <v>46</v>
       </c>
       <c r="D292" t="s">
@@ -10470,12 +10467,12 @@
     </row>
     <row r="293" spans="1:7">
       <c r="A293" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B293" t="s">
         <v>365</v>
       </c>
-      <c r="C293" s="1" t="s">
+      <c r="C293" t="s">
         <v>46</v>
       </c>
       <c r="D293" t="s">
@@ -10493,12 +10490,12 @@
     </row>
     <row r="294" spans="1:7">
       <c r="A294" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B294" t="s">
         <v>365</v>
       </c>
-      <c r="C294" s="1" t="s">
+      <c r="C294" t="s">
         <v>46</v>
       </c>
       <c r="D294" t="s">
@@ -10516,7 +10513,7 @@
     </row>
     <row r="295" spans="1:7">
       <c r="A295" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B295" t="s">
         <v>365</v>
@@ -10544,7 +10541,7 @@
       <c r="B296" t="s">
         <v>348</v>
       </c>
-      <c r="C296" s="1" t="s">
+      <c r="C296" t="s">
         <v>46</v>
       </c>
       <c r="D296" t="s">
@@ -10590,7 +10587,7 @@
       <c r="B298" t="s">
         <v>356</v>
       </c>
-      <c r="C298" s="1" t="s">
+      <c r="C298" t="s">
         <v>46</v>
       </c>
       <c r="D298" t="s">
@@ -10608,13 +10605,13 @@
     </row>
     <row r="299" spans="1:7">
       <c r="A299" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B299" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C299" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D299" t="s">
         <v>25</v>
@@ -10626,15 +10623,15 @@
         <v>332</v>
       </c>
       <c r="G299" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="300" spans="1:7">
       <c r="A300" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B300" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C300" t="s">
         <v>107</v>
@@ -10649,18 +10646,18 @@
         <v>244</v>
       </c>
       <c r="G300" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="301" spans="1:7">
       <c r="A301" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B301" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C301" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D301" t="s">
         <v>32</v>
@@ -10672,7 +10669,7 @@
         <v>332</v>
       </c>
       <c r="G301" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="302" spans="1:7">
@@ -10680,7 +10677,7 @@
         <v>81</v>
       </c>
       <c r="B302" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C302" t="s">
         <v>370</v>
@@ -10695,18 +10692,18 @@
         <v>146</v>
       </c>
       <c r="G302" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="303" spans="1:7">
       <c r="A303" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B303" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C303" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D303" t="s">
         <v>57</v>
@@ -10718,21 +10715,21 @@
         <v>146</v>
       </c>
       <c r="G303" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="304" spans="1:7">
       <c r="A304" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B304" t="s">
         <v>37</v>
       </c>
       <c r="C304" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D304" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E304" t="s">
         <v>20</v>
@@ -10741,12 +10738,12 @@
         <v>358</v>
       </c>
       <c r="G304" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="305" spans="1:7">
       <c r="A305" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B305" t="s">
         <v>8</v>
@@ -10761,20 +10758,20 @@
         <v>20</v>
       </c>
       <c r="F305" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G305" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="306" spans="1:7">
       <c r="A306" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B306" t="s">
-        <v>464</v>
-      </c>
-      <c r="C306" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C306" t="s">
         <v>46</v>
       </c>
       <c r="D306" t="s">
@@ -10784,15 +10781,15 @@
         <v>20</v>
       </c>
       <c r="F306" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G306" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="307" spans="1:7">
       <c r="A307" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B307" t="s">
         <v>8</v>
@@ -10807,20 +10804,20 @@
         <v>20</v>
       </c>
       <c r="F307" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G307" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="308" spans="1:7">
       <c r="A308" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B308" t="s">
-        <v>464</v>
-      </c>
-      <c r="C308" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C308" t="s">
         <v>46</v>
       </c>
       <c r="D308" t="s">
@@ -10830,21 +10827,21 @@
         <v>20</v>
       </c>
       <c r="F308" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G308" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="309" spans="1:7">
       <c r="A309" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B309" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C309" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D309" t="s">
         <v>43</v>
@@ -10853,21 +10850,21 @@
         <v>44</v>
       </c>
       <c r="F309" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G309" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="310" spans="1:7">
       <c r="A310" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B310" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C310" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D310" t="s">
         <v>43</v>
@@ -10876,18 +10873,18 @@
         <v>44</v>
       </c>
       <c r="F310" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G310" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="311" spans="1:7">
       <c r="A311" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B311" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C311" t="s">
         <v>77</v>
@@ -10902,12 +10899,12 @@
         <v>358</v>
       </c>
       <c r="G311" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="312" spans="1:7">
       <c r="A312" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B312" t="s">
         <v>64</v>
@@ -10925,7 +10922,7 @@
         <v>332</v>
       </c>
       <c r="G312" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="313" spans="1:7">
@@ -10948,17 +10945,17 @@
         <v>358</v>
       </c>
       <c r="G313" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="314" spans="1:7">
       <c r="A314" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B314" t="s">
-        <v>477</v>
-      </c>
-      <c r="C314" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C314" t="s">
         <v>46</v>
       </c>
       <c r="D314" t="s">
@@ -10968,20 +10965,20 @@
         <v>44</v>
       </c>
       <c r="F314" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G314" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="315" spans="1:7">
       <c r="A315" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B315" t="s">
-        <v>477</v>
-      </c>
-      <c r="C315" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C315" t="s">
         <v>46</v>
       </c>
       <c r="D315" t="s">
@@ -10991,18 +10988,18 @@
         <v>44</v>
       </c>
       <c r="F315" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G315" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="316" spans="1:7">
       <c r="A316" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B316" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C316" t="s">
         <v>370</v>
@@ -11014,21 +11011,21 @@
         <v>44</v>
       </c>
       <c r="F316" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G316" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="317" spans="1:7">
       <c r="A317" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B317" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C317" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D317" t="s">
         <v>57</v>
@@ -11037,21 +11034,21 @@
         <v>44</v>
       </c>
       <c r="F317" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G317" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="318" spans="1:7">
       <c r="A318" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B318" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C318" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D318" t="s">
         <v>57</v>
@@ -11060,20 +11057,20 @@
         <v>44</v>
       </c>
       <c r="F318" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G318" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="319" spans="1:7">
       <c r="A319" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B319" t="s">
-        <v>477</v>
-      </c>
-      <c r="C319" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C319" t="s">
         <v>46</v>
       </c>
       <c r="D319" t="s">
@@ -11083,20 +11080,20 @@
         <v>44</v>
       </c>
       <c r="F319" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G319" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="320" spans="1:7">
       <c r="A320" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B320" t="s">
-        <v>477</v>
-      </c>
-      <c r="C320" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C320" t="s">
         <v>46</v>
       </c>
       <c r="D320" t="s">
@@ -11106,18 +11103,18 @@
         <v>44</v>
       </c>
       <c r="F320" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G320" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="321" spans="1:7">
       <c r="A321" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B321" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C321" t="s">
         <v>370</v>
@@ -11129,10 +11126,10 @@
         <v>44</v>
       </c>
       <c r="F321" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G321" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="322" spans="1:7">
@@ -11140,10 +11137,10 @@
         <v>120</v>
       </c>
       <c r="B322" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C322" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D322" t="s">
         <v>43</v>
@@ -11155,17 +11152,17 @@
         <v>146</v>
       </c>
       <c r="G322" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="323" spans="1:7">
       <c r="A323" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B323" t="s">
-        <v>485</v>
-      </c>
-      <c r="C323" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C323" t="s">
         <v>46</v>
       </c>
       <c r="D323" t="s">
@@ -11178,18 +11175,18 @@
         <v>332</v>
       </c>
       <c r="G323" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="324" spans="1:7">
       <c r="A324" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B324" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C324" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D324" t="s">
         <v>25</v>
@@ -11201,17 +11198,17 @@
         <v>244</v>
       </c>
       <c r="G324" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="325" spans="1:7">
       <c r="A325" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B325" t="s">
-        <v>485</v>
-      </c>
-      <c r="C325" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C325" t="s">
         <v>46</v>
       </c>
       <c r="D325" t="s">
@@ -11224,18 +11221,18 @@
         <v>332</v>
       </c>
       <c r="G325" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="326" spans="1:7">
       <c r="A326" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B326" t="s">
         <v>37</v>
       </c>
       <c r="C326" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D326" t="s">
         <v>35</v>
@@ -11247,18 +11244,18 @@
         <v>146</v>
       </c>
       <c r="G326" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="327" spans="1:7">
       <c r="A327" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B327" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C327" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D327" t="s">
         <v>57</v>
@@ -11267,18 +11264,18 @@
         <v>59</v>
       </c>
       <c r="F327" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G327" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="328" spans="1:7">
       <c r="A328" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B328" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C328" t="s">
         <v>162</v>
@@ -11290,21 +11287,21 @@
         <v>59</v>
       </c>
       <c r="F328" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G328" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="329" spans="1:7">
       <c r="A329" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B329" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C329" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D329" t="s">
         <v>10</v>
@@ -11316,17 +11313,17 @@
         <v>332</v>
       </c>
       <c r="G329" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="330" spans="1:7">
       <c r="A330" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B330" t="s">
-        <v>495</v>
-      </c>
-      <c r="C330" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C330" t="s">
         <v>46</v>
       </c>
       <c r="D330" t="s">
@@ -11339,17 +11336,17 @@
         <v>332</v>
       </c>
       <c r="G330" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="331" spans="1:7">
       <c r="A331" t="s">
+        <v>497</v>
+      </c>
+      <c r="B331" t="s">
         <v>496</v>
       </c>
-      <c r="B331" t="s">
-        <v>495</v>
-      </c>
-      <c r="C331" s="1" t="s">
+      <c r="C331" t="s">
         <v>46</v>
       </c>
       <c r="D331" t="s">
@@ -11362,18 +11359,18 @@
         <v>332</v>
       </c>
       <c r="G331" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="332" spans="1:7">
       <c r="A332" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B332" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C332" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D332" t="s">
         <v>32</v>
@@ -11385,18 +11382,18 @@
         <v>53</v>
       </c>
       <c r="G332" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="333" spans="1:7">
       <c r="A333" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B333" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C333" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D333" t="s">
         <v>17</v>
@@ -11408,18 +11405,18 @@
         <v>358</v>
       </c>
       <c r="G333" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="334" spans="1:7">
       <c r="A334" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B334" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C334" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D334" t="s">
         <v>57</v>
@@ -11431,12 +11428,12 @@
         <v>332</v>
       </c>
       <c r="G334" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="335" spans="1:7">
       <c r="A335" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B335" t="s">
         <v>64</v>
@@ -11451,21 +11448,21 @@
         <v>11</v>
       </c>
       <c r="F335" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G335" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="336" spans="1:7">
       <c r="A336" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B336" t="s">
         <v>64</v>
       </c>
       <c r="C336" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D336" t="s">
         <v>10</v>
@@ -11474,21 +11471,21 @@
         <v>11</v>
       </c>
       <c r="F336" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G336" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="337" spans="1:7">
       <c r="A337" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B337" t="s">
         <v>8</v>
       </c>
       <c r="C337" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D337" t="s">
         <v>87</v>
@@ -11497,21 +11494,21 @@
         <v>11</v>
       </c>
       <c r="F337" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G337" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="338" spans="1:7">
       <c r="A338" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B338" t="s">
         <v>8</v>
       </c>
       <c r="C338" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D338" t="s">
         <v>87</v>
@@ -11520,21 +11517,21 @@
         <v>11</v>
       </c>
       <c r="F338" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G338" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="339" spans="1:7">
       <c r="A339" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B339" t="s">
         <v>8</v>
       </c>
       <c r="C339" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D339" t="s">
         <v>87</v>
@@ -11543,15 +11540,15 @@
         <v>11</v>
       </c>
       <c r="F339" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="G339" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="340" spans="1:7">
       <c r="A340" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B340" t="s">
         <v>8</v>
@@ -11566,21 +11563,21 @@
         <v>11</v>
       </c>
       <c r="F340" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G340" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="341" spans="1:7">
       <c r="A341" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B341" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C341" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D341" t="s">
         <v>25</v>
@@ -11589,21 +11586,21 @@
         <v>11</v>
       </c>
       <c r="F341" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G341" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="342" spans="1:7">
       <c r="A342" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B342" t="s">
         <v>8</v>
       </c>
       <c r="C342" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D342" t="s">
         <v>138</v>
@@ -11612,21 +11609,21 @@
         <v>11</v>
       </c>
       <c r="F342" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G342" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="343" spans="1:7">
       <c r="A343" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B343" t="s">
         <v>8</v>
       </c>
       <c r="C343" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D343" t="s">
         <v>138</v>
@@ -11635,10 +11632,10 @@
         <v>11</v>
       </c>
       <c r="F343" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G343" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="344" spans="1:7">
@@ -11646,10 +11643,10 @@
         <v>220</v>
       </c>
       <c r="B344" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C344" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D344" t="s">
         <v>32</v>
@@ -11658,21 +11655,21 @@
         <v>11</v>
       </c>
       <c r="F344" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="G344" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="345" spans="1:7">
       <c r="A345" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B345" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C345" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D345" t="s">
         <v>32</v>
@@ -11681,18 +11678,18 @@
         <v>11</v>
       </c>
       <c r="F345" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G345" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="346" spans="1:7">
       <c r="A346" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B346" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C346" t="s">
         <v>182</v>
@@ -11704,21 +11701,21 @@
         <v>11</v>
       </c>
       <c r="F346" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G346" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="347" spans="1:7">
       <c r="A347" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B347" t="s">
         <v>37</v>
       </c>
       <c r="C347" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D347" t="s">
         <v>35</v>
@@ -11730,18 +11727,18 @@
         <v>244</v>
       </c>
       <c r="G347" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="348" spans="1:7">
       <c r="A348" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B348" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C348" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D348" t="s">
         <v>57</v>
@@ -11753,18 +11750,18 @@
         <v>137</v>
       </c>
       <c r="G348" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="349" spans="1:7">
       <c r="A349" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B349" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C349" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D349" t="s">
         <v>17</v>
@@ -11776,18 +11773,18 @@
         <v>39</v>
       </c>
       <c r="G349" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="350" spans="1:7">
       <c r="A350" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B350" t="s">
         <v>37</v>
       </c>
       <c r="C350" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D350" t="s">
         <v>18</v>
@@ -11799,12 +11796,12 @@
         <v>137</v>
       </c>
       <c r="G350" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="351" spans="1:7">
       <c r="A351" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B351" t="s">
         <v>64</v>
@@ -11819,15 +11816,15 @@
         <v>44</v>
       </c>
       <c r="F351" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G351" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="352" spans="1:7">
       <c r="A352" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B352" t="s">
         <v>64</v>
@@ -11842,20 +11839,20 @@
         <v>44</v>
       </c>
       <c r="F352" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="G352" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="353" spans="1:7">
       <c r="A353" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B353" t="s">
-        <v>536</v>
-      </c>
-      <c r="C353" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C353" t="s">
         <v>46</v>
       </c>
       <c r="D353" t="s">
@@ -11865,15 +11862,15 @@
         <v>44</v>
       </c>
       <c r="F353" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G353" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="354" spans="1:7">
       <c r="A354" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B354" t="s">
         <v>64</v>
@@ -11891,17 +11888,17 @@
         <v>137</v>
       </c>
       <c r="G354" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="355" spans="1:7">
       <c r="A355" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B355" t="s">
-        <v>536</v>
-      </c>
-      <c r="C355" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C355" t="s">
         <v>46</v>
       </c>
       <c r="D355" t="s">
@@ -11911,21 +11908,21 @@
         <v>44</v>
       </c>
       <c r="F355" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G355" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="356" spans="1:7">
       <c r="A356" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B356" t="s">
         <v>64</v>
       </c>
       <c r="C356" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D356" t="s">
         <v>35</v>
@@ -11934,15 +11931,15 @@
         <v>44</v>
       </c>
       <c r="F356" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G356" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="357" spans="1:7">
       <c r="A357" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B357" t="s">
         <v>64</v>
@@ -11960,12 +11957,12 @@
         <v>137</v>
       </c>
       <c r="G357" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="358" spans="1:7">
       <c r="A358" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B358" t="s">
         <v>37</v>
@@ -11983,15 +11980,15 @@
         <v>83</v>
       </c>
       <c r="G358" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="359" spans="1:7">
       <c r="A359" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B359" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C359" t="s">
         <v>189</v>
@@ -12006,15 +12003,15 @@
         <v>83</v>
       </c>
       <c r="G359" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="360" spans="1:7">
       <c r="A360" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B360" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C360" t="s">
         <v>189</v>
@@ -12026,20 +12023,20 @@
         <v>59</v>
       </c>
       <c r="F360" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="G360" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="361" spans="1:7">
       <c r="A361" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B361" t="s">
-        <v>536</v>
-      </c>
-      <c r="C361" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C361" t="s">
         <v>46</v>
       </c>
       <c r="D361" t="s">
@@ -12049,10 +12046,10 @@
         <v>59</v>
       </c>
       <c r="F361" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="G361" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="362" spans="1:7">
@@ -12060,7 +12057,7 @@
         <v>220</v>
       </c>
       <c r="B362" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C362" t="s">
         <v>189</v>
@@ -12072,20 +12069,20 @@
         <v>59</v>
       </c>
       <c r="F362" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="G362" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="363" spans="1:7">
       <c r="A363" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B363" t="s">
-        <v>536</v>
-      </c>
-      <c r="C363" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C363" t="s">
         <v>46</v>
       </c>
       <c r="D363" t="s">
@@ -12095,18 +12092,18 @@
         <v>59</v>
       </c>
       <c r="F363" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="G363" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="364" spans="1:7">
       <c r="A364" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B364" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C364" t="s">
         <v>46</v>
@@ -12121,12 +12118,12 @@
         <v>83</v>
       </c>
       <c r="G364" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="365" spans="1:7">
       <c r="A365" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B365" t="s">
         <v>64</v>
@@ -12141,18 +12138,18 @@
         <v>59</v>
       </c>
       <c r="F365" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G365" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="366" spans="1:7">
       <c r="A366" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B366" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C366" t="s">
         <v>340</v>
@@ -12167,18 +12164,18 @@
         <v>137</v>
       </c>
       <c r="G366" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="367" spans="1:7">
       <c r="A367" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B367" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C367" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D367" t="s">
         <v>25</v>
@@ -12187,21 +12184,21 @@
         <v>69</v>
       </c>
       <c r="F367" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="G367" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="368" spans="1:7">
       <c r="A368" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B368" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C368" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D368" t="s">
         <v>25</v>
@@ -12210,18 +12207,18 @@
         <v>69</v>
       </c>
       <c r="F368" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G368" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="369" spans="1:7">
       <c r="A369" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B369" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C369" t="s">
         <v>178</v>
@@ -12233,21 +12230,21 @@
         <v>69</v>
       </c>
       <c r="F369" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G369" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="370" spans="1:7">
       <c r="A370" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B370" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C370" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D370" t="s">
         <v>32</v>
@@ -12256,21 +12253,21 @@
         <v>69</v>
       </c>
       <c r="F370" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="G370" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="371" spans="1:7">
       <c r="A371" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B371" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C371" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D371" t="s">
         <v>32</v>
@@ -12279,18 +12276,18 @@
         <v>69</v>
       </c>
       <c r="F371" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G371" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="372" spans="1:7">
       <c r="A372" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B372" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C372" t="s">
         <v>178</v>
@@ -12302,10 +12299,10 @@
         <v>69</v>
       </c>
       <c r="F372" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G372" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="373" spans="1:7">
@@ -12313,10 +12310,10 @@
         <v>208</v>
       </c>
       <c r="B373" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C373" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D373" t="s">
         <v>17</v>
@@ -12328,12 +12325,12 @@
         <v>137</v>
       </c>
       <c r="G373" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="374" spans="1:7">
       <c r="A374" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B374" t="s">
         <v>64</v>
@@ -12348,10 +12345,10 @@
         <v>69</v>
       </c>
       <c r="F374" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="G374" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="375" spans="1:7">
@@ -12359,7 +12356,7 @@
         <v>292</v>
       </c>
       <c r="B375" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C375" t="s">
         <v>243</v>
@@ -12374,15 +12371,15 @@
         <v>235</v>
       </c>
       <c r="G375" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="376" spans="1:7">
       <c r="A376" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B376" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C376" t="s">
         <v>234</v>
@@ -12397,17 +12394,17 @@
         <v>235</v>
       </c>
       <c r="G376" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="377" spans="1:7">
       <c r="A377" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B377" t="s">
         <v>64</v>
       </c>
-      <c r="C377" s="1" t="s">
+      <c r="C377" t="s">
         <v>46</v>
       </c>
       <c r="D377" t="s">
@@ -12420,7 +12417,7 @@
         <v>235</v>
       </c>
       <c r="G377" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="378" spans="1:7">
@@ -12428,10 +12425,10 @@
         <v>294</v>
       </c>
       <c r="B378" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C378" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D378" t="s">
         <v>17</v>
@@ -12443,15 +12440,15 @@
         <v>235</v>
       </c>
       <c r="G378" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="379" spans="1:7">
       <c r="A379" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B379" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C379" t="s">
         <v>214</v>
@@ -12466,15 +12463,15 @@
         <v>235</v>
       </c>
       <c r="G379" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="380" spans="1:7">
       <c r="A380" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B380" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C380" t="s">
         <v>9</v>
@@ -12486,10 +12483,10 @@
         <v>20</v>
       </c>
       <c r="F380" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G380" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="381" spans="1:7">
@@ -12497,7 +12494,7 @@
         <v>246</v>
       </c>
       <c r="B381" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C381" t="s">
         <v>248</v>
@@ -12512,15 +12509,15 @@
         <v>235</v>
       </c>
       <c r="G381" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="382" spans="1:7">
       <c r="A382" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B382" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C382" t="s">
         <v>9</v>
@@ -12532,21 +12529,21 @@
         <v>20</v>
       </c>
       <c r="F382" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G382" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="383" spans="1:7">
       <c r="A383" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B383" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C383" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D383" t="s">
         <v>43</v>
@@ -12558,18 +12555,18 @@
         <v>235</v>
       </c>
       <c r="G383" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="384" spans="1:7">
       <c r="A384" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B384" t="s">
         <v>8</v>
       </c>
       <c r="C384" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D384" t="s">
         <v>87</v>
@@ -12578,21 +12575,21 @@
         <v>44</v>
       </c>
       <c r="F384" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G384" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="385" spans="1:7">
       <c r="A385" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B385" t="s">
         <v>8</v>
       </c>
       <c r="C385" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D385" t="s">
         <v>138</v>
@@ -12601,21 +12598,21 @@
         <v>44</v>
       </c>
       <c r="F385" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G385" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="386" spans="1:7">
       <c r="A386" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B386" t="s">
         <v>37</v>
       </c>
       <c r="C386" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D386" t="s">
         <v>18</v>
@@ -12627,17 +12624,17 @@
         <v>95</v>
       </c>
       <c r="G386" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="387" spans="1:7">
       <c r="A387" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B387" t="s">
-        <v>588</v>
-      </c>
-      <c r="C387" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="C387" t="s">
         <v>46</v>
       </c>
       <c r="D387" t="s">
@@ -12650,7 +12647,7 @@
         <v>235</v>
       </c>
       <c r="G387" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="388" spans="1:7">
@@ -12658,7 +12655,7 @@
         <v>260</v>
       </c>
       <c r="B388" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C388" t="s">
         <v>248</v>
@@ -12673,18 +12670,18 @@
         <v>235</v>
       </c>
       <c r="G388" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="389" spans="1:7">
       <c r="A389" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B389" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C389" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D389" t="s">
         <v>43</v>
@@ -12693,21 +12690,21 @@
         <v>69</v>
       </c>
       <c r="F389" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G389" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="390" spans="1:7">
       <c r="A390" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B390" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C390" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D390" t="s">
         <v>43</v>
@@ -12716,18 +12713,18 @@
         <v>69</v>
       </c>
       <c r="F390" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G390" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="391" spans="1:7">
       <c r="A391" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B391" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C391" t="s">
         <v>243</v>
@@ -12739,20 +12736,20 @@
         <v>69</v>
       </c>
       <c r="F391" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G391" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="392" spans="1:7">
       <c r="A392" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B392" t="s">
-        <v>601</v>
-      </c>
-      <c r="C392" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C392" t="s">
         <v>46</v>
       </c>
       <c r="D392" t="s">
@@ -12762,18 +12759,18 @@
         <v>69</v>
       </c>
       <c r="F392" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G392" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="393" spans="1:7">
       <c r="A393" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B393" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C393" t="s">
         <v>243</v>
@@ -12785,20 +12782,20 @@
         <v>69</v>
       </c>
       <c r="F393" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G393" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="394" spans="1:7">
       <c r="A394" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B394" t="s">
-        <v>601</v>
-      </c>
-      <c r="C394" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C394" t="s">
         <v>46</v>
       </c>
       <c r="D394" t="s">
@@ -12808,10 +12805,10 @@
         <v>69</v>
       </c>
       <c r="F394" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G394" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="395" spans="1:7">
@@ -12819,7 +12816,7 @@
         <v>265</v>
       </c>
       <c r="B395" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C395" t="s">
         <v>266</v>
@@ -12834,18 +12831,18 @@
         <v>235</v>
       </c>
       <c r="G395" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="396" spans="1:7">
       <c r="A396" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B396" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C396" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D396" t="s">
         <v>57</v>
@@ -12854,21 +12851,21 @@
         <v>69</v>
       </c>
       <c r="F396" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G396" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="397" spans="1:7">
       <c r="A397" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B397" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C397" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D397" t="s">
         <v>57</v>
@@ -12877,10 +12874,10 @@
         <v>69</v>
       </c>
       <c r="F397" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G397" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="398" spans="1:7">
@@ -12888,7 +12885,7 @@
         <v>292</v>
       </c>
       <c r="B398" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C398" t="s">
         <v>243</v>
@@ -12903,15 +12900,15 @@
         <v>235</v>
       </c>
       <c r="G398" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="399" spans="1:7">
       <c r="A399" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B399" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C399" t="s">
         <v>234</v>
@@ -12926,17 +12923,17 @@
         <v>235</v>
       </c>
       <c r="G399" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="400" spans="1:7">
       <c r="A400" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B400" t="s">
         <v>64</v>
       </c>
-      <c r="C400" s="1" t="s">
+      <c r="C400" t="s">
         <v>46</v>
       </c>
       <c r="D400" t="s">
@@ -12949,7 +12946,7 @@
         <v>235</v>
       </c>
       <c r="G400" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="401" spans="1:7">
@@ -12957,10 +12954,10 @@
         <v>294</v>
       </c>
       <c r="B401" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C401" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D401" t="s">
         <v>17</v>
@@ -12972,15 +12969,15 @@
         <v>235</v>
       </c>
       <c r="G401" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="402" spans="1:7">
       <c r="A402" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B402" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C402" t="s">
         <v>214</v>
@@ -12995,17 +12992,17 @@
         <v>235</v>
       </c>
       <c r="G402" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="403" spans="1:7">
       <c r="A403" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B403" t="s">
-        <v>614</v>
-      </c>
-      <c r="C403" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="C403" t="s">
         <v>46</v>
       </c>
       <c r="D403" t="s">
@@ -13015,21 +13012,21 @@
         <v>20</v>
       </c>
       <c r="F403" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G403" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="404" spans="1:7">
       <c r="A404" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B404" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C404" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D404" t="s">
         <v>25</v>
@@ -13038,20 +13035,20 @@
         <v>20</v>
       </c>
       <c r="F404" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G404" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="405" spans="1:7">
       <c r="A405" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B405" t="s">
-        <v>614</v>
-      </c>
-      <c r="C405" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="C405" t="s">
         <v>46</v>
       </c>
       <c r="D405" t="s">
@@ -13061,21 +13058,21 @@
         <v>20</v>
       </c>
       <c r="F405" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G405" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="406" spans="1:7">
       <c r="A406" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B406" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C406" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D406" t="s">
         <v>32</v>
@@ -13084,10 +13081,10 @@
         <v>20</v>
       </c>
       <c r="F406" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G406" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="407" spans="1:7">
@@ -13095,7 +13092,7 @@
         <v>246</v>
       </c>
       <c r="B407" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C407" t="s">
         <v>248</v>
@@ -13110,18 +13107,18 @@
         <v>235</v>
       </c>
       <c r="G407" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="408" spans="1:7">
       <c r="A408" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B408" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C408" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D408" t="s">
         <v>43</v>
@@ -13133,17 +13130,17 @@
         <v>235</v>
       </c>
       <c r="G408" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="409" spans="1:7">
       <c r="A409" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B409" t="s">
-        <v>619</v>
-      </c>
-      <c r="C409" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="C409" t="s">
         <v>46</v>
       </c>
       <c r="D409" t="s">
@@ -13156,18 +13153,18 @@
         <v>235</v>
       </c>
       <c r="G409" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="410" spans="1:7">
       <c r="A410" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B410" t="s">
         <v>8</v>
       </c>
       <c r="C410" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D410" t="s">
         <v>87</v>
@@ -13176,20 +13173,20 @@
         <v>59</v>
       </c>
       <c r="F410" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G410" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="411" spans="1:7">
       <c r="A411" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B411" t="s">
-        <v>620</v>
-      </c>
-      <c r="C411" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="C411" t="s">
         <v>46</v>
       </c>
       <c r="D411" t="s">
@@ -13199,21 +13196,21 @@
         <v>59</v>
       </c>
       <c r="F411" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G411" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="412" spans="1:7">
       <c r="A412" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B412" t="s">
         <v>8</v>
       </c>
       <c r="C412" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D412" t="s">
         <v>138</v>
@@ -13222,20 +13219,20 @@
         <v>59</v>
       </c>
       <c r="F412" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G412" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="413" spans="1:7">
       <c r="A413" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B413" t="s">
-        <v>620</v>
-      </c>
-      <c r="C413" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="C413" t="s">
         <v>46</v>
       </c>
       <c r="D413" t="s">
@@ -13245,10 +13242,10 @@
         <v>59</v>
       </c>
       <c r="F413" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G413" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="414" spans="1:7">
@@ -13256,7 +13253,7 @@
         <v>260</v>
       </c>
       <c r="B414" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C414" t="s">
         <v>248</v>
@@ -13271,15 +13268,15 @@
         <v>235</v>
       </c>
       <c r="G414" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="415" spans="1:7">
       <c r="A415" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B415" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C415" t="s">
         <v>243</v>
@@ -13291,18 +13288,18 @@
         <v>69</v>
       </c>
       <c r="F415" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G415" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="416" spans="1:7">
       <c r="A416" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B416" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C416" t="s">
         <v>97</v>
@@ -13314,18 +13311,18 @@
         <v>69</v>
       </c>
       <c r="F416" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G416" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="417" spans="1:7">
       <c r="A417" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B417" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C417" t="s">
         <v>243</v>
@@ -13337,18 +13334,18 @@
         <v>69</v>
       </c>
       <c r="F417" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G417" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="418" spans="1:7">
       <c r="A418" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B418" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C418" t="s">
         <v>97</v>
@@ -13360,10 +13357,10 @@
         <v>69</v>
       </c>
       <c r="F418" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G418" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="419" spans="1:7">
@@ -13371,7 +13368,7 @@
         <v>265</v>
       </c>
       <c r="B419" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C419" t="s">
         <v>266</v>
@@ -13386,18 +13383,18 @@
         <v>235</v>
       </c>
       <c r="G419" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="420" spans="1:7">
       <c r="A420" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B420" t="s">
         <v>37</v>
       </c>
       <c r="C420" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D420" t="s">
         <v>18</v>
@@ -13409,18 +13406,18 @@
         <v>95</v>
       </c>
       <c r="G420" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="421" spans="1:7">
       <c r="A421" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B421" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C421" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D421" t="s">
         <v>43</v>
@@ -13429,41 +13426,41 @@
         <v>11</v>
       </c>
       <c r="F421" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G421" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="422" spans="1:7">
       <c r="A422" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B422" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C422" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D422" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E422" t="s">
         <v>11</v>
       </c>
       <c r="F422" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="G422" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="423" spans="1:7">
       <c r="A423" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B423" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C423" t="s">
         <v>275</v>
@@ -13475,38 +13472,38 @@
         <v>11</v>
       </c>
       <c r="F423" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G423" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="424" spans="1:7">
       <c r="A424" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B424" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C424" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D424" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E424" t="s">
         <v>11</v>
       </c>
       <c r="F424" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="G424" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="425" spans="1:7">
       <c r="A425" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B425" t="s">
         <v>37</v>
@@ -13521,10 +13518,10 @@
         <v>11</v>
       </c>
       <c r="F425" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G425" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="426" spans="1:7">
@@ -13532,7 +13529,7 @@
         <v>260</v>
       </c>
       <c r="B426" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C426" t="s">
         <v>162</v>
@@ -13544,18 +13541,18 @@
         <v>11</v>
       </c>
       <c r="F426" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G426" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="427" spans="1:7">
       <c r="A427" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B427" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C427" t="s">
         <v>196</v>
@@ -13567,18 +13564,18 @@
         <v>44</v>
       </c>
       <c r="F427" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G427" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="428" spans="1:7">
       <c r="A428" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B428" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C428" t="s">
         <v>321</v>
@@ -13590,18 +13587,18 @@
         <v>44</v>
       </c>
       <c r="F428" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="G428" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="429" spans="1:7">
       <c r="A429" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B429" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C429" t="s">
         <v>321</v>
@@ -13613,21 +13610,21 @@
         <v>44</v>
       </c>
       <c r="F429" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="G429" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="430" spans="1:7">
       <c r="A430" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B430" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C430" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D430" t="s">
         <v>17</v>
@@ -13636,18 +13633,18 @@
         <v>44</v>
       </c>
       <c r="F430" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="G430" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="431" spans="1:7">
       <c r="A431" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B431" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C431" t="s">
         <v>97</v>
@@ -13659,10 +13656,10 @@
         <v>44</v>
       </c>
       <c r="F431" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="G431" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="432" spans="1:7">
@@ -13670,7 +13667,7 @@
         <v>246</v>
       </c>
       <c r="B432" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C432" t="s">
         <v>248</v>
@@ -13682,10 +13679,10 @@
         <v>59</v>
       </c>
       <c r="F432" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G432" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="433" spans="1:7">
@@ -13693,10 +13690,10 @@
         <v>292</v>
       </c>
       <c r="B433" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C433" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D433" t="s">
         <v>25</v>
@@ -13705,20 +13702,20 @@
         <v>59</v>
       </c>
       <c r="F433" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G433" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="434" spans="1:7">
       <c r="A434" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B434" t="s">
         <v>37</v>
       </c>
-      <c r="C434" s="1" t="s">
+      <c r="C434" t="s">
         <v>46</v>
       </c>
       <c r="D434" t="s">
@@ -13731,15 +13728,15 @@
         <v>39</v>
       </c>
       <c r="G434" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="435" spans="1:7">
       <c r="A435" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B435" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C435" t="s">
         <v>280</v>
@@ -13751,18 +13748,18 @@
         <v>59</v>
       </c>
       <c r="F435" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G435" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="436" spans="1:7">
       <c r="A436" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B436" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C436" t="s">
         <v>280</v>
@@ -13774,10 +13771,10 @@
         <v>59</v>
       </c>
       <c r="F436" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G436" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="437" spans="1:7">
@@ -13785,10 +13782,10 @@
         <v>294</v>
       </c>
       <c r="B437" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C437" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D437" t="s">
         <v>43</v>
@@ -13797,21 +13794,21 @@
         <v>69</v>
       </c>
       <c r="F437" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G437" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="438" spans="1:7">
       <c r="A438" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B438" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C438" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D438" t="s">
         <v>25</v>
@@ -13820,18 +13817,18 @@
         <v>69</v>
       </c>
       <c r="F438" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="G438" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="439" spans="1:7">
       <c r="A439" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B439" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C439" t="s">
         <v>9</v>
@@ -13843,21 +13840,21 @@
         <v>69</v>
       </c>
       <c r="F439" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G439" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="440" spans="1:7">
       <c r="A440" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B440" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C440" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D440" t="s">
         <v>32</v>
@@ -13866,18 +13863,18 @@
         <v>69</v>
       </c>
       <c r="F440" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="G440" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="441" spans="1:7">
       <c r="A441" t="s">
+        <v>658</v>
+      </c>
+      <c r="B441" t="s">
         <v>657</v>
-      </c>
-      <c r="B441" t="s">
-        <v>656</v>
       </c>
       <c r="C441" t="s">
         <v>9</v>
@@ -13889,21 +13886,21 @@
         <v>69</v>
       </c>
       <c r="F441" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G441" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="442" spans="1:7">
       <c r="A442" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B442" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C442" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D442" t="s">
         <v>57</v>
@@ -13912,10 +13909,10 @@
         <v>69</v>
       </c>
       <c r="F442" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G442" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="443" spans="1:7">
@@ -13923,10 +13920,10 @@
         <v>292</v>
       </c>
       <c r="B443" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C443" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D443" t="s">
         <v>43</v>
@@ -13938,15 +13935,15 @@
         <v>244</v>
       </c>
       <c r="G443" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="444" spans="1:7">
       <c r="A444" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B444" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C444" t="s">
         <v>234</v>
@@ -13961,12 +13958,12 @@
         <v>235</v>
       </c>
       <c r="G444" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="445" spans="1:7">
       <c r="A445" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B445" t="s">
         <v>64</v>
@@ -13984,7 +13981,7 @@
         <v>244</v>
       </c>
       <c r="G445" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="446" spans="1:7">
@@ -13992,10 +13989,10 @@
         <v>294</v>
       </c>
       <c r="B446" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C446" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D446" t="s">
         <v>17</v>
@@ -14007,15 +14004,15 @@
         <v>235</v>
       </c>
       <c r="G446" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="447" spans="1:7">
       <c r="A447" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B447" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C447" t="s">
         <v>214</v>
@@ -14030,15 +14027,15 @@
         <v>235</v>
       </c>
       <c r="G447" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="448" spans="1:7">
       <c r="A448" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B448" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C448" t="s">
         <v>321</v>
@@ -14050,21 +14047,21 @@
         <v>20</v>
       </c>
       <c r="F448" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G448" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="449" spans="1:7">
       <c r="A449" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B449" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C449" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D449" t="s">
         <v>43</v>
@@ -14073,10 +14070,10 @@
         <v>20</v>
       </c>
       <c r="F449" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G449" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="450" spans="1:7">
@@ -14099,15 +14096,15 @@
         <v>244</v>
       </c>
       <c r="G450" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="451" spans="1:7">
       <c r="A451" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B451" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C451" t="s">
         <v>321</v>
@@ -14119,21 +14116,21 @@
         <v>20</v>
       </c>
       <c r="F451" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G451" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="452" spans="1:7">
       <c r="A452" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B452" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C452" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D452" t="s">
         <v>57</v>
@@ -14142,21 +14139,21 @@
         <v>20</v>
       </c>
       <c r="F452" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G452" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="453" spans="1:7">
       <c r="A453" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B453" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C453" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D453" t="s">
         <v>43</v>
@@ -14168,18 +14165,18 @@
         <v>235</v>
       </c>
       <c r="G453" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="454" spans="1:7">
       <c r="A454" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B454" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C454" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D454" t="s">
         <v>25</v>
@@ -14188,18 +14185,18 @@
         <v>44</v>
       </c>
       <c r="F454" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G454" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="455" spans="1:7">
       <c r="A455" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B455" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C455" t="s">
         <v>214</v>
@@ -14211,21 +14208,21 @@
         <v>44</v>
       </c>
       <c r="F455" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G455" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="456" spans="1:7">
       <c r="A456" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B456" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C456" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D456" t="s">
         <v>32</v>
@@ -14234,18 +14231,18 @@
         <v>44</v>
       </c>
       <c r="F456" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G456" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="457" spans="1:7">
       <c r="A457" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B457" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C457" t="s">
         <v>214</v>
@@ -14257,21 +14254,21 @@
         <v>44</v>
       </c>
       <c r="F457" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G457" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="458" spans="1:7">
       <c r="A458" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B458" t="s">
         <v>37</v>
       </c>
       <c r="C458" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D458" t="s">
         <v>18</v>
@@ -14283,15 +14280,15 @@
         <v>39</v>
       </c>
       <c r="G458" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="459" spans="1:7">
       <c r="A459" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B459" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C459" t="s">
         <v>266</v>
@@ -14306,18 +14303,18 @@
         <v>244</v>
       </c>
       <c r="G459" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="460" spans="1:7">
       <c r="A460" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B460" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C460" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D460" t="s">
         <v>25</v>
@@ -14326,18 +14323,18 @@
         <v>59</v>
       </c>
       <c r="F460" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G460" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="461" spans="1:7">
       <c r="A461" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B461" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C461" t="s">
         <v>266</v>
@@ -14349,21 +14346,21 @@
         <v>59</v>
       </c>
       <c r="F461" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G461" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="462" spans="1:7">
       <c r="A462" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B462" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C462" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D462" t="s">
         <v>32</v>
@@ -14372,18 +14369,18 @@
         <v>59</v>
       </c>
       <c r="F462" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G462" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="463" spans="1:7">
       <c r="A463" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B463" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C463" t="s">
         <v>266</v>
@@ -14395,10 +14392,10 @@
         <v>59</v>
       </c>
       <c r="F463" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G463" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="464" spans="1:7">
@@ -14406,7 +14403,7 @@
         <v>260</v>
       </c>
       <c r="B464" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C464" t="s">
         <v>248</v>
@@ -14421,7 +14418,7 @@
         <v>235</v>
       </c>
       <c r="G464" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="465" spans="1:7">
@@ -14429,7 +14426,7 @@
         <v>265</v>
       </c>
       <c r="B465" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C465" t="s">
         <v>266</v>
@@ -14444,7 +14441,7 @@
         <v>235</v>
       </c>
       <c r="G465" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="466" spans="1:7">
@@ -14452,10 +14449,10 @@
         <v>292</v>
       </c>
       <c r="B466" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C466" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D466" t="s">
         <v>43</v>
@@ -14467,15 +14464,15 @@
         <v>244</v>
       </c>
       <c r="G466" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="467" spans="1:7">
       <c r="A467" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B467" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C467" t="s">
         <v>234</v>
@@ -14490,12 +14487,12 @@
         <v>235</v>
       </c>
       <c r="G467" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="468" spans="1:7">
       <c r="A468" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B468" t="s">
         <v>64</v>
@@ -14513,7 +14510,7 @@
         <v>244</v>
       </c>
       <c r="G468" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="469" spans="1:7">
@@ -14521,10 +14518,10 @@
         <v>294</v>
       </c>
       <c r="B469" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C469" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D469" t="s">
         <v>17</v>
@@ -14536,15 +14533,15 @@
         <v>235</v>
       </c>
       <c r="G469" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="470" spans="1:7">
       <c r="A470" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B470" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C470" t="s">
         <v>214</v>
@@ -14559,18 +14556,18 @@
         <v>235</v>
       </c>
       <c r="G470" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="471" spans="1:7">
       <c r="A471" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B471" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C471" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D471" t="s">
         <v>43</v>
@@ -14579,10 +14576,10 @@
         <v>20</v>
       </c>
       <c r="F471" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G471" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="472" spans="1:7">
@@ -14605,18 +14602,18 @@
         <v>244</v>
       </c>
       <c r="G472" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="473" spans="1:7">
       <c r="A473" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B473" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C473" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D473" t="s">
         <v>57</v>
@@ -14625,18 +14622,18 @@
         <v>20</v>
       </c>
       <c r="F473" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G473" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="474" spans="1:7">
       <c r="A474" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B474" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C474" t="s">
         <v>214</v>
@@ -14648,21 +14645,21 @@
         <v>20</v>
       </c>
       <c r="F474" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G474" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="475" spans="1:7">
       <c r="A475" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B475" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C475" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D475" t="s">
         <v>43</v>
@@ -14674,18 +14671,18 @@
         <v>235</v>
       </c>
       <c r="G475" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="476" spans="1:7">
       <c r="A476" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B476" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C476" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D476" t="s">
         <v>25</v>
@@ -14694,18 +14691,18 @@
         <v>44</v>
       </c>
       <c r="F476" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G476" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="477" spans="1:7">
       <c r="A477" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B477" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C477" t="s">
         <v>266</v>
@@ -14717,21 +14714,21 @@
         <v>44</v>
       </c>
       <c r="F477" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G477" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="478" spans="1:7">
       <c r="A478" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B478" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C478" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D478" t="s">
         <v>32</v>
@@ -14740,18 +14737,18 @@
         <v>44</v>
       </c>
       <c r="F478" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G478" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="479" spans="1:7">
       <c r="A479" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B479" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C479" t="s">
         <v>266</v>
@@ -14763,21 +14760,21 @@
         <v>44</v>
       </c>
       <c r="F479" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G479" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="480" spans="1:7">
       <c r="A480" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B480" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C480" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D480" t="s">
         <v>17</v>
@@ -14786,18 +14783,18 @@
         <v>44</v>
       </c>
       <c r="F480" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G480" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="481" spans="1:7">
       <c r="A481" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B481" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C481" t="s">
         <v>234</v>
@@ -14809,21 +14806,21 @@
         <v>44</v>
       </c>
       <c r="F481" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G481" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="482" spans="1:7">
       <c r="A482" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B482" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C482" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D482" t="s">
         <v>57</v>
@@ -14832,18 +14829,18 @@
         <v>44</v>
       </c>
       <c r="F482" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G482" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="483" spans="1:7">
       <c r="A483" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B483" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C483" t="s">
         <v>234</v>
@@ -14855,18 +14852,18 @@
         <v>44</v>
       </c>
       <c r="F483" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G483" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="484" spans="1:7">
       <c r="A484" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B484" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C484" t="s">
         <v>266</v>
@@ -14881,7 +14878,7 @@
         <v>244</v>
       </c>
       <c r="G484" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="485" spans="1:7">
@@ -14889,7 +14886,7 @@
         <v>260</v>
       </c>
       <c r="B485" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C485" t="s">
         <v>248</v>
@@ -14904,12 +14901,12 @@
         <v>235</v>
       </c>
       <c r="G485" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="486" spans="1:7">
       <c r="A486" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B486" t="s">
         <v>8</v>
@@ -14924,10 +14921,10 @@
         <v>69</v>
       </c>
       <c r="F486" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G486" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="487" spans="1:7">
@@ -14935,7 +14932,7 @@
         <v>265</v>
       </c>
       <c r="B487" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C487" t="s">
         <v>266</v>
@@ -14950,18 +14947,18 @@
         <v>235</v>
       </c>
       <c r="G487" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="488" spans="1:7">
       <c r="A488" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B488" t="s">
         <v>37</v>
       </c>
       <c r="C488" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D488" t="s">
         <v>18</v>
@@ -14973,15 +14970,15 @@
         <v>95</v>
       </c>
       <c r="G488" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="489" spans="1:7">
       <c r="A489" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B489" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C489" t="s">
         <v>337</v>
@@ -14993,21 +14990,21 @@
         <v>11</v>
       </c>
       <c r="F489" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="G489" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="490" spans="1:7">
       <c r="A490" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B490" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C490" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D490" t="s">
         <v>32</v>
@@ -15016,21 +15013,21 @@
         <v>11</v>
       </c>
       <c r="F490" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="G490" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="491" spans="1:7">
       <c r="A491" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B491" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C491" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D491" t="s">
         <v>17</v>
@@ -15039,18 +15036,18 @@
         <v>11</v>
       </c>
       <c r="F491" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G491" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="492" spans="1:7">
       <c r="A492" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B492" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C492" t="s">
         <v>162</v>
@@ -15062,15 +15059,15 @@
         <v>11</v>
       </c>
       <c r="F492" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G492" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="493" spans="1:7">
       <c r="A493" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B493" t="s">
         <v>8</v>
@@ -15088,12 +15085,12 @@
         <v>45</v>
       </c>
       <c r="G493" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="494" spans="1:7">
       <c r="A494" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B494" t="s">
         <v>37</v>
@@ -15111,15 +15108,15 @@
         <v>45</v>
       </c>
       <c r="G494" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="495" spans="1:7">
       <c r="A495" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B495" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C495" t="s">
         <v>321</v>
@@ -15134,17 +15131,17 @@
         <v>39</v>
       </c>
       <c r="G495" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="496" spans="1:7">
       <c r="A496" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B496" t="s">
         <v>8</v>
       </c>
-      <c r="C496" s="1" t="s">
+      <c r="C496" t="s">
         <v>46</v>
       </c>
       <c r="D496" t="s">
@@ -15157,17 +15154,17 @@
         <v>46</v>
       </c>
       <c r="G496" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="497" spans="1:7">
       <c r="A497" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B497" t="s">
         <v>64</v>
       </c>
-      <c r="C497" s="1" t="s">
+      <c r="C497" t="s">
         <v>46</v>
       </c>
       <c r="D497" t="s">
@@ -15180,12 +15177,12 @@
         <v>45</v>
       </c>
       <c r="G497" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="498" spans="1:7">
       <c r="A498" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B498" t="s">
         <v>37</v>
@@ -15203,12 +15200,12 @@
         <v>45</v>
       </c>
       <c r="G498" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="499" spans="1:7">
       <c r="A499" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B499" t="s">
         <v>37</v>
@@ -15226,17 +15223,17 @@
         <v>45</v>
       </c>
       <c r="G499" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="500" spans="1:7">
       <c r="A500" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B500" t="s">
         <v>8</v>
       </c>
-      <c r="C500" s="1" t="s">
+      <c r="C500" t="s">
         <v>46</v>
       </c>
       <c r="D500" t="s">
@@ -15249,18 +15246,18 @@
         <v>46</v>
       </c>
       <c r="G500" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="501" spans="1:7">
       <c r="A501" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B501" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C501" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D501" t="s">
         <v>25</v>
@@ -15272,18 +15269,18 @@
         <v>45</v>
       </c>
       <c r="G501" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="502" spans="1:7">
       <c r="A502" t="s">
+        <v>719</v>
+      </c>
+      <c r="B502" t="s">
+        <v>720</v>
+      </c>
+      <c r="C502" t="s">
         <v>718</v>
-      </c>
-      <c r="B502" t="s">
-        <v>719</v>
-      </c>
-      <c r="C502" t="s">
-        <v>717</v>
       </c>
       <c r="D502" t="s">
         <v>32</v>
@@ -15295,18 +15292,18 @@
         <v>45</v>
       </c>
       <c r="G502" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="503" spans="1:7">
       <c r="A503" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B503" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C503" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D503" t="s">
         <v>17</v>
@@ -15318,18 +15315,18 @@
         <v>45</v>
       </c>
       <c r="G503" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="504" spans="1:7">
       <c r="A504" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B504" t="s">
         <v>37</v>
       </c>
       <c r="C504" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D504" t="s">
         <v>18</v>
@@ -15341,12 +15338,12 @@
         <v>45</v>
       </c>
       <c r="G504" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="505" spans="1:7">
       <c r="A505" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B505" t="s">
         <v>8</v>
@@ -15364,18 +15361,18 @@
         <v>46</v>
       </c>
       <c r="G505" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="506" spans="1:7">
       <c r="A506" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B506" t="s">
         <v>8</v>
       </c>
       <c r="C506" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D506" t="s">
         <v>18</v>
@@ -15387,15 +15384,15 @@
         <v>46</v>
       </c>
       <c r="G506" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="507" spans="1:7">
       <c r="A507" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B507" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C507" t="s">
         <v>297</v>
@@ -15410,12 +15407,12 @@
         <v>50</v>
       </c>
       <c r="G507" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="508" spans="1:7">
       <c r="A508" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B508" t="s">
         <v>8</v>
@@ -15430,20 +15427,20 @@
         <v>11</v>
       </c>
       <c r="F508" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G508" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="509" spans="1:7">
       <c r="A509" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B509" t="s">
         <v>8</v>
       </c>
-      <c r="C509" s="1" t="s">
+      <c r="C509" t="s">
         <v>46</v>
       </c>
       <c r="D509" t="s">
@@ -15453,15 +15450,15 @@
         <v>11</v>
       </c>
       <c r="F509" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G509" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="510" spans="1:7">
       <c r="A510" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B510" t="s">
         <v>37</v>
@@ -15479,15 +15476,15 @@
         <v>50</v>
       </c>
       <c r="G510" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="511" spans="1:7">
       <c r="A511" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B511" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C511" t="s">
         <v>297</v>
@@ -15502,12 +15499,12 @@
         <v>50</v>
       </c>
       <c r="G511" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="512" spans="1:7">
       <c r="A512" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B512" t="s">
         <v>8</v>
@@ -15525,12 +15522,12 @@
         <v>50</v>
       </c>
       <c r="G512" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="513" spans="1:7">
       <c r="A513" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B513" t="s">
         <v>37</v>
@@ -15548,15 +15545,15 @@
         <v>50</v>
       </c>
       <c r="G513" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="514" spans="1:7">
       <c r="A514" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B514" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C514" t="s">
         <v>321</v>
@@ -15571,7 +15568,7 @@
         <v>39</v>
       </c>
       <c r="G514" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="515" spans="1:7">
@@ -15579,7 +15576,7 @@
         <v>322</v>
       </c>
       <c r="B515" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C515" t="s">
         <v>324</v>
@@ -15594,17 +15591,17 @@
         <v>316</v>
       </c>
       <c r="G515" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="516" spans="1:7">
       <c r="A516" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B516" t="s">
         <v>8</v>
       </c>
-      <c r="C516" s="1" t="s">
+      <c r="C516" t="s">
         <v>46</v>
       </c>
       <c r="D516" t="s">
@@ -15614,15 +15611,15 @@
         <v>44</v>
       </c>
       <c r="F516" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G516" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="517" spans="1:7">
       <c r="A517" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B517" t="s">
         <v>8</v>
@@ -15637,18 +15634,18 @@
         <v>44</v>
       </c>
       <c r="F517" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G517" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="518" spans="1:7">
       <c r="A518" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B518" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C518" t="s">
         <v>326</v>
@@ -15663,7 +15660,7 @@
         <v>50</v>
       </c>
       <c r="G518" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="519" spans="1:7">
@@ -15671,7 +15668,7 @@
         <v>330</v>
       </c>
       <c r="B519" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C519" t="s">
         <v>324</v>
@@ -15686,15 +15683,15 @@
         <v>332</v>
       </c>
       <c r="G519" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="520" spans="1:7">
       <c r="A520" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B520" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C520" t="s">
         <v>240</v>
@@ -15709,12 +15706,12 @@
         <v>50</v>
       </c>
       <c r="G520" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="521" spans="1:7">
       <c r="A521" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B521" t="s">
         <v>37</v>
@@ -15732,12 +15729,12 @@
         <v>50</v>
       </c>
       <c r="G521" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="522" spans="1:7">
       <c r="A522" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B522" t="s">
         <v>37</v>
@@ -15755,12 +15752,12 @@
         <v>50</v>
       </c>
       <c r="G522" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="523" spans="1:7">
       <c r="A523" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B523" t="s">
         <v>64</v>
@@ -15778,12 +15775,12 @@
         <v>50</v>
       </c>
       <c r="G523" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="524" spans="1:7">
       <c r="A524" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B524" t="s">
         <v>64</v>
@@ -15801,7 +15798,7 @@
         <v>174</v>
       </c>
       <c r="G524" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="525" spans="1:7">
@@ -15824,15 +15821,15 @@
         <v>174</v>
       </c>
       <c r="G525" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="526" spans="1:7">
       <c r="A526" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B526" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C526" t="s">
         <v>275</v>
@@ -15847,12 +15844,12 @@
         <v>174</v>
       </c>
       <c r="G526" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="527" spans="1:7">
       <c r="A527" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B527" t="s">
         <v>8</v>
@@ -15867,15 +15864,15 @@
         <v>20</v>
       </c>
       <c r="F527" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="G527" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="528" spans="1:7">
       <c r="A528" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B528" t="s">
         <v>37</v>
@@ -15893,15 +15890,15 @@
         <v>174</v>
       </c>
       <c r="G528" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="529" spans="1:7">
       <c r="A529" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B529" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C529" t="s">
         <v>321</v>
@@ -15916,15 +15913,15 @@
         <v>39</v>
       </c>
       <c r="G529" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="530" spans="1:7">
       <c r="A530" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B530" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C530" t="s">
         <v>309</v>
@@ -15939,15 +15936,15 @@
         <v>174</v>
       </c>
       <c r="G530" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="531" spans="1:7">
       <c r="A531" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B531" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C531" t="s">
         <v>334</v>
@@ -15962,15 +15959,15 @@
         <v>174</v>
       </c>
       <c r="G531" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="532" spans="1:7">
       <c r="A532" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B532" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C532" t="s">
         <v>334</v>
@@ -15985,18 +15982,18 @@
         <v>174</v>
       </c>
       <c r="G532" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="533" spans="1:7">
       <c r="A533" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B533" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C533" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D533" t="s">
         <v>17</v>
@@ -16008,15 +16005,15 @@
         <v>174</v>
       </c>
       <c r="G533" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="534" spans="1:7">
       <c r="A534" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B534" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C534" t="s">
         <v>340</v>
@@ -16031,15 +16028,15 @@
         <v>174</v>
       </c>
       <c r="G534" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="535" spans="1:7">
       <c r="A535" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B535" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C535" t="s">
         <v>340</v>
@@ -16054,12 +16051,12 @@
         <v>174</v>
       </c>
       <c r="G535" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="536" spans="1:7">
       <c r="A536" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B536" t="s">
         <v>8</v>
@@ -16068,27 +16065,27 @@
         <v>309</v>
       </c>
       <c r="D536" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E536" t="s">
         <v>69</v>
       </c>
       <c r="F536" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G536" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="537" spans="1:7">
       <c r="A537" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B537" t="s">
         <v>8</v>
       </c>
       <c r="C537" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D537" t="s">
         <v>87</v>
@@ -16097,18 +16094,18 @@
         <v>69</v>
       </c>
       <c r="F537" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="G537" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="538" spans="1:7">
       <c r="A538" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B538" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C538" t="s">
         <v>312</v>
@@ -16120,21 +16117,21 @@
         <v>69</v>
       </c>
       <c r="F538" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G538" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="539" spans="1:7">
       <c r="A539" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B539" t="s">
         <v>8</v>
       </c>
       <c r="C539" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D539" t="s">
         <v>138</v>
@@ -16143,18 +16140,18 @@
         <v>69</v>
       </c>
       <c r="F539" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="G539" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="540" spans="1:7">
       <c r="A540" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B540" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C540" t="s">
         <v>312</v>
@@ -16166,15 +16163,15 @@
         <v>69</v>
       </c>
       <c r="F540" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G540" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="541" spans="1:7">
       <c r="A541" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B541" t="s">
         <v>8</v>
@@ -16183,27 +16180,27 @@
         <v>309</v>
       </c>
       <c r="D541" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="E541" t="s">
         <v>69</v>
       </c>
       <c r="F541" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G541" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="542" spans="1:7">
       <c r="A542" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B542" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C542" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D542" t="s">
         <v>43</v>
@@ -16215,18 +16212,18 @@
         <v>187</v>
       </c>
       <c r="G542" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="543" spans="1:7">
       <c r="A543" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B543" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C543" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D543" t="s">
         <v>87</v>
@@ -16235,21 +16232,21 @@
         <v>11</v>
       </c>
       <c r="F543" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="G543" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="544" spans="1:7">
       <c r="A544" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B544" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C544" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D544" t="s">
         <v>32</v>
@@ -16258,21 +16255,21 @@
         <v>11</v>
       </c>
       <c r="F544" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G544" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="545" spans="1:7">
       <c r="A545" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B545" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C545" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D545" t="s">
         <v>17</v>
@@ -16284,18 +16281,18 @@
         <v>187</v>
       </c>
       <c r="G545" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="546" spans="1:7">
       <c r="A546" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B546" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C546" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D546" t="s">
         <v>57</v>
@@ -16307,15 +16304,15 @@
         <v>187</v>
       </c>
       <c r="G546" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="547" spans="1:7">
       <c r="A547" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B547" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C547" t="s">
         <v>312</v>
@@ -16330,15 +16327,15 @@
         <v>187</v>
       </c>
       <c r="G547" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="548" spans="1:7">
       <c r="A548" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B548" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C548" t="s">
         <v>312</v>
@@ -16353,15 +16350,15 @@
         <v>187</v>
       </c>
       <c r="G548" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="549" spans="1:7">
       <c r="A549" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B549" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C549" t="s">
         <v>321</v>
@@ -16376,18 +16373,18 @@
         <v>39</v>
       </c>
       <c r="G549" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="550" spans="1:7">
       <c r="A550" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B550" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C550" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D550" t="s">
         <v>43</v>
@@ -16396,21 +16393,21 @@
         <v>44</v>
       </c>
       <c r="F550" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="G550" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="551" spans="1:7">
       <c r="A551" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B551" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C551" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D551" t="s">
         <v>25</v>
@@ -16422,18 +16419,18 @@
         <v>187</v>
       </c>
       <c r="G551" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="552" spans="1:7">
       <c r="A552" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B552" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C552" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D552" t="s">
         <v>32</v>
@@ -16445,15 +16442,15 @@
         <v>187</v>
       </c>
       <c r="G552" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="553" spans="1:7">
       <c r="A553" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B553" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C553" t="s">
         <v>266</v>
@@ -16468,18 +16465,18 @@
         <v>187</v>
       </c>
       <c r="G553" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="554" spans="1:7">
       <c r="A554" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B554" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C554" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D554" t="s">
         <v>57</v>
@@ -16488,21 +16485,21 @@
         <v>44</v>
       </c>
       <c r="F554" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="G554" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="555" spans="1:7">
       <c r="A555" t="s">
+        <v>805</v>
+      </c>
+      <c r="B555" t="s">
+        <v>806</v>
+      </c>
+      <c r="C555" t="s">
         <v>804</v>
-      </c>
-      <c r="B555" t="s">
-        <v>805</v>
-      </c>
-      <c r="C555" t="s">
-        <v>803</v>
       </c>
       <c r="D555" t="s">
         <v>17</v>
@@ -16514,18 +16511,18 @@
         <v>187</v>
       </c>
       <c r="G555" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="556" spans="1:7">
       <c r="A556" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B556" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C556" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D556" t="s">
         <v>57</v>
@@ -16537,18 +16534,18 @@
         <v>187</v>
       </c>
       <c r="G556" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="557" spans="1:7">
       <c r="A557" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B557" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C557" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D557" t="s">
         <v>25</v>
@@ -16557,21 +16554,21 @@
         <v>69</v>
       </c>
       <c r="F557" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="G557" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="558" spans="1:7">
       <c r="A558" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B558" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C558" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D558" t="s">
         <v>57</v>
@@ -16583,15 +16580,15 @@
         <v>187</v>
       </c>
       <c r="G558" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="559" spans="1:7">
       <c r="A559" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B559" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C559" t="s">
         <v>312</v>
@@ -16603,10 +16600,10 @@
         <v>11</v>
       </c>
       <c r="F559" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G559" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="560" spans="1:7">
@@ -16629,15 +16626,15 @@
         <v>53</v>
       </c>
       <c r="G560" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="561" spans="1:7">
       <c r="A561" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B561" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C561" t="s">
         <v>309</v>
@@ -16652,12 +16649,12 @@
         <v>53</v>
       </c>
       <c r="G561" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="562" spans="1:7">
       <c r="A562" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B562" t="s">
         <v>8</v>
@@ -16672,15 +16669,15 @@
         <v>20</v>
       </c>
       <c r="F562" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G562" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="563" spans="1:7">
       <c r="A563" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B563" t="s">
         <v>37</v>
@@ -16698,15 +16695,15 @@
         <v>53</v>
       </c>
       <c r="G563" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="564" spans="1:7">
       <c r="A564" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B564" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C564" t="s">
         <v>321</v>
@@ -16721,15 +16718,15 @@
         <v>39</v>
       </c>
       <c r="G564" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="565" spans="1:7">
       <c r="A565" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B565" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C565" t="s">
         <v>240</v>
@@ -16744,17 +16741,17 @@
         <v>53</v>
       </c>
       <c r="G565" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="566" spans="1:7">
       <c r="A566" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B566" t="s">
-        <v>822</v>
-      </c>
-      <c r="C566" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="C566" t="s">
         <v>46</v>
       </c>
       <c r="D566" t="s">
@@ -16767,12 +16764,12 @@
         <v>53</v>
       </c>
       <c r="G566" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="567" spans="1:7">
       <c r="A567" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B567" t="s">
         <v>8</v>
@@ -16787,18 +16784,18 @@
         <v>44</v>
       </c>
       <c r="F567" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G567" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="568" spans="1:7">
       <c r="A568" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B568" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C568" t="s">
         <v>309</v>
@@ -16810,15 +16807,15 @@
         <v>44</v>
       </c>
       <c r="F568" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="G568" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="569" spans="1:7">
       <c r="A569" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B569" t="s">
         <v>64</v>
@@ -16836,12 +16833,12 @@
         <v>53</v>
       </c>
       <c r="G569" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="570" spans="1:7">
       <c r="A570" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B570" t="s">
         <v>64</v>
@@ -16859,12 +16856,12 @@
         <v>53</v>
       </c>
       <c r="G570" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="571" spans="1:7">
       <c r="A571" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B571" t="s">
         <v>37</v>
@@ -16882,15 +16879,15 @@
         <v>53</v>
       </c>
       <c r="G571" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="572" spans="1:7">
       <c r="A572" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B572" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C572" t="s">
         <v>334</v>
@@ -16905,7 +16902,7 @@
         <v>53</v>
       </c>
       <c r="G572" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="573" spans="1:7">
@@ -16913,7 +16910,7 @@
         <v>342</v>
       </c>
       <c r="B573" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C573" t="s">
         <v>209</v>
@@ -16928,15 +16925,15 @@
         <v>53</v>
       </c>
       <c r="G573" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="574" spans="1:7">
       <c r="A574" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B574" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C574" t="s">
         <v>114</v>
@@ -16951,17 +16948,17 @@
         <v>53</v>
       </c>
       <c r="G574" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="575" spans="1:7">
       <c r="A575" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B575" t="s">
-        <v>836</v>
-      </c>
-      <c r="C575" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="C575" t="s">
         <v>46</v>
       </c>
       <c r="D575" t="s">
@@ -16974,17 +16971,17 @@
         <v>53</v>
       </c>
       <c r="G575" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="576" spans="1:7">
       <c r="A576" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B576" t="s">
         <v>64</v>
       </c>
-      <c r="C576" s="1" t="s">
+      <c r="C576" t="s">
         <v>46</v>
       </c>
       <c r="D576" t="s">
@@ -16997,18 +16994,18 @@
         <v>210</v>
       </c>
       <c r="G576" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="577" spans="1:7">
       <c r="A577" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B577" t="s">
         <v>8</v>
       </c>
       <c r="C577" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D577" t="s">
         <v>10</v>
@@ -17017,20 +17014,20 @@
         <v>11</v>
       </c>
       <c r="F577" t="s">
+        <v>840</v>
+      </c>
+      <c r="G577" t="s">
         <v>839</v>
-      </c>
-      <c r="G577" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="578" spans="1:7">
       <c r="A578" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B578" t="s">
         <v>8</v>
       </c>
-      <c r="C578" s="1" t="s">
+      <c r="C578" t="s">
         <v>46</v>
       </c>
       <c r="D578" t="s">
@@ -17040,21 +17037,21 @@
         <v>11</v>
       </c>
       <c r="F578" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G578" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="579" spans="1:7">
       <c r="A579" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B579" t="s">
         <v>8</v>
       </c>
       <c r="C579" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D579" t="s">
         <v>14</v>
@@ -17063,21 +17060,21 @@
         <v>11</v>
       </c>
       <c r="F579" t="s">
+        <v>840</v>
+      </c>
+      <c r="G579" t="s">
         <v>839</v>
-      </c>
-      <c r="G579" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="580" spans="1:7">
       <c r="A580" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B580" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C580" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D580" t="s">
         <v>21</v>
@@ -17089,15 +17086,15 @@
         <v>172</v>
       </c>
       <c r="G580" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="581" spans="1:7">
       <c r="A581" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B581" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C581" t="s">
         <v>77</v>
@@ -17112,15 +17109,15 @@
         <v>210</v>
       </c>
       <c r="G581" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="582" spans="1:7">
       <c r="A582" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B582" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C582" t="s">
         <v>117</v>
@@ -17135,17 +17132,17 @@
         <v>172</v>
       </c>
       <c r="G582" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="583" spans="1:7">
       <c r="A583" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B583" t="s">
-        <v>844</v>
-      </c>
-      <c r="C583" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="C583" t="s">
         <v>46</v>
       </c>
       <c r="D583" t="s">
@@ -17158,17 +17155,17 @@
         <v>172</v>
       </c>
       <c r="G583" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="584" spans="1:7">
       <c r="A584" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B584" t="s">
-        <v>844</v>
-      </c>
-      <c r="C584" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="C584" t="s">
         <v>46</v>
       </c>
       <c r="D584" t="s">
@@ -17181,17 +17178,17 @@
         <v>172</v>
       </c>
       <c r="G584" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="585" spans="1:7">
       <c r="A585" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B585" t="s">
-        <v>844</v>
-      </c>
-      <c r="C585" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="C585" t="s">
         <v>46</v>
       </c>
       <c r="D585" t="s">
@@ -17204,15 +17201,15 @@
         <v>172</v>
       </c>
       <c r="G585" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="586" spans="1:7">
       <c r="A586" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B586" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C586" t="s">
         <v>77</v>
@@ -17227,7 +17224,7 @@
         <v>210</v>
       </c>
       <c r="G586" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="587" spans="1:7">
@@ -17235,7 +17232,7 @@
         <v>120</v>
       </c>
       <c r="B587" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C587" t="s">
         <v>77</v>
@@ -17250,15 +17247,15 @@
         <v>137</v>
       </c>
       <c r="G587" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="588" spans="1:7">
       <c r="A588" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B588" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C588" t="s">
         <v>77</v>
@@ -17273,15 +17270,15 @@
         <v>172</v>
       </c>
       <c r="G588" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="589" spans="1:7">
       <c r="A589" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B589" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C589" t="s">
         <v>370</v>
@@ -17296,15 +17293,15 @@
         <v>210</v>
       </c>
       <c r="G589" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="590" spans="1:7">
       <c r="A590" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B590" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C590" t="s">
         <v>107</v>
@@ -17319,15 +17316,15 @@
         <v>210</v>
       </c>
       <c r="G590" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="591" spans="1:7">
       <c r="A591" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B591" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C591" t="s">
         <v>107</v>
@@ -17342,15 +17339,15 @@
         <v>210</v>
       </c>
       <c r="G591" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="592" spans="1:7">
       <c r="A592" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B592" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C592" t="s">
         <v>250</v>
@@ -17362,20 +17359,20 @@
         <v>20</v>
       </c>
       <c r="F592" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="G592" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="593" spans="1:7">
       <c r="A593" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B593" t="s">
-        <v>853</v>
-      </c>
-      <c r="C593" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="C593" t="s">
         <v>46</v>
       </c>
       <c r="D593" t="s">
@@ -17385,18 +17382,18 @@
         <v>20</v>
       </c>
       <c r="F593" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="G593" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="594" spans="1:7">
       <c r="A594" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B594" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C594" t="s">
         <v>250</v>
@@ -17408,20 +17405,20 @@
         <v>20</v>
       </c>
       <c r="F594" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="G594" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="595" spans="1:7">
       <c r="A595" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B595" t="s">
-        <v>857</v>
-      </c>
-      <c r="C595" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="C595" t="s">
         <v>46</v>
       </c>
       <c r="D595" t="s">
@@ -17431,20 +17428,20 @@
         <v>20</v>
       </c>
       <c r="F595" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="G595" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="596" spans="1:7">
       <c r="A596" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B596" t="s">
-        <v>853</v>
-      </c>
-      <c r="C596" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="C596" t="s">
         <v>46</v>
       </c>
       <c r="D596" t="s">
@@ -17454,18 +17451,18 @@
         <v>20</v>
       </c>
       <c r="F596" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="G596" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="597" spans="1:7">
       <c r="A597" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B597" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C597" t="s">
         <v>42</v>
@@ -17477,20 +17474,20 @@
         <v>20</v>
       </c>
       <c r="F597" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="G597" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="598" spans="1:7">
       <c r="A598" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B598" t="s">
-        <v>857</v>
-      </c>
-      <c r="C598" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="C598" t="s">
         <v>46</v>
       </c>
       <c r="D598" t="s">
@@ -17500,20 +17497,20 @@
         <v>20</v>
       </c>
       <c r="F598" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="G598" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="599" spans="1:7">
       <c r="A599" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B599" t="s">
         <v>8</v>
       </c>
-      <c r="C599" s="1" t="s">
+      <c r="C599" t="s">
         <v>46</v>
       </c>
       <c r="D599" t="s">
@@ -17523,20 +17520,20 @@
         <v>20</v>
       </c>
       <c r="F599" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G599" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="600" spans="1:7">
       <c r="A600" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B600" t="s">
-        <v>857</v>
-      </c>
-      <c r="C600" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="C600" t="s">
         <v>46</v>
       </c>
       <c r="D600" t="s">
@@ -17546,18 +17543,18 @@
         <v>20</v>
       </c>
       <c r="F600" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="G600" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="601" spans="1:7">
       <c r="A601" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B601" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C601" t="s">
         <v>186</v>
@@ -17569,20 +17566,20 @@
         <v>20</v>
       </c>
       <c r="F601" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="G601" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="602" spans="1:7">
       <c r="A602" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B602" t="s">
         <v>8</v>
       </c>
-      <c r="C602" s="1" t="s">
+      <c r="C602" t="s">
         <v>46</v>
       </c>
       <c r="D602" t="s">
@@ -17592,20 +17589,20 @@
         <v>20</v>
       </c>
       <c r="F602" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G602" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="603" spans="1:7">
       <c r="A603" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B603" t="s">
-        <v>857</v>
-      </c>
-      <c r="C603" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="C603" t="s">
         <v>46</v>
       </c>
       <c r="D603" t="s">
@@ -17615,18 +17612,18 @@
         <v>20</v>
       </c>
       <c r="F603" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G603" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="604" spans="1:7">
       <c r="A604" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B604" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C604" t="s">
         <v>186</v>
@@ -17638,15 +17635,15 @@
         <v>20</v>
       </c>
       <c r="F604" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="G604" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="605" spans="1:7">
       <c r="A605" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B605" t="s">
         <v>37</v>
@@ -17664,15 +17661,15 @@
         <v>137</v>
       </c>
       <c r="G605" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="606" spans="1:7">
       <c r="A606" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B606" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C606" t="s">
         <v>77</v>
@@ -17687,18 +17684,18 @@
         <v>172</v>
       </c>
       <c r="G606" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="607" spans="1:7">
       <c r="A607" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B607" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C607" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D607" t="s">
         <v>25</v>
@@ -17710,18 +17707,18 @@
         <v>172</v>
       </c>
       <c r="G607" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="608" spans="1:7">
       <c r="A608" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B608" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C608" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D608" t="s">
         <v>25</v>
@@ -17730,20 +17727,20 @@
         <v>44</v>
       </c>
       <c r="F608" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="G608" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="609" spans="1:7">
       <c r="A609" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B609" t="s">
-        <v>850</v>
-      </c>
-      <c r="C609" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="C609" t="s">
         <v>46</v>
       </c>
       <c r="D609" t="s">
@@ -17753,21 +17750,21 @@
         <v>44</v>
       </c>
       <c r="F609" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="G609" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="610" spans="1:7">
       <c r="A610" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B610" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C610" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D610" t="s">
         <v>32</v>
@@ -17779,18 +17776,18 @@
         <v>210</v>
       </c>
       <c r="G610" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="611" spans="1:7">
       <c r="A611" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B611" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C611" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D611" t="s">
         <v>32</v>
@@ -17799,20 +17796,20 @@
         <v>44</v>
       </c>
       <c r="F611" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="G611" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="612" spans="1:7">
       <c r="A612" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B612" t="s">
-        <v>850</v>
-      </c>
-      <c r="C612" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="C612" t="s">
         <v>46</v>
       </c>
       <c r="D612" t="s">
@@ -17822,10 +17819,10 @@
         <v>44</v>
       </c>
       <c r="F612" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="G612" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="613" spans="1:7">
@@ -17848,17 +17845,17 @@
         <v>137</v>
       </c>
       <c r="G613" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="614" spans="1:7">
       <c r="A614" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B614" t="s">
-        <v>866</v>
-      </c>
-      <c r="C614" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="C614" t="s">
         <v>46</v>
       </c>
       <c r="D614" t="s">
@@ -17871,15 +17868,15 @@
         <v>210</v>
       </c>
       <c r="G614" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="615" spans="1:7">
       <c r="A615" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B615" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C615" t="s">
         <v>107</v>
@@ -17894,18 +17891,18 @@
         <v>172</v>
       </c>
       <c r="G615" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="616" spans="1:7">
       <c r="A616" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B616" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C616" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D616" t="s">
         <v>43</v>
@@ -17917,15 +17914,15 @@
         <v>137</v>
       </c>
       <c r="G616" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="617" spans="1:7">
       <c r="A617" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B617" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C617" t="s">
         <v>77</v>
@@ -17940,15 +17937,15 @@
         <v>210</v>
       </c>
       <c r="G617" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="618" spans="1:7">
       <c r="A618" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B618" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C618" t="s">
         <v>186</v>
@@ -17963,15 +17960,15 @@
         <v>210</v>
       </c>
       <c r="G618" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="619" spans="1:7">
       <c r="A619" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B619" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C619" t="s">
         <v>186</v>
@@ -17986,15 +17983,15 @@
         <v>172</v>
       </c>
       <c r="G619" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="620" spans="1:7">
       <c r="A620" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B620" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C620" t="s">
         <v>92</v>
@@ -18006,20 +18003,20 @@
         <v>59</v>
       </c>
       <c r="F620" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G620" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="621" spans="1:7">
       <c r="A621" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B621" t="s">
-        <v>877</v>
-      </c>
-      <c r="C621" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="C621" t="s">
         <v>46</v>
       </c>
       <c r="D621" t="s">
@@ -18032,18 +18029,18 @@
         <v>210</v>
       </c>
       <c r="G621" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="622" spans="1:7">
       <c r="A622" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B622" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C622" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D622" t="s">
         <v>32</v>
@@ -18055,15 +18052,15 @@
         <v>172</v>
       </c>
       <c r="G622" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="623" spans="1:7">
       <c r="A623" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B623" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C623" t="s">
         <v>92</v>
@@ -18075,18 +18072,18 @@
         <v>59</v>
       </c>
       <c r="F623" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G623" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="624" spans="1:7">
       <c r="A624" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B624" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C624" t="s">
         <v>74</v>
@@ -18101,7 +18098,7 @@
         <v>137</v>
       </c>
       <c r="G624" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="625" spans="1:7">
@@ -18109,7 +18106,7 @@
         <v>81</v>
       </c>
       <c r="B625" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C625" t="s">
         <v>370</v>
@@ -18124,12 +18121,12 @@
         <v>137</v>
       </c>
       <c r="G625" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="626" spans="1:7">
       <c r="A626" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B626" t="s">
         <v>37</v>
@@ -18147,15 +18144,15 @@
         <v>137</v>
       </c>
       <c r="G626" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="627" spans="1:7">
       <c r="A627" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B627" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C627" t="s">
         <v>42</v>
@@ -18167,20 +18164,20 @@
         <v>69</v>
       </c>
       <c r="F627" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="G627" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="628" spans="1:7">
       <c r="A628" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B628" t="s">
-        <v>877</v>
-      </c>
-      <c r="C628" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="C628" t="s">
         <v>46</v>
       </c>
       <c r="D628" t="s">
@@ -18193,18 +18190,18 @@
         <v>210</v>
       </c>
       <c r="G628" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="629" spans="1:7">
       <c r="A629" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B629" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C629" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D629" t="s">
         <v>25</v>
@@ -18216,12 +18213,12 @@
         <v>172</v>
       </c>
       <c r="G629" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="630" spans="1:7">
       <c r="A630" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B630" t="s">
         <v>64</v>
@@ -18239,17 +18236,17 @@
         <v>210</v>
       </c>
       <c r="G630" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="631" spans="1:7">
       <c r="A631" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B631" t="s">
-        <v>877</v>
-      </c>
-      <c r="C631" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="C631" t="s">
         <v>46</v>
       </c>
       <c r="D631" t="s">
@@ -18262,17 +18259,17 @@
         <v>172</v>
       </c>
       <c r="G631" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="632" spans="1:7">
       <c r="A632" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B632" t="s">
         <v>64</v>
       </c>
-      <c r="C632" s="1" t="s">
+      <c r="C632" t="s">
         <v>46</v>
       </c>
       <c r="D632" t="s">
@@ -18285,15 +18282,15 @@
         <v>172</v>
       </c>
       <c r="G632" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="633" spans="1:7">
       <c r="A633" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B633" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C633" t="s">
         <v>77</v>
@@ -18308,18 +18305,18 @@
         <v>210</v>
       </c>
       <c r="G633" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="634" spans="1:7">
       <c r="A634" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B634" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C634" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D634" t="s">
         <v>57</v>
@@ -18331,12 +18328,12 @@
         <v>137</v>
       </c>
       <c r="G634" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="635" spans="1:7">
       <c r="A635" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B635" t="s">
         <v>64</v>
@@ -18354,12 +18351,12 @@
         <v>316</v>
       </c>
       <c r="G635" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="636" spans="1:7">
       <c r="A636" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B636" t="s">
         <v>64</v>
@@ -18377,12 +18374,12 @@
         <v>332</v>
       </c>
       <c r="G636" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="637" spans="1:7">
       <c r="A637" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B637" t="s">
         <v>37</v>
@@ -18400,12 +18397,12 @@
         <v>53</v>
       </c>
       <c r="G637" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="638" spans="1:7">
       <c r="A638" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B638" t="s">
         <v>64</v>
@@ -18423,12 +18420,12 @@
         <v>53</v>
       </c>
       <c r="G638" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="639" spans="1:7">
       <c r="A639" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B639" t="s">
         <v>37</v>
@@ -18446,12 +18443,12 @@
         <v>332</v>
       </c>
       <c r="G639" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="640" spans="1:7">
       <c r="A640" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B640" t="s">
         <v>64</v>
@@ -18469,12 +18466,12 @@
         <v>244</v>
       </c>
       <c r="G640" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="641" spans="1:7">
       <c r="A641" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B641" t="s">
         <v>64</v>
@@ -18492,18 +18489,18 @@
         <v>332</v>
       </c>
       <c r="G641" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="642" spans="1:7">
       <c r="A642" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B642" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C642" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D642" t="s">
         <v>17</v>
@@ -18515,12 +18512,12 @@
         <v>39</v>
       </c>
       <c r="G642" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="643" spans="1:7">
       <c r="A643" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B643" t="s">
         <v>64</v>
@@ -18538,12 +18535,12 @@
         <v>244</v>
       </c>
       <c r="G643" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="644" spans="1:7">
       <c r="A644" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B644" t="s">
         <v>64</v>
@@ -18561,12 +18558,12 @@
         <v>332</v>
       </c>
       <c r="G644" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="645" spans="1:7">
       <c r="A645" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B645" t="s">
         <v>37</v>
@@ -18584,12 +18581,12 @@
         <v>332</v>
       </c>
       <c r="G645" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="646" spans="1:7">
       <c r="A646" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B646" t="s">
         <v>64</v>
@@ -18607,12 +18604,12 @@
         <v>244</v>
       </c>
       <c r="G646" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="647" spans="1:7">
       <c r="A647" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B647" t="s">
         <v>37</v>
@@ -18630,12 +18627,12 @@
         <v>332</v>
       </c>
       <c r="G647" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="648" spans="1:7">
       <c r="A648" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B648" t="s">
         <v>37</v>
@@ -18653,12 +18650,12 @@
         <v>235</v>
       </c>
       <c r="G648" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="649" spans="1:7">
       <c r="A649" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B649" t="s">
         <v>64</v>
@@ -18676,12 +18673,12 @@
         <v>332</v>
       </c>
       <c r="G649" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="650" spans="1:7">
       <c r="A650" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B650" t="s">
         <v>64</v>
@@ -18699,12 +18696,12 @@
         <v>45</v>
       </c>
       <c r="G650" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="651" spans="1:7">
       <c r="A651" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B651" t="s">
         <v>8</v>
@@ -18719,15 +18716,15 @@
         <v>59</v>
       </c>
       <c r="F651" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="G651" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="652" spans="1:7">
       <c r="A652" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B652" t="s">
         <v>8</v>
@@ -18742,15 +18739,15 @@
         <v>59</v>
       </c>
       <c r="F652" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="G652" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="653" spans="1:7">
       <c r="A653" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B653" t="s">
         <v>37</v>
@@ -18768,12 +18765,12 @@
         <v>332</v>
       </c>
       <c r="G653" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="654" spans="1:7">
       <c r="A654" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B654" t="s">
         <v>37</v>
@@ -18791,12 +18788,12 @@
         <v>332</v>
       </c>
       <c r="G654" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="655" spans="1:7">
       <c r="A655" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B655" t="s">
         <v>8</v>
@@ -18811,15 +18808,15 @@
         <v>69</v>
       </c>
       <c r="F655" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="G655" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="656" spans="1:7">
       <c r="A656" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B656" t="s">
         <v>64</v>
@@ -18837,18 +18834,18 @@
         <v>244</v>
       </c>
       <c r="G656" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="657" spans="1:7">
       <c r="A657" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B657" t="s">
         <v>8</v>
       </c>
       <c r="C657" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D657" t="s">
         <v>87</v>
@@ -18857,20 +18854,20 @@
         <v>69</v>
       </c>
       <c r="F657" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="G657" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="658" spans="1:7">
       <c r="A658" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B658" t="s">
         <v>8</v>
       </c>
-      <c r="C658" s="1" t="s">
+      <c r="C658" t="s">
         <v>46</v>
       </c>
       <c r="D658" t="s">
@@ -18883,18 +18880,18 @@
         <v>95</v>
       </c>
       <c r="G658" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="659" spans="1:7">
       <c r="A659" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B659" t="s">
         <v>8</v>
       </c>
       <c r="C659" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D659" t="s">
         <v>138</v>
@@ -18903,20 +18900,20 @@
         <v>69</v>
       </c>
       <c r="F659" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="G659" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="660" spans="1:7">
       <c r="A660" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B660" t="s">
         <v>8</v>
       </c>
-      <c r="C660" s="1" t="s">
+      <c r="C660" t="s">
         <v>46</v>
       </c>
       <c r="D660" t="s">
@@ -18929,12 +18926,12 @@
         <v>95</v>
       </c>
       <c r="G660" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="661" spans="1:7">
       <c r="A661" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B661" t="s">
         <v>37</v>
@@ -18952,12 +18949,12 @@
         <v>332</v>
       </c>
       <c r="G661" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="662" spans="1:7">
       <c r="A662" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B662" t="s">
         <v>8</v>
@@ -18972,15 +18969,15 @@
         <v>69</v>
       </c>
       <c r="F662" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="G662" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="663" spans="1:7">
       <c r="A663" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B663" t="s">
         <v>64</v>
@@ -18998,7 +18995,7 @@
         <v>244</v>
       </c>
       <c r="G663" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
   </sheetData>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -3730,9 +3730,6 @@
   <sheetPr/>
   <dimension ref="A1:G663"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
-  <cols>
-    <col min="3" max="3" width="32.2857142857143" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
@@ -7224,7 +7221,7 @@
         <v>59</v>
       </c>
       <c r="F152" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="G152" t="s">
         <v>236</v>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7020"/>
+    <workbookView windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$665</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4641" uniqueCount="907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4655" uniqueCount="909">
   <si>
     <t>Enseignements</t>
   </si>
@@ -563,7 +566,7 @@
     <t>TP- schéma électriques industrielles</t>
   </si>
   <si>
-    <t>M.BRAHAMI MOSTEFA</t>
+    <t>BRAHAMI MOHAMED NADJIB</t>
   </si>
   <si>
     <t>Cours-Anglais technique en relation ave la spéialité</t>
@@ -989,21 +992,21 @@
     <t>NEMMICH SAID</t>
   </si>
   <si>
+    <t>TD-Diagnostic et maintenance des systèmes électriques</t>
+  </si>
+  <si>
+    <t>ZEBLAH ABDELKADER</t>
+  </si>
+  <si>
+    <t>Cours-Diagnostic et maintenance des systèmes électriques</t>
+  </si>
+  <si>
     <t>TD-Intégration des énergies renouvelables aux réseaux</t>
   </si>
   <si>
     <t>MEKHFI KHALIDA</t>
   </si>
   <si>
-    <t>TD-Diagnostic et maintenance des systèmes électriques</t>
-  </si>
-  <si>
-    <t>ZEBLAH ABDELKADER</t>
-  </si>
-  <si>
-    <t>Cours-Diagnostic et maintenance des systèmes électriques</t>
-  </si>
-  <si>
     <t>TP-Dimensionnement des systèmes à énergies renouvelables</t>
   </si>
   <si>
@@ -2462,15 +2465,15 @@
     <t>Cours-EAD-RDCM-M2RE</t>
   </si>
   <si>
+    <t>TD-Intégration des ressoures renouvelables aux réseaux électriques</t>
+  </si>
+  <si>
+    <t>TD-IRRRE-M2RE</t>
+  </si>
+  <si>
     <t>Cours-Intégration des ressources renouvelables aux réseaux électriques</t>
   </si>
   <si>
-    <t>TD-Intégration des ressoures renouvelables aux réseaux électriques</t>
-  </si>
-  <si>
-    <t>TD-IRRRE-M2RE</t>
-  </si>
-  <si>
     <t>TP-Réseaux électriques industriels-G2</t>
   </si>
   <si>
@@ -2702,10 +2705,16 @@
     <t>HADJERI Samir</t>
   </si>
   <si>
+    <t>TP-Réseaux électriques-SG12/SG22/SG32</t>
+  </si>
+  <si>
     <t>TP-Schémas électriques-SG11/SG21/SG31</t>
   </si>
   <si>
     <t>Labo Schémas</t>
+  </si>
+  <si>
+    <t>TP-Réseaux électriques-SG11/SG21/SG31</t>
   </si>
   <si>
     <t>TP-Schémas électriques-SG12/SG22/SG32</t>
@@ -3716,7 +3725,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G663"/>
+  <dimension ref="A1:G665"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -8100,7 +8109,7 @@
         <v>321</v>
       </c>
       <c r="D191" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="E191" t="s">
         <v>44</v>
@@ -8117,13 +8126,13 @@
         <v>322</v>
       </c>
       <c r="B192" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="C192" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D192" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="E192" t="s">
         <v>44</v>
@@ -8137,16 +8146,16 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" t="s">
+        <v>323</v>
+      </c>
+      <c r="B193" t="s">
+        <v>64</v>
+      </c>
+      <c r="C193" t="s">
         <v>324</v>
       </c>
-      <c r="B193" t="s">
-        <v>37</v>
-      </c>
-      <c r="C193" t="s">
-        <v>323</v>
-      </c>
       <c r="D193" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="E193" t="s">
         <v>44</v>
@@ -8189,7 +8198,7 @@
         <v>328</v>
       </c>
       <c r="C195" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D195" t="s">
         <v>57</v>
@@ -13519,19 +13528,19 @@
     </row>
     <row r="427" spans="1:7">
       <c r="A427" t="s">
-        <v>635</v>
+        <v>245</v>
       </c>
       <c r="B427" t="s">
-        <v>636</v>
+        <v>64</v>
       </c>
       <c r="C427" t="s">
-        <v>195</v>
+        <v>247</v>
       </c>
       <c r="D427" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E427" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="F427" t="s">
         <v>625</v>
@@ -13542,22 +13551,22 @@
     </row>
     <row r="428" spans="1:7">
       <c r="A428" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B428" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C428" t="s">
-        <v>319</v>
+        <v>195</v>
       </c>
       <c r="D428" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="E428" t="s">
         <v>44</v>
       </c>
       <c r="F428" t="s">
-        <v>639</v>
+        <v>625</v>
       </c>
       <c r="G428" t="s">
         <v>626</v>
@@ -13565,7 +13574,7 @@
     </row>
     <row r="429" spans="1:7">
       <c r="A429" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B429" t="s">
         <v>638</v>
@@ -13574,7 +13583,7 @@
         <v>319</v>
       </c>
       <c r="D429" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E429" t="s">
         <v>44</v>
@@ -13588,22 +13597,22 @@
     </row>
     <row r="430" spans="1:7">
       <c r="A430" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B430" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="C430" t="s">
-        <v>590</v>
+        <v>319</v>
       </c>
       <c r="D430" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E430" t="s">
         <v>44</v>
       </c>
       <c r="F430" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="G430" t="s">
         <v>626</v>
@@ -13611,16 +13620,16 @@
     </row>
     <row r="431" spans="1:7">
       <c r="A431" t="s">
-        <v>588</v>
+        <v>641</v>
       </c>
       <c r="B431" t="s">
         <v>642</v>
       </c>
       <c r="C431" t="s">
-        <v>97</v>
+        <v>590</v>
       </c>
       <c r="D431" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="E431" t="s">
         <v>44</v>
@@ -13634,22 +13643,22 @@
     </row>
     <row r="432" spans="1:7">
       <c r="A432" t="s">
-        <v>245</v>
+        <v>588</v>
       </c>
       <c r="B432" t="s">
-        <v>64</v>
+        <v>642</v>
       </c>
       <c r="C432" t="s">
-        <v>247</v>
+        <v>97</v>
       </c>
       <c r="D432" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="E432" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="F432" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="G432" t="s">
         <v>626</v>
@@ -15388,7 +15397,7 @@
         <v>8</v>
       </c>
       <c r="C508" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D508" t="s">
         <v>87</v>
@@ -15543,22 +15552,22 @@
     </row>
     <row r="515" spans="1:7">
       <c r="A515" t="s">
-        <v>320</v>
+        <v>726</v>
       </c>
       <c r="B515" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="C515" t="s">
-        <v>321</v>
+        <v>46</v>
       </c>
       <c r="D515" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="E515" t="s">
         <v>44</v>
       </c>
       <c r="F515" t="s">
-        <v>314</v>
+        <v>727</v>
       </c>
       <c r="G515" t="s">
         <v>719</v>
@@ -15566,16 +15575,16 @@
     </row>
     <row r="516" spans="1:7">
       <c r="A516" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B516" t="s">
         <v>8</v>
       </c>
       <c r="C516" t="s">
-        <v>46</v>
+        <v>334</v>
       </c>
       <c r="D516" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="E516" t="s">
         <v>44</v>
@@ -15589,22 +15598,22 @@
     </row>
     <row r="517" spans="1:7">
       <c r="A517" t="s">
-        <v>728</v>
+        <v>323</v>
       </c>
       <c r="B517" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="C517" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="D517" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="E517" t="s">
         <v>44</v>
       </c>
       <c r="F517" t="s">
-        <v>727</v>
+        <v>314</v>
       </c>
       <c r="G517" t="s">
         <v>719</v>
@@ -15618,7 +15627,7 @@
         <v>730</v>
       </c>
       <c r="C518" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D518" t="s">
         <v>17</v>
@@ -15641,7 +15650,7 @@
         <v>731</v>
       </c>
       <c r="C519" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D519" t="s">
         <v>57</v>
@@ -16696,13 +16705,13 @@
         <v>811</v>
       </c>
       <c r="B565" t="s">
-        <v>37</v>
+        <v>812</v>
       </c>
       <c r="C565" t="s">
         <v>46</v>
       </c>
       <c r="D565" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E565" t="s">
         <v>44</v>
@@ -16716,16 +16725,16 @@
     </row>
     <row r="566" spans="1:7">
       <c r="A566" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B566" t="s">
-        <v>813</v>
+        <v>37</v>
       </c>
       <c r="C566" t="s">
         <v>46</v>
       </c>
       <c r="D566" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E566" t="s">
         <v>44</v>
@@ -18677,7 +18686,7 @@
         <v>8</v>
       </c>
       <c r="C651" t="s">
-        <v>178</v>
+        <v>890</v>
       </c>
       <c r="D651" t="s">
         <v>87</v>
@@ -18686,7 +18695,7 @@
         <v>59</v>
       </c>
       <c r="F651" t="s">
-        <v>892</v>
+        <v>95</v>
       </c>
       <c r="G651" t="s">
         <v>879</v>
@@ -18694,7 +18703,7 @@
     </row>
     <row r="652" spans="1:7">
       <c r="A652" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B652" t="s">
         <v>8</v>
@@ -18703,13 +18712,13 @@
         <v>178</v>
       </c>
       <c r="D652" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="E652" t="s">
         <v>59</v>
       </c>
       <c r="F652" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="G652" t="s">
         <v>879</v>
@@ -18720,19 +18729,19 @@
         <v>894</v>
       </c>
       <c r="B653" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C653" t="s">
-        <v>208</v>
+        <v>890</v>
       </c>
       <c r="D653" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="E653" t="s">
         <v>59</v>
       </c>
       <c r="F653" t="s">
-        <v>329</v>
+        <v>95</v>
       </c>
       <c r="G653" t="s">
         <v>879</v>
@@ -18743,19 +18752,19 @@
         <v>895</v>
       </c>
       <c r="B654" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C654" t="s">
-        <v>890</v>
+        <v>178</v>
       </c>
       <c r="D654" t="s">
-        <v>18</v>
+        <v>138</v>
       </c>
       <c r="E654" t="s">
         <v>59</v>
       </c>
       <c r="F654" t="s">
-        <v>329</v>
+        <v>893</v>
       </c>
       <c r="G654" t="s">
         <v>879</v>
@@ -18766,19 +18775,19 @@
         <v>896</v>
       </c>
       <c r="B655" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C655" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="D655" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E655" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F655" t="s">
-        <v>897</v>
+        <v>329</v>
       </c>
       <c r="G655" t="s">
         <v>879</v>
@@ -18786,22 +18795,22 @@
     </row>
     <row r="656" spans="1:7">
       <c r="A656" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B656" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="C656" t="s">
         <v>890</v>
       </c>
       <c r="D656" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E656" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F656" t="s">
-        <v>243</v>
+        <v>329</v>
       </c>
       <c r="G656" t="s">
         <v>879</v>
@@ -18809,22 +18818,22 @@
     </row>
     <row r="657" spans="1:7">
       <c r="A657" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B657" t="s">
         <v>8</v>
       </c>
       <c r="C657" t="s">
-        <v>470</v>
+        <v>188</v>
       </c>
       <c r="D657" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="E657" t="s">
         <v>69</v>
       </c>
       <c r="F657" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G657" t="s">
         <v>879</v>
@@ -18832,22 +18841,22 @@
     </row>
     <row r="658" spans="1:7">
       <c r="A658" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B658" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="C658" t="s">
-        <v>46</v>
+        <v>890</v>
       </c>
       <c r="D658" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="E658" t="s">
         <v>69</v>
       </c>
       <c r="F658" t="s">
-        <v>95</v>
+        <v>243</v>
       </c>
       <c r="G658" t="s">
         <v>879</v>
@@ -18855,7 +18864,7 @@
     </row>
     <row r="659" spans="1:7">
       <c r="A659" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B659" t="s">
         <v>8</v>
@@ -18864,13 +18873,13 @@
         <v>470</v>
       </c>
       <c r="D659" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="E659" t="s">
         <v>69</v>
       </c>
       <c r="F659" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="G659" t="s">
         <v>879</v>
@@ -18887,7 +18896,7 @@
         <v>46</v>
       </c>
       <c r="D660" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="E660" t="s">
         <v>69</v>
@@ -18901,22 +18910,22 @@
     </row>
     <row r="661" spans="1:7">
       <c r="A661" t="s">
-        <v>895</v>
+        <v>904</v>
       </c>
       <c r="B661" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C661" t="s">
-        <v>890</v>
+        <v>470</v>
       </c>
       <c r="D661" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="E661" t="s">
         <v>69</v>
       </c>
       <c r="F661" t="s">
-        <v>329</v>
+        <v>902</v>
       </c>
       <c r="G661" t="s">
         <v>879</v>
@@ -18924,22 +18933,22 @@
     </row>
     <row r="662" spans="1:7">
       <c r="A662" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B662" t="s">
         <v>8</v>
       </c>
       <c r="C662" t="s">
-        <v>188</v>
+        <v>46</v>
       </c>
       <c r="D662" t="s">
-        <v>18</v>
+        <v>138</v>
       </c>
       <c r="E662" t="s">
         <v>69</v>
       </c>
       <c r="F662" t="s">
-        <v>905</v>
+        <v>95</v>
       </c>
       <c r="G662" t="s">
         <v>879</v>
@@ -18947,28 +18956,77 @@
     </row>
     <row r="663" spans="1:7">
       <c r="A663" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="B663" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="C663" t="s">
         <v>890</v>
       </c>
       <c r="D663" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E663" t="s">
         <v>69</v>
       </c>
       <c r="F663" t="s">
-        <v>243</v>
+        <v>329</v>
       </c>
       <c r="G663" t="s">
         <v>879</v>
       </c>
     </row>
+    <row r="664" spans="1:7">
+      <c r="A664" t="s">
+        <v>906</v>
+      </c>
+      <c r="B664" t="s">
+        <v>8</v>
+      </c>
+      <c r="C664" t="s">
+        <v>188</v>
+      </c>
+      <c r="D664" t="s">
+        <v>18</v>
+      </c>
+      <c r="E664" t="s">
+        <v>69</v>
+      </c>
+      <c r="F664" t="s">
+        <v>907</v>
+      </c>
+      <c r="G664" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="665" spans="1:7">
+      <c r="A665" t="s">
+        <v>908</v>
+      </c>
+      <c r="B665" t="s">
+        <v>64</v>
+      </c>
+      <c r="C665" t="s">
+        <v>890</v>
+      </c>
+      <c r="D665" t="s">
+        <v>18</v>
+      </c>
+      <c r="E665" t="s">
+        <v>69</v>
+      </c>
+      <c r="F665" t="s">
+        <v>243</v>
+      </c>
+      <c r="G665" t="s">
+        <v>879</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G665" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -9,9 +9,6 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$665</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -185,6 +182,15 @@
     <t>AS18</t>
   </si>
   <si>
+    <t>TD</t>
+  </si>
+  <si>
+    <t>15h30 - 17h</t>
+  </si>
+  <si>
+    <t>AS3</t>
+  </si>
+  <si>
     <t>Cours-Éléments de Mécanique (Physique 1)</t>
   </si>
   <si>
@@ -224,12 +230,12 @@
     <t>TD-Structure de la matière</t>
   </si>
   <si>
-    <t>TD</t>
-  </si>
-  <si>
     <t>BADIS KARIMA</t>
   </si>
   <si>
+    <t>AS19</t>
+  </si>
+  <si>
     <t>G1 S0 / G2 S0</t>
   </si>
   <si>
@@ -446,9 +452,6 @@
     <t>Amphi 12</t>
   </si>
   <si>
-    <t>15h30 - 17h</t>
-  </si>
-  <si>
     <t>TP-Programmation python- G2 -</t>
   </si>
   <si>
@@ -548,9 +551,6 @@
     <t>MILOUA FETHI</t>
   </si>
   <si>
-    <t>AS19</t>
-  </si>
-  <si>
     <t>TD-Automates programmables industriels PLC</t>
   </si>
   <si>
@@ -701,9 +701,6 @@
     <t>FELLAH MOHAMMED KARIM</t>
   </si>
   <si>
-    <t>AS3</t>
-  </si>
-  <si>
     <t>TD- Asservissement 1</t>
   </si>
   <si>
@@ -1454,6 +1451,9 @@
     <t>Cours-PST-L2ELT</t>
   </si>
   <si>
+    <t>Amphi 07</t>
+  </si>
+  <si>
     <t>TD-Ondes et vibrations-G1</t>
   </si>
   <si>
@@ -1677,9 +1677,6 @@
   </si>
   <si>
     <t>Cours-Schémas et Appareillage électrique</t>
-  </si>
-  <si>
-    <t>Cours-S &amp; A</t>
   </si>
   <si>
     <t>TD-Systèmes Asservis-G2</t>
@@ -4170,19 +4167,19 @@
         <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
         <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="E20" t="s">
         <v>44</v>
       </c>
       <c r="F20" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -4190,10 +4187,10 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
         <v>42</v>
@@ -4205,7 +4202,7 @@
         <v>44</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
@@ -4213,16 +4210,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E22" t="s">
         <v>44</v>
@@ -4236,7 +4233,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
@@ -4248,7 +4245,7 @@
         <v>43</v>
       </c>
       <c r="E23" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F23" t="s">
         <v>26</v>
@@ -4259,19 +4256,19 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
         <v>21</v>
       </c>
       <c r="E24" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F24" t="s">
         <v>26</v>
@@ -4294,10 +4291,10 @@
         <v>25</v>
       </c>
       <c r="E25" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F25" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
@@ -4317,10 +4314,10 @@
         <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F26" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
@@ -4340,10 +4337,10 @@
         <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F27" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
@@ -4363,10 +4360,10 @@
         <v>25</v>
       </c>
       <c r="E28" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F28" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
@@ -4386,10 +4383,10 @@
         <v>25</v>
       </c>
       <c r="E29" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F29" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
@@ -4409,10 +4406,10 @@
         <v>25</v>
       </c>
       <c r="E30" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F30" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
@@ -4420,22 +4417,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D31" t="s">
         <v>35</v>
       </c>
       <c r="E31" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F31" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
@@ -4455,10 +4452,10 @@
         <v>18</v>
       </c>
       <c r="E32" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F32" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
@@ -4478,10 +4475,10 @@
         <v>18</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F33" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G33" t="s">
         <v>13</v>
@@ -4501,10 +4498,10 @@
         <v>18</v>
       </c>
       <c r="E34" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F34" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G34" t="s">
         <v>13</v>
@@ -4521,13 +4518,13 @@
         <v>46</v>
       </c>
       <c r="D35" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E35" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F35" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G35" t="s">
         <v>13</v>
@@ -4544,13 +4541,13 @@
         <v>46</v>
       </c>
       <c r="D36" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E36" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F36" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G36" t="s">
         <v>13</v>
@@ -4567,13 +4564,13 @@
         <v>46</v>
       </c>
       <c r="D37" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E37" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F37" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G37" t="s">
         <v>13</v>
@@ -4581,10 +4578,10 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C38" t="s">
         <v>49</v>
@@ -4593,7 +4590,7 @@
         <v>43</v>
       </c>
       <c r="E38" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F38" t="s">
         <v>45</v>
@@ -4604,19 +4601,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B39" t="s">
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D39" t="s">
         <v>14</v>
       </c>
       <c r="E39" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F39" t="s">
         <v>45</v>
@@ -4627,19 +4624,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B40" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C40" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D40" t="s">
         <v>25</v>
       </c>
       <c r="E40" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F40" t="s">
         <v>45</v>
@@ -4650,19 +4647,19 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C41" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D41" t="s">
         <v>32</v>
       </c>
       <c r="E41" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F41" t="s">
         <v>45</v>
@@ -4673,22 +4670,22 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B42" t="s">
         <v>37</v>
       </c>
       <c r="C42" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D42" t="s">
         <v>35</v>
       </c>
       <c r="E42" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F42" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="G42" t="s">
         <v>13</v>
@@ -4696,19 +4693,19 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B43" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C43" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
       </c>
       <c r="E43" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F43" t="s">
         <v>45</v>
@@ -4719,19 +4716,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B44" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C44" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D44" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E44" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F44" t="s">
         <v>45</v>
@@ -4742,59 +4739,59 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B45" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C45" t="s">
         <v>42</v>
       </c>
       <c r="D45" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E45" t="s">
         <v>11</v>
       </c>
       <c r="F45" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G45" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D46" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E46" t="s">
         <v>11</v>
       </c>
       <c r="F46" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G46" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C47" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D47" t="s">
         <v>32</v>
@@ -4803,21 +4800,21 @@
         <v>11</v>
       </c>
       <c r="F47" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G47" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B48" t="s">
         <v>8</v>
       </c>
       <c r="C48" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D48" t="s">
         <v>35</v>
@@ -4826,15 +4823,15 @@
         <v>11</v>
       </c>
       <c r="F48" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G48" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B49" t="s">
         <v>8</v>
@@ -4849,21 +4846,21 @@
         <v>11</v>
       </c>
       <c r="F49" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G49" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B50" t="s">
         <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -4872,15 +4869,15 @@
         <v>11</v>
       </c>
       <c r="F50" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G50" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B51" t="s">
         <v>8</v>
@@ -4895,44 +4892,44 @@
         <v>11</v>
       </c>
       <c r="F51" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G51" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B52" t="s">
         <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D52" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E52" t="s">
         <v>20</v>
       </c>
       <c r="F52" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G52" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B53" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C53" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D53" t="s">
         <v>17</v>
@@ -4941,21 +4938,21 @@
         <v>20</v>
       </c>
       <c r="F53" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G53" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B54" t="s">
         <v>8</v>
       </c>
       <c r="C54" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D54" t="s">
         <v>18</v>
@@ -4964,44 +4961,44 @@
         <v>20</v>
       </c>
       <c r="F54" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G54" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B55" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C55" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D55" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E55" t="s">
         <v>44</v>
       </c>
       <c r="F55" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G55" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B56" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C56" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D56" t="s">
         <v>25</v>
@@ -5010,21 +5007,21 @@
         <v>44</v>
       </c>
       <c r="F56" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G56" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B57" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C57" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D57" t="s">
         <v>32</v>
@@ -5033,21 +5030,21 @@
         <v>44</v>
       </c>
       <c r="F57" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G57" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B58" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C58" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D58" t="s">
         <v>17</v>
@@ -5056,21 +5053,21 @@
         <v>44</v>
       </c>
       <c r="F58" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G58" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B59" t="s">
         <v>37</v>
       </c>
       <c r="C59" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -5079,41 +5076,41 @@
         <v>44</v>
       </c>
       <c r="F59" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G59" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B60" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C60" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D60" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E60" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F60" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G60" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B61" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C61" t="s">
         <v>9</v>
@@ -5122,87 +5119,87 @@
         <v>17</v>
       </c>
       <c r="E61" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F61" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G61" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B62" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C62" t="s">
+        <v>89</v>
+      </c>
+      <c r="D62" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" t="s">
+        <v>72</v>
+      </c>
+      <c r="F62" t="s">
         <v>86</v>
       </c>
-      <c r="D62" t="s">
-        <v>14</v>
-      </c>
-      <c r="E62" t="s">
-        <v>69</v>
-      </c>
-      <c r="F62" t="s">
-        <v>83</v>
-      </c>
       <c r="G62" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B63" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C63" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D63" t="s">
         <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F63" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G63" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C64" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D64" t="s">
         <v>32</v>
       </c>
       <c r="E64" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F64" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G64" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B65" t="s">
         <v>8</v>
@@ -5214,41 +5211,41 @@
         <v>35</v>
       </c>
       <c r="E65" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F65" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G65" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B66" t="s">
         <v>8</v>
       </c>
       <c r="C66" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D66" t="s">
         <v>35</v>
       </c>
       <c r="E66" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F66" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G66" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B67" t="s">
         <v>8</v>
@@ -5260,116 +5257,116 @@
         <v>18</v>
       </c>
       <c r="E67" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F67" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G67" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B68" t="s">
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D68" t="s">
         <v>18</v>
       </c>
       <c r="E68" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F68" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G68" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B69" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C69" t="s">
         <v>42</v>
       </c>
       <c r="D69" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E69" t="s">
         <v>11</v>
       </c>
       <c r="F69" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G69" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B70" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C70" t="s">
         <v>46</v>
       </c>
       <c r="D70" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E70" t="s">
         <v>11</v>
       </c>
       <c r="F70" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G70" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B71" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C71" t="s">
         <v>46</v>
       </c>
       <c r="D71" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E71" t="s">
         <v>11</v>
       </c>
       <c r="F71" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G71" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B72" t="s">
         <v>8</v>
       </c>
       <c r="C72" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D72" t="s">
         <v>35</v>
@@ -5378,21 +5375,21 @@
         <v>11</v>
       </c>
       <c r="F72" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G72" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B73" t="s">
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D73" t="s">
         <v>35</v>
@@ -5401,21 +5398,21 @@
         <v>11</v>
       </c>
       <c r="F73" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G73" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B74" t="s">
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
@@ -5424,21 +5421,21 @@
         <v>11</v>
       </c>
       <c r="F74" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G74" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B75" t="s">
         <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
@@ -5447,21 +5444,21 @@
         <v>11</v>
       </c>
       <c r="F75" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G75" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B76" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C76" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D76" t="s">
         <v>17</v>
@@ -5470,21 +5467,21 @@
         <v>20</v>
       </c>
       <c r="F76" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G76" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B77" t="s">
         <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D77" t="s">
         <v>18</v>
@@ -5493,110 +5490,110 @@
         <v>20</v>
       </c>
       <c r="F77" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G77" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B78" t="s">
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D78" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E78" t="s">
         <v>20</v>
       </c>
       <c r="F78" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G78" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B79" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C79" t="s">
         <v>46</v>
       </c>
       <c r="D79" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E79" t="s">
         <v>44</v>
       </c>
       <c r="F79" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G79" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B80" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C80" t="s">
         <v>46</v>
       </c>
       <c r="D80" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E80" t="s">
         <v>44</v>
       </c>
       <c r="F80" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G80" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B81" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C81" t="s">
         <v>46</v>
       </c>
       <c r="D81" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E81" t="s">
         <v>44</v>
       </c>
       <c r="F81" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G81" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B82" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C82" t="s">
         <v>46</v>
@@ -5608,21 +5605,21 @@
         <v>44</v>
       </c>
       <c r="F82" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G82" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B83" t="s">
         <v>37</v>
       </c>
       <c r="C83" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
@@ -5631,41 +5628,41 @@
         <v>44</v>
       </c>
       <c r="F83" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G83" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B84" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C84" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D84" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E84" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F84" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G84" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B85" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C85" t="s">
         <v>9</v>
@@ -5674,133 +5671,133 @@
         <v>17</v>
       </c>
       <c r="E85" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F85" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G85" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B86" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C86" t="s">
+        <v>89</v>
+      </c>
+      <c r="D86" t="s">
+        <v>10</v>
+      </c>
+      <c r="E86" t="s">
+        <v>72</v>
+      </c>
+      <c r="F86" t="s">
         <v>86</v>
       </c>
-      <c r="D86" t="s">
-        <v>14</v>
-      </c>
-      <c r="E86" t="s">
-        <v>69</v>
-      </c>
-      <c r="F86" t="s">
-        <v>83</v>
-      </c>
       <c r="G86" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B87" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C87" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D87" t="s">
         <v>25</v>
       </c>
       <c r="E87" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F87" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G87" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B88" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C88" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D88" t="s">
         <v>32</v>
       </c>
       <c r="E88" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F88" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G88" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B89" t="s">
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D89" t="s">
         <v>35</v>
       </c>
       <c r="E89" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F89" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G89" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B90" t="s">
         <v>8</v>
       </c>
       <c r="C90" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D90" t="s">
         <v>35</v>
       </c>
       <c r="E90" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F90" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G90" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B91" t="s">
         <v>8</v>
@@ -5812,47 +5809,47 @@
         <v>18</v>
       </c>
       <c r="E91" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F91" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G91" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B92" t="s">
         <v>8</v>
       </c>
       <c r="C92" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
       </c>
       <c r="E92" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F92" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G92" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B93" t="s">
         <v>37</v>
       </c>
       <c r="C93" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D93" t="s">
         <v>10</v>
@@ -5861,21 +5858,21 @@
         <v>11</v>
       </c>
       <c r="F93" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G93" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B94" t="s">
         <v>37</v>
       </c>
       <c r="C94" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D94" t="s">
         <v>10</v>
@@ -5884,15 +5881,15 @@
         <v>20</v>
       </c>
       <c r="F94" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G94" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B95" t="s">
         <v>8</v>
@@ -5901,44 +5898,44 @@
         <v>9</v>
       </c>
       <c r="D95" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E95" t="s">
         <v>20</v>
       </c>
       <c r="F95" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G95" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B96" t="s">
         <v>8</v>
       </c>
       <c r="C96" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D96" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E96" t="s">
         <v>20</v>
       </c>
       <c r="F96" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G96" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B97" t="s">
         <v>8</v>
@@ -5947,50 +5944,50 @@
         <v>46</v>
       </c>
       <c r="D97" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E97" t="s">
         <v>20</v>
       </c>
       <c r="F97" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G97" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B98" t="s">
         <v>8</v>
       </c>
       <c r="C98" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D98" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E98" t="s">
         <v>20</v>
       </c>
       <c r="F98" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G98" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B99" t="s">
         <v>37</v>
       </c>
       <c r="C99" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D99" t="s">
         <v>35</v>
@@ -5999,21 +5996,21 @@
         <v>20</v>
       </c>
       <c r="F99" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G99" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
+        <v>174</v>
+      </c>
+      <c r="B100" t="s">
+        <v>51</v>
+      </c>
+      <c r="C100" t="s">
         <v>173</v>
-      </c>
-      <c r="B100" t="s">
-        <v>64</v>
-      </c>
-      <c r="C100" t="s">
-        <v>171</v>
       </c>
       <c r="D100" t="s">
         <v>18</v>
@@ -6022,21 +6019,21 @@
         <v>20</v>
       </c>
       <c r="F100" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G100" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B101" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C101" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D101" t="s">
         <v>10</v>
@@ -6045,67 +6042,67 @@
         <v>44</v>
       </c>
       <c r="F101" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G101" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B102" t="s">
         <v>8</v>
       </c>
       <c r="C102" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D102" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E102" t="s">
         <v>44</v>
       </c>
       <c r="F102" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G102" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B103" t="s">
         <v>8</v>
       </c>
       <c r="C103" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D103" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E103" t="s">
         <v>44</v>
       </c>
       <c r="F103" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G103" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B104" t="s">
         <v>37</v>
       </c>
       <c r="C104" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D104" t="s">
         <v>35</v>
@@ -6114,21 +6111,21 @@
         <v>44</v>
       </c>
       <c r="F104" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G104" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B105" t="s">
         <v>37</v>
       </c>
       <c r="C105" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D105" t="s">
         <v>18</v>
@@ -6137,199 +6134,199 @@
         <v>44</v>
       </c>
       <c r="F105" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G105" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B106" t="s">
         <v>37</v>
       </c>
       <c r="C106" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D106" t="s">
         <v>10</v>
       </c>
       <c r="E106" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F106" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G106" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B107" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C107" t="s">
+        <v>164</v>
+      </c>
+      <c r="D107" t="s">
+        <v>90</v>
+      </c>
+      <c r="E107" t="s">
+        <v>62</v>
+      </c>
+      <c r="F107" t="s">
+        <v>187</v>
+      </c>
+      <c r="G107" t="s">
         <v>162</v>
-      </c>
-      <c r="D107" t="s">
-        <v>87</v>
-      </c>
-      <c r="E107" t="s">
-        <v>59</v>
-      </c>
-      <c r="F107" t="s">
-        <v>186</v>
-      </c>
-      <c r="G107" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B108" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C108" t="s">
+        <v>164</v>
+      </c>
+      <c r="D108" t="s">
+        <v>52</v>
+      </c>
+      <c r="E108" t="s">
+        <v>62</v>
+      </c>
+      <c r="F108" t="s">
+        <v>187</v>
+      </c>
+      <c r="G108" t="s">
         <v>162</v>
-      </c>
-      <c r="D108" t="s">
-        <v>138</v>
-      </c>
-      <c r="E108" t="s">
-        <v>59</v>
-      </c>
-      <c r="F108" t="s">
-        <v>186</v>
-      </c>
-      <c r="G108" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B109" t="s">
         <v>8</v>
       </c>
       <c r="C109" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D109" t="s">
         <v>35</v>
       </c>
       <c r="E109" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F109" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G109" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B110" t="s">
         <v>8</v>
       </c>
       <c r="C110" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D110" t="s">
         <v>35</v>
       </c>
       <c r="E110" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F110" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G110" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B111" t="s">
         <v>8</v>
       </c>
       <c r="C111" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D111" t="s">
         <v>18</v>
       </c>
       <c r="E111" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F111" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G111" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B112" t="s">
         <v>8</v>
       </c>
       <c r="C112" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D112" t="s">
         <v>18</v>
       </c>
       <c r="E112" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F112" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G112" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B113" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C113" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D113" t="s">
         <v>10</v>
       </c>
       <c r="E113" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F113" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G113" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B114" t="s">
         <v>37</v>
@@ -6338,73 +6335,73 @@
         <v>46</v>
       </c>
       <c r="D114" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E114" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F114" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G114" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B115" t="s">
         <v>37</v>
       </c>
       <c r="C115" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D115" t="s">
         <v>35</v>
       </c>
       <c r="E115" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F115" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G115" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B116" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C116" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D116" t="s">
         <v>18</v>
       </c>
       <c r="E116" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F116" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G116" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B117" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C117" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D117" t="s">
         <v>10</v>
@@ -6413,113 +6410,113 @@
         <v>11</v>
       </c>
       <c r="F117" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="G117" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B118" t="s">
         <v>8</v>
       </c>
       <c r="C118" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D118" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E118" t="s">
         <v>11</v>
       </c>
       <c r="F118" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G118" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B119" t="s">
         <v>8</v>
       </c>
       <c r="C119" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D119" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E119" t="s">
         <v>11</v>
       </c>
       <c r="F119" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G119" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B120" t="s">
         <v>8</v>
       </c>
       <c r="C120" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D120" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E120" t="s">
         <v>11</v>
       </c>
       <c r="F120" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G120" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B121" t="s">
         <v>8</v>
       </c>
       <c r="C121" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D121" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E121" t="s">
         <v>11</v>
       </c>
       <c r="F121" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G121" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B122" t="s">
         <v>37</v>
       </c>
       <c r="C122" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D122" t="s">
         <v>35</v>
@@ -6528,21 +6525,21 @@
         <v>11</v>
       </c>
       <c r="F122" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G122" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B123" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C123" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D123" t="s">
         <v>18</v>
@@ -6551,21 +6548,21 @@
         <v>11</v>
       </c>
       <c r="F123" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G123" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B124" t="s">
         <v>37</v>
       </c>
       <c r="C124" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D124" t="s">
         <v>10</v>
@@ -6574,15 +6571,15 @@
         <v>20</v>
       </c>
       <c r="F124" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G124" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B125" t="s">
         <v>8</v>
@@ -6591,44 +6588,44 @@
         <v>46</v>
       </c>
       <c r="D125" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E125" t="s">
         <v>20</v>
       </c>
       <c r="F125" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G125" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B126" t="s">
         <v>8</v>
       </c>
       <c r="C126" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D126" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E126" t="s">
         <v>20</v>
       </c>
       <c r="F126" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G126" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B127" t="s">
         <v>8</v>
@@ -6637,50 +6634,50 @@
         <v>46</v>
       </c>
       <c r="D127" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E127" t="s">
         <v>20</v>
       </c>
       <c r="F127" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G127" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B128" t="s">
         <v>8</v>
       </c>
       <c r="C128" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D128" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E128" t="s">
         <v>20</v>
       </c>
       <c r="F128" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G128" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B129" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C129" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D129" t="s">
         <v>35</v>
@@ -6689,21 +6686,21 @@
         <v>20</v>
       </c>
       <c r="F129" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G129" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B130" t="s">
         <v>37</v>
       </c>
       <c r="C130" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D130" t="s">
         <v>18</v>
@@ -6712,15 +6709,15 @@
         <v>20</v>
       </c>
       <c r="F130" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G130" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B131" t="s">
         <v>8</v>
@@ -6729,21 +6726,21 @@
         <v>46</v>
       </c>
       <c r="D131" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E131" t="s">
         <v>44</v>
       </c>
       <c r="F131" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G131" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B132" t="s">
         <v>8</v>
@@ -6752,27 +6749,27 @@
         <v>46</v>
       </c>
       <c r="D132" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E132" t="s">
         <v>44</v>
       </c>
       <c r="F132" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G132" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B133" t="s">
         <v>37</v>
       </c>
       <c r="C133" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D133" t="s">
         <v>35</v>
@@ -6781,10 +6778,10 @@
         <v>44</v>
       </c>
       <c r="F133" t="s">
-        <v>223</v>
+        <v>53</v>
       </c>
       <c r="G133" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -6792,10 +6789,10 @@
         <v>224</v>
       </c>
       <c r="B134" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C134" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D134" t="s">
         <v>18</v>
@@ -6804,10 +6801,10 @@
         <v>44</v>
       </c>
       <c r="F134" t="s">
-        <v>223</v>
+        <v>53</v>
       </c>
       <c r="G134" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -6824,13 +6821,13 @@
         <v>10</v>
       </c>
       <c r="E135" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F135" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G135" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -6838,22 +6835,22 @@
         <v>227</v>
       </c>
       <c r="B136" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C136" t="s">
         <v>228</v>
       </c>
       <c r="D136" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E136" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F136" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G136" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -6864,19 +6861,19 @@
         <v>37</v>
       </c>
       <c r="C137" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D137" t="s">
         <v>35</v>
       </c>
       <c r="E137" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F137" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G137" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -6884,45 +6881,45 @@
         <v>230</v>
       </c>
       <c r="B138" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C138" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D138" t="s">
         <v>18</v>
       </c>
       <c r="E138" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F138" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G138" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B139" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C139" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D139" t="s">
         <v>10</v>
       </c>
       <c r="E139" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F139" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G139" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -6930,22 +6927,22 @@
         <v>231</v>
       </c>
       <c r="B140" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C140" t="s">
         <v>46</v>
       </c>
       <c r="D140" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E140" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F140" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G140" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -6959,7 +6956,7 @@
         <v>233</v>
       </c>
       <c r="D141" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E141" t="s">
         <v>11</v>
@@ -6982,13 +6979,13 @@
         <v>46</v>
       </c>
       <c r="D142" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E142" t="s">
         <v>11</v>
       </c>
       <c r="F142" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G142" t="s">
         <v>235</v>
@@ -7002,7 +6999,7 @@
         <v>37</v>
       </c>
       <c r="C143" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D143" t="s">
         <v>35</v>
@@ -7011,7 +7008,7 @@
         <v>11</v>
       </c>
       <c r="F143" t="s">
-        <v>223</v>
+        <v>53</v>
       </c>
       <c r="G143" t="s">
         <v>235</v>
@@ -7034,7 +7031,7 @@
         <v>11</v>
       </c>
       <c r="F144" t="s">
-        <v>223</v>
+        <v>53</v>
       </c>
       <c r="G144" t="s">
         <v>235</v>
@@ -7057,7 +7054,7 @@
         <v>20</v>
       </c>
       <c r="F145" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G145" t="s">
         <v>235</v>
@@ -7068,13 +7065,13 @@
         <v>241</v>
       </c>
       <c r="B146" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C146" t="s">
         <v>242</v>
       </c>
       <c r="D146" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E146" t="s">
         <v>20</v>
@@ -7091,7 +7088,7 @@
         <v>244</v>
       </c>
       <c r="B147" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C147" t="s">
         <v>233</v>
@@ -7103,7 +7100,7 @@
         <v>44</v>
       </c>
       <c r="F147" t="s">
-        <v>223</v>
+        <v>53</v>
       </c>
       <c r="G147" t="s">
         <v>235</v>
@@ -7143,7 +7140,7 @@
         <v>249</v>
       </c>
       <c r="D149" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E149" t="s">
         <v>44</v>
@@ -7160,7 +7157,7 @@
         <v>250</v>
       </c>
       <c r="B150" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C150" t="s">
         <v>46</v>
@@ -7183,7 +7180,7 @@
         <v>250</v>
       </c>
       <c r="B151" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C151" t="s">
         <v>46</v>
@@ -7215,10 +7212,10 @@
         <v>10</v>
       </c>
       <c r="E152" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F152" t="s">
-        <v>223</v>
+        <v>53</v>
       </c>
       <c r="G152" t="s">
         <v>235</v>
@@ -7238,7 +7235,7 @@
         <v>25</v>
       </c>
       <c r="E153" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F153" t="s">
         <v>254</v>
@@ -7258,10 +7255,10 @@
         <v>46</v>
       </c>
       <c r="D154" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E154" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F154" t="s">
         <v>256</v>
@@ -7278,13 +7275,13 @@
         <v>258</v>
       </c>
       <c r="C155" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D155" t="s">
         <v>35</v>
       </c>
       <c r="E155" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F155" t="s">
         <v>234</v>
@@ -7307,7 +7304,7 @@
         <v>18</v>
       </c>
       <c r="E156" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F156" t="s">
         <v>234</v>
@@ -7330,7 +7327,7 @@
         <v>10</v>
       </c>
       <c r="E157" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F157" t="s">
         <v>261</v>
@@ -7350,10 +7347,10 @@
         <v>46</v>
       </c>
       <c r="D158" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E158" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F158" t="s">
         <v>263</v>
@@ -7376,7 +7373,7 @@
         <v>35</v>
       </c>
       <c r="E159" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F159" t="s">
         <v>234</v>
@@ -7399,10 +7396,10 @@
         <v>18</v>
       </c>
       <c r="E160" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F160" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G160" t="s">
         <v>235</v>
@@ -7439,7 +7436,7 @@
         <v>271</v>
       </c>
       <c r="C162" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D162" t="s">
         <v>25</v>
@@ -7459,13 +7456,13 @@
         <v>272</v>
       </c>
       <c r="B163" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C163" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D163" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E163" t="s">
         <v>11</v>
@@ -7517,7 +7514,7 @@
         <v>11</v>
       </c>
       <c r="F165" t="s">
-        <v>223</v>
+        <v>53</v>
       </c>
       <c r="G165" t="s">
         <v>269</v>
@@ -7580,7 +7577,7 @@
         <v>278</v>
       </c>
       <c r="D168" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E168" t="s">
         <v>20</v>
@@ -7603,7 +7600,7 @@
         <v>282</v>
       </c>
       <c r="D169" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E169" t="s">
         <v>20</v>
@@ -7632,7 +7629,7 @@
         <v>44</v>
       </c>
       <c r="F170" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G170" t="s">
         <v>269</v>
@@ -7649,13 +7646,13 @@
         <v>46</v>
       </c>
       <c r="D171" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E171" t="s">
         <v>44</v>
       </c>
       <c r="F171" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G171" t="s">
         <v>269</v>
@@ -7672,7 +7669,7 @@
         <v>249</v>
       </c>
       <c r="D172" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E172" t="s">
         <v>44</v>
@@ -7701,7 +7698,7 @@
         <v>44</v>
       </c>
       <c r="F173" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G173" t="s">
         <v>269</v>
@@ -7724,7 +7721,7 @@
         <v>44</v>
       </c>
       <c r="F174" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G174" t="s">
         <v>269</v>
@@ -7735,7 +7732,7 @@
         <v>293</v>
       </c>
       <c r="B175" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C175" t="s">
         <v>282</v>
@@ -7744,10 +7741,10 @@
         <v>10</v>
       </c>
       <c r="E175" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F175" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G175" t="s">
         <v>269</v>
@@ -7764,10 +7761,10 @@
         <v>295</v>
       </c>
       <c r="D176" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E176" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F176" t="s">
         <v>296</v>
@@ -7787,13 +7784,13 @@
         <v>295</v>
       </c>
       <c r="D177" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E177" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F177" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G177" t="s">
         <v>269</v>
@@ -7813,10 +7810,10 @@
         <v>35</v>
       </c>
       <c r="E178" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F178" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G178" t="s">
         <v>269</v>
@@ -7833,13 +7830,13 @@
         <v>282</v>
       </c>
       <c r="D179" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E179" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F179" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G179" t="s">
         <v>269</v>
@@ -7859,7 +7856,7 @@
         <v>43</v>
       </c>
       <c r="E180" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F180" t="s">
         <v>303</v>
@@ -7879,10 +7876,10 @@
         <v>46</v>
       </c>
       <c r="D181" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E181" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F181" t="s">
         <v>303</v>
@@ -7902,13 +7899,13 @@
         <v>46</v>
       </c>
       <c r="D182" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E182" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F182" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G182" t="s">
         <v>269</v>
@@ -7928,10 +7925,10 @@
         <v>17</v>
       </c>
       <c r="E183" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F183" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G183" t="s">
         <v>269</v>
@@ -7942,7 +7939,7 @@
         <v>308</v>
       </c>
       <c r="B184" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C184" t="s">
         <v>307</v>
@@ -7951,10 +7948,10 @@
         <v>18</v>
       </c>
       <c r="E184" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F184" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G184" t="s">
         <v>269</v>
@@ -7994,7 +7991,7 @@
         <v>295</v>
       </c>
       <c r="D186" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E186" t="s">
         <v>11</v>
@@ -8011,13 +8008,13 @@
         <v>315</v>
       </c>
       <c r="B187" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C187" t="s">
         <v>295</v>
       </c>
       <c r="D187" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E187" t="s">
         <v>11</v>
@@ -8034,7 +8031,7 @@
         <v>316</v>
       </c>
       <c r="B188" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C188" t="s">
         <v>46</v>
@@ -8060,7 +8057,7 @@
         <v>37</v>
       </c>
       <c r="C189" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D189" t="s">
         <v>18</v>
@@ -8103,13 +8100,13 @@
         <v>320</v>
       </c>
       <c r="B191" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C191" t="s">
         <v>321</v>
       </c>
       <c r="D191" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E191" t="s">
         <v>44</v>
@@ -8132,7 +8129,7 @@
         <v>321</v>
       </c>
       <c r="D192" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E192" t="s">
         <v>44</v>
@@ -8149,7 +8146,7 @@
         <v>323</v>
       </c>
       <c r="B193" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C193" t="s">
         <v>324</v>
@@ -8201,7 +8198,7 @@
         <v>324</v>
       </c>
       <c r="D195" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E195" t="s">
         <v>44</v>
@@ -8218,7 +8215,7 @@
         <v>330</v>
       </c>
       <c r="B196" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C196" t="s">
         <v>331</v>
@@ -8227,7 +8224,7 @@
         <v>10</v>
       </c>
       <c r="E196" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F196" t="s">
         <v>314</v>
@@ -8250,7 +8247,7 @@
         <v>25</v>
       </c>
       <c r="E197" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F197" t="s">
         <v>335</v>
@@ -8273,7 +8270,7 @@
         <v>35</v>
       </c>
       <c r="E198" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F198" t="s">
         <v>314</v>
@@ -8296,7 +8293,7 @@
         <v>18</v>
       </c>
       <c r="E199" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F199" t="s">
         <v>314</v>
@@ -8313,13 +8310,13 @@
         <v>37</v>
       </c>
       <c r="C200" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D200" t="s">
         <v>10</v>
       </c>
       <c r="E200" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F200" t="s">
         <v>314</v>
@@ -8339,10 +8336,10 @@
         <v>46</v>
       </c>
       <c r="D201" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E201" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F201" t="s">
         <v>341</v>
@@ -8359,13 +8356,13 @@
         <v>37</v>
       </c>
       <c r="C202" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D202" t="s">
         <v>35</v>
       </c>
       <c r="E202" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F202" t="s">
         <v>314</v>
@@ -8388,7 +8385,7 @@
         <v>18</v>
       </c>
       <c r="E203" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F203" t="s">
         <v>314</v>
@@ -8414,7 +8411,7 @@
         <v>11</v>
       </c>
       <c r="F204" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G204" t="s">
         <v>347</v>
@@ -8474,7 +8471,7 @@
         <v>37</v>
       </c>
       <c r="C207" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D207" t="s">
         <v>10</v>
@@ -8483,7 +8480,7 @@
         <v>11</v>
       </c>
       <c r="F207" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G207" t="s">
         <v>347</v>
@@ -8552,7 +8549,7 @@
         <v>11</v>
       </c>
       <c r="F210" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G210" t="s">
         <v>347</v>
@@ -8592,7 +8589,7 @@
         <v>359</v>
       </c>
       <c r="D212" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E212" t="s">
         <v>11</v>
@@ -8615,7 +8612,7 @@
         <v>46</v>
       </c>
       <c r="D213" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E213" t="s">
         <v>11</v>
@@ -8638,7 +8635,7 @@
         <v>46</v>
       </c>
       <c r="D214" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E214" t="s">
         <v>11</v>
@@ -8661,7 +8658,7 @@
         <v>367</v>
       </c>
       <c r="D215" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E215" t="s">
         <v>11</v>
@@ -8684,13 +8681,13 @@
         <v>346</v>
       </c>
       <c r="D216" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E216" t="s">
         <v>11</v>
       </c>
       <c r="F216" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G216" t="s">
         <v>347</v>
@@ -8707,7 +8704,7 @@
         <v>350</v>
       </c>
       <c r="D217" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E217" t="s">
         <v>11</v>
@@ -8730,7 +8727,7 @@
         <v>354</v>
       </c>
       <c r="D218" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E218" t="s">
         <v>11</v>
@@ -8753,13 +8750,13 @@
         <v>346</v>
       </c>
       <c r="D219" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E219" t="s">
         <v>11</v>
       </c>
       <c r="F219" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G219" t="s">
         <v>347</v>
@@ -8776,7 +8773,7 @@
         <v>350</v>
       </c>
       <c r="D220" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E220" t="s">
         <v>11</v>
@@ -8799,7 +8796,7 @@
         <v>354</v>
       </c>
       <c r="D221" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E221" t="s">
         <v>11</v>
@@ -8842,7 +8839,7 @@
         <v>37</v>
       </c>
       <c r="C223" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D223" t="s">
         <v>18</v>
@@ -8888,7 +8885,7 @@
         <v>345</v>
       </c>
       <c r="C225" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D225" t="s">
         <v>10</v>
@@ -8897,7 +8894,7 @@
         <v>20</v>
       </c>
       <c r="F225" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G225" t="s">
         <v>347</v>
@@ -8957,7 +8954,7 @@
         <v>37</v>
       </c>
       <c r="C228" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D228" t="s">
         <v>10</v>
@@ -8980,7 +8977,7 @@
         <v>345</v>
       </c>
       <c r="C229" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D229" t="s">
         <v>14</v>
@@ -8989,7 +8986,7 @@
         <v>20</v>
       </c>
       <c r="F229" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G229" t="s">
         <v>347</v>
@@ -9052,7 +9049,7 @@
         <v>46</v>
       </c>
       <c r="D232" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E232" t="s">
         <v>20</v>
@@ -9075,7 +9072,7 @@
         <v>384</v>
       </c>
       <c r="D233" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E233" t="s">
         <v>20</v>
@@ -9095,16 +9092,16 @@
         <v>345</v>
       </c>
       <c r="C234" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D234" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E234" t="s">
         <v>20</v>
       </c>
       <c r="F234" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G234" t="s">
         <v>347</v>
@@ -9121,7 +9118,7 @@
         <v>377</v>
       </c>
       <c r="D235" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E235" t="s">
         <v>20</v>
@@ -9144,7 +9141,7 @@
         <v>379</v>
       </c>
       <c r="D236" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E236" t="s">
         <v>20</v>
@@ -9167,7 +9164,7 @@
         <v>46</v>
       </c>
       <c r="D237" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E237" t="s">
         <v>20</v>
@@ -9187,16 +9184,16 @@
         <v>345</v>
       </c>
       <c r="C238" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D238" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E238" t="s">
         <v>20</v>
       </c>
       <c r="F238" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G238" t="s">
         <v>347</v>
@@ -9213,7 +9210,7 @@
         <v>377</v>
       </c>
       <c r="D239" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E239" t="s">
         <v>20</v>
@@ -9236,7 +9233,7 @@
         <v>379</v>
       </c>
       <c r="D240" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E240" t="s">
         <v>20</v>
@@ -9279,7 +9276,7 @@
         <v>37</v>
       </c>
       <c r="C242" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D242" t="s">
         <v>18</v>
@@ -9345,7 +9342,7 @@
         <v>397</v>
       </c>
       <c r="B245" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C245" t="s">
         <v>398</v>
@@ -9357,7 +9354,7 @@
         <v>44</v>
       </c>
       <c r="F245" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G245" t="s">
         <v>347</v>
@@ -9391,7 +9388,7 @@
         <v>401</v>
       </c>
       <c r="B247" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C247" t="s">
         <v>46</v>
@@ -9437,7 +9434,7 @@
         <v>348</v>
       </c>
       <c r="B249" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C249" t="s">
         <v>350</v>
@@ -9466,7 +9463,7 @@
         <v>404</v>
       </c>
       <c r="D250" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E250" t="s">
         <v>44</v>
@@ -9483,19 +9480,19 @@
         <v>405</v>
       </c>
       <c r="B251" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C251" t="s">
         <v>49</v>
       </c>
       <c r="D251" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E251" t="s">
         <v>44</v>
       </c>
       <c r="F251" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G251" t="s">
         <v>347</v>
@@ -9512,7 +9509,7 @@
         <v>404</v>
       </c>
       <c r="D252" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E252" t="s">
         <v>44</v>
@@ -9529,13 +9526,13 @@
         <v>407</v>
       </c>
       <c r="B253" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C253" t="s">
         <v>46</v>
       </c>
       <c r="D253" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E253" t="s">
         <v>44</v>
@@ -9558,7 +9555,7 @@
         <v>379</v>
       </c>
       <c r="D254" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E254" t="s">
         <v>44</v>
@@ -9581,7 +9578,7 @@
         <v>404</v>
       </c>
       <c r="D255" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E255" t="s">
         <v>44</v>
@@ -9604,13 +9601,13 @@
         <v>398</v>
       </c>
       <c r="D256" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E256" t="s">
         <v>44</v>
       </c>
       <c r="F256" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G256" t="s">
         <v>347</v>
@@ -9627,7 +9624,7 @@
         <v>404</v>
       </c>
       <c r="D257" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E257" t="s">
         <v>44</v>
@@ -9644,13 +9641,13 @@
         <v>407</v>
       </c>
       <c r="B258" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C258" t="s">
         <v>46</v>
       </c>
       <c r="D258" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E258" t="s">
         <v>44</v>
@@ -9713,7 +9710,7 @@
         <v>414</v>
       </c>
       <c r="B261" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C261" t="s">
         <v>46</v>
@@ -9791,7 +9788,7 @@
         <v>10</v>
       </c>
       <c r="E264" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F264" t="s">
         <v>396</v>
@@ -9814,7 +9811,7 @@
         <v>10</v>
       </c>
       <c r="E265" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F265" t="s">
         <v>394</v>
@@ -9837,7 +9834,7 @@
         <v>10</v>
       </c>
       <c r="E266" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F266" t="s">
         <v>351</v>
@@ -9860,7 +9857,7 @@
         <v>10</v>
       </c>
       <c r="E267" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F267" t="s">
         <v>355</v>
@@ -9874,16 +9871,16 @@
         <v>422</v>
       </c>
       <c r="B268" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C268" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D268" t="s">
         <v>10</v>
       </c>
       <c r="E268" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F268" t="s">
         <v>423</v>
@@ -9906,10 +9903,10 @@
         <v>14</v>
       </c>
       <c r="E269" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F269" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G269" t="s">
         <v>347</v>
@@ -9929,7 +9926,7 @@
         <v>14</v>
       </c>
       <c r="E270" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F270" t="s">
         <v>351</v>
@@ -9943,7 +9940,7 @@
         <v>424</v>
       </c>
       <c r="B271" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C271" t="s">
         <v>46</v>
@@ -9952,7 +9949,7 @@
         <v>14</v>
       </c>
       <c r="E271" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F271" t="s">
         <v>355</v>
@@ -9966,7 +9963,7 @@
         <v>425</v>
       </c>
       <c r="B272" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C272" t="s">
         <v>228</v>
@@ -9975,10 +9972,10 @@
         <v>14</v>
       </c>
       <c r="E272" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F272" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G272" t="s">
         <v>347</v>
@@ -9995,10 +9992,10 @@
         <v>46</v>
       </c>
       <c r="D273" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E273" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F273" t="s">
         <v>409</v>
@@ -10018,10 +10015,10 @@
         <v>404</v>
       </c>
       <c r="D274" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E274" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F274" t="s">
         <v>363</v>
@@ -10041,13 +10038,13 @@
         <v>346</v>
       </c>
       <c r="D275" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E275" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F275" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G275" t="s">
         <v>347</v>
@@ -10064,10 +10061,10 @@
         <v>350</v>
       </c>
       <c r="D276" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E276" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F276" t="s">
         <v>351</v>
@@ -10087,10 +10084,10 @@
         <v>359</v>
       </c>
       <c r="D277" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E277" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F277" t="s">
         <v>355</v>
@@ -10110,13 +10107,13 @@
         <v>346</v>
       </c>
       <c r="D278" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E278" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F278" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G278" t="s">
         <v>347</v>
@@ -10133,10 +10130,10 @@
         <v>350</v>
       </c>
       <c r="D279" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E279" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F279" t="s">
         <v>351</v>
@@ -10156,10 +10153,10 @@
         <v>359</v>
       </c>
       <c r="D280" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E280" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F280" t="s">
         <v>355</v>
@@ -10182,7 +10179,7 @@
         <v>35</v>
       </c>
       <c r="E281" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F281" t="s">
         <v>351</v>
@@ -10205,7 +10202,7 @@
         <v>35</v>
       </c>
       <c r="E282" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F282" t="s">
         <v>355</v>
@@ -10228,7 +10225,7 @@
         <v>18</v>
       </c>
       <c r="E283" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F283" t="s">
         <v>355</v>
@@ -10251,10 +10248,10 @@
         <v>18</v>
       </c>
       <c r="E284" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F284" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G284" t="s">
         <v>347</v>
@@ -10274,7 +10271,7 @@
         <v>14</v>
       </c>
       <c r="E285" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F285" t="s">
         <v>351</v>
@@ -10297,7 +10294,7 @@
         <v>14</v>
       </c>
       <c r="E286" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F286" t="s">
         <v>355</v>
@@ -10314,13 +10311,13 @@
         <v>358</v>
       </c>
       <c r="C287" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D287" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E287" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F287" t="s">
         <v>409</v>
@@ -10340,10 +10337,10 @@
         <v>24</v>
       </c>
       <c r="D288" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E288" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F288" t="s">
         <v>363</v>
@@ -10360,16 +10357,16 @@
         <v>400</v>
       </c>
       <c r="C289" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D289" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E289" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F289" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G289" t="s">
         <v>347</v>
@@ -10380,16 +10377,16 @@
         <v>440</v>
       </c>
       <c r="B290" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C290" t="s">
         <v>49</v>
       </c>
       <c r="D290" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E290" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F290" t="s">
         <v>351</v>
@@ -10406,13 +10403,13 @@
         <v>442</v>
       </c>
       <c r="C291" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D291" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E291" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F291" t="s">
         <v>355</v>
@@ -10435,7 +10432,7 @@
         <v>35</v>
       </c>
       <c r="E292" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F292" t="s">
         <v>409</v>
@@ -10458,7 +10455,7 @@
         <v>35</v>
       </c>
       <c r="E293" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F293" t="s">
         <v>363</v>
@@ -10481,7 +10478,7 @@
         <v>35</v>
       </c>
       <c r="E294" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F294" t="s">
         <v>363</v>
@@ -10504,7 +10501,7 @@
         <v>35</v>
       </c>
       <c r="E295" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F295" t="s">
         <v>363</v>
@@ -10527,10 +10524,10 @@
         <v>18</v>
       </c>
       <c r="E296" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F296" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G296" t="s">
         <v>347</v>
@@ -10544,13 +10541,13 @@
         <v>349</v>
       </c>
       <c r="C297" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D297" t="s">
         <v>18</v>
       </c>
       <c r="E297" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F297" t="s">
         <v>351</v>
@@ -10573,7 +10570,7 @@
         <v>18</v>
       </c>
       <c r="E298" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F298" t="s">
         <v>355</v>
@@ -10613,7 +10610,7 @@
         <v>450</v>
       </c>
       <c r="C300" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D300" t="s">
         <v>25</v>
@@ -10653,7 +10650,7 @@
     </row>
     <row r="302" spans="1:7">
       <c r="A302" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B302" t="s">
         <v>452</v>
@@ -10668,7 +10665,7 @@
         <v>11</v>
       </c>
       <c r="F302" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G302" t="s">
         <v>448</v>
@@ -10685,13 +10682,13 @@
         <v>455</v>
       </c>
       <c r="D303" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E303" t="s">
         <v>11</v>
       </c>
       <c r="F303" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G303" t="s">
         <v>448</v>
@@ -10800,7 +10797,7 @@
         <v>46</v>
       </c>
       <c r="D308" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E308" t="s">
         <v>20</v>
@@ -10866,7 +10863,7 @@
         <v>473</v>
       </c>
       <c r="C311" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D311" t="s">
         <v>25</v>
@@ -10875,7 +10872,7 @@
         <v>44</v>
       </c>
       <c r="F311" t="s">
-        <v>355</v>
+        <v>474</v>
       </c>
       <c r="G311" t="s">
         <v>448</v>
@@ -10883,16 +10880,16 @@
     </row>
     <row r="312" spans="1:7">
       <c r="A312" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B312" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C312" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D312" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E312" t="s">
         <v>44</v>
@@ -10906,7 +10903,7 @@
     </row>
     <row r="313" spans="1:7">
       <c r="A313" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B313" t="s">
         <v>37</v>
@@ -10932,7 +10929,7 @@
         <v>459</v>
       </c>
       <c r="B314" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C314" t="s">
         <v>46</v>
@@ -10944,7 +10941,7 @@
         <v>44</v>
       </c>
       <c r="F314" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G314" t="s">
         <v>448</v>
@@ -10955,7 +10952,7 @@
         <v>459</v>
       </c>
       <c r="B315" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C315" t="s">
         <v>46</v>
@@ -10967,7 +10964,7 @@
         <v>44</v>
       </c>
       <c r="F315" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G315" t="s">
         <v>448</v>
@@ -10978,7 +10975,7 @@
         <v>459</v>
       </c>
       <c r="B316" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C316" t="s">
         <v>367</v>
@@ -10990,7 +10987,7 @@
         <v>44</v>
       </c>
       <c r="F316" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G316" t="s">
         <v>448</v>
@@ -11007,13 +11004,13 @@
         <v>466</v>
       </c>
       <c r="D317" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E317" t="s">
         <v>44</v>
       </c>
       <c r="F317" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G317" t="s">
         <v>448</v>
@@ -11030,13 +11027,13 @@
         <v>470</v>
       </c>
       <c r="D318" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E318" t="s">
         <v>44</v>
       </c>
       <c r="F318" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G318" t="s">
         <v>448</v>
@@ -11047,19 +11044,19 @@
         <v>459</v>
       </c>
       <c r="B319" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C319" t="s">
         <v>46</v>
       </c>
       <c r="D319" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E319" t="s">
         <v>44</v>
       </c>
       <c r="F319" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G319" t="s">
         <v>448</v>
@@ -11070,19 +11067,19 @@
         <v>459</v>
       </c>
       <c r="B320" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C320" t="s">
         <v>46</v>
       </c>
       <c r="D320" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E320" t="s">
         <v>44</v>
       </c>
       <c r="F320" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G320" t="s">
         <v>448</v>
@@ -11093,19 +11090,19 @@
         <v>459</v>
       </c>
       <c r="B321" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C321" t="s">
         <v>367</v>
       </c>
       <c r="D321" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E321" t="s">
         <v>44</v>
       </c>
       <c r="F321" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G321" t="s">
         <v>448</v>
@@ -11113,22 +11110,22 @@
     </row>
     <row r="322" spans="1:7">
       <c r="A322" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B322" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C322" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D322" t="s">
         <v>43</v>
       </c>
       <c r="E322" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F322" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G322" t="s">
         <v>448</v>
@@ -11136,10 +11133,10 @@
     </row>
     <row r="323" spans="1:7">
       <c r="A323" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B323" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C323" t="s">
         <v>46</v>
@@ -11148,7 +11145,7 @@
         <v>25</v>
       </c>
       <c r="E323" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F323" t="s">
         <v>329</v>
@@ -11159,19 +11156,19 @@
     </row>
     <row r="324" spans="1:7">
       <c r="A324" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B324" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C324" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D324" t="s">
         <v>25</v>
       </c>
       <c r="E324" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F324" t="s">
         <v>243</v>
@@ -11182,10 +11179,10 @@
     </row>
     <row r="325" spans="1:7">
       <c r="A325" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B325" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C325" t="s">
         <v>46</v>
@@ -11194,7 +11191,7 @@
         <v>32</v>
       </c>
       <c r="E325" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F325" t="s">
         <v>329</v>
@@ -11205,22 +11202,22 @@
     </row>
     <row r="326" spans="1:7">
       <c r="A326" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B326" t="s">
         <v>37</v>
       </c>
       <c r="C326" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D326" t="s">
         <v>35</v>
       </c>
       <c r="E326" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F326" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G326" t="s">
         <v>448</v>
@@ -11234,16 +11231,16 @@
         <v>469</v>
       </c>
       <c r="C327" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D327" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E327" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F327" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G327" t="s">
         <v>448</v>
@@ -11257,16 +11254,16 @@
         <v>469</v>
       </c>
       <c r="C328" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D328" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E328" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F328" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G328" t="s">
         <v>448</v>
@@ -11274,19 +11271,19 @@
     </row>
     <row r="329" spans="1:7">
       <c r="A329" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B329" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C329" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D329" t="s">
         <v>10</v>
       </c>
       <c r="E329" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F329" t="s">
         <v>329</v>
@@ -11297,10 +11294,10 @@
     </row>
     <row r="330" spans="1:7">
       <c r="A330" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B330" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C330" t="s">
         <v>46</v>
@@ -11309,7 +11306,7 @@
         <v>25</v>
       </c>
       <c r="E330" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F330" t="s">
         <v>329</v>
@@ -11320,10 +11317,10 @@
     </row>
     <row r="331" spans="1:7">
       <c r="A331" t="s">
+        <v>495</v>
+      </c>
+      <c r="B331" t="s">
         <v>494</v>
-      </c>
-      <c r="B331" t="s">
-        <v>493</v>
       </c>
       <c r="C331" t="s">
         <v>46</v>
@@ -11332,7 +11329,7 @@
         <v>32</v>
       </c>
       <c r="E331" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F331" t="s">
         <v>329</v>
@@ -11343,22 +11340,22 @@
     </row>
     <row r="332" spans="1:7">
       <c r="A332" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B332" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C332" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D332" t="s">
         <v>32</v>
       </c>
       <c r="E332" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F332" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G332" t="s">
         <v>448</v>
@@ -11366,19 +11363,19 @@
     </row>
     <row r="333" spans="1:7">
       <c r="A333" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B333" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C333" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D333" t="s">
         <v>17</v>
       </c>
       <c r="E333" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F333" t="s">
         <v>355</v>
@@ -11389,19 +11386,19 @@
     </row>
     <row r="334" spans="1:7">
       <c r="A334" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B334" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C334" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D334" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E334" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F334" t="s">
         <v>329</v>
@@ -11412,13 +11409,13 @@
     </row>
     <row r="335" spans="1:7">
       <c r="A335" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B335" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C335" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D335" t="s">
         <v>10</v>
@@ -11427,21 +11424,21 @@
         <v>11</v>
       </c>
       <c r="F335" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G335" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="336" spans="1:7">
       <c r="A336" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B336" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C336" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D336" t="s">
         <v>10</v>
@@ -11450,38 +11447,38 @@
         <v>11</v>
       </c>
       <c r="F336" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G336" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="337" spans="1:7">
       <c r="A337" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B337" t="s">
         <v>8</v>
       </c>
       <c r="C337" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D337" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E337" t="s">
         <v>11</v>
       </c>
       <c r="F337" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G337" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="338" spans="1:7">
       <c r="A338" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B338" t="s">
         <v>8</v>
@@ -11490,70 +11487,70 @@
         <v>455</v>
       </c>
       <c r="D338" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E338" t="s">
         <v>11</v>
       </c>
       <c r="F338" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G338" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="339" spans="1:7">
       <c r="A339" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B339" t="s">
         <v>8</v>
       </c>
       <c r="C339" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D339" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E339" t="s">
         <v>11</v>
       </c>
       <c r="F339" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G339" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="340" spans="1:7">
       <c r="A340" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B340" t="s">
         <v>8</v>
       </c>
       <c r="C340" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D340" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E340" t="s">
         <v>11</v>
       </c>
       <c r="F340" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="G340" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="341" spans="1:7">
       <c r="A341" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B341" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C341" t="s">
         <v>470</v>
@@ -11565,38 +11562,38 @@
         <v>11</v>
       </c>
       <c r="F341" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G341" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="342" spans="1:7">
       <c r="A342" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B342" t="s">
         <v>8</v>
       </c>
       <c r="C342" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D342" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E342" t="s">
         <v>11</v>
       </c>
       <c r="F342" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G342" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="343" spans="1:7">
       <c r="A343" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B343" t="s">
         <v>8</v>
@@ -11605,24 +11602,24 @@
         <v>455</v>
       </c>
       <c r="D343" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E343" t="s">
         <v>11</v>
       </c>
       <c r="F343" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G343" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="344" spans="1:7">
       <c r="A344" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B344" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C344" t="s">
         <v>470</v>
@@ -11634,21 +11631,21 @@
         <v>11</v>
       </c>
       <c r="F344" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G344" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="345" spans="1:7">
       <c r="A345" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B345" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C345" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D345" t="s">
         <v>32</v>
@@ -11657,21 +11654,21 @@
         <v>11</v>
       </c>
       <c r="F345" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G345" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="346" spans="1:7">
       <c r="A346" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B346" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C346" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D346" t="s">
         <v>32</v>
@@ -11680,21 +11677,21 @@
         <v>11</v>
       </c>
       <c r="F346" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="G346" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="347" spans="1:7">
       <c r="A347" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B347" t="s">
         <v>37</v>
       </c>
       <c r="C347" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D347" t="s">
         <v>35</v>
@@ -11706,41 +11703,41 @@
         <v>243</v>
       </c>
       <c r="G347" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="348" spans="1:7">
       <c r="A348" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B348" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C348" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D348" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E348" t="s">
         <v>11</v>
       </c>
       <c r="F348" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G348" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="349" spans="1:7">
       <c r="A349" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B349" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C349" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D349" t="s">
         <v>17</v>
@@ -11752,18 +11749,18 @@
         <v>39</v>
       </c>
       <c r="G349" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="350" spans="1:7">
       <c r="A350" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B350" t="s">
         <v>37</v>
       </c>
       <c r="C350" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D350" t="s">
         <v>18</v>
@@ -11772,18 +11769,18 @@
         <v>20</v>
       </c>
       <c r="F350" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G350" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="351" spans="1:7">
       <c r="A351" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B351" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C351" t="s">
         <v>242</v>
@@ -11795,41 +11792,41 @@
         <v>44</v>
       </c>
       <c r="F351" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G351" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="352" spans="1:7">
       <c r="A352" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B352" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C352" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D352" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E352" t="s">
         <v>44</v>
       </c>
       <c r="F352" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G352" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="353" spans="1:7">
       <c r="A353" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B353" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C353" t="s">
         <v>46</v>
@@ -11841,41 +11838,41 @@
         <v>44</v>
       </c>
       <c r="F353" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G353" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="354" spans="1:7">
       <c r="A354" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B354" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C354" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D354" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E354" t="s">
         <v>44</v>
       </c>
       <c r="F354" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G354" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="355" spans="1:7">
       <c r="A355" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B355" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C355" t="s">
         <v>46</v>
@@ -11887,21 +11884,21 @@
         <v>44</v>
       </c>
       <c r="F355" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G355" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="356" spans="1:7">
       <c r="A356" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B356" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C356" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D356" t="s">
         <v>35</v>
@@ -11910,18 +11907,18 @@
         <v>44</v>
       </c>
       <c r="F356" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G356" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="357" spans="1:7">
       <c r="A357" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B357" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C357" t="s">
         <v>247</v>
@@ -11933,21 +11930,21 @@
         <v>44</v>
       </c>
       <c r="F357" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G357" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="358" spans="1:7">
       <c r="A358" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B358" t="s">
         <v>37</v>
       </c>
       <c r="C358" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D358" t="s">
         <v>18</v>
@@ -11956,64 +11953,64 @@
         <v>44</v>
       </c>
       <c r="F358" t="s">
-        <v>83</v>
+        <v>148</v>
       </c>
       <c r="G358" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="359" spans="1:7">
       <c r="A359" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B359" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C359" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D359" t="s">
         <v>43</v>
       </c>
       <c r="E359" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F359" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G359" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="360" spans="1:7">
       <c r="A360" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B360" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C360" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D360" t="s">
         <v>25</v>
       </c>
       <c r="E360" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F360" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="G360" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="361" spans="1:7">
       <c r="A361" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B361" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C361" t="s">
         <v>46</v>
@@ -12022,21 +12019,21 @@
         <v>25</v>
       </c>
       <c r="E361" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F361" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="G361" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="362" spans="1:7">
       <c r="A362" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B362" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C362" t="s">
         <v>46</v>
@@ -12045,59 +12042,59 @@
         <v>32</v>
       </c>
       <c r="E362" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F362" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="G362" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="363" spans="1:7">
       <c r="A363" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B363" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C363" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D363" t="s">
         <v>32</v>
       </c>
       <c r="E363" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F363" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="G363" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="364" spans="1:7">
       <c r="A364" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B364" t="s">
-        <v>549</v>
+        <v>37</v>
       </c>
       <c r="C364" t="s">
-        <v>46</v>
+        <v>183</v>
       </c>
       <c r="D364" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E364" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F364" t="s">
-        <v>83</v>
+        <v>474</v>
       </c>
       <c r="G364" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="365" spans="1:7">
@@ -12105,7 +12102,7 @@
         <v>550</v>
       </c>
       <c r="B365" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C365" t="s">
         <v>282</v>
@@ -12114,13 +12111,13 @@
         <v>18</v>
       </c>
       <c r="E365" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F365" t="s">
         <v>551</v>
       </c>
       <c r="G365" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="366" spans="1:7">
@@ -12137,13 +12134,13 @@
         <v>43</v>
       </c>
       <c r="E366" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F366" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G366" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="367" spans="1:7">
@@ -12154,27 +12151,27 @@
         <v>555</v>
       </c>
       <c r="C367" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D367" t="s">
         <v>25</v>
       </c>
       <c r="E367" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F367" t="s">
         <v>556</v>
       </c>
       <c r="G367" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="368" spans="1:7">
       <c r="A368" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B368" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C368" t="s">
         <v>470</v>
@@ -12183,36 +12180,36 @@
         <v>25</v>
       </c>
       <c r="E368" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F368" t="s">
         <v>557</v>
       </c>
       <c r="G368" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="369" spans="1:7">
       <c r="A369" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B369" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C369" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D369" t="s">
         <v>25</v>
       </c>
       <c r="E369" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F369" t="s">
         <v>558</v>
       </c>
       <c r="G369" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="370" spans="1:7">
@@ -12223,27 +12220,27 @@
         <v>555</v>
       </c>
       <c r="C370" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D370" t="s">
         <v>32</v>
       </c>
       <c r="E370" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F370" t="s">
         <v>556</v>
       </c>
       <c r="G370" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="371" spans="1:7">
       <c r="A371" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B371" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C371" t="s">
         <v>470</v>
@@ -12252,59 +12249,59 @@
         <v>32</v>
       </c>
       <c r="E371" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F371" t="s">
         <v>557</v>
       </c>
       <c r="G371" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="372" spans="1:7">
       <c r="A372" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B372" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C372" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D372" t="s">
         <v>32</v>
       </c>
       <c r="E372" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F372" t="s">
         <v>558</v>
       </c>
       <c r="G372" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="373" spans="1:7">
       <c r="A373" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B373" t="s">
         <v>559</v>
       </c>
       <c r="C373" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D373" t="s">
         <v>17</v>
       </c>
       <c r="E373" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F373" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G373" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="374" spans="1:7">
@@ -12312,22 +12309,22 @@
         <v>560</v>
       </c>
       <c r="B374" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C374" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D374" t="s">
         <v>18</v>
       </c>
       <c r="E374" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F374" t="s">
         <v>561</v>
       </c>
       <c r="G374" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="375" spans="1:7">
@@ -12381,13 +12378,13 @@
         <v>566</v>
       </c>
       <c r="B377" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C377" t="s">
         <v>46</v>
       </c>
       <c r="D377" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E377" t="s">
         <v>11</v>
@@ -12430,10 +12427,10 @@
         <v>570</v>
       </c>
       <c r="C379" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D379" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E379" t="s">
         <v>11</v>
@@ -12479,7 +12476,7 @@
         <v>575</v>
       </c>
       <c r="D381" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E381" t="s">
         <v>20</v>
@@ -12525,7 +12522,7 @@
         <v>9</v>
       </c>
       <c r="D383" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E383" t="s">
         <v>20</v>
@@ -12571,7 +12568,7 @@
         <v>582</v>
       </c>
       <c r="D385" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E385" t="s">
         <v>44</v>
@@ -12594,7 +12591,7 @@
         <v>582</v>
       </c>
       <c r="D386" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E386" t="s">
         <v>44</v>
@@ -12620,7 +12617,7 @@
         <v>43</v>
       </c>
       <c r="E387" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F387" t="s">
         <v>234</v>
@@ -12640,10 +12637,10 @@
         <v>247</v>
       </c>
       <c r="D388" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E388" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F388" t="s">
         <v>234</v>
@@ -12666,7 +12663,7 @@
         <v>43</v>
       </c>
       <c r="E389" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F389" t="s">
         <v>591</v>
@@ -12689,7 +12686,7 @@
         <v>43</v>
       </c>
       <c r="E390" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F390" t="s">
         <v>595</v>
@@ -12712,7 +12709,7 @@
         <v>25</v>
       </c>
       <c r="E391" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F391" t="s">
         <v>583</v>
@@ -12735,7 +12732,7 @@
         <v>25</v>
       </c>
       <c r="E392" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F392" t="s">
         <v>600</v>
@@ -12758,7 +12755,7 @@
         <v>32</v>
       </c>
       <c r="E393" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F393" t="s">
         <v>583</v>
@@ -12781,7 +12778,7 @@
         <v>32</v>
       </c>
       <c r="E394" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F394" t="s">
         <v>600</v>
@@ -12804,7 +12801,7 @@
         <v>17</v>
       </c>
       <c r="E395" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F395" t="s">
         <v>234</v>
@@ -12824,10 +12821,10 @@
         <v>590</v>
       </c>
       <c r="D396" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E396" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F396" t="s">
         <v>591</v>
@@ -12847,10 +12844,10 @@
         <v>594</v>
       </c>
       <c r="D397" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E397" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F397" t="s">
         <v>595</v>
@@ -12910,13 +12907,13 @@
         <v>566</v>
       </c>
       <c r="B400" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C400" t="s">
         <v>46</v>
       </c>
       <c r="D400" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E400" t="s">
         <v>11</v>
@@ -12959,10 +12956,10 @@
         <v>611</v>
       </c>
       <c r="C402" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D402" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E402" t="s">
         <v>11</v>
@@ -13031,7 +13028,7 @@
         <v>575</v>
       </c>
       <c r="D405" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E405" t="s">
         <v>20</v>
@@ -13149,7 +13146,7 @@
         <v>43</v>
       </c>
       <c r="E410" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F410" t="s">
         <v>234</v>
@@ -13169,10 +13166,10 @@
         <v>582</v>
       </c>
       <c r="D411" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E411" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F411" t="s">
         <v>583</v>
@@ -13195,7 +13192,7 @@
         <v>25</v>
       </c>
       <c r="E412" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F412" t="s">
         <v>600</v>
@@ -13215,10 +13212,10 @@
         <v>582</v>
       </c>
       <c r="D413" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E413" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F413" t="s">
         <v>583</v>
@@ -13241,7 +13238,7 @@
         <v>32</v>
       </c>
       <c r="E414" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F414" t="s">
         <v>600</v>
@@ -13261,10 +13258,10 @@
         <v>247</v>
       </c>
       <c r="D415" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E415" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F415" t="s">
         <v>234</v>
@@ -13287,7 +13284,7 @@
         <v>25</v>
       </c>
       <c r="E416" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F416" t="s">
         <v>573</v>
@@ -13304,13 +13301,13 @@
         <v>621</v>
       </c>
       <c r="C417" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D417" t="s">
         <v>25</v>
       </c>
       <c r="E417" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F417" t="s">
         <v>622</v>
@@ -13333,7 +13330,7 @@
         <v>32</v>
       </c>
       <c r="E418" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F418" t="s">
         <v>573</v>
@@ -13350,13 +13347,13 @@
         <v>621</v>
       </c>
       <c r="C419" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D419" t="s">
         <v>32</v>
       </c>
       <c r="E419" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F419" t="s">
         <v>622</v>
@@ -13379,7 +13376,7 @@
         <v>17</v>
       </c>
       <c r="E420" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F420" t="s">
         <v>234</v>
@@ -13491,7 +13488,7 @@
         <v>274</v>
       </c>
       <c r="D425" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E425" t="s">
         <v>11</v>
@@ -13511,7 +13508,7 @@
         <v>634</v>
       </c>
       <c r="C426" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D426" t="s">
         <v>17</v>
@@ -13531,7 +13528,7 @@
         <v>245</v>
       </c>
       <c r="B427" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C427" t="s">
         <v>247</v>
@@ -13557,7 +13554,7 @@
         <v>636</v>
       </c>
       <c r="C428" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D428" t="s">
         <v>43</v>
@@ -13649,10 +13646,10 @@
         <v>642</v>
       </c>
       <c r="C432" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D432" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E432" t="s">
         <v>44</v>
@@ -13678,7 +13675,7 @@
         <v>25</v>
       </c>
       <c r="E433" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F433" t="s">
         <v>625</v>
@@ -13698,10 +13695,10 @@
         <v>46</v>
       </c>
       <c r="D434" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E434" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F434" t="s">
         <v>39</v>
@@ -13724,7 +13721,7 @@
         <v>17</v>
       </c>
       <c r="E435" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F435" t="s">
         <v>625</v>
@@ -13744,10 +13741,10 @@
         <v>278</v>
       </c>
       <c r="D436" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E436" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F436" t="s">
         <v>625</v>
@@ -13770,7 +13767,7 @@
         <v>43</v>
       </c>
       <c r="E437" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F437" t="s">
         <v>625</v>
@@ -13793,7 +13790,7 @@
         <v>25</v>
       </c>
       <c r="E438" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F438" t="s">
         <v>639</v>
@@ -13816,7 +13813,7 @@
         <v>25</v>
       </c>
       <c r="E439" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F439" t="s">
         <v>583</v>
@@ -13839,7 +13836,7 @@
         <v>32</v>
       </c>
       <c r="E440" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F440" t="s">
         <v>639</v>
@@ -13862,7 +13859,7 @@
         <v>32</v>
       </c>
       <c r="E441" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F441" t="s">
         <v>583</v>
@@ -13882,10 +13879,10 @@
         <v>657</v>
       </c>
       <c r="D442" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E442" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F442" t="s">
         <v>625</v>
@@ -13922,13 +13919,13 @@
         <v>585</v>
       </c>
       <c r="B444" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C444" t="s">
         <v>233</v>
       </c>
       <c r="D444" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E444" t="s">
         <v>11</v>
@@ -13971,10 +13968,10 @@
         <v>661</v>
       </c>
       <c r="C446" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D446" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E446" t="s">
         <v>11</v>
@@ -14043,7 +14040,7 @@
         <v>575</v>
       </c>
       <c r="D449" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E449" t="s">
         <v>20</v>
@@ -14066,7 +14063,7 @@
         <v>319</v>
       </c>
       <c r="D450" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E450" t="s">
         <v>20</v>
@@ -14089,7 +14086,7 @@
         <v>580</v>
       </c>
       <c r="D451" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E451" t="s">
         <v>20</v>
@@ -14155,7 +14152,7 @@
         <v>667</v>
       </c>
       <c r="C454" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D454" t="s">
         <v>25</v>
@@ -14201,7 +14198,7 @@
         <v>667</v>
       </c>
       <c r="C456" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D456" t="s">
         <v>32</v>
@@ -14230,7 +14227,7 @@
         <v>43</v>
       </c>
       <c r="E457" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F457" t="s">
         <v>243</v>
@@ -14253,7 +14250,7 @@
         <v>25</v>
       </c>
       <c r="E458" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F458" t="s">
         <v>600</v>
@@ -14276,7 +14273,7 @@
         <v>25</v>
       </c>
       <c r="E459" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F459" t="s">
         <v>573</v>
@@ -14290,16 +14287,16 @@
         <v>290</v>
       </c>
       <c r="B460" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C460" t="s">
         <v>568</v>
       </c>
       <c r="D460" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E460" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F460" t="s">
         <v>243</v>
@@ -14322,7 +14319,7 @@
         <v>32</v>
       </c>
       <c r="E461" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F461" t="s">
         <v>600</v>
@@ -14345,7 +14342,7 @@
         <v>32</v>
       </c>
       <c r="E462" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F462" t="s">
         <v>573</v>
@@ -14359,7 +14356,7 @@
         <v>245</v>
       </c>
       <c r="B463" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C463" t="s">
         <v>247</v>
@@ -14368,7 +14365,7 @@
         <v>35</v>
       </c>
       <c r="E463" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F463" t="s">
         <v>243</v>
@@ -14388,10 +14385,10 @@
         <v>247</v>
       </c>
       <c r="D464" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E464" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F464" t="s">
         <v>234</v>
@@ -14414,7 +14411,7 @@
         <v>17</v>
       </c>
       <c r="E465" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F465" t="s">
         <v>234</v>
@@ -14451,13 +14448,13 @@
         <v>585</v>
       </c>
       <c r="B467" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C467" t="s">
         <v>233</v>
       </c>
       <c r="D467" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E467" t="s">
         <v>11</v>
@@ -14500,10 +14497,10 @@
         <v>676</v>
       </c>
       <c r="C469" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D469" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E469" t="s">
         <v>11</v>
@@ -14549,7 +14546,7 @@
         <v>575</v>
       </c>
       <c r="D471" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E471" t="s">
         <v>20</v>
@@ -14572,7 +14569,7 @@
         <v>466</v>
       </c>
       <c r="D472" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E472" t="s">
         <v>20</v>
@@ -14592,10 +14589,10 @@
         <v>678</v>
       </c>
       <c r="C473" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D473" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E473" t="s">
         <v>20</v>
@@ -14802,7 +14799,7 @@
         <v>580</v>
       </c>
       <c r="D482" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E482" t="s">
         <v>44</v>
@@ -14828,7 +14825,7 @@
         <v>43</v>
       </c>
       <c r="E483" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F483" t="s">
         <v>243</v>
@@ -14842,16 +14839,16 @@
         <v>290</v>
       </c>
       <c r="B484" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C484" t="s">
         <v>568</v>
       </c>
       <c r="D484" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E484" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F484" t="s">
         <v>243</v>
@@ -14865,7 +14862,7 @@
         <v>245</v>
       </c>
       <c r="B485" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C485" t="s">
         <v>247</v>
@@ -14874,7 +14871,7 @@
         <v>35</v>
       </c>
       <c r="E485" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F485" t="s">
         <v>243</v>
@@ -14894,10 +14891,10 @@
         <v>247</v>
       </c>
       <c r="D486" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E486" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F486" t="s">
         <v>234</v>
@@ -14914,13 +14911,13 @@
         <v>8</v>
       </c>
       <c r="C487" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D487" t="s">
         <v>10</v>
       </c>
       <c r="E487" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F487" t="s">
         <v>600</v>
@@ -14943,7 +14940,7 @@
         <v>17</v>
       </c>
       <c r="E488" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F488" t="s">
         <v>234</v>
@@ -15015,7 +15012,7 @@
         <v>11</v>
       </c>
       <c r="F491" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G491" t="s">
         <v>690</v>
@@ -15029,10 +15026,10 @@
         <v>698</v>
       </c>
       <c r="C492" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D492" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E492" t="s">
         <v>11</v>
@@ -15101,7 +15098,7 @@
         <v>319</v>
       </c>
       <c r="D495" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E495" t="s">
         <v>20</v>
@@ -15141,13 +15138,13 @@
         <v>705</v>
       </c>
       <c r="B497" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C497" t="s">
         <v>46</v>
       </c>
       <c r="D497" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E497" t="s">
         <v>44</v>
@@ -15167,10 +15164,10 @@
         <v>37</v>
       </c>
       <c r="C498" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D498" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E498" t="s">
         <v>44</v>
@@ -15190,7 +15187,7 @@
         <v>37</v>
       </c>
       <c r="C499" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D499" t="s">
         <v>35</v>
@@ -15242,7 +15239,7 @@
         <v>25</v>
       </c>
       <c r="E501" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F501" t="s">
         <v>45</v>
@@ -15265,7 +15262,7 @@
         <v>32</v>
       </c>
       <c r="E502" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F502" t="s">
         <v>45</v>
@@ -15288,7 +15285,7 @@
         <v>17</v>
       </c>
       <c r="E503" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F503" t="s">
         <v>45</v>
@@ -15311,7 +15308,7 @@
         <v>18</v>
       </c>
       <c r="E504" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F504" t="s">
         <v>45</v>
@@ -15334,7 +15331,7 @@
         <v>10</v>
       </c>
       <c r="E505" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F505" t="s">
         <v>46</v>
@@ -15357,7 +15354,7 @@
         <v>18</v>
       </c>
       <c r="E506" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F506" t="s">
         <v>46</v>
@@ -15400,7 +15397,7 @@
         <v>321</v>
       </c>
       <c r="D508" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E508" t="s">
         <v>11</v>
@@ -15423,7 +15420,7 @@
         <v>46</v>
       </c>
       <c r="D509" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E509" t="s">
         <v>11</v>
@@ -15469,7 +15466,7 @@
         <v>295</v>
       </c>
       <c r="D511" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E511" t="s">
         <v>11</v>
@@ -15538,7 +15535,7 @@
         <v>319</v>
       </c>
       <c r="D514" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E514" t="s">
         <v>20</v>
@@ -15561,7 +15558,7 @@
         <v>46</v>
       </c>
       <c r="D515" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E515" t="s">
         <v>44</v>
@@ -15584,7 +15581,7 @@
         <v>334</v>
       </c>
       <c r="D516" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E516" t="s">
         <v>44</v>
@@ -15601,7 +15598,7 @@
         <v>323</v>
       </c>
       <c r="B517" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C517" t="s">
         <v>324</v>
@@ -15653,7 +15650,7 @@
         <v>324</v>
       </c>
       <c r="D519" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E519" t="s">
         <v>44</v>
@@ -15679,7 +15676,7 @@
         <v>35</v>
       </c>
       <c r="E520" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F520" t="s">
         <v>50</v>
@@ -15702,7 +15699,7 @@
         <v>18</v>
       </c>
       <c r="E521" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F521" t="s">
         <v>50</v>
@@ -15725,7 +15722,7 @@
         <v>35</v>
       </c>
       <c r="E522" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F522" t="s">
         <v>50</v>
@@ -15739,7 +15736,7 @@
         <v>736</v>
       </c>
       <c r="B523" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C523" t="s">
         <v>334</v>
@@ -15748,7 +15745,7 @@
         <v>18</v>
       </c>
       <c r="E523" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F523" t="s">
         <v>50</v>
@@ -15762,7 +15759,7 @@
         <v>737</v>
       </c>
       <c r="B524" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C524" t="s">
         <v>274</v>
@@ -15774,7 +15771,7 @@
         <v>11</v>
       </c>
       <c r="F524" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G524" t="s">
         <v>738</v>
@@ -15797,7 +15794,7 @@
         <v>11</v>
       </c>
       <c r="F525" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G525" t="s">
         <v>738</v>
@@ -15820,7 +15817,7 @@
         <v>11</v>
       </c>
       <c r="F526" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G526" t="s">
         <v>738</v>
@@ -15866,7 +15863,7 @@
         <v>20</v>
       </c>
       <c r="F528" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G528" t="s">
         <v>738</v>
@@ -15883,7 +15880,7 @@
         <v>319</v>
       </c>
       <c r="D529" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E529" t="s">
         <v>20</v>
@@ -15912,7 +15909,7 @@
         <v>44</v>
       </c>
       <c r="F530" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G530" t="s">
         <v>738</v>
@@ -15929,13 +15926,13 @@
         <v>331</v>
       </c>
       <c r="D531" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E531" t="s">
         <v>44</v>
       </c>
       <c r="F531" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G531" t="s">
         <v>738</v>
@@ -15952,13 +15949,13 @@
         <v>331</v>
       </c>
       <c r="D532" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E532" t="s">
         <v>44</v>
       </c>
       <c r="F532" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G532" t="s">
         <v>738</v>
@@ -15981,7 +15978,7 @@
         <v>44</v>
       </c>
       <c r="F533" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G533" t="s">
         <v>738</v>
@@ -16001,10 +15998,10 @@
         <v>43</v>
       </c>
       <c r="E534" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F534" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G534" t="s">
         <v>738</v>
@@ -16021,13 +16018,13 @@
         <v>337</v>
       </c>
       <c r="D535" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E535" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F535" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G535" t="s">
         <v>738</v>
@@ -16047,7 +16044,7 @@
         <v>756</v>
       </c>
       <c r="E536" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F536" t="s">
         <v>757</v>
@@ -16067,10 +16064,10 @@
         <v>447</v>
       </c>
       <c r="D537" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E537" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F537" t="s">
         <v>759</v>
@@ -16093,7 +16090,7 @@
         <v>25</v>
       </c>
       <c r="E538" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F538" t="s">
         <v>762</v>
@@ -16113,10 +16110,10 @@
         <v>447</v>
       </c>
       <c r="D539" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E539" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F539" t="s">
         <v>759</v>
@@ -16139,7 +16136,7 @@
         <v>32</v>
       </c>
       <c r="E540" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F540" t="s">
         <v>762</v>
@@ -16162,7 +16159,7 @@
         <v>765</v>
       </c>
       <c r="E541" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F541" t="s">
         <v>757</v>
@@ -16188,7 +16185,7 @@
         <v>11</v>
       </c>
       <c r="F542" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G542" t="s">
         <v>769</v>
@@ -16205,7 +16202,7 @@
         <v>580</v>
       </c>
       <c r="D543" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E543" t="s">
         <v>11</v>
@@ -16257,7 +16254,7 @@
         <v>11</v>
       </c>
       <c r="F545" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G545" t="s">
         <v>769</v>
@@ -16274,13 +16271,13 @@
         <v>768</v>
       </c>
       <c r="D546" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E546" t="s">
         <v>11</v>
       </c>
       <c r="F546" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G546" t="s">
         <v>769</v>
@@ -16303,7 +16300,7 @@
         <v>20</v>
       </c>
       <c r="F547" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G547" t="s">
         <v>769</v>
@@ -16326,7 +16323,7 @@
         <v>20</v>
       </c>
       <c r="F548" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G548" t="s">
         <v>769</v>
@@ -16343,7 +16340,7 @@
         <v>319</v>
       </c>
       <c r="D549" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E549" t="s">
         <v>20</v>
@@ -16363,7 +16360,7 @@
         <v>785</v>
       </c>
       <c r="C550" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D550" t="s">
         <v>43</v>
@@ -16395,7 +16392,7 @@
         <v>44</v>
       </c>
       <c r="F551" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G551" t="s">
         <v>769</v>
@@ -16418,7 +16415,7 @@
         <v>44</v>
       </c>
       <c r="F552" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G552" t="s">
         <v>769</v>
@@ -16441,7 +16438,7 @@
         <v>44</v>
       </c>
       <c r="F553" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G553" t="s">
         <v>769</v>
@@ -16458,7 +16455,7 @@
         <v>795</v>
       </c>
       <c r="D554" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E554" t="s">
         <v>44</v>
@@ -16484,10 +16481,10 @@
         <v>17</v>
       </c>
       <c r="E555" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F555" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G555" t="s">
         <v>769</v>
@@ -16504,13 +16501,13 @@
         <v>795</v>
       </c>
       <c r="D556" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E556" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F556" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G556" t="s">
         <v>769</v>
@@ -16530,7 +16527,7 @@
         <v>25</v>
       </c>
       <c r="E557" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F557" t="s">
         <v>772</v>
@@ -16550,13 +16547,13 @@
         <v>580</v>
       </c>
       <c r="D558" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E558" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F558" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G558" t="s">
         <v>769</v>
@@ -16602,7 +16599,7 @@
         <v>11</v>
       </c>
       <c r="F560" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G560" t="s">
         <v>807</v>
@@ -16619,13 +16616,13 @@
         <v>307</v>
       </c>
       <c r="D561" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E561" t="s">
         <v>11</v>
       </c>
       <c r="F561" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G561" t="s">
         <v>807</v>
@@ -16671,7 +16668,7 @@
         <v>20</v>
       </c>
       <c r="F563" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G563" t="s">
         <v>807</v>
@@ -16688,7 +16685,7 @@
         <v>319</v>
       </c>
       <c r="D564" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E564" t="s">
         <v>20</v>
@@ -16717,7 +16714,7 @@
         <v>44</v>
       </c>
       <c r="F565" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G565" t="s">
         <v>807</v>
@@ -16740,7 +16737,7 @@
         <v>44</v>
       </c>
       <c r="F566" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G566" t="s">
         <v>807</v>
@@ -16780,7 +16777,7 @@
         <v>307</v>
       </c>
       <c r="D568" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E568" t="s">
         <v>44</v>
@@ -16797,7 +16794,7 @@
         <v>818</v>
       </c>
       <c r="B569" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C569" t="s">
         <v>331</v>
@@ -16806,7 +16803,7 @@
         <v>10</v>
       </c>
       <c r="E569" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F569" t="s">
         <v>314</v>
@@ -16820,19 +16817,19 @@
         <v>819</v>
       </c>
       <c r="B570" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C570" t="s">
         <v>337</v>
       </c>
       <c r="D570" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E570" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F570" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G570" t="s">
         <v>807</v>
@@ -16852,10 +16849,10 @@
         <v>35</v>
       </c>
       <c r="E571" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F571" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G571" t="s">
         <v>807</v>
@@ -16875,7 +16872,7 @@
         <v>18</v>
       </c>
       <c r="E572" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F572" t="s">
         <v>314</v>
@@ -16892,16 +16889,16 @@
         <v>822</v>
       </c>
       <c r="C573" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D573" t="s">
         <v>43</v>
       </c>
       <c r="E573" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F573" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G573" t="s">
         <v>807</v>
@@ -16915,16 +16912,16 @@
         <v>824</v>
       </c>
       <c r="C574" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D574" t="s">
         <v>17</v>
       </c>
       <c r="E574" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F574" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G574" t="s">
         <v>807</v>
@@ -16941,13 +16938,13 @@
         <v>46</v>
       </c>
       <c r="D575" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E575" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F575" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G575" t="s">
         <v>807</v>
@@ -16958,7 +16955,7 @@
         <v>827</v>
       </c>
       <c r="B576" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C576" t="s">
         <v>46</v>
@@ -16970,7 +16967,7 @@
         <v>11</v>
       </c>
       <c r="F576" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G576" t="s">
         <v>828</v>
@@ -17047,13 +17044,13 @@
     </row>
     <row r="580" spans="1:7">
       <c r="A580" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B580" t="s">
         <v>831</v>
       </c>
       <c r="C580" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D580" t="s">
         <v>21</v>
@@ -17062,7 +17059,7 @@
         <v>11</v>
       </c>
       <c r="F580" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G580" t="s">
         <v>828</v>
@@ -17070,13 +17067,13 @@
     </row>
     <row r="581" spans="1:7">
       <c r="A581" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B581" t="s">
         <v>831</v>
       </c>
       <c r="C581" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D581" t="s">
         <v>25</v>
@@ -17085,7 +17082,7 @@
         <v>11</v>
       </c>
       <c r="F581" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G581" t="s">
         <v>828</v>
@@ -17093,13 +17090,13 @@
     </row>
     <row r="582" spans="1:7">
       <c r="A582" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B582" t="s">
         <v>832</v>
       </c>
       <c r="C582" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D582" t="s">
         <v>25</v>
@@ -17108,7 +17105,7 @@
         <v>11</v>
       </c>
       <c r="F582" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G582" t="s">
         <v>828</v>
@@ -17131,7 +17128,7 @@
         <v>11</v>
       </c>
       <c r="F583" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G583" t="s">
         <v>828</v>
@@ -17154,7 +17151,7 @@
         <v>11</v>
       </c>
       <c r="F584" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G584" t="s">
         <v>828</v>
@@ -17177,7 +17174,7 @@
         <v>11</v>
       </c>
       <c r="F585" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G585" t="s">
         <v>828</v>
@@ -17191,7 +17188,7 @@
         <v>831</v>
       </c>
       <c r="C586" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D586" t="s">
         <v>32</v>
@@ -17200,7 +17197,7 @@
         <v>11</v>
       </c>
       <c r="F586" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G586" t="s">
         <v>828</v>
@@ -17208,13 +17205,13 @@
     </row>
     <row r="587" spans="1:7">
       <c r="A587" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B587" t="s">
         <v>836</v>
       </c>
       <c r="C587" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D587" t="s">
         <v>17</v>
@@ -17223,7 +17220,7 @@
         <v>11</v>
       </c>
       <c r="F587" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G587" t="s">
         <v>828</v>
@@ -17237,16 +17234,16 @@
         <v>831</v>
       </c>
       <c r="C588" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D588" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E588" t="s">
         <v>11</v>
       </c>
       <c r="F588" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G588" t="s">
         <v>828</v>
@@ -17263,13 +17260,13 @@
         <v>367</v>
       </c>
       <c r="D589" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E589" t="s">
         <v>11</v>
       </c>
       <c r="F589" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G589" t="s">
         <v>828</v>
@@ -17283,16 +17280,16 @@
         <v>832</v>
       </c>
       <c r="C590" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D590" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E590" t="s">
         <v>11</v>
       </c>
       <c r="F590" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G590" t="s">
         <v>828</v>
@@ -17306,16 +17303,16 @@
         <v>832</v>
       </c>
       <c r="C591" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D591" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E591" t="s">
         <v>11</v>
       </c>
       <c r="F591" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G591" t="s">
         <v>828</v>
@@ -17585,7 +17582,7 @@
         <v>46</v>
       </c>
       <c r="D603" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E603" t="s">
         <v>20</v>
@@ -17608,7 +17605,7 @@
         <v>853</v>
       </c>
       <c r="D604" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E604" t="s">
         <v>20</v>
@@ -17637,7 +17634,7 @@
         <v>44</v>
       </c>
       <c r="F605" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G605" t="s">
         <v>828</v>
@@ -17645,13 +17642,13 @@
     </row>
     <row r="606" spans="1:7">
       <c r="A606" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B606" t="s">
         <v>831</v>
       </c>
       <c r="C606" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D606" t="s">
         <v>21</v>
@@ -17660,7 +17657,7 @@
         <v>44</v>
       </c>
       <c r="F606" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G606" t="s">
         <v>828</v>
@@ -17668,13 +17665,13 @@
     </row>
     <row r="607" spans="1:7">
       <c r="A607" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B607" t="s">
         <v>857</v>
       </c>
       <c r="C607" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D607" t="s">
         <v>25</v>
@@ -17683,7 +17680,7 @@
         <v>44</v>
       </c>
       <c r="F607" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G607" t="s">
         <v>828</v>
@@ -17737,13 +17734,13 @@
     </row>
     <row r="610" spans="1:7">
       <c r="A610" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B610" t="s">
         <v>857</v>
       </c>
       <c r="C610" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D610" t="s">
         <v>32</v>
@@ -17752,7 +17749,7 @@
         <v>44</v>
       </c>
       <c r="F610" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G610" t="s">
         <v>828</v>
@@ -17806,7 +17803,7 @@
     </row>
     <row r="613" spans="1:7">
       <c r="A613" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B613" t="s">
         <v>37</v>
@@ -17821,7 +17818,7 @@
         <v>44</v>
       </c>
       <c r="F613" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G613" t="s">
         <v>828</v>
@@ -17838,13 +17835,13 @@
         <v>46</v>
       </c>
       <c r="D614" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E614" t="s">
         <v>44</v>
       </c>
       <c r="F614" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G614" t="s">
         <v>828</v>
@@ -17858,16 +17855,16 @@
         <v>832</v>
       </c>
       <c r="C615" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D615" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E615" t="s">
         <v>44</v>
       </c>
       <c r="F615" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G615" t="s">
         <v>828</v>
@@ -17881,16 +17878,16 @@
         <v>863</v>
       </c>
       <c r="C616" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D616" t="s">
         <v>43</v>
       </c>
       <c r="E616" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F616" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G616" t="s">
         <v>828</v>
@@ -17898,22 +17895,22 @@
     </row>
     <row r="617" spans="1:7">
       <c r="A617" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B617" t="s">
         <v>831</v>
       </c>
       <c r="C617" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D617" t="s">
         <v>21</v>
       </c>
       <c r="E617" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F617" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G617" t="s">
         <v>828</v>
@@ -17924,19 +17921,19 @@
         <v>864</v>
       </c>
       <c r="B618" t="s">
-        <v>834</v>
+        <v>51</v>
       </c>
       <c r="C618" t="s">
         <v>853</v>
       </c>
       <c r="D618" t="s">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="E618" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F618" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="G618" t="s">
         <v>828</v>
@@ -17956,10 +17953,10 @@
         <v>25</v>
       </c>
       <c r="E619" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F619" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G619" t="s">
         <v>828</v>
@@ -17973,13 +17970,13 @@
         <v>843</v>
       </c>
       <c r="C620" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D620" t="s">
         <v>25</v>
       </c>
       <c r="E620" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F620" t="s">
         <v>867</v>
@@ -17990,7 +17987,7 @@
     </row>
     <row r="621" spans="1:7">
       <c r="A621" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B621" t="s">
         <v>868</v>
@@ -18002,10 +17999,10 @@
         <v>32</v>
       </c>
       <c r="E621" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F621" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G621" t="s">
         <v>828</v>
@@ -18025,10 +18022,10 @@
         <v>32</v>
       </c>
       <c r="E622" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F622" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G622" t="s">
         <v>828</v>
@@ -18042,13 +18039,13 @@
         <v>843</v>
       </c>
       <c r="C623" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D623" t="s">
         <v>32</v>
       </c>
       <c r="E623" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F623" t="s">
         <v>867</v>
@@ -18065,16 +18062,16 @@
         <v>870</v>
       </c>
       <c r="C624" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D624" t="s">
         <v>17</v>
       </c>
       <c r="E624" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F624" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G624" t="s">
         <v>828</v>
@@ -18082,7 +18079,7 @@
     </row>
     <row r="625" spans="1:7">
       <c r="A625" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B625" t="s">
         <v>871</v>
@@ -18091,13 +18088,13 @@
         <v>367</v>
       </c>
       <c r="D625" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E625" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F625" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G625" t="s">
         <v>828</v>
@@ -18111,16 +18108,16 @@
         <v>37</v>
       </c>
       <c r="C626" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D626" t="s">
         <v>10</v>
       </c>
       <c r="E626" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F626" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G626" t="s">
         <v>828</v>
@@ -18140,7 +18137,7 @@
         <v>25</v>
       </c>
       <c r="E627" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F627" t="s">
         <v>873</v>
@@ -18163,10 +18160,10 @@
         <v>25</v>
       </c>
       <c r="E628" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F628" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G628" t="s">
         <v>828</v>
@@ -18180,16 +18177,16 @@
         <v>831</v>
       </c>
       <c r="C629" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D629" t="s">
         <v>25</v>
       </c>
       <c r="E629" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F629" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G629" t="s">
         <v>828</v>
@@ -18200,19 +18197,19 @@
         <v>449</v>
       </c>
       <c r="B630" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C630" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D630" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E630" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F630" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G630" t="s">
         <v>828</v>
@@ -18232,10 +18229,10 @@
         <v>32</v>
       </c>
       <c r="E631" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F631" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G631" t="s">
         <v>828</v>
@@ -18243,10 +18240,10 @@
     </row>
     <row r="632" spans="1:7">
       <c r="A632" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B632" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C632" t="s">
         <v>46</v>
@@ -18255,10 +18252,10 @@
         <v>35</v>
       </c>
       <c r="E632" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F632" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="G632" t="s">
         <v>828</v>
@@ -18272,16 +18269,16 @@
         <v>831</v>
       </c>
       <c r="C633" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D633" t="s">
         <v>17</v>
       </c>
       <c r="E633" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F633" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G633" t="s">
         <v>828</v>
@@ -18295,16 +18292,16 @@
         <v>877</v>
       </c>
       <c r="C634" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D634" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E634" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F634" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G634" t="s">
         <v>828</v>
@@ -18315,10 +18312,10 @@
         <v>878</v>
       </c>
       <c r="B635" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C635" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D635" t="s">
         <v>10</v>
@@ -18338,10 +18335,10 @@
         <v>550</v>
       </c>
       <c r="B636" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C636" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D636" t="s">
         <v>10</v>
@@ -18364,16 +18361,16 @@
         <v>37</v>
       </c>
       <c r="C637" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D637" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E637" t="s">
         <v>11</v>
       </c>
       <c r="F637" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G637" t="s">
         <v>879</v>
@@ -18381,22 +18378,22 @@
     </row>
     <row r="638" spans="1:7">
       <c r="A638" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B638" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C638" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D638" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E638" t="s">
         <v>11</v>
       </c>
       <c r="F638" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G638" t="s">
         <v>879</v>
@@ -18404,13 +18401,13 @@
     </row>
     <row r="639" spans="1:7">
       <c r="A639" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B639" t="s">
         <v>37</v>
       </c>
       <c r="C639" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D639" t="s">
         <v>35</v>
@@ -18430,10 +18427,10 @@
         <v>881</v>
       </c>
       <c r="B640" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C640" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D640" t="s">
         <v>18</v>
@@ -18453,10 +18450,10 @@
         <v>882</v>
       </c>
       <c r="B641" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C641" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D641" t="s">
         <v>18</v>
@@ -18479,7 +18476,7 @@
         <v>884</v>
       </c>
       <c r="C642" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D642" t="s">
         <v>17</v>
@@ -18499,10 +18496,10 @@
         <v>885</v>
       </c>
       <c r="B643" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C643" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D643" t="s">
         <v>10</v>
@@ -18519,13 +18516,13 @@
     </row>
     <row r="644" spans="1:7">
       <c r="A644" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B644" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C644" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D644" t="s">
         <v>10</v>
@@ -18551,7 +18548,7 @@
         <v>310</v>
       </c>
       <c r="D645" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E645" t="s">
         <v>44</v>
@@ -18565,16 +18562,16 @@
     </row>
     <row r="646" spans="1:7">
       <c r="A646" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B646" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C646" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D646" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E646" t="s">
         <v>44</v>
@@ -18594,7 +18591,7 @@
         <v>37</v>
       </c>
       <c r="C647" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D647" t="s">
         <v>35</v>
@@ -18611,13 +18608,13 @@
     </row>
     <row r="648" spans="1:7">
       <c r="A648" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B648" t="s">
         <v>37</v>
       </c>
       <c r="C648" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D648" t="s">
         <v>18</v>
@@ -18626,7 +18623,7 @@
         <v>44</v>
       </c>
       <c r="F648" t="s">
-        <v>234</v>
+        <v>148</v>
       </c>
       <c r="G648" t="s">
         <v>879</v>
@@ -18637,16 +18634,16 @@
         <v>888</v>
       </c>
       <c r="B649" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C649" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D649" t="s">
         <v>10</v>
       </c>
       <c r="E649" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F649" t="s">
         <v>45</v>
@@ -18660,7 +18657,7 @@
         <v>889</v>
       </c>
       <c r="B650" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C650" t="s">
         <v>890</v>
@@ -18669,7 +18666,7 @@
         <v>10</v>
       </c>
       <c r="E650" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F650" t="s">
         <v>329</v>
@@ -18689,13 +18686,13 @@
         <v>890</v>
       </c>
       <c r="D651" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E651" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F651" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G651" t="s">
         <v>879</v>
@@ -18709,13 +18706,13 @@
         <v>8</v>
       </c>
       <c r="C652" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D652" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E652" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F652" t="s">
         <v>893</v>
@@ -18735,13 +18732,13 @@
         <v>890</v>
       </c>
       <c r="D653" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E653" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F653" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G653" t="s">
         <v>879</v>
@@ -18755,13 +18752,13 @@
         <v>8</v>
       </c>
       <c r="C654" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D654" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E654" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F654" t="s">
         <v>893</v>
@@ -18778,13 +18775,13 @@
         <v>37</v>
       </c>
       <c r="C655" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D655" t="s">
         <v>35</v>
       </c>
       <c r="E655" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F655" t="s">
         <v>329</v>
@@ -18807,7 +18804,7 @@
         <v>18</v>
       </c>
       <c r="E656" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F656" t="s">
         <v>329</v>
@@ -18824,13 +18821,13 @@
         <v>8</v>
       </c>
       <c r="C657" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D657" t="s">
         <v>10</v>
       </c>
       <c r="E657" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F657" t="s">
         <v>899</v>
@@ -18844,7 +18841,7 @@
         <v>900</v>
       </c>
       <c r="B658" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C658" t="s">
         <v>890</v>
@@ -18853,7 +18850,7 @@
         <v>10</v>
       </c>
       <c r="E658" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F658" t="s">
         <v>243</v>
@@ -18873,10 +18870,10 @@
         <v>470</v>
       </c>
       <c r="D659" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E659" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F659" t="s">
         <v>902</v>
@@ -18896,13 +18893,13 @@
         <v>46</v>
       </c>
       <c r="D660" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E660" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F660" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G660" t="s">
         <v>879</v>
@@ -18919,10 +18916,10 @@
         <v>470</v>
       </c>
       <c r="D661" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E661" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F661" t="s">
         <v>902</v>
@@ -18942,13 +18939,13 @@
         <v>46</v>
       </c>
       <c r="D662" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="E662" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F662" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G662" t="s">
         <v>879</v>
@@ -18968,7 +18965,7 @@
         <v>35</v>
       </c>
       <c r="E663" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F663" t="s">
         <v>329</v>
@@ -18985,13 +18982,13 @@
         <v>8</v>
       </c>
       <c r="C664" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D664" t="s">
         <v>18</v>
       </c>
       <c r="E664" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F664" t="s">
         <v>907</v>
@@ -19005,7 +19002,7 @@
         <v>908</v>
       </c>
       <c r="B665" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C665" t="s">
         <v>890</v>
@@ -19014,7 +19011,7 @@
         <v>18</v>
       </c>
       <c r="E665" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F665" t="s">
         <v>243</v>
@@ -19024,9 +19021,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G665" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$665</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -464,15 +467,15 @@
     <t>TP-Electricité fondamentale -G2</t>
   </si>
   <si>
+    <t>TP-Dessin Assisté par Ordinateur -G2</t>
+  </si>
+  <si>
     <t>Cours-E&amp;e-ING2RSE</t>
   </si>
   <si>
     <t>TP-Dessin Assisté par Ordinateur -G1-</t>
   </si>
   <si>
-    <t>TP-Dessin Assisté par Ordinateur -G2</t>
-  </si>
-  <si>
     <t>Amphi 08</t>
   </si>
   <si>
@@ -548,7 +551,7 @@
     <t>Cours-Automates programmables industriels PLC</t>
   </si>
   <si>
-    <t>MILOUA FETHI</t>
+    <t>AREZKI MOUFOK</t>
   </si>
   <si>
     <t>TD-Automates programmables industriels PLC</t>
@@ -5452,22 +5455,22 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="B76" t="s">
-        <v>145</v>
+        <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D76" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E76" t="s">
         <v>20</v>
       </c>
       <c r="F76" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="G76" t="s">
         <v>139</v>
@@ -5475,22 +5478,22 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
+        <v>106</v>
+      </c>
+      <c r="B77" t="s">
         <v>146</v>
       </c>
-      <c r="B77" t="s">
-        <v>8</v>
-      </c>
       <c r="C77" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D77" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E77" t="s">
         <v>20</v>
       </c>
       <c r="F77" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="G77" t="s">
         <v>139</v>
@@ -5504,16 +5507,16 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D78" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E78" t="s">
         <v>20</v>
       </c>
       <c r="F78" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G78" t="s">
         <v>139</v>
@@ -19021,6 +19024,9 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G665" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4643" uniqueCount="893">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4643" uniqueCount="894">
   <si>
     <t>Enseignements</t>
   </si>
@@ -2706,6 +2706,9 @@
   </si>
   <si>
     <t>BENSEDDIK NADIA</t>
+  </si>
+  <si>
+    <t>MAHKOUKA ZAZA</t>
   </si>
 </sst>
 </file>
@@ -3674,7 +3677,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G664"/>
+  <dimension ref="A1:G665"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -18930,8 +18933,10 @@
       <c r="C664" t="s">
         <v>892</v>
       </c>
-      <c r="D664" t="s">
-        <v>22</v>
+    </row>
+    <row r="665" spans="1:7">
+      <c r="C665" t="s">
+        <v>893</v>
       </c>
     </row>
   </sheetData>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -9,9 +9,6 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$675</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -30,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4725" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4725" uniqueCount="893">
   <si>
     <t>Enseignements</t>
   </si>
@@ -1457,6 +1454,9 @@
     <t>TP-PPYTH-L2ELT</t>
   </si>
   <si>
+    <t>BERREKHCHI BERRAHMA NEILA</t>
+  </si>
+  <si>
     <t>Labo A8/SG12</t>
   </si>
   <si>
@@ -1466,24 +1466,24 @@
     <t>Labo A8/SG11</t>
   </si>
   <si>
+    <t>TP-Electronique &amp; Electrotechnique</t>
+  </si>
+  <si>
+    <t>TP-ELN1/ELT1-L2ELT</t>
+  </si>
+  <si>
+    <t>LATRECHE MOKHTAR</t>
+  </si>
+  <si>
+    <t>Labo A1/SG11</t>
+  </si>
+  <si>
     <t>BENGRIT MALIKA</t>
   </si>
   <si>
     <t>Labo A9/SG22</t>
   </si>
   <si>
-    <t>TP-Electronique &amp; Electrotechnique</t>
-  </si>
-  <si>
-    <t>TP-ELN1/ELT1-L2ELT</t>
-  </si>
-  <si>
-    <t>LATRECHE MOKHTAR</t>
-  </si>
-  <si>
-    <t>Labo A1/SG11</t>
-  </si>
-  <si>
     <t>TAIBI SOUMIA</t>
   </si>
   <si>
@@ -1499,10 +1499,10 @@
     <t>TP-OV-L2ELT</t>
   </si>
   <si>
+    <t>Labo A1/SG12</t>
+  </si>
+  <si>
     <t>Labo A9/SG21</t>
-  </si>
-  <si>
-    <t>Labo A1/SG12</t>
   </si>
   <si>
     <t>TD-Analyse 3-G1</t>
@@ -10838,7 +10838,7 @@
         <v>474</v>
       </c>
       <c r="C312" t="s">
-        <v>55</v>
+        <v>475</v>
       </c>
       <c r="D312" t="s">
         <v>38</v>
@@ -10847,7 +10847,7 @@
         <v>22</v>
       </c>
       <c r="F312" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G312" t="s">
         <v>459</v>
@@ -10870,7 +10870,7 @@
         <v>22</v>
       </c>
       <c r="F313" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G313" t="s">
         <v>459</v>
@@ -10884,7 +10884,7 @@
         <v>474</v>
       </c>
       <c r="C314" t="s">
-        <v>55</v>
+        <v>475</v>
       </c>
       <c r="D314" t="s">
         <v>43</v>
@@ -10893,7 +10893,7 @@
         <v>22</v>
       </c>
       <c r="F314" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G314" t="s">
         <v>459</v>
@@ -10901,13 +10901,13 @@
     </row>
     <row r="315" spans="1:7">
       <c r="A315" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B315" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="C315" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D315" t="s">
         <v>27</v>
@@ -10916,7 +10916,7 @@
         <v>28</v>
       </c>
       <c r="F315" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="G315" t="s">
         <v>459</v>
@@ -10924,13 +10924,13 @@
     </row>
     <row r="316" spans="1:7">
       <c r="A316" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="B316" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="C316" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D316" t="s">
         <v>27</v>
@@ -10939,7 +10939,7 @@
         <v>28</v>
       </c>
       <c r="F316" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G316" t="s">
         <v>459</v>
@@ -10953,7 +10953,7 @@
         <v>19</v>
       </c>
       <c r="C317" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D317" t="s">
         <v>10</v>
@@ -10970,7 +10970,7 @@
     </row>
     <row r="318" spans="1:7">
       <c r="A318" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B318" t="s">
         <v>30</v>
@@ -11008,7 +11008,7 @@
         <v>28</v>
       </c>
       <c r="F319" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G319" t="s">
         <v>459</v>
@@ -11054,7 +11054,7 @@
         <v>28</v>
       </c>
       <c r="F321" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G321" t="s">
         <v>459</v>
@@ -11065,7 +11065,7 @@
         <v>471</v>
       </c>
       <c r="B322" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C322" t="s">
         <v>55</v>
@@ -11077,7 +11077,7 @@
         <v>28</v>
       </c>
       <c r="F322" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G322" t="s">
         <v>459</v>
@@ -11088,7 +11088,7 @@
         <v>471</v>
       </c>
       <c r="B323" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C323" t="s">
         <v>55</v>
@@ -11100,7 +11100,7 @@
         <v>28</v>
       </c>
       <c r="F323" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G323" t="s">
         <v>459</v>
@@ -11108,13 +11108,13 @@
     </row>
     <row r="324" spans="1:7">
       <c r="A324" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B324" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="C324" t="s">
-        <v>478</v>
+        <v>55</v>
       </c>
       <c r="D324" t="s">
         <v>43</v>
@@ -11123,7 +11123,7 @@
         <v>28</v>
       </c>
       <c r="F324" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G324" t="s">
         <v>459</v>
@@ -11134,7 +11134,7 @@
         <v>471</v>
       </c>
       <c r="B325" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C325" t="s">
         <v>55</v>
@@ -11146,7 +11146,7 @@
         <v>28</v>
       </c>
       <c r="F325" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G325" t="s">
         <v>459</v>
@@ -11154,13 +11154,13 @@
     </row>
     <row r="326" spans="1:7">
       <c r="A326" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="B326" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="C326" t="s">
-        <v>55</v>
+        <v>481</v>
       </c>
       <c r="D326" t="s">
         <v>43</v>
@@ -11169,7 +11169,7 @@
         <v>28</v>
       </c>
       <c r="F326" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="G326" t="s">
         <v>459</v>
@@ -11177,13 +11177,13 @@
     </row>
     <row r="327" spans="1:7">
       <c r="A327" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="B327" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="C327" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D327" t="s">
         <v>43</v>
@@ -11192,7 +11192,7 @@
         <v>28</v>
       </c>
       <c r="F327" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G327" t="s">
         <v>459</v>
@@ -11223,13 +11223,13 @@
     </row>
     <row r="329" spans="1:7">
       <c r="A329" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B329" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C329" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D329" t="s">
         <v>111</v>
@@ -11246,13 +11246,13 @@
     </row>
     <row r="330" spans="1:7">
       <c r="A330" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B330" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C330" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D330" t="s">
         <v>111</v>
@@ -11269,13 +11269,13 @@
     </row>
     <row r="331" spans="1:7">
       <c r="A331" t="s">
+        <v>498</v>
+      </c>
+      <c r="B331" t="s">
+        <v>496</v>
+      </c>
+      <c r="C331" t="s">
         <v>497</v>
-      </c>
-      <c r="B331" t="s">
-        <v>495</v>
-      </c>
-      <c r="C331" t="s">
-        <v>496</v>
       </c>
       <c r="D331" t="s">
         <v>78</v>
@@ -11292,13 +11292,13 @@
     </row>
     <row r="332" spans="1:7">
       <c r="A332" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B332" t="s">
         <v>30</v>
       </c>
       <c r="C332" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D332" t="s">
         <v>21</v>
@@ -11315,13 +11315,13 @@
     </row>
     <row r="333" spans="1:7">
       <c r="A333" t="s">
+        <v>479</v>
+      </c>
+      <c r="B333" t="s">
         <v>480</v>
       </c>
-      <c r="B333" t="s">
-        <v>481</v>
-      </c>
       <c r="C333" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D333" t="s">
         <v>43</v>
@@ -11330,7 +11330,7 @@
         <v>47</v>
       </c>
       <c r="F333" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G333" t="s">
         <v>459</v>
@@ -11338,10 +11338,10 @@
     </row>
     <row r="334" spans="1:7">
       <c r="A334" t="s">
+        <v>479</v>
+      </c>
+      <c r="B334" t="s">
         <v>480</v>
-      </c>
-      <c r="B334" t="s">
-        <v>481</v>
       </c>
       <c r="C334" t="s">
         <v>168</v>
@@ -11353,7 +11353,7 @@
         <v>47</v>
       </c>
       <c r="F334" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G334" t="s">
         <v>459</v>
@@ -11361,13 +11361,13 @@
     </row>
     <row r="335" spans="1:7">
       <c r="A335" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B335" t="s">
         <v>19</v>
       </c>
       <c r="C335" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D335" t="s">
         <v>46</v>
@@ -11384,7 +11384,7 @@
     </row>
     <row r="336" spans="1:7">
       <c r="A336" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B336" t="s">
         <v>30</v>
@@ -11407,7 +11407,7 @@
     </row>
     <row r="337" spans="1:7">
       <c r="A337" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B337" t="s">
         <v>30</v>
@@ -11430,7 +11430,7 @@
     </row>
     <row r="338" spans="1:7">
       <c r="A338" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B338" t="s">
         <v>30</v>
@@ -11453,13 +11453,13 @@
     </row>
     <row r="339" spans="1:7">
       <c r="A339" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B339" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C339" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D339" t="s">
         <v>38</v>
@@ -11476,7 +11476,7 @@
     </row>
     <row r="340" spans="1:7">
       <c r="A340" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B340" t="s">
         <v>30</v>
@@ -11499,7 +11499,7 @@
     </row>
     <row r="341" spans="1:7">
       <c r="A341" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B341" t="s">
         <v>30</v>
@@ -11514,15 +11514,15 @@
         <v>11</v>
       </c>
       <c r="F341" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G341" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="342" spans="1:7">
       <c r="A342" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B342" t="s">
         <v>30</v>
@@ -11537,21 +11537,21 @@
         <v>11</v>
       </c>
       <c r="F342" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G342" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="343" spans="1:7">
       <c r="A343" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B343" t="s">
         <v>8</v>
       </c>
       <c r="C343" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D343" t="s">
         <v>10</v>
@@ -11560,15 +11560,15 @@
         <v>11</v>
       </c>
       <c r="F343" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G343" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="344" spans="1:7">
       <c r="A344" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B344" t="s">
         <v>8</v>
@@ -11583,21 +11583,21 @@
         <v>11</v>
       </c>
       <c r="F344" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G344" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="345" spans="1:7">
       <c r="A345" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B345" t="s">
         <v>8</v>
       </c>
       <c r="C345" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D345" t="s">
         <v>10</v>
@@ -11606,21 +11606,21 @@
         <v>11</v>
       </c>
       <c r="F345" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G345" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="346" spans="1:7">
       <c r="A346" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B346" t="s">
         <v>8</v>
       </c>
       <c r="C346" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D346" t="s">
         <v>10</v>
@@ -11629,21 +11629,21 @@
         <v>11</v>
       </c>
       <c r="F346" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G346" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="347" spans="1:7">
       <c r="A347" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B347" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C347" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D347" t="s">
         <v>111</v>
@@ -11652,21 +11652,21 @@
         <v>11</v>
       </c>
       <c r="F347" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="G347" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="348" spans="1:7">
       <c r="A348" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B348" t="s">
         <v>8</v>
       </c>
       <c r="C348" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D348" t="s">
         <v>14</v>
@@ -11675,15 +11675,15 @@
         <v>11</v>
       </c>
       <c r="F348" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G348" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="349" spans="1:7">
       <c r="A349" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B349" t="s">
         <v>8</v>
@@ -11698,21 +11698,21 @@
         <v>11</v>
       </c>
       <c r="F349" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G349" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="350" spans="1:7">
       <c r="A350" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B350" t="s">
         <v>8</v>
       </c>
       <c r="C350" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D350" t="s">
         <v>14</v>
@@ -11721,21 +11721,21 @@
         <v>11</v>
       </c>
       <c r="F350" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G350" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="351" spans="1:7">
       <c r="A351" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B351" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C351" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D351" t="s">
         <v>78</v>
@@ -11744,10 +11744,10 @@
         <v>11</v>
       </c>
       <c r="F351" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="G351" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="352" spans="1:7">
@@ -11755,10 +11755,10 @@
         <v>201</v>
       </c>
       <c r="B352" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C352" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D352" t="s">
         <v>78</v>
@@ -11767,15 +11767,15 @@
         <v>11</v>
       </c>
       <c r="F352" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G352" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="353" spans="1:7">
       <c r="A353" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B353" t="s">
         <v>19</v>
@@ -11793,18 +11793,18 @@
         <v>232</v>
       </c>
       <c r="G353" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="354" spans="1:7">
       <c r="A354" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B354" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C354" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D354" t="s">
         <v>43</v>
@@ -11816,18 +11816,18 @@
         <v>128</v>
       </c>
       <c r="G354" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="355" spans="1:7">
       <c r="A355" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B355" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C355" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D355" t="s">
         <v>38</v>
@@ -11839,12 +11839,12 @@
         <v>23</v>
       </c>
       <c r="G355" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="356" spans="1:7">
       <c r="A356" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B356" t="s">
         <v>30</v>
@@ -11862,12 +11862,12 @@
         <v>128</v>
       </c>
       <c r="G356" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="357" spans="1:7">
       <c r="A357" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B357" t="s">
         <v>30</v>
@@ -11882,15 +11882,15 @@
         <v>28</v>
       </c>
       <c r="F357" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G357" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="358" spans="1:7">
       <c r="A358" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B358" t="s">
         <v>8</v>
@@ -11905,15 +11905,15 @@
         <v>28</v>
       </c>
       <c r="F358" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="G358" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="359" spans="1:7">
       <c r="A359" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B359" t="s">
         <v>8</v>
@@ -11928,15 +11928,15 @@
         <v>28</v>
       </c>
       <c r="F359" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="G359" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="360" spans="1:7">
       <c r="A360" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B360" t="s">
         <v>30</v>
@@ -11951,15 +11951,15 @@
         <v>28</v>
       </c>
       <c r="F360" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="G360" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="361" spans="1:7">
       <c r="A361" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B361" t="s">
         <v>30</v>
@@ -11974,15 +11974,15 @@
         <v>28</v>
       </c>
       <c r="F361" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G361" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="362" spans="1:7">
       <c r="A362" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B362" t="s">
         <v>19</v>
@@ -12000,12 +12000,12 @@
         <v>216</v>
       </c>
       <c r="G362" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="363" spans="1:7">
       <c r="A363" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B363" t="s">
         <v>19</v>
@@ -12023,12 +12023,12 @@
         <v>129</v>
       </c>
       <c r="G363" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="364" spans="1:7">
       <c r="A364" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B364" t="s">
         <v>19</v>
@@ -12046,12 +12046,12 @@
         <v>455</v>
       </c>
       <c r="G364" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="365" spans="1:7">
       <c r="A365" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B365" t="s">
         <v>8</v>
@@ -12066,18 +12066,18 @@
         <v>47</v>
       </c>
       <c r="F365" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="G365" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="366" spans="1:7">
       <c r="A366" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B366" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C366" t="s">
         <v>171</v>
@@ -12089,18 +12089,18 @@
         <v>47</v>
       </c>
       <c r="F366" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G366" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="367" spans="1:7">
       <c r="A367" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B367" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C367" t="s">
         <v>55</v>
@@ -12112,10 +12112,10 @@
         <v>47</v>
       </c>
       <c r="F367" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G367" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="368" spans="1:7">
@@ -12123,7 +12123,7 @@
         <v>201</v>
       </c>
       <c r="B368" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C368" t="s">
         <v>171</v>
@@ -12135,21 +12135,21 @@
         <v>47</v>
       </c>
       <c r="F368" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="G368" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="369" spans="1:7">
       <c r="A369" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B369" t="s">
         <v>19</v>
       </c>
       <c r="C369" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D369" t="s">
         <v>21</v>
@@ -12161,12 +12161,12 @@
         <v>455</v>
       </c>
       <c r="G369" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="370" spans="1:7">
       <c r="A370" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B370" t="s">
         <v>30</v>
@@ -12181,15 +12181,15 @@
         <v>47</v>
       </c>
       <c r="F370" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="G370" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="371" spans="1:7">
       <c r="A371" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B371" t="s">
         <v>19</v>
@@ -12207,18 +12207,18 @@
         <v>455</v>
       </c>
       <c r="G371" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="372" spans="1:7">
       <c r="A372" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B372" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C372" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D372" t="s">
         <v>111</v>
@@ -12227,21 +12227,21 @@
         <v>63</v>
       </c>
       <c r="F372" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G372" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="373" spans="1:7">
       <c r="A373" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B373" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C373" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D373" t="s">
         <v>111</v>
@@ -12250,21 +12250,21 @@
         <v>63</v>
       </c>
       <c r="F373" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="G373" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="374" spans="1:7">
       <c r="A374" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B374" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C374" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D374" t="s">
         <v>111</v>
@@ -12273,21 +12273,21 @@
         <v>63</v>
       </c>
       <c r="F374" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G374" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="375" spans="1:7">
       <c r="A375" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B375" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C375" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D375" t="s">
         <v>78</v>
@@ -12296,21 +12296,21 @@
         <v>63</v>
       </c>
       <c r="F375" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G375" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="376" spans="1:7">
       <c r="A376" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B376" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C376" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D376" t="s">
         <v>78</v>
@@ -12319,21 +12319,21 @@
         <v>63</v>
       </c>
       <c r="F376" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="G376" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="377" spans="1:7">
       <c r="A377" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B377" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C377" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D377" t="s">
         <v>78</v>
@@ -12342,10 +12342,10 @@
         <v>63</v>
       </c>
       <c r="F377" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G377" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="378" spans="1:7">
@@ -12353,7 +12353,7 @@
         <v>192</v>
       </c>
       <c r="B378" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C378" t="s">
         <v>193</v>
@@ -12368,12 +12368,12 @@
         <v>128</v>
       </c>
       <c r="G378" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="379" spans="1:7">
       <c r="A379" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B379" t="s">
         <v>30</v>
@@ -12388,10 +12388,10 @@
         <v>63</v>
       </c>
       <c r="F379" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="G379" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="380" spans="1:7">
@@ -12414,15 +12414,15 @@
         <v>216</v>
       </c>
       <c r="G380" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="381" spans="1:7">
       <c r="A381" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B381" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C381" t="s">
         <v>215</v>
@@ -12437,7 +12437,7 @@
         <v>216</v>
       </c>
       <c r="G381" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="382" spans="1:7">
@@ -12445,10 +12445,10 @@
         <v>272</v>
       </c>
       <c r="B382" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C382" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D382" t="s">
         <v>38</v>
@@ -12460,15 +12460,15 @@
         <v>216</v>
       </c>
       <c r="G382" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="383" spans="1:7">
       <c r="A383" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B383" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C383" t="s">
         <v>184</v>
@@ -12483,12 +12483,12 @@
         <v>216</v>
       </c>
       <c r="G383" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="384" spans="1:7">
       <c r="A384" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B384" t="s">
         <v>8</v>
@@ -12503,21 +12503,21 @@
         <v>22</v>
       </c>
       <c r="F384" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G384" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="385" spans="1:7">
       <c r="A385" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B385" t="s">
         <v>19</v>
       </c>
       <c r="C385" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D385" t="s">
         <v>14</v>
@@ -12529,7 +12529,7 @@
         <v>23</v>
       </c>
       <c r="G385" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="386" spans="1:7">
@@ -12537,7 +12537,7 @@
         <v>226</v>
       </c>
       <c r="B386" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C386" t="s">
         <v>228</v>
@@ -12552,7 +12552,7 @@
         <v>216</v>
       </c>
       <c r="G386" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="387" spans="1:7">
@@ -12560,10 +12560,10 @@
         <v>260</v>
       </c>
       <c r="B387" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C387" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D387" t="s">
         <v>43</v>
@@ -12572,21 +12572,21 @@
         <v>22</v>
       </c>
       <c r="F387" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G387" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="388" spans="1:7">
       <c r="A388" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B388" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C388" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D388" t="s">
         <v>27</v>
@@ -12598,15 +12598,15 @@
         <v>216</v>
       </c>
       <c r="G388" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="389" spans="1:7">
       <c r="A389" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B389" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C389" t="s">
         <v>215</v>
@@ -12618,18 +12618,18 @@
         <v>28</v>
       </c>
       <c r="F389" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G389" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="390" spans="1:7">
       <c r="A390" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B390" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C390" t="s">
         <v>55</v>
@@ -12644,18 +12644,18 @@
         <v>216</v>
       </c>
       <c r="G390" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="391" spans="1:7">
       <c r="A391" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B391" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C391" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D391" t="s">
         <v>14</v>
@@ -12664,10 +12664,10 @@
         <v>47</v>
       </c>
       <c r="F391" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G391" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="392" spans="1:7">
@@ -12675,7 +12675,7 @@
         <v>237</v>
       </c>
       <c r="B392" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C392" t="s">
         <v>228</v>
@@ -12690,12 +12690,12 @@
         <v>216</v>
       </c>
       <c r="G392" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="393" spans="1:7">
       <c r="A393" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B393" t="s">
         <v>30</v>
@@ -12713,7 +12713,7 @@
         <v>216</v>
       </c>
       <c r="G393" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="394" spans="1:7">
@@ -12721,7 +12721,7 @@
         <v>238</v>
       </c>
       <c r="B394" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C394" t="s">
         <v>85</v>
@@ -12733,10 +12733,10 @@
         <v>63</v>
       </c>
       <c r="F394" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G394" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="395" spans="1:7">
@@ -12744,7 +12744,7 @@
         <v>245</v>
       </c>
       <c r="B395" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C395" t="s">
         <v>246</v>
@@ -12759,12 +12759,12 @@
         <v>216</v>
       </c>
       <c r="G395" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="396" spans="1:7">
       <c r="A396" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B396" t="s">
         <v>8</v>
@@ -12779,10 +12779,10 @@
         <v>63</v>
       </c>
       <c r="F396" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G396" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="397" spans="1:7">
@@ -12805,15 +12805,15 @@
         <v>216</v>
       </c>
       <c r="G397" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="398" spans="1:7">
       <c r="A398" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B398" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C398" t="s">
         <v>215</v>
@@ -12828,7 +12828,7 @@
         <v>216</v>
       </c>
       <c r="G398" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="399" spans="1:7">
@@ -12836,10 +12836,10 @@
         <v>272</v>
       </c>
       <c r="B399" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C399" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D399" t="s">
         <v>38</v>
@@ -12851,15 +12851,15 @@
         <v>216</v>
       </c>
       <c r="G399" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="400" spans="1:7">
       <c r="A400" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B400" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C400" t="s">
         <v>184</v>
@@ -12874,15 +12874,15 @@
         <v>216</v>
       </c>
       <c r="G400" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="401" spans="1:7">
       <c r="A401" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B401" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C401" t="s">
         <v>300</v>
@@ -12894,21 +12894,21 @@
         <v>22</v>
       </c>
       <c r="F401" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G401" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="402" spans="1:7">
       <c r="A402" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B402" t="s">
         <v>19</v>
       </c>
       <c r="C402" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D402" t="s">
         <v>14</v>
@@ -12920,7 +12920,7 @@
         <v>23</v>
       </c>
       <c r="G402" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="403" spans="1:7">
@@ -12928,7 +12928,7 @@
         <v>226</v>
       </c>
       <c r="B403" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C403" t="s">
         <v>228</v>
@@ -12943,12 +12943,12 @@
         <v>216</v>
       </c>
       <c r="G403" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="404" spans="1:7">
       <c r="A404" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B404" t="s">
         <v>8</v>
@@ -12963,21 +12963,21 @@
         <v>22</v>
       </c>
       <c r="F404" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G404" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="405" spans="1:7">
       <c r="A405" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B405" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C405" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D405" t="s">
         <v>27</v>
@@ -12989,7 +12989,7 @@
         <v>216</v>
       </c>
       <c r="G405" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="406" spans="1:7">
@@ -12997,10 +12997,10 @@
         <v>238</v>
       </c>
       <c r="B406" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C406" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D406" t="s">
         <v>111</v>
@@ -13009,21 +13009,21 @@
         <v>28</v>
       </c>
       <c r="F406" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G406" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="407" spans="1:7">
       <c r="A407" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B407" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C407" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D407" t="s">
         <v>43</v>
@@ -13032,18 +13032,18 @@
         <v>28</v>
       </c>
       <c r="F407" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G407" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="408" spans="1:7">
       <c r="A408" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B408" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C408" t="s">
         <v>55</v>
@@ -13058,15 +13058,15 @@
         <v>216</v>
       </c>
       <c r="G408" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="409" spans="1:7">
       <c r="A409" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B409" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C409" t="s">
         <v>246</v>
@@ -13078,10 +13078,10 @@
         <v>47</v>
       </c>
       <c r="F409" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G409" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="410" spans="1:7">
@@ -13089,7 +13089,7 @@
         <v>237</v>
       </c>
       <c r="B410" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C410" t="s">
         <v>228</v>
@@ -13104,12 +13104,12 @@
         <v>216</v>
       </c>
       <c r="G410" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="411" spans="1:7">
       <c r="A411" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B411" t="s">
         <v>30</v>
@@ -13127,7 +13127,7 @@
         <v>216</v>
       </c>
       <c r="G411" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="412" spans="1:7">
@@ -13135,7 +13135,7 @@
         <v>260</v>
       </c>
       <c r="B412" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C412" t="s">
         <v>221</v>
@@ -13147,10 +13147,10 @@
         <v>63</v>
       </c>
       <c r="F412" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G412" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="413" spans="1:7">
@@ -13158,7 +13158,7 @@
         <v>245</v>
       </c>
       <c r="B413" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C413" t="s">
         <v>246</v>
@@ -13173,18 +13173,18 @@
         <v>216</v>
       </c>
       <c r="G413" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="414" spans="1:7">
       <c r="A414" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B414" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C414" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D414" t="s">
         <v>27</v>
@@ -13193,21 +13193,21 @@
         <v>11</v>
       </c>
       <c r="F414" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G414" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="415" spans="1:7">
       <c r="A415" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B415" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C415" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D415" t="s">
         <v>470</v>
@@ -13216,33 +13216,33 @@
         <v>11</v>
       </c>
       <c r="F415" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="G415" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="416" spans="1:7">
       <c r="A416" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B416" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C416" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D416" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E416" t="s">
         <v>11</v>
       </c>
       <c r="F416" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="G416" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="417" spans="1:7">
@@ -13250,7 +13250,7 @@
         <v>237</v>
       </c>
       <c r="B417" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C417" t="s">
         <v>168</v>
@@ -13262,10 +13262,10 @@
         <v>11</v>
       </c>
       <c r="F417" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G417" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="418" spans="1:7">
@@ -13285,18 +13285,18 @@
         <v>11</v>
       </c>
       <c r="F418" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G418" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="419" spans="1:7">
       <c r="A419" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B419" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C419" t="s">
         <v>178</v>
@@ -13308,18 +13308,18 @@
         <v>28</v>
       </c>
       <c r="F419" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G419" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="420" spans="1:7">
       <c r="A420" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B420" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C420" t="s">
         <v>300</v>
@@ -13331,18 +13331,18 @@
         <v>28</v>
       </c>
       <c r="F420" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G420" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="421" spans="1:7">
       <c r="A421" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B421" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C421" t="s">
         <v>300</v>
@@ -13354,18 +13354,18 @@
         <v>28</v>
       </c>
       <c r="F421" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G421" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="422" spans="1:7">
       <c r="A422" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B422" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C422" t="s">
         <v>239</v>
@@ -13377,18 +13377,18 @@
         <v>28</v>
       </c>
       <c r="F422" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G422" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="423" spans="1:7">
       <c r="A423" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B423" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C423" t="s">
         <v>85</v>
@@ -13400,15 +13400,15 @@
         <v>28</v>
       </c>
       <c r="F423" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G423" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="424" spans="1:7">
       <c r="A424" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B424" t="s">
         <v>19</v>
@@ -13423,10 +13423,10 @@
         <v>47</v>
       </c>
       <c r="F424" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G424" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="425" spans="1:7">
@@ -13434,10 +13434,10 @@
         <v>270</v>
       </c>
       <c r="B425" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C425" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D425" t="s">
         <v>111</v>
@@ -13446,15 +13446,15 @@
         <v>47</v>
       </c>
       <c r="F425" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G425" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="426" spans="1:7">
       <c r="A426" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B426" t="s">
         <v>19</v>
@@ -13469,18 +13469,18 @@
         <v>47</v>
       </c>
       <c r="F426" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G426" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="427" spans="1:7">
       <c r="A427" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B427" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C427" t="s">
         <v>262</v>
@@ -13492,18 +13492,18 @@
         <v>47</v>
       </c>
       <c r="F427" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G427" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="428" spans="1:7">
       <c r="A428" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B428" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C428" t="s">
         <v>262</v>
@@ -13515,10 +13515,10 @@
         <v>47</v>
       </c>
       <c r="F428" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G428" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="429" spans="1:7">
@@ -13526,10 +13526,10 @@
         <v>272</v>
       </c>
       <c r="B429" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C429" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D429" t="s">
         <v>27</v>
@@ -13538,15 +13538,15 @@
         <v>63</v>
       </c>
       <c r="F429" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G429" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="430" spans="1:7">
       <c r="A430" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B430" t="s">
         <v>8</v>
@@ -13561,21 +13561,21 @@
         <v>63</v>
       </c>
       <c r="F430" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G430" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="431" spans="1:7">
       <c r="A431" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B431" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C431" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D431" t="s">
         <v>111</v>
@@ -13584,15 +13584,15 @@
         <v>63</v>
       </c>
       <c r="F431" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G431" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="432" spans="1:7">
       <c r="A432" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B432" t="s">
         <v>8</v>
@@ -13607,21 +13607,21 @@
         <v>63</v>
       </c>
       <c r="F432" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G432" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="433" spans="1:7">
       <c r="A433" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B433" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C433" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D433" t="s">
         <v>78</v>
@@ -13630,15 +13630,15 @@
         <v>63</v>
       </c>
       <c r="F433" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G433" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="434" spans="1:7">
       <c r="A434" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B434" t="s">
         <v>19</v>
@@ -13653,15 +13653,15 @@
         <v>63</v>
       </c>
       <c r="F434" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G434" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="435" spans="1:7">
       <c r="A435" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B435" t="s">
         <v>30</v>
@@ -13676,18 +13676,18 @@
         <v>63</v>
       </c>
       <c r="F435" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G435" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="436" spans="1:7">
       <c r="A436" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B436" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C436" t="s">
         <v>215</v>
@@ -13702,12 +13702,12 @@
         <v>216</v>
       </c>
       <c r="G436" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="437" spans="1:7">
       <c r="A437" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B437" t="s">
         <v>30</v>
@@ -13725,7 +13725,7 @@
         <v>232</v>
       </c>
       <c r="G437" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="438" spans="1:7">
@@ -13733,10 +13733,10 @@
         <v>272</v>
       </c>
       <c r="B438" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C438" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D438" t="s">
         <v>38</v>
@@ -13748,15 +13748,15 @@
         <v>216</v>
       </c>
       <c r="G438" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="439" spans="1:7">
       <c r="A439" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B439" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C439" t="s">
         <v>184</v>
@@ -13771,18 +13771,18 @@
         <v>216</v>
       </c>
       <c r="G439" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="440" spans="1:7">
       <c r="A440" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B440" t="s">
         <v>19</v>
       </c>
       <c r="C440" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D440" t="s">
         <v>14</v>
@@ -13794,15 +13794,15 @@
         <v>23</v>
       </c>
       <c r="G440" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="441" spans="1:7">
       <c r="A441" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B441" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C441" t="s">
         <v>300</v>
@@ -13814,21 +13814,21 @@
         <v>22</v>
       </c>
       <c r="F441" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G441" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="442" spans="1:7">
       <c r="A442" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B442" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C442" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D442" t="s">
         <v>27</v>
@@ -13840,15 +13840,15 @@
         <v>216</v>
       </c>
       <c r="G442" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="443" spans="1:7">
       <c r="A443" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B443" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C443" t="s">
         <v>184</v>
@@ -13860,10 +13860,10 @@
         <v>28</v>
       </c>
       <c r="F443" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G443" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="444" spans="1:7">
@@ -13874,7 +13874,7 @@
         <v>8</v>
       </c>
       <c r="C444" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D444" t="s">
         <v>14</v>
@@ -13883,21 +13883,21 @@
         <v>28</v>
       </c>
       <c r="F444" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G444" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="445" spans="1:7">
       <c r="A445" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B445" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C445" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D445" t="s">
         <v>38</v>
@@ -13906,21 +13906,21 @@
         <v>28</v>
       </c>
       <c r="F445" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G445" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="446" spans="1:7">
       <c r="A446" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B446" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C446" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D446" t="s">
         <v>10</v>
@@ -13929,10 +13929,10 @@
         <v>47</v>
       </c>
       <c r="F446" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G446" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="447" spans="1:7">
@@ -13943,7 +13943,7 @@
         <v>30</v>
       </c>
       <c r="C447" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D447" t="s">
         <v>14</v>
@@ -13955,7 +13955,7 @@
         <v>232</v>
       </c>
       <c r="G447" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="448" spans="1:7">
@@ -13978,7 +13978,7 @@
         <v>232</v>
       </c>
       <c r="G448" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="449" spans="1:7">
@@ -13986,7 +13986,7 @@
         <v>237</v>
       </c>
       <c r="B449" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C449" t="s">
         <v>228</v>
@@ -14001,7 +14001,7 @@
         <v>216</v>
       </c>
       <c r="G449" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="450" spans="1:7">
@@ -14009,7 +14009,7 @@
         <v>260</v>
       </c>
       <c r="B450" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C450" t="s">
         <v>221</v>
@@ -14021,10 +14021,10 @@
         <v>63</v>
       </c>
       <c r="F450" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G450" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="451" spans="1:7">
@@ -14032,7 +14032,7 @@
         <v>245</v>
       </c>
       <c r="B451" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C451" t="s">
         <v>246</v>
@@ -14047,12 +14047,12 @@
         <v>216</v>
       </c>
       <c r="G451" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="452" spans="1:7">
       <c r="A452" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B452" t="s">
         <v>30</v>
@@ -14070,18 +14070,18 @@
         <v>232</v>
       </c>
       <c r="G452" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="453" spans="1:7">
       <c r="A453" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B453" t="s">
         <v>8</v>
       </c>
       <c r="C453" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D453" t="s">
         <v>46</v>
@@ -14090,18 +14090,18 @@
         <v>11</v>
       </c>
       <c r="F453" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G453" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="454" spans="1:7">
       <c r="A454" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B454" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C454" t="s">
         <v>215</v>
@@ -14116,12 +14116,12 @@
         <v>216</v>
       </c>
       <c r="G454" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="455" spans="1:7">
       <c r="A455" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B455" t="s">
         <v>30</v>
@@ -14139,7 +14139,7 @@
         <v>232</v>
       </c>
       <c r="G455" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="456" spans="1:7">
@@ -14147,10 +14147,10 @@
         <v>272</v>
       </c>
       <c r="B456" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C456" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D456" t="s">
         <v>38</v>
@@ -14162,15 +14162,15 @@
         <v>216</v>
       </c>
       <c r="G456" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="457" spans="1:7">
       <c r="A457" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B457" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C457" t="s">
         <v>184</v>
@@ -14185,7 +14185,7 @@
         <v>216</v>
       </c>
       <c r="G457" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="458" spans="1:7">
@@ -14193,10 +14193,10 @@
         <v>260</v>
       </c>
       <c r="B458" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C458" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D458" t="s">
         <v>27</v>
@@ -14205,21 +14205,21 @@
         <v>22</v>
       </c>
       <c r="F458" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G458" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="459" spans="1:7">
       <c r="A459" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B459" t="s">
         <v>19</v>
       </c>
       <c r="C459" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D459" t="s">
         <v>14</v>
@@ -14231,18 +14231,18 @@
         <v>23</v>
       </c>
       <c r="G459" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="460" spans="1:7">
       <c r="A460" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B460" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C460" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D460" t="s">
         <v>27</v>
@@ -14254,15 +14254,15 @@
         <v>216</v>
       </c>
       <c r="G460" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="461" spans="1:7">
       <c r="A461" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B461" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C461" t="s">
         <v>184</v>
@@ -14274,18 +14274,18 @@
         <v>28</v>
       </c>
       <c r="F461" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G461" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="462" spans="1:7">
       <c r="A462" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B462" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C462" t="s">
         <v>215</v>
@@ -14297,18 +14297,18 @@
         <v>28</v>
       </c>
       <c r="F462" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G462" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="463" spans="1:7">
       <c r="A463" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B463" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C463" t="s">
         <v>246</v>
@@ -14320,10 +14320,10 @@
         <v>47</v>
       </c>
       <c r="F463" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G463" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="464" spans="1:7">
@@ -14334,7 +14334,7 @@
         <v>30</v>
       </c>
       <c r="C464" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D464" t="s">
         <v>14</v>
@@ -14346,7 +14346,7 @@
         <v>232</v>
       </c>
       <c r="G464" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="465" spans="1:7">
@@ -14369,7 +14369,7 @@
         <v>232</v>
       </c>
       <c r="G465" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="466" spans="1:7">
@@ -14377,7 +14377,7 @@
         <v>237</v>
       </c>
       <c r="B466" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C466" t="s">
         <v>228</v>
@@ -14392,7 +14392,7 @@
         <v>216</v>
       </c>
       <c r="G466" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="467" spans="1:7">
@@ -14400,7 +14400,7 @@
         <v>238</v>
       </c>
       <c r="B467" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C467" t="s">
         <v>85</v>
@@ -14412,10 +14412,10 @@
         <v>63</v>
       </c>
       <c r="F467" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G467" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="468" spans="1:7">
@@ -14423,7 +14423,7 @@
         <v>245</v>
       </c>
       <c r="B468" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C468" t="s">
         <v>246</v>
@@ -14438,12 +14438,12 @@
         <v>216</v>
       </c>
       <c r="G468" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="469" spans="1:7">
       <c r="A469" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B469" t="s">
         <v>30</v>
@@ -14461,18 +14461,18 @@
         <v>232</v>
       </c>
       <c r="G469" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="470" spans="1:7">
       <c r="A470" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B470" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C470" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D470" t="s">
         <v>111</v>
@@ -14481,15 +14481,15 @@
         <v>11</v>
       </c>
       <c r="F470" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="G470" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="471" spans="1:7">
       <c r="A471" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B471" t="s">
         <v>8</v>
@@ -14507,12 +14507,12 @@
         <v>12</v>
       </c>
       <c r="G471" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="472" spans="1:7">
       <c r="A472" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B472" t="s">
         <v>8</v>
@@ -14530,15 +14530,15 @@
         <v>55</v>
       </c>
       <c r="G472" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="473" spans="1:7">
       <c r="A473" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B473" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C473" t="s">
         <v>168</v>
@@ -14550,15 +14550,15 @@
         <v>11</v>
       </c>
       <c r="F473" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="G473" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="474" spans="1:7">
       <c r="A474" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B474" t="s">
         <v>19</v>
@@ -14576,12 +14576,12 @@
         <v>29</v>
       </c>
       <c r="G474" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="475" spans="1:7">
       <c r="A475" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B475" t="s">
         <v>8</v>
@@ -14599,12 +14599,12 @@
         <v>29</v>
       </c>
       <c r="G475" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="476" spans="1:7">
       <c r="A476" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B476" t="s">
         <v>19</v>
@@ -14622,12 +14622,12 @@
         <v>23</v>
       </c>
       <c r="G476" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="477" spans="1:7">
       <c r="A477" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B477" t="s">
         <v>8</v>
@@ -14645,12 +14645,12 @@
         <v>55</v>
       </c>
       <c r="G477" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="478" spans="1:7">
       <c r="A478" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B478" t="s">
         <v>30</v>
@@ -14668,12 +14668,12 @@
         <v>29</v>
       </c>
       <c r="G478" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="479" spans="1:7">
       <c r="A479" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B479" t="s">
         <v>19</v>
@@ -14691,12 +14691,12 @@
         <v>29</v>
       </c>
       <c r="G479" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="480" spans="1:7">
       <c r="A480" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B480" t="s">
         <v>19</v>
@@ -14714,12 +14714,12 @@
         <v>29</v>
       </c>
       <c r="G480" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="481" spans="1:7">
       <c r="A481" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B481" t="s">
         <v>8</v>
@@ -14737,18 +14737,18 @@
         <v>83</v>
       </c>
       <c r="G481" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="482" spans="1:7">
       <c r="A482" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B482" t="s">
         <v>8</v>
       </c>
       <c r="C482" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D482" t="s">
         <v>46</v>
@@ -14760,18 +14760,18 @@
         <v>55</v>
       </c>
       <c r="G482" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="483" spans="1:7">
       <c r="A483" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B483" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C483" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D483" t="s">
         <v>111</v>
@@ -14783,18 +14783,18 @@
         <v>29</v>
       </c>
       <c r="G483" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="484" spans="1:7">
       <c r="A484" t="s">
+        <v>697</v>
+      </c>
+      <c r="B484" t="s">
+        <v>698</v>
+      </c>
+      <c r="C484" t="s">
         <v>696</v>
-      </c>
-      <c r="B484" t="s">
-        <v>697</v>
-      </c>
-      <c r="C484" t="s">
-        <v>695</v>
       </c>
       <c r="D484" t="s">
         <v>78</v>
@@ -14806,18 +14806,18 @@
         <v>29</v>
       </c>
       <c r="G484" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="485" spans="1:7">
       <c r="A485" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B485" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C485" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D485" t="s">
         <v>38</v>
@@ -14829,18 +14829,18 @@
         <v>29</v>
       </c>
       <c r="G485" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="486" spans="1:7">
       <c r="A486" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B486" t="s">
         <v>19</v>
       </c>
       <c r="C486" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D486" t="s">
         <v>17</v>
@@ -14852,18 +14852,18 @@
         <v>29</v>
       </c>
       <c r="G486" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="487" spans="1:7">
       <c r="A487" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B487" t="s">
         <v>19</v>
       </c>
       <c r="C487" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D487" t="s">
         <v>21</v>
@@ -14875,15 +14875,15 @@
         <v>159</v>
       </c>
       <c r="G487" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="488" spans="1:7">
       <c r="A488" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B488" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C488" t="s">
         <v>275</v>
@@ -14898,7 +14898,7 @@
         <v>34</v>
       </c>
       <c r="G488" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="489" spans="1:7">
@@ -14921,7 +14921,7 @@
         <v>304</v>
       </c>
       <c r="G489" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="490" spans="1:7">
@@ -14944,12 +14944,12 @@
         <v>293</v>
       </c>
       <c r="G490" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="491" spans="1:7">
       <c r="A491" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B491" t="s">
         <v>19</v>
@@ -14967,15 +14967,15 @@
         <v>34</v>
       </c>
       <c r="G491" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="492" spans="1:7">
       <c r="A492" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B492" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C492" t="s">
         <v>275</v>
@@ -14990,18 +14990,18 @@
         <v>34</v>
       </c>
       <c r="G492" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="493" spans="1:7">
       <c r="A493" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B493" t="s">
         <v>8</v>
       </c>
       <c r="C493" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D493" t="s">
         <v>46</v>
@@ -15013,12 +15013,12 @@
         <v>34</v>
       </c>
       <c r="G493" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="494" spans="1:7">
       <c r="A494" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B494" t="s">
         <v>19</v>
@@ -15036,18 +15036,18 @@
         <v>23</v>
       </c>
       <c r="G494" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="495" spans="1:7">
       <c r="A495" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B495" t="s">
         <v>19</v>
       </c>
       <c r="C495" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D495" t="s">
         <v>17</v>
@@ -15059,12 +15059,12 @@
         <v>34</v>
       </c>
       <c r="G495" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="496" spans="1:7">
       <c r="A496" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B496" t="s">
         <v>8</v>
@@ -15079,15 +15079,15 @@
         <v>28</v>
       </c>
       <c r="F496" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G496" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="497" spans="1:7">
       <c r="A497" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B497" t="s">
         <v>8</v>
@@ -15105,18 +15105,18 @@
         <v>386</v>
       </c>
       <c r="G497" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="498" spans="1:7">
       <c r="A498" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B498" t="s">
         <v>8</v>
       </c>
       <c r="C498" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D498" t="s">
         <v>14</v>
@@ -15128,15 +15128,15 @@
         <v>386</v>
       </c>
       <c r="G498" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="499" spans="1:7">
       <c r="A499" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B499" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C499" t="s">
         <v>148</v>
@@ -15151,12 +15151,12 @@
         <v>34</v>
       </c>
       <c r="G499" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="500" spans="1:7">
       <c r="A500" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B500" t="s">
         <v>8</v>
@@ -15171,18 +15171,18 @@
         <v>28</v>
       </c>
       <c r="F500" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G500" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="501" spans="1:7">
       <c r="A501" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B501" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C501" t="s">
         <v>219</v>
@@ -15197,12 +15197,12 @@
         <v>34</v>
       </c>
       <c r="G501" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="502" spans="1:7">
       <c r="A502" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B502" t="s">
         <v>19</v>
@@ -15220,18 +15220,18 @@
         <v>34</v>
       </c>
       <c r="G502" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="503" spans="1:7">
       <c r="A503" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B503" t="s">
         <v>19</v>
       </c>
       <c r="C503" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D503" t="s">
         <v>21</v>
@@ -15243,18 +15243,18 @@
         <v>34</v>
       </c>
       <c r="G503" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="504" spans="1:7">
       <c r="A504" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B504" t="s">
         <v>30</v>
       </c>
       <c r="C504" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D504" t="s">
         <v>17</v>
@@ -15266,12 +15266,12 @@
         <v>34</v>
       </c>
       <c r="G504" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="505" spans="1:7">
       <c r="A505" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B505" t="s">
         <v>30</v>
@@ -15289,7 +15289,7 @@
         <v>159</v>
       </c>
       <c r="G505" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="506" spans="1:7">
@@ -15312,15 +15312,15 @@
         <v>39</v>
       </c>
       <c r="G506" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="507" spans="1:7">
       <c r="A507" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B507" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C507" t="s">
         <v>223</v>
@@ -15335,18 +15335,18 @@
         <v>159</v>
       </c>
       <c r="G507" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="508" spans="1:7">
       <c r="A508" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B508" t="s">
         <v>8</v>
       </c>
       <c r="C508" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D508" t="s">
         <v>46</v>
@@ -15355,15 +15355,15 @@
         <v>22</v>
       </c>
       <c r="F508" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="G508" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="509" spans="1:7">
       <c r="A509" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B509" t="s">
         <v>19</v>
@@ -15381,18 +15381,18 @@
         <v>23</v>
       </c>
       <c r="G509" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="510" spans="1:7">
       <c r="A510" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B510" t="s">
         <v>19</v>
       </c>
       <c r="C510" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D510" t="s">
         <v>17</v>
@@ -15404,15 +15404,15 @@
         <v>159</v>
       </c>
       <c r="G510" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="511" spans="1:7">
       <c r="A511" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B511" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C511" t="s">
         <v>286</v>
@@ -15427,15 +15427,15 @@
         <v>159</v>
       </c>
       <c r="G511" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="512" spans="1:7">
       <c r="A512" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B512" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C512" t="s">
         <v>310</v>
@@ -15450,15 +15450,15 @@
         <v>159</v>
       </c>
       <c r="G512" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="513" spans="1:7">
       <c r="A513" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B513" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C513" t="s">
         <v>310</v>
@@ -15473,15 +15473,15 @@
         <v>159</v>
       </c>
       <c r="G513" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="514" spans="1:7">
       <c r="A514" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B514" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C514" t="s">
         <v>462</v>
@@ -15496,15 +15496,15 @@
         <v>159</v>
       </c>
       <c r="G514" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="515" spans="1:7">
       <c r="A515" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B515" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C515" t="s">
         <v>316</v>
@@ -15519,12 +15519,12 @@
         <v>159</v>
       </c>
       <c r="G515" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="516" spans="1:7">
       <c r="A516" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B516" t="s">
         <v>19</v>
@@ -15542,15 +15542,15 @@
         <v>159</v>
       </c>
       <c r="G516" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="517" spans="1:7">
       <c r="A517" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B517" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C517" t="s">
         <v>316</v>
@@ -15565,12 +15565,12 @@
         <v>159</v>
       </c>
       <c r="G517" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="518" spans="1:7">
       <c r="A518" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B518" t="s">
         <v>8</v>
@@ -15579,21 +15579,21 @@
         <v>286</v>
       </c>
       <c r="D518" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E518" t="s">
         <v>63</v>
       </c>
       <c r="F518" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="G518" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="519" spans="1:7">
       <c r="A519" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B519" t="s">
         <v>8</v>
@@ -15608,21 +15608,21 @@
         <v>63</v>
       </c>
       <c r="F519" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G519" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="520" spans="1:7">
       <c r="A520" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B520" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C520" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D520" t="s">
         <v>111</v>
@@ -15631,15 +15631,15 @@
         <v>63</v>
       </c>
       <c r="F520" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="G520" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="521" spans="1:7">
       <c r="A521" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B521" t="s">
         <v>8</v>
@@ -15654,21 +15654,21 @@
         <v>63</v>
       </c>
       <c r="F521" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G521" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="522" spans="1:7">
       <c r="A522" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B522" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C522" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D522" t="s">
         <v>78</v>
@@ -15677,15 +15677,15 @@
         <v>63</v>
       </c>
       <c r="F522" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="G522" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="523" spans="1:7">
       <c r="A523" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B523" t="s">
         <v>8</v>
@@ -15694,27 +15694,27 @@
         <v>286</v>
       </c>
       <c r="D523" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E523" t="s">
         <v>63</v>
       </c>
       <c r="F523" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="G523" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="524" spans="1:7">
       <c r="A524" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B524" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C524" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D524" t="s">
         <v>27</v>
@@ -15726,18 +15726,18 @@
         <v>169</v>
       </c>
       <c r="G524" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="525" spans="1:7">
       <c r="A525" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B525" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C525" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D525" t="s">
         <v>10</v>
@@ -15746,21 +15746,21 @@
         <v>11</v>
       </c>
       <c r="F525" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="G525" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="526" spans="1:7">
       <c r="A526" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B526" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C526" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D526" t="s">
         <v>78</v>
@@ -15769,21 +15769,21 @@
         <v>11</v>
       </c>
       <c r="F526" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="G526" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="527" spans="1:7">
       <c r="A527" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B527" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C527" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D527" t="s">
         <v>38</v>
@@ -15795,18 +15795,18 @@
         <v>169</v>
       </c>
       <c r="G527" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="528" spans="1:7">
       <c r="A528" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B528" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C528" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D528" t="s">
         <v>43</v>
@@ -15818,18 +15818,18 @@
         <v>169</v>
       </c>
       <c r="G528" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="529" spans="1:7">
       <c r="A529" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B529" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C529" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D529" t="s">
         <v>46</v>
@@ -15841,12 +15841,12 @@
         <v>169</v>
       </c>
       <c r="G529" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="530" spans="1:7">
       <c r="A530" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B530" t="s">
         <v>19</v>
@@ -15864,18 +15864,18 @@
         <v>23</v>
       </c>
       <c r="G530" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="531" spans="1:7">
       <c r="A531" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B531" t="s">
         <v>19</v>
       </c>
       <c r="C531" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D531" t="s">
         <v>17</v>
@@ -15887,18 +15887,18 @@
         <v>169</v>
       </c>
       <c r="G531" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="532" spans="1:7">
       <c r="A532" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B532" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C532" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D532" t="s">
         <v>27</v>
@@ -15907,18 +15907,18 @@
         <v>28</v>
       </c>
       <c r="F532" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="G532" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="533" spans="1:7">
       <c r="A533" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B533" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C533" t="s">
         <v>239</v>
@@ -15933,15 +15933,15 @@
         <v>169</v>
       </c>
       <c r="G533" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="534" spans="1:7">
       <c r="A534" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B534" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C534" t="s">
         <v>239</v>
@@ -15956,15 +15956,15 @@
         <v>169</v>
       </c>
       <c r="G534" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="535" spans="1:7">
       <c r="A535" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B535" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C535" t="s">
         <v>246</v>
@@ -15979,18 +15979,18 @@
         <v>169</v>
       </c>
       <c r="G535" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="536" spans="1:7">
       <c r="A536" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B536" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C536" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D536" t="s">
         <v>43</v>
@@ -15999,21 +15999,21 @@
         <v>28</v>
       </c>
       <c r="F536" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="G536" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="537" spans="1:7">
       <c r="A537" t="s">
+        <v>778</v>
+      </c>
+      <c r="B537" t="s">
+        <v>779</v>
+      </c>
+      <c r="C537" t="s">
         <v>777</v>
-      </c>
-      <c r="B537" t="s">
-        <v>778</v>
-      </c>
-      <c r="C537" t="s">
-        <v>776</v>
       </c>
       <c r="D537" t="s">
         <v>38</v>
@@ -16025,18 +16025,18 @@
         <v>169</v>
       </c>
       <c r="G537" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="538" spans="1:7">
       <c r="A538" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B538" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C538" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D538" t="s">
         <v>43</v>
@@ -16048,15 +16048,15 @@
         <v>169</v>
       </c>
       <c r="G538" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="539" spans="1:7">
       <c r="A539" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B539" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C539" t="s">
         <v>239</v>
@@ -16068,21 +16068,21 @@
         <v>63</v>
       </c>
       <c r="F539" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="G539" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="540" spans="1:7">
       <c r="A540" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B540" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C540" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D540" t="s">
         <v>43</v>
@@ -16094,18 +16094,18 @@
         <v>169</v>
       </c>
       <c r="G540" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="541" spans="1:7">
       <c r="A541" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B541" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C541" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D541" t="s">
         <v>111</v>
@@ -16114,10 +16114,10 @@
         <v>11</v>
       </c>
       <c r="F541" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G541" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="542" spans="1:7">
@@ -16140,15 +16140,15 @@
         <v>39</v>
       </c>
       <c r="G542" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="543" spans="1:7">
       <c r="A543" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B543" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C543" t="s">
         <v>286</v>
@@ -16163,18 +16163,18 @@
         <v>39</v>
       </c>
       <c r="G543" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="544" spans="1:7">
       <c r="A544" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B544" t="s">
         <v>8</v>
       </c>
       <c r="C544" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D544" t="s">
         <v>46</v>
@@ -16183,15 +16183,15 @@
         <v>22</v>
       </c>
       <c r="F544" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="G544" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="545" spans="1:7">
       <c r="A545" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B545" t="s">
         <v>19</v>
@@ -16209,18 +16209,18 @@
         <v>23</v>
       </c>
       <c r="G545" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="546" spans="1:7">
       <c r="A546" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B546" t="s">
         <v>19</v>
       </c>
       <c r="C546" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D546" t="s">
         <v>17</v>
@@ -16232,12 +16232,12 @@
         <v>39</v>
       </c>
       <c r="G546" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="547" spans="1:7">
       <c r="A547" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B547" t="s">
         <v>30</v>
@@ -16255,12 +16255,12 @@
         <v>39</v>
       </c>
       <c r="G547" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="548" spans="1:7">
       <c r="A548" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B548" t="s">
         <v>19</v>
@@ -16278,12 +16278,12 @@
         <v>39</v>
       </c>
       <c r="G548" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="549" spans="1:7">
       <c r="A549" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B549" t="s">
         <v>8</v>
@@ -16298,18 +16298,18 @@
         <v>28</v>
       </c>
       <c r="F549" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="G549" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="550" spans="1:7">
       <c r="A550" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B550" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C550" t="s">
         <v>286</v>
@@ -16321,15 +16321,15 @@
         <v>28</v>
       </c>
       <c r="F550" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G550" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="551" spans="1:7">
       <c r="A551" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B551" t="s">
         <v>30</v>
@@ -16347,12 +16347,12 @@
         <v>293</v>
       </c>
       <c r="G551" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="552" spans="1:7">
       <c r="A552" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B552" t="s">
         <v>30</v>
@@ -16370,12 +16370,12 @@
         <v>39</v>
       </c>
       <c r="G552" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="553" spans="1:7">
       <c r="A553" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B553" t="s">
         <v>19</v>
@@ -16393,12 +16393,12 @@
         <v>39</v>
       </c>
       <c r="G553" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="554" spans="1:7">
       <c r="A554" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B554" t="s">
         <v>19</v>
@@ -16416,7 +16416,7 @@
         <v>293</v>
       </c>
       <c r="G554" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="555" spans="1:7">
@@ -16424,7 +16424,7 @@
         <v>318</v>
       </c>
       <c r="B555" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C555" t="s">
         <v>319</v>
@@ -16439,15 +16439,15 @@
         <v>39</v>
       </c>
       <c r="G555" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="556" spans="1:7">
       <c r="A556" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B556" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C556" t="s">
         <v>296</v>
@@ -16462,12 +16462,12 @@
         <v>39</v>
       </c>
       <c r="G556" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="557" spans="1:7">
       <c r="A557" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B557" t="s">
         <v>30</v>
@@ -16485,7 +16485,7 @@
         <v>39</v>
       </c>
       <c r="G557" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="558" spans="1:7">
@@ -16496,7 +16496,7 @@
         <v>8</v>
       </c>
       <c r="C558" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D558" t="s">
         <v>46</v>
@@ -16505,21 +16505,21 @@
         <v>11</v>
       </c>
       <c r="F558" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="G558" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="559" spans="1:7">
       <c r="A559" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B559" t="s">
         <v>30</v>
       </c>
       <c r="C559" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D559" t="s">
         <v>46</v>
@@ -16531,7 +16531,7 @@
         <v>185</v>
       </c>
       <c r="G559" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="560" spans="1:7">
@@ -16551,10 +16551,10 @@
         <v>11</v>
       </c>
       <c r="F560" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G560" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="561" spans="1:7">
@@ -16565,7 +16565,7 @@
         <v>8</v>
       </c>
       <c r="C561" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D561" t="s">
         <v>31</v>
@@ -16574,21 +16574,21 @@
         <v>11</v>
       </c>
       <c r="F561" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="G561" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="562" spans="1:7">
       <c r="A562" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B562" t="s">
         <v>30</v>
       </c>
       <c r="C562" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D562" t="s">
         <v>31</v>
@@ -16600,18 +16600,18 @@
         <v>185</v>
       </c>
       <c r="G562" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="563" spans="1:7">
       <c r="A563" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B563" t="s">
         <v>30</v>
       </c>
       <c r="C563" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D563" t="s">
         <v>31</v>
@@ -16623,12 +16623,12 @@
         <v>216</v>
       </c>
       <c r="G563" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="564" spans="1:7">
       <c r="A564" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B564" t="s">
         <v>30</v>
@@ -16646,12 +16646,12 @@
         <v>68</v>
       </c>
       <c r="G564" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="565" spans="1:7">
       <c r="A565" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B565" t="s">
         <v>8</v>
@@ -16666,21 +16666,21 @@
         <v>11</v>
       </c>
       <c r="F565" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G565" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="566" spans="1:7">
       <c r="A566" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B566" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C566" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D566" t="s">
         <v>111</v>
@@ -16692,15 +16692,15 @@
         <v>185</v>
       </c>
       <c r="G566" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="567" spans="1:7">
       <c r="A567" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B567" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C567" t="s">
         <v>100</v>
@@ -16715,18 +16715,18 @@
         <v>68</v>
       </c>
       <c r="G567" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="568" spans="1:7">
       <c r="A568" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B568" t="s">
         <v>30</v>
       </c>
       <c r="C568" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D568" t="s">
         <v>14</v>
@@ -16738,12 +16738,12 @@
         <v>68</v>
       </c>
       <c r="G568" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="569" spans="1:7">
       <c r="A569" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B569" t="s">
         <v>8</v>
@@ -16758,21 +16758,21 @@
         <v>11</v>
       </c>
       <c r="F569" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G569" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="570" spans="1:7">
       <c r="A570" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B570" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C570" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D570" t="s">
         <v>78</v>
@@ -16784,7 +16784,7 @@
         <v>185</v>
       </c>
       <c r="G570" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="571" spans="1:7">
@@ -16792,10 +16792,10 @@
         <v>102</v>
       </c>
       <c r="B571" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C571" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D571" t="s">
         <v>38</v>
@@ -16807,12 +16807,12 @@
         <v>128</v>
       </c>
       <c r="G571" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="572" spans="1:7">
       <c r="A572" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B572" t="s">
         <v>30</v>
@@ -16830,7 +16830,7 @@
         <v>185</v>
       </c>
       <c r="G572" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="573" spans="1:7">
@@ -16853,12 +16853,12 @@
         <v>185</v>
       </c>
       <c r="G573" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="574" spans="1:7">
       <c r="A574" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B574" t="s">
         <v>30</v>
@@ -16876,18 +16876,18 @@
         <v>185</v>
       </c>
       <c r="G574" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="575" spans="1:7">
       <c r="A575" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B575" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C575" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D575" t="s">
         <v>43</v>
@@ -16899,12 +16899,12 @@
         <v>68</v>
       </c>
       <c r="G575" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="576" spans="1:7">
       <c r="A576" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B576" t="s">
         <v>8</v>
@@ -16919,15 +16919,15 @@
         <v>22</v>
       </c>
       <c r="F576" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="G576" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="577" spans="1:7">
       <c r="A577" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B577" t="s">
         <v>8</v>
@@ -16942,33 +16942,33 @@
         <v>22</v>
       </c>
       <c r="F577" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="G577" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="578" spans="1:7">
       <c r="A578" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B578" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C578" t="s">
         <v>55</v>
       </c>
       <c r="D578" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E578" t="s">
         <v>22</v>
       </c>
       <c r="F578" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G578" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="579" spans="1:7">
@@ -16988,18 +16988,18 @@
         <v>22</v>
       </c>
       <c r="F579" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="G579" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="580" spans="1:7">
       <c r="A580" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B580" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C580" t="s">
         <v>55</v>
@@ -17011,15 +17011,15 @@
         <v>22</v>
       </c>
       <c r="F580" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G580" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="581" spans="1:7">
       <c r="A581" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B581" t="s">
         <v>8</v>
@@ -17034,21 +17034,21 @@
         <v>22</v>
       </c>
       <c r="F581" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="G581" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="582" spans="1:7">
       <c r="A582" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B582" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C582" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D582" t="s">
         <v>38</v>
@@ -17057,18 +17057,18 @@
         <v>22</v>
       </c>
       <c r="F582" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="G582" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="583" spans="1:7">
       <c r="A583" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B583" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C583" t="s">
         <v>55</v>
@@ -17080,15 +17080,15 @@
         <v>22</v>
       </c>
       <c r="F583" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="G583" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="584" spans="1:7">
       <c r="A584" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B584" t="s">
         <v>8</v>
@@ -17103,21 +17103,21 @@
         <v>22</v>
       </c>
       <c r="F584" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="G584" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="585" spans="1:7">
       <c r="A585" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B585" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C585" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D585" t="s">
         <v>43</v>
@@ -17126,18 +17126,18 @@
         <v>22</v>
       </c>
       <c r="F585" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="G585" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="586" spans="1:7">
       <c r="A586" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B586" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C586" t="s">
         <v>55</v>
@@ -17149,10 +17149,10 @@
         <v>22</v>
       </c>
       <c r="F586" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="G586" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="587" spans="1:7">
@@ -17175,21 +17175,21 @@
         <v>128</v>
       </c>
       <c r="G587" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="588" spans="1:7">
       <c r="A588" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B588" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C588" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D588" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E588" t="s">
         <v>28</v>
@@ -17198,18 +17198,18 @@
         <v>68</v>
       </c>
       <c r="G588" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="589" spans="1:7">
       <c r="A589" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B589" t="s">
         <v>30</v>
       </c>
       <c r="C589" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D589" t="s">
         <v>10</v>
@@ -17221,18 +17221,18 @@
         <v>185</v>
       </c>
       <c r="G589" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="590" spans="1:7">
       <c r="A590" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B590" t="s">
         <v>8</v>
       </c>
       <c r="C590" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D590" t="s">
         <v>10</v>
@@ -17241,21 +17241,21 @@
         <v>28</v>
       </c>
       <c r="F590" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G590" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="591" spans="1:7">
       <c r="A591" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B591" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C591" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D591" t="s">
         <v>111</v>
@@ -17264,21 +17264,21 @@
         <v>28</v>
       </c>
       <c r="F591" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="G591" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="592" spans="1:7">
       <c r="A592" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B592" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C592" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D592" t="s">
         <v>111</v>
@@ -17290,18 +17290,18 @@
         <v>68</v>
       </c>
       <c r="G592" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="593" spans="1:7">
       <c r="A593" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B593" t="s">
         <v>8</v>
       </c>
       <c r="C593" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D593" t="s">
         <v>14</v>
@@ -17310,21 +17310,21 @@
         <v>28</v>
       </c>
       <c r="F593" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G593" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="594" spans="1:7">
       <c r="A594" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B594" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C594" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D594" t="s">
         <v>78</v>
@@ -17333,21 +17333,21 @@
         <v>28</v>
       </c>
       <c r="F594" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="G594" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="595" spans="1:7">
       <c r="A595" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B595" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C595" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D595" t="s">
         <v>78</v>
@@ -17359,7 +17359,7 @@
         <v>185</v>
       </c>
       <c r="G595" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="596" spans="1:7">
@@ -17382,12 +17382,12 @@
         <v>330</v>
       </c>
       <c r="G596" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="597" spans="1:7">
       <c r="A597" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B597" t="s">
         <v>30</v>
@@ -17405,12 +17405,12 @@
         <v>68</v>
       </c>
       <c r="G597" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="598" spans="1:7">
       <c r="A598" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B598" t="s">
         <v>30</v>
@@ -17428,15 +17428,15 @@
         <v>83</v>
       </c>
       <c r="G598" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="599" spans="1:7">
       <c r="A599" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B599" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C599" t="s">
         <v>207</v>
@@ -17451,12 +17451,12 @@
         <v>185</v>
       </c>
       <c r="G599" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="600" spans="1:7">
       <c r="A600" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B600" t="s">
         <v>30</v>
@@ -17474,12 +17474,12 @@
         <v>216</v>
       </c>
       <c r="G600" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="601" spans="1:7">
       <c r="A601" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B601" t="s">
         <v>30</v>
@@ -17497,18 +17497,18 @@
         <v>216</v>
       </c>
       <c r="G601" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="602" spans="1:7">
       <c r="A602" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B602" t="s">
         <v>30</v>
       </c>
       <c r="C602" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D602" t="s">
         <v>10</v>
@@ -17520,18 +17520,18 @@
         <v>216</v>
       </c>
       <c r="G602" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="603" spans="1:7">
       <c r="A603" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B603" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C603" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D603" t="s">
         <v>111</v>
@@ -17543,15 +17543,15 @@
         <v>68</v>
       </c>
       <c r="G603" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="604" spans="1:7">
       <c r="A604" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B604" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C604" t="s">
         <v>80</v>
@@ -17563,21 +17563,21 @@
         <v>47</v>
       </c>
       <c r="F604" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G604" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="605" spans="1:7">
       <c r="A605" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B605" t="s">
         <v>30</v>
       </c>
       <c r="C605" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D605" t="s">
         <v>14</v>
@@ -17589,15 +17589,15 @@
         <v>68</v>
       </c>
       <c r="G605" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="606" spans="1:7">
       <c r="A606" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B606" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C606" t="s">
         <v>80</v>
@@ -17609,18 +17609,18 @@
         <v>47</v>
       </c>
       <c r="F606" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G606" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="607" spans="1:7">
       <c r="A607" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B607" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C607" t="s">
         <v>55</v>
@@ -17635,7 +17635,7 @@
         <v>185</v>
       </c>
       <c r="G607" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="608" spans="1:7">
@@ -17646,7 +17646,7 @@
         <v>19</v>
       </c>
       <c r="C608" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D608" t="s">
         <v>21</v>
@@ -17658,7 +17658,7 @@
         <v>128</v>
       </c>
       <c r="G608" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="609" spans="1:7">
@@ -17666,7 +17666,7 @@
         <v>69</v>
       </c>
       <c r="B609" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C609" t="s">
         <v>454</v>
@@ -17681,12 +17681,12 @@
         <v>128</v>
       </c>
       <c r="G609" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="610" spans="1:7">
       <c r="A610" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B610" t="s">
         <v>19</v>
@@ -17704,18 +17704,18 @@
         <v>128</v>
       </c>
       <c r="G610" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="611" spans="1:7">
       <c r="A611" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B611" t="s">
         <v>19</v>
       </c>
       <c r="C611" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D611" t="s">
         <v>31</v>
@@ -17727,7 +17727,7 @@
         <v>128</v>
       </c>
       <c r="G611" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="612" spans="1:7">
@@ -17747,15 +17747,15 @@
         <v>63</v>
       </c>
       <c r="F612" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="G612" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="613" spans="1:7">
       <c r="A613" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B613" t="s">
         <v>30</v>
@@ -17773,15 +17773,15 @@
         <v>68</v>
       </c>
       <c r="G613" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="614" spans="1:7">
       <c r="A614" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B614" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C614" t="s">
         <v>55</v>
@@ -17796,12 +17796,12 @@
         <v>185</v>
       </c>
       <c r="G614" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="615" spans="1:7">
       <c r="A615" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B615" t="s">
         <v>30</v>
@@ -17819,15 +17819,15 @@
         <v>216</v>
       </c>
       <c r="G615" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="616" spans="1:7">
       <c r="A616" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B616" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C616" t="s">
         <v>55</v>
@@ -17842,12 +17842,12 @@
         <v>68</v>
       </c>
       <c r="G616" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="617" spans="1:7">
       <c r="A617" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B617" t="s">
         <v>30</v>
@@ -17865,18 +17865,18 @@
         <v>68</v>
       </c>
       <c r="G617" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="618" spans="1:7">
       <c r="A618" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B618" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C618" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D618" t="s">
         <v>43</v>
@@ -17888,12 +17888,12 @@
         <v>128</v>
       </c>
       <c r="G618" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="619" spans="1:7">
       <c r="A619" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B619" t="s">
         <v>30</v>
@@ -17911,12 +17911,12 @@
         <v>293</v>
       </c>
       <c r="G619" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="620" spans="1:7">
       <c r="A620" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B620" t="s">
         <v>30</v>
@@ -17934,12 +17934,12 @@
         <v>304</v>
       </c>
       <c r="G620" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="621" spans="1:7">
       <c r="A621" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B621" t="s">
         <v>19</v>
@@ -17957,12 +17957,12 @@
         <v>39</v>
       </c>
       <c r="G621" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="622" spans="1:7">
       <c r="A622" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B622" t="s">
         <v>30</v>
@@ -17980,12 +17980,12 @@
         <v>39</v>
       </c>
       <c r="G622" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="623" spans="1:7">
       <c r="A623" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B623" t="s">
         <v>19</v>
@@ -18003,12 +18003,12 @@
         <v>304</v>
       </c>
       <c r="G623" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="624" spans="1:7">
       <c r="A624" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B624" t="s">
         <v>30</v>
@@ -18026,12 +18026,12 @@
         <v>232</v>
       </c>
       <c r="G624" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="625" spans="1:7">
       <c r="A625" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B625" t="s">
         <v>30</v>
@@ -18049,12 +18049,12 @@
         <v>304</v>
       </c>
       <c r="G625" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="626" spans="1:7">
       <c r="A626" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B626" t="s">
         <v>30</v>
@@ -18072,18 +18072,18 @@
         <v>232</v>
       </c>
       <c r="G626" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="627" spans="1:7">
       <c r="A627" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B627" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C627" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D627" t="s">
         <v>38</v>
@@ -18095,12 +18095,12 @@
         <v>23</v>
       </c>
       <c r="G627" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="628" spans="1:7">
       <c r="A628" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B628" t="s">
         <v>30</v>
@@ -18118,12 +18118,12 @@
         <v>232</v>
       </c>
       <c r="G628" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="629" spans="1:7">
       <c r="A629" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B629" t="s">
         <v>30</v>
@@ -18141,18 +18141,18 @@
         <v>304</v>
       </c>
       <c r="G629" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="630" spans="1:7">
       <c r="A630" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B630" t="s">
         <v>19</v>
       </c>
       <c r="C630" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D630" t="s">
         <v>10</v>
@@ -18164,18 +18164,18 @@
         <v>304</v>
       </c>
       <c r="G630" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="631" spans="1:7">
       <c r="A631" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B631" t="s">
         <v>19</v>
       </c>
       <c r="C631" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D631" t="s">
         <v>21</v>
@@ -18187,12 +18187,12 @@
         <v>304</v>
       </c>
       <c r="G631" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="632" spans="1:7">
       <c r="A632" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B632" t="s">
         <v>19</v>
@@ -18210,12 +18210,12 @@
         <v>129</v>
       </c>
       <c r="G632" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="633" spans="1:7">
       <c r="A633" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B633" t="s">
         <v>30</v>
@@ -18233,18 +18233,18 @@
         <v>29</v>
       </c>
       <c r="G633" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="634" spans="1:7">
       <c r="A634" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B634" t="s">
         <v>30</v>
       </c>
       <c r="C634" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D634" t="s">
         <v>46</v>
@@ -18256,18 +18256,18 @@
         <v>304</v>
       </c>
       <c r="G634" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="635" spans="1:7">
       <c r="A635" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B635" t="s">
         <v>8</v>
       </c>
       <c r="C635" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D635" t="s">
         <v>10</v>
@@ -18279,18 +18279,18 @@
         <v>83</v>
       </c>
       <c r="G635" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="636" spans="1:7">
       <c r="A636" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B636" t="s">
         <v>8</v>
       </c>
       <c r="C636" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D636" t="s">
         <v>10</v>
@@ -18299,21 +18299,21 @@
         <v>47</v>
       </c>
       <c r="F636" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G636" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="637" spans="1:7">
       <c r="A637" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B637" t="s">
         <v>8</v>
       </c>
       <c r="C637" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D637" t="s">
         <v>14</v>
@@ -18325,18 +18325,18 @@
         <v>83</v>
       </c>
       <c r="G637" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="638" spans="1:7">
       <c r="A638" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B638" t="s">
         <v>8</v>
       </c>
       <c r="C638" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D638" t="s">
         <v>14</v>
@@ -18345,15 +18345,15 @@
         <v>47</v>
       </c>
       <c r="F638" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G638" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="639" spans="1:7">
       <c r="A639" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B639" t="s">
         <v>19</v>
@@ -18371,18 +18371,18 @@
         <v>304</v>
       </c>
       <c r="G639" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="640" spans="1:7">
       <c r="A640" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B640" t="s">
         <v>19</v>
       </c>
       <c r="C640" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D640" t="s">
         <v>17</v>
@@ -18394,12 +18394,12 @@
         <v>304</v>
       </c>
       <c r="G640" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="641" spans="1:7">
       <c r="A641" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B641" t="s">
         <v>8</v>
@@ -18414,21 +18414,21 @@
         <v>63</v>
       </c>
       <c r="F641" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="G641" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="642" spans="1:7">
       <c r="A642" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B642" t="s">
         <v>30</v>
       </c>
       <c r="C642" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D642" t="s">
         <v>46</v>
@@ -18440,18 +18440,18 @@
         <v>232</v>
       </c>
       <c r="G642" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="643" spans="1:7">
       <c r="A643" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B643" t="s">
         <v>8</v>
       </c>
       <c r="C643" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D643" t="s">
         <v>10</v>
@@ -18460,15 +18460,15 @@
         <v>63</v>
       </c>
       <c r="F643" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G643" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="644" spans="1:7">
       <c r="A644" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B644" t="s">
         <v>8</v>
@@ -18486,18 +18486,18 @@
         <v>83</v>
       </c>
       <c r="G644" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="645" spans="1:7">
       <c r="A645" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B645" t="s">
         <v>8</v>
       </c>
       <c r="C645" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D645" t="s">
         <v>14</v>
@@ -18506,15 +18506,15 @@
         <v>63</v>
       </c>
       <c r="F645" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G645" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="646" spans="1:7">
       <c r="A646" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B646" t="s">
         <v>8</v>
@@ -18532,18 +18532,18 @@
         <v>83</v>
       </c>
       <c r="G646" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="647" spans="1:7">
       <c r="A647" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B647" t="s">
         <v>19</v>
       </c>
       <c r="C647" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D647" t="s">
         <v>21</v>
@@ -18555,12 +18555,12 @@
         <v>304</v>
       </c>
       <c r="G647" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="648" spans="1:7">
       <c r="A648" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B648" t="s">
         <v>8</v>
@@ -18575,21 +18575,21 @@
         <v>63</v>
       </c>
       <c r="F648" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="G648" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="649" spans="1:7">
       <c r="A649" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B649" t="s">
         <v>30</v>
       </c>
       <c r="C649" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D649" t="s">
         <v>17</v>
@@ -18601,7 +18601,7 @@
         <v>232</v>
       </c>
       <c r="G649" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="650" spans="1:7">
@@ -19203,9 +19203,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G675" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$675</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4725" uniqueCount="893">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4725" uniqueCount="892">
   <si>
     <t>Enseignements</t>
   </si>
@@ -1448,7 +1451,7 @@
     <t>Labo A19 /SG11</t>
   </si>
   <si>
-    <t>TP-Programation Python</t>
+    <t>TP-Programmation Python</t>
   </si>
   <si>
     <t>TP-PPYTH-L2ELT</t>
@@ -2469,9 +2472,6 @@
   </si>
   <si>
     <t>TD-Electronique fondamentale 1-G5</t>
-  </si>
-  <si>
-    <t>TP-Programmation Python</t>
   </si>
   <si>
     <t>salle micro 3/G41/G42</t>
@@ -2718,14 +2718,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3181,28 +3174,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3211,118 +3207,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3673,9 +3666,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G675"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="59.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="6" max="6" width="43.5714285714286" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
@@ -3700,7 +3698,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" hidden="1" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -3723,7 +3721,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" hidden="1" spans="1:7">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -3746,7 +3744,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" hidden="1" spans="1:7">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -3769,7 +3767,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" hidden="1" spans="1:7">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -3792,7 +3790,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" hidden="1" spans="1:7">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -3815,7 +3813,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" hidden="1" spans="1:7">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -3838,7 +3836,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" hidden="1" spans="1:7">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -3861,7 +3859,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" hidden="1" spans="1:7">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -3884,7 +3882,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" hidden="1" spans="1:7">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -3907,7 +3905,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" hidden="1" spans="1:7">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -3930,7 +3928,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" hidden="1" spans="1:7">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -3953,7 +3951,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" hidden="1" spans="1:7">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -3976,7 +3974,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" hidden="1" spans="1:7">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -3999,7 +3997,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" hidden="1" spans="1:7">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -4022,7 +4020,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" hidden="1" spans="1:7">
       <c r="A16" t="s">
         <v>54</v>
       </c>
@@ -4045,7 +4043,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" hidden="1" spans="1:7">
       <c r="A17" t="s">
         <v>56</v>
       </c>
@@ -4068,7 +4066,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" hidden="1" spans="1:7">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -4091,7 +4089,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" hidden="1" spans="1:7">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -4114,7 +4112,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" hidden="1" spans="1:7">
       <c r="A20" t="s">
         <v>64</v>
       </c>
@@ -4137,7 +4135,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" hidden="1" spans="1:7">
       <c r="A21" t="s">
         <v>65</v>
       </c>
@@ -4160,7 +4158,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" hidden="1" spans="1:7">
       <c r="A22" t="s">
         <v>66</v>
       </c>
@@ -4183,7 +4181,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" hidden="1" spans="1:7">
       <c r="A23" t="s">
         <v>67</v>
       </c>
@@ -4206,7 +4204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" hidden="1" spans="1:7">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -4229,7 +4227,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" hidden="1" spans="1:7">
       <c r="A25" t="s">
         <v>69</v>
       </c>
@@ -4252,7 +4250,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" hidden="1" spans="1:7">
       <c r="A26" t="s">
         <v>73</v>
       </c>
@@ -4275,7 +4273,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" hidden="1" spans="1:7">
       <c r="A27" t="s">
         <v>75</v>
       </c>
@@ -4298,7 +4296,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" hidden="1" spans="1:7">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -4321,7 +4319,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" hidden="1" spans="1:7">
       <c r="A29" t="s">
         <v>82</v>
       </c>
@@ -4344,7 +4342,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" hidden="1" spans="1:7">
       <c r="A30" t="s">
         <v>84</v>
       </c>
@@ -4367,7 +4365,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" hidden="1" spans="1:7">
       <c r="A31" t="s">
         <v>86</v>
       </c>
@@ -4390,7 +4388,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" hidden="1" spans="1:7">
       <c r="A32" t="s">
         <v>88</v>
       </c>
@@ -4413,7 +4411,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" hidden="1" spans="1:7">
       <c r="A33" t="s">
         <v>91</v>
       </c>
@@ -4436,7 +4434,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" hidden="1" spans="1:7">
       <c r="A34" t="s">
         <v>92</v>
       </c>
@@ -4459,7 +4457,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" hidden="1" spans="1:7">
       <c r="A35" t="s">
         <v>96</v>
       </c>
@@ -4482,7 +4480,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" hidden="1" spans="1:7">
       <c r="A36" t="s">
         <v>96</v>
       </c>
@@ -4505,7 +4503,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" hidden="1" spans="1:7">
       <c r="A37" t="s">
         <v>98</v>
       </c>
@@ -4528,7 +4526,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" hidden="1" spans="1:7">
       <c r="A38" t="s">
         <v>101</v>
       </c>
@@ -4551,7 +4549,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" hidden="1" spans="1:7">
       <c r="A39" t="s">
         <v>102</v>
       </c>
@@ -4574,7 +4572,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" hidden="1" spans="1:7">
       <c r="A40" t="s">
         <v>103</v>
       </c>
@@ -4597,7 +4595,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" hidden="1" spans="1:7">
       <c r="A41" t="s">
         <v>105</v>
       </c>
@@ -4620,7 +4618,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" hidden="1" spans="1:7">
       <c r="A42" t="s">
         <v>107</v>
       </c>
@@ -4643,7 +4641,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" hidden="1" spans="1:7">
       <c r="A43" t="s">
         <v>109</v>
       </c>
@@ -4666,7 +4664,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" hidden="1" spans="1:7">
       <c r="A44" t="s">
         <v>112</v>
       </c>
@@ -4689,7 +4687,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" hidden="1" spans="1:7">
       <c r="A45" t="s">
         <v>114</v>
       </c>
@@ -4712,7 +4710,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" hidden="1" spans="1:7">
       <c r="A46" t="s">
         <v>117</v>
       </c>
@@ -4735,7 +4733,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" hidden="1" spans="1:7">
       <c r="A47" t="s">
         <v>118</v>
       </c>
@@ -4758,7 +4756,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" hidden="1" spans="1:7">
       <c r="A48" t="s">
         <v>119</v>
       </c>
@@ -4781,7 +4779,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" hidden="1" spans="1:7">
       <c r="A49" t="s">
         <v>69</v>
       </c>
@@ -4804,7 +4802,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" hidden="1" spans="1:7">
       <c r="A50" t="s">
         <v>96</v>
       </c>
@@ -4827,7 +4825,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" hidden="1" spans="1:7">
       <c r="A51" t="s">
         <v>96</v>
       </c>
@@ -4850,7 +4848,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" hidden="1" spans="1:7">
       <c r="A52" t="s">
         <v>123</v>
       </c>
@@ -4873,7 +4871,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" hidden="1" spans="1:7">
       <c r="A53" t="s">
         <v>124</v>
       </c>
@@ -4896,7 +4894,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" hidden="1" spans="1:7">
       <c r="A54" t="s">
         <v>125</v>
       </c>
@@ -4919,7 +4917,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" hidden="1" spans="1:7">
       <c r="A55" t="s">
         <v>126</v>
       </c>
@@ -4942,7 +4940,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" hidden="1" spans="1:7">
       <c r="A56" t="s">
         <v>92</v>
       </c>
@@ -4965,7 +4963,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" hidden="1" spans="1:7">
       <c r="A57" t="s">
         <v>73</v>
       </c>
@@ -4988,7 +4986,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" hidden="1" spans="1:7">
       <c r="A58" t="s">
         <v>75</v>
       </c>
@@ -5011,7 +5009,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" hidden="1" spans="1:7">
       <c r="A59" t="s">
         <v>98</v>
       </c>
@@ -5034,7 +5032,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" hidden="1" spans="1:7">
       <c r="A60" t="s">
         <v>101</v>
       </c>
@@ -5057,7 +5055,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" hidden="1" spans="1:7">
       <c r="A61" t="s">
         <v>102</v>
       </c>
@@ -5080,7 +5078,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" hidden="1" spans="1:7">
       <c r="A62" t="s">
         <v>131</v>
       </c>
@@ -5103,7 +5101,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" hidden="1" spans="1:7">
       <c r="A63" t="s">
         <v>132</v>
       </c>
@@ -5126,7 +5124,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" hidden="1" spans="1:7">
       <c r="A64" t="s">
         <v>103</v>
       </c>
@@ -5149,7 +5147,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" hidden="1" spans="1:7">
       <c r="A65" t="s">
         <v>105</v>
       </c>
@@ -5172,7 +5170,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" hidden="1" spans="1:7">
       <c r="A66" t="s">
         <v>107</v>
       </c>
@@ -5195,7 +5193,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" hidden="1" spans="1:7">
       <c r="A67" t="s">
         <v>109</v>
       </c>
@@ -5218,7 +5216,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" hidden="1" spans="1:7">
       <c r="A68" t="s">
         <v>112</v>
       </c>
@@ -5241,7 +5239,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" hidden="1" spans="1:7">
       <c r="A69" t="s">
         <v>137</v>
       </c>
@@ -5264,7 +5262,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" hidden="1" spans="1:7">
       <c r="A70" t="s">
         <v>138</v>
       </c>
@@ -5287,7 +5285,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" hidden="1" spans="1:7">
       <c r="A71" t="s">
         <v>139</v>
       </c>
@@ -5310,7 +5308,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" hidden="1" spans="1:7">
       <c r="A72" t="s">
         <v>140</v>
       </c>
@@ -5333,7 +5331,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" hidden="1" spans="1:7">
       <c r="A73" t="s">
         <v>142</v>
       </c>
@@ -5356,7 +5354,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" hidden="1" spans="1:7">
       <c r="A74" t="s">
         <v>145</v>
       </c>
@@ -5379,7 +5377,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" hidden="1" spans="1:7">
       <c r="A75" t="s">
         <v>147</v>
       </c>
@@ -5402,7 +5400,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" hidden="1" spans="1:7">
       <c r="A76" t="s">
         <v>149</v>
       </c>
@@ -5425,7 +5423,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" hidden="1" spans="1:7">
       <c r="A77" t="s">
         <v>152</v>
       </c>
@@ -5448,7 +5446,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" hidden="1" spans="1:7">
       <c r="A78" t="s">
         <v>154</v>
       </c>
@@ -5471,7 +5469,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" hidden="1" spans="1:7">
       <c r="A79" t="s">
         <v>156</v>
       </c>
@@ -5494,7 +5492,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" hidden="1" spans="1:7">
       <c r="A80" t="s">
         <v>157</v>
       </c>
@@ -5517,7 +5515,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" hidden="1" spans="1:7">
       <c r="A81" t="s">
         <v>158</v>
       </c>
@@ -5540,7 +5538,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" hidden="1" spans="1:7">
       <c r="A82" t="s">
         <v>160</v>
       </c>
@@ -5563,7 +5561,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" hidden="1" spans="1:7">
       <c r="A83" t="s">
         <v>162</v>
       </c>
@@ -5586,7 +5584,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" hidden="1" spans="1:7">
       <c r="A84" t="s">
         <v>162</v>
       </c>
@@ -5609,7 +5607,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" hidden="1" spans="1:7">
       <c r="A85" t="s">
         <v>164</v>
       </c>
@@ -5632,7 +5630,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" hidden="1" spans="1:7">
       <c r="A86" t="s">
         <v>165</v>
       </c>
@@ -5655,7 +5653,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" hidden="1" spans="1:7">
       <c r="A87" t="s">
         <v>167</v>
       </c>
@@ -5678,7 +5676,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" hidden="1" spans="1:7">
       <c r="A88" t="s">
         <v>167</v>
       </c>
@@ -5701,7 +5699,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" hidden="1" spans="1:7">
       <c r="A89" t="s">
         <v>170</v>
       </c>
@@ -5724,7 +5722,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" hidden="1" spans="1:7">
       <c r="A90" t="s">
         <v>173</v>
       </c>
@@ -5747,7 +5745,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" hidden="1" spans="1:7">
       <c r="A91" t="s">
         <v>175</v>
       </c>
@@ -5770,7 +5768,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" hidden="1" spans="1:7">
       <c r="A92" t="s">
         <v>173</v>
       </c>
@@ -5793,7 +5791,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" hidden="1" spans="1:7">
       <c r="A93" t="s">
         <v>177</v>
       </c>
@@ -5816,7 +5814,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" hidden="1" spans="1:7">
       <c r="A94" t="s">
         <v>179</v>
       </c>
@@ -5839,7 +5837,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" hidden="1" spans="1:7">
       <c r="A95" t="s">
         <v>181</v>
       </c>
@@ -5862,7 +5860,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" hidden="1" spans="1:7">
       <c r="A96" t="s">
         <v>182</v>
       </c>
@@ -5885,7 +5883,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" hidden="1" spans="1:7">
       <c r="A97" t="s">
         <v>183</v>
       </c>
@@ -5908,7 +5906,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" hidden="1" spans="1:7">
       <c r="A98" t="s">
         <v>187</v>
       </c>
@@ -5931,7 +5929,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" hidden="1" spans="1:7">
       <c r="A99" t="s">
         <v>189</v>
       </c>
@@ -5954,7 +5952,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" hidden="1" spans="1:7">
       <c r="A100" t="s">
         <v>187</v>
       </c>
@@ -5977,7 +5975,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" hidden="1" spans="1:7">
       <c r="A101" t="s">
         <v>189</v>
       </c>
@@ -6000,7 +5998,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" hidden="1" spans="1:7">
       <c r="A102" t="s">
         <v>192</v>
       </c>
@@ -6023,7 +6021,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" hidden="1" spans="1:7">
       <c r="A103" t="s">
         <v>194</v>
       </c>
@@ -6046,7 +6044,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" hidden="1" spans="1:7">
       <c r="A104" t="s">
         <v>195</v>
       </c>
@@ -6069,7 +6067,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" hidden="1" spans="1:7">
       <c r="A105" t="s">
         <v>196</v>
       </c>
@@ -6092,7 +6090,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" hidden="1" spans="1:7">
       <c r="A106" t="s">
         <v>195</v>
       </c>
@@ -6115,7 +6113,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" hidden="1" spans="1:7">
       <c r="A107" t="s">
         <v>196</v>
       </c>
@@ -6138,7 +6136,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" hidden="1" spans="1:7">
       <c r="A108" t="s">
         <v>198</v>
       </c>
@@ -6161,7 +6159,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" hidden="1" spans="1:7">
       <c r="A109" t="s">
         <v>199</v>
       </c>
@@ -6184,7 +6182,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" hidden="1" spans="1:7">
       <c r="A110" t="s">
         <v>200</v>
       </c>
@@ -6207,7 +6205,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" hidden="1" spans="1:7">
       <c r="A111" t="s">
         <v>201</v>
       </c>
@@ -6230,7 +6228,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" hidden="1" spans="1:7">
       <c r="A112" t="s">
         <v>201</v>
       </c>
@@ -6253,7 +6251,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" hidden="1" spans="1:7">
       <c r="A113" t="s">
         <v>203</v>
       </c>
@@ -6276,7 +6274,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" hidden="1" spans="1:7">
       <c r="A114" t="s">
         <v>205</v>
       </c>
@@ -6299,7 +6297,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" hidden="1" spans="1:7">
       <c r="A115" t="s">
         <v>206</v>
       </c>
@@ -6322,7 +6320,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" hidden="1" spans="1:7">
       <c r="A116" t="s">
         <v>208</v>
       </c>
@@ -6345,7 +6343,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" hidden="1" spans="1:7">
       <c r="A117" t="s">
         <v>209</v>
       </c>
@@ -6368,7 +6366,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" hidden="1" spans="1:7">
       <c r="A118" t="s">
         <v>210</v>
       </c>
@@ -6391,7 +6389,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" hidden="1" spans="1:7">
       <c r="A119" t="s">
         <v>211</v>
       </c>
@@ -6414,7 +6412,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" hidden="1" spans="1:7">
       <c r="A120" t="s">
         <v>211</v>
       </c>
@@ -6437,7 +6435,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" hidden="1" spans="1:7">
       <c r="A121" t="s">
         <v>212</v>
       </c>
@@ -6460,7 +6458,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" hidden="1" spans="1:7">
       <c r="A122" t="s">
         <v>214</v>
       </c>
@@ -6483,7 +6481,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" hidden="1" spans="1:7">
       <c r="A123" t="s">
         <v>217</v>
       </c>
@@ -6506,7 +6504,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" hidden="1" spans="1:7">
       <c r="A124" t="s">
         <v>218</v>
       </c>
@@ -6529,7 +6527,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" hidden="1" spans="1:7">
       <c r="A125" t="s">
         <v>220</v>
       </c>
@@ -6552,7 +6550,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" hidden="1" spans="1:7">
       <c r="A126" t="s">
         <v>222</v>
       </c>
@@ -6575,7 +6573,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" hidden="1" spans="1:7">
       <c r="A127" t="s">
         <v>222</v>
       </c>
@@ -6598,7 +6596,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" hidden="1" spans="1:7">
       <c r="A128" t="s">
         <v>220</v>
       </c>
@@ -6621,7 +6619,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" hidden="1" spans="1:7">
       <c r="A129" t="s">
         <v>225</v>
       </c>
@@ -6644,7 +6642,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" hidden="1" spans="1:7">
       <c r="A130" t="s">
         <v>226</v>
       </c>
@@ -6667,7 +6665,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" hidden="1" spans="1:7">
       <c r="A131" t="s">
         <v>229</v>
       </c>
@@ -6690,7 +6688,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" hidden="1" spans="1:7">
       <c r="A132" t="s">
         <v>230</v>
       </c>
@@ -6713,7 +6711,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" hidden="1" spans="1:7">
       <c r="A133" t="s">
         <v>230</v>
       </c>
@@ -6736,7 +6734,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" hidden="1" spans="1:7">
       <c r="A134" t="s">
         <v>233</v>
       </c>
@@ -6759,7 +6757,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" hidden="1" spans="1:7">
       <c r="A135" t="s">
         <v>234</v>
       </c>
@@ -6782,7 +6780,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" hidden="1" spans="1:7">
       <c r="A136" t="s">
         <v>235</v>
       </c>
@@ -6805,7 +6803,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" hidden="1" spans="1:7">
       <c r="A137" t="s">
         <v>237</v>
       </c>
@@ -6828,7 +6826,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" hidden="1" spans="1:7">
       <c r="A138" t="s">
         <v>238</v>
       </c>
@@ -6851,7 +6849,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" hidden="1" spans="1:7">
       <c r="A139" t="s">
         <v>241</v>
       </c>
@@ -6874,7 +6872,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" hidden="1" spans="1:7">
       <c r="A140" t="s">
         <v>242</v>
       </c>
@@ -6897,7 +6895,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" hidden="1" spans="1:7">
       <c r="A141" t="s">
         <v>244</v>
       </c>
@@ -6920,7 +6918,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" hidden="1" spans="1:7">
       <c r="A142" t="s">
         <v>244</v>
       </c>
@@ -6943,7 +6941,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" hidden="1" spans="1:7">
       <c r="A143" t="s">
         <v>242</v>
       </c>
@@ -6966,7 +6964,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" hidden="1" spans="1:7">
       <c r="A144" t="s">
         <v>245</v>
       </c>
@@ -6989,7 +6987,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" hidden="1" spans="1:7">
       <c r="A145" t="s">
         <v>247</v>
       </c>
@@ -7012,7 +7010,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" hidden="1" spans="1:7">
       <c r="A146" t="s">
         <v>238</v>
       </c>
@@ -7035,7 +7033,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" hidden="1" spans="1:7">
       <c r="A147" t="s">
         <v>248</v>
       </c>
@@ -7058,7 +7056,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" hidden="1" spans="1:7">
       <c r="A148" t="s">
         <v>251</v>
       </c>
@@ -7081,7 +7079,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" hidden="1" spans="1:7">
       <c r="A149" t="s">
         <v>253</v>
       </c>
@@ -7104,7 +7102,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" hidden="1" spans="1:7">
       <c r="A150" t="s">
         <v>254</v>
       </c>
@@ -7127,7 +7125,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" hidden="1" spans="1:7">
       <c r="A151" t="s">
         <v>255</v>
       </c>
@@ -7150,7 +7148,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" hidden="1" spans="1:7">
       <c r="A152" t="s">
         <v>256</v>
       </c>
@@ -7173,7 +7171,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" hidden="1" spans="1:7">
       <c r="A153" t="s">
         <v>260</v>
       </c>
@@ -7196,7 +7194,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" hidden="1" spans="1:7">
       <c r="A154" t="s">
         <v>256</v>
       </c>
@@ -7219,7 +7217,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" hidden="1" spans="1:7">
       <c r="A155" t="s">
         <v>260</v>
       </c>
@@ -7242,7 +7240,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" hidden="1" spans="1:7">
       <c r="A156" t="s">
         <v>266</v>
       </c>
@@ -7265,7 +7263,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" hidden="1" spans="1:7">
       <c r="A157" t="s">
         <v>268</v>
       </c>
@@ -7288,7 +7286,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" hidden="1" spans="1:7">
       <c r="A158" t="s">
         <v>269</v>
       </c>
@@ -7311,7 +7309,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" hidden="1" spans="1:7">
       <c r="A159" t="s">
         <v>270</v>
       </c>
@@ -7334,7 +7332,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="160" spans="1:7">
+    <row r="160" hidden="1" spans="1:7">
       <c r="A160" t="s">
         <v>272</v>
       </c>
@@ -7357,7 +7355,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="161" spans="1:7">
+    <row r="161" hidden="1" spans="1:7">
       <c r="A161" t="s">
         <v>273</v>
       </c>
@@ -7380,7 +7378,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="162" spans="1:7">
+    <row r="162" hidden="1" spans="1:7">
       <c r="A162" t="s">
         <v>274</v>
       </c>
@@ -7403,7 +7401,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="163" spans="1:7">
+    <row r="163" hidden="1" spans="1:7">
       <c r="A163" t="s">
         <v>274</v>
       </c>
@@ -7426,7 +7424,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" hidden="1" spans="1:7">
       <c r="A164" t="s">
         <v>277</v>
       </c>
@@ -7449,7 +7447,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="165" spans="1:7">
+    <row r="165" hidden="1" spans="1:7">
       <c r="A165" t="s">
         <v>279</v>
       </c>
@@ -7472,7 +7470,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" hidden="1" spans="1:7">
       <c r="A166" t="s">
         <v>281</v>
       </c>
@@ -7495,7 +7493,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" hidden="1" spans="1:7">
       <c r="A167" t="s">
         <v>281</v>
       </c>
@@ -7518,7 +7516,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="168" spans="1:7">
+    <row r="168" hidden="1" spans="1:7">
       <c r="A168" t="s">
         <v>284</v>
       </c>
@@ -7541,7 +7539,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" hidden="1" spans="1:7">
       <c r="A169" t="s">
         <v>287</v>
       </c>
@@ -7564,7 +7562,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" hidden="1" spans="1:7">
       <c r="A170" t="s">
         <v>288</v>
       </c>
@@ -7587,7 +7585,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" hidden="1" spans="1:7">
       <c r="A171" t="s">
         <v>292</v>
       </c>
@@ -7610,7 +7608,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" hidden="1" spans="1:7">
       <c r="A172" t="s">
         <v>294</v>
       </c>
@@ -7633,7 +7631,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" hidden="1" spans="1:7">
       <c r="A173" t="s">
         <v>295</v>
       </c>
@@ -7656,7 +7654,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" hidden="1" spans="1:7">
       <c r="A174" t="s">
         <v>297</v>
       </c>
@@ -7679,7 +7677,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" hidden="1" spans="1:7">
       <c r="A175" t="s">
         <v>299</v>
       </c>
@@ -7702,7 +7700,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" hidden="1" spans="1:7">
       <c r="A176" t="s">
         <v>301</v>
       </c>
@@ -7725,7 +7723,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" hidden="1" spans="1:7">
       <c r="A177" t="s">
         <v>302</v>
       </c>
@@ -7748,7 +7746,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" hidden="1" spans="1:7">
       <c r="A178" t="s">
         <v>305</v>
       </c>
@@ -7771,7 +7769,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" hidden="1" spans="1:7">
       <c r="A179" t="s">
         <v>306</v>
       </c>
@@ -7794,7 +7792,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" hidden="1" spans="1:7">
       <c r="A180" t="s">
         <v>308</v>
       </c>
@@ -7817,7 +7815,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" hidden="1" spans="1:7">
       <c r="A181" t="s">
         <v>309</v>
       </c>
@@ -7840,7 +7838,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" hidden="1" spans="1:7">
       <c r="A182" t="s">
         <v>311</v>
       </c>
@@ -7863,7 +7861,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" hidden="1" spans="1:7">
       <c r="A183" t="s">
         <v>314</v>
       </c>
@@ -7886,7 +7884,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" hidden="1" spans="1:7">
       <c r="A184" t="s">
         <v>315</v>
       </c>
@@ -7909,7 +7907,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" hidden="1" spans="1:7">
       <c r="A185" t="s">
         <v>317</v>
       </c>
@@ -7932,7 +7930,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" hidden="1" spans="1:7">
       <c r="A186" t="s">
         <v>318</v>
       </c>
@@ -7955,7 +7953,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" hidden="1" spans="1:7">
       <c r="A187" t="s">
         <v>320</v>
       </c>
@@ -7978,7 +7976,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" hidden="1" spans="1:7">
       <c r="A188" t="s">
         <v>322</v>
       </c>
@@ -8001,7 +7999,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" hidden="1" spans="1:7">
       <c r="A189" t="s">
         <v>323</v>
       </c>
@@ -8024,7 +8022,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" hidden="1" spans="1:7">
       <c r="A190" t="s">
         <v>327</v>
       </c>
@@ -8047,7 +8045,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" hidden="1" spans="1:7">
       <c r="A191" t="s">
         <v>331</v>
       </c>
@@ -8070,7 +8068,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="192" spans="1:7">
+    <row r="192" hidden="1" spans="1:7">
       <c r="A192" t="s">
         <v>49</v>
       </c>
@@ -8093,7 +8091,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="193" spans="1:7">
+    <row r="193" hidden="1" spans="1:7">
       <c r="A193" t="s">
         <v>334</v>
       </c>
@@ -8116,7 +8114,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" hidden="1" spans="1:7">
       <c r="A194" t="s">
         <v>323</v>
       </c>
@@ -8139,7 +8137,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="195" spans="1:7">
+    <row r="195" hidden="1" spans="1:7">
       <c r="A195" t="s">
         <v>327</v>
       </c>
@@ -8162,7 +8160,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="196" spans="1:7">
+    <row r="196" hidden="1" spans="1:7">
       <c r="A196" t="s">
         <v>52</v>
       </c>
@@ -8185,7 +8183,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="197" spans="1:7">
+    <row r="197" hidden="1" spans="1:7">
       <c r="A197" t="s">
         <v>338</v>
       </c>
@@ -8208,7 +8206,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="198" spans="1:7">
+    <row r="198" hidden="1" spans="1:7">
       <c r="A198" t="s">
         <v>339</v>
       </c>
@@ -8231,7 +8229,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="199" spans="1:7">
+    <row r="199" hidden="1" spans="1:7">
       <c r="A199" t="s">
         <v>340</v>
       </c>
@@ -8254,7 +8252,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="200" spans="1:7">
+    <row r="200" hidden="1" spans="1:7">
       <c r="A200" t="s">
         <v>344</v>
       </c>
@@ -8277,7 +8275,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="201" spans="1:7">
+    <row r="201" hidden="1" spans="1:7">
       <c r="A201" t="s">
         <v>345</v>
       </c>
@@ -8300,7 +8298,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="202" spans="1:7">
+    <row r="202" hidden="1" spans="1:7">
       <c r="A202" t="s">
         <v>346</v>
       </c>
@@ -8323,7 +8321,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="203" spans="1:7">
+    <row r="203" hidden="1" spans="1:7">
       <c r="A203" t="s">
         <v>339</v>
       </c>
@@ -8346,7 +8344,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="204" spans="1:7">
+    <row r="204" hidden="1" spans="1:7">
       <c r="A204" t="s">
         <v>340</v>
       </c>
@@ -8369,7 +8367,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="205" spans="1:7">
+    <row r="205" hidden="1" spans="1:7">
       <c r="A205" t="s">
         <v>344</v>
       </c>
@@ -8392,7 +8390,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="206" spans="1:7">
+    <row r="206" hidden="1" spans="1:7">
       <c r="A206" t="s">
         <v>347</v>
       </c>
@@ -8415,7 +8413,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="207" spans="1:7">
+    <row r="207" hidden="1" spans="1:7">
       <c r="A207" t="s">
         <v>348</v>
       </c>
@@ -8438,7 +8436,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="208" spans="1:7">
+    <row r="208" hidden="1" spans="1:7">
       <c r="A208" t="s">
         <v>349</v>
       </c>
@@ -8461,7 +8459,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="209" spans="1:7">
+    <row r="209" hidden="1" spans="1:7">
       <c r="A209" t="s">
         <v>350</v>
       </c>
@@ -8484,7 +8482,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="210" spans="1:7">
+    <row r="210" hidden="1" spans="1:7">
       <c r="A210" t="s">
         <v>351</v>
       </c>
@@ -8507,7 +8505,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="211" spans="1:7">
+    <row r="211" hidden="1" spans="1:7">
       <c r="A211" t="s">
         <v>353</v>
       </c>
@@ -8530,7 +8528,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="212" spans="1:7">
+    <row r="212" hidden="1" spans="1:7">
       <c r="A212" t="s">
         <v>354</v>
       </c>
@@ -8553,7 +8551,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="213" spans="1:7">
+    <row r="213" hidden="1" spans="1:7">
       <c r="A213" t="s">
         <v>356</v>
       </c>
@@ -8576,7 +8574,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="214" spans="1:7">
+    <row r="214" hidden="1" spans="1:7">
       <c r="A214" t="s">
         <v>358</v>
       </c>
@@ -8599,7 +8597,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="215" spans="1:7">
+    <row r="215" hidden="1" spans="1:7">
       <c r="A215" t="s">
         <v>353</v>
       </c>
@@ -8622,7 +8620,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="216" spans="1:7">
+    <row r="216" hidden="1" spans="1:7">
       <c r="A216" t="s">
         <v>354</v>
       </c>
@@ -8645,7 +8643,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="217" spans="1:7">
+    <row r="217" hidden="1" spans="1:7">
       <c r="A217" t="s">
         <v>356</v>
       </c>
@@ -8668,7 +8666,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="218" spans="1:7">
+    <row r="218" hidden="1" spans="1:7">
       <c r="A218" t="s">
         <v>359</v>
       </c>
@@ -8691,7 +8689,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="219" spans="1:7">
+    <row r="219" hidden="1" spans="1:7">
       <c r="A219" t="s">
         <v>360</v>
       </c>
@@ -8714,7 +8712,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="220" spans="1:7">
+    <row r="220" hidden="1" spans="1:7">
       <c r="A220" t="s">
         <v>361</v>
       </c>
@@ -8737,7 +8735,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="221" spans="1:7">
+    <row r="221" hidden="1" spans="1:7">
       <c r="A221" t="s">
         <v>364</v>
       </c>
@@ -8760,7 +8758,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="222" spans="1:7">
+    <row r="222" hidden="1" spans="1:7">
       <c r="A222" t="s">
         <v>359</v>
       </c>
@@ -8783,7 +8781,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="223" spans="1:7">
+    <row r="223" hidden="1" spans="1:7">
       <c r="A223" t="s">
         <v>360</v>
       </c>
@@ -8806,7 +8804,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="224" spans="1:7">
+    <row r="224" hidden="1" spans="1:7">
       <c r="A224" t="s">
         <v>365</v>
       </c>
@@ -8829,7 +8827,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="225" spans="1:7">
+    <row r="225" hidden="1" spans="1:7">
       <c r="A225" t="s">
         <v>366</v>
       </c>
@@ -8852,7 +8850,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="226" spans="1:7">
+    <row r="226" hidden="1" spans="1:7">
       <c r="A226" t="s">
         <v>367</v>
       </c>
@@ -8875,7 +8873,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="227" spans="1:7">
+    <row r="227" hidden="1" spans="1:7">
       <c r="A227" t="s">
         <v>368</v>
       </c>
@@ -8898,7 +8896,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="228" spans="1:7">
+    <row r="228" hidden="1" spans="1:7">
       <c r="A228" t="s">
         <v>369</v>
       </c>
@@ -8921,7 +8919,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="229" spans="1:7">
+    <row r="229" hidden="1" spans="1:7">
       <c r="A229" t="s">
         <v>373</v>
       </c>
@@ -8944,7 +8942,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="230" spans="1:7">
+    <row r="230" hidden="1" spans="1:7">
       <c r="A230" t="s">
         <v>375</v>
       </c>
@@ -8967,7 +8965,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="231" spans="1:7">
+    <row r="231" hidden="1" spans="1:7">
       <c r="A231" t="s">
         <v>377</v>
       </c>
@@ -8990,7 +8988,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="232" spans="1:7">
+    <row r="232" hidden="1" spans="1:7">
       <c r="A232" t="s">
         <v>378</v>
       </c>
@@ -9013,7 +9011,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="233" spans="1:7">
+    <row r="233" hidden="1" spans="1:7">
       <c r="A233" t="s">
         <v>379</v>
       </c>
@@ -9036,7 +9034,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="234" spans="1:7">
+    <row r="234" hidden="1" spans="1:7">
       <c r="A234" t="s">
         <v>381</v>
       </c>
@@ -9059,7 +9057,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="235" spans="1:7">
+    <row r="235" hidden="1" spans="1:7">
       <c r="A235" t="s">
         <v>383</v>
       </c>
@@ -9082,7 +9080,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="236" spans="1:7">
+    <row r="236" hidden="1" spans="1:7">
       <c r="A236" t="s">
         <v>387</v>
       </c>
@@ -9105,7 +9103,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="237" spans="1:7">
+    <row r="237" hidden="1" spans="1:7">
       <c r="A237" t="s">
         <v>377</v>
       </c>
@@ -9128,7 +9126,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="238" spans="1:7">
+    <row r="238" hidden="1" spans="1:7">
       <c r="A238" t="s">
         <v>388</v>
       </c>
@@ -9151,7 +9149,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="239" spans="1:7">
+    <row r="239" hidden="1" spans="1:7">
       <c r="A239" t="s">
         <v>379</v>
       </c>
@@ -9174,7 +9172,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="240" spans="1:7">
+    <row r="240" hidden="1" spans="1:7">
       <c r="A240" t="s">
         <v>389</v>
       </c>
@@ -9197,7 +9195,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="241" spans="1:7">
+    <row r="241" hidden="1" spans="1:7">
       <c r="A241" t="s">
         <v>390</v>
       </c>
@@ -9220,7 +9218,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="242" spans="1:7">
+    <row r="242" hidden="1" spans="1:7">
       <c r="A242" t="s">
         <v>392</v>
       </c>
@@ -9243,7 +9241,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="243" spans="1:7">
+    <row r="243" hidden="1" spans="1:7">
       <c r="A243" t="s">
         <v>393</v>
       </c>
@@ -9266,7 +9264,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="244" spans="1:7">
+    <row r="244" hidden="1" spans="1:7">
       <c r="A244" t="s">
         <v>395</v>
       </c>
@@ -9289,7 +9287,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="245" spans="1:7">
+    <row r="245" hidden="1" spans="1:7">
       <c r="A245" t="s">
         <v>397</v>
       </c>
@@ -9312,7 +9310,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="246" spans="1:7">
+    <row r="246" hidden="1" spans="1:7">
       <c r="A246" t="s">
         <v>398</v>
       </c>
@@ -9335,7 +9333,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="247" spans="1:7">
+    <row r="247" hidden="1" spans="1:7">
       <c r="A247" t="s">
         <v>399</v>
       </c>
@@ -9358,7 +9356,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="248" spans="1:7">
+    <row r="248" hidden="1" spans="1:7">
       <c r="A248" t="s">
         <v>400</v>
       </c>
@@ -9381,7 +9379,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="249" spans="1:7">
+    <row r="249" hidden="1" spans="1:7">
       <c r="A249" t="s">
         <v>393</v>
       </c>
@@ -9404,7 +9402,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="250" spans="1:7">
+    <row r="250" hidden="1" spans="1:7">
       <c r="A250" t="s">
         <v>395</v>
       </c>
@@ -9427,7 +9425,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="251" spans="1:7">
+    <row r="251" hidden="1" spans="1:7">
       <c r="A251" t="s">
         <v>398</v>
       </c>
@@ -9450,7 +9448,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="252" spans="1:7">
+    <row r="252" hidden="1" spans="1:7">
       <c r="A252" t="s">
         <v>402</v>
       </c>
@@ -9473,7 +9471,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="253" spans="1:7">
+    <row r="253" hidden="1" spans="1:7">
       <c r="A253" t="s">
         <v>403</v>
       </c>
@@ -9496,7 +9494,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="254" spans="1:7">
+    <row r="254" hidden="1" spans="1:7">
       <c r="A254" t="s">
         <v>404</v>
       </c>
@@ -9519,7 +9517,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="255" spans="1:7">
+    <row r="255" hidden="1" spans="1:7">
       <c r="A255" t="s">
         <v>15</v>
       </c>
@@ -9542,7 +9540,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="256" spans="1:7">
+    <row r="256" hidden="1" spans="1:7">
       <c r="A256" t="s">
         <v>406</v>
       </c>
@@ -9565,7 +9563,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="257" spans="1:7">
+    <row r="257" hidden="1" spans="1:7">
       <c r="A257" t="s">
         <v>408</v>
       </c>
@@ -9588,7 +9586,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="258" spans="1:7">
+    <row r="258" hidden="1" spans="1:7">
       <c r="A258" t="s">
         <v>7</v>
       </c>
@@ -9611,7 +9609,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="259" spans="1:7">
+    <row r="259" hidden="1" spans="1:7">
       <c r="A259" t="s">
         <v>411</v>
       </c>
@@ -9634,7 +9632,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="260" spans="1:7">
+    <row r="260" hidden="1" spans="1:7">
       <c r="A260" t="s">
         <v>413</v>
       </c>
@@ -9657,7 +9655,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="261" spans="1:7">
+    <row r="261" hidden="1" spans="1:7">
       <c r="A261" t="s">
         <v>414</v>
       </c>
@@ -9680,7 +9678,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="262" spans="1:7">
+    <row r="262" hidden="1" spans="1:7">
       <c r="A262" t="s">
         <v>416</v>
       </c>
@@ -9703,7 +9701,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="263" spans="1:7">
+    <row r="263" hidden="1" spans="1:7">
       <c r="A263" t="s">
         <v>417</v>
       </c>
@@ -9726,7 +9724,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="264" spans="1:7">
+    <row r="264" hidden="1" spans="1:7">
       <c r="A264" t="s">
         <v>418</v>
       </c>
@@ -9749,7 +9747,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="265" spans="1:7">
+    <row r="265" hidden="1" spans="1:7">
       <c r="A265" t="s">
         <v>419</v>
       </c>
@@ -9772,7 +9770,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="266" spans="1:7">
+    <row r="266" hidden="1" spans="1:7">
       <c r="A266" t="s">
         <v>420</v>
       </c>
@@ -9795,7 +9793,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="267" spans="1:7">
+    <row r="267" hidden="1" spans="1:7">
       <c r="A267" t="s">
         <v>421</v>
       </c>
@@ -9818,7 +9816,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="268" spans="1:7">
+    <row r="268" hidden="1" spans="1:7">
       <c r="A268" t="s">
         <v>423</v>
       </c>
@@ -9841,7 +9839,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="269" spans="1:7">
+    <row r="269" hidden="1" spans="1:7">
       <c r="A269" t="s">
         <v>424</v>
       </c>
@@ -9864,7 +9862,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="270" spans="1:7">
+    <row r="270" hidden="1" spans="1:7">
       <c r="A270" t="s">
         <v>420</v>
       </c>
@@ -9887,7 +9885,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="271" spans="1:7">
+    <row r="271" hidden="1" spans="1:7">
       <c r="A271" t="s">
         <v>419</v>
       </c>
@@ -9910,7 +9908,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="272" spans="1:7">
+    <row r="272" hidden="1" spans="1:7">
       <c r="A272" t="s">
         <v>425</v>
       </c>
@@ -9933,7 +9931,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="273" spans="1:7">
+    <row r="273" hidden="1" spans="1:7">
       <c r="A273" t="s">
         <v>426</v>
       </c>
@@ -9956,7 +9954,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="274" spans="1:7">
+    <row r="274" hidden="1" spans="1:7">
       <c r="A274" t="s">
         <v>427</v>
       </c>
@@ -9979,7 +9977,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="275" spans="1:7">
+    <row r="275" hidden="1" spans="1:7">
       <c r="A275" t="s">
         <v>428</v>
       </c>
@@ -10002,7 +10000,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="276" spans="1:7">
+    <row r="276" hidden="1" spans="1:7">
       <c r="A276" t="s">
         <v>421</v>
       </c>
@@ -10025,7 +10023,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="277" spans="1:7">
+    <row r="277" hidden="1" spans="1:7">
       <c r="A277" t="s">
         <v>429</v>
       </c>
@@ -10048,7 +10046,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="278" spans="1:7">
+    <row r="278" hidden="1" spans="1:7">
       <c r="A278" t="s">
         <v>431</v>
       </c>
@@ -10071,7 +10069,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="279" spans="1:7">
+    <row r="279" hidden="1" spans="1:7">
       <c r="A279" t="s">
         <v>426</v>
       </c>
@@ -10094,7 +10092,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="280" spans="1:7">
+    <row r="280" hidden="1" spans="1:7">
       <c r="A280" t="s">
         <v>427</v>
       </c>
@@ -10117,7 +10115,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="281" spans="1:7">
+    <row r="281" hidden="1" spans="1:7">
       <c r="A281" t="s">
         <v>432</v>
       </c>
@@ -10140,7 +10138,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="282" spans="1:7">
+    <row r="282" hidden="1" spans="1:7">
       <c r="A282" t="s">
         <v>429</v>
       </c>
@@ -10163,7 +10161,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="283" spans="1:7">
+    <row r="283" hidden="1" spans="1:7">
       <c r="A283" t="s">
         <v>433</v>
       </c>
@@ -10186,7 +10184,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="284" spans="1:7">
+    <row r="284" hidden="1" spans="1:7">
       <c r="A284" t="s">
         <v>434</v>
       </c>
@@ -10209,7 +10207,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="285" spans="1:7">
+    <row r="285" hidden="1" spans="1:7">
       <c r="A285" t="s">
         <v>435</v>
       </c>
@@ -10232,7 +10230,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="286" spans="1:7">
+    <row r="286" hidden="1" spans="1:7">
       <c r="A286" t="s">
         <v>436</v>
       </c>
@@ -10255,7 +10253,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="287" spans="1:7">
+    <row r="287" hidden="1" spans="1:7">
       <c r="A287" t="s">
         <v>437</v>
       </c>
@@ -10278,7 +10276,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="288" spans="1:7">
+    <row r="288" hidden="1" spans="1:7">
       <c r="A288" t="s">
         <v>439</v>
       </c>
@@ -10301,7 +10299,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="289" spans="1:7">
+    <row r="289" hidden="1" spans="1:7">
       <c r="A289" t="s">
         <v>440</v>
       </c>
@@ -10324,7 +10322,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="290" spans="1:7">
+    <row r="290" hidden="1" spans="1:7">
       <c r="A290" t="s">
         <v>389</v>
       </c>
@@ -10347,7 +10345,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="291" spans="1:7">
+    <row r="291" hidden="1" spans="1:7">
       <c r="A291" t="s">
         <v>441</v>
       </c>
@@ -10370,7 +10368,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="292" spans="1:7">
+    <row r="292" hidden="1" spans="1:7">
       <c r="A292" t="s">
         <v>442</v>
       </c>
@@ -10393,7 +10391,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="293" spans="1:7">
+    <row r="293" hidden="1" spans="1:7">
       <c r="A293" t="s">
         <v>443</v>
       </c>
@@ -10416,7 +10414,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="294" spans="1:7">
+    <row r="294" hidden="1" spans="1:7">
       <c r="A294" t="s">
         <v>444</v>
       </c>
@@ -10439,7 +10437,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="295" spans="1:7">
+    <row r="295" hidden="1" spans="1:7">
       <c r="A295" t="s">
         <v>445</v>
       </c>
@@ -10462,7 +10460,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="296" spans="1:7">
+    <row r="296" hidden="1" spans="1:7">
       <c r="A296" t="s">
         <v>446</v>
       </c>
@@ -10485,7 +10483,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="297" spans="1:7">
+    <row r="297" hidden="1" spans="1:7">
       <c r="A297" t="s">
         <v>448</v>
       </c>
@@ -10508,7 +10506,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="298" spans="1:7">
+    <row r="298" hidden="1" spans="1:7">
       <c r="A298" t="s">
         <v>450</v>
       </c>
@@ -10531,7 +10529,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="299" spans="1:7">
+    <row r="299" hidden="1" spans="1:7">
       <c r="A299" t="s">
         <v>451</v>
       </c>
@@ -10554,7 +10552,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="300" spans="1:7">
+    <row r="300" hidden="1" spans="1:7">
       <c r="A300" t="s">
         <v>453</v>
       </c>
@@ -10577,7 +10575,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="301" spans="1:7">
+    <row r="301" hidden="1" spans="1:7">
       <c r="A301" t="s">
         <v>450</v>
       </c>
@@ -10600,7 +10598,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="302" spans="1:7">
+    <row r="302" hidden="1" spans="1:7">
       <c r="A302" t="s">
         <v>378</v>
       </c>
@@ -10623,7 +10621,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="303" spans="1:7">
+    <row r="303" hidden="1" spans="1:7">
       <c r="A303" t="s">
         <v>456</v>
       </c>
@@ -10646,7 +10644,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="304" spans="1:7">
+    <row r="304" hidden="1" spans="1:7">
       <c r="A304" t="s">
         <v>457</v>
       </c>
@@ -10669,7 +10667,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="305" spans="1:7">
+    <row r="305" hidden="1" spans="1:7">
       <c r="A305" t="s">
         <v>458</v>
       </c>
@@ -10692,7 +10690,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="306" spans="1:7">
+    <row r="306" hidden="1" spans="1:7">
       <c r="A306" t="s">
         <v>460</v>
       </c>
@@ -10715,7 +10713,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="307" spans="1:7">
+    <row r="307" hidden="1" spans="1:7">
       <c r="A307" t="s">
         <v>463</v>
       </c>
@@ -10738,7 +10736,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="308" spans="1:7">
+    <row r="308" hidden="1" spans="1:7">
       <c r="A308" t="s">
         <v>69</v>
       </c>
@@ -10761,7 +10759,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="309" spans="1:7">
+    <row r="309" hidden="1" spans="1:7">
       <c r="A309" t="s">
         <v>465</v>
       </c>
@@ -10784,7 +10782,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="310" spans="1:7">
+    <row r="310" hidden="1" spans="1:7">
       <c r="A310" t="s">
         <v>468</v>
       </c>
@@ -10807,7 +10805,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="311" spans="1:7">
+    <row r="311" hidden="1" spans="1:7">
       <c r="A311" t="s">
         <v>471</v>
       </c>
@@ -10853,7 +10851,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="313" spans="1:7">
+    <row r="313" hidden="1" spans="1:7">
       <c r="A313" t="s">
         <v>471</v>
       </c>
@@ -10899,7 +10897,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="315" spans="1:7">
+    <row r="315" hidden="1" spans="1:7">
       <c r="A315" t="s">
         <v>479</v>
       </c>
@@ -10945,7 +10943,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="317" spans="1:7">
+    <row r="317" hidden="1" spans="1:7">
       <c r="A317" t="s">
         <v>65</v>
       </c>
@@ -10968,7 +10966,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="318" spans="1:7">
+    <row r="318" hidden="1" spans="1:7">
       <c r="A318" t="s">
         <v>486</v>
       </c>
@@ -10991,7 +10989,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="319" spans="1:7">
+    <row r="319" hidden="1" spans="1:7">
       <c r="A319" t="s">
         <v>471</v>
       </c>
@@ -11014,7 +11012,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="320" spans="1:7">
+    <row r="320" hidden="1" spans="1:7">
       <c r="A320" t="s">
         <v>103</v>
       </c>
@@ -11037,7 +11035,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="321" spans="1:7">
+    <row r="321" hidden="1" spans="1:7">
       <c r="A321" t="s">
         <v>471</v>
       </c>
@@ -11060,7 +11058,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="322" spans="1:7">
+    <row r="322" hidden="1" spans="1:7">
       <c r="A322" t="s">
         <v>471</v>
       </c>
@@ -11083,7 +11081,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="323" spans="1:7">
+    <row r="323" hidden="1" spans="1:7">
       <c r="A323" t="s">
         <v>471</v>
       </c>
@@ -11106,7 +11104,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="324" spans="1:7">
+    <row r="324" hidden="1" spans="1:7">
       <c r="A324" t="s">
         <v>471</v>
       </c>
@@ -11129,7 +11127,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="325" spans="1:7">
+    <row r="325" hidden="1" spans="1:7">
       <c r="A325" t="s">
         <v>471</v>
       </c>
@@ -11152,7 +11150,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="326" spans="1:7">
+    <row r="326" hidden="1" spans="1:7">
       <c r="A326" t="s">
         <v>479</v>
       </c>
@@ -11198,7 +11196,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="328" spans="1:7">
+    <row r="328" hidden="1" spans="1:7">
       <c r="A328" t="s">
         <v>102</v>
       </c>
@@ -11221,7 +11219,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="329" spans="1:7">
+    <row r="329" hidden="1" spans="1:7">
       <c r="A329" t="s">
         <v>492</v>
       </c>
@@ -11244,7 +11242,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="330" spans="1:7">
+    <row r="330" hidden="1" spans="1:7">
       <c r="A330" t="s">
         <v>495</v>
       </c>
@@ -11267,7 +11265,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="331" spans="1:7">
+    <row r="331" hidden="1" spans="1:7">
       <c r="A331" t="s">
         <v>498</v>
       </c>
@@ -11290,7 +11288,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="332" spans="1:7">
+    <row r="332" hidden="1" spans="1:7">
       <c r="A332" t="s">
         <v>499</v>
       </c>
@@ -11313,7 +11311,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="333" spans="1:7">
+    <row r="333" hidden="1" spans="1:7">
       <c r="A333" t="s">
         <v>479</v>
       </c>
@@ -11336,7 +11334,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="334" spans="1:7">
+    <row r="334" hidden="1" spans="1:7">
       <c r="A334" t="s">
         <v>479</v>
       </c>
@@ -11359,7 +11357,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="335" spans="1:7">
+    <row r="335" hidden="1" spans="1:7">
       <c r="A335" t="s">
         <v>503</v>
       </c>
@@ -11382,7 +11380,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="336" spans="1:7">
+    <row r="336" hidden="1" spans="1:7">
       <c r="A336" t="s">
         <v>504</v>
       </c>
@@ -11405,7 +11403,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="337" spans="1:7">
+    <row r="337" hidden="1" spans="1:7">
       <c r="A337" t="s">
         <v>505</v>
       </c>
@@ -11428,7 +11426,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="338" spans="1:7">
+    <row r="338" hidden="1" spans="1:7">
       <c r="A338" t="s">
         <v>492</v>
       </c>
@@ -11451,7 +11449,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="339" spans="1:7">
+    <row r="339" hidden="1" spans="1:7">
       <c r="A339" t="s">
         <v>506</v>
       </c>
@@ -11474,7 +11472,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="340" spans="1:7">
+    <row r="340" hidden="1" spans="1:7">
       <c r="A340" t="s">
         <v>499</v>
       </c>
@@ -11497,7 +11495,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="341" spans="1:7">
+    <row r="341" hidden="1" spans="1:7">
       <c r="A341" t="s">
         <v>509</v>
       </c>
@@ -11520,7 +11518,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="342" spans="1:7">
+    <row r="342" hidden="1" spans="1:7">
       <c r="A342" t="s">
         <v>512</v>
       </c>
@@ -11543,7 +11541,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="343" spans="1:7">
+    <row r="343" hidden="1" spans="1:7">
       <c r="A343" t="s">
         <v>514</v>
       </c>
@@ -11566,7 +11564,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="344" spans="1:7">
+    <row r="344" hidden="1" spans="1:7">
       <c r="A344" t="s">
         <v>517</v>
       </c>
@@ -11589,7 +11587,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="345" spans="1:7">
+    <row r="345" hidden="1" spans="1:7">
       <c r="A345" t="s">
         <v>519</v>
       </c>
@@ -11612,7 +11610,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="346" spans="1:7">
+    <row r="346" hidden="1" spans="1:7">
       <c r="A346" t="s">
         <v>522</v>
       </c>
@@ -11635,7 +11633,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="347" spans="1:7">
+    <row r="347" hidden="1" spans="1:7">
       <c r="A347" t="s">
         <v>525</v>
       </c>
@@ -11658,7 +11656,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="348" spans="1:7">
+    <row r="348" hidden="1" spans="1:7">
       <c r="A348" t="s">
         <v>528</v>
       </c>
@@ -11681,7 +11679,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="349" spans="1:7">
+    <row r="349" hidden="1" spans="1:7">
       <c r="A349" t="s">
         <v>529</v>
       </c>
@@ -11704,7 +11702,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="350" spans="1:7">
+    <row r="350" hidden="1" spans="1:7">
       <c r="A350" t="s">
         <v>530</v>
       </c>
@@ -11727,7 +11725,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="351" spans="1:7">
+    <row r="351" hidden="1" spans="1:7">
       <c r="A351" t="s">
         <v>525</v>
       </c>
@@ -11750,7 +11748,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="352" spans="1:7">
+    <row r="352" hidden="1" spans="1:7">
       <c r="A352" t="s">
         <v>201</v>
       </c>
@@ -11773,7 +11771,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="353" spans="1:7">
+    <row r="353" hidden="1" spans="1:7">
       <c r="A353" t="s">
         <v>532</v>
       </c>
@@ -11796,7 +11794,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="354" spans="1:7">
+    <row r="354" hidden="1" spans="1:7">
       <c r="A354" t="s">
         <v>533</v>
       </c>
@@ -11819,7 +11817,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="355" spans="1:7">
+    <row r="355" hidden="1" spans="1:7">
       <c r="A355" t="s">
         <v>535</v>
       </c>
@@ -11842,7 +11840,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="356" spans="1:7">
+    <row r="356" hidden="1" spans="1:7">
       <c r="A356" t="s">
         <v>538</v>
       </c>
@@ -11865,7 +11863,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="357" spans="1:7">
+    <row r="357" hidden="1" spans="1:7">
       <c r="A357" t="s">
         <v>539</v>
       </c>
@@ -11888,7 +11886,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="358" spans="1:7">
+    <row r="358" hidden="1" spans="1:7">
       <c r="A358" t="s">
         <v>541</v>
       </c>
@@ -11911,7 +11909,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="359" spans="1:7">
+    <row r="359" hidden="1" spans="1:7">
       <c r="A359" t="s">
         <v>541</v>
       </c>
@@ -11934,7 +11932,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="360" spans="1:7">
+    <row r="360" hidden="1" spans="1:7">
       <c r="A360" t="s">
         <v>544</v>
       </c>
@@ -11957,7 +11955,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="361" spans="1:7">
+    <row r="361" hidden="1" spans="1:7">
       <c r="A361" t="s">
         <v>546</v>
       </c>
@@ -11980,7 +11978,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="362" spans="1:7">
+    <row r="362" hidden="1" spans="1:7">
       <c r="A362" t="s">
         <v>532</v>
       </c>
@@ -12003,7 +12001,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="363" spans="1:7">
+    <row r="363" hidden="1" spans="1:7">
       <c r="A363" t="s">
         <v>547</v>
       </c>
@@ -12026,7 +12024,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="364" spans="1:7">
+    <row r="364" hidden="1" spans="1:7">
       <c r="A364" t="s">
         <v>548</v>
       </c>
@@ -12049,7 +12047,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="365" spans="1:7">
+    <row r="365" hidden="1" spans="1:7">
       <c r="A365" t="s">
         <v>541</v>
       </c>
@@ -12072,7 +12070,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="366" spans="1:7">
+    <row r="366" hidden="1" spans="1:7">
       <c r="A366" t="s">
         <v>550</v>
       </c>
@@ -12095,7 +12093,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="367" spans="1:7">
+    <row r="367" hidden="1" spans="1:7">
       <c r="A367" t="s">
         <v>541</v>
       </c>
@@ -12118,7 +12116,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="368" spans="1:7">
+    <row r="368" hidden="1" spans="1:7">
       <c r="A368" t="s">
         <v>201</v>
       </c>
@@ -12141,7 +12139,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="369" spans="1:7">
+    <row r="369" hidden="1" spans="1:7">
       <c r="A369" t="s">
         <v>556</v>
       </c>
@@ -12164,7 +12162,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="370" spans="1:7">
+    <row r="370" hidden="1" spans="1:7">
       <c r="A370" t="s">
         <v>557</v>
       </c>
@@ -12187,7 +12185,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="371" spans="1:7">
+    <row r="371" hidden="1" spans="1:7">
       <c r="A371" t="s">
         <v>559</v>
       </c>
@@ -12210,7 +12208,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="372" spans="1:7">
+    <row r="372" hidden="1" spans="1:7">
       <c r="A372" t="s">
         <v>560</v>
       </c>
@@ -12233,7 +12231,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="373" spans="1:7">
+    <row r="373" hidden="1" spans="1:7">
       <c r="A373" t="s">
         <v>525</v>
       </c>
@@ -12256,7 +12254,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="374" spans="1:7">
+    <row r="374" hidden="1" spans="1:7">
       <c r="A374" t="s">
         <v>530</v>
       </c>
@@ -12279,7 +12277,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="375" spans="1:7">
+    <row r="375" hidden="1" spans="1:7">
       <c r="A375" t="s">
         <v>560</v>
       </c>
@@ -12302,7 +12300,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="376" spans="1:7">
+    <row r="376" hidden="1" spans="1:7">
       <c r="A376" t="s">
         <v>525</v>
       </c>
@@ -12325,7 +12323,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="377" spans="1:7">
+    <row r="377" hidden="1" spans="1:7">
       <c r="A377" t="s">
         <v>530</v>
       </c>
@@ -12348,7 +12346,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="378" spans="1:7">
+    <row r="378" hidden="1" spans="1:7">
       <c r="A378" t="s">
         <v>192</v>
       </c>
@@ -12371,7 +12369,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="379" spans="1:7">
+    <row r="379" hidden="1" spans="1:7">
       <c r="A379" t="s">
         <v>567</v>
       </c>
@@ -12394,7 +12392,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="380" spans="1:7">
+    <row r="380" hidden="1" spans="1:7">
       <c r="A380" t="s">
         <v>270</v>
       </c>
@@ -12417,7 +12415,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="381" spans="1:7">
+    <row r="381" hidden="1" spans="1:7">
       <c r="A381" t="s">
         <v>570</v>
       </c>
@@ -12440,7 +12438,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="382" spans="1:7">
+    <row r="382" hidden="1" spans="1:7">
       <c r="A382" t="s">
         <v>272</v>
       </c>
@@ -12463,7 +12461,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="383" spans="1:7">
+    <row r="383" hidden="1" spans="1:7">
       <c r="A383" t="s">
         <v>574</v>
       </c>
@@ -12486,7 +12484,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="384" spans="1:7">
+    <row r="384" hidden="1" spans="1:7">
       <c r="A384" t="s">
         <v>576</v>
       </c>
@@ -12509,7 +12507,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="385" spans="1:7">
+    <row r="385" hidden="1" spans="1:7">
       <c r="A385" t="s">
         <v>578</v>
       </c>
@@ -12532,7 +12530,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="386" spans="1:7">
+    <row r="386" hidden="1" spans="1:7">
       <c r="A386" t="s">
         <v>226</v>
       </c>
@@ -12555,7 +12553,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="387" spans="1:7">
+    <row r="387" hidden="1" spans="1:7">
       <c r="A387" t="s">
         <v>260</v>
       </c>
@@ -12578,7 +12576,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="388" spans="1:7">
+    <row r="388" hidden="1" spans="1:7">
       <c r="A388" t="s">
         <v>583</v>
       </c>
@@ -12601,7 +12599,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="389" spans="1:7">
+    <row r="389" hidden="1" spans="1:7">
       <c r="A389" t="s">
         <v>586</v>
       </c>
@@ -12624,7 +12622,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="390" spans="1:7">
+    <row r="390" hidden="1" spans="1:7">
       <c r="A390" t="s">
         <v>588</v>
       </c>
@@ -12647,7 +12645,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="391" spans="1:7">
+    <row r="391" hidden="1" spans="1:7">
       <c r="A391" t="s">
         <v>590</v>
       </c>
@@ -12670,7 +12668,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="392" spans="1:7">
+    <row r="392" hidden="1" spans="1:7">
       <c r="A392" t="s">
         <v>237</v>
       </c>
@@ -12693,7 +12691,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="393" spans="1:7">
+    <row r="393" hidden="1" spans="1:7">
       <c r="A393" t="s">
         <v>594</v>
       </c>
@@ -12716,7 +12714,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="394" spans="1:7">
+    <row r="394" hidden="1" spans="1:7">
       <c r="A394" t="s">
         <v>238</v>
       </c>
@@ -12739,7 +12737,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="395" spans="1:7">
+    <row r="395" hidden="1" spans="1:7">
       <c r="A395" t="s">
         <v>245</v>
       </c>
@@ -12762,7 +12760,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="396" spans="1:7">
+    <row r="396" hidden="1" spans="1:7">
       <c r="A396" t="s">
         <v>598</v>
       </c>
@@ -12785,7 +12783,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="397" spans="1:7">
+    <row r="397" hidden="1" spans="1:7">
       <c r="A397" t="s">
         <v>270</v>
       </c>
@@ -12808,7 +12806,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="398" spans="1:7">
+    <row r="398" hidden="1" spans="1:7">
       <c r="A398" t="s">
         <v>570</v>
       </c>
@@ -12831,7 +12829,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="399" spans="1:7">
+    <row r="399" hidden="1" spans="1:7">
       <c r="A399" t="s">
         <v>272</v>
       </c>
@@ -12854,7 +12852,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="400" spans="1:7">
+    <row r="400" hidden="1" spans="1:7">
       <c r="A400" t="s">
         <v>574</v>
       </c>
@@ -12877,7 +12875,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="401" spans="1:7">
+    <row r="401" hidden="1" spans="1:7">
       <c r="A401" t="s">
         <v>586</v>
       </c>
@@ -12900,7 +12898,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="402" spans="1:7">
+    <row r="402" hidden="1" spans="1:7">
       <c r="A402" t="s">
         <v>578</v>
       </c>
@@ -12923,7 +12921,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="403" spans="1:7">
+    <row r="403" hidden="1" spans="1:7">
       <c r="A403" t="s">
         <v>226</v>
       </c>
@@ -12946,7 +12944,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="404" spans="1:7">
+    <row r="404" hidden="1" spans="1:7">
       <c r="A404" t="s">
         <v>576</v>
       </c>
@@ -12969,7 +12967,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="405" spans="1:7">
+    <row r="405" hidden="1" spans="1:7">
       <c r="A405" t="s">
         <v>583</v>
       </c>
@@ -12992,7 +12990,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="406" spans="1:7">
+    <row r="406" hidden="1" spans="1:7">
       <c r="A406" t="s">
         <v>238</v>
       </c>
@@ -13015,7 +13013,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="407" spans="1:7">
+    <row r="407" hidden="1" spans="1:7">
       <c r="A407" t="s">
         <v>598</v>
       </c>
@@ -13038,7 +13036,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="408" spans="1:7">
+    <row r="408" hidden="1" spans="1:7">
       <c r="A408" t="s">
         <v>588</v>
       </c>
@@ -13061,7 +13059,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="409" spans="1:7">
+    <row r="409" hidden="1" spans="1:7">
       <c r="A409" t="s">
         <v>590</v>
       </c>
@@ -13084,7 +13082,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="410" spans="1:7">
+    <row r="410" hidden="1" spans="1:7">
       <c r="A410" t="s">
         <v>237</v>
       </c>
@@ -13107,7 +13105,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="411" spans="1:7">
+    <row r="411" hidden="1" spans="1:7">
       <c r="A411" t="s">
         <v>594</v>
       </c>
@@ -13130,7 +13128,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="412" spans="1:7">
+    <row r="412" hidden="1" spans="1:7">
       <c r="A412" t="s">
         <v>260</v>
       </c>
@@ -13153,7 +13151,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="413" spans="1:7">
+    <row r="413" hidden="1" spans="1:7">
       <c r="A413" t="s">
         <v>245</v>
       </c>
@@ -13176,7 +13174,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="414" spans="1:7">
+    <row r="414" hidden="1" spans="1:7">
       <c r="A414" t="s">
         <v>583</v>
       </c>
@@ -13199,7 +13197,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="415" spans="1:7">
+    <row r="415" hidden="1" spans="1:7">
       <c r="A415" t="s">
         <v>621</v>
       </c>
@@ -13222,7 +13220,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="416" spans="1:7">
+    <row r="416" hidden="1" spans="1:7">
       <c r="A416" t="s">
         <v>624</v>
       </c>
@@ -13245,7 +13243,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="417" spans="1:7">
+    <row r="417" hidden="1" spans="1:7">
       <c r="A417" t="s">
         <v>237</v>
       </c>
@@ -13268,7 +13266,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="418" spans="1:7">
+    <row r="418" hidden="1" spans="1:7">
       <c r="A418" t="s">
         <v>226</v>
       </c>
@@ -13291,7 +13289,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="419" spans="1:7">
+    <row r="419" hidden="1" spans="1:7">
       <c r="A419" t="s">
         <v>627</v>
       </c>
@@ -13314,7 +13312,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="420" spans="1:7">
+    <row r="420" hidden="1" spans="1:7">
       <c r="A420" t="s">
         <v>629</v>
       </c>
@@ -13337,7 +13335,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="421" spans="1:7">
+    <row r="421" hidden="1" spans="1:7">
       <c r="A421" t="s">
         <v>632</v>
       </c>
@@ -13360,7 +13358,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="422" spans="1:7">
+    <row r="422" hidden="1" spans="1:7">
       <c r="A422" t="s">
         <v>633</v>
       </c>
@@ -13383,7 +13381,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="423" spans="1:7">
+    <row r="423" hidden="1" spans="1:7">
       <c r="A423" t="s">
         <v>636</v>
       </c>
@@ -13406,7 +13404,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="424" spans="1:7">
+    <row r="424" hidden="1" spans="1:7">
       <c r="A424" t="s">
         <v>637</v>
       </c>
@@ -13429,7 +13427,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="425" spans="1:7">
+    <row r="425" hidden="1" spans="1:7">
       <c r="A425" t="s">
         <v>270</v>
       </c>
@@ -13452,7 +13450,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="426" spans="1:7">
+    <row r="426" hidden="1" spans="1:7">
       <c r="A426" t="s">
         <v>639</v>
       </c>
@@ -13475,7 +13473,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="427" spans="1:7">
+    <row r="427" hidden="1" spans="1:7">
       <c r="A427" t="s">
         <v>640</v>
       </c>
@@ -13498,7 +13496,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="428" spans="1:7">
+    <row r="428" hidden="1" spans="1:7">
       <c r="A428" t="s">
         <v>642</v>
       </c>
@@ -13521,7 +13519,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="429" spans="1:7">
+    <row r="429" hidden="1" spans="1:7">
       <c r="A429" t="s">
         <v>272</v>
       </c>
@@ -13544,7 +13542,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="430" spans="1:7">
+    <row r="430" hidden="1" spans="1:7">
       <c r="A430" t="s">
         <v>645</v>
       </c>
@@ -13567,7 +13565,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="431" spans="1:7">
+    <row r="431" hidden="1" spans="1:7">
       <c r="A431" t="s">
         <v>646</v>
       </c>
@@ -13590,7 +13588,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="432" spans="1:7">
+    <row r="432" hidden="1" spans="1:7">
       <c r="A432" t="s">
         <v>648</v>
       </c>
@@ -13613,7 +13611,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="433" spans="1:7">
+    <row r="433" hidden="1" spans="1:7">
       <c r="A433" t="s">
         <v>649</v>
       </c>
@@ -13636,7 +13634,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="434" spans="1:7">
+    <row r="434" hidden="1" spans="1:7">
       <c r="A434" t="s">
         <v>650</v>
       </c>
@@ -13659,7 +13657,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="435" spans="1:7">
+    <row r="435" hidden="1" spans="1:7">
       <c r="A435" t="s">
         <v>651</v>
       </c>
@@ -13682,7 +13680,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="436" spans="1:7">
+    <row r="436" hidden="1" spans="1:7">
       <c r="A436" t="s">
         <v>570</v>
       </c>
@@ -13705,7 +13703,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="437" spans="1:7">
+    <row r="437" hidden="1" spans="1:7">
       <c r="A437" t="s">
         <v>588</v>
       </c>
@@ -13728,7 +13726,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="438" spans="1:7">
+    <row r="438" hidden="1" spans="1:7">
       <c r="A438" t="s">
         <v>272</v>
       </c>
@@ -13751,7 +13749,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="439" spans="1:7">
+    <row r="439" hidden="1" spans="1:7">
       <c r="A439" t="s">
         <v>574</v>
       </c>
@@ -13774,7 +13772,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="440" spans="1:7">
+    <row r="440" hidden="1" spans="1:7">
       <c r="A440" t="s">
         <v>578</v>
       </c>
@@ -13797,7 +13795,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="441" spans="1:7">
+    <row r="441" hidden="1" spans="1:7">
       <c r="A441" t="s">
         <v>586</v>
       </c>
@@ -13820,7 +13818,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="442" spans="1:7">
+    <row r="442" hidden="1" spans="1:7">
       <c r="A442" t="s">
         <v>583</v>
       </c>
@@ -13843,7 +13841,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="443" spans="1:7">
+    <row r="443" hidden="1" spans="1:7">
       <c r="A443" t="s">
         <v>576</v>
       </c>
@@ -13866,7 +13864,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="444" spans="1:7">
+    <row r="444" hidden="1" spans="1:7">
       <c r="A444" t="s">
         <v>238</v>
       </c>
@@ -13889,7 +13887,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="445" spans="1:7">
+    <row r="445" hidden="1" spans="1:7">
       <c r="A445" t="s">
         <v>598</v>
       </c>
@@ -13912,7 +13910,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="446" spans="1:7">
+    <row r="446" hidden="1" spans="1:7">
       <c r="A446" t="s">
         <v>590</v>
       </c>
@@ -13935,7 +13933,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="447" spans="1:7">
+    <row r="447" hidden="1" spans="1:7">
       <c r="A447" t="s">
         <v>270</v>
       </c>
@@ -13958,7 +13956,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="448" spans="1:7">
+    <row r="448" hidden="1" spans="1:7">
       <c r="A448" t="s">
         <v>226</v>
       </c>
@@ -13981,7 +13979,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="449" spans="1:7">
+    <row r="449" hidden="1" spans="1:7">
       <c r="A449" t="s">
         <v>237</v>
       </c>
@@ -14004,7 +14002,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="450" spans="1:7">
+    <row r="450" hidden="1" spans="1:7">
       <c r="A450" t="s">
         <v>260</v>
       </c>
@@ -14027,7 +14025,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="451" spans="1:7">
+    <row r="451" hidden="1" spans="1:7">
       <c r="A451" t="s">
         <v>245</v>
       </c>
@@ -14050,7 +14048,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="452" spans="1:7">
+    <row r="452" hidden="1" spans="1:7">
       <c r="A452" t="s">
         <v>594</v>
       </c>
@@ -14073,7 +14071,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="453" spans="1:7">
+    <row r="453" hidden="1" spans="1:7">
       <c r="A453" t="s">
         <v>598</v>
       </c>
@@ -14096,7 +14094,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="454" spans="1:7">
+    <row r="454" hidden="1" spans="1:7">
       <c r="A454" t="s">
         <v>570</v>
       </c>
@@ -14119,7 +14117,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="455" spans="1:7">
+    <row r="455" hidden="1" spans="1:7">
       <c r="A455" t="s">
         <v>588</v>
       </c>
@@ -14142,7 +14140,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="456" spans="1:7">
+    <row r="456" hidden="1" spans="1:7">
       <c r="A456" t="s">
         <v>272</v>
       </c>
@@ -14165,7 +14163,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="457" spans="1:7">
+    <row r="457" hidden="1" spans="1:7">
       <c r="A457" t="s">
         <v>574</v>
       </c>
@@ -14188,7 +14186,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="458" spans="1:7">
+    <row r="458" hidden="1" spans="1:7">
       <c r="A458" t="s">
         <v>260</v>
       </c>
@@ -14211,7 +14209,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="459" spans="1:7">
+    <row r="459" hidden="1" spans="1:7">
       <c r="A459" t="s">
         <v>578</v>
       </c>
@@ -14234,7 +14232,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="460" spans="1:7">
+    <row r="460" hidden="1" spans="1:7">
       <c r="A460" t="s">
         <v>583</v>
       </c>
@@ -14257,7 +14255,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="461" spans="1:7">
+    <row r="461" hidden="1" spans="1:7">
       <c r="A461" t="s">
         <v>576</v>
       </c>
@@ -14280,7 +14278,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="462" spans="1:7">
+    <row r="462" hidden="1" spans="1:7">
       <c r="A462" t="s">
         <v>586</v>
       </c>
@@ -14303,7 +14301,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="463" spans="1:7">
+    <row r="463" hidden="1" spans="1:7">
       <c r="A463" t="s">
         <v>590</v>
       </c>
@@ -14326,7 +14324,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="464" spans="1:7">
+    <row r="464" hidden="1" spans="1:7">
       <c r="A464" t="s">
         <v>270</v>
       </c>
@@ -14349,7 +14347,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="465" spans="1:7">
+    <row r="465" hidden="1" spans="1:7">
       <c r="A465" t="s">
         <v>226</v>
       </c>
@@ -14372,7 +14370,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="466" spans="1:7">
+    <row r="466" hidden="1" spans="1:7">
       <c r="A466" t="s">
         <v>237</v>
       </c>
@@ -14395,7 +14393,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="467" spans="1:7">
+    <row r="467" hidden="1" spans="1:7">
       <c r="A467" t="s">
         <v>238</v>
       </c>
@@ -14418,7 +14416,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="468" spans="1:7">
+    <row r="468" hidden="1" spans="1:7">
       <c r="A468" t="s">
         <v>245</v>
       </c>
@@ -14441,7 +14439,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="469" spans="1:7">
+    <row r="469" hidden="1" spans="1:7">
       <c r="A469" t="s">
         <v>594</v>
       </c>
@@ -14464,7 +14462,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="470" spans="1:7">
+    <row r="470" hidden="1" spans="1:7">
       <c r="A470" t="s">
         <v>676</v>
       </c>
@@ -14487,7 +14485,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="471" spans="1:7">
+    <row r="471" hidden="1" spans="1:7">
       <c r="A471" t="s">
         <v>681</v>
       </c>
@@ -14510,7 +14508,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="472" spans="1:7">
+    <row r="472" hidden="1" spans="1:7">
       <c r="A472" t="s">
         <v>682</v>
       </c>
@@ -14533,7 +14531,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="473" spans="1:7">
+    <row r="473" hidden="1" spans="1:7">
       <c r="A473" t="s">
         <v>683</v>
       </c>
@@ -14556,7 +14554,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="474" spans="1:7">
+    <row r="474" hidden="1" spans="1:7">
       <c r="A474" t="s">
         <v>686</v>
       </c>
@@ -14579,7 +14577,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="475" spans="1:7">
+    <row r="475" hidden="1" spans="1:7">
       <c r="A475" t="s">
         <v>687</v>
       </c>
@@ -14602,7 +14600,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="476" spans="1:7">
+    <row r="476" hidden="1" spans="1:7">
       <c r="A476" t="s">
         <v>688</v>
       </c>
@@ -14625,7 +14623,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="477" spans="1:7">
+    <row r="477" hidden="1" spans="1:7">
       <c r="A477" t="s">
         <v>689</v>
       </c>
@@ -14648,7 +14646,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="478" spans="1:7">
+    <row r="478" hidden="1" spans="1:7">
       <c r="A478" t="s">
         <v>690</v>
       </c>
@@ -14671,7 +14669,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="479" spans="1:7">
+    <row r="479" hidden="1" spans="1:7">
       <c r="A479" t="s">
         <v>691</v>
       </c>
@@ -14694,7 +14692,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="480" spans="1:7">
+    <row r="480" hidden="1" spans="1:7">
       <c r="A480" t="s">
         <v>691</v>
       </c>
@@ -14717,7 +14715,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="481" spans="1:7">
+    <row r="481" hidden="1" spans="1:7">
       <c r="A481" t="s">
         <v>689</v>
       </c>
@@ -14740,7 +14738,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="482" spans="1:7">
+    <row r="482" hidden="1" spans="1:7">
       <c r="A482" t="s">
         <v>692</v>
       </c>
@@ -14763,7 +14761,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="483" spans="1:7">
+    <row r="483" hidden="1" spans="1:7">
       <c r="A483" t="s">
         <v>694</v>
       </c>
@@ -14786,7 +14784,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="484" spans="1:7">
+    <row r="484" hidden="1" spans="1:7">
       <c r="A484" t="s">
         <v>697</v>
       </c>
@@ -14809,7 +14807,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="485" spans="1:7">
+    <row r="485" hidden="1" spans="1:7">
       <c r="A485" t="s">
         <v>699</v>
       </c>
@@ -14832,7 +14830,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="486" spans="1:7">
+    <row r="486" hidden="1" spans="1:7">
       <c r="A486" t="s">
         <v>702</v>
       </c>
@@ -14855,7 +14853,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="487" spans="1:7">
+    <row r="487" hidden="1" spans="1:7">
       <c r="A487" t="s">
         <v>699</v>
       </c>
@@ -14878,7 +14876,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="488" spans="1:7">
+    <row r="488" hidden="1" spans="1:7">
       <c r="A488" t="s">
         <v>703</v>
       </c>
@@ -14901,7 +14899,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="489" spans="1:7">
+    <row r="489" hidden="1" spans="1:7">
       <c r="A489" t="s">
         <v>302</v>
       </c>
@@ -14924,7 +14922,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="490" spans="1:7">
+    <row r="490" hidden="1" spans="1:7">
       <c r="A490" t="s">
         <v>305</v>
       </c>
@@ -14947,7 +14945,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="491" spans="1:7">
+    <row r="491" hidden="1" spans="1:7">
       <c r="A491" t="s">
         <v>706</v>
       </c>
@@ -14970,7 +14968,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="492" spans="1:7">
+    <row r="492" hidden="1" spans="1:7">
       <c r="A492" t="s">
         <v>707</v>
       </c>
@@ -14993,7 +14991,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="493" spans="1:7">
+    <row r="493" hidden="1" spans="1:7">
       <c r="A493" t="s">
         <v>687</v>
       </c>
@@ -15016,7 +15014,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="494" spans="1:7">
+    <row r="494" hidden="1" spans="1:7">
       <c r="A494" t="s">
         <v>688</v>
       </c>
@@ -15039,7 +15037,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="495" spans="1:7">
+    <row r="495" hidden="1" spans="1:7">
       <c r="A495" t="s">
         <v>686</v>
       </c>
@@ -15062,7 +15060,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="496" spans="1:7">
+    <row r="496" hidden="1" spans="1:7">
       <c r="A496" t="s">
         <v>710</v>
       </c>
@@ -15085,7 +15083,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="497" spans="1:7">
+    <row r="497" hidden="1" spans="1:7">
       <c r="A497" t="s">
         <v>711</v>
       </c>
@@ -15108,7 +15106,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="498" spans="1:7">
+    <row r="498" hidden="1" spans="1:7">
       <c r="A498" t="s">
         <v>712</v>
       </c>
@@ -15131,7 +15129,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="499" spans="1:7">
+    <row r="499" hidden="1" spans="1:7">
       <c r="A499" t="s">
         <v>713</v>
       </c>
@@ -15154,7 +15152,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="500" spans="1:7">
+    <row r="500" hidden="1" spans="1:7">
       <c r="A500" t="s">
         <v>715</v>
       </c>
@@ -15177,7 +15175,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="501" spans="1:7">
+    <row r="501" hidden="1" spans="1:7">
       <c r="A501" t="s">
         <v>716</v>
       </c>
@@ -15200,7 +15198,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="502" spans="1:7">
+    <row r="502" hidden="1" spans="1:7">
       <c r="A502" t="s">
         <v>718</v>
       </c>
@@ -15223,7 +15221,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="503" spans="1:7">
+    <row r="503" hidden="1" spans="1:7">
       <c r="A503" t="s">
         <v>719</v>
       </c>
@@ -15246,7 +15244,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="504" spans="1:7">
+    <row r="504" hidden="1" spans="1:7">
       <c r="A504" t="s">
         <v>720</v>
       </c>
@@ -15269,7 +15267,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="505" spans="1:7">
+    <row r="505" hidden="1" spans="1:7">
       <c r="A505" t="s">
         <v>721</v>
       </c>
@@ -15292,7 +15290,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="506" spans="1:7">
+    <row r="506" hidden="1" spans="1:7">
       <c r="A506" t="s">
         <v>284</v>
       </c>
@@ -15315,7 +15313,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="507" spans="1:7">
+    <row r="507" hidden="1" spans="1:7">
       <c r="A507" t="s">
         <v>723</v>
       </c>
@@ -15338,7 +15336,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="508" spans="1:7">
+    <row r="508" hidden="1" spans="1:7">
       <c r="A508" t="s">
         <v>687</v>
       </c>
@@ -15361,7 +15359,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="509" spans="1:7">
+    <row r="509" hidden="1" spans="1:7">
       <c r="A509" t="s">
         <v>688</v>
       </c>
@@ -15384,7 +15382,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="510" spans="1:7">
+    <row r="510" hidden="1" spans="1:7">
       <c r="A510" t="s">
         <v>686</v>
       </c>
@@ -15407,7 +15405,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="511" spans="1:7">
+    <row r="511" hidden="1" spans="1:7">
       <c r="A511" t="s">
         <v>726</v>
       </c>
@@ -15430,7 +15428,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="512" spans="1:7">
+    <row r="512" hidden="1" spans="1:7">
       <c r="A512" t="s">
         <v>728</v>
       </c>
@@ -15453,7 +15451,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="513" spans="1:7">
+    <row r="513" hidden="1" spans="1:7">
       <c r="A513" t="s">
         <v>730</v>
       </c>
@@ -15476,7 +15474,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="514" spans="1:7">
+    <row r="514" hidden="1" spans="1:7">
       <c r="A514" t="s">
         <v>732</v>
       </c>
@@ -15499,7 +15497,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="515" spans="1:7">
+    <row r="515" hidden="1" spans="1:7">
       <c r="A515" t="s">
         <v>734</v>
       </c>
@@ -15522,7 +15520,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="516" spans="1:7">
+    <row r="516" hidden="1" spans="1:7">
       <c r="A516" t="s">
         <v>736</v>
       </c>
@@ -15545,7 +15543,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="517" spans="1:7">
+    <row r="517" hidden="1" spans="1:7">
       <c r="A517" t="s">
         <v>737</v>
       </c>
@@ -15568,7 +15566,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="518" spans="1:7">
+    <row r="518" hidden="1" spans="1:7">
       <c r="A518" t="s">
         <v>739</v>
       </c>
@@ -15591,7 +15589,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="519" spans="1:7">
+    <row r="519" hidden="1" spans="1:7">
       <c r="A519" t="s">
         <v>742</v>
       </c>
@@ -15614,7 +15612,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="520" spans="1:7">
+    <row r="520" hidden="1" spans="1:7">
       <c r="A520" t="s">
         <v>744</v>
       </c>
@@ -15637,7 +15635,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="521" spans="1:7">
+    <row r="521" hidden="1" spans="1:7">
       <c r="A521" t="s">
         <v>742</v>
       </c>
@@ -15660,7 +15658,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="522" spans="1:7">
+    <row r="522" hidden="1" spans="1:7">
       <c r="A522" t="s">
         <v>747</v>
       </c>
@@ -15683,7 +15681,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="523" spans="1:7">
+    <row r="523" hidden="1" spans="1:7">
       <c r="A523" t="s">
         <v>748</v>
       </c>
@@ -15706,7 +15704,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="524" spans="1:7">
+    <row r="524" hidden="1" spans="1:7">
       <c r="A524" t="s">
         <v>750</v>
       </c>
@@ -15729,7 +15727,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="525" spans="1:7">
+    <row r="525" hidden="1" spans="1:7">
       <c r="A525" t="s">
         <v>754</v>
       </c>
@@ -15752,7 +15750,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="526" spans="1:7">
+    <row r="526" hidden="1" spans="1:7">
       <c r="A526" t="s">
         <v>757</v>
       </c>
@@ -15775,7 +15773,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="527" spans="1:7">
+    <row r="527" hidden="1" spans="1:7">
       <c r="A527" t="s">
         <v>760</v>
       </c>
@@ -15798,7 +15796,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="528" spans="1:7">
+    <row r="528" hidden="1" spans="1:7">
       <c r="A528" t="s">
         <v>762</v>
       </c>
@@ -15821,7 +15819,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="529" spans="1:7">
+    <row r="529" hidden="1" spans="1:7">
       <c r="A529" t="s">
         <v>687</v>
       </c>
@@ -15844,7 +15842,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="530" spans="1:7">
+    <row r="530" hidden="1" spans="1:7">
       <c r="A530" t="s">
         <v>765</v>
       </c>
@@ -15867,7 +15865,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="531" spans="1:7">
+    <row r="531" hidden="1" spans="1:7">
       <c r="A531" t="s">
         <v>686</v>
       </c>
@@ -15890,7 +15888,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="532" spans="1:7">
+    <row r="532" hidden="1" spans="1:7">
       <c r="A532" t="s">
         <v>766</v>
       </c>
@@ -15913,7 +15911,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="533" spans="1:7">
+    <row r="533" hidden="1" spans="1:7">
       <c r="A533" t="s">
         <v>769</v>
       </c>
@@ -15936,7 +15934,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="534" spans="1:7">
+    <row r="534" hidden="1" spans="1:7">
       <c r="A534" t="s">
         <v>771</v>
       </c>
@@ -15959,7 +15957,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="535" spans="1:7">
+    <row r="535" hidden="1" spans="1:7">
       <c r="A535" t="s">
         <v>773</v>
       </c>
@@ -15982,7 +15980,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="536" spans="1:7">
+    <row r="536" hidden="1" spans="1:7">
       <c r="A536" t="s">
         <v>775</v>
       </c>
@@ -16005,7 +16003,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="537" spans="1:7">
+    <row r="537" hidden="1" spans="1:7">
       <c r="A537" t="s">
         <v>778</v>
       </c>
@@ -16028,7 +16026,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="538" spans="1:7">
+    <row r="538" hidden="1" spans="1:7">
       <c r="A538" t="s">
         <v>780</v>
       </c>
@@ -16051,7 +16049,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="539" spans="1:7">
+    <row r="539" hidden="1" spans="1:7">
       <c r="A539" t="s">
         <v>782</v>
       </c>
@@ -16074,7 +16072,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="540" spans="1:7">
+    <row r="540" hidden="1" spans="1:7">
       <c r="A540" t="s">
         <v>784</v>
       </c>
@@ -16097,7 +16095,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="541" spans="1:7">
+    <row r="541" hidden="1" spans="1:7">
       <c r="A541" t="s">
         <v>786</v>
       </c>
@@ -16120,7 +16118,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="542" spans="1:7">
+    <row r="542" hidden="1" spans="1:7">
       <c r="A542" t="s">
         <v>284</v>
       </c>
@@ -16143,7 +16141,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="543" spans="1:7">
+    <row r="543" hidden="1" spans="1:7">
       <c r="A543" t="s">
         <v>726</v>
       </c>
@@ -16166,7 +16164,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="544" spans="1:7">
+    <row r="544" hidden="1" spans="1:7">
       <c r="A544" t="s">
         <v>687</v>
       </c>
@@ -16189,7 +16187,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="545" spans="1:7">
+    <row r="545" hidden="1" spans="1:7">
       <c r="A545" t="s">
         <v>688</v>
       </c>
@@ -16212,7 +16210,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="546" spans="1:7">
+    <row r="546" hidden="1" spans="1:7">
       <c r="A546" t="s">
         <v>686</v>
       </c>
@@ -16235,7 +16233,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="547" spans="1:7">
+    <row r="547" hidden="1" spans="1:7">
       <c r="A547" t="s">
         <v>792</v>
       </c>
@@ -16258,7 +16256,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="548" spans="1:7">
+    <row r="548" hidden="1" spans="1:7">
       <c r="A548" t="s">
         <v>793</v>
       </c>
@@ -16281,7 +16279,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="549" spans="1:7">
+    <row r="549" hidden="1" spans="1:7">
       <c r="A549" t="s">
         <v>794</v>
       </c>
@@ -16304,7 +16302,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="550" spans="1:7">
+    <row r="550" hidden="1" spans="1:7">
       <c r="A550" t="s">
         <v>795</v>
       </c>
@@ -16327,7 +16325,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="551" spans="1:7">
+    <row r="551" hidden="1" spans="1:7">
       <c r="A551" t="s">
         <v>798</v>
       </c>
@@ -16350,7 +16348,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="552" spans="1:7">
+    <row r="552" hidden="1" spans="1:7">
       <c r="A552" t="s">
         <v>799</v>
       </c>
@@ -16373,7 +16371,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="553" spans="1:7">
+    <row r="553" hidden="1" spans="1:7">
       <c r="A553" t="s">
         <v>800</v>
       </c>
@@ -16396,7 +16394,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="554" spans="1:7">
+    <row r="554" hidden="1" spans="1:7">
       <c r="A554" t="s">
         <v>801</v>
       </c>
@@ -16419,7 +16417,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="555" spans="1:7">
+    <row r="555" hidden="1" spans="1:7">
       <c r="A555" t="s">
         <v>318</v>
       </c>
@@ -16442,7 +16440,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="556" spans="1:7">
+    <row r="556" hidden="1" spans="1:7">
       <c r="A556" t="s">
         <v>803</v>
       </c>
@@ -16465,7 +16463,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="557" spans="1:7">
+    <row r="557" hidden="1" spans="1:7">
       <c r="A557" t="s">
         <v>805</v>
       </c>
@@ -16488,7 +16486,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="558" spans="1:7">
+    <row r="558" hidden="1" spans="1:7">
       <c r="A558" t="s">
         <v>471</v>
       </c>
@@ -16511,7 +16509,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="559" spans="1:7">
+    <row r="559" hidden="1" spans="1:7">
       <c r="A559" t="s">
         <v>808</v>
       </c>
@@ -16534,7 +16532,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="560" spans="1:7">
+    <row r="560" hidden="1" spans="1:7">
       <c r="A560" t="s">
         <v>471</v>
       </c>
@@ -16557,7 +16555,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="561" spans="1:7">
+    <row r="561" hidden="1" spans="1:7">
       <c r="A561" t="s">
         <v>471</v>
       </c>
@@ -16580,7 +16578,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="562" spans="1:7">
+    <row r="562" hidden="1" spans="1:7">
       <c r="A562" t="s">
         <v>811</v>
       </c>
@@ -16603,7 +16601,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="563" spans="1:7">
+    <row r="563" hidden="1" spans="1:7">
       <c r="A563" t="s">
         <v>813</v>
       </c>
@@ -16626,7 +16624,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="564" spans="1:7">
+    <row r="564" hidden="1" spans="1:7">
       <c r="A564" t="s">
         <v>492</v>
       </c>
@@ -16649,9 +16647,9 @@
         <v>807</v>
       </c>
     </row>
-    <row r="565" spans="1:7">
+    <row r="565" hidden="1" spans="1:7">
       <c r="A565" t="s">
-        <v>814</v>
+        <v>473</v>
       </c>
       <c r="B565" t="s">
         <v>8</v>
@@ -16666,18 +16664,18 @@
         <v>11</v>
       </c>
       <c r="F565" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="G565" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="566" spans="1:7">
+    <row r="566" hidden="1" spans="1:7">
       <c r="A566" t="s">
         <v>499</v>
       </c>
       <c r="B566" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C566" t="s">
         <v>812</v>
@@ -16695,12 +16693,12 @@
         <v>807</v>
       </c>
     </row>
-    <row r="567" spans="1:7">
+    <row r="567" hidden="1" spans="1:7">
       <c r="A567" t="s">
         <v>486</v>
       </c>
       <c r="B567" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C567" t="s">
         <v>100</v>
@@ -16718,9 +16716,9 @@
         <v>807</v>
       </c>
     </row>
-    <row r="568" spans="1:7">
+    <row r="568" hidden="1" spans="1:7">
       <c r="A568" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B568" t="s">
         <v>30</v>
@@ -16741,9 +16739,9 @@
         <v>807</v>
       </c>
     </row>
-    <row r="569" spans="1:7">
+    <row r="569" hidden="1" spans="1:7">
       <c r="A569" t="s">
-        <v>814</v>
+        <v>473</v>
       </c>
       <c r="B569" t="s">
         <v>8</v>
@@ -16758,18 +16756,18 @@
         <v>11</v>
       </c>
       <c r="F569" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="G569" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="570" spans="1:7">
+    <row r="570" hidden="1" spans="1:7">
       <c r="A570" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B570" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C570" t="s">
         <v>812</v>
@@ -16787,12 +16785,12 @@
         <v>807</v>
       </c>
     </row>
-    <row r="571" spans="1:7">
+    <row r="571" hidden="1" spans="1:7">
       <c r="A571" t="s">
         <v>102</v>
       </c>
       <c r="B571" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C571" t="s">
         <v>812</v>
@@ -16810,9 +16808,9 @@
         <v>807</v>
       </c>
     </row>
-    <row r="572" spans="1:7">
+    <row r="572" hidden="1" spans="1:7">
       <c r="A572" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B572" t="s">
         <v>30</v>
@@ -16833,7 +16831,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="573" spans="1:7">
+    <row r="573" hidden="1" spans="1:7">
       <c r="A573" t="s">
         <v>458</v>
       </c>
@@ -16856,9 +16854,9 @@
         <v>807</v>
       </c>
     </row>
-    <row r="574" spans="1:7">
+    <row r="574" hidden="1" spans="1:7">
       <c r="A574" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B574" t="s">
         <v>30</v>
@@ -16879,12 +16877,12 @@
         <v>807</v>
       </c>
     </row>
-    <row r="575" spans="1:7">
+    <row r="575" hidden="1" spans="1:7">
       <c r="A575" t="s">
         <v>811</v>
       </c>
       <c r="B575" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C575" t="s">
         <v>812</v>
@@ -16902,9 +16900,9 @@
         <v>807</v>
       </c>
     </row>
-    <row r="576" spans="1:7">
+    <row r="576" hidden="1" spans="1:7">
       <c r="A576" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B576" t="s">
         <v>8</v>
@@ -16919,15 +16917,15 @@
         <v>22</v>
       </c>
       <c r="F576" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="G576" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="577" spans="1:7">
+    <row r="577" hidden="1" spans="1:7">
       <c r="A577" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B577" t="s">
         <v>8</v>
@@ -16942,36 +16940,36 @@
         <v>22</v>
       </c>
       <c r="F577" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="G577" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="578" spans="1:7">
+    <row r="578" hidden="1" spans="1:7">
       <c r="A578" t="s">
+        <v>825</v>
+      </c>
+      <c r="B578" t="s">
         <v>826</v>
       </c>
-      <c r="B578" t="s">
+      <c r="C578" t="s">
+        <v>55</v>
+      </c>
+      <c r="D578" t="s">
         <v>827</v>
-      </c>
-      <c r="C578" t="s">
-        <v>55</v>
-      </c>
-      <c r="D578" t="s">
-        <v>828</v>
       </c>
       <c r="E578" t="s">
         <v>22</v>
       </c>
       <c r="F578" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="G578" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="579" spans="1:7">
+    <row r="579" hidden="1" spans="1:7">
       <c r="A579" t="s">
         <v>471</v>
       </c>
@@ -16988,18 +16986,18 @@
         <v>22</v>
       </c>
       <c r="F579" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G579" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="580" spans="1:7">
+    <row r="580" hidden="1" spans="1:7">
       <c r="A580" t="s">
+        <v>825</v>
+      </c>
+      <c r="B580" t="s">
         <v>826</v>
-      </c>
-      <c r="B580" t="s">
-        <v>827</v>
       </c>
       <c r="C580" t="s">
         <v>55</v>
@@ -17011,15 +17009,15 @@
         <v>22</v>
       </c>
       <c r="F580" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="G580" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="581" spans="1:7">
+    <row r="581" hidden="1" spans="1:7">
       <c r="A581" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B581" t="s">
         <v>8</v>
@@ -17034,21 +17032,21 @@
         <v>22</v>
       </c>
       <c r="F581" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G581" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="582" spans="1:7">
+    <row r="582" hidden="1" spans="1:7">
       <c r="A582" t="s">
-        <v>814</v>
+        <v>473</v>
       </c>
       <c r="B582" t="s">
+        <v>831</v>
+      </c>
+      <c r="C582" t="s">
         <v>832</v>
-      </c>
-      <c r="C582" t="s">
-        <v>833</v>
       </c>
       <c r="D582" t="s">
         <v>38</v>
@@ -17057,18 +17055,18 @@
         <v>22</v>
       </c>
       <c r="F582" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G582" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="583" spans="1:7">
+    <row r="583" hidden="1" spans="1:7">
       <c r="A583" t="s">
+        <v>825</v>
+      </c>
+      <c r="B583" t="s">
         <v>826</v>
-      </c>
-      <c r="B583" t="s">
-        <v>827</v>
       </c>
       <c r="C583" t="s">
         <v>55</v>
@@ -17080,15 +17078,15 @@
         <v>22</v>
       </c>
       <c r="F583" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G583" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="584" spans="1:7">
+    <row r="584" hidden="1" spans="1:7">
       <c r="A584" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B584" t="s">
         <v>8</v>
@@ -17103,21 +17101,21 @@
         <v>22</v>
       </c>
       <c r="F584" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G584" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="585" spans="1:7">
+    <row r="585" hidden="1" spans="1:7">
       <c r="A585" t="s">
-        <v>814</v>
+        <v>473</v>
       </c>
       <c r="B585" t="s">
+        <v>831</v>
+      </c>
+      <c r="C585" t="s">
         <v>832</v>
-      </c>
-      <c r="C585" t="s">
-        <v>833</v>
       </c>
       <c r="D585" t="s">
         <v>43</v>
@@ -17126,18 +17124,18 @@
         <v>22</v>
       </c>
       <c r="F585" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G585" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="586" spans="1:7">
+    <row r="586" hidden="1" spans="1:7">
       <c r="A586" t="s">
+        <v>825</v>
+      </c>
+      <c r="B586" t="s">
         <v>826</v>
-      </c>
-      <c r="B586" t="s">
-        <v>827</v>
       </c>
       <c r="C586" t="s">
         <v>55</v>
@@ -17149,13 +17147,13 @@
         <v>22</v>
       </c>
       <c r="F586" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="G586" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="587" spans="1:7">
+    <row r="587" hidden="1" spans="1:7">
       <c r="A587" t="s">
         <v>465</v>
       </c>
@@ -17178,18 +17176,18 @@
         <v>807</v>
       </c>
     </row>
-    <row r="588" spans="1:7">
+    <row r="588" hidden="1" spans="1:7">
       <c r="A588" t="s">
         <v>492</v>
       </c>
       <c r="B588" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C588" t="s">
         <v>812</v>
       </c>
       <c r="D588" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E588" t="s">
         <v>28</v>
@@ -17201,7 +17199,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="589" spans="1:7">
+    <row r="589" hidden="1" spans="1:7">
       <c r="A589" t="s">
         <v>499</v>
       </c>
@@ -17224,15 +17222,15 @@
         <v>807</v>
       </c>
     </row>
-    <row r="590" spans="1:7">
+    <row r="590" hidden="1" spans="1:7">
       <c r="A590" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B590" t="s">
         <v>8</v>
       </c>
       <c r="C590" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D590" t="s">
         <v>10</v>
@@ -17241,18 +17239,18 @@
         <v>28</v>
       </c>
       <c r="F590" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G590" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="591" spans="1:7">
+    <row r="591" hidden="1" spans="1:7">
       <c r="A591" t="s">
+        <v>825</v>
+      </c>
+      <c r="B591" t="s">
         <v>826</v>
-      </c>
-      <c r="B591" t="s">
-        <v>827</v>
       </c>
       <c r="C591" t="s">
         <v>481</v>
@@ -17264,18 +17262,18 @@
         <v>28</v>
       </c>
       <c r="F591" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G591" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="592" spans="1:7">
+    <row r="592" hidden="1" spans="1:7">
       <c r="A592" t="s">
         <v>504</v>
       </c>
       <c r="B592" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C592" t="s">
         <v>508</v>
@@ -17293,15 +17291,15 @@
         <v>807</v>
       </c>
     </row>
-    <row r="593" spans="1:7">
+    <row r="593" hidden="1" spans="1:7">
       <c r="A593" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B593" t="s">
         <v>8</v>
       </c>
       <c r="C593" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D593" t="s">
         <v>14</v>
@@ -17310,18 +17308,18 @@
         <v>28</v>
       </c>
       <c r="F593" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G593" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="594" spans="1:7">
+    <row r="594" hidden="1" spans="1:7">
       <c r="A594" t="s">
+        <v>825</v>
+      </c>
+      <c r="B594" t="s">
         <v>826</v>
-      </c>
-      <c r="B594" t="s">
-        <v>827</v>
       </c>
       <c r="C594" t="s">
         <v>481</v>
@@ -17333,18 +17331,18 @@
         <v>28</v>
       </c>
       <c r="F594" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G594" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="595" spans="1:7">
+    <row r="595" hidden="1" spans="1:7">
       <c r="A595" t="s">
         <v>505</v>
       </c>
       <c r="B595" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C595" t="s">
         <v>508</v>
@@ -17362,7 +17360,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="596" spans="1:7">
+    <row r="596" hidden="1" spans="1:7">
       <c r="A596" t="s">
         <v>103</v>
       </c>
@@ -17385,9 +17383,9 @@
         <v>807</v>
       </c>
     </row>
-    <row r="597" spans="1:7">
+    <row r="597" hidden="1" spans="1:7">
       <c r="A597" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B597" t="s">
         <v>30</v>
@@ -17408,9 +17406,9 @@
         <v>807</v>
       </c>
     </row>
-    <row r="598" spans="1:7">
+    <row r="598" hidden="1" spans="1:7">
       <c r="A598" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B598" t="s">
         <v>30</v>
@@ -17431,12 +17429,12 @@
         <v>807</v>
       </c>
     </row>
-    <row r="599" spans="1:7">
+    <row r="599" hidden="1" spans="1:7">
       <c r="A599" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B599" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C599" t="s">
         <v>207</v>
@@ -17454,9 +17452,9 @@
         <v>807</v>
       </c>
     </row>
-    <row r="600" spans="1:7">
+    <row r="600" hidden="1" spans="1:7">
       <c r="A600" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B600" t="s">
         <v>30</v>
@@ -17477,9 +17475,9 @@
         <v>807</v>
       </c>
     </row>
-    <row r="601" spans="1:7">
+    <row r="601" hidden="1" spans="1:7">
       <c r="A601" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B601" t="s">
         <v>30</v>
@@ -17500,15 +17498,15 @@
         <v>807</v>
       </c>
     </row>
-    <row r="602" spans="1:7">
+    <row r="602" hidden="1" spans="1:7">
       <c r="A602" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B602" t="s">
         <v>30</v>
       </c>
       <c r="C602" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D602" t="s">
         <v>10</v>
@@ -17523,15 +17521,15 @@
         <v>807</v>
       </c>
     </row>
-    <row r="603" spans="1:7">
+    <row r="603" hidden="1" spans="1:7">
       <c r="A603" t="s">
+        <v>846</v>
+      </c>
+      <c r="B603" t="s">
         <v>847</v>
       </c>
-      <c r="B603" t="s">
-        <v>848</v>
-      </c>
       <c r="C603" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D603" t="s">
         <v>111</v>
@@ -17546,12 +17544,12 @@
         <v>807</v>
       </c>
     </row>
-    <row r="604" spans="1:7">
+    <row r="604" hidden="1" spans="1:7">
       <c r="A604" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B604" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C604" t="s">
         <v>80</v>
@@ -17563,15 +17561,15 @@
         <v>47</v>
       </c>
       <c r="F604" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="G604" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="605" spans="1:7">
+    <row r="605" hidden="1" spans="1:7">
       <c r="A605" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B605" t="s">
         <v>30</v>
@@ -17592,12 +17590,12 @@
         <v>807</v>
       </c>
     </row>
-    <row r="606" spans="1:7">
+    <row r="606" hidden="1" spans="1:7">
       <c r="A606" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B606" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C606" t="s">
         <v>80</v>
@@ -17609,18 +17607,18 @@
         <v>47</v>
       </c>
       <c r="F606" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="G606" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="607" spans="1:7">
+    <row r="607" hidden="1" spans="1:7">
       <c r="A607" t="s">
         <v>495</v>
       </c>
       <c r="B607" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C607" t="s">
         <v>55</v>
@@ -17638,7 +17636,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="608" spans="1:7">
+    <row r="608" hidden="1" spans="1:7">
       <c r="A608" t="s">
         <v>65</v>
       </c>
@@ -17661,12 +17659,12 @@
         <v>807</v>
       </c>
     </row>
-    <row r="609" spans="1:7">
+    <row r="609" hidden="1" spans="1:7">
       <c r="A609" t="s">
         <v>69</v>
       </c>
       <c r="B609" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C609" t="s">
         <v>454</v>
@@ -17684,9 +17682,9 @@
         <v>807</v>
       </c>
     </row>
-    <row r="610" spans="1:7">
+    <row r="610" hidden="1" spans="1:7">
       <c r="A610" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B610" t="s">
         <v>19</v>
@@ -17707,9 +17705,9 @@
         <v>807</v>
       </c>
     </row>
-    <row r="611" spans="1:7">
+    <row r="611" hidden="1" spans="1:7">
       <c r="A611" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B611" t="s">
         <v>19</v>
@@ -17730,7 +17728,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="612" spans="1:7">
+    <row r="612" hidden="1" spans="1:7">
       <c r="A612" t="s">
         <v>471</v>
       </c>
@@ -17747,15 +17745,15 @@
         <v>63</v>
       </c>
       <c r="F612" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="G612" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="613" spans="1:7">
+    <row r="613" hidden="1" spans="1:7">
       <c r="A613" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B613" t="s">
         <v>30</v>
@@ -17776,12 +17774,12 @@
         <v>807</v>
       </c>
     </row>
-    <row r="614" spans="1:7">
+    <row r="614" hidden="1" spans="1:7">
       <c r="A614" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B614" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C614" t="s">
         <v>55</v>
@@ -17799,9 +17797,9 @@
         <v>807</v>
       </c>
     </row>
-    <row r="615" spans="1:7">
+    <row r="615" hidden="1" spans="1:7">
       <c r="A615" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B615" t="s">
         <v>30</v>
@@ -17822,12 +17820,12 @@
         <v>807</v>
       </c>
     </row>
-    <row r="616" spans="1:7">
+    <row r="616" hidden="1" spans="1:7">
       <c r="A616" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B616" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C616" t="s">
         <v>55</v>
@@ -17845,7 +17843,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="617" spans="1:7">
+    <row r="617" hidden="1" spans="1:7">
       <c r="A617" t="s">
         <v>498</v>
       </c>
@@ -17868,12 +17866,12 @@
         <v>807</v>
       </c>
     </row>
-    <row r="618" spans="1:7">
+    <row r="618" hidden="1" spans="1:7">
       <c r="A618" t="s">
+        <v>859</v>
+      </c>
+      <c r="B618" t="s">
         <v>860</v>
-      </c>
-      <c r="B618" t="s">
-        <v>861</v>
       </c>
       <c r="C618" t="s">
         <v>508</v>
@@ -17891,9 +17889,9 @@
         <v>807</v>
       </c>
     </row>
-    <row r="619" spans="1:7">
+    <row r="619" hidden="1" spans="1:7">
       <c r="A619" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B619" t="s">
         <v>30</v>
@@ -17911,10 +17909,10 @@
         <v>293</v>
       </c>
       <c r="G619" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="620" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="620" hidden="1" spans="1:7">
       <c r="A620" t="s">
         <v>557</v>
       </c>
@@ -17934,12 +17932,12 @@
         <v>304</v>
       </c>
       <c r="G620" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="621" hidden="1" spans="1:7">
+      <c r="A621" t="s">
         <v>863</v>
-      </c>
-    </row>
-    <row r="621" spans="1:7">
-      <c r="A621" t="s">
-        <v>864</v>
       </c>
       <c r="B621" t="s">
         <v>19</v>
@@ -17957,10 +17955,10 @@
         <v>39</v>
       </c>
       <c r="G621" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="622" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="622" hidden="1" spans="1:7">
       <c r="A622" t="s">
         <v>538</v>
       </c>
@@ -17980,10 +17978,10 @@
         <v>39</v>
       </c>
       <c r="G622" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="623" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="623" hidden="1" spans="1:7">
       <c r="A623" t="s">
         <v>533</v>
       </c>
@@ -18003,12 +18001,12 @@
         <v>304</v>
       </c>
       <c r="G623" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="624" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="624" hidden="1" spans="1:7">
       <c r="A624" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B624" t="s">
         <v>30</v>
@@ -18026,12 +18024,12 @@
         <v>232</v>
       </c>
       <c r="G624" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="625" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="625" hidden="1" spans="1:7">
       <c r="A625" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B625" t="s">
         <v>30</v>
@@ -18049,10 +18047,10 @@
         <v>304</v>
       </c>
       <c r="G625" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="626" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="626" hidden="1" spans="1:7">
       <c r="A626" t="s">
         <v>544</v>
       </c>
@@ -18072,15 +18070,15 @@
         <v>232</v>
       </c>
       <c r="G626" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="627" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="627" hidden="1" spans="1:7">
       <c r="A627" t="s">
+        <v>866</v>
+      </c>
+      <c r="B627" t="s">
         <v>867</v>
-      </c>
-      <c r="B627" t="s">
-        <v>868</v>
       </c>
       <c r="C627" t="s">
         <v>537</v>
@@ -18095,12 +18093,12 @@
         <v>23</v>
       </c>
       <c r="G627" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="628" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="628" hidden="1" spans="1:7">
       <c r="A628" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B628" t="s">
         <v>30</v>
@@ -18118,10 +18116,10 @@
         <v>232</v>
       </c>
       <c r="G628" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="629" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="629" hidden="1" spans="1:7">
       <c r="A629" t="s">
         <v>539</v>
       </c>
@@ -18141,12 +18139,12 @@
         <v>304</v>
       </c>
       <c r="G629" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="630" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="630" hidden="1" spans="1:7">
       <c r="A630" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B630" t="s">
         <v>19</v>
@@ -18164,12 +18162,12 @@
         <v>304</v>
       </c>
       <c r="G630" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="631" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="631" hidden="1" spans="1:7">
       <c r="A631" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B631" t="s">
         <v>19</v>
@@ -18187,10 +18185,10 @@
         <v>304</v>
       </c>
       <c r="G631" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="632" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="632" hidden="1" spans="1:7">
       <c r="A632" t="s">
         <v>547</v>
       </c>
@@ -18210,12 +18208,12 @@
         <v>129</v>
       </c>
       <c r="G632" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="633" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="633" hidden="1" spans="1:7">
       <c r="A633" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B633" t="s">
         <v>30</v>
@@ -18233,18 +18231,18 @@
         <v>29</v>
       </c>
       <c r="G633" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="634" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="634" hidden="1" spans="1:7">
       <c r="A634" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B634" t="s">
         <v>30</v>
       </c>
       <c r="C634" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D634" t="s">
         <v>46</v>
@@ -18256,18 +18254,18 @@
         <v>304</v>
       </c>
       <c r="G634" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="635" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="635" hidden="1" spans="1:7">
       <c r="A635" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B635" t="s">
         <v>8</v>
       </c>
       <c r="C635" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D635" t="s">
         <v>10</v>
@@ -18279,12 +18277,12 @@
         <v>83</v>
       </c>
       <c r="G635" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="636" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="636" hidden="1" spans="1:7">
       <c r="A636" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B636" t="s">
         <v>8</v>
@@ -18299,21 +18297,21 @@
         <v>47</v>
       </c>
       <c r="F636" t="s">
+        <v>876</v>
+      </c>
+      <c r="G636" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="637" hidden="1" spans="1:7">
+      <c r="A637" t="s">
         <v>877</v>
-      </c>
-      <c r="G636" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="637" spans="1:7">
-      <c r="A637" t="s">
-        <v>878</v>
       </c>
       <c r="B637" t="s">
         <v>8</v>
       </c>
       <c r="C637" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D637" t="s">
         <v>14</v>
@@ -18325,12 +18323,12 @@
         <v>83</v>
       </c>
       <c r="G637" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="638" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="638" hidden="1" spans="1:7">
       <c r="A638" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B638" t="s">
         <v>8</v>
@@ -18345,15 +18343,15 @@
         <v>47</v>
       </c>
       <c r="F638" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="G638" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="639" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="639" hidden="1" spans="1:7">
       <c r="A639" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B639" t="s">
         <v>19</v>
@@ -18371,18 +18369,18 @@
         <v>304</v>
       </c>
       <c r="G639" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="640" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="640" hidden="1" spans="1:7">
       <c r="A640" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B640" t="s">
         <v>19</v>
       </c>
       <c r="C640" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D640" t="s">
         <v>17</v>
@@ -18394,12 +18392,12 @@
         <v>304</v>
       </c>
       <c r="G640" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="641" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="641" hidden="1" spans="1:7">
       <c r="A641" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B641" t="s">
         <v>8</v>
@@ -18414,21 +18412,21 @@
         <v>63</v>
       </c>
       <c r="F641" t="s">
+        <v>882</v>
+      </c>
+      <c r="G641" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="642" hidden="1" spans="1:7">
+      <c r="A642" t="s">
         <v>883</v>
-      </c>
-      <c r="G641" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="642" spans="1:7">
-      <c r="A642" t="s">
-        <v>884</v>
       </c>
       <c r="B642" t="s">
         <v>30</v>
       </c>
       <c r="C642" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D642" t="s">
         <v>46</v>
@@ -18440,12 +18438,12 @@
         <v>232</v>
       </c>
       <c r="G642" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="643" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="643" hidden="1" spans="1:7">
       <c r="A643" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B643" t="s">
         <v>8</v>
@@ -18460,15 +18458,15 @@
         <v>63</v>
       </c>
       <c r="F643" t="s">
+        <v>885</v>
+      </c>
+      <c r="G643" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="644" hidden="1" spans="1:7">
+      <c r="A644" t="s">
         <v>886</v>
-      </c>
-      <c r="G643" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="644" spans="1:7">
-      <c r="A644" t="s">
-        <v>887</v>
       </c>
       <c r="B644" t="s">
         <v>8</v>
@@ -18486,12 +18484,12 @@
         <v>83</v>
       </c>
       <c r="G644" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="645" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="645" hidden="1" spans="1:7">
       <c r="A645" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B645" t="s">
         <v>8</v>
@@ -18506,15 +18504,15 @@
         <v>63</v>
       </c>
       <c r="F645" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="G645" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="646" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="646" hidden="1" spans="1:7">
       <c r="A646" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B646" t="s">
         <v>8</v>
@@ -18532,18 +18530,18 @@
         <v>83</v>
       </c>
       <c r="G646" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="647" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="647" hidden="1" spans="1:7">
       <c r="A647" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B647" t="s">
         <v>19</v>
       </c>
       <c r="C647" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D647" t="s">
         <v>21</v>
@@ -18555,12 +18553,12 @@
         <v>304</v>
       </c>
       <c r="G647" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="648" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="648" hidden="1" spans="1:7">
       <c r="A648" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B648" t="s">
         <v>8</v>
@@ -18575,21 +18573,21 @@
         <v>63</v>
       </c>
       <c r="F648" t="s">
+        <v>890</v>
+      </c>
+      <c r="G648" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="649" hidden="1" spans="1:7">
+      <c r="A649" t="s">
         <v>891</v>
-      </c>
-      <c r="G648" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="649" spans="1:7">
-      <c r="A649" t="s">
-        <v>892</v>
       </c>
       <c r="B649" t="s">
         <v>30</v>
       </c>
       <c r="C649" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D649" t="s">
         <v>17</v>
@@ -18601,10 +18599,10 @@
         <v>232</v>
       </c>
       <c r="G649" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="650" spans="1:7">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="650" hidden="1" spans="1:7">
       <c r="A650" t="s">
         <v>55</v>
       </c>
@@ -18627,7 +18625,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="651" spans="1:7">
+    <row r="651" hidden="1" spans="1:7">
       <c r="A651" t="s">
         <v>55</v>
       </c>
@@ -18650,7 +18648,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="652" spans="1:7">
+    <row r="652" hidden="1" spans="1:7">
       <c r="A652" t="s">
         <v>55</v>
       </c>
@@ -18673,7 +18671,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="653" spans="1:7">
+    <row r="653" hidden="1" spans="1:7">
       <c r="A653" t="s">
         <v>55</v>
       </c>
@@ -18696,7 +18694,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="654" spans="1:7">
+    <row r="654" hidden="1" spans="1:7">
       <c r="A654" t="s">
         <v>55</v>
       </c>
@@ -18719,7 +18717,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="655" spans="1:7">
+    <row r="655" hidden="1" spans="1:7">
       <c r="A655" t="s">
         <v>55</v>
       </c>
@@ -18742,7 +18740,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="656" spans="1:7">
+    <row r="656" hidden="1" spans="1:7">
       <c r="A656" t="s">
         <v>55</v>
       </c>
@@ -18765,7 +18763,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="657" spans="1:7">
+    <row r="657" hidden="1" spans="1:7">
       <c r="A657" t="s">
         <v>55</v>
       </c>
@@ -18788,7 +18786,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="658" spans="1:7">
+    <row r="658" hidden="1" spans="1:7">
       <c r="A658" t="s">
         <v>55</v>
       </c>
@@ -18811,7 +18809,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="659" spans="1:7">
+    <row r="659" hidden="1" spans="1:7">
       <c r="A659" t="s">
         <v>55</v>
       </c>
@@ -18834,7 +18832,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="660" spans="1:7">
+    <row r="660" hidden="1" spans="1:7">
       <c r="A660" t="s">
         <v>55</v>
       </c>
@@ -18857,7 +18855,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="661" spans="1:7">
+    <row r="661" hidden="1" spans="1:7">
       <c r="A661" t="s">
         <v>55</v>
       </c>
@@ -18880,7 +18878,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="662" spans="1:7">
+    <row r="662" hidden="1" spans="1:7">
       <c r="A662" t="s">
         <v>55</v>
       </c>
@@ -18903,7 +18901,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="663" spans="1:7">
+    <row r="663" hidden="1" spans="1:7">
       <c r="A663" t="s">
         <v>55</v>
       </c>
@@ -18926,7 +18924,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="664" spans="1:7">
+    <row r="664" hidden="1" spans="1:7">
       <c r="A664" t="s">
         <v>55</v>
       </c>
@@ -18949,7 +18947,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="665" spans="1:7">
+    <row r="665" hidden="1" spans="1:7">
       <c r="A665" t="s">
         <v>55</v>
       </c>
@@ -18972,7 +18970,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="666" spans="1:7">
+    <row r="666" hidden="1" spans="1:7">
       <c r="A666" t="s">
         <v>55</v>
       </c>
@@ -18995,7 +18993,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="667" spans="1:7">
+    <row r="667" hidden="1" spans="1:7">
       <c r="A667" t="s">
         <v>55</v>
       </c>
@@ -19018,7 +19016,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="668" spans="1:7">
+    <row r="668" hidden="1" spans="1:7">
       <c r="A668" t="s">
         <v>55</v>
       </c>
@@ -19041,7 +19039,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="669" spans="1:7">
+    <row r="669" hidden="1" spans="1:7">
       <c r="A669" t="s">
         <v>55</v>
       </c>
@@ -19064,7 +19062,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="670" spans="1:7">
+    <row r="670" hidden="1" spans="1:7">
       <c r="A670" t="s">
         <v>55</v>
       </c>
@@ -19087,7 +19085,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="671" spans="1:7">
+    <row r="671" hidden="1" spans="1:7">
       <c r="A671" t="s">
         <v>55</v>
       </c>
@@ -19110,7 +19108,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="672" spans="1:7">
+    <row r="672" hidden="1" spans="1:7">
       <c r="A672" t="s">
         <v>55</v>
       </c>
@@ -19133,7 +19131,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="673" spans="1:7">
+    <row r="673" hidden="1" spans="1:7">
       <c r="A673" t="s">
         <v>55</v>
       </c>
@@ -19156,7 +19154,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="674" spans="1:7">
+    <row r="674" hidden="1" spans="1:7">
       <c r="A674" t="s">
         <v>55</v>
       </c>
@@ -19179,7 +19177,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="675" spans="1:7">
+    <row r="675" hidden="1" spans="1:7">
       <c r="A675" t="s">
         <v>55</v>
       </c>
@@ -19203,6 +19201,14 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G675" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="TP-Programation Python"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4802" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4942" uniqueCount="991">
   <si>
     <t>Enseignements</t>
   </si>
@@ -2837,27 +2837,99 @@
     <t>MCIL3</t>
   </si>
   <si>
+    <t>TP-Capteurs-SG32</t>
+  </si>
+  <si>
+    <t>Labo Mesures N°10 département ELN SG32</t>
+  </si>
+  <si>
+    <t>TP-Systèmes Asservis-SG31</t>
+  </si>
+  <si>
+    <t>Salle de TP Systèmes Asservis SG31</t>
+  </si>
+  <si>
     <t>Cours-Métrologie en haute tension</t>
   </si>
   <si>
+    <t>HADJERI Samir</t>
+  </si>
+  <si>
+    <t>TP-Systèmes Asservis-SG32</t>
+  </si>
+  <si>
+    <t>Salle de TP Systèmes Asservis SG32</t>
+  </si>
+  <si>
     <t>TD-Électronique de puissance-G2</t>
   </si>
   <si>
     <t>TD-Systèmes Asservis-G3</t>
   </si>
   <si>
+    <t>TP-Réseaux électriques-SG32</t>
+  </si>
+  <si>
+    <t>Labo Réseaux SG32</t>
+  </si>
+  <si>
+    <t>Salle de TP Systèmes Asservis SG12</t>
+  </si>
+  <si>
+    <t>Labo Mesures N°10 département ELN SG21</t>
+  </si>
+  <si>
+    <t>TP-Schémas électriques-SG32</t>
+  </si>
+  <si>
+    <t>Labo Schémas SG32</t>
+  </si>
+  <si>
+    <t>TP-Électronique de puissance-SG32</t>
+  </si>
+  <si>
+    <t>Labo ELN-P SG32</t>
+  </si>
+  <si>
     <t>Cours-EAD-Outils de simulation numérique 1</t>
   </si>
   <si>
     <t>Cours-EAD-OSN1-MCIL3</t>
   </si>
   <si>
+    <t>Labo Mesures N°10 département ELN SG12</t>
+  </si>
+  <si>
+    <t>TP-Électronique de puissance-SG31</t>
+  </si>
+  <si>
+    <t>Labo ELN-P SG31</t>
+  </si>
+  <si>
     <t>TD-Électronique de puissance-G3</t>
   </si>
   <si>
+    <t>Labo Mesures N°10 département ELN SG22</t>
+  </si>
+  <si>
+    <t>TP-Schémas électriques-SG21</t>
+  </si>
+  <si>
+    <t>Labo Schémas SG21</t>
+  </si>
+  <si>
     <t>Cours-Introdution à la haute tension</t>
   </si>
   <si>
+    <t>TP-Schémas électriques-SG11</t>
+  </si>
+  <si>
+    <t>Labo Schémas SG11</t>
+  </si>
+  <si>
+    <t>Salle de TP Systèmes Asservis SG21</t>
+  </si>
+  <si>
     <t>Cours-Schémas électriques</t>
   </si>
   <si>
@@ -2867,22 +2939,22 @@
     <t>TD-Modélisation des Réseaux électriques-G1</t>
   </si>
   <si>
-    <t>HADJERI Samir</t>
-  </si>
-  <si>
-    <t>TP-Réseaux électriques-SG12/SG22/SG32</t>
-  </si>
-  <si>
-    <t>TP-Schémas électriques-SG11/SG21/SG31</t>
-  </si>
-  <si>
-    <t>Labo Schémas</t>
-  </si>
-  <si>
-    <t>TP-Réseaux électriques-SG11/SG21/SG31</t>
-  </si>
-  <si>
-    <t>TP-Schémas électriques-SG12/SG22/SG32</t>
+    <t>TP-Électronique de puissance-SG21</t>
+  </si>
+  <si>
+    <t>TP-Schémas électriques-SG22</t>
+  </si>
+  <si>
+    <t>Labo Schémas SG22</t>
+  </si>
+  <si>
+    <t>TP-Électronique de puissance-SG11</t>
+  </si>
+  <si>
+    <t>Labo Mesures N°10 département ELN SG11</t>
+  </si>
+  <si>
+    <t>Salle de TP Systèmes Asservis SG22</t>
   </si>
   <si>
     <t>Cours-Électronique de puissance</t>
@@ -2891,37 +2963,43 @@
     <t>Cours-Modélisation des Réseaux électriques</t>
   </si>
   <si>
-    <t>TP-Életronique de puissance-SG12/SG22/SG32</t>
-  </si>
-  <si>
-    <t>Labo ELN-P G2</t>
-  </si>
-  <si>
     <t>TD-Modélisation des Réseaux électriques-G3</t>
   </si>
   <si>
-    <t>TP-Capteurs-SG11/SG21/SG31</t>
-  </si>
-  <si>
-    <t>Labo Mesures N°10 département ELN</t>
-  </si>
-  <si>
-    <t>TP-Système Asservis-SG12/SG22/SG32</t>
-  </si>
-  <si>
-    <t>TP-Capteurs-SG12/SG22/SG32</t>
-  </si>
-  <si>
-    <t>TP-Système Asservis-SG11/SG21/SG31</t>
-  </si>
-  <si>
-    <t>TP-Életronique de puissance-SG11/SG21/SG31</t>
-  </si>
-  <si>
-    <t>Labo ELN-P G1</t>
+    <t>TP-Électronique de puissance-SG22</t>
+  </si>
+  <si>
+    <t>TP-Capteurs-SG31</t>
+  </si>
+  <si>
+    <t>Labo Mesures N°10 département ELN SG31</t>
+  </si>
+  <si>
+    <t>TP-Schémas électriques-SG12</t>
+  </si>
+  <si>
+    <t>Labo Schémas SG12</t>
+  </si>
+  <si>
+    <t>TP-Électronique de puissance-SG12</t>
+  </si>
+  <si>
+    <t>TP-Schémas électriques-SG31</t>
+  </si>
+  <si>
+    <t>Labo Schémas SG31</t>
   </si>
   <si>
     <t>TD-Modélisation des Réseaux électriques-G2</t>
+  </si>
+  <si>
+    <t>TP-Réseaux électriques-SG31</t>
+  </si>
+  <si>
+    <t>Labo Réseaux SG31</t>
+  </si>
+  <si>
+    <t>Salle de TP Systèmes Asservis SG11</t>
   </si>
 </sst>
 </file>
@@ -3890,11 +3968,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G686"/>
+  <dimension ref="A1:G706"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
-  <cols>
-    <col min="1" max="1" width="80.5714285714286" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
@@ -18414,19 +18489,19 @@
         <v>936</v>
       </c>
       <c r="B632" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C632" t="s">
-        <v>161</v>
+        <v>484</v>
       </c>
       <c r="D632" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="E632" t="s">
         <v>11</v>
       </c>
       <c r="F632" t="s">
-        <v>39</v>
+        <v>937</v>
       </c>
       <c r="G632" t="s">
         <v>935</v>
@@ -18434,22 +18509,22 @@
     </row>
     <row r="633" spans="1:7">
       <c r="A633" t="s">
-        <v>548</v>
+        <v>938</v>
       </c>
       <c r="B633" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C633" t="s">
-        <v>161</v>
+        <v>55</v>
       </c>
       <c r="D633" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E633" t="s">
         <v>11</v>
       </c>
       <c r="F633" t="s">
-        <v>39</v>
+        <v>939</v>
       </c>
       <c r="G633" t="s">
         <v>935</v>
@@ -18457,22 +18532,22 @@
     </row>
     <row r="634" spans="1:7">
       <c r="A634" t="s">
-        <v>543</v>
+        <v>940</v>
       </c>
       <c r="B634" t="s">
         <v>19</v>
       </c>
       <c r="C634" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="D634" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E634" t="s">
         <v>11</v>
       </c>
       <c r="F634" t="s">
-        <v>304</v>
+        <v>39</v>
       </c>
       <c r="G634" t="s">
         <v>935</v>
@@ -18480,22 +18555,22 @@
     </row>
     <row r="635" spans="1:7">
       <c r="A635" t="s">
-        <v>937</v>
+        <v>548</v>
       </c>
       <c r="B635" t="s">
         <v>30</v>
       </c>
       <c r="C635" t="s">
-        <v>319</v>
+        <v>161</v>
       </c>
       <c r="D635" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E635" t="s">
         <v>11</v>
       </c>
       <c r="F635" t="s">
-        <v>232</v>
+        <v>39</v>
       </c>
       <c r="G635" t="s">
         <v>935</v>
@@ -18503,22 +18578,22 @@
     </row>
     <row r="636" spans="1:7">
       <c r="A636" t="s">
-        <v>938</v>
+        <v>538</v>
       </c>
       <c r="B636" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C636" t="s">
-        <v>204</v>
+        <v>941</v>
       </c>
       <c r="D636" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E636" t="s">
         <v>11</v>
       </c>
       <c r="F636" t="s">
-        <v>304</v>
+        <v>539</v>
       </c>
       <c r="G636" t="s">
         <v>935</v>
@@ -18526,22 +18601,22 @@
     </row>
     <row r="637" spans="1:7">
       <c r="A637" t="s">
-        <v>551</v>
+        <v>942</v>
       </c>
       <c r="B637" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C637" t="s">
-        <v>161</v>
+        <v>55</v>
       </c>
       <c r="D637" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E637" t="s">
         <v>11</v>
       </c>
       <c r="F637" t="s">
-        <v>232</v>
+        <v>943</v>
       </c>
       <c r="G637" t="s">
         <v>935</v>
@@ -18549,22 +18624,22 @@
     </row>
     <row r="638" spans="1:7">
       <c r="A638" t="s">
-        <v>939</v>
+        <v>543</v>
       </c>
       <c r="B638" t="s">
-        <v>940</v>
+        <v>19</v>
       </c>
       <c r="C638" t="s">
-        <v>547</v>
+        <v>204</v>
       </c>
       <c r="D638" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="E638" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F638" t="s">
-        <v>23</v>
+        <v>304</v>
       </c>
       <c r="G638" t="s">
         <v>935</v>
@@ -18572,7 +18647,7 @@
     </row>
     <row r="639" spans="1:7">
       <c r="A639" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B639" t="s">
         <v>30</v>
@@ -18581,10 +18656,10 @@
         <v>319</v>
       </c>
       <c r="D639" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E639" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F639" t="s">
         <v>232</v>
@@ -18595,7 +18670,7 @@
     </row>
     <row r="640" spans="1:7">
       <c r="A640" t="s">
-        <v>549</v>
+        <v>945</v>
       </c>
       <c r="B640" t="s">
         <v>30</v>
@@ -18604,10 +18679,10 @@
         <v>204</v>
       </c>
       <c r="D640" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E640" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F640" t="s">
         <v>304</v>
@@ -18618,22 +18693,22 @@
     </row>
     <row r="641" spans="1:7">
       <c r="A641" t="s">
-        <v>942</v>
+        <v>551</v>
       </c>
       <c r="B641" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C641" t="s">
-        <v>727</v>
+        <v>161</v>
       </c>
       <c r="D641" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E641" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F641" t="s">
-        <v>304</v>
+        <v>232</v>
       </c>
       <c r="G641" t="s">
         <v>935</v>
@@ -18641,22 +18716,22 @@
     </row>
     <row r="642" spans="1:7">
       <c r="A642" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="B642" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C642" t="s">
-        <v>529</v>
+        <v>941</v>
       </c>
       <c r="D642" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="E642" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F642" t="s">
-        <v>304</v>
+        <v>947</v>
       </c>
       <c r="G642" t="s">
         <v>935</v>
@@ -18664,22 +18739,22 @@
     </row>
     <row r="643" spans="1:7">
       <c r="A643" t="s">
-        <v>554</v>
+        <v>582</v>
       </c>
       <c r="B643" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C643" t="s">
-        <v>143</v>
+        <v>55</v>
       </c>
       <c r="D643" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E643" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F643" t="s">
-        <v>129</v>
+        <v>948</v>
       </c>
       <c r="G643" t="s">
         <v>935</v>
@@ -18687,22 +18762,22 @@
     </row>
     <row r="644" spans="1:7">
       <c r="A644" t="s">
-        <v>944</v>
+        <v>556</v>
       </c>
       <c r="B644" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C644" t="s">
-        <v>161</v>
+        <v>484</v>
       </c>
       <c r="D644" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="E644" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F644" t="s">
-        <v>29</v>
+        <v>949</v>
       </c>
       <c r="G644" t="s">
         <v>935</v>
@@ -18710,22 +18785,22 @@
     </row>
     <row r="645" spans="1:7">
       <c r="A645" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="B645" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C645" t="s">
-        <v>946</v>
+        <v>529</v>
       </c>
       <c r="D645" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="E645" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F645" t="s">
-        <v>304</v>
+        <v>951</v>
       </c>
       <c r="G645" t="s">
         <v>935</v>
@@ -18733,22 +18808,22 @@
     </row>
     <row r="646" spans="1:7">
       <c r="A646" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="B646" t="s">
         <v>8</v>
       </c>
       <c r="C646" t="s">
-        <v>946</v>
+        <v>171</v>
       </c>
       <c r="D646" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E646" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F646" t="s">
-        <v>83</v>
+        <v>953</v>
       </c>
       <c r="G646" t="s">
         <v>935</v>
@@ -18756,22 +18831,22 @@
     </row>
     <row r="647" spans="1:7">
       <c r="A647" t="s">
-        <v>948</v>
+        <v>578</v>
       </c>
       <c r="B647" t="s">
         <v>8</v>
       </c>
       <c r="C647" t="s">
-        <v>529</v>
+        <v>941</v>
       </c>
       <c r="D647" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E647" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F647" t="s">
-        <v>949</v>
+        <v>579</v>
       </c>
       <c r="G647" t="s">
         <v>935</v>
@@ -18779,22 +18854,22 @@
     </row>
     <row r="648" spans="1:7">
       <c r="A648" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="B648" t="s">
-        <v>8</v>
+        <v>955</v>
       </c>
       <c r="C648" t="s">
-        <v>946</v>
+        <v>547</v>
       </c>
       <c r="D648" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E648" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F648" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="G648" t="s">
         <v>935</v>
@@ -18802,22 +18877,22 @@
     </row>
     <row r="649" spans="1:7">
       <c r="A649" t="s">
-        <v>951</v>
+        <v>564</v>
       </c>
       <c r="B649" t="s">
         <v>8</v>
       </c>
       <c r="C649" t="s">
-        <v>529</v>
+        <v>484</v>
       </c>
       <c r="D649" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E649" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F649" t="s">
-        <v>949</v>
+        <v>956</v>
       </c>
       <c r="G649" t="s">
         <v>935</v>
@@ -18825,22 +18900,22 @@
     </row>
     <row r="650" spans="1:7">
       <c r="A650" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="B650" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C650" t="s">
-        <v>319</v>
+        <v>171</v>
       </c>
       <c r="D650" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E650" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F650" t="s">
-        <v>304</v>
+        <v>958</v>
       </c>
       <c r="G650" t="s">
         <v>935</v>
@@ -18848,22 +18923,22 @@
     </row>
     <row r="651" spans="1:7">
       <c r="A651" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="B651" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C651" t="s">
-        <v>946</v>
+        <v>319</v>
       </c>
       <c r="D651" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E651" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="F651" t="s">
-        <v>304</v>
+        <v>232</v>
       </c>
       <c r="G651" t="s">
         <v>935</v>
@@ -18871,22 +18946,22 @@
     </row>
     <row r="652" spans="1:7">
       <c r="A652" t="s">
-        <v>954</v>
+        <v>549</v>
       </c>
       <c r="B652" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C652" t="s">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="D652" t="s">
         <v>46</v>
       </c>
       <c r="E652" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F652" t="s">
-        <v>955</v>
+        <v>304</v>
       </c>
       <c r="G652" t="s">
         <v>935</v>
@@ -18894,22 +18969,22 @@
     </row>
     <row r="653" spans="1:7">
       <c r="A653" t="s">
-        <v>956</v>
+        <v>534</v>
       </c>
       <c r="B653" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C653" t="s">
-        <v>946</v>
+        <v>484</v>
       </c>
       <c r="D653" t="s">
         <v>46</v>
       </c>
       <c r="E653" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F653" t="s">
-        <v>232</v>
+        <v>960</v>
       </c>
       <c r="G653" t="s">
         <v>935</v>
@@ -18917,22 +18992,22 @@
     </row>
     <row r="654" spans="1:7">
       <c r="A654" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="B654" t="s">
         <v>8</v>
       </c>
       <c r="C654" t="s">
-        <v>484</v>
+        <v>529</v>
       </c>
       <c r="D654" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="E654" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F654" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="G654" t="s">
         <v>935</v>
@@ -18940,22 +19015,22 @@
     </row>
     <row r="655" spans="1:7">
       <c r="A655" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="B655" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C655" t="s">
-        <v>55</v>
+        <v>727</v>
       </c>
       <c r="D655" t="s">
         <v>10</v>
       </c>
       <c r="E655" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F655" t="s">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="G655" t="s">
         <v>935</v>
@@ -18963,22 +19038,22 @@
     </row>
     <row r="656" spans="1:7">
       <c r="A656" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="B656" t="s">
         <v>8</v>
       </c>
       <c r="C656" t="s">
-        <v>484</v>
+        <v>529</v>
       </c>
       <c r="D656" t="s">
         <v>14</v>
       </c>
       <c r="E656" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F656" t="s">
-        <v>958</v>
+        <v>965</v>
       </c>
       <c r="G656" t="s">
         <v>935</v>
@@ -18986,7 +19061,7 @@
     </row>
     <row r="657" spans="1:7">
       <c r="A657" t="s">
-        <v>961</v>
+        <v>570</v>
       </c>
       <c r="B657" t="s">
         <v>8</v>
@@ -18998,10 +19073,10 @@
         <v>14</v>
       </c>
       <c r="E657" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F657" t="s">
-        <v>83</v>
+        <v>966</v>
       </c>
       <c r="G657" t="s">
         <v>935</v>
@@ -19009,19 +19084,19 @@
     </row>
     <row r="658" spans="1:7">
       <c r="A658" t="s">
-        <v>953</v>
+        <v>967</v>
       </c>
       <c r="B658" t="s">
         <v>19</v>
       </c>
       <c r="C658" t="s">
-        <v>946</v>
+        <v>529</v>
       </c>
       <c r="D658" t="s">
         <v>21</v>
       </c>
       <c r="E658" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F658" t="s">
         <v>304</v>
@@ -19032,22 +19107,22 @@
     </row>
     <row r="659" spans="1:7">
       <c r="A659" t="s">
-        <v>962</v>
+        <v>554</v>
       </c>
       <c r="B659" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C659" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="D659" t="s">
         <v>17</v>
       </c>
       <c r="E659" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F659" t="s">
-        <v>963</v>
+        <v>129</v>
       </c>
       <c r="G659" t="s">
         <v>935</v>
@@ -19055,22 +19130,22 @@
     </row>
     <row r="660" spans="1:7">
       <c r="A660" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="B660" t="s">
         <v>30</v>
       </c>
       <c r="C660" t="s">
-        <v>946</v>
+        <v>161</v>
       </c>
       <c r="D660" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E660" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="F660" t="s">
-        <v>232</v>
+        <v>29</v>
       </c>
       <c r="G660" t="s">
         <v>935</v>
@@ -19078,462 +19153,462 @@
     </row>
     <row r="661" spans="1:7">
       <c r="A661" t="s">
-        <v>55</v>
+        <v>969</v>
       </c>
       <c r="B661" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C661" t="s">
-        <v>55</v>
+        <v>941</v>
       </c>
       <c r="D661" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E661" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F661" t="s">
-        <v>55</v>
+        <v>304</v>
       </c>
       <c r="G661" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="662" spans="1:7">
       <c r="A662" t="s">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="B662" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="C662" t="s">
-        <v>55</v>
+        <v>171</v>
       </c>
       <c r="D662" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E662" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F662" t="s">
-        <v>55</v>
+        <v>537</v>
       </c>
       <c r="G662" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="663" spans="1:7">
       <c r="A663" t="s">
-        <v>55</v>
+        <v>971</v>
       </c>
       <c r="B663" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="C663" t="s">
-        <v>55</v>
+        <v>529</v>
       </c>
       <c r="D663" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E663" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F663" t="s">
-        <v>55</v>
+        <v>972</v>
       </c>
       <c r="G663" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="664" spans="1:7">
       <c r="A664" t="s">
-        <v>55</v>
+        <v>973</v>
       </c>
       <c r="B664" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="C664" t="s">
-        <v>55</v>
+        <v>171</v>
       </c>
       <c r="D664" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="E664" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F664" t="s">
-        <v>55</v>
+        <v>567</v>
       </c>
       <c r="G664" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="665" spans="1:7">
       <c r="A665" t="s">
-        <v>55</v>
+        <v>568</v>
       </c>
       <c r="B665" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="C665" t="s">
-        <v>55</v>
+        <v>941</v>
       </c>
       <c r="D665" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="E665" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F665" t="s">
-        <v>55</v>
+        <v>569</v>
       </c>
       <c r="G665" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="666" spans="1:7">
       <c r="A666" t="s">
-        <v>55</v>
+        <v>576</v>
       </c>
       <c r="B666" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="C666" t="s">
-        <v>55</v>
+        <v>484</v>
       </c>
       <c r="D666" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E666" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F666" t="s">
-        <v>55</v>
+        <v>974</v>
       </c>
       <c r="G666" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="667" spans="1:7">
       <c r="A667" t="s">
-        <v>55</v>
+        <v>562</v>
       </c>
       <c r="B667" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="C667" t="s">
         <v>55</v>
       </c>
       <c r="D667" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E667" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F667" t="s">
-        <v>55</v>
+        <v>975</v>
       </c>
       <c r="G667" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="668" spans="1:7">
       <c r="A668" t="s">
-        <v>55</v>
+        <v>976</v>
       </c>
       <c r="B668" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="C668" t="s">
-        <v>55</v>
+        <v>319</v>
       </c>
       <c r="D668" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E668" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F668" t="s">
-        <v>55</v>
+        <v>304</v>
       </c>
       <c r="G668" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="669" spans="1:7">
       <c r="A669" t="s">
-        <v>55</v>
+        <v>977</v>
       </c>
       <c r="B669" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="C669" t="s">
-        <v>55</v>
+        <v>941</v>
       </c>
       <c r="D669" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="E669" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F669" t="s">
-        <v>55</v>
+        <v>304</v>
       </c>
       <c r="G669" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="670" spans="1:7">
       <c r="A670" t="s">
-        <v>55</v>
+        <v>978</v>
       </c>
       <c r="B670" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C670" t="s">
-        <v>55</v>
+        <v>941</v>
       </c>
       <c r="D670" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E670" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F670" t="s">
-        <v>55</v>
+        <v>232</v>
       </c>
       <c r="G670" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="671" spans="1:7">
       <c r="A671" t="s">
-        <v>55</v>
+        <v>979</v>
       </c>
       <c r="B671" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="C671" t="s">
-        <v>55</v>
+        <v>171</v>
       </c>
       <c r="D671" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E671" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F671" t="s">
-        <v>55</v>
+        <v>525</v>
       </c>
       <c r="G671" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="672" spans="1:7">
       <c r="A672" t="s">
-        <v>55</v>
+        <v>526</v>
       </c>
       <c r="B672" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="C672" t="s">
-        <v>55</v>
+        <v>941</v>
       </c>
       <c r="D672" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E672" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F672" t="s">
-        <v>55</v>
+        <v>527</v>
       </c>
       <c r="G672" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="673" spans="1:7">
       <c r="A673" t="s">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="B673" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="C673" t="s">
-        <v>55</v>
+        <v>484</v>
       </c>
       <c r="D673" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="E673" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F673" t="s">
-        <v>55</v>
+        <v>981</v>
       </c>
       <c r="G673" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="674" spans="1:7">
       <c r="A674" t="s">
-        <v>55</v>
+        <v>982</v>
       </c>
       <c r="B674" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="C674" t="s">
-        <v>55</v>
+        <v>529</v>
       </c>
       <c r="D674" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="E674" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F674" t="s">
-        <v>55</v>
+        <v>983</v>
       </c>
       <c r="G674" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="675" spans="1:7">
       <c r="A675" t="s">
-        <v>55</v>
+        <v>984</v>
       </c>
       <c r="B675" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="C675" t="s">
-        <v>55</v>
+        <v>171</v>
       </c>
       <c r="D675" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E675" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F675" t="s">
-        <v>55</v>
+        <v>559</v>
       </c>
       <c r="G675" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="676" spans="1:7">
       <c r="A676" t="s">
-        <v>55</v>
+        <v>985</v>
       </c>
       <c r="B676" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="C676" t="s">
-        <v>55</v>
+        <v>529</v>
       </c>
       <c r="D676" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E676" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F676" t="s">
-        <v>55</v>
+        <v>986</v>
       </c>
       <c r="G676" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="677" spans="1:7">
       <c r="A677" t="s">
-        <v>55</v>
+        <v>977</v>
       </c>
       <c r="B677" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="C677" t="s">
-        <v>55</v>
+        <v>941</v>
       </c>
       <c r="D677" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E677" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F677" t="s">
-        <v>55</v>
+        <v>304</v>
       </c>
       <c r="G677" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="678" spans="1:7">
       <c r="A678" t="s">
-        <v>55</v>
+        <v>987</v>
       </c>
       <c r="B678" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C678" t="s">
-        <v>55</v>
+        <v>941</v>
       </c>
       <c r="D678" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="E678" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F678" t="s">
-        <v>55</v>
+        <v>232</v>
       </c>
       <c r="G678" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="679" spans="1:7">
       <c r="A679" t="s">
-        <v>55</v>
+        <v>988</v>
       </c>
       <c r="B679" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="C679" t="s">
-        <v>55</v>
+        <v>941</v>
       </c>
       <c r="D679" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="E679" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F679" t="s">
-        <v>55</v>
+        <v>989</v>
       </c>
       <c r="G679" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="680" spans="1:7">
       <c r="A680" t="s">
-        <v>55</v>
+        <v>531</v>
       </c>
       <c r="B680" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="C680" t="s">
         <v>55</v>
       </c>
       <c r="D680" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="E680" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F680" t="s">
-        <v>55</v>
+        <v>990</v>
       </c>
       <c r="G680" t="s">
-        <v>55</v>
+        <v>935</v>
       </c>
     </row>
     <row r="681" spans="1:7">
@@ -19636,7 +19711,7 @@
         <v>55</v>
       </c>
       <c r="C685" t="s">
-        <v>335</v>
+        <v>55</v>
       </c>
       <c r="D685" t="s">
         <v>55</v>
@@ -19659,18 +19734,478 @@
         <v>55</v>
       </c>
       <c r="C686" t="s">
+        <v>55</v>
+      </c>
+      <c r="D686" t="s">
+        <v>55</v>
+      </c>
+      <c r="E686" t="s">
+        <v>55</v>
+      </c>
+      <c r="F686" t="s">
+        <v>55</v>
+      </c>
+      <c r="G686" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="687" spans="1:7">
+      <c r="A687" t="s">
+        <v>55</v>
+      </c>
+      <c r="B687" t="s">
+        <v>55</v>
+      </c>
+      <c r="C687" t="s">
+        <v>55</v>
+      </c>
+      <c r="D687" t="s">
+        <v>55</v>
+      </c>
+      <c r="E687" t="s">
+        <v>55</v>
+      </c>
+      <c r="F687" t="s">
+        <v>55</v>
+      </c>
+      <c r="G687" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="688" spans="1:7">
+      <c r="A688" t="s">
+        <v>55</v>
+      </c>
+      <c r="B688" t="s">
+        <v>55</v>
+      </c>
+      <c r="C688" t="s">
+        <v>55</v>
+      </c>
+      <c r="D688" t="s">
+        <v>55</v>
+      </c>
+      <c r="E688" t="s">
+        <v>55</v>
+      </c>
+      <c r="F688" t="s">
+        <v>55</v>
+      </c>
+      <c r="G688" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="689" spans="1:7">
+      <c r="A689" t="s">
+        <v>55</v>
+      </c>
+      <c r="B689" t="s">
+        <v>55</v>
+      </c>
+      <c r="C689" t="s">
+        <v>55</v>
+      </c>
+      <c r="D689" t="s">
+        <v>55</v>
+      </c>
+      <c r="E689" t="s">
+        <v>55</v>
+      </c>
+      <c r="F689" t="s">
+        <v>55</v>
+      </c>
+      <c r="G689" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="690" spans="1:7">
+      <c r="A690" t="s">
+        <v>55</v>
+      </c>
+      <c r="B690" t="s">
+        <v>55</v>
+      </c>
+      <c r="C690" t="s">
+        <v>55</v>
+      </c>
+      <c r="D690" t="s">
+        <v>55</v>
+      </c>
+      <c r="E690" t="s">
+        <v>55</v>
+      </c>
+      <c r="F690" t="s">
+        <v>55</v>
+      </c>
+      <c r="G690" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="691" spans="1:7">
+      <c r="A691" t="s">
+        <v>55</v>
+      </c>
+      <c r="B691" t="s">
+        <v>55</v>
+      </c>
+      <c r="C691" t="s">
+        <v>55</v>
+      </c>
+      <c r="D691" t="s">
+        <v>55</v>
+      </c>
+      <c r="E691" t="s">
+        <v>55</v>
+      </c>
+      <c r="F691" t="s">
+        <v>55</v>
+      </c>
+      <c r="G691" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="692" spans="1:7">
+      <c r="A692" t="s">
+        <v>55</v>
+      </c>
+      <c r="B692" t="s">
+        <v>55</v>
+      </c>
+      <c r="C692" t="s">
+        <v>55</v>
+      </c>
+      <c r="D692" t="s">
+        <v>55</v>
+      </c>
+      <c r="E692" t="s">
+        <v>55</v>
+      </c>
+      <c r="F692" t="s">
+        <v>55</v>
+      </c>
+      <c r="G692" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="693" spans="1:7">
+      <c r="A693" t="s">
+        <v>55</v>
+      </c>
+      <c r="B693" t="s">
+        <v>55</v>
+      </c>
+      <c r="C693" t="s">
+        <v>55</v>
+      </c>
+      <c r="D693" t="s">
+        <v>55</v>
+      </c>
+      <c r="E693" t="s">
+        <v>55</v>
+      </c>
+      <c r="F693" t="s">
+        <v>55</v>
+      </c>
+      <c r="G693" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="694" spans="1:7">
+      <c r="A694" t="s">
+        <v>55</v>
+      </c>
+      <c r="B694" t="s">
+        <v>55</v>
+      </c>
+      <c r="C694" t="s">
+        <v>55</v>
+      </c>
+      <c r="D694" t="s">
+        <v>55</v>
+      </c>
+      <c r="E694" t="s">
+        <v>55</v>
+      </c>
+      <c r="F694" t="s">
+        <v>55</v>
+      </c>
+      <c r="G694" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="695" spans="1:7">
+      <c r="A695" t="s">
+        <v>55</v>
+      </c>
+      <c r="B695" t="s">
+        <v>55</v>
+      </c>
+      <c r="C695" t="s">
+        <v>55</v>
+      </c>
+      <c r="D695" t="s">
+        <v>55</v>
+      </c>
+      <c r="E695" t="s">
+        <v>55</v>
+      </c>
+      <c r="F695" t="s">
+        <v>55</v>
+      </c>
+      <c r="G695" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="696" spans="1:7">
+      <c r="A696" t="s">
+        <v>55</v>
+      </c>
+      <c r="B696" t="s">
+        <v>55</v>
+      </c>
+      <c r="C696" t="s">
+        <v>55</v>
+      </c>
+      <c r="D696" t="s">
+        <v>55</v>
+      </c>
+      <c r="E696" t="s">
+        <v>55</v>
+      </c>
+      <c r="F696" t="s">
+        <v>55</v>
+      </c>
+      <c r="G696" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="697" spans="1:7">
+      <c r="A697" t="s">
+        <v>55</v>
+      </c>
+      <c r="B697" t="s">
+        <v>55</v>
+      </c>
+      <c r="C697" t="s">
+        <v>55</v>
+      </c>
+      <c r="D697" t="s">
+        <v>55</v>
+      </c>
+      <c r="E697" t="s">
+        <v>55</v>
+      </c>
+      <c r="F697" t="s">
+        <v>55</v>
+      </c>
+      <c r="G697" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="698" spans="1:7">
+      <c r="A698" t="s">
+        <v>55</v>
+      </c>
+      <c r="B698" t="s">
+        <v>55</v>
+      </c>
+      <c r="C698" t="s">
+        <v>55</v>
+      </c>
+      <c r="D698" t="s">
+        <v>55</v>
+      </c>
+      <c r="E698" t="s">
+        <v>55</v>
+      </c>
+      <c r="F698" t="s">
+        <v>55</v>
+      </c>
+      <c r="G698" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="699" spans="1:7">
+      <c r="A699" t="s">
+        <v>55</v>
+      </c>
+      <c r="B699" t="s">
+        <v>55</v>
+      </c>
+      <c r="C699" t="s">
+        <v>55</v>
+      </c>
+      <c r="D699" t="s">
+        <v>55</v>
+      </c>
+      <c r="E699" t="s">
+        <v>55</v>
+      </c>
+      <c r="F699" t="s">
+        <v>55</v>
+      </c>
+      <c r="G699" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="700" spans="1:7">
+      <c r="A700" t="s">
+        <v>55</v>
+      </c>
+      <c r="B700" t="s">
+        <v>55</v>
+      </c>
+      <c r="C700" t="s">
+        <v>55</v>
+      </c>
+      <c r="D700" t="s">
+        <v>55</v>
+      </c>
+      <c r="E700" t="s">
+        <v>55</v>
+      </c>
+      <c r="F700" t="s">
+        <v>55</v>
+      </c>
+      <c r="G700" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="701" spans="1:7">
+      <c r="A701" t="s">
+        <v>55</v>
+      </c>
+      <c r="B701" t="s">
+        <v>55</v>
+      </c>
+      <c r="C701" t="s">
+        <v>55</v>
+      </c>
+      <c r="D701" t="s">
+        <v>55</v>
+      </c>
+      <c r="E701" t="s">
+        <v>55</v>
+      </c>
+      <c r="F701" t="s">
+        <v>55</v>
+      </c>
+      <c r="G701" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="702" spans="1:7">
+      <c r="A702" t="s">
+        <v>55</v>
+      </c>
+      <c r="B702" t="s">
+        <v>55</v>
+      </c>
+      <c r="C702" t="s">
+        <v>55</v>
+      </c>
+      <c r="D702" t="s">
+        <v>55</v>
+      </c>
+      <c r="E702" t="s">
+        <v>55</v>
+      </c>
+      <c r="F702" t="s">
+        <v>55</v>
+      </c>
+      <c r="G702" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="703" spans="1:7">
+      <c r="A703" t="s">
+        <v>55</v>
+      </c>
+      <c r="B703" t="s">
+        <v>55</v>
+      </c>
+      <c r="C703" t="s">
+        <v>55</v>
+      </c>
+      <c r="D703" t="s">
+        <v>55</v>
+      </c>
+      <c r="E703" t="s">
+        <v>55</v>
+      </c>
+      <c r="F703" t="s">
+        <v>55</v>
+      </c>
+      <c r="G703" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="704" spans="1:7">
+      <c r="A704" t="s">
+        <v>55</v>
+      </c>
+      <c r="B704" t="s">
+        <v>55</v>
+      </c>
+      <c r="C704" t="s">
+        <v>55</v>
+      </c>
+      <c r="D704" t="s">
+        <v>55</v>
+      </c>
+      <c r="E704" t="s">
+        <v>55</v>
+      </c>
+      <c r="F704" t="s">
+        <v>55</v>
+      </c>
+      <c r="G704" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="705" spans="1:7">
+      <c r="A705" t="s">
+        <v>55</v>
+      </c>
+      <c r="B705" t="s">
+        <v>55</v>
+      </c>
+      <c r="C705" t="s">
+        <v>335</v>
+      </c>
+      <c r="D705" t="s">
+        <v>55</v>
+      </c>
+      <c r="E705" t="s">
+        <v>55</v>
+      </c>
+      <c r="F705" t="s">
+        <v>55</v>
+      </c>
+      <c r="G705" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="706" spans="1:7">
+      <c r="A706" t="s">
+        <v>55</v>
+      </c>
+      <c r="B706" t="s">
+        <v>55</v>
+      </c>
+      <c r="C706" t="s">
         <v>180</v>
       </c>
-      <c r="D686" t="s">
-        <v>55</v>
-      </c>
-      <c r="E686" t="s">
-        <v>55</v>
-      </c>
-      <c r="F686" t="s">
-        <v>55</v>
-      </c>
-      <c r="G686" t="s">
+      <c r="D706" t="s">
+        <v>55</v>
+      </c>
+      <c r="E706" t="s">
+        <v>55</v>
+      </c>
+      <c r="F706" t="s">
+        <v>55</v>
+      </c>
+      <c r="G706" t="s">
         <v>55</v>
       </c>
     </row>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4767" uniqueCount="996">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4781" uniqueCount="994">
   <si>
     <t>Enseignements</t>
   </si>
@@ -2306,6 +2306,15 @@
     <t>Cours-THT-M2MCIL</t>
   </si>
   <si>
+    <t>TP-Techniques de protection des réseaux électriques-SG11</t>
+  </si>
+  <si>
+    <t>TP-TPRE-M2MCIL</t>
+  </si>
+  <si>
+    <t>Labo A13</t>
+  </si>
+  <si>
     <t>TP-Systèmes d’éclairage LED :  mesures et performances-SG12</t>
   </si>
   <si>
@@ -2318,15 +2327,6 @@
     <t>TP-Techniques de protection des réseaux électriques-SG12</t>
   </si>
   <si>
-    <t>TP-TPRE-M2MCIL</t>
-  </si>
-  <si>
-    <t>13h - 15h30</t>
-  </si>
-  <si>
-    <t>Labo A13</t>
-  </si>
-  <si>
     <t>TP-Techniques de la Haute tension-SG11</t>
   </si>
   <si>
@@ -2340,12 +2340,6 @@
   </si>
   <si>
     <t>TP-Techniques de la Haute tension-SG12</t>
-  </si>
-  <si>
-    <t>TP-Techniques de protection des réseaux électriques-SG11</t>
-  </si>
-  <si>
-    <t>9h30 - 12h</t>
   </si>
   <si>
     <t>Cours-Identifiation et diagnostique des machines électriques</t>
@@ -3983,7 +3977,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G681"/>
+  <dimension ref="A1:G683"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -15770,10 +15764,10 @@
         <v>760</v>
       </c>
       <c r="C513" t="s">
-        <v>55</v>
+        <v>286</v>
       </c>
       <c r="D513" t="s">
-        <v>46</v>
+        <v>371</v>
       </c>
       <c r="E513" t="s">
         <v>63</v>
@@ -15787,22 +15781,22 @@
     </row>
     <row r="514" spans="1:7">
       <c r="A514" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B514" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="C514" t="s">
         <v>286</v>
       </c>
       <c r="D514" t="s">
-        <v>764</v>
+        <v>46</v>
       </c>
       <c r="E514" t="s">
         <v>63</v>
       </c>
       <c r="F514" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="G514" t="s">
         <v>739</v>
@@ -15810,22 +15804,22 @@
     </row>
     <row r="515" spans="1:7">
       <c r="A515" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="B515" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="C515" t="s">
-        <v>312</v>
+        <v>55</v>
       </c>
       <c r="D515" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="E515" t="s">
         <v>63</v>
       </c>
       <c r="F515" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="G515" t="s">
         <v>739</v>
@@ -15833,16 +15827,16 @@
     </row>
     <row r="516" spans="1:7">
       <c r="A516" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="B516" t="s">
         <v>760</v>
       </c>
       <c r="C516" t="s">
-        <v>55</v>
+        <v>286</v>
       </c>
       <c r="D516" t="s">
-        <v>14</v>
+        <v>391</v>
       </c>
       <c r="E516" t="s">
         <v>63</v>
@@ -15856,7 +15850,7 @@
     </row>
     <row r="517" spans="1:7">
       <c r="A517" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="B517" t="s">
         <v>767</v>
@@ -15865,7 +15859,7 @@
         <v>312</v>
       </c>
       <c r="D517" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E517" t="s">
         <v>63</v>
@@ -15879,22 +15873,22 @@
     </row>
     <row r="518" spans="1:7">
       <c r="A518" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="B518" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="C518" t="s">
         <v>286</v>
       </c>
       <c r="D518" t="s">
-        <v>772</v>
+        <v>10</v>
       </c>
       <c r="E518" t="s">
         <v>63</v>
       </c>
       <c r="F518" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="G518" t="s">
         <v>739</v>
@@ -15902,177 +15896,177 @@
     </row>
     <row r="519" spans="1:7">
       <c r="A519" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B519" t="s">
-        <v>774</v>
+        <v>763</v>
       </c>
       <c r="C519" t="s">
-        <v>775</v>
+        <v>55</v>
       </c>
       <c r="D519" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E519" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="F519" t="s">
-        <v>169</v>
+        <v>764</v>
       </c>
       <c r="G519" t="s">
-        <v>776</v>
+        <v>739</v>
       </c>
     </row>
     <row r="520" spans="1:7">
       <c r="A520" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="B520" t="s">
-        <v>778</v>
+        <v>767</v>
       </c>
       <c r="C520" t="s">
-        <v>603</v>
+        <v>312</v>
       </c>
       <c r="D520" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E520" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="F520" t="s">
-        <v>779</v>
+        <v>768</v>
       </c>
       <c r="G520" t="s">
-        <v>776</v>
+        <v>739</v>
       </c>
     </row>
     <row r="521" spans="1:7">
       <c r="A521" t="s">
-        <v>780</v>
+        <v>771</v>
       </c>
       <c r="B521" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
       <c r="C521" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D521" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E521" t="s">
         <v>11</v>
       </c>
       <c r="F521" t="s">
-        <v>782</v>
+        <v>169</v>
       </c>
       <c r="G521" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="522" spans="1:7">
       <c r="A522" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="B522" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="C522" t="s">
-        <v>775</v>
+        <v>603</v>
       </c>
       <c r="D522" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E522" t="s">
         <v>11</v>
       </c>
       <c r="F522" t="s">
-        <v>169</v>
+        <v>777</v>
       </c>
       <c r="G522" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="523" spans="1:7">
       <c r="A523" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="B523" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="C523" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D523" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="E523" t="s">
         <v>11</v>
       </c>
       <c r="F523" t="s">
-        <v>169</v>
+        <v>780</v>
       </c>
       <c r="G523" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="524" spans="1:7">
       <c r="A524" t="s">
-        <v>704</v>
+        <v>781</v>
       </c>
       <c r="B524" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="C524" t="s">
-        <v>312</v>
+        <v>773</v>
       </c>
       <c r="D524" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E524" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F524" t="s">
         <v>169</v>
       </c>
       <c r="G524" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="525" spans="1:7">
       <c r="A525" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B525" t="s">
-        <v>19</v>
+        <v>784</v>
       </c>
       <c r="C525" t="s">
-        <v>300</v>
+        <v>773</v>
       </c>
       <c r="D525" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="E525" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F525" t="s">
-        <v>23</v>
+        <v>169</v>
       </c>
       <c r="G525" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="526" spans="1:7">
       <c r="A526" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B526" t="s">
-        <v>19</v>
+        <v>785</v>
       </c>
       <c r="C526" t="s">
         <v>312</v>
       </c>
       <c r="D526" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E526" t="s">
         <v>22</v>
@@ -16081,90 +16075,90 @@
         <v>169</v>
       </c>
       <c r="G526" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="527" spans="1:7">
       <c r="A527" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="B527" t="s">
-        <v>790</v>
+        <v>19</v>
       </c>
       <c r="C527" t="s">
-        <v>532</v>
+        <v>300</v>
       </c>
       <c r="D527" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E527" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F527" t="s">
-        <v>791</v>
+        <v>23</v>
       </c>
       <c r="G527" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="528" spans="1:7">
       <c r="A528" t="s">
-        <v>792</v>
+        <v>706</v>
       </c>
       <c r="B528" t="s">
-        <v>793</v>
+        <v>19</v>
       </c>
       <c r="C528" t="s">
-        <v>239</v>
+        <v>312</v>
       </c>
       <c r="D528" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="E528" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F528" t="s">
         <v>169</v>
       </c>
       <c r="G528" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="529" spans="1:7">
       <c r="A529" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="B529" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="C529" t="s">
-        <v>239</v>
+        <v>532</v>
       </c>
       <c r="D529" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E529" t="s">
         <v>28</v>
       </c>
       <c r="F529" t="s">
-        <v>169</v>
+        <v>789</v>
       </c>
       <c r="G529" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="530" spans="1:7">
       <c r="A530" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="B530" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="C530" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D530" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="E530" t="s">
         <v>28</v>
@@ -16173,504 +16167,504 @@
         <v>169</v>
       </c>
       <c r="G530" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="531" spans="1:7">
       <c r="A531" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="B531" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="C531" t="s">
-        <v>800</v>
+        <v>239</v>
       </c>
       <c r="D531" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="E531" t="s">
         <v>28</v>
       </c>
       <c r="F531" t="s">
-        <v>791</v>
+        <v>169</v>
       </c>
       <c r="G531" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="532" spans="1:7">
       <c r="A532" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="B532" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="C532" t="s">
-        <v>800</v>
+        <v>246</v>
       </c>
       <c r="D532" t="s">
         <v>38</v>
       </c>
       <c r="E532" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="F532" t="s">
         <v>169</v>
       </c>
       <c r="G532" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="533" spans="1:7">
       <c r="A533" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="B533" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="C533" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="D533" t="s">
         <v>43</v>
       </c>
       <c r="E533" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="F533" t="s">
-        <v>169</v>
+        <v>789</v>
       </c>
       <c r="G533" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="534" spans="1:7">
       <c r="A534" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="B534" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="C534" t="s">
-        <v>239</v>
+        <v>798</v>
       </c>
       <c r="D534" t="s">
-        <v>111</v>
+        <v>38</v>
       </c>
       <c r="E534" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="F534" t="s">
-        <v>779</v>
+        <v>169</v>
       </c>
       <c r="G534" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="535" spans="1:7">
       <c r="A535" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="B535" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="C535" t="s">
-        <v>603</v>
+        <v>798</v>
       </c>
       <c r="D535" t="s">
         <v>43</v>
       </c>
       <c r="E535" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="F535" t="s">
         <v>169</v>
       </c>
       <c r="G535" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="536" spans="1:7">
       <c r="A536" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="B536" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="C536" t="s">
-        <v>312</v>
+        <v>239</v>
       </c>
       <c r="D536" t="s">
         <v>111</v>
       </c>
       <c r="E536" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="F536" t="s">
-        <v>811</v>
+        <v>777</v>
       </c>
       <c r="G536" t="s">
-        <v>812</v>
+        <v>774</v>
       </c>
     </row>
     <row r="537" spans="1:7">
       <c r="A537" t="s">
-        <v>284</v>
+        <v>805</v>
       </c>
       <c r="B537" t="s">
-        <v>19</v>
+        <v>806</v>
       </c>
       <c r="C537" t="s">
-        <v>286</v>
+        <v>603</v>
       </c>
       <c r="D537" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="E537" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="F537" t="s">
-        <v>39</v>
+        <v>169</v>
       </c>
       <c r="G537" t="s">
-        <v>812</v>
+        <v>774</v>
       </c>
     </row>
     <row r="538" spans="1:7">
       <c r="A538" t="s">
-        <v>746</v>
+        <v>807</v>
       </c>
       <c r="B538" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="C538" t="s">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="D538" t="s">
-        <v>43</v>
+        <v>111</v>
       </c>
       <c r="E538" t="s">
         <v>11</v>
       </c>
       <c r="F538" t="s">
-        <v>39</v>
+        <v>809</v>
       </c>
       <c r="G538" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="539" spans="1:7">
       <c r="A539" t="s">
-        <v>704</v>
+        <v>284</v>
       </c>
       <c r="B539" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C539" t="s">
-        <v>312</v>
+        <v>286</v>
       </c>
       <c r="D539" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="E539" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F539" t="s">
-        <v>814</v>
+        <v>39</v>
       </c>
       <c r="G539" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="540" spans="1:7">
       <c r="A540" t="s">
-        <v>705</v>
+        <v>746</v>
       </c>
       <c r="B540" t="s">
-        <v>19</v>
+        <v>811</v>
       </c>
       <c r="C540" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="D540" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="E540" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F540" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="G540" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="541" spans="1:7">
       <c r="A541" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B541" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C541" t="s">
         <v>312</v>
       </c>
       <c r="D541" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E541" t="s">
         <v>22</v>
       </c>
       <c r="F541" t="s">
-        <v>39</v>
+        <v>812</v>
       </c>
       <c r="G541" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="542" spans="1:7">
       <c r="A542" t="s">
-        <v>815</v>
+        <v>705</v>
       </c>
       <c r="B542" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C542" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D542" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E542" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F542" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="G542" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="543" spans="1:7">
       <c r="A543" t="s">
-        <v>816</v>
+        <v>706</v>
       </c>
       <c r="B543" t="s">
         <v>19</v>
       </c>
       <c r="C543" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="D543" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E543" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F543" t="s">
         <v>39</v>
       </c>
       <c r="G543" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="544" spans="1:7">
       <c r="A544" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="B544" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C544" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D544" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E544" t="s">
         <v>28</v>
       </c>
       <c r="F544" t="s">
-        <v>765</v>
+        <v>39</v>
       </c>
       <c r="G544" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="545" spans="1:7">
       <c r="A545" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="B545" t="s">
-        <v>819</v>
+        <v>19</v>
       </c>
       <c r="C545" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="D545" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="E545" t="s">
         <v>28</v>
       </c>
       <c r="F545" t="s">
-        <v>820</v>
+        <v>39</v>
       </c>
       <c r="G545" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="546" spans="1:7">
       <c r="A546" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="B546" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C546" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="D546" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="E546" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="F546" t="s">
-        <v>293</v>
+        <v>761</v>
       </c>
       <c r="G546" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="547" spans="1:7">
       <c r="A547" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="B547" t="s">
-        <v>30</v>
+        <v>817</v>
       </c>
       <c r="C547" t="s">
-        <v>316</v>
+        <v>286</v>
       </c>
       <c r="D547" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="E547" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="F547" t="s">
-        <v>39</v>
+        <v>818</v>
       </c>
       <c r="G547" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="548" spans="1:7">
       <c r="A548" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="B548" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C548" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="D548" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="E548" t="s">
         <v>47</v>
       </c>
       <c r="F548" t="s">
-        <v>39</v>
+        <v>293</v>
       </c>
       <c r="G548" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="549" spans="1:7">
       <c r="A549" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="B549" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C549" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="D549" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E549" t="s">
         <v>47</v>
       </c>
       <c r="F549" t="s">
-        <v>293</v>
+        <v>39</v>
       </c>
       <c r="G549" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="550" spans="1:7">
       <c r="A550" t="s">
-        <v>318</v>
+        <v>821</v>
       </c>
       <c r="B550" t="s">
-        <v>825</v>
+        <v>19</v>
       </c>
       <c r="C550" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D550" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E550" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="F550" t="s">
         <v>39</v>
       </c>
       <c r="G550" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="551" spans="1:7">
       <c r="A551" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="B551" t="s">
-        <v>827</v>
+        <v>19</v>
       </c>
       <c r="C551" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D551" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="E551" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="F551" t="s">
-        <v>39</v>
+        <v>293</v>
       </c>
       <c r="G551" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="552" spans="1:7">
       <c r="A552" t="s">
-        <v>828</v>
+        <v>318</v>
       </c>
       <c r="B552" t="s">
-        <v>30</v>
+        <v>823</v>
       </c>
       <c r="C552" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="D552" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E552" t="s">
         <v>63</v>
@@ -16679,110 +16673,110 @@
         <v>39</v>
       </c>
       <c r="G552" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="553" spans="1:7">
       <c r="A553" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="B553" t="s">
-        <v>30</v>
+        <v>825</v>
       </c>
       <c r="C553" t="s">
-        <v>830</v>
+        <v>296</v>
       </c>
       <c r="D553" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E553" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="F553" t="s">
-        <v>185</v>
+        <v>39</v>
       </c>
       <c r="G553" t="s">
-        <v>831</v>
+        <v>810</v>
       </c>
     </row>
     <row r="554" spans="1:7">
       <c r="A554" t="s">
-        <v>491</v>
+        <v>826</v>
       </c>
       <c r="B554" t="s">
-        <v>832</v>
+        <v>30</v>
       </c>
       <c r="C554" t="s">
-        <v>597</v>
+        <v>296</v>
       </c>
       <c r="D554" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E554" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="F554" t="s">
-        <v>833</v>
+        <v>39</v>
       </c>
       <c r="G554" t="s">
-        <v>831</v>
+        <v>810</v>
       </c>
     </row>
     <row r="555" spans="1:7">
       <c r="A555" t="s">
-        <v>499</v>
+        <v>827</v>
       </c>
       <c r="B555" t="s">
         <v>30</v>
       </c>
       <c r="C555" t="s">
-        <v>55</v>
+        <v>828</v>
       </c>
       <c r="D555" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E555" t="s">
         <v>11</v>
       </c>
       <c r="F555" t="s">
-        <v>68</v>
+        <v>185</v>
       </c>
       <c r="G555" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="556" spans="1:7">
       <c r="A556" t="s">
-        <v>834</v>
+        <v>491</v>
       </c>
       <c r="B556" t="s">
-        <v>30</v>
+        <v>830</v>
       </c>
       <c r="C556" t="s">
-        <v>835</v>
+        <v>597</v>
       </c>
       <c r="D556" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E556" t="s">
         <v>11</v>
       </c>
       <c r="F556" t="s">
-        <v>185</v>
+        <v>831</v>
       </c>
       <c r="G556" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="557" spans="1:7">
       <c r="A557" t="s">
-        <v>836</v>
+        <v>499</v>
       </c>
       <c r="B557" t="s">
         <v>30</v>
       </c>
       <c r="C557" t="s">
-        <v>517</v>
+        <v>55</v>
       </c>
       <c r="D557" t="s">
         <v>31</v>
@@ -16791,21 +16785,21 @@
         <v>11</v>
       </c>
       <c r="F557" t="s">
-        <v>216</v>
+        <v>68</v>
       </c>
       <c r="G557" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="558" spans="1:7">
       <c r="A558" t="s">
-        <v>497</v>
+        <v>832</v>
       </c>
       <c r="B558" t="s">
-        <v>832</v>
+        <v>30</v>
       </c>
       <c r="C558" t="s">
-        <v>597</v>
+        <v>833</v>
       </c>
       <c r="D558" t="s">
         <v>31</v>
@@ -16814,21 +16808,21 @@
         <v>11</v>
       </c>
       <c r="F558" t="s">
-        <v>837</v>
+        <v>185</v>
       </c>
       <c r="G558" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="559" spans="1:7">
       <c r="A559" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="B559" t="s">
-        <v>832</v>
+        <v>30</v>
       </c>
       <c r="C559" t="s">
-        <v>55</v>
+        <v>517</v>
       </c>
       <c r="D559" t="s">
         <v>31</v>
@@ -16837,208 +16831,208 @@
         <v>11</v>
       </c>
       <c r="F559" t="s">
-        <v>839</v>
+        <v>216</v>
       </c>
       <c r="G559" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="560" spans="1:7">
       <c r="A560" t="s">
-        <v>840</v>
+        <v>497</v>
       </c>
       <c r="B560" t="s">
-        <v>841</v>
+        <v>830</v>
       </c>
       <c r="C560" t="s">
-        <v>184</v>
+        <v>597</v>
       </c>
       <c r="D560" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E560" t="s">
         <v>11</v>
       </c>
       <c r="F560" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="G560" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="561" spans="1:7">
       <c r="A561" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
       <c r="B561" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C561" t="s">
         <v>55</v>
       </c>
       <c r="D561" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E561" t="s">
         <v>11</v>
       </c>
       <c r="F561" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
       <c r="G561" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="562" spans="1:7">
       <c r="A562" t="s">
-        <v>506</v>
+        <v>838</v>
       </c>
       <c r="B562" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="C562" t="s">
-        <v>835</v>
+        <v>184</v>
       </c>
       <c r="D562" t="s">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="E562" t="s">
         <v>11</v>
       </c>
       <c r="F562" t="s">
-        <v>185</v>
+        <v>840</v>
       </c>
       <c r="G562" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="563" spans="1:7">
       <c r="A563" t="s">
-        <v>490</v>
+        <v>841</v>
       </c>
       <c r="B563" t="s">
-        <v>846</v>
+        <v>830</v>
       </c>
       <c r="C563" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="D563" t="s">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="E563" t="s">
         <v>11</v>
       </c>
       <c r="F563" t="s">
-        <v>68</v>
+        <v>842</v>
       </c>
       <c r="G563" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="564" spans="1:7">
       <c r="A564" t="s">
-        <v>847</v>
+        <v>506</v>
       </c>
       <c r="B564" t="s">
-        <v>30</v>
+        <v>843</v>
       </c>
       <c r="C564" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D564" t="s">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="E564" t="s">
         <v>11</v>
       </c>
       <c r="F564" t="s">
-        <v>68</v>
+        <v>185</v>
       </c>
       <c r="G564" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="565" spans="1:7">
       <c r="A565" t="s">
-        <v>848</v>
+        <v>490</v>
       </c>
       <c r="B565" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="C565" t="s">
-        <v>184</v>
+        <v>100</v>
       </c>
       <c r="D565" t="s">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="E565" t="s">
         <v>11</v>
       </c>
       <c r="F565" t="s">
-        <v>849</v>
+        <v>68</v>
       </c>
       <c r="G565" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="566" spans="1:7">
       <c r="A566" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="B566" t="s">
-        <v>845</v>
+        <v>30</v>
       </c>
       <c r="C566" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="D566" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="E566" t="s">
         <v>11</v>
       </c>
       <c r="F566" t="s">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="G566" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="567" spans="1:7">
       <c r="A567" t="s">
-        <v>102</v>
+        <v>846</v>
       </c>
       <c r="B567" t="s">
-        <v>851</v>
+        <v>839</v>
       </c>
       <c r="C567" t="s">
-        <v>835</v>
+        <v>184</v>
       </c>
       <c r="D567" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E567" t="s">
         <v>11</v>
       </c>
       <c r="F567" t="s">
-        <v>128</v>
+        <v>847</v>
       </c>
       <c r="G567" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="568" spans="1:7">
       <c r="A568" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B568" t="s">
-        <v>30</v>
+        <v>843</v>
       </c>
       <c r="C568" t="s">
-        <v>55</v>
+        <v>833</v>
       </c>
       <c r="D568" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="E568" t="s">
         <v>11</v>
@@ -17047,41 +17041,41 @@
         <v>185</v>
       </c>
       <c r="G568" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="569" spans="1:7">
       <c r="A569" t="s">
-        <v>853</v>
+        <v>102</v>
       </c>
       <c r="B569" t="s">
-        <v>30</v>
+        <v>849</v>
       </c>
       <c r="C569" t="s">
-        <v>454</v>
+        <v>833</v>
       </c>
       <c r="D569" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="E569" t="s">
         <v>11</v>
       </c>
       <c r="F569" t="s">
-        <v>185</v>
+        <v>128</v>
       </c>
       <c r="G569" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="570" spans="1:7">
       <c r="A570" t="s">
-        <v>458</v>
+        <v>850</v>
       </c>
       <c r="B570" t="s">
         <v>30</v>
       </c>
       <c r="C570" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D570" t="s">
         <v>17</v>
@@ -17093,133 +17087,133 @@
         <v>185</v>
       </c>
       <c r="G570" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="571" spans="1:7">
       <c r="A571" t="s">
-        <v>834</v>
+        <v>851</v>
       </c>
       <c r="B571" t="s">
-        <v>845</v>
+        <v>30</v>
       </c>
       <c r="C571" t="s">
-        <v>835</v>
+        <v>454</v>
       </c>
       <c r="D571" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="E571" t="s">
         <v>11</v>
       </c>
       <c r="F571" t="s">
-        <v>68</v>
+        <v>185</v>
       </c>
       <c r="G571" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="572" spans="1:7">
       <c r="A572" t="s">
-        <v>854</v>
+        <v>458</v>
       </c>
       <c r="B572" t="s">
-        <v>841</v>
+        <v>30</v>
       </c>
       <c r="C572" t="s">
-        <v>855</v>
+        <v>59</v>
       </c>
       <c r="D572" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E572" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F572" t="s">
-        <v>856</v>
+        <v>185</v>
       </c>
       <c r="G572" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="573" spans="1:7">
       <c r="A573" t="s">
-        <v>857</v>
+        <v>832</v>
       </c>
       <c r="B573" t="s">
-        <v>832</v>
+        <v>843</v>
       </c>
       <c r="C573" t="s">
-        <v>55</v>
+        <v>833</v>
       </c>
       <c r="D573" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E573" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F573" t="s">
-        <v>858</v>
+        <v>68</v>
       </c>
       <c r="G573" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="574" spans="1:7">
       <c r="A574" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="B574" t="s">
-        <v>860</v>
+        <v>839</v>
       </c>
       <c r="C574" t="s">
-        <v>55</v>
+        <v>853</v>
       </c>
       <c r="D574" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E574" t="s">
         <v>22</v>
       </c>
       <c r="F574" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="G574" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="575" spans="1:7">
       <c r="A575" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="B575" t="s">
-        <v>863</v>
+        <v>830</v>
       </c>
       <c r="C575" t="s">
         <v>55</v>
       </c>
       <c r="D575" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E575" t="s">
         <v>22</v>
       </c>
       <c r="F575" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
       <c r="G575" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="576" spans="1:7">
       <c r="A576" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="B576" t="s">
-        <v>841</v>
+        <v>858</v>
       </c>
       <c r="C576" t="s">
-        <v>855</v>
+        <v>55</v>
       </c>
       <c r="D576" t="s">
         <v>31</v>
@@ -17228,64 +17222,64 @@
         <v>22</v>
       </c>
       <c r="F576" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="G576" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="577" spans="1:7">
       <c r="A577" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="B577" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C577" t="s">
         <v>55</v>
       </c>
       <c r="D577" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E577" t="s">
         <v>22</v>
       </c>
       <c r="F577" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="G577" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="578" spans="1:7">
       <c r="A578" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="B578" t="s">
-        <v>863</v>
+        <v>839</v>
       </c>
       <c r="C578" t="s">
-        <v>55</v>
+        <v>853</v>
       </c>
       <c r="D578" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E578" t="s">
         <v>22</v>
       </c>
       <c r="F578" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="G578" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="579" spans="1:7">
       <c r="A579" t="s">
-        <v>475</v>
+        <v>865</v>
       </c>
       <c r="B579" t="s">
-        <v>832</v>
+        <v>858</v>
       </c>
       <c r="C579" t="s">
         <v>55</v>
@@ -17297,90 +17291,90 @@
         <v>22</v>
       </c>
       <c r="F579" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="G579" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="580" spans="1:7">
       <c r="A580" t="s">
-        <v>480</v>
+        <v>867</v>
       </c>
       <c r="B580" t="s">
-        <v>832</v>
+        <v>861</v>
       </c>
       <c r="C580" t="s">
         <v>55</v>
       </c>
       <c r="D580" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E580" t="s">
         <v>22</v>
       </c>
       <c r="F580" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="G580" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="581" spans="1:7">
       <c r="A581" t="s">
-        <v>873</v>
+        <v>475</v>
       </c>
       <c r="B581" t="s">
-        <v>860</v>
+        <v>830</v>
       </c>
       <c r="C581" t="s">
         <v>55</v>
       </c>
       <c r="D581" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E581" t="s">
         <v>22</v>
       </c>
       <c r="F581" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="G581" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="582" spans="1:7">
       <c r="A582" t="s">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="B582" t="s">
-        <v>841</v>
+        <v>830</v>
       </c>
       <c r="C582" t="s">
-        <v>855</v>
+        <v>55</v>
       </c>
       <c r="D582" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E582" t="s">
         <v>22</v>
       </c>
       <c r="F582" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="G582" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="583" spans="1:7">
       <c r="A583" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="B583" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="C583" t="s">
-        <v>462</v>
+        <v>55</v>
       </c>
       <c r="D583" t="s">
         <v>21</v>
@@ -17389,67 +17383,67 @@
         <v>22</v>
       </c>
       <c r="F583" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="G583" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="584" spans="1:7">
       <c r="A584" t="s">
-        <v>878</v>
+        <v>495</v>
       </c>
       <c r="B584" t="s">
-        <v>860</v>
+        <v>839</v>
       </c>
       <c r="C584" t="s">
-        <v>55</v>
+        <v>853</v>
       </c>
       <c r="D584" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E584" t="s">
         <v>22</v>
       </c>
       <c r="F584" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="G584" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="585" spans="1:7">
       <c r="A585" t="s">
-        <v>486</v>
+        <v>874</v>
       </c>
       <c r="B585" t="s">
-        <v>841</v>
+        <v>861</v>
       </c>
       <c r="C585" t="s">
-        <v>855</v>
+        <v>462</v>
       </c>
       <c r="D585" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E585" t="s">
         <v>22</v>
       </c>
       <c r="F585" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G585" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="586" spans="1:7">
       <c r="A586" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="B586" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="C586" t="s">
-        <v>462</v>
+        <v>55</v>
       </c>
       <c r="D586" t="s">
         <v>17</v>
@@ -17458,159 +17452,159 @@
         <v>22</v>
       </c>
       <c r="F586" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G586" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="587" spans="1:7">
       <c r="A587" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B587" t="s">
-        <v>19</v>
+        <v>839</v>
       </c>
       <c r="C587" t="s">
-        <v>310</v>
+        <v>853</v>
       </c>
       <c r="D587" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E587" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F587" t="s">
-        <v>128</v>
+        <v>878</v>
       </c>
       <c r="G587" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="588" spans="1:7">
       <c r="A588" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="B588" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C588" t="s">
-        <v>55</v>
+        <v>462</v>
       </c>
       <c r="D588" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="E588" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F588" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="G588" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="589" spans="1:7">
       <c r="A589" t="s">
-        <v>885</v>
+        <v>465</v>
       </c>
       <c r="B589" t="s">
-        <v>863</v>
+        <v>19</v>
       </c>
       <c r="C589" t="s">
-        <v>55</v>
+        <v>310</v>
       </c>
       <c r="D589" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E589" t="s">
         <v>28</v>
       </c>
       <c r="F589" t="s">
-        <v>886</v>
+        <v>128</v>
       </c>
       <c r="G589" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="590" spans="1:7">
       <c r="A590" t="s">
-        <v>499</v>
+        <v>881</v>
       </c>
       <c r="B590" t="s">
-        <v>845</v>
+        <v>858</v>
       </c>
       <c r="C590" t="s">
-        <v>835</v>
+        <v>55</v>
       </c>
       <c r="D590" t="s">
-        <v>887</v>
+        <v>31</v>
       </c>
       <c r="E590" t="s">
         <v>28</v>
       </c>
       <c r="F590" t="s">
-        <v>68</v>
+        <v>882</v>
       </c>
       <c r="G590" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="591" spans="1:7">
       <c r="A591" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="B591" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C591" t="s">
         <v>55</v>
       </c>
       <c r="D591" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E591" t="s">
         <v>28</v>
       </c>
       <c r="F591" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="G591" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="592" spans="1:7">
       <c r="A592" t="s">
-        <v>890</v>
+        <v>499</v>
       </c>
       <c r="B592" t="s">
-        <v>863</v>
+        <v>843</v>
       </c>
       <c r="C592" t="s">
-        <v>55</v>
+        <v>833</v>
       </c>
       <c r="D592" t="s">
-        <v>10</v>
+        <v>885</v>
       </c>
       <c r="E592" t="s">
         <v>28</v>
       </c>
       <c r="F592" t="s">
-        <v>891</v>
+        <v>68</v>
       </c>
       <c r="G592" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="593" spans="1:7">
       <c r="A593" t="s">
-        <v>506</v>
+        <v>886</v>
       </c>
       <c r="B593" t="s">
-        <v>30</v>
+        <v>858</v>
       </c>
       <c r="C593" t="s">
-        <v>835</v>
+        <v>55</v>
       </c>
       <c r="D593" t="s">
         <v>10</v>
@@ -17619,21 +17613,21 @@
         <v>28</v>
       </c>
       <c r="F593" t="s">
-        <v>185</v>
+        <v>887</v>
       </c>
       <c r="G593" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="594" spans="1:7">
       <c r="A594" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="B594" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C594" t="s">
-        <v>484</v>
+        <v>55</v>
       </c>
       <c r="D594" t="s">
         <v>10</v>
@@ -17642,21 +17636,21 @@
         <v>28</v>
       </c>
       <c r="F594" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="G594" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="595" spans="1:7">
       <c r="A595" t="s">
-        <v>894</v>
+        <v>506</v>
       </c>
       <c r="B595" t="s">
-        <v>863</v>
+        <v>30</v>
       </c>
       <c r="C595" t="s">
-        <v>895</v>
+        <v>833</v>
       </c>
       <c r="D595" t="s">
         <v>10</v>
@@ -17665,332 +17659,332 @@
         <v>28</v>
       </c>
       <c r="F595" t="s">
-        <v>896</v>
+        <v>185</v>
       </c>
       <c r="G595" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="596" spans="1:7">
       <c r="A596" t="s">
-        <v>513</v>
+        <v>890</v>
       </c>
       <c r="B596" t="s">
-        <v>897</v>
+        <v>858</v>
       </c>
       <c r="C596" t="s">
-        <v>517</v>
+        <v>484</v>
       </c>
       <c r="D596" t="s">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="E596" t="s">
         <v>28</v>
       </c>
       <c r="F596" t="s">
-        <v>68</v>
+        <v>891</v>
       </c>
       <c r="G596" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="597" spans="1:7">
       <c r="A597" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="B597" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C597" t="s">
-        <v>484</v>
+        <v>893</v>
       </c>
       <c r="D597" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E597" t="s">
         <v>28</v>
       </c>
       <c r="F597" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="G597" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="598" spans="1:7">
       <c r="A598" t="s">
-        <v>900</v>
+        <v>513</v>
       </c>
       <c r="B598" t="s">
-        <v>863</v>
+        <v>895</v>
       </c>
       <c r="C598" t="s">
-        <v>895</v>
+        <v>517</v>
       </c>
       <c r="D598" t="s">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="E598" t="s">
         <v>28</v>
       </c>
       <c r="F598" t="s">
-        <v>901</v>
+        <v>68</v>
       </c>
       <c r="G598" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="599" spans="1:7">
       <c r="A599" t="s">
-        <v>514</v>
+        <v>896</v>
       </c>
       <c r="B599" t="s">
-        <v>897</v>
+        <v>858</v>
       </c>
       <c r="C599" t="s">
-        <v>517</v>
+        <v>484</v>
       </c>
       <c r="D599" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="E599" t="s">
         <v>28</v>
       </c>
       <c r="F599" t="s">
-        <v>185</v>
+        <v>897</v>
       </c>
       <c r="G599" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="600" spans="1:7">
       <c r="A600" t="s">
-        <v>103</v>
+        <v>898</v>
       </c>
       <c r="B600" t="s">
-        <v>19</v>
+        <v>861</v>
       </c>
       <c r="C600" t="s">
-        <v>370</v>
+        <v>893</v>
       </c>
       <c r="D600" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E600" t="s">
         <v>28</v>
       </c>
       <c r="F600" t="s">
-        <v>330</v>
+        <v>899</v>
       </c>
       <c r="G600" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="601" spans="1:7">
       <c r="A601" t="s">
-        <v>902</v>
+        <v>514</v>
       </c>
       <c r="B601" t="s">
-        <v>30</v>
+        <v>895</v>
       </c>
       <c r="C601" t="s">
-        <v>26</v>
+        <v>517</v>
       </c>
       <c r="D601" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="E601" t="s">
         <v>28</v>
       </c>
       <c r="F601" t="s">
-        <v>68</v>
+        <v>185</v>
       </c>
       <c r="G601" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="602" spans="1:7">
       <c r="A602" t="s">
-        <v>903</v>
+        <v>103</v>
       </c>
       <c r="B602" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C602" t="s">
-        <v>462</v>
+        <v>370</v>
       </c>
       <c r="D602" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E602" t="s">
         <v>28</v>
       </c>
       <c r="F602" t="s">
-        <v>83</v>
+        <v>330</v>
       </c>
       <c r="G602" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="603" spans="1:7">
       <c r="A603" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="B603" t="s">
-        <v>897</v>
+        <v>30</v>
       </c>
       <c r="C603" t="s">
-        <v>207</v>
+        <v>26</v>
       </c>
       <c r="D603" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="E603" t="s">
         <v>28</v>
       </c>
       <c r="F603" t="s">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="G603" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="604" spans="1:7">
       <c r="A604" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="B604" t="s">
-        <v>832</v>
+        <v>30</v>
       </c>
       <c r="C604" t="s">
-        <v>55</v>
+        <v>462</v>
       </c>
       <c r="D604" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E604" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="F604" t="s">
-        <v>906</v>
+        <v>83</v>
       </c>
       <c r="G604" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="605" spans="1:7">
       <c r="A605" t="s">
-        <v>478</v>
+        <v>902</v>
       </c>
       <c r="B605" t="s">
-        <v>841</v>
+        <v>895</v>
       </c>
       <c r="C605" t="s">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="D605" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E605" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="F605" t="s">
-        <v>907</v>
+        <v>185</v>
       </c>
       <c r="G605" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="606" spans="1:7">
       <c r="A606" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="B606" t="s">
-        <v>30</v>
+        <v>830</v>
       </c>
       <c r="C606" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="D606" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E606" t="s">
         <v>47</v>
       </c>
       <c r="F606" t="s">
-        <v>216</v>
+        <v>904</v>
       </c>
       <c r="G606" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="607" spans="1:7">
       <c r="A607" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B607" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C607" t="s">
         <v>80</v>
       </c>
       <c r="D607" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E607" t="s">
         <v>47</v>
       </c>
       <c r="F607" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="G607" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="608" spans="1:7">
       <c r="A608" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B608" t="s">
-        <v>860</v>
+        <v>30</v>
       </c>
       <c r="C608" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="D608" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E608" t="s">
         <v>47</v>
       </c>
       <c r="F608" t="s">
-        <v>911</v>
+        <v>216</v>
       </c>
       <c r="G608" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="609" spans="1:7">
       <c r="A609" t="s">
-        <v>912</v>
+        <v>472</v>
       </c>
       <c r="B609" t="s">
-        <v>863</v>
+        <v>839</v>
       </c>
       <c r="C609" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="D609" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E609" t="s">
         <v>47</v>
       </c>
       <c r="F609" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="G609" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="610" spans="1:7">
@@ -17998,10 +17992,10 @@
         <v>908</v>
       </c>
       <c r="B610" t="s">
-        <v>30</v>
+        <v>858</v>
       </c>
       <c r="C610" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="D610" t="s">
         <v>10</v>
@@ -18010,21 +18004,21 @@
         <v>47</v>
       </c>
       <c r="F610" t="s">
-        <v>216</v>
+        <v>909</v>
       </c>
       <c r="G610" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="611" spans="1:7">
       <c r="A611" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="B611" t="s">
-        <v>30</v>
+        <v>861</v>
       </c>
       <c r="C611" t="s">
-        <v>855</v>
+        <v>55</v>
       </c>
       <c r="D611" t="s">
         <v>10</v>
@@ -18033,87 +18027,87 @@
         <v>47</v>
       </c>
       <c r="F611" t="s">
-        <v>216</v>
+        <v>911</v>
       </c>
       <c r="G611" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="612" spans="1:7">
       <c r="A612" t="s">
-        <v>915</v>
+        <v>906</v>
       </c>
       <c r="B612" t="s">
-        <v>916</v>
+        <v>30</v>
       </c>
       <c r="C612" t="s">
-        <v>855</v>
+        <v>97</v>
       </c>
       <c r="D612" t="s">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="E612" t="s">
         <v>47</v>
       </c>
       <c r="F612" t="s">
-        <v>68</v>
+        <v>216</v>
       </c>
       <c r="G612" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="613" spans="1:7">
       <c r="A613" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="B613" t="s">
-        <v>860</v>
+        <v>30</v>
       </c>
       <c r="C613" t="s">
-        <v>55</v>
+        <v>853</v>
       </c>
       <c r="D613" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E613" t="s">
         <v>47</v>
       </c>
       <c r="F613" t="s">
-        <v>918</v>
+        <v>216</v>
       </c>
       <c r="G613" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="614" spans="1:7">
       <c r="A614" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="B614" t="s">
-        <v>863</v>
+        <v>914</v>
       </c>
       <c r="C614" t="s">
-        <v>55</v>
+        <v>853</v>
       </c>
       <c r="D614" t="s">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="E614" t="s">
         <v>47</v>
       </c>
       <c r="F614" t="s">
-        <v>920</v>
+        <v>68</v>
       </c>
       <c r="G614" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="615" spans="1:7">
       <c r="A615" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="B615" t="s">
-        <v>832</v>
+        <v>858</v>
       </c>
       <c r="C615" t="s">
         <v>55</v>
@@ -18125,21 +18119,21 @@
         <v>47</v>
       </c>
       <c r="F615" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="G615" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="616" spans="1:7">
       <c r="A616" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="B616" t="s">
-        <v>30</v>
+        <v>861</v>
       </c>
       <c r="C616" t="s">
-        <v>830</v>
+        <v>55</v>
       </c>
       <c r="D616" t="s">
         <v>14</v>
@@ -18148,389 +18142,389 @@
         <v>47</v>
       </c>
       <c r="F616" t="s">
-        <v>68</v>
+        <v>918</v>
       </c>
       <c r="G616" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="617" spans="1:7">
       <c r="A617" t="s">
-        <v>502</v>
+        <v>919</v>
       </c>
       <c r="B617" t="s">
-        <v>924</v>
+        <v>830</v>
       </c>
       <c r="C617" t="s">
         <v>55</v>
       </c>
       <c r="D617" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="E617" t="s">
         <v>47</v>
       </c>
       <c r="F617" t="s">
-        <v>185</v>
+        <v>920</v>
       </c>
       <c r="G617" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="618" spans="1:7">
       <c r="A618" t="s">
-        <v>65</v>
+        <v>921</v>
       </c>
       <c r="B618" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C618" t="s">
-        <v>489</v>
+        <v>828</v>
       </c>
       <c r="D618" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E618" t="s">
         <v>47</v>
       </c>
       <c r="F618" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="G618" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="619" spans="1:7">
       <c r="A619" t="s">
-        <v>69</v>
+        <v>502</v>
       </c>
       <c r="B619" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="C619" t="s">
-        <v>454</v>
+        <v>55</v>
       </c>
       <c r="D619" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="E619" t="s">
         <v>47</v>
       </c>
       <c r="F619" t="s">
-        <v>128</v>
+        <v>185</v>
       </c>
       <c r="G619" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="620" spans="1:7">
       <c r="A620" t="s">
-        <v>926</v>
+        <v>65</v>
       </c>
       <c r="B620" t="s">
         <v>19</v>
       </c>
       <c r="C620" t="s">
-        <v>106</v>
+        <v>489</v>
       </c>
       <c r="D620" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="E620" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="F620" t="s">
         <v>128</v>
       </c>
       <c r="G620" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="621" spans="1:7">
       <c r="A621" t="s">
-        <v>927</v>
+        <v>69</v>
       </c>
       <c r="B621" t="s">
-        <v>19</v>
+        <v>923</v>
       </c>
       <c r="C621" t="s">
-        <v>508</v>
+        <v>454</v>
       </c>
       <c r="D621" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E621" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="F621" t="s">
         <v>128</v>
       </c>
       <c r="G621" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="622" spans="1:7">
       <c r="A622" t="s">
-        <v>850</v>
+        <v>924</v>
       </c>
       <c r="B622" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C622" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="D622" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="E622" t="s">
         <v>63</v>
       </c>
       <c r="F622" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="G622" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="623" spans="1:7">
       <c r="A623" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B623" t="s">
-        <v>841</v>
+        <v>19</v>
       </c>
       <c r="C623" t="s">
-        <v>55</v>
+        <v>508</v>
       </c>
       <c r="D623" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E623" t="s">
         <v>63</v>
       </c>
       <c r="F623" t="s">
-        <v>929</v>
+        <v>128</v>
       </c>
       <c r="G623" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="624" spans="1:7">
       <c r="A624" t="s">
-        <v>930</v>
+        <v>848</v>
       </c>
       <c r="B624" t="s">
-        <v>924</v>
+        <v>30</v>
       </c>
       <c r="C624" t="s">
         <v>55</v>
       </c>
       <c r="D624" t="s">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="E624" t="s">
         <v>63</v>
       </c>
       <c r="F624" t="s">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="G624" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="625" spans="1:7">
       <c r="A625" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="B625" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="C625" t="s">
         <v>55</v>
       </c>
       <c r="D625" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E625" t="s">
         <v>63</v>
       </c>
       <c r="F625" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="G625" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="626" spans="1:7">
       <c r="A626" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="B626" t="s">
-        <v>30</v>
+        <v>922</v>
       </c>
       <c r="C626" t="s">
-        <v>223</v>
+        <v>55</v>
       </c>
       <c r="D626" t="s">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="E626" t="s">
         <v>63</v>
       </c>
       <c r="F626" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="G626" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="627" spans="1:7">
       <c r="A627" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="B627" t="s">
-        <v>924</v>
+        <v>830</v>
       </c>
       <c r="C627" t="s">
         <v>55</v>
       </c>
       <c r="D627" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="E627" t="s">
         <v>63</v>
       </c>
       <c r="F627" t="s">
-        <v>68</v>
+        <v>930</v>
       </c>
       <c r="G627" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="628" spans="1:7">
       <c r="A628" t="s">
-        <v>505</v>
+        <v>931</v>
       </c>
       <c r="B628" t="s">
         <v>30</v>
       </c>
       <c r="C628" t="s">
-        <v>55</v>
+        <v>223</v>
       </c>
       <c r="D628" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E628" t="s">
         <v>63</v>
       </c>
       <c r="F628" t="s">
-        <v>68</v>
+        <v>216</v>
       </c>
       <c r="G628" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="629" spans="1:7">
       <c r="A629" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="B629" t="s">
-        <v>841</v>
+        <v>922</v>
       </c>
       <c r="C629" t="s">
         <v>55</v>
       </c>
       <c r="D629" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="E629" t="s">
         <v>63</v>
       </c>
       <c r="F629" t="s">
-        <v>936</v>
+        <v>68</v>
       </c>
       <c r="G629" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="630" spans="1:7">
       <c r="A630" t="s">
-        <v>937</v>
+        <v>505</v>
       </c>
       <c r="B630" t="s">
-        <v>938</v>
+        <v>30</v>
       </c>
       <c r="C630" t="s">
-        <v>517</v>
+        <v>55</v>
       </c>
       <c r="D630" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="E630" t="s">
         <v>63</v>
       </c>
       <c r="F630" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="G630" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="631" spans="1:7">
       <c r="A631" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="B631" t="s">
-        <v>30</v>
+        <v>839</v>
       </c>
       <c r="C631" t="s">
-        <v>319</v>
+        <v>55</v>
       </c>
       <c r="D631" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="E631" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="F631" t="s">
-        <v>293</v>
+        <v>934</v>
       </c>
       <c r="G631" t="s">
-        <v>940</v>
+        <v>829</v>
       </c>
     </row>
     <row r="632" spans="1:7">
       <c r="A632" t="s">
-        <v>573</v>
+        <v>935</v>
       </c>
       <c r="B632" t="s">
-        <v>30</v>
+        <v>936</v>
       </c>
       <c r="C632" t="s">
-        <v>204</v>
+        <v>517</v>
       </c>
       <c r="D632" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E632" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="F632" t="s">
-        <v>304</v>
+        <v>128</v>
       </c>
       <c r="G632" t="s">
-        <v>940</v>
+        <v>829</v>
       </c>
     </row>
     <row r="633" spans="1:7">
       <c r="A633" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="B633" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C633" t="s">
-        <v>484</v>
+        <v>319</v>
       </c>
       <c r="D633" t="s">
         <v>46</v>
@@ -18539,21 +18533,21 @@
         <v>11</v>
       </c>
       <c r="F633" t="s">
-        <v>942</v>
+        <v>293</v>
       </c>
       <c r="G633" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="634" spans="1:7">
       <c r="A634" t="s">
-        <v>943</v>
+        <v>573</v>
       </c>
       <c r="B634" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C634" t="s">
-        <v>55</v>
+        <v>204</v>
       </c>
       <c r="D634" t="s">
         <v>46</v>
@@ -18562,90 +18556,90 @@
         <v>11</v>
       </c>
       <c r="F634" t="s">
-        <v>944</v>
+        <v>304</v>
       </c>
       <c r="G634" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="635" spans="1:7">
       <c r="A635" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="B635" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C635" t="s">
-        <v>161</v>
+        <v>484</v>
       </c>
       <c r="D635" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="E635" t="s">
         <v>11</v>
       </c>
       <c r="F635" t="s">
-        <v>39</v>
+        <v>940</v>
       </c>
       <c r="G635" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="636" spans="1:7">
       <c r="A636" t="s">
-        <v>548</v>
+        <v>941</v>
       </c>
       <c r="B636" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C636" t="s">
-        <v>161</v>
+        <v>55</v>
       </c>
       <c r="D636" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E636" t="s">
         <v>11</v>
       </c>
       <c r="F636" t="s">
-        <v>39</v>
+        <v>942</v>
       </c>
       <c r="G636" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="637" spans="1:7">
       <c r="A637" t="s">
-        <v>538</v>
+        <v>943</v>
       </c>
       <c r="B637" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C637" t="s">
-        <v>946</v>
+        <v>161</v>
       </c>
       <c r="D637" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E637" t="s">
         <v>11</v>
       </c>
       <c r="F637" t="s">
-        <v>539</v>
+        <v>39</v>
       </c>
       <c r="G637" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="638" spans="1:7">
       <c r="A638" t="s">
-        <v>947</v>
+        <v>548</v>
       </c>
       <c r="B638" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C638" t="s">
-        <v>55</v>
+        <v>161</v>
       </c>
       <c r="D638" t="s">
         <v>14</v>
@@ -18654,70 +18648,70 @@
         <v>11</v>
       </c>
       <c r="F638" t="s">
-        <v>948</v>
+        <v>39</v>
       </c>
       <c r="G638" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="639" spans="1:7">
       <c r="A639" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="B639" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C639" t="s">
-        <v>204</v>
+        <v>944</v>
       </c>
       <c r="D639" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E639" t="s">
         <v>11</v>
       </c>
       <c r="F639" t="s">
-        <v>304</v>
+        <v>539</v>
       </c>
       <c r="G639" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="640" spans="1:7">
       <c r="A640" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="B640" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C640" t="s">
-        <v>319</v>
+        <v>55</v>
       </c>
       <c r="D640" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E640" t="s">
         <v>11</v>
       </c>
       <c r="F640" t="s">
-        <v>232</v>
+        <v>946</v>
       </c>
       <c r="G640" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="641" spans="1:7">
       <c r="A641" t="s">
-        <v>950</v>
+        <v>543</v>
       </c>
       <c r="B641" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C641" t="s">
         <v>204</v>
       </c>
       <c r="D641" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E641" t="s">
         <v>11</v>
@@ -18726,18 +18720,18 @@
         <v>304</v>
       </c>
       <c r="G641" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="642" spans="1:7">
       <c r="A642" t="s">
-        <v>551</v>
+        <v>947</v>
       </c>
       <c r="B642" t="s">
         <v>30</v>
       </c>
       <c r="C642" t="s">
-        <v>161</v>
+        <v>319</v>
       </c>
       <c r="D642" t="s">
         <v>17</v>
@@ -18749,271 +18743,271 @@
         <v>232</v>
       </c>
       <c r="G642" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="643" spans="1:7">
       <c r="A643" t="s">
-        <v>582</v>
+        <v>948</v>
       </c>
       <c r="B643" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C643" t="s">
-        <v>55</v>
+        <v>204</v>
       </c>
       <c r="D643" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E643" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F643" t="s">
-        <v>951</v>
+        <v>304</v>
       </c>
       <c r="G643" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="644" spans="1:7">
       <c r="A644" t="s">
-        <v>952</v>
+        <v>551</v>
       </c>
       <c r="B644" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C644" t="s">
-        <v>946</v>
+        <v>161</v>
       </c>
       <c r="D644" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E644" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F644" t="s">
-        <v>953</v>
+        <v>232</v>
       </c>
       <c r="G644" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="645" spans="1:7">
       <c r="A645" t="s">
-        <v>556</v>
+        <v>582</v>
       </c>
       <c r="B645" t="s">
         <v>8</v>
       </c>
       <c r="C645" t="s">
-        <v>484</v>
+        <v>55</v>
       </c>
       <c r="D645" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="E645" t="s">
         <v>22</v>
       </c>
       <c r="F645" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="G645" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="646" spans="1:7">
       <c r="A646" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="B646" t="s">
         <v>8</v>
       </c>
       <c r="C646" t="s">
-        <v>529</v>
+        <v>944</v>
       </c>
       <c r="D646" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="E646" t="s">
         <v>22</v>
       </c>
       <c r="F646" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="G646" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="647" spans="1:7">
       <c r="A647" t="s">
-        <v>957</v>
+        <v>556</v>
       </c>
       <c r="B647" t="s">
         <v>8</v>
       </c>
       <c r="C647" t="s">
-        <v>171</v>
+        <v>484</v>
       </c>
       <c r="D647" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E647" t="s">
         <v>22</v>
       </c>
       <c r="F647" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="G647" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="648" spans="1:7">
       <c r="A648" t="s">
-        <v>578</v>
+        <v>953</v>
       </c>
       <c r="B648" t="s">
         <v>8</v>
       </c>
       <c r="C648" t="s">
-        <v>946</v>
+        <v>529</v>
       </c>
       <c r="D648" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E648" t="s">
         <v>22</v>
       </c>
       <c r="F648" t="s">
-        <v>579</v>
+        <v>954</v>
       </c>
       <c r="G648" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="649" spans="1:7">
       <c r="A649" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="B649" t="s">
-        <v>960</v>
+        <v>8</v>
       </c>
       <c r="C649" t="s">
-        <v>547</v>
+        <v>171</v>
       </c>
       <c r="D649" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E649" t="s">
         <v>22</v>
       </c>
       <c r="F649" t="s">
-        <v>23</v>
+        <v>956</v>
       </c>
       <c r="G649" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="650" spans="1:7">
       <c r="A650" t="s">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="B650" t="s">
         <v>8</v>
       </c>
       <c r="C650" t="s">
-        <v>484</v>
+        <v>944</v>
       </c>
       <c r="D650" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E650" t="s">
         <v>22</v>
       </c>
       <c r="F650" t="s">
-        <v>961</v>
+        <v>579</v>
       </c>
       <c r="G650" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="651" spans="1:7">
       <c r="A651" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="B651" t="s">
-        <v>8</v>
+        <v>958</v>
       </c>
       <c r="C651" t="s">
-        <v>171</v>
+        <v>547</v>
       </c>
       <c r="D651" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="E651" t="s">
         <v>22</v>
       </c>
       <c r="F651" t="s">
-        <v>963</v>
+        <v>23</v>
       </c>
       <c r="G651" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="652" spans="1:7">
       <c r="A652" t="s">
-        <v>964</v>
+        <v>564</v>
       </c>
       <c r="B652" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C652" t="s">
-        <v>319</v>
+        <v>484</v>
       </c>
       <c r="D652" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E652" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F652" t="s">
-        <v>232</v>
+        <v>959</v>
       </c>
       <c r="G652" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="653" spans="1:7">
       <c r="A653" t="s">
-        <v>549</v>
+        <v>960</v>
       </c>
       <c r="B653" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C653" t="s">
-        <v>204</v>
+        <v>171</v>
       </c>
       <c r="D653" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E653" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F653" t="s">
-        <v>304</v>
+        <v>961</v>
       </c>
       <c r="G653" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="654" spans="1:7">
       <c r="A654" t="s">
-        <v>534</v>
+        <v>962</v>
       </c>
       <c r="B654" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C654" t="s">
-        <v>484</v>
+        <v>319</v>
       </c>
       <c r="D654" t="s">
         <v>46</v>
@@ -19022,21 +19016,21 @@
         <v>28</v>
       </c>
       <c r="F654" t="s">
-        <v>965</v>
+        <v>232</v>
       </c>
       <c r="G654" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="655" spans="1:7">
       <c r="A655" t="s">
-        <v>966</v>
+        <v>549</v>
       </c>
       <c r="B655" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C655" t="s">
-        <v>529</v>
+        <v>204</v>
       </c>
       <c r="D655" t="s">
         <v>46</v>
@@ -19045,182 +19039,182 @@
         <v>28</v>
       </c>
       <c r="F655" t="s">
-        <v>967</v>
+        <v>304</v>
       </c>
       <c r="G655" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="656" spans="1:7">
       <c r="A656" t="s">
-        <v>968</v>
+        <v>534</v>
       </c>
       <c r="B656" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C656" t="s">
-        <v>312</v>
+        <v>484</v>
       </c>
       <c r="D656" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="E656" t="s">
         <v>28</v>
       </c>
       <c r="F656" t="s">
-        <v>304</v>
+        <v>963</v>
       </c>
       <c r="G656" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="657" spans="1:7">
       <c r="A657" t="s">
-        <v>570</v>
+        <v>964</v>
       </c>
       <c r="B657" t="s">
         <v>8</v>
       </c>
       <c r="C657" t="s">
-        <v>55</v>
+        <v>529</v>
       </c>
       <c r="D657" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E657" t="s">
         <v>28</v>
       </c>
       <c r="F657" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="G657" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="658" spans="1:7">
       <c r="A658" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="B658" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C658" t="s">
-        <v>529</v>
+        <v>312</v>
       </c>
       <c r="D658" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E658" t="s">
         <v>28</v>
       </c>
       <c r="F658" t="s">
-        <v>971</v>
+        <v>304</v>
       </c>
       <c r="G658" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="659" spans="1:7">
       <c r="A659" t="s">
-        <v>972</v>
+        <v>570</v>
       </c>
       <c r="B659" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C659" t="s">
-        <v>529</v>
+        <v>55</v>
       </c>
       <c r="D659" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E659" t="s">
         <v>28</v>
       </c>
       <c r="F659" t="s">
-        <v>304</v>
+        <v>967</v>
       </c>
       <c r="G659" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="660" spans="1:7">
       <c r="A660" t="s">
-        <v>554</v>
+        <v>968</v>
       </c>
       <c r="B660" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C660" t="s">
-        <v>143</v>
+        <v>529</v>
       </c>
       <c r="D660" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E660" t="s">
         <v>28</v>
       </c>
       <c r="F660" t="s">
-        <v>129</v>
+        <v>969</v>
       </c>
       <c r="G660" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="661" spans="1:7">
       <c r="A661" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="B661" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C661" t="s">
-        <v>161</v>
+        <v>529</v>
       </c>
       <c r="D661" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="E661" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="F661" t="s">
-        <v>29</v>
+        <v>304</v>
       </c>
       <c r="G661" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="662" spans="1:7">
       <c r="A662" t="s">
-        <v>974</v>
+        <v>554</v>
       </c>
       <c r="B662" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C662" t="s">
-        <v>946</v>
+        <v>143</v>
       </c>
       <c r="D662" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E662" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="F662" t="s">
-        <v>304</v>
+        <v>129</v>
       </c>
       <c r="G662" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="663" spans="1:7">
       <c r="A663" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="B663" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C663" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D663" t="s">
         <v>46</v>
@@ -19229,21 +19223,21 @@
         <v>47</v>
       </c>
       <c r="F663" t="s">
-        <v>537</v>
+        <v>29</v>
       </c>
       <c r="G663" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="664" spans="1:7">
       <c r="A664" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="B664" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C664" t="s">
-        <v>529</v>
+        <v>944</v>
       </c>
       <c r="D664" t="s">
         <v>46</v>
@@ -19252,15 +19246,15 @@
         <v>47</v>
       </c>
       <c r="F664" t="s">
-        <v>977</v>
+        <v>304</v>
       </c>
       <c r="G664" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="665" spans="1:7">
       <c r="A665" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="B665" t="s">
         <v>8</v>
@@ -19269,188 +19263,188 @@
         <v>171</v>
       </c>
       <c r="D665" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="E665" t="s">
         <v>47</v>
       </c>
       <c r="F665" t="s">
-        <v>567</v>
+        <v>537</v>
       </c>
       <c r="G665" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="666" spans="1:7">
       <c r="A666" t="s">
-        <v>568</v>
+        <v>974</v>
       </c>
       <c r="B666" t="s">
         <v>8</v>
       </c>
       <c r="C666" t="s">
-        <v>946</v>
+        <v>529</v>
       </c>
       <c r="D666" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="E666" t="s">
         <v>47</v>
       </c>
       <c r="F666" t="s">
-        <v>569</v>
+        <v>975</v>
       </c>
       <c r="G666" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="667" spans="1:7">
       <c r="A667" t="s">
-        <v>562</v>
+        <v>976</v>
       </c>
       <c r="B667" t="s">
         <v>8</v>
       </c>
       <c r="C667" t="s">
-        <v>55</v>
+        <v>171</v>
       </c>
       <c r="D667" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E667" t="s">
         <v>47</v>
       </c>
       <c r="F667" t="s">
-        <v>979</v>
+        <v>567</v>
       </c>
       <c r="G667" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="668" spans="1:7">
       <c r="A668" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="B668" t="s">
         <v>8</v>
       </c>
       <c r="C668" t="s">
-        <v>484</v>
+        <v>944</v>
       </c>
       <c r="D668" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E668" t="s">
         <v>47</v>
       </c>
       <c r="F668" t="s">
-        <v>980</v>
+        <v>569</v>
       </c>
       <c r="G668" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="669" spans="1:7">
       <c r="A669" t="s">
-        <v>981</v>
+        <v>562</v>
       </c>
       <c r="B669" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C669" t="s">
-        <v>319</v>
+        <v>55</v>
       </c>
       <c r="D669" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E669" t="s">
         <v>47</v>
       </c>
       <c r="F669" t="s">
-        <v>304</v>
+        <v>977</v>
       </c>
       <c r="G669" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="670" spans="1:7">
       <c r="A670" t="s">
-        <v>982</v>
+        <v>576</v>
       </c>
       <c r="B670" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C670" t="s">
-        <v>946</v>
+        <v>484</v>
       </c>
       <c r="D670" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E670" t="s">
         <v>47</v>
       </c>
       <c r="F670" t="s">
-        <v>304</v>
+        <v>978</v>
       </c>
       <c r="G670" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="671" spans="1:7">
       <c r="A671" t="s">
-        <v>526</v>
+        <v>979</v>
       </c>
       <c r="B671" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C671" t="s">
-        <v>55</v>
+        <v>319</v>
       </c>
       <c r="D671" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="E671" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="F671" t="s">
-        <v>527</v>
+        <v>304</v>
       </c>
       <c r="G671" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="672" spans="1:7">
       <c r="A672" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="B672" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C672" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="D672" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E672" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="F672" t="s">
-        <v>232</v>
+        <v>304</v>
       </c>
       <c r="G672" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="673" spans="1:7">
       <c r="A673" t="s">
-        <v>984</v>
+        <v>526</v>
       </c>
       <c r="B673" t="s">
         <v>8</v>
       </c>
       <c r="C673" t="s">
-        <v>171</v>
+        <v>55</v>
       </c>
       <c r="D673" t="s">
         <v>46</v>
@@ -19459,84 +19453,84 @@
         <v>63</v>
       </c>
       <c r="F673" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="G673" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="674" spans="1:7">
       <c r="A674" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="B674" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C674" t="s">
-        <v>484</v>
+        <v>944</v>
       </c>
       <c r="D674" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="E674" t="s">
         <v>63</v>
       </c>
       <c r="F674" t="s">
-        <v>986</v>
+        <v>232</v>
       </c>
       <c r="G674" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="675" spans="1:7">
       <c r="A675" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="B675" t="s">
         <v>8</v>
       </c>
       <c r="C675" t="s">
-        <v>529</v>
+        <v>171</v>
       </c>
       <c r="D675" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="E675" t="s">
         <v>63</v>
       </c>
       <c r="F675" t="s">
-        <v>988</v>
+        <v>525</v>
       </c>
       <c r="G675" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="676" spans="1:7">
       <c r="A676" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="B676" t="s">
         <v>8</v>
       </c>
       <c r="C676" t="s">
-        <v>171</v>
+        <v>484</v>
       </c>
       <c r="D676" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E676" t="s">
         <v>63</v>
       </c>
       <c r="F676" t="s">
-        <v>559</v>
+        <v>984</v>
       </c>
       <c r="G676" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="677" spans="1:7">
       <c r="A677" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="B677" t="s">
         <v>8</v>
@@ -19545,96 +19539,96 @@
         <v>529</v>
       </c>
       <c r="D677" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E677" t="s">
         <v>63</v>
       </c>
       <c r="F677" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="G677" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="678" spans="1:7">
       <c r="A678" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="B678" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C678" t="s">
-        <v>946</v>
+        <v>171</v>
       </c>
       <c r="D678" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E678" t="s">
         <v>63</v>
       </c>
       <c r="F678" t="s">
-        <v>304</v>
+        <v>559</v>
       </c>
       <c r="G678" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="679" spans="1:7">
       <c r="A679" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="B679" t="s">
         <v>8</v>
       </c>
       <c r="C679" t="s">
-        <v>55</v>
+        <v>529</v>
       </c>
       <c r="D679" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E679" t="s">
         <v>63</v>
       </c>
       <c r="F679" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="G679" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="680" spans="1:7">
       <c r="A680" t="s">
-        <v>531</v>
+        <v>980</v>
       </c>
       <c r="B680" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C680" t="s">
-        <v>55</v>
+        <v>944</v>
       </c>
       <c r="D680" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E680" t="s">
         <v>63</v>
       </c>
       <c r="F680" t="s">
-        <v>994</v>
+        <v>304</v>
       </c>
       <c r="G680" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="681" spans="1:7">
       <c r="A681" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="B681" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C681" t="s">
-        <v>946</v>
+        <v>55</v>
       </c>
       <c r="D681" t="s">
         <v>17</v>
@@ -19643,10 +19637,56 @@
         <v>63</v>
       </c>
       <c r="F681" t="s">
+        <v>991</v>
+      </c>
+      <c r="G681" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="682" spans="1:7">
+      <c r="A682" t="s">
+        <v>531</v>
+      </c>
+      <c r="B682" t="s">
+        <v>8</v>
+      </c>
+      <c r="C682" t="s">
+        <v>55</v>
+      </c>
+      <c r="D682" t="s">
+        <v>17</v>
+      </c>
+      <c r="E682" t="s">
+        <v>63</v>
+      </c>
+      <c r="F682" t="s">
+        <v>992</v>
+      </c>
+      <c r="G682" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="683" spans="1:7">
+      <c r="A683" t="s">
+        <v>993</v>
+      </c>
+      <c r="B683" t="s">
+        <v>30</v>
+      </c>
+      <c r="C683" t="s">
+        <v>944</v>
+      </c>
+      <c r="D683" t="s">
+        <v>17</v>
+      </c>
+      <c r="E683" t="s">
+        <v>63</v>
+      </c>
+      <c r="F683" t="s">
         <v>232</v>
       </c>
-      <c r="G681" t="s">
-        <v>940</v>
+      <c r="G683" t="s">
+        <v>938</v>
       </c>
     </row>
   </sheetData>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$1231</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$1437</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9848" uniqueCount="1783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11496" uniqueCount="1948">
   <si>
     <t>Enseignements</t>
   </si>
@@ -5379,6 +5379,501 @@
   </si>
   <si>
     <t>YAHI HICHEM</t>
+  </si>
+  <si>
+    <t>BENGHAREZ</t>
+  </si>
+  <si>
+    <t>BS 19</t>
+  </si>
+  <si>
+    <t>ING2TLC</t>
+  </si>
+  <si>
+    <t>TLC</t>
+  </si>
+  <si>
+    <t>BS 04</t>
+  </si>
+  <si>
+    <t>L2TLC</t>
+  </si>
+  <si>
+    <t>Cours-Antennas and Wireless Propagation</t>
+  </si>
+  <si>
+    <t>FARAH</t>
+  </si>
+  <si>
+    <t>ING3TLC</t>
+  </si>
+  <si>
+    <t>Cours-Calculateurs et interfaçage (G1)</t>
+  </si>
+  <si>
+    <t>CHOUAKRI</t>
+  </si>
+  <si>
+    <t>BS 05</t>
+  </si>
+  <si>
+    <t>L3TLC</t>
+  </si>
+  <si>
+    <t>Cours-Calculateurs et interfaçage (G2)</t>
+  </si>
+  <si>
+    <t>Cours-Capteurs et mesures en télécommunications</t>
+  </si>
+  <si>
+    <t>OUAHAB</t>
+  </si>
+  <si>
+    <t>Cours-Circuits programmables FPGA</t>
+  </si>
+  <si>
+    <t>DRIZ</t>
+  </si>
+  <si>
+    <t>BS 15</t>
+  </si>
+  <si>
+    <t>M1ST</t>
+  </si>
+  <si>
+    <t>Cours-Communications Analogiques</t>
+  </si>
+  <si>
+    <t>DJEBBARI</t>
+  </si>
+  <si>
+    <t>Cours-Communications numériques avancées</t>
+  </si>
+  <si>
+    <t>HADJI</t>
+  </si>
+  <si>
+    <t>EL AHMAR</t>
+  </si>
+  <si>
+    <t>BS 18</t>
+  </si>
+  <si>
+    <t>M1RT</t>
+  </si>
+  <si>
+    <t>Cours-Communications optiques</t>
+  </si>
+  <si>
+    <t>ABOURA</t>
+  </si>
+  <si>
+    <t>BS 09</t>
+  </si>
+  <si>
+    <t>M2ST</t>
+  </si>
+  <si>
+    <t>Cours-Cryptographie et Sécurité Réseaux</t>
+  </si>
+  <si>
+    <t>SEDDIKI</t>
+  </si>
+  <si>
+    <t>BS 06</t>
+  </si>
+  <si>
+    <t>M2RT</t>
+  </si>
+  <si>
+    <t>Cours-Data Science in Telecommunication Industry: use cases</t>
+  </si>
+  <si>
+    <t>MESKINE</t>
+  </si>
+  <si>
+    <t>Cours-Digital Electronics</t>
+  </si>
+  <si>
+    <t>SEKKAL</t>
+  </si>
+  <si>
+    <t>Cours-Digital Signal Processing</t>
+  </si>
+  <si>
+    <t>Cours-Dispositifs (Passifs/Actifs) RF et Micro-ondes</t>
+  </si>
+  <si>
+    <t>TEHAMI</t>
+  </si>
+  <si>
+    <t>GHEZALI</t>
+  </si>
+  <si>
+    <t>Cours-English for Engineers</t>
+  </si>
+  <si>
+    <t>ADDAD</t>
+  </si>
+  <si>
+    <t>BENIEDDI</t>
+  </si>
+  <si>
+    <t>Cours-Object Oriented Programming</t>
+  </si>
+  <si>
+    <t>GRABA</t>
+  </si>
+  <si>
+    <t>Cours-Ondes et Propagation</t>
+  </si>
+  <si>
+    <t>AZZAZ RAHMANI</t>
+  </si>
+  <si>
+    <t>ZAOUI</t>
+  </si>
+  <si>
+    <t>Cours-Optimization Techniques and Algorithms</t>
+  </si>
+  <si>
+    <t>MAHIDDINE</t>
+  </si>
+  <si>
+    <t>Cours-Planification et optimisation des réseaux d'accès radio</t>
+  </si>
+  <si>
+    <t>Cours-Programmation avancée Python</t>
+  </si>
+  <si>
+    <t>BEDDAD</t>
+  </si>
+  <si>
+    <t>GHAZ</t>
+  </si>
+  <si>
+    <t>Cours-Propagation et Antennes</t>
+  </si>
+  <si>
+    <t>Cours-Radiocommunication</t>
+  </si>
+  <si>
+    <t>KANDOUCI</t>
+  </si>
+  <si>
+    <t>Cours-Réseaux IoT</t>
+  </si>
+  <si>
+    <t>Cours-Réseaux sans fil et réseaux mobiles</t>
+  </si>
+  <si>
+    <t>BOUZIANI</t>
+  </si>
+  <si>
+    <t>NAIMI</t>
+  </si>
+  <si>
+    <t>Cours-Respect des normes et règles d'éthique et d'intégrité</t>
+  </si>
+  <si>
+    <t>SABOUNDJI</t>
+  </si>
+  <si>
+    <t>Cours-Reverse engineering</t>
+  </si>
+  <si>
+    <t>Cours-RF Communication Fundamentals</t>
+  </si>
+  <si>
+    <t>Cours-Routage IP</t>
+  </si>
+  <si>
+    <t>ZERROUKI</t>
+  </si>
+  <si>
+    <t>Cours-Signaux aléatoires et Processus stochastiques</t>
+  </si>
+  <si>
+    <t>Cours-Supports de transmission</t>
+  </si>
+  <si>
+    <t>Cours-Système Linux</t>
+  </si>
+  <si>
+    <t>Cours-Systèmes embarqués et Télécommunications</t>
+  </si>
+  <si>
+    <t>Cours-Systèmes et réseaux de télécommunication</t>
+  </si>
+  <si>
+    <t>Cours-Technologie et Protocoles pour le multimédia</t>
+  </si>
+  <si>
+    <t>Cours-Technologies du Web</t>
+  </si>
+  <si>
+    <t>Cours-Téléphonie</t>
+  </si>
+  <si>
+    <t>FASSI</t>
+  </si>
+  <si>
+    <t>Cours-Traitement avancé du signal</t>
+  </si>
+  <si>
+    <t>BELLOULA</t>
+  </si>
+  <si>
+    <t>Cours-Vidéo et Audio sur IP</t>
+  </si>
+  <si>
+    <t>BS 16</t>
+  </si>
+  <si>
+    <t>TD-Antennas and Wireless Propagation</t>
+  </si>
+  <si>
+    <t>TD-Circuits programmables FPGA</t>
+  </si>
+  <si>
+    <t>TD-Communications Analogiques</t>
+  </si>
+  <si>
+    <t>TD-Communications numériques avancées</t>
+  </si>
+  <si>
+    <t>BOUDA</t>
+  </si>
+  <si>
+    <t>TD-Communications optiques</t>
+  </si>
+  <si>
+    <t>TD-Cryptographie et Sécurité Réseaux</t>
+  </si>
+  <si>
+    <t>TD-Digital Electronics</t>
+  </si>
+  <si>
+    <t>TD-Digital Signal Processing</t>
+  </si>
+  <si>
+    <t>TD-Dispositifs (Passifs/Actifs) RF et Micro-ondes</t>
+  </si>
+  <si>
+    <t>TD-Ondes et Propagation-G1</t>
+  </si>
+  <si>
+    <t>TD-Ondes et Propagation-G2</t>
+  </si>
+  <si>
+    <t>TD-Propagation et Antennes</t>
+  </si>
+  <si>
+    <t>TD-Radiocommunication</t>
+  </si>
+  <si>
+    <t>TD-Réseaux sans fil et réseaux mobiles</t>
+  </si>
+  <si>
+    <t>TD-RF Communication Fundamentals</t>
+  </si>
+  <si>
+    <t>TD-Routage IP</t>
+  </si>
+  <si>
+    <t>TD-Signaux aléatoires et Processus stochastiques</t>
+  </si>
+  <si>
+    <t>TD-Systèmes et réseaux de télécommunication-G1</t>
+  </si>
+  <si>
+    <t>TD-Systèmes et réseaux de télécommunication-G2</t>
+  </si>
+  <si>
+    <t>TD-Technologie et Protocoles pour le multimédia</t>
+  </si>
+  <si>
+    <t>TD-Technologies du Web</t>
+  </si>
+  <si>
+    <t>TD-Traitement avancé du signal</t>
+  </si>
+  <si>
+    <t>TD-Traitement du signal-G1</t>
+  </si>
+  <si>
+    <t>TD-Traitement du signal-G2</t>
+  </si>
+  <si>
+    <t>TD-Vidéo et Audio sur IP</t>
+  </si>
+  <si>
+    <t>TP-Analyse numérique 1-SG11/SG12</t>
+  </si>
+  <si>
+    <t>CC TLC2</t>
+  </si>
+  <si>
+    <t>TP-Antennas and Wireless Propagation-SG11/SG12</t>
+  </si>
+  <si>
+    <t>MOSTEFAOUI</t>
+  </si>
+  <si>
+    <t>Lab. B10</t>
+  </si>
+  <si>
+    <t>TP-Calculateurs et interfaçage-SG11/SG12</t>
+  </si>
+  <si>
+    <t>Lab. B15</t>
+  </si>
+  <si>
+    <t>TP-Calculateurs et interfaçage-SG21/SG22</t>
+  </si>
+  <si>
+    <t>TP-Circuits programmables FPGA-SG11/SG12</t>
+  </si>
+  <si>
+    <t>MELIANI</t>
+  </si>
+  <si>
+    <t>Lab. B07</t>
+  </si>
+  <si>
+    <t>TP-Communications Analogiques-SG11/SG12</t>
+  </si>
+  <si>
+    <t>Lab. B11</t>
+  </si>
+  <si>
+    <t>TP-Communications Analogiques-SG21/SG22</t>
+  </si>
+  <si>
+    <t>TP-Communications numériques avancées-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Communications optiques-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Cryptographie et Sécurité Réseaux-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Dessin Assisté par Ordinateur-SG11/SG12</t>
+  </si>
+  <si>
+    <t>CC Auto 3</t>
+  </si>
+  <si>
+    <t>TP-Digital Electronics-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Digital Signal Processing-SG11/SG12</t>
+  </si>
+  <si>
+    <t>CC Tel 1</t>
+  </si>
+  <si>
+    <t>TP-Dispositifs (Passifs/Actifs) RF et Micro-ondes-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Electricité fondamentale-SG11/SG12</t>
+  </si>
+  <si>
+    <t>FILALI</t>
+  </si>
+  <si>
+    <t>TP-Electronique fondamentale 1-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Electronique fondamentale 1-SG21/SG22</t>
+  </si>
+  <si>
+    <t>TP-Electrotechnique fondamentale 1-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Electrotechnique fondamentale 1-SG21/SG22</t>
+  </si>
+  <si>
+    <t>TP-Object Oriented Programming-SG11/SG12</t>
+  </si>
+  <si>
+    <t>CC Tel 2</t>
+  </si>
+  <si>
+    <t>TP-Ondes et Propagation-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Ondes et Propagation-SG21/SG22</t>
+  </si>
+  <si>
+    <t>TP-Ondes et vibrations-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Ondes et vibrations-SG21/SG22</t>
+  </si>
+  <si>
+    <t>TP-Optimization Techniques and Algorithms-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Planification et optimisation des réseaux d'accès radio-SG11/SG12</t>
+  </si>
+  <si>
+    <t>CC TLC1</t>
+  </si>
+  <si>
+    <t>TP-Programmation avancée Python-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Programmation python-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Programmation Python-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Programmation Python-SG21/SG22</t>
+  </si>
+  <si>
+    <t>TP-Réseaux IoT-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Réseaux sans fil et réseaux mobiles-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Reverse engineering-SG11/SG12</t>
+  </si>
+  <si>
+    <t>Lab</t>
+  </si>
+  <si>
+    <t>TP-RF Communication Fundamentals-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Routage IP-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Signaux aléatoires et Processus stochastiques-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Système Linux-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Systèmes embarqués et Télécommunications-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Technologies du Web et VoIP-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Traitement avancé du signal-SG11/SG12</t>
+  </si>
+  <si>
+    <t>CC Bloc B</t>
+  </si>
+  <si>
+    <t>TP-Traitement du signal-SG11/SG12</t>
+  </si>
+  <si>
+    <t>TP-Traitement du signal-SG21/SG22</t>
   </si>
 </sst>
 </file>
@@ -5400,6 +5895,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -5407,7 +5903,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -6028,14 +6523,14 @@
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6382,7 +6877,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H1231"/>
+  <dimension ref="A1:H1437"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="58" style="2" customWidth="1"/>
@@ -12470,7 +12965,7 @@
       <c r="E234" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F234" s="7" t="s">
+      <c r="F234" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G234" s="6" t="s">
@@ -12626,7 +13121,7 @@
       <c r="E240" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F240" s="7" t="s">
+      <c r="F240" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G240" s="6" t="s">
@@ -12730,7 +13225,7 @@
       <c r="E244" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F244" s="7" t="s">
+      <c r="F244" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G244" s="6" t="s">
@@ -12756,7 +13251,7 @@
       <c r="E245" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F245" s="7" t="s">
+      <c r="F245" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G245" s="6" t="s">
@@ -38402,11 +38897,5364 @@
         <v>929</v>
       </c>
     </row>
+    <row r="1232" customFormat="1" spans="1:8">
+      <c r="A1232" s="7" t="s">
+        <v>993</v>
+      </c>
+      <c r="B1232" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1232" s="7" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D1232" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1232" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1232" s="7" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G1232" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1232" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1233" customFormat="1" spans="1:8">
+      <c r="A1233" s="7" t="s">
+        <v>993</v>
+      </c>
+      <c r="B1233" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1233" s="7" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D1233" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1233" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1233" s="7" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G1233" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1233" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1234" customFormat="1" spans="1:8">
+      <c r="A1234" s="7" t="s">
+        <v>992</v>
+      </c>
+      <c r="B1234" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1234" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1234" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1234" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1234" s="7" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G1234" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1234" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1235" customFormat="1" spans="1:8">
+      <c r="A1235" s="7" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B1235" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1235" s="7" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D1235" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1235" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1235" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="G1235" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1235" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1236" customFormat="1" spans="1:8">
+      <c r="A1236" s="7" t="s">
+        <v>1792</v>
+      </c>
+      <c r="B1236" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1236" s="7" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D1236" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1236" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1236" s="7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G1236" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1236" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1237" customFormat="1" spans="1:8">
+      <c r="A1237" s="7" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B1237" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1237" s="7" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D1237" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1237" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1237" s="7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G1237" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1237" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1238" customFormat="1" spans="1:8">
+      <c r="A1238" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B1238" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1238" s="7" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D1238" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1238" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1238" s="7" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G1238" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1238" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1239" customFormat="1" spans="1:8">
+      <c r="A1239" s="7" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B1239" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1239" s="7" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D1239" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1239" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1239" s="7" t="s">
+        <v>1801</v>
+      </c>
+      <c r="G1239" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1239" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1240" customFormat="1" spans="1:8">
+      <c r="A1240" s="7" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B1240" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1240" s="7" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D1240" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1240" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1240" s="7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G1240" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1240" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1241" customFormat="1" spans="1:8">
+      <c r="A1241" s="7" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B1241" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1241" s="7" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D1241" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1241" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1241" s="7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G1241" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1241" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1242" customFormat="1" spans="1:8">
+      <c r="A1242" s="7" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B1242" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1242" s="7" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D1242" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1242" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1242" s="7" t="s">
+        <v>1801</v>
+      </c>
+      <c r="G1242" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1242" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1243" customFormat="1" spans="1:8">
+      <c r="A1243" s="7" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B1243" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1243" s="7" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D1243" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1243" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1243" s="7" t="s">
+        <v>1801</v>
+      </c>
+      <c r="G1243" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1243" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1244" customFormat="1" spans="1:8">
+      <c r="A1244" s="7" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B1244" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1244" s="7" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D1244" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1244" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1244" s="7" t="s">
+        <v>1808</v>
+      </c>
+      <c r="G1244" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1244" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1245" customFormat="1" spans="1:8">
+      <c r="A1245" s="7" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B1245" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1245" s="7" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D1245" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1245" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1245" s="7" t="s">
+        <v>1808</v>
+      </c>
+      <c r="G1245" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1245" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1246" customFormat="1" spans="1:8">
+      <c r="A1246" s="7" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B1246" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1246" s="7" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D1246" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1246" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1246" s="7" t="s">
+        <v>1812</v>
+      </c>
+      <c r="G1246" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1246" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1247" customFormat="1" spans="1:8">
+      <c r="A1247" s="7" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B1247" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1247" s="7" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D1247" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1247" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1247" s="7" t="s">
+        <v>1816</v>
+      </c>
+      <c r="G1247" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1247" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1248" customFormat="1" spans="1:8">
+      <c r="A1248" s="7" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B1248" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1248" s="7" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D1248" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1248" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1248" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="G1248" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1248" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1249" customFormat="1" spans="1:8">
+      <c r="A1249" s="7" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B1249" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1249" s="7" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D1249" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1249" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1249" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="G1249" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1249" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1250" customFormat="1" spans="1:8">
+      <c r="A1250" s="7" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B1250" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1250" s="7" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D1250" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1250" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1250" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="G1250" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1250" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1251" customFormat="1" spans="1:8">
+      <c r="A1251" s="7" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B1251" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1251" s="7" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D1251" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1251" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1251" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="G1251" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1251" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1252" customFormat="1" spans="1:8">
+      <c r="A1252" s="7" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B1252" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1252" s="7" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D1252" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1252" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1252" s="7" t="s">
+        <v>1812</v>
+      </c>
+      <c r="G1252" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1252" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1253" customFormat="1" spans="1:8">
+      <c r="A1253" s="7" t="s">
+        <v>998</v>
+      </c>
+      <c r="B1253" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1253" s="7" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D1253" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1253" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1253" s="7" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G1253" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1253" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1254" customFormat="1" spans="1:8">
+      <c r="A1254" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1254" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1254" s="7" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D1254" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1254" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1254" s="7" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G1254" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1254" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1255" customFormat="1" spans="1:8">
+      <c r="A1255" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1255" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1255" s="7" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D1255" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1255" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1255" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="G1255" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1255" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1256" customFormat="1" spans="1:8">
+      <c r="A1256" s="7" t="s">
+        <v>996</v>
+      </c>
+      <c r="B1256" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1256" s="7" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D1256" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1256" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1256" s="7" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G1256" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1256" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1257" customFormat="1" spans="1:8">
+      <c r="A1257" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1257" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1257" s="7" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D1257" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1257" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1257" s="7" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G1257" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1257" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1258" customFormat="1" spans="1:8">
+      <c r="A1258" s="7" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1258" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1258" s="7" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D1258" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1258" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1258" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="G1258" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1258" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1259" customFormat="1" spans="1:8">
+      <c r="A1259" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1259" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1259" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="D1259" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1259" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1259" s="7" t="s">
+        <v>1812</v>
+      </c>
+      <c r="G1259" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1259" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1260" customFormat="1" spans="1:8">
+      <c r="A1260" s="7" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B1260" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1260" s="7" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D1260" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1260" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1260" s="7" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G1260" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1260" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1261" customFormat="1" spans="1:8">
+      <c r="A1261" s="7" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B1261" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1261" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1261" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1261" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1261" s="7" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G1261" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1261" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1262" customFormat="1" spans="1:8">
+      <c r="A1262" s="7" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B1262" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1262" s="7" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D1262" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1262" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1262" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="G1262" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1262" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1263" customFormat="1" spans="1:8">
+      <c r="A1263" s="7" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B1263" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1263" s="7" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D1263" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1263" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1263" s="7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G1263" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1263" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1264" customFormat="1" spans="1:8">
+      <c r="A1264" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1264" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1264" s="7" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D1264" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1264" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1264" s="7" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G1264" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1264" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1265" customFormat="1" spans="1:8">
+      <c r="A1265" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1265" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1265" s="7" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D1265" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1265" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1265" s="7" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G1265" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1265" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1266" customFormat="1" spans="1:8">
+      <c r="A1266" s="7" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B1266" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1266" s="7" t="s">
+        <v>1835</v>
+      </c>
+      <c r="D1266" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1266" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1266" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="G1266" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1266" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1267" customFormat="1" spans="1:8">
+      <c r="A1267" s="7" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B1267" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1267" s="7" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D1267" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1267" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1267" s="7" t="s">
+        <v>1812</v>
+      </c>
+      <c r="G1267" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1267" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1268" customFormat="1" spans="1:8">
+      <c r="A1268" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1268" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1268" s="7" t="s">
+        <v>1835</v>
+      </c>
+      <c r="D1268" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1268" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1268" s="7" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G1268" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1268" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1269" customFormat="1" spans="1:8">
+      <c r="A1269" s="7" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B1269" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1269" s="7" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D1269" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1269" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1269" s="7" t="s">
+        <v>1801</v>
+      </c>
+      <c r="G1269" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1269" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1270" customFormat="1" spans="1:8">
+      <c r="A1270" s="7" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B1270" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1270" s="7" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D1270" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1270" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1270" s="7" t="s">
+        <v>1808</v>
+      </c>
+      <c r="G1270" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1270" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1271" customFormat="1" spans="1:8">
+      <c r="A1271" s="7" t="s">
+        <v>994</v>
+      </c>
+      <c r="B1271" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1271" s="7" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D1271" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1271" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1271" s="7" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G1271" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1271" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1272" customFormat="1" spans="1:8">
+      <c r="A1272" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1272" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1272" s="7" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D1272" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1272" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1272" s="7" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G1272" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1272" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1273" customFormat="1" spans="1:8">
+      <c r="A1273" s="7" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B1273" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1273" s="7" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D1273" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1273" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1273" s="7" t="s">
+        <v>1808</v>
+      </c>
+      <c r="G1273" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1273" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1274" customFormat="1" spans="1:8">
+      <c r="A1274" s="7" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B1274" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1274" s="7" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D1274" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1274" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1274" s="7" t="s">
+        <v>1801</v>
+      </c>
+      <c r="G1274" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1274" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1275" customFormat="1" spans="1:8">
+      <c r="A1275" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1275" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1275" s="7" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D1275" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1275" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1275" s="7" t="s">
+        <v>1812</v>
+      </c>
+      <c r="G1275" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1275" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1276" customFormat="1" spans="1:8">
+      <c r="A1276" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1276" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1276" s="7" t="s">
+        <v>1842</v>
+      </c>
+      <c r="D1276" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1276" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1276" s="7" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G1276" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1276" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1277" customFormat="1" spans="1:8">
+      <c r="A1277" s="7" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B1277" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1277" s="7" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D1277" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1277" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1277" s="7" t="s">
+        <v>1816</v>
+      </c>
+      <c r="G1277" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1277" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1278" customFormat="1" spans="1:8">
+      <c r="A1278" s="7" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B1278" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1278" s="7" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D1278" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1278" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1278" s="7" t="s">
+        <v>1812</v>
+      </c>
+      <c r="G1278" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1278" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1279" customFormat="1" spans="1:8">
+      <c r="A1279" s="7" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B1279" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1279" s="7" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D1279" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1279" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1279" s="7" t="s">
+        <v>1812</v>
+      </c>
+      <c r="G1279" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1279" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1280" customFormat="1" spans="1:8">
+      <c r="A1280" s="7" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B1280" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1280" s="7" t="s">
+        <v>1846</v>
+      </c>
+      <c r="D1280" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1280" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1280" s="7" t="s">
+        <v>1816</v>
+      </c>
+      <c r="G1280" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1280" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1281" customFormat="1" spans="1:8">
+      <c r="A1281" s="7" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B1281" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1281" s="7" t="s">
+        <v>1846</v>
+      </c>
+      <c r="D1281" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1281" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1281" s="7" t="s">
+        <v>1816</v>
+      </c>
+      <c r="G1281" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1281" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1282" customFormat="1" spans="1:8">
+      <c r="A1282" s="7" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B1282" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1282" s="7" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D1282" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1282" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1282" s="7" t="s">
+        <v>1801</v>
+      </c>
+      <c r="G1282" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1282" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1283" customFormat="1" spans="1:8">
+      <c r="A1283" s="7" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B1283" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1283" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="D1283" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1283" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1283" s="7" t="s">
+        <v>1808</v>
+      </c>
+      <c r="G1283" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1283" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1284" customFormat="1" spans="1:8">
+      <c r="A1284" s="7" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B1284" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1284" s="7" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D1284" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1284" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1284" s="7" t="s">
+        <v>1812</v>
+      </c>
+      <c r="G1284" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1284" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1285" customFormat="1" spans="1:8">
+      <c r="A1285" s="7" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B1285" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1285" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1285" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1285" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1285" s="7" t="s">
+        <v>1816</v>
+      </c>
+      <c r="G1285" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1285" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1286" customFormat="1" spans="1:8">
+      <c r="A1286" s="7" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B1286" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1286" s="7" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D1286" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1286" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1286" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="G1286" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1286" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1287" customFormat="1" spans="1:8">
+      <c r="A1287" s="7" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B1287" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1287" s="7" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D1287" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1287" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1287" s="7" t="s">
+        <v>1808</v>
+      </c>
+      <c r="G1287" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1287" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1288" customFormat="1" spans="1:8">
+      <c r="A1288" s="7" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B1288" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1288" s="7" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D1288" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1288" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1288" s="7" t="s">
+        <v>1801</v>
+      </c>
+      <c r="G1288" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1288" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1289" customFormat="1" spans="1:8">
+      <c r="A1289" s="7" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B1289" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1289" s="7" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D1289" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1289" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1289" s="7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G1289" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1289" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1290" customFormat="1" spans="1:8">
+      <c r="A1290" s="7" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B1290" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1290" s="7" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D1290" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1290" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1290" s="7" t="s">
+        <v>1808</v>
+      </c>
+      <c r="G1290" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1290" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1291" customFormat="1" spans="1:8">
+      <c r="A1291" s="7" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B1291" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1291" s="7" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D1291" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1291" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1291" s="7" t="s">
+        <v>1801</v>
+      </c>
+      <c r="G1291" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1291" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1292" customFormat="1" spans="1:8">
+      <c r="A1292" s="7" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B1292" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1292" s="7" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D1292" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1292" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1292" s="7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G1292" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1292" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1293" customFormat="1" spans="1:8">
+      <c r="A1293" s="7" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B1293" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1293" s="7" t="s">
+        <v>1842</v>
+      </c>
+      <c r="D1293" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1293" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1293" s="7" t="s">
+        <v>1812</v>
+      </c>
+      <c r="G1293" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1293" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1294" customFormat="1" spans="1:8">
+      <c r="A1294" s="7" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B1294" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1294" s="7" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D1294" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1294" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1294" s="7" t="s">
+        <v>1816</v>
+      </c>
+      <c r="G1294" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1294" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1295" customFormat="1" spans="1:8">
+      <c r="A1295" s="7" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B1295" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1295" s="7" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D1295" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1295" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1295" s="7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G1295" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1295" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1296" customFormat="1" spans="1:8">
+      <c r="A1296" s="7" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B1296" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1296" s="7" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D1296" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1296" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1296" s="7" t="s">
+        <v>1808</v>
+      </c>
+      <c r="G1296" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1296" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1297" customFormat="1" spans="1:8">
+      <c r="A1297" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B1297" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1297" s="7" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D1297" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1297" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1297" s="7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G1297" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1297" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1298" customFormat="1" spans="1:8">
+      <c r="A1298" s="7" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B1298" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1298" s="7" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D1298" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1298" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1298" s="7" t="s">
+        <v>1816</v>
+      </c>
+      <c r="G1298" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1298" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1299" customFormat="1" spans="1:8">
+      <c r="A1299" s="7" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1299" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1299" s="7" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D1299" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1299" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1299" s="7" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G1299" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1299" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1300" customFormat="1" spans="1:8">
+      <c r="A1300" s="7" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1300" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1300" s="7" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D1300" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1300" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1300" s="7" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G1300" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1300" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1301" customFormat="1" spans="1:8">
+      <c r="A1301" s="7" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B1301" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1301" s="7" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D1301" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1301" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1301" s="7" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G1301" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1301" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1302" customFormat="1" spans="1:8">
+      <c r="A1302" s="7" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B1302" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1302" s="7" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D1302" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1302" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1302" s="7" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G1302" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1302" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1303" customFormat="1" spans="1:8">
+      <c r="A1303" s="7" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B1303" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1303" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1303" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1303" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1303" s="7" t="s">
+        <v>1865</v>
+      </c>
+      <c r="G1303" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1303" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1304" customFormat="1" spans="1:8">
+      <c r="A1304" s="7" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B1304" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1304" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1304" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1304" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1304" s="7" t="s">
+        <v>1865</v>
+      </c>
+      <c r="G1304" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1304" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1305" customFormat="1" spans="1:8">
+      <c r="A1305" s="7" t="s">
+        <v>986</v>
+      </c>
+      <c r="B1305" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1305" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1305" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1305" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1305" s="7" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G1305" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1305" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1306" customFormat="1" spans="1:8">
+      <c r="A1306" s="7" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B1306" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1306" s="7" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D1306" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1306" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1306" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="G1306" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1306" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1307" customFormat="1" spans="1:8">
+      <c r="A1307" s="7" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B1307" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1307" s="7" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D1307" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1307" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1307" s="7" t="s">
+        <v>1801</v>
+      </c>
+      <c r="G1307" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1307" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1308" customFormat="1" spans="1:8">
+      <c r="A1308" s="7" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B1308" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1308" s="7" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D1308" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1308" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1308" s="7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G1308" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1308" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1309" customFormat="1" spans="1:8">
+      <c r="A1309" s="7" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B1309" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1309" s="7" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D1309" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1309" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1309" s="7" t="s">
+        <v>1801</v>
+      </c>
+      <c r="G1309" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1309" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1310" customFormat="1" spans="1:8">
+      <c r="A1310" s="7" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B1310" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1310" s="7" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D1310" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1310" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1310" s="7" t="s">
+        <v>1808</v>
+      </c>
+      <c r="G1310" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1310" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1311" customFormat="1" spans="1:8">
+      <c r="A1311" s="7" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B1311" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1311" s="7" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D1311" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1311" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1311" s="7" t="s">
+        <v>1812</v>
+      </c>
+      <c r="G1311" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1311" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1312" customFormat="1" spans="1:8">
+      <c r="A1312" s="7" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B1312" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1312" s="7" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D1312" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1312" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1312" s="7" t="s">
+        <v>1816</v>
+      </c>
+      <c r="G1312" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1312" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1313" customFormat="1" spans="1:8">
+      <c r="A1313" s="7" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B1313" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1313" s="7" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D1313" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1313" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1313" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="G1313" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1313" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1314" customFormat="1" spans="1:8">
+      <c r="A1314" s="7" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B1314" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1314" s="7" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D1314" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1314" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1314" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="G1314" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1314" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1315" customFormat="1" spans="1:8">
+      <c r="A1315" s="7" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B1315" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1315" s="7" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D1315" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1315" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1315" s="7" t="s">
+        <v>1812</v>
+      </c>
+      <c r="G1315" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1315" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1316" customFormat="1" spans="1:8">
+      <c r="A1316" s="7" t="s">
+        <v>969</v>
+      </c>
+      <c r="B1316" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1316" s="7" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D1316" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1316" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1316" s="7" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G1316" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1316" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1317" customFormat="1" spans="1:8">
+      <c r="A1317" s="7" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B1317" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1317" s="7" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D1317" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1317" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1317" s="7" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G1317" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1317" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1318" customFormat="1" spans="1:8">
+      <c r="A1318" s="7" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B1318" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1318" s="7" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D1318" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1318" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1318" s="7" t="s">
+        <v>1865</v>
+      </c>
+      <c r="G1318" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1318" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1319" customFormat="1" spans="1:8">
+      <c r="A1319" s="7" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B1319" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1319" s="7" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D1319" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1319" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1319" s="7" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G1319" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1319" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1320" customFormat="1" spans="1:8">
+      <c r="A1320" s="7" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B1320" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1320" s="7" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D1320" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1320" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1320" s="7" t="s">
+        <v>1865</v>
+      </c>
+      <c r="G1320" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1320" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1321" customFormat="1" spans="1:8">
+      <c r="A1321" s="7" t="s">
+        <v>971</v>
+      </c>
+      <c r="B1321" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1321" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1321" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1321" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1321" s="7" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G1321" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1321" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1322" customFormat="1" spans="1:8">
+      <c r="A1322" s="7" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B1322" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1322" s="7" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D1322" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1322" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1322" s="7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G1322" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1322" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1323" customFormat="1" spans="1:8">
+      <c r="A1323" s="7" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B1323" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1323" s="7" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D1323" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1323" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1323" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="G1323" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1323" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1324" customFormat="1" spans="1:8">
+      <c r="A1324" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1324" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1324" s="7" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D1324" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1324" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1324" s="7" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G1324" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1324" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1325" customFormat="1" spans="1:8">
+      <c r="A1325" s="7" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B1325" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1325" s="7" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D1325" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1325" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1325" s="7" t="s">
+        <v>1801</v>
+      </c>
+      <c r="G1325" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1325" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1326" customFormat="1" spans="1:8">
+      <c r="A1326" s="7" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B1326" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1326" s="7" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D1326" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1326" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1326" s="7" t="s">
+        <v>1865</v>
+      </c>
+      <c r="G1326" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1326" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1327" customFormat="1" spans="1:8">
+      <c r="A1327" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="B1327" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1327" s="7" t="s">
+        <v>1835</v>
+      </c>
+      <c r="D1327" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1327" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1327" s="7" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G1327" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1327" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1328" customFormat="1" spans="1:8">
+      <c r="A1328" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1328" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1328" s="7" t="s">
+        <v>1835</v>
+      </c>
+      <c r="D1328" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1328" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1328" s="7" t="s">
+        <v>1865</v>
+      </c>
+      <c r="G1328" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1328" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1329" customFormat="1" spans="1:8">
+      <c r="A1329" s="7" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B1329" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1329" s="7" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D1329" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1329" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1329" s="7" t="s">
+        <v>1808</v>
+      </c>
+      <c r="G1329" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1329" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1330" customFormat="1" spans="1:8">
+      <c r="A1330" s="7" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B1330" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1330" s="7" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D1330" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1330" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1330" s="7" t="s">
+        <v>1801</v>
+      </c>
+      <c r="G1330" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1330" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1331" customFormat="1" spans="1:8">
+      <c r="A1331" s="7" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B1331" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1331" s="7" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D1331" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1331" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1331" s="7" t="s">
+        <v>1812</v>
+      </c>
+      <c r="G1331" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1331" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1332" customFormat="1" spans="1:8">
+      <c r="A1332" s="7" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B1332" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1332" s="7" t="s">
+        <v>1846</v>
+      </c>
+      <c r="D1332" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1332" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1332" s="7" t="s">
+        <v>1816</v>
+      </c>
+      <c r="G1332" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1332" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1333" customFormat="1" spans="1:8">
+      <c r="A1333" s="7" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B1333" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1333" s="7" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D1333" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1333" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1333" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="G1333" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1333" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1334" customFormat="1" spans="1:8">
+      <c r="A1334" s="7" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B1334" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1334" s="7" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D1334" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1334" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1334" s="7" t="s">
+        <v>1808</v>
+      </c>
+      <c r="G1334" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1334" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1335" customFormat="1" spans="1:8">
+      <c r="A1335" s="7" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B1335" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1335" s="7" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D1335" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1335" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1335" s="7" t="s">
+        <v>1801</v>
+      </c>
+      <c r="G1335" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1335" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1336" customFormat="1" spans="1:8">
+      <c r="A1336" s="7" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B1336" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1336" s="7" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D1336" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1336" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1336" s="7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G1336" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1336" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1337" customFormat="1" spans="1:8">
+      <c r="A1337" s="7" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B1337" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1337" s="7" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D1337" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1337" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1337" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="G1337" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1337" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1338" customFormat="1" spans="1:8">
+      <c r="A1338" s="7" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B1338" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1338" s="7" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D1338" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1338" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1338" s="7" t="s">
+        <v>1812</v>
+      </c>
+      <c r="G1338" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1338" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1339" customFormat="1" spans="1:8">
+      <c r="A1339" s="7" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B1339" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1339" s="7" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D1339" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1339" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1339" s="7" t="s">
+        <v>1816</v>
+      </c>
+      <c r="G1339" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1339" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1340" customFormat="1" spans="1:8">
+      <c r="A1340" s="7" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B1340" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1340" s="7" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D1340" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1340" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1340" s="7" t="s">
+        <v>1808</v>
+      </c>
+      <c r="G1340" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1340" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1341" customFormat="1" spans="1:8">
+      <c r="A1341" s="7" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B1341" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1341" s="7" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D1341" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1341" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1341" s="7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G1341" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1341" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1342" customFormat="1" spans="1:8">
+      <c r="A1342" s="7" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B1342" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1342" s="7" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D1342" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1342" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1342" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="G1342" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1342" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1343" customFormat="1" spans="1:8">
+      <c r="A1343" s="7" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B1343" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1343" s="7" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D1343" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1343" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1343" s="7" t="s">
+        <v>1816</v>
+      </c>
+      <c r="G1343" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1343" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1344" customFormat="1" spans="1:8">
+      <c r="A1344" s="7" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B1344" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1344" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="D1344" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1344" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1344" s="7" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G1344" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1344" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1345" customFormat="1" spans="1:8">
+      <c r="A1345" s="7" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B1345" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1345" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="D1345" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1345" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1345" s="7" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G1345" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1345" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1346" customFormat="1" spans="1:8">
+      <c r="A1346" s="7" t="s">
+        <v>1894</v>
+      </c>
+      <c r="B1346" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1346" s="7" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D1346" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1346" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1346" s="7" t="s">
+        <v>1896</v>
+      </c>
+      <c r="G1346" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1346" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1347" customFormat="1" spans="1:8">
+      <c r="A1347" s="7" t="s">
+        <v>1894</v>
+      </c>
+      <c r="B1347" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1347" s="7" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D1347" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1347" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1347" s="7" t="s">
+        <v>1896</v>
+      </c>
+      <c r="G1347" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1347" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1348" customFormat="1" spans="1:8">
+      <c r="A1348" s="7" t="s">
+        <v>1897</v>
+      </c>
+      <c r="B1348" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1348" s="7" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D1348" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1348" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1348" s="7" t="s">
+        <v>1898</v>
+      </c>
+      <c r="G1348" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1348" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1349" customFormat="1" spans="1:8">
+      <c r="A1349" s="7" t="s">
+        <v>1897</v>
+      </c>
+      <c r="B1349" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1349" s="7" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D1349" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1349" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1349" s="7" t="s">
+        <v>1898</v>
+      </c>
+      <c r="G1349" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1349" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1350" customFormat="1" spans="1:8">
+      <c r="A1350" s="7" t="s">
+        <v>1899</v>
+      </c>
+      <c r="B1350" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1350" s="7" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D1350" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1350" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1350" s="7" t="s">
+        <v>1898</v>
+      </c>
+      <c r="G1350" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1350" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1351" customFormat="1" spans="1:8">
+      <c r="A1351" s="7" t="s">
+        <v>1899</v>
+      </c>
+      <c r="B1351" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1351" s="7" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D1351" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1351" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1351" s="7" t="s">
+        <v>1898</v>
+      </c>
+      <c r="G1351" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1351" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1352" customFormat="1" spans="1:8">
+      <c r="A1352" s="7" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B1352" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1352" s="7" t="s">
+        <v>1901</v>
+      </c>
+      <c r="D1352" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1352" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1352" s="7" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G1352" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1352" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1353" customFormat="1" spans="1:8">
+      <c r="A1353" s="7" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B1353" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1353" s="7" t="s">
+        <v>1901</v>
+      </c>
+      <c r="D1353" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1353" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1353" s="7" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G1353" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1353" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1354" customFormat="1" spans="1:8">
+      <c r="A1354" s="7" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B1354" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1354" s="7" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D1354" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1354" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1354" s="7" t="s">
+        <v>1904</v>
+      </c>
+      <c r="G1354" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1354" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1355" customFormat="1" spans="1:8">
+      <c r="A1355" s="7" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B1355" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1355" s="7" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D1355" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1355" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1355" s="7" t="s">
+        <v>1904</v>
+      </c>
+      <c r="G1355" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1355" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1356" customFormat="1" spans="1:8">
+      <c r="A1356" s="7" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B1356" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1356" s="7" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D1356" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1356" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1356" s="7" t="s">
+        <v>1904</v>
+      </c>
+      <c r="G1356" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1356" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1357" customFormat="1" spans="1:8">
+      <c r="A1357" s="7" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B1357" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1357" s="7" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D1357" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1357" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1357" s="7" t="s">
+        <v>1904</v>
+      </c>
+      <c r="G1357" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1357" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1358" customFormat="1" spans="1:8">
+      <c r="A1358" s="7" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B1358" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1358" s="7" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D1358" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1358" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1358" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G1358" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1358" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1359" customFormat="1" spans="1:8">
+      <c r="A1359" s="7" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B1359" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1359" s="7" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D1359" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1359" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1359" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G1359" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1359" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1360" customFormat="1" spans="1:8">
+      <c r="A1360" s="7" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B1360" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1360" s="7" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D1360" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1360" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1360" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G1360" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1360" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1361" customFormat="1" spans="1:8">
+      <c r="A1361" s="7" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B1361" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1361" s="7" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D1361" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1361" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1361" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G1361" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1361" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1362" customFormat="1" spans="1:8">
+      <c r="A1362" s="7" t="s">
+        <v>1907</v>
+      </c>
+      <c r="B1362" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1362" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1362" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1362" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1362" s="7" t="s">
+        <v>1896</v>
+      </c>
+      <c r="G1362" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1362" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1363" customFormat="1" spans="1:8">
+      <c r="A1363" s="7" t="s">
+        <v>1907</v>
+      </c>
+      <c r="B1363" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1363" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1363" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1363" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1363" s="7" t="s">
+        <v>1896</v>
+      </c>
+      <c r="G1363" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1363" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1364" customFormat="1" spans="1:8">
+      <c r="A1364" s="7" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B1364" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1364" s="7" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D1364" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1364" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1364" s="7" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G1364" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1364" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1365" customFormat="1" spans="1:8">
+      <c r="A1365" s="7" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B1365" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1365" s="7" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D1365" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1365" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1365" s="7" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G1365" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1365" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1366" customFormat="1" spans="1:8">
+      <c r="A1366" s="7" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B1366" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1366" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1366" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1366" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1366" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="G1366" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1366" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1367" customFormat="1" spans="1:8">
+      <c r="A1367" s="7" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B1367" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1367" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1367" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1367" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1367" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="G1367" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1367" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1368" customFormat="1" spans="1:8">
+      <c r="A1368" s="7" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B1368" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1368" s="7" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D1368" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1368" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1368" s="7" t="s">
+        <v>1898</v>
+      </c>
+      <c r="G1368" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1368" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1369" customFormat="1" spans="1:8">
+      <c r="A1369" s="7" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B1369" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1369" s="7" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D1369" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1369" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1369" s="7" t="s">
+        <v>1898</v>
+      </c>
+      <c r="G1369" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1369" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1370" customFormat="1" spans="1:8">
+      <c r="A1370" s="7" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B1370" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1370" s="7" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D1370" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1370" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1370" s="7" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G1370" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1370" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1371" customFormat="1" spans="1:8">
+      <c r="A1371" s="7" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B1371" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1371" s="7" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D1371" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1371" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1371" s="7" t="s">
+        <v>1913</v>
+      </c>
+      <c r="G1371" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1371" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1372" customFormat="1" spans="1:8">
+      <c r="A1372" s="7" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B1372" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1372" s="7" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D1372" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1372" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1372" s="7" t="s">
+        <v>1896</v>
+      </c>
+      <c r="G1372" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1372" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1373" customFormat="1" spans="1:8">
+      <c r="A1373" s="7" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B1373" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1373" s="7" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D1373" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1373" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1373" s="7" t="s">
+        <v>1896</v>
+      </c>
+      <c r="G1373" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1373" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1374" customFormat="1" spans="1:8">
+      <c r="A1374" s="7" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B1374" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1374" s="7" t="s">
+        <v>1916</v>
+      </c>
+      <c r="D1374" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1374" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1374" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="G1374" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1374" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1375" customFormat="1" spans="1:8">
+      <c r="A1375" s="7" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B1375" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1375" s="7" t="s">
+        <v>1916</v>
+      </c>
+      <c r="D1375" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1375" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1375" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="G1375" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1375" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1376" customFormat="1" spans="1:8">
+      <c r="A1376" s="7" t="s">
+        <v>1917</v>
+      </c>
+      <c r="B1376" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1376" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1376" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1376" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1376" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="G1376" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1376" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1377" customFormat="1" spans="1:8">
+      <c r="A1377" s="7" t="s">
+        <v>1917</v>
+      </c>
+      <c r="B1377" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1377" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1377" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1377" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1377" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="G1377" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1377" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1378" customFormat="1" spans="1:8">
+      <c r="A1378" s="7" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B1378" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1378" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1378" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1378" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1378" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="G1378" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1378" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1379" customFormat="1" spans="1:8">
+      <c r="A1379" s="7" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B1379" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1379" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1379" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1379" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1379" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="G1379" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1379" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1380" customFormat="1" spans="1:8">
+      <c r="A1380" s="7" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B1380" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1380" s="7" t="s">
+        <v>1916</v>
+      </c>
+      <c r="D1380" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1380" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1380" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1380" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1380" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1381" customFormat="1" spans="1:8">
+      <c r="A1381" s="7" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B1381" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1381" s="7" t="s">
+        <v>1916</v>
+      </c>
+      <c r="D1381" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1381" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1381" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1381" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1381" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1382" customFormat="1" spans="1:8">
+      <c r="A1382" s="7" t="s">
+        <v>1920</v>
+      </c>
+      <c r="B1382" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1382" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1382" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1382" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1382" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1382" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1382" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1383" customFormat="1" spans="1:8">
+      <c r="A1383" s="7" t="s">
+        <v>1920</v>
+      </c>
+      <c r="B1383" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1383" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1383" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1383" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1383" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1383" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1383" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1384" customFormat="1" spans="1:8">
+      <c r="A1384" s="7" t="s">
+        <v>1921</v>
+      </c>
+      <c r="B1384" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1384" s="7" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D1384" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1384" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1384" s="7" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G1384" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1384" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1385" customFormat="1" spans="1:8">
+      <c r="A1385" s="7" t="s">
+        <v>1921</v>
+      </c>
+      <c r="B1385" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1385" s="7" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D1385" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1385" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1385" s="7" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G1385" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1385" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1386" customFormat="1" spans="1:8">
+      <c r="A1386" s="7" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B1386" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1386" s="7" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D1386" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1386" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1386" s="7" t="s">
+        <v>1896</v>
+      </c>
+      <c r="G1386" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1386" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1387" customFormat="1" spans="1:8">
+      <c r="A1387" s="7" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B1387" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1387" s="7" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D1387" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1387" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1387" s="7" t="s">
+        <v>1896</v>
+      </c>
+      <c r="G1387" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1387" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1388" customFormat="1" spans="1:8">
+      <c r="A1388" s="7" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B1388" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1388" s="7" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D1388" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1388" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1388" s="7" t="s">
+        <v>1896</v>
+      </c>
+      <c r="G1388" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1388" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1389" customFormat="1" spans="1:8">
+      <c r="A1389" s="7" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B1389" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1389" s="7" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D1389" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1389" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1389" s="7" t="s">
+        <v>1896</v>
+      </c>
+      <c r="G1389" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1389" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1390" customFormat="1" spans="1:8">
+      <c r="A1390" s="7" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B1390" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1390" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1390" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1390" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1390" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="G1390" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1390" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1391" customFormat="1" spans="1:8">
+      <c r="A1391" s="7" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B1391" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1391" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1391" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1391" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1391" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="G1391" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1391" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1392" customFormat="1" spans="1:8">
+      <c r="A1392" s="7" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B1392" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1392" s="7" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D1392" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1392" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1392" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="G1392" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1392" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1393" customFormat="1" spans="1:8">
+      <c r="A1393" s="7" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B1393" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1393" s="7" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D1393" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1393" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1393" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="G1393" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1393" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1394" customFormat="1" spans="1:8">
+      <c r="A1394" s="7" t="s">
+        <v>1926</v>
+      </c>
+      <c r="B1394" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1394" s="7" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D1394" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1394" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1394" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="G1394" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1394" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1395" customFormat="1" spans="1:8">
+      <c r="A1395" s="7" t="s">
+        <v>1926</v>
+      </c>
+      <c r="B1395" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1395" s="7" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D1395" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1395" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1395" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="G1395" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1395" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1396" customFormat="1" spans="1:8">
+      <c r="A1396" s="7" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B1396" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1396" s="7" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D1396" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1396" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1396" s="7" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G1396" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1396" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1397" customFormat="1" spans="1:8">
+      <c r="A1397" s="7" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B1397" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1397" s="7" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D1397" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1397" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1397" s="7" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G1397" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1397" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1398" customFormat="1" spans="1:8">
+      <c r="A1398" s="7" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B1398" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1398" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1398" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1398" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1398" s="7" t="s">
+        <v>1929</v>
+      </c>
+      <c r="G1398" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1398" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1399" customFormat="1" spans="1:8">
+      <c r="A1399" s="7" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B1399" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1399" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1399" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1399" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1399" s="7" t="s">
+        <v>1929</v>
+      </c>
+      <c r="G1399" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1399" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1400" customFormat="1" spans="1:8">
+      <c r="A1400" s="7" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B1400" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1400" s="7" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D1400" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1400" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1400" s="7" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G1400" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1400" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1401" customFormat="1" spans="1:8">
+      <c r="A1401" s="7" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B1401" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1401" s="7" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D1401" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1401" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1401" s="7" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G1401" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1401" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1402" customFormat="1" spans="1:8">
+      <c r="A1402" s="7" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B1402" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1402" s="7" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D1402" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1402" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1402" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G1402" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1402" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1403" customFormat="1" spans="1:8">
+      <c r="A1403" s="7" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B1403" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1403" s="7" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D1403" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1403" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1403" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G1403" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1403" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1404" customFormat="1" spans="1:8">
+      <c r="A1404" s="7" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B1404" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1404" s="7" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D1404" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1404" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1404" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G1404" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1404" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1405" customFormat="1" spans="1:8">
+      <c r="A1405" s="7" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B1405" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1405" s="7" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D1405" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1405" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1405" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G1405" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H1405" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1406" customFormat="1" spans="1:8">
+      <c r="A1406" s="7" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B1406" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1406" s="7" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D1406" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1406" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1406" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G1406" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1406" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1407" customFormat="1" spans="1:8">
+      <c r="A1407" s="7" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B1407" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1407" s="7" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D1407" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1407" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1407" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G1407" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1407" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1408" customFormat="1" spans="1:8">
+      <c r="A1408" s="7" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B1408" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1408" s="7" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D1408" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1408" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1408" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G1408" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1408" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1409" customFormat="1" spans="1:8">
+      <c r="A1409" s="7" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B1409" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1409" s="7" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D1409" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1409" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1409" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G1409" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H1409" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1410" customFormat="1" spans="1:8">
+      <c r="A1410" s="7" t="s">
+        <v>1934</v>
+      </c>
+      <c r="B1410" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1410" s="7" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D1410" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1410" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1410" s="7" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G1410" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1410" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1411" customFormat="1" spans="1:8">
+      <c r="A1411" s="7" t="s">
+        <v>1934</v>
+      </c>
+      <c r="B1411" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1411" s="7" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D1411" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1411" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1411" s="7" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G1411" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1411" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1412" customFormat="1" spans="1:8">
+      <c r="A1412" s="7" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B1412" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1412" s="7" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D1412" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1412" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1412" s="7" t="s">
+        <v>1929</v>
+      </c>
+      <c r="G1412" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1412" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1413" customFormat="1" spans="1:8">
+      <c r="A1413" s="7" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B1413" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1413" s="7" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D1413" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1413" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1413" s="7" t="s">
+        <v>1929</v>
+      </c>
+      <c r="G1413" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1413" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1414" customFormat="1" spans="1:8">
+      <c r="A1414" s="7" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B1414" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1414" s="7" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D1414" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1414" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1414" s="7" t="s">
+        <v>1929</v>
+      </c>
+      <c r="G1414" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1414" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1415" customFormat="1" spans="1:8">
+      <c r="A1415" s="7" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B1415" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1415" s="7" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D1415" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1415" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1415" s="7" t="s">
+        <v>1929</v>
+      </c>
+      <c r="G1415" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1415" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1416" customFormat="1" spans="1:8">
+      <c r="A1416" s="7" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B1416" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1416" s="7" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D1416" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1416" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1416" s="7" t="s">
+        <v>1937</v>
+      </c>
+      <c r="G1416" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1416" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1417" customFormat="1" spans="1:8">
+      <c r="A1417" s="7" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B1417" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1417" s="7" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D1417" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1417" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1417" s="7" t="s">
+        <v>1937</v>
+      </c>
+      <c r="G1417" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1417" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1418" customFormat="1" spans="1:8">
+      <c r="A1418" s="7" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B1418" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1418" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1418" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1418" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1418" s="7" t="s">
+        <v>1937</v>
+      </c>
+      <c r="G1418" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1418" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1419" customFormat="1" spans="1:8">
+      <c r="A1419" s="7" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B1419" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1419" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1419" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1419" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1419" s="7" t="s">
+        <v>1937</v>
+      </c>
+      <c r="G1419" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1419" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1420" customFormat="1" spans="1:8">
+      <c r="A1420" s="7" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B1420" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1420" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1420" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1420" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1420" s="7" t="s">
+        <v>1937</v>
+      </c>
+      <c r="G1420" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1420" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1421" customFormat="1" spans="1:8">
+      <c r="A1421" s="7" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B1421" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1421" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D1421" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1421" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1421" s="7" t="s">
+        <v>1937</v>
+      </c>
+      <c r="G1421" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H1421" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1422" customFormat="1" spans="1:8">
+      <c r="A1422" s="7" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B1422" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1422" s="7" t="s">
+        <v>1846</v>
+      </c>
+      <c r="D1422" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1422" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1422" s="7" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G1422" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1422" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1423" customFormat="1" spans="1:8">
+      <c r="A1423" s="7" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B1423" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1423" s="7" t="s">
+        <v>1846</v>
+      </c>
+      <c r="D1423" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1423" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1423" s="7" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G1423" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1423" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1424" customFormat="1" spans="1:8">
+      <c r="A1424" s="7" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B1424" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1424" s="7" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D1424" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1424" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1424" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G1424" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1424" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1425" customFormat="1" spans="1:8">
+      <c r="A1425" s="7" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B1425" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1425" s="7" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D1425" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1425" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1425" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G1425" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1425" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1426" customFormat="1" spans="1:8">
+      <c r="A1426" s="7" t="s">
+        <v>1941</v>
+      </c>
+      <c r="B1426" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1426" s="7" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D1426" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1426" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1426" s="7" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G1426" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1426" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1427" customFormat="1" spans="1:8">
+      <c r="A1427" s="7" t="s">
+        <v>1941</v>
+      </c>
+      <c r="B1427" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1427" s="7" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D1427" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1427" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1427" s="7" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G1427" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1427" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1428" customFormat="1" spans="1:8">
+      <c r="A1428" s="7" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B1428" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1428" s="7" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D1428" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1428" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1428" s="7" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G1428" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1428" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1429" customFormat="1" spans="1:8">
+      <c r="A1429" s="7" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B1429" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1429" s="7" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D1429" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1429" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1429" s="7" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G1429" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H1429" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1430" customFormat="1" spans="1:8">
+      <c r="A1430" s="7" t="s">
+        <v>1943</v>
+      </c>
+      <c r="B1430" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1430" s="7" t="s">
+        <v>1846</v>
+      </c>
+      <c r="D1430" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1430" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1430" s="7" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G1430" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1430" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1431" customFormat="1" spans="1:8">
+      <c r="A1431" s="7" t="s">
+        <v>1943</v>
+      </c>
+      <c r="B1431" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1431" s="7" t="s">
+        <v>1846</v>
+      </c>
+      <c r="D1431" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1431" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1431" s="7" t="s">
+        <v>1902</v>
+      </c>
+      <c r="G1431" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1431" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1432" customFormat="1" spans="1:8">
+      <c r="A1432" s="7" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B1432" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1432" s="7" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D1432" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1432" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1432" s="7" t="s">
+        <v>1945</v>
+      </c>
+      <c r="G1432" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1432" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1433" customFormat="1" spans="1:8">
+      <c r="A1433" s="7" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B1433" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1433" s="7" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D1433" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1433" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1433" s="7" t="s">
+        <v>1945</v>
+      </c>
+      <c r="G1433" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H1433" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1434" customFormat="1" spans="1:8">
+      <c r="A1434" s="7" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B1434" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1434" s="7" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D1434" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1434" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1434" s="7" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G1434" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1434" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1435" customFormat="1" spans="1:8">
+      <c r="A1435" s="7" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B1435" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1435" s="7" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D1435" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1435" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1435" s="7" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G1435" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1435" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1436" customFormat="1" spans="1:8">
+      <c r="A1436" s="7" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B1436" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1436" s="7" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D1436" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1436" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1436" s="7" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G1436" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1436" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1437" customFormat="1" spans="1:8">
+      <c r="A1437" s="7" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B1437" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1437" s="7" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D1437" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1437" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1437" s="7" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G1437" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1437" s="7" t="s">
+        <v>1786</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1231" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:H1231">
-      <sortCondition ref="H1"/>
-    </sortState>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1437" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12688" uniqueCount="1891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12688" uniqueCount="1890">
   <si>
     <t>Enseignements</t>
   </si>
@@ -5691,9 +5691,6 @@
   </si>
   <si>
     <t>TP-Travaux d’avant-projet-G3B/G3A</t>
-  </si>
-  <si>
-    <t>Mr. K. Benkhalouk</t>
   </si>
   <si>
     <t>Dr. A. H. Yahi</t>
@@ -5715,8 +5712,16 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -5875,12 +5880,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -6178,31 +6189,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6211,37 +6219,37 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6256,75 +6264,79 @@
     <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18613,7 +18625,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="460" hidden="1" spans="1:8">
+    <row r="460" spans="1:8">
       <c r="A460" t="s">
         <v>618</v>
       </c>
@@ -19055,7 +19067,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="477" hidden="1" spans="1:8">
+    <row r="477" spans="1:8">
       <c r="A477" t="s">
         <v>618</v>
       </c>
@@ -21421,7 +21433,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="568" hidden="1" spans="1:8">
+    <row r="568" spans="1:8">
       <c r="A568" t="s">
         <v>740</v>
       </c>
@@ -23137,29 +23149,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="634" hidden="1" spans="1:8">
-      <c r="A634" t="s">
+    <row r="634" spans="1:8">
+      <c r="A634" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="B634" t="s">
-        <v>17</v>
-      </c>
-      <c r="C634" t="s">
-        <v>548</v>
-      </c>
-      <c r="D634" t="s">
+      <c r="B634" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C634" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="D634" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E634" t="s">
+      <c r="E634" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F634" t="s">
+      <c r="F634" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="G634" t="s">
+      <c r="G634" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="H634" t="s">
+      <c r="H634" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -23267,29 +23279,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="639" hidden="1" spans="1:8">
-      <c r="A639" t="s">
+    <row r="639" spans="1:8">
+      <c r="A639" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="B639" t="s">
-        <v>17</v>
-      </c>
-      <c r="C639" t="s">
-        <v>548</v>
-      </c>
-      <c r="D639" t="s">
+      <c r="B639" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C639" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="D639" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E639" t="s">
+      <c r="E639" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F639" t="s">
+      <c r="F639" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="G639" t="s">
+      <c r="G639" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="H639" t="s">
+      <c r="H639" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -29585,7 +29597,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="882" spans="1:8">
+    <row r="882" hidden="1" spans="1:8">
       <c r="A882" t="s">
         <v>1121</v>
       </c>
@@ -29637,7 +29649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="884" spans="1:8">
+    <row r="884" hidden="1" spans="1:8">
       <c r="A884" t="s">
         <v>1083</v>
       </c>
@@ -30625,7 +30637,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="922" spans="1:8">
+    <row r="922" hidden="1" spans="1:8">
       <c r="A922" t="s">
         <v>1121</v>
       </c>
@@ -30677,7 +30689,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="924" spans="1:8">
+    <row r="924" hidden="1" spans="1:8">
       <c r="A924" t="s">
         <v>1083</v>
       </c>
@@ -31015,7 +31027,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="937" spans="1:8">
+    <row r="937" hidden="1" spans="1:8">
       <c r="A937" t="s">
         <v>1193</v>
       </c>
@@ -31093,7 +31105,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="940" spans="1:8">
+    <row r="940" hidden="1" spans="1:8">
       <c r="A940" t="s">
         <v>1083</v>
       </c>
@@ -31613,7 +31625,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="960" spans="1:8">
+    <row r="960" hidden="1" spans="1:8">
       <c r="A960" t="s">
         <v>1121</v>
       </c>
@@ -31665,7 +31677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="962" spans="1:8">
+    <row r="962" hidden="1" spans="1:8">
       <c r="A962" t="s">
         <v>1083</v>
       </c>
@@ -32003,7 +32015,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="975" spans="1:8">
+    <row r="975" hidden="1" spans="1:8">
       <c r="A975" t="s">
         <v>1121</v>
       </c>
@@ -32055,7 +32067,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="977" spans="1:8">
+    <row r="977" hidden="1" spans="1:8">
       <c r="A977" t="s">
         <v>1083</v>
       </c>
@@ -47811,15 +47823,15 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="1583" hidden="1" spans="1:8">
+    <row r="1583" spans="1:8">
       <c r="A1583" t="s">
         <v>1886</v>
       </c>
       <c r="B1583" t="s">
         <v>17</v>
       </c>
-      <c r="C1583" t="s">
-        <v>1887</v>
+      <c r="C1583" s="1" t="s">
+        <v>622</v>
       </c>
       <c r="D1583" t="s">
         <v>1883</v>
@@ -47845,7 +47857,7 @@
         <v>1405</v>
       </c>
       <c r="C1584" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="D1584" t="s">
         <v>23</v>
@@ -47871,7 +47883,7 @@
         <v>1405</v>
       </c>
       <c r="C1585" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="D1585" t="s">
         <v>25</v>
@@ -47880,7 +47892,7 @@
         <v>101</v>
       </c>
       <c r="F1585" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="G1585" t="s">
         <v>1855</v>
@@ -47917,17 +47929,10 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1586" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="0">
+    <filterColumn colId="2">
       <filters>
-        <filter val="TP-Reverse engineering-SG11/SG12"/>
-        <filter val="TP-Reverse Engineering (Atelier)-SG11/SG12"/>
-        <filter val="Cours-Reverse Engineering"/>
-        <filter val="TP-Reverse Engineering (Atelier)"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="7">
-      <filters>
-        <filter val="ELT"/>
+        <filter val="BENKHALOUK KADOUR"/>
+        <filter val="Mr. K. Benkhalouk"/>
       </filters>
     </filterColumn>
     <sortState ref="A2:H1586">

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -1685,15 +1685,18 @@
     <t>L3ELT</t>
   </si>
   <si>
+    <t>TP-Capteurs-SG12</t>
+  </si>
+  <si>
+    <t>TP-Structure de la matière-SG71</t>
+  </si>
+  <si>
+    <t>BENKHALOUK KADOUR</t>
+  </si>
+  <si>
     <t>MCIL3</t>
   </si>
   <si>
-    <t>TP-Structure de la matière-SG71</t>
-  </si>
-  <si>
-    <t>TP-Capteurs-SG12</t>
-  </si>
-  <si>
     <t>TP-Structure des ordinateurs et applications-SG71</t>
   </si>
   <si>
@@ -1896,9 +1899,6 @@
   </si>
   <si>
     <t>Bloc B</t>
-  </si>
-  <si>
-    <t>BENKHALOUK KADOUR</t>
   </si>
   <si>
     <t>TP-Electrotechnique fondamentale 1-SG1/SG2</t>
@@ -6334,8 +6334,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -16701,7 +16702,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="386" hidden="1" spans="1:8">
+    <row r="386" spans="1:8">
       <c r="A386" t="s">
         <v>547</v>
       </c>
@@ -16753,9 +16754,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="388" hidden="1" spans="1:8">
+    <row r="388" spans="1:8">
       <c r="A388" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B388" t="s">
         <v>17</v>
@@ -16767,13 +16768,13 @@
         <v>21</v>
       </c>
       <c r="E388" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="F388" t="s">
         <v>549</v>
       </c>
       <c r="G388" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H388" t="s">
         <v>15</v>
@@ -16885,25 +16886,25 @@
     </row>
     <row r="393" hidden="1" spans="1:8">
       <c r="A393" t="s">
+        <v>547</v>
+      </c>
+      <c r="B393" t="s">
+        <v>17</v>
+      </c>
+      <c r="C393" t="s">
         <v>553</v>
-      </c>
-      <c r="B393" t="s">
-        <v>17</v>
-      </c>
-      <c r="C393" t="s">
-        <v>548</v>
       </c>
       <c r="D393" t="s">
         <v>21</v>
       </c>
       <c r="E393" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F393" t="s">
         <v>549</v>
       </c>
       <c r="G393" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="H393" t="s">
         <v>15</v>
@@ -16911,7 +16912,7 @@
     </row>
     <row r="394" hidden="1" spans="1:8">
       <c r="A394" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B394" t="s">
         <v>17</v>
@@ -16920,7 +16921,7 @@
         <v>539</v>
       </c>
       <c r="D394" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E394" t="s">
         <v>30</v>
@@ -16943,10 +16944,10 @@
         <v>17</v>
       </c>
       <c r="C395" t="s">
+        <v>557</v>
+      </c>
+      <c r="D395" t="s">
         <v>556</v>
-      </c>
-      <c r="D395" t="s">
-        <v>555</v>
       </c>
       <c r="E395" t="s">
         <v>30</v>
@@ -16963,7 +16964,7 @@
     </row>
     <row r="396" hidden="1" spans="1:8">
       <c r="A396" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B396" t="s">
         <v>32</v>
@@ -16992,7 +16993,7 @@
         <v>163</v>
       </c>
       <c r="B397" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C397" t="s">
         <v>507</v>
@@ -17015,7 +17016,7 @@
     </row>
     <row r="398" hidden="1" spans="1:8">
       <c r="A398" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B398" t="s">
         <v>17</v>
@@ -17041,7 +17042,7 @@
     </row>
     <row r="399" hidden="1" spans="1:8">
       <c r="A399" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B399" t="s">
         <v>17</v>
@@ -17050,7 +17051,7 @@
         <v>528</v>
       </c>
       <c r="D399" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E399" t="s">
         <v>30</v>
@@ -17067,7 +17068,7 @@
     </row>
     <row r="400" hidden="1" spans="1:8">
       <c r="A400" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B400" t="s">
         <v>17</v>
@@ -17076,7 +17077,7 @@
         <v>539</v>
       </c>
       <c r="D400" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E400" t="s">
         <v>30</v>
@@ -17099,10 +17100,10 @@
         <v>17</v>
       </c>
       <c r="C401" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D401" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E401" t="s">
         <v>30</v>
@@ -17119,7 +17120,7 @@
     </row>
     <row r="402" hidden="1" spans="1:8">
       <c r="A402" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B402" t="s">
         <v>518</v>
@@ -17145,10 +17146,10 @@
     </row>
     <row r="403" hidden="1" spans="1:8">
       <c r="A403" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B403" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C403" t="s">
         <v>507</v>
@@ -17171,7 +17172,7 @@
     </row>
     <row r="404" hidden="1" spans="1:8">
       <c r="A404" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B404" t="s">
         <v>17</v>
@@ -17197,13 +17198,13 @@
     </row>
     <row r="405" hidden="1" spans="1:8">
       <c r="A405" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B405" t="s">
         <v>17</v>
       </c>
       <c r="C405" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D405" t="s">
         <v>533</v>
@@ -17223,7 +17224,7 @@
     </row>
     <row r="406" hidden="1" spans="1:8">
       <c r="A406" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B406" t="s">
         <v>17</v>
@@ -17249,7 +17250,7 @@
     </row>
     <row r="407" hidden="1" spans="1:8">
       <c r="A407" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B407" t="s">
         <v>518</v>
@@ -17275,7 +17276,7 @@
     </row>
     <row r="408" hidden="1" spans="1:8">
       <c r="A408" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B408" t="s">
         <v>496</v>
@@ -17301,7 +17302,7 @@
     </row>
     <row r="409" hidden="1" spans="1:8">
       <c r="A409" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B409" t="s">
         <v>32</v>
@@ -17327,13 +17328,13 @@
     </row>
     <row r="410" hidden="1" spans="1:8">
       <c r="A410" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B410" t="s">
         <v>17</v>
       </c>
       <c r="C410" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D410" t="s">
         <v>540</v>
@@ -17353,7 +17354,7 @@
     </row>
     <row r="411" hidden="1" spans="1:8">
       <c r="A411" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B411" t="s">
         <v>17</v>
@@ -17379,7 +17380,7 @@
     </row>
     <row r="412" hidden="1" spans="1:8">
       <c r="A412" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B412" t="s">
         <v>496</v>
@@ -17405,7 +17406,7 @@
     </row>
     <row r="413" hidden="1" spans="1:8">
       <c r="A413" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B413" t="s">
         <v>518</v>
@@ -17483,7 +17484,7 @@
     </row>
     <row r="416" hidden="1" spans="1:8">
       <c r="A416" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B416" t="s">
         <v>518</v>
@@ -17535,7 +17536,7 @@
     </row>
     <row r="418" hidden="1" spans="1:8">
       <c r="A418" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B418" t="s">
         <v>32</v>
@@ -17561,13 +17562,13 @@
     </row>
     <row r="419" hidden="1" spans="1:8">
       <c r="A419" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B419" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C419" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D419" t="s">
         <v>19</v>
@@ -17639,7 +17640,7 @@
     </row>
     <row r="422" hidden="1" spans="1:8">
       <c r="A422" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B422" t="s">
         <v>518</v>
@@ -17691,13 +17692,13 @@
     </row>
     <row r="424" hidden="1" spans="1:8">
       <c r="A424" t="s">
+        <v>578</v>
+      </c>
+      <c r="B424" t="s">
+        <v>576</v>
+      </c>
+      <c r="C424" t="s">
         <v>577</v>
-      </c>
-      <c r="B424" t="s">
-        <v>575</v>
-      </c>
-      <c r="C424" t="s">
-        <v>576</v>
       </c>
       <c r="D424" t="s">
         <v>21</v>
@@ -17717,7 +17718,7 @@
     </row>
     <row r="425" hidden="1" spans="1:8">
       <c r="A425" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B425" t="s">
         <v>17</v>
@@ -17743,7 +17744,7 @@
     </row>
     <row r="426" hidden="1" spans="1:8">
       <c r="A426" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B426" t="s">
         <v>9</v>
@@ -17769,7 +17770,7 @@
     </row>
     <row r="427" hidden="1" spans="1:8">
       <c r="A427" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B427" t="s">
         <v>9</v>
@@ -17795,10 +17796,10 @@
     </row>
     <row r="428" hidden="1" spans="1:8">
       <c r="A428" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B428" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C428" t="s">
         <v>528</v>
@@ -17821,7 +17822,7 @@
     </row>
     <row r="429" hidden="1" spans="1:8">
       <c r="A429" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B429" t="s">
         <v>515</v>
@@ -17873,7 +17874,7 @@
     </row>
     <row r="431" hidden="1" spans="1:8">
       <c r="A431" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B431" t="s">
         <v>17</v>
@@ -17899,13 +17900,13 @@
     </row>
     <row r="432" hidden="1" spans="1:8">
       <c r="A432" t="s">
+        <v>551</v>
+      </c>
+      <c r="B432" t="s">
+        <v>17</v>
+      </c>
+      <c r="C432" t="s">
         <v>553</v>
-      </c>
-      <c r="B432" t="s">
-        <v>17</v>
-      </c>
-      <c r="C432" t="s">
-        <v>548</v>
       </c>
       <c r="D432" t="s">
         <v>25</v>
@@ -17917,7 +17918,7 @@
         <v>549</v>
       </c>
       <c r="G432" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H432" t="s">
         <v>15</v>
@@ -17951,7 +17952,7 @@
     </row>
     <row r="434" hidden="1" spans="1:8">
       <c r="A434" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B434" t="s">
         <v>17</v>
@@ -17977,13 +17978,13 @@
     </row>
     <row r="435" hidden="1" spans="1:8">
       <c r="A435" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B435" t="s">
         <v>17</v>
       </c>
       <c r="C435" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="D435" t="s">
         <v>19</v>
@@ -17995,7 +17996,7 @@
         <v>549</v>
       </c>
       <c r="G435" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H435" t="s">
         <v>15</v>
@@ -18006,7 +18007,7 @@
         <v>161</v>
       </c>
       <c r="B436" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C436" t="s">
         <v>35</v>
@@ -18029,13 +18030,13 @@
     </row>
     <row r="437" hidden="1" spans="1:8">
       <c r="A437" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B437" t="s">
         <v>17</v>
       </c>
       <c r="C437" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="D437" t="s">
         <v>11</v>
@@ -18047,7 +18048,7 @@
         <v>549</v>
       </c>
       <c r="G437" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H437" t="s">
         <v>15</v>
@@ -18055,10 +18056,10 @@
     </row>
     <row r="438" hidden="1" spans="1:8">
       <c r="A438" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B438" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C438" t="s">
         <v>44</v>
@@ -18087,7 +18088,7 @@
         <v>32</v>
       </c>
       <c r="C439" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D439" t="s">
         <v>23</v>
@@ -18107,13 +18108,13 @@
     </row>
     <row r="440" hidden="1" spans="1:8">
       <c r="A440" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B440" t="s">
         <v>32</v>
       </c>
       <c r="C440" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D440" t="s">
         <v>23</v>
@@ -18162,10 +18163,10 @@
         <v>151</v>
       </c>
       <c r="B442" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C442" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D442" t="s">
         <v>23</v>
@@ -18185,13 +18186,13 @@
     </row>
     <row r="443" hidden="1" spans="1:8">
       <c r="A443" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B443" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C443" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D443" t="s">
         <v>23</v>
@@ -18243,7 +18244,7 @@
         <v>32</v>
       </c>
       <c r="C445" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D445" t="s">
         <v>25</v>
@@ -18263,13 +18264,13 @@
     </row>
     <row r="446" hidden="1" spans="1:8">
       <c r="A446" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B446" t="s">
         <v>32</v>
       </c>
       <c r="C446" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D446" t="s">
         <v>25</v>
@@ -18289,13 +18290,13 @@
     </row>
     <row r="447" hidden="1" spans="1:8">
       <c r="A447" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B447" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C447" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D447" t="s">
         <v>25</v>
@@ -18315,13 +18316,13 @@
     </row>
     <row r="448" hidden="1" spans="1:8">
       <c r="A448" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B448" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C448" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D448" t="s">
         <v>25</v>
@@ -18341,10 +18342,10 @@
     </row>
     <row r="449" hidden="1" spans="1:8">
       <c r="A449" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B449" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C449" t="s">
         <v>253</v>
@@ -18359,7 +18360,7 @@
         <v>72</v>
       </c>
       <c r="G449" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H449" t="s">
         <v>74</v>
@@ -18367,13 +18368,13 @@
     </row>
     <row r="450" hidden="1" spans="1:8">
       <c r="A450" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B450" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C450" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D450" t="s">
         <v>23</v>
@@ -18385,7 +18386,7 @@
         <v>126</v>
       </c>
       <c r="G450" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H450" t="s">
         <v>74</v>
@@ -18393,13 +18394,13 @@
     </row>
     <row r="451" hidden="1" spans="1:8">
       <c r="A451" t="s">
+        <v>606</v>
+      </c>
+      <c r="B451" t="s">
+        <v>607</v>
+      </c>
+      <c r="C451" t="s">
         <v>605</v>
-      </c>
-      <c r="B451" t="s">
-        <v>606</v>
-      </c>
-      <c r="C451" t="s">
-        <v>604</v>
       </c>
       <c r="D451" t="s">
         <v>25</v>
@@ -18411,7 +18412,7 @@
         <v>126</v>
       </c>
       <c r="G451" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H451" t="s">
         <v>74</v>
@@ -18419,13 +18420,13 @@
     </row>
     <row r="452" hidden="1" spans="1:8">
       <c r="A452" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B452" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C452" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D452" t="s">
         <v>11</v>
@@ -18437,7 +18438,7 @@
         <v>77</v>
       </c>
       <c r="G452" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H452" t="s">
         <v>74</v>
@@ -18445,13 +18446,13 @@
     </row>
     <row r="453" hidden="1" spans="1:8">
       <c r="A453" t="s">
+        <v>611</v>
+      </c>
+      <c r="B453" t="s">
+        <v>612</v>
+      </c>
+      <c r="C453" t="s">
         <v>610</v>
-      </c>
-      <c r="B453" t="s">
-        <v>611</v>
-      </c>
-      <c r="C453" t="s">
-        <v>609</v>
       </c>
       <c r="D453" t="s">
         <v>23</v>
@@ -18463,7 +18464,7 @@
         <v>77</v>
       </c>
       <c r="G453" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H453" t="s">
         <v>74</v>
@@ -18471,13 +18472,13 @@
     </row>
     <row r="454" hidden="1" spans="1:8">
       <c r="A454" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B454" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C454" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D454" t="s">
         <v>25</v>
@@ -18489,7 +18490,7 @@
         <v>77</v>
       </c>
       <c r="G454" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H454" t="s">
         <v>74</v>
@@ -18500,7 +18501,7 @@
         <v>56</v>
       </c>
       <c r="B455" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C455" t="s">
         <v>149</v>
@@ -18515,7 +18516,7 @@
         <v>126</v>
       </c>
       <c r="G455" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H455" t="s">
         <v>74</v>
@@ -18526,10 +18527,10 @@
         <v>187</v>
       </c>
       <c r="B456" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C456" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D456" t="s">
         <v>19</v>
@@ -18541,7 +18542,7 @@
         <v>126</v>
       </c>
       <c r="G456" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H456" t="s">
         <v>74</v>
@@ -18549,13 +18550,13 @@
     </row>
     <row r="457" hidden="1" spans="1:8">
       <c r="A457" t="s">
+        <v>616</v>
+      </c>
+      <c r="B457" t="s">
+        <v>617</v>
+      </c>
+      <c r="C457" t="s">
         <v>615</v>
-      </c>
-      <c r="B457" t="s">
-        <v>616</v>
-      </c>
-      <c r="C457" t="s">
-        <v>614</v>
       </c>
       <c r="D457" t="s">
         <v>21</v>
@@ -18567,7 +18568,7 @@
         <v>126</v>
       </c>
       <c r="G457" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H457" t="s">
         <v>74</v>
@@ -18578,7 +18579,7 @@
         <v>53</v>
       </c>
       <c r="B458" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C458" t="s">
         <v>149</v>
@@ -18593,7 +18594,7 @@
         <v>126</v>
       </c>
       <c r="G458" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H458" t="s">
         <v>74</v>
@@ -18601,13 +18602,13 @@
     </row>
     <row r="459" hidden="1" spans="1:8">
       <c r="A459" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B459" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C459" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D459" t="s">
         <v>11</v>
@@ -18616,24 +18617,24 @@
         <v>48</v>
       </c>
       <c r="F459" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G459" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H459" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="460" spans="1:8">
+    <row r="460" hidden="1" spans="1:8">
       <c r="A460" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B460" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C460" t="s">
-        <v>622</v>
+        <v>553</v>
       </c>
       <c r="D460" t="s">
         <v>11</v>
@@ -18642,10 +18643,10 @@
         <v>48</v>
       </c>
       <c r="F460" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G460" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H460" t="s">
         <v>74</v>
@@ -18671,7 +18672,7 @@
         <v>626</v>
       </c>
       <c r="G461" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H461" t="s">
         <v>74</v>
@@ -18697,7 +18698,7 @@
         <v>77</v>
       </c>
       <c r="G462" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H462" t="s">
         <v>74</v>
@@ -18723,7 +18724,7 @@
         <v>77</v>
       </c>
       <c r="G463" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H463" t="s">
         <v>74</v>
@@ -18749,7 +18750,7 @@
         <v>83</v>
       </c>
       <c r="G464" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H464" t="s">
         <v>74</v>
@@ -18775,7 +18776,7 @@
         <v>83</v>
       </c>
       <c r="G465" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H465" t="s">
         <v>74</v>
@@ -18801,7 +18802,7 @@
         <v>83</v>
       </c>
       <c r="G466" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H466" t="s">
         <v>74</v>
@@ -18827,7 +18828,7 @@
         <v>83</v>
       </c>
       <c r="G467" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H467" t="s">
         <v>74</v>
@@ -18853,7 +18854,7 @@
         <v>638</v>
       </c>
       <c r="G468" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H468" t="s">
         <v>74</v>
@@ -18879,7 +18880,7 @@
         <v>80</v>
       </c>
       <c r="G469" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H469" t="s">
         <v>74</v>
@@ -18905,7 +18906,7 @@
         <v>80</v>
       </c>
       <c r="G470" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H470" t="s">
         <v>74</v>
@@ -18913,7 +18914,7 @@
     </row>
     <row r="471" hidden="1" spans="1:8">
       <c r="A471" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B471" t="s">
         <v>645</v>
@@ -18991,13 +18992,13 @@
     </row>
     <row r="474" hidden="1" spans="1:8">
       <c r="A474" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B474" t="s">
         <v>648</v>
       </c>
       <c r="C474" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D474" t="s">
         <v>23</v>
@@ -19017,13 +19018,13 @@
     </row>
     <row r="475" hidden="1" spans="1:8">
       <c r="A475" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B475" t="s">
         <v>649</v>
       </c>
       <c r="C475" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D475" t="s">
         <v>25</v>
@@ -19043,7 +19044,7 @@
     </row>
     <row r="476" hidden="1" spans="1:8">
       <c r="A476" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B476" t="s">
         <v>650</v>
@@ -19067,15 +19068,15 @@
         <v>74</v>
       </c>
     </row>
-    <row r="477" spans="1:8">
+    <row r="477" hidden="1" spans="1:8">
       <c r="A477" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B477" t="s">
         <v>652</v>
       </c>
       <c r="C477" t="s">
-        <v>622</v>
+        <v>553</v>
       </c>
       <c r="D477" t="s">
         <v>33</v>
@@ -19121,7 +19122,7 @@
     </row>
     <row r="479" hidden="1" spans="1:8">
       <c r="A479" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B479" t="s">
         <v>655</v>
@@ -19147,7 +19148,7 @@
     </row>
     <row r="480" hidden="1" spans="1:8">
       <c r="A480" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B480" t="s">
         <v>650</v>
@@ -19205,7 +19206,7 @@
         <v>657</v>
       </c>
       <c r="C482" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D482" t="s">
         <v>19</v>
@@ -19231,7 +19232,7 @@
         <v>658</v>
       </c>
       <c r="C483" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D483" t="s">
         <v>21</v>
@@ -19595,7 +19596,7 @@
         <v>674</v>
       </c>
       <c r="C497" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D497" t="s">
         <v>40</v>
@@ -20993,7 +20994,7 @@
     </row>
     <row r="551" hidden="1" spans="1:8">
       <c r="A551" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B551" t="s">
         <v>9</v>
@@ -21201,7 +21202,7 @@
     </row>
     <row r="559" hidden="1" spans="1:8">
       <c r="A559" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B559" t="s">
         <v>9</v>
@@ -21433,7 +21434,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="568" spans="1:8">
+    <row r="568" hidden="1" spans="1:8">
       <c r="A568" t="s">
         <v>740</v>
       </c>
@@ -21441,7 +21442,7 @@
         <v>741</v>
       </c>
       <c r="C568" t="s">
-        <v>622</v>
+        <v>553</v>
       </c>
       <c r="D568" t="s">
         <v>11</v>
@@ -21467,7 +21468,7 @@
         <v>743</v>
       </c>
       <c r="C569" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D569" t="s">
         <v>19</v>
@@ -21493,7 +21494,7 @@
         <v>745</v>
       </c>
       <c r="C570" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D570" t="s">
         <v>21</v>
@@ -22091,7 +22092,7 @@
         <v>791</v>
       </c>
       <c r="C593" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D593" t="s">
         <v>11</v>
@@ -22273,7 +22274,7 @@
         <v>791</v>
       </c>
       <c r="C600" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D600" t="s">
         <v>25</v>
@@ -22429,7 +22430,7 @@
         <v>32</v>
       </c>
       <c r="C606" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D606" t="s">
         <v>11</v>
@@ -22995,7 +22996,7 @@
     </row>
     <row r="628" hidden="1" spans="1:8">
       <c r="A628" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B628" t="s">
         <v>17</v>
@@ -23021,7 +23022,7 @@
     </row>
     <row r="629" hidden="1" spans="1:8">
       <c r="A629" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B629" t="s">
         <v>17</v>
@@ -23157,7 +23158,7 @@
         <v>17</v>
       </c>
       <c r="C634" s="1" t="s">
-        <v>622</v>
+        <v>548</v>
       </c>
       <c r="D634" s="1" t="s">
         <v>19</v>
@@ -23287,7 +23288,7 @@
         <v>17</v>
       </c>
       <c r="C639" s="1" t="s">
-        <v>622</v>
+        <v>548</v>
       </c>
       <c r="D639" s="1" t="s">
         <v>21</v>
@@ -31365,12 +31366,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="950" hidden="1" spans="1:8">
+    <row r="950" spans="1:8">
       <c r="A950" t="s">
         <v>1209</v>
       </c>
       <c r="B950" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C950" t="s">
         <v>548</v>
@@ -31469,12 +31470,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="954" hidden="1" spans="1:8">
+    <row r="954" spans="1:8">
       <c r="A954" t="s">
         <v>1214</v>
       </c>
       <c r="B954" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C954" t="s">
         <v>548</v>
@@ -33941,13 +33942,13 @@
     </row>
     <row r="1049" hidden="1" spans="1:8">
       <c r="A1049" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B1049" t="s">
         <v>32</v>
       </c>
       <c r="C1049" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D1049" t="s">
         <v>25</v>
@@ -34857,7 +34858,7 @@
         <v>1298</v>
       </c>
       <c r="C1084" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D1084" t="s">
         <v>11</v>
@@ -35273,7 +35274,7 @@
         <v>1351</v>
       </c>
       <c r="C1100" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D1100" t="s">
         <v>45</v>
@@ -35533,7 +35534,7 @@
         <v>1298</v>
       </c>
       <c r="C1110" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D1110" t="s">
         <v>23</v>
@@ -35623,7 +35624,7 @@
         <v>478</v>
       </c>
       <c r="G1113" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1113" t="s">
         <v>15</v>
@@ -35649,7 +35650,7 @@
         <v>55</v>
       </c>
       <c r="G1114" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1114" t="s">
         <v>15</v>
@@ -35675,7 +35676,7 @@
         <v>285</v>
       </c>
       <c r="G1115" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1115" t="s">
         <v>15</v>
@@ -35701,7 +35702,7 @@
         <v>31</v>
       </c>
       <c r="G1116" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1116" t="s">
         <v>15</v>
@@ -35727,7 +35728,7 @@
         <v>41</v>
       </c>
       <c r="G1117" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1117" t="s">
         <v>15</v>
@@ -35753,7 +35754,7 @@
         <v>41</v>
       </c>
       <c r="G1118" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1118" t="s">
         <v>15</v>
@@ -35779,7 +35780,7 @@
         <v>1364</v>
       </c>
       <c r="G1119" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1119" t="s">
         <v>15</v>
@@ -35805,7 +35806,7 @@
         <v>478</v>
       </c>
       <c r="G1120" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1120" t="s">
         <v>15</v>
@@ -35831,7 +35832,7 @@
         <v>809</v>
       </c>
       <c r="G1121" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1121" t="s">
         <v>15</v>
@@ -35857,7 +35858,7 @@
         <v>320</v>
       </c>
       <c r="G1122" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1122" t="s">
         <v>15</v>
@@ -35883,7 +35884,7 @@
         <v>478</v>
       </c>
       <c r="G1123" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1123" t="s">
         <v>15</v>
@@ -35909,7 +35910,7 @@
         <v>397</v>
       </c>
       <c r="G1124" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1124" t="s">
         <v>15</v>
@@ -35935,13 +35936,13 @@
         <v>397</v>
       </c>
       <c r="G1125" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1125" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="1126" hidden="1" spans="1:8">
+    <row r="1126" spans="1:8">
       <c r="A1126" t="s">
         <v>1368</v>
       </c>
@@ -35987,13 +35988,13 @@
         <v>474</v>
       </c>
       <c r="G1127" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1127" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="1128" hidden="1" spans="1:8">
+    <row r="1128" spans="1:8">
       <c r="A1128" t="s">
         <v>1371</v>
       </c>
@@ -36039,7 +36040,7 @@
         <v>320</v>
       </c>
       <c r="G1129" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1129" t="s">
         <v>15</v>
@@ -36065,13 +36066,13 @@
         <v>478</v>
       </c>
       <c r="G1130" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1130" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="1131" hidden="1" spans="1:8">
+    <row r="1131" spans="1:8">
       <c r="A1131" t="s">
         <v>1373</v>
       </c>
@@ -36117,7 +36118,7 @@
         <v>237</v>
       </c>
       <c r="G1132" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1132" t="s">
         <v>15</v>
@@ -36143,13 +36144,13 @@
         <v>1364</v>
       </c>
       <c r="G1133" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1133" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="1134" hidden="1" spans="1:8">
+    <row r="1134" spans="1:8">
       <c r="A1134" t="s">
         <v>1377</v>
       </c>
@@ -36195,7 +36196,7 @@
         <v>478</v>
       </c>
       <c r="G1135" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1135" t="s">
         <v>15</v>
@@ -36221,7 +36222,7 @@
         <v>245</v>
       </c>
       <c r="G1136" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1136" t="s">
         <v>15</v>
@@ -36247,7 +36248,7 @@
         <v>478</v>
       </c>
       <c r="G1137" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1137" t="s">
         <v>15</v>
@@ -36273,7 +36274,7 @@
         <v>1364</v>
       </c>
       <c r="G1138" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1138" t="s">
         <v>15</v>
@@ -36299,7 +36300,7 @@
         <v>285</v>
       </c>
       <c r="G1139" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1139" t="s">
         <v>15</v>
@@ -36325,7 +36326,7 @@
         <v>298</v>
       </c>
       <c r="G1140" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1140" t="s">
         <v>15</v>
@@ -36351,7 +36352,7 @@
         <v>1364</v>
       </c>
       <c r="G1141" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1141" t="s">
         <v>15</v>
@@ -36377,7 +36378,7 @@
         <v>298</v>
       </c>
       <c r="G1142" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1142" t="s">
         <v>15</v>
@@ -36403,7 +36404,7 @@
         <v>1364</v>
       </c>
       <c r="G1143" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1143" t="s">
         <v>15</v>
@@ -36429,7 +36430,7 @@
         <v>478</v>
       </c>
       <c r="G1144" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1144" t="s">
         <v>15</v>
@@ -36455,7 +36456,7 @@
         <v>478</v>
       </c>
       <c r="G1145" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1145" t="s">
         <v>15</v>
@@ -36481,7 +36482,7 @@
         <v>320</v>
       </c>
       <c r="G1146" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1146" t="s">
         <v>15</v>
@@ -36507,7 +36508,7 @@
         <v>285</v>
       </c>
       <c r="G1147" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1147" t="s">
         <v>15</v>
@@ -36533,7 +36534,7 @@
         <v>397</v>
       </c>
       <c r="G1148" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1148" t="s">
         <v>15</v>
@@ -36559,7 +36560,7 @@
         <v>549</v>
       </c>
       <c r="G1149" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1149" t="s">
         <v>15</v>
@@ -36585,7 +36586,7 @@
         <v>285</v>
       </c>
       <c r="G1150" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1150" t="s">
         <v>15</v>
@@ -36611,7 +36612,7 @@
         <v>549</v>
       </c>
       <c r="G1151" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1151" t="s">
         <v>15</v>
@@ -36637,7 +36638,7 @@
         <v>397</v>
       </c>
       <c r="G1152" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1152" t="s">
         <v>15</v>
@@ -36663,7 +36664,7 @@
         <v>298</v>
       </c>
       <c r="G1153" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1153" t="s">
         <v>15</v>
@@ -36689,7 +36690,7 @@
         <v>298</v>
       </c>
       <c r="G1154" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1154" t="s">
         <v>15</v>
@@ -36715,7 +36716,7 @@
         <v>285</v>
       </c>
       <c r="G1155" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1155" t="s">
         <v>15</v>
@@ -36741,7 +36742,7 @@
         <v>397</v>
       </c>
       <c r="G1156" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1156" t="s">
         <v>15</v>
@@ -36767,7 +36768,7 @@
         <v>298</v>
       </c>
       <c r="G1157" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1157" t="s">
         <v>15</v>
@@ -36793,7 +36794,7 @@
         <v>298</v>
       </c>
       <c r="G1158" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1158" t="s">
         <v>15</v>
@@ -36819,7 +36820,7 @@
         <v>478</v>
       </c>
       <c r="G1159" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1159" t="s">
         <v>15</v>
@@ -36845,7 +36846,7 @@
         <v>320</v>
       </c>
       <c r="G1160" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1160" t="s">
         <v>15</v>
@@ -36871,7 +36872,7 @@
         <v>285</v>
       </c>
       <c r="G1161" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1161" t="s">
         <v>15</v>
@@ -36897,7 +36898,7 @@
         <v>397</v>
       </c>
       <c r="G1162" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1162" t="s">
         <v>15</v>
@@ -36923,7 +36924,7 @@
         <v>1364</v>
       </c>
       <c r="G1163" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H1163" t="s">
         <v>15</v>
@@ -37399,7 +37400,7 @@
     </row>
     <row r="1182" hidden="1" spans="1:8">
       <c r="A1182" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B1182" t="s">
         <v>1405</v>
@@ -45251,7 +45252,7 @@
     </row>
     <row r="1484" hidden="1" spans="1:8">
       <c r="A1484" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B1484" t="s">
         <v>1405</v>
@@ -45303,7 +45304,7 @@
     </row>
     <row r="1486" hidden="1" spans="1:8">
       <c r="A1486" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B1486" t="s">
         <v>32</v>
@@ -47823,15 +47824,15 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="1583" spans="1:8">
+    <row r="1583" hidden="1" spans="1:8">
       <c r="A1583" t="s">
         <v>1886</v>
       </c>
       <c r="B1583" t="s">
         <v>17</v>
       </c>
-      <c r="C1583" s="1" t="s">
-        <v>622</v>
+      <c r="C1583" s="2" t="s">
+        <v>553</v>
       </c>
       <c r="D1583" t="s">
         <v>1883</v>
@@ -47931,8 +47932,7 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1586" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="2">
       <filters>
-        <filter val="BENKHALOUK KADOUR"/>
-        <filter val="Mr. K. Benkhalouk"/>
+        <filter val="Non défini-ELT"/>
       </filters>
     </filterColumn>
     <sortState ref="A2:H1586">

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -1691,7 +1691,7 @@
     <t>TP-Structure de la matière-SG71</t>
   </si>
   <si>
-    <t>BENKHALOUK KADOUR</t>
+    <t>BENKHALOUK KADDOUR</t>
   </si>
   <si>
     <t>MCIL3</t>
@@ -5712,16 +5712,8 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -6189,28 +6181,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6219,125 +6214,121 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16702,7 +16693,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="386" spans="1:8">
+    <row r="386" hidden="1" spans="1:8">
       <c r="A386" t="s">
         <v>547</v>
       </c>
@@ -16754,7 +16745,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="388" spans="1:8">
+    <row r="388" hidden="1" spans="1:8">
       <c r="A388" t="s">
         <v>551</v>
       </c>
@@ -16884,7 +16875,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="393" hidden="1" spans="1:8">
+    <row r="393" spans="1:8">
       <c r="A393" t="s">
         <v>547</v>
       </c>
@@ -17898,7 +17889,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="432" hidden="1" spans="1:8">
+    <row r="432" spans="1:8">
       <c r="A432" t="s">
         <v>551</v>
       </c>
@@ -17976,7 +17967,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="435" hidden="1" spans="1:8">
+    <row r="435" spans="1:8">
       <c r="A435" t="s">
         <v>587</v>
       </c>
@@ -18028,7 +18019,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="437" hidden="1" spans="1:8">
+    <row r="437" spans="1:8">
       <c r="A437" t="s">
         <v>589</v>
       </c>
@@ -18626,7 +18617,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="460" hidden="1" spans="1:8">
+    <row r="460" spans="1:8">
       <c r="A460" t="s">
         <v>619</v>
       </c>
@@ -19068,7 +19059,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="477" hidden="1" spans="1:8">
+    <row r="477" spans="1:8">
       <c r="A477" t="s">
         <v>619</v>
       </c>
@@ -21434,7 +21425,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="568" hidden="1" spans="1:8">
+    <row r="568" spans="1:8">
       <c r="A568" t="s">
         <v>740</v>
       </c>
@@ -23150,7 +23141,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="634" spans="1:8">
+    <row r="634" hidden="1" spans="1:8">
       <c r="A634" s="1" t="s">
         <v>836</v>
       </c>
@@ -23280,7 +23271,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="639" spans="1:8">
+    <row r="639" hidden="1" spans="1:8">
       <c r="A639" s="1" t="s">
         <v>836</v>
       </c>
@@ -31366,7 +31357,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="950" spans="1:8">
+    <row r="950" hidden="1" spans="1:8">
       <c r="A950" t="s">
         <v>1209</v>
       </c>
@@ -31470,7 +31461,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="954" spans="1:8">
+    <row r="954" hidden="1" spans="1:8">
       <c r="A954" t="s">
         <v>1214</v>
       </c>
@@ -35942,7 +35933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1126" spans="1:8">
+    <row r="1126" hidden="1" spans="1:8">
       <c r="A1126" t="s">
         <v>1368</v>
       </c>
@@ -35994,7 +35985,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1128" spans="1:8">
+    <row r="1128" hidden="1" spans="1:8">
       <c r="A1128" t="s">
         <v>1371</v>
       </c>
@@ -36072,7 +36063,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1131" spans="1:8">
+    <row r="1131" hidden="1" spans="1:8">
       <c r="A1131" t="s">
         <v>1373</v>
       </c>
@@ -36150,7 +36141,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="1134" spans="1:8">
+    <row r="1134" hidden="1" spans="1:8">
       <c r="A1134" t="s">
         <v>1377</v>
       </c>
@@ -47824,14 +47815,14 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="1583" hidden="1" spans="1:8">
+    <row r="1583" spans="1:8">
       <c r="A1583" t="s">
         <v>1886</v>
       </c>
       <c r="B1583" t="s">
         <v>17</v>
       </c>
-      <c r="C1583" s="2" t="s">
+      <c r="C1583" t="s">
         <v>553</v>
       </c>
       <c r="D1583" t="s">
@@ -47932,7 +47923,7 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1586" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="2">
       <filters>
-        <filter val="Non défini-ELT"/>
+        <filter val="BENKHALOUK KADOUR"/>
       </filters>
     </filterColumn>
     <sortState ref="A2:H1586">

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -45171,13 +45171,13 @@
     </row>
     <row r="1512" spans="1:8">
       <c r="A1512" t="s">
-        <v>407</v>
+        <v>914</v>
       </c>
       <c r="B1512" t="s">
         <v>961</v>
       </c>
       <c r="C1512" t="s">
-        <v>1305</v>
+        <v>1317</v>
       </c>
       <c r="D1512" t="s">
         <v>1616</v>
@@ -45186,7 +45186,7 @@
         <v>1635</v>
       </c>
       <c r="F1512" t="s">
-        <v>1709</v>
+        <v>1704</v>
       </c>
       <c r="G1512" t="s">
         <v>1839</v>
@@ -45197,13 +45197,13 @@
     </row>
     <row r="1513" spans="1:8">
       <c r="A1513" t="s">
-        <v>914</v>
+        <v>407</v>
       </c>
       <c r="B1513" t="s">
         <v>961</v>
       </c>
       <c r="C1513" t="s">
-        <v>1317</v>
+        <v>1305</v>
       </c>
       <c r="D1513" t="s">
         <v>1616</v>
@@ -45212,7 +45212,7 @@
         <v>1635</v>
       </c>
       <c r="F1513" t="s">
-        <v>1704</v>
+        <v>1660</v>
       </c>
       <c r="G1513" t="s">
         <v>1839</v>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -481,12 +481,12 @@
     <t>TD-Anglais technique</t>
   </si>
   <si>
+    <t>TP- Méthodes numériques appliquées- Python</t>
+  </si>
+  <si>
     <t>TP-Electronique appliquée</t>
   </si>
   <si>
-    <t>TP- Méthodes numériques appliquées- Python</t>
-  </si>
-  <si>
     <t>TD-Transfert thermique</t>
   </si>
   <si>
@@ -3961,208 +3961,208 @@
     <t>SEMMAK ABDELKADER</t>
   </si>
   <si>
+    <t>Non défini-ELT</t>
+  </si>
+  <si>
+    <t>KHIAT WALID</t>
+  </si>
+  <si>
+    <t>FELLAH MOHAMMED KARIM</t>
+  </si>
+  <si>
+    <t>BELAIDI OUAFIA</t>
+  </si>
+  <si>
+    <t>GRABA ABDELMADJID GUESSOUM</t>
+  </si>
+  <si>
+    <t>MOSTEFAOUI</t>
+  </si>
+  <si>
+    <t>ADDAD MOUAD</t>
+  </si>
+  <si>
+    <t>SEKKAL SIDI MOHAMMED</t>
+  </si>
+  <si>
+    <t>SEDDIKI ALI</t>
+  </si>
+  <si>
+    <t>FARAH MEHDI CHEMSEDDINE</t>
+  </si>
+  <si>
+    <t>DJEBBARI ALI</t>
+  </si>
+  <si>
+    <t>MAHIDDINE ABDERRAHIM</t>
+  </si>
+  <si>
+    <t>ABOURA LAMIA TOURIA</t>
+  </si>
+  <si>
+    <t>MESKINE FATIHA</t>
+  </si>
+  <si>
+    <t>BENHAMIDA FARID</t>
+  </si>
+  <si>
+    <t>JBILOU MOKHTARIA</t>
+  </si>
+  <si>
+    <t>GHAZEL FATIHA</t>
+  </si>
+  <si>
+    <t>BENDIMERAD SALAH EDDINE</t>
+  </si>
+  <si>
+    <t>MEGUEDAD ABOUBAKR</t>
+  </si>
+  <si>
+    <t>BECHEKIR SEYF EDDINE</t>
+  </si>
+  <si>
+    <t>DJELLOULI YOUNES</t>
+  </si>
+  <si>
+    <t>TOUHAMI SEDDIK</t>
+  </si>
+  <si>
+    <t>NASSOUR KAMEL</t>
+  </si>
+  <si>
+    <t>AYAD ABDELGHANI</t>
+  </si>
+  <si>
+    <t>SEMMAH ABDELHAFID</t>
+  </si>
+  <si>
+    <t>BOUBEKEUR HALIMA</t>
+  </si>
+  <si>
+    <t>MANSOURI ABDERRAZAK</t>
+  </si>
+  <si>
+    <t>ZIDI SID AHMED</t>
+  </si>
+  <si>
+    <t>HADJ BOULANOUAR RACHID</t>
+  </si>
+  <si>
+    <t>REGUIEG ZAKARIA</t>
+  </si>
+  <si>
+    <t>BOUKHOULDA FODIL</t>
+  </si>
+  <si>
+    <t>NEMMICH SAID</t>
+  </si>
+  <si>
+    <t>MEKHFI KHALIDA</t>
+  </si>
+  <si>
+    <t>REZOUG MOHAMMED</t>
+  </si>
+  <si>
+    <t>MILOUA FARID</t>
+  </si>
+  <si>
+    <t>BELLEBNA YASSINE</t>
+  </si>
+  <si>
+    <t>MAAMMAR MOHAMED</t>
+  </si>
+  <si>
+    <t>BAHLIL MOUNIR</t>
+  </si>
+  <si>
+    <t>MECHETTEM KHALIDA</t>
+  </si>
+  <si>
+    <t>BENSEDDIK NADIA</t>
+  </si>
+  <si>
+    <t>CHIRANI SOUMIA</t>
+  </si>
+  <si>
+    <t>LARBI ZIDI</t>
+  </si>
+  <si>
+    <t>DOUIAICI MOHAMED</t>
+  </si>
+  <si>
+    <t>BEDDAD BOUCIF</t>
+  </si>
+  <si>
+    <t>BELHALLOUCHE LAKHDAR</t>
+  </si>
+  <si>
+    <t>ATTAR IMAD</t>
+  </si>
+  <si>
+    <t>BENSALEM MOHAMMED MUSTAPHA</t>
+  </si>
+  <si>
+    <t>DRIEF FAIZA</t>
+  </si>
+  <si>
+    <t>BENOUAR MOHAMED</t>
+  </si>
+  <si>
+    <t>ELGHODASSE ABDEL MADJID</t>
+  </si>
+  <si>
+    <t>HAMMAR MEHDI</t>
+  </si>
+  <si>
+    <t>IKKACHE NARIMEN</t>
+  </si>
+  <si>
+    <t>SAHRAOUI HADIL</t>
+  </si>
+  <si>
+    <t>MELIANI ABDELHAK</t>
+  </si>
+  <si>
+    <t>KADRI RANIA</t>
+  </si>
+  <si>
+    <t>BOULARAF AICHA</t>
+  </si>
+  <si>
+    <t>TALEB SOUMIA</t>
+  </si>
+  <si>
+    <t>BENMESSAOUD LEYLA</t>
+  </si>
+  <si>
+    <t>SAYAH RAFIK</t>
+  </si>
+  <si>
+    <t>NON DÉFINI-AUTO</t>
+  </si>
+  <si>
+    <t>BENSAID DJILALI</t>
+  </si>
+  <si>
+    <t>BENKHALLOUK KADDOUR</t>
+  </si>
+  <si>
+    <t>MILOUDI + BOUDRAA</t>
+  </si>
+  <si>
+    <t>BENAMARA ZINEB</t>
+  </si>
+  <si>
+    <t>BENSAID DJILALI + MASSIM</t>
+  </si>
+  <si>
+    <t>MILOUDI MOHAMED</t>
+  </si>
+  <si>
+    <t>DJEHAF MOHAMMED ABDELJALIL</t>
+  </si>
+  <si>
     <t>EL-FIAD MOHAMED DJILLALI</t>
-  </si>
-  <si>
-    <t>KHIAT WALID</t>
-  </si>
-  <si>
-    <t>FELLAH MOHAMMED KARIM</t>
-  </si>
-  <si>
-    <t>BELAIDI OUAFIA</t>
-  </si>
-  <si>
-    <t>GRABA ABDELMADJID GUESSOUM</t>
-  </si>
-  <si>
-    <t>MOSTEFAOUI</t>
-  </si>
-  <si>
-    <t>ADDAD MOUAD</t>
-  </si>
-  <si>
-    <t>SEKKAL SIDI MOHAMMED</t>
-  </si>
-  <si>
-    <t>SEDDIKI ALI</t>
-  </si>
-  <si>
-    <t>FARAH MEHDI CHEMSEDDINE</t>
-  </si>
-  <si>
-    <t>DJEBBARI ALI</t>
-  </si>
-  <si>
-    <t>MAHIDDINE ABDERRAHIM</t>
-  </si>
-  <si>
-    <t>ABOURA LAMIA TOURIA</t>
-  </si>
-  <si>
-    <t>MESKINE FATIHA</t>
-  </si>
-  <si>
-    <t>BENHAMIDA FARID</t>
-  </si>
-  <si>
-    <t>JBILOU MOKHTARIA</t>
-  </si>
-  <si>
-    <t>GHAZEL FATIHA</t>
-  </si>
-  <si>
-    <t>Non défini-ELT</t>
-  </si>
-  <si>
-    <t>BENDIMERAD SALAH EDDINE</t>
-  </si>
-  <si>
-    <t>MEGUEDAD ABOUBAKR</t>
-  </si>
-  <si>
-    <t>BECHEKIR SEYF EDDINE</t>
-  </si>
-  <si>
-    <t>DJELLOULI YOUNES</t>
-  </si>
-  <si>
-    <t>TOUHAMI SEDDIK</t>
-  </si>
-  <si>
-    <t>NASSOUR KAMEL</t>
-  </si>
-  <si>
-    <t>AYAD ABDELGHANI</t>
-  </si>
-  <si>
-    <t>SEMMAH ABDELHAFID</t>
-  </si>
-  <si>
-    <t>BOUBEKEUR HALIMA</t>
-  </si>
-  <si>
-    <t>MANSOURI ABDERRAZAK</t>
-  </si>
-  <si>
-    <t>ZIDI SID AHMED</t>
-  </si>
-  <si>
-    <t>HADJ BOULANOUAR RACHID</t>
-  </si>
-  <si>
-    <t>REGUIEG ZAKARIA</t>
-  </si>
-  <si>
-    <t>BOUKHOULDA FODIL</t>
-  </si>
-  <si>
-    <t>NEMMICH SAID</t>
-  </si>
-  <si>
-    <t>MEKHFI KHALIDA</t>
-  </si>
-  <si>
-    <t>REZOUG MOHAMMED</t>
-  </si>
-  <si>
-    <t>MILOUA FARID</t>
-  </si>
-  <si>
-    <t>BELLEBNA YASSINE</t>
-  </si>
-  <si>
-    <t>MAAMMAR MOHAMED</t>
-  </si>
-  <si>
-    <t>BAHLIL MOUNIR</t>
-  </si>
-  <si>
-    <t>MECHETTEM KHALIDA</t>
-  </si>
-  <si>
-    <t>BENSEDDIK NADIA</t>
-  </si>
-  <si>
-    <t>CHIRANI SOUMIA</t>
-  </si>
-  <si>
-    <t>LARBI ZIDI</t>
-  </si>
-  <si>
-    <t>DOUIAICI MOHAMED</t>
-  </si>
-  <si>
-    <t>BEDDAD BOUCIF</t>
-  </si>
-  <si>
-    <t>BELHALLOUCHE LAKHDAR</t>
-  </si>
-  <si>
-    <t>ATTAR IMAD</t>
-  </si>
-  <si>
-    <t>BENSALEM MOHAMMED MUSTAPHA</t>
-  </si>
-  <si>
-    <t>DRIEF FAIZA</t>
-  </si>
-  <si>
-    <t>BENOUAR MOHAMED</t>
-  </si>
-  <si>
-    <t>ELGHODASSE ABDEL MADJID</t>
-  </si>
-  <si>
-    <t>HAMMAR MEHDI</t>
-  </si>
-  <si>
-    <t>IKKACHE NARIMEN</t>
-  </si>
-  <si>
-    <t>SAHRAOUI HADIL</t>
-  </si>
-  <si>
-    <t>MELIANI ABDELHAK</t>
-  </si>
-  <si>
-    <t>KADRI RANIA</t>
-  </si>
-  <si>
-    <t>BOULARAF AICHA</t>
-  </si>
-  <si>
-    <t>TALEB SOUMIA</t>
-  </si>
-  <si>
-    <t>BENMESSAOUD LEYLA</t>
-  </si>
-  <si>
-    <t>SAYAH RAFIK</t>
-  </si>
-  <si>
-    <t>NON DÉFINI-AUTO</t>
-  </si>
-  <si>
-    <t>BENSAID DJILALI</t>
-  </si>
-  <si>
-    <t>BENKHALLOUK KADDOUR</t>
-  </si>
-  <si>
-    <t>MILOUDI + BOUDRAA</t>
-  </si>
-  <si>
-    <t>BENAMARA ZINEB</t>
-  </si>
-  <si>
-    <t>BENSAID DJILALI + MASSIM</t>
-  </si>
-  <si>
-    <t>MILOUDI MOHAMED</t>
-  </si>
-  <si>
-    <t>DJEHAF MOHAMMED ABDELJALIL</t>
   </si>
   <si>
     <t>MEDLES IMED</t>
@@ -11715,7 +11715,7 @@
         <v>959</v>
       </c>
       <c r="C225" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="D225" t="s">
         <v>1613</v>
@@ -11724,7 +11724,7 @@
         <v>1639</v>
       </c>
       <c r="F225" t="s">
-        <v>1690</v>
+        <v>1642</v>
       </c>
       <c r="G225" t="s">
         <v>1795</v>
@@ -11741,7 +11741,7 @@
         <v>959</v>
       </c>
       <c r="C226" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="D226" t="s">
         <v>1613</v>
@@ -11750,7 +11750,7 @@
         <v>1639</v>
       </c>
       <c r="F226" t="s">
-        <v>1642</v>
+        <v>1690</v>
       </c>
       <c r="G226" t="s">
         <v>1795</v>
@@ -11767,7 +11767,7 @@
         <v>959</v>
       </c>
       <c r="C227" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="D227" t="s">
         <v>1614</v>
@@ -11776,7 +11776,7 @@
         <v>1639</v>
       </c>
       <c r="F227" t="s">
-        <v>1690</v>
+        <v>1642</v>
       </c>
       <c r="G227" t="s">
         <v>1795</v>
@@ -11793,7 +11793,7 @@
         <v>959</v>
       </c>
       <c r="C228" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="D228" t="s">
         <v>1614</v>
@@ -11802,7 +11802,7 @@
         <v>1639</v>
       </c>
       <c r="F228" t="s">
-        <v>1642</v>
+        <v>1690</v>
       </c>
       <c r="G228" t="s">
         <v>1795</v>
@@ -12937,7 +12937,7 @@
         <v>959</v>
       </c>
       <c r="C272" t="s">
-        <v>1332</v>
+        <v>1315</v>
       </c>
       <c r="D272" t="s">
         <v>1612</v>
@@ -12989,7 +12989,7 @@
         <v>959</v>
       </c>
       <c r="C274" t="s">
-        <v>1332</v>
+        <v>1315</v>
       </c>
       <c r="D274" t="s">
         <v>1616</v>
@@ -13015,7 +13015,7 @@
         <v>958</v>
       </c>
       <c r="C275" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D275" t="s">
         <v>1612</v>
@@ -13067,7 +13067,7 @@
         <v>978</v>
       </c>
       <c r="C277" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D277" t="s">
         <v>1622</v>
@@ -13119,7 +13119,7 @@
         <v>961</v>
       </c>
       <c r="C279" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="D279" t="s">
         <v>1615</v>
@@ -13145,7 +13145,7 @@
         <v>961</v>
       </c>
       <c r="C280" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="D280" t="s">
         <v>1616</v>
@@ -13249,7 +13249,7 @@
         <v>959</v>
       </c>
       <c r="C284" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D284" t="s">
         <v>1612</v>
@@ -13275,7 +13275,7 @@
         <v>959</v>
       </c>
       <c r="C285" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D285" t="s">
         <v>1612</v>
@@ -13301,7 +13301,7 @@
         <v>959</v>
       </c>
       <c r="C286" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="D286" t="s">
         <v>1613</v>
@@ -13353,7 +13353,7 @@
         <v>959</v>
       </c>
       <c r="C288" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="D288" t="s">
         <v>1614</v>
@@ -13405,7 +13405,7 @@
         <v>958</v>
       </c>
       <c r="C290" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D290" t="s">
         <v>1615</v>
@@ -13431,7 +13431,7 @@
         <v>959</v>
       </c>
       <c r="C291" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D291" t="s">
         <v>1616</v>
@@ -13457,7 +13457,7 @@
         <v>959</v>
       </c>
       <c r="C292" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D292" t="s">
         <v>1616</v>
@@ -13561,7 +13561,7 @@
         <v>958</v>
       </c>
       <c r="C296" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="D296" t="s">
         <v>1615</v>
@@ -13613,7 +13613,7 @@
         <v>982</v>
       </c>
       <c r="C298" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="D298" t="s">
         <v>1619</v>
@@ -13639,7 +13639,7 @@
         <v>983</v>
       </c>
       <c r="C299" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="D299" t="s">
         <v>1619</v>
@@ -13665,7 +13665,7 @@
         <v>982</v>
       </c>
       <c r="C300" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="D300" t="s">
         <v>1620</v>
@@ -13691,7 +13691,7 @@
         <v>983</v>
       </c>
       <c r="C301" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="D301" t="s">
         <v>1620</v>
@@ -13717,7 +13717,7 @@
         <v>984</v>
       </c>
       <c r="C302" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="D302" t="s">
         <v>1617</v>
@@ -13795,7 +13795,7 @@
         <v>985</v>
       </c>
       <c r="C305" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="D305" t="s">
         <v>1619</v>
@@ -13821,7 +13821,7 @@
         <v>958</v>
       </c>
       <c r="C306" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="D306" t="s">
         <v>1616</v>
@@ -13847,7 +13847,7 @@
         <v>961</v>
       </c>
       <c r="C307" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="D307" t="s">
         <v>1612</v>
@@ -13873,7 +13873,7 @@
         <v>958</v>
       </c>
       <c r="C308" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="D308" t="s">
         <v>1615</v>
@@ -13899,7 +13899,7 @@
         <v>986</v>
       </c>
       <c r="C309" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="D309" t="s">
         <v>1620</v>
@@ -13925,7 +13925,7 @@
         <v>959</v>
       </c>
       <c r="C310" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D310" t="s">
         <v>1612</v>
@@ -13951,7 +13951,7 @@
         <v>959</v>
       </c>
       <c r="C311" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D311" t="s">
         <v>1618</v>
@@ -13977,7 +13977,7 @@
         <v>959</v>
       </c>
       <c r="C312" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D312" t="s">
         <v>1613</v>
@@ -14003,7 +14003,7 @@
         <v>959</v>
       </c>
       <c r="C313" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D313" t="s">
         <v>1614</v>
@@ -14029,7 +14029,7 @@
         <v>987</v>
       </c>
       <c r="C314" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D314" t="s">
         <v>1619</v>
@@ -14055,7 +14055,7 @@
         <v>961</v>
       </c>
       <c r="C315" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D315" t="s">
         <v>1616</v>
@@ -14081,7 +14081,7 @@
         <v>959</v>
       </c>
       <c r="C316" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D316" t="s">
         <v>1612</v>
@@ -14159,7 +14159,7 @@
         <v>961</v>
       </c>
       <c r="C319" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="D319" t="s">
         <v>1615</v>
@@ -14185,7 +14185,7 @@
         <v>958</v>
       </c>
       <c r="C320" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D320" t="s">
         <v>1616</v>
@@ -14211,7 +14211,7 @@
         <v>958</v>
       </c>
       <c r="C321" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D321" t="s">
         <v>1616</v>
@@ -14237,7 +14237,7 @@
         <v>961</v>
       </c>
       <c r="C322" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D322" t="s">
         <v>1612</v>
@@ -14263,7 +14263,7 @@
         <v>958</v>
       </c>
       <c r="C323" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D323" t="s">
         <v>1613</v>
@@ -14289,7 +14289,7 @@
         <v>961</v>
       </c>
       <c r="C324" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D324" t="s">
         <v>1614</v>
@@ -14315,7 +14315,7 @@
         <v>959</v>
       </c>
       <c r="C325" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D325" t="s">
         <v>1615</v>
@@ -14341,7 +14341,7 @@
         <v>958</v>
       </c>
       <c r="C326" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D326" t="s">
         <v>1616</v>
@@ -14367,7 +14367,7 @@
         <v>961</v>
       </c>
       <c r="C327" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D327" t="s">
         <v>1612</v>
@@ -14393,7 +14393,7 @@
         <v>959</v>
       </c>
       <c r="C328" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D328" t="s">
         <v>1613</v>
@@ -14419,7 +14419,7 @@
         <v>958</v>
       </c>
       <c r="C329" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="D329" t="s">
         <v>1614</v>
@@ -14445,7 +14445,7 @@
         <v>958</v>
       </c>
       <c r="C330" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D330" t="s">
         <v>1615</v>
@@ -14471,7 +14471,7 @@
         <v>958</v>
       </c>
       <c r="C331" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D331" t="s">
         <v>1616</v>
@@ -14497,7 +14497,7 @@
         <v>958</v>
       </c>
       <c r="C332" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D332" t="s">
         <v>1612</v>
@@ -14523,7 +14523,7 @@
         <v>959</v>
       </c>
       <c r="C333" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D333" t="s">
         <v>1613</v>
@@ -14601,7 +14601,7 @@
         <v>988</v>
       </c>
       <c r="C336" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D336" t="s">
         <v>1612</v>
@@ -14627,7 +14627,7 @@
         <v>989</v>
       </c>
       <c r="C337" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D337" t="s">
         <v>1612</v>
@@ -14653,7 +14653,7 @@
         <v>959</v>
       </c>
       <c r="C338" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="D338" t="s">
         <v>1612</v>
@@ -14731,7 +14731,7 @@
         <v>988</v>
       </c>
       <c r="C341" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D341" t="s">
         <v>1618</v>
@@ -14757,7 +14757,7 @@
         <v>989</v>
       </c>
       <c r="C342" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D342" t="s">
         <v>1618</v>
@@ -14783,7 +14783,7 @@
         <v>959</v>
       </c>
       <c r="C343" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="D343" t="s">
         <v>1618</v>
@@ -14861,7 +14861,7 @@
         <v>988</v>
       </c>
       <c r="C346" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D346" t="s">
         <v>1613</v>
@@ -14887,7 +14887,7 @@
         <v>959</v>
       </c>
       <c r="C347" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D347" t="s">
         <v>1613</v>
@@ -14913,7 +14913,7 @@
         <v>989</v>
       </c>
       <c r="C348" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D348" t="s">
         <v>1613</v>
@@ -14939,7 +14939,7 @@
         <v>959</v>
       </c>
       <c r="C349" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="D349" t="s">
         <v>1613</v>
@@ -14965,7 +14965,7 @@
         <v>988</v>
       </c>
       <c r="C350" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D350" t="s">
         <v>1614</v>
@@ -14991,7 +14991,7 @@
         <v>959</v>
       </c>
       <c r="C351" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D351" t="s">
         <v>1614</v>
@@ -15017,7 +15017,7 @@
         <v>989</v>
       </c>
       <c r="C352" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D352" t="s">
         <v>1614</v>
@@ -15043,7 +15043,7 @@
         <v>959</v>
       </c>
       <c r="C353" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="D353" t="s">
         <v>1614</v>
@@ -15069,7 +15069,7 @@
         <v>958</v>
       </c>
       <c r="C354" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D354" t="s">
         <v>1615</v>
@@ -15121,7 +15121,7 @@
         <v>990</v>
       </c>
       <c r="C356" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D356" t="s">
         <v>1616</v>
@@ -15173,7 +15173,7 @@
         <v>991</v>
       </c>
       <c r="C358" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="D358" t="s">
         <v>1612</v>
@@ -15199,7 +15199,7 @@
         <v>991</v>
       </c>
       <c r="C359" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="D359" t="s">
         <v>1618</v>
@@ -15225,7 +15225,7 @@
         <v>959</v>
       </c>
       <c r="C360" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D360" t="s">
         <v>1613</v>
@@ -15251,7 +15251,7 @@
         <v>959</v>
       </c>
       <c r="C361" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D361" t="s">
         <v>1613</v>
@@ -15277,7 +15277,7 @@
         <v>991</v>
       </c>
       <c r="C362" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="D362" t="s">
         <v>1613</v>
@@ -15303,7 +15303,7 @@
         <v>959</v>
       </c>
       <c r="C363" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D363" t="s">
         <v>1614</v>
@@ -15329,7 +15329,7 @@
         <v>959</v>
       </c>
       <c r="C364" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D364" t="s">
         <v>1614</v>
@@ -15355,7 +15355,7 @@
         <v>991</v>
       </c>
       <c r="C365" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="D365" t="s">
         <v>1614</v>
@@ -15433,7 +15433,7 @@
         <v>959</v>
       </c>
       <c r="C368" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D368" t="s">
         <v>1623</v>
@@ -15459,7 +15459,7 @@
         <v>959</v>
       </c>
       <c r="C369" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D369" t="s">
         <v>1623</v>
@@ -15485,7 +15485,7 @@
         <v>959</v>
       </c>
       <c r="C370" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D370" t="s">
         <v>1624</v>
@@ -15511,7 +15511,7 @@
         <v>961</v>
       </c>
       <c r="C371" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D371" t="s">
         <v>1612</v>
@@ -15537,7 +15537,7 @@
         <v>961</v>
       </c>
       <c r="C372" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D372" t="s">
         <v>1612</v>
@@ -15563,7 +15563,7 @@
         <v>961</v>
       </c>
       <c r="C373" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D373" t="s">
         <v>1612</v>
@@ -15589,7 +15589,7 @@
         <v>959</v>
       </c>
       <c r="C374" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D374" t="s">
         <v>1625</v>
@@ -15615,7 +15615,7 @@
         <v>959</v>
       </c>
       <c r="C375" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="D375" t="s">
         <v>1625</v>
@@ -15641,7 +15641,7 @@
         <v>961</v>
       </c>
       <c r="C376" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D376" t="s">
         <v>1618</v>
@@ -15667,7 +15667,7 @@
         <v>961</v>
       </c>
       <c r="C377" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D377" t="s">
         <v>1618</v>
@@ -15693,7 +15693,7 @@
         <v>959</v>
       </c>
       <c r="C378" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D378" t="s">
         <v>1626</v>
@@ -15719,7 +15719,7 @@
         <v>959</v>
       </c>
       <c r="C379" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="D379" t="s">
         <v>1626</v>
@@ -15745,7 +15745,7 @@
         <v>961</v>
       </c>
       <c r="C380" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D380" t="s">
         <v>1613</v>
@@ -15771,7 +15771,7 @@
         <v>961</v>
       </c>
       <c r="C381" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D381" t="s">
         <v>1613</v>
@@ -15797,7 +15797,7 @@
         <v>961</v>
       </c>
       <c r="C382" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="D382" t="s">
         <v>1613</v>
@@ -15823,7 +15823,7 @@
         <v>959</v>
       </c>
       <c r="C383" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D383" t="s">
         <v>1613</v>
@@ -15849,7 +15849,7 @@
         <v>961</v>
       </c>
       <c r="C384" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D384" t="s">
         <v>1613</v>
@@ -15875,7 +15875,7 @@
         <v>992</v>
       </c>
       <c r="C385" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D385" t="s">
         <v>1613</v>
@@ -15901,7 +15901,7 @@
         <v>988</v>
       </c>
       <c r="C386" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D386" t="s">
         <v>1614</v>
@@ -15927,7 +15927,7 @@
         <v>961</v>
       </c>
       <c r="C387" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D387" t="s">
         <v>1614</v>
@@ -15953,7 +15953,7 @@
         <v>961</v>
       </c>
       <c r="C388" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="D388" t="s">
         <v>1614</v>
@@ -15979,7 +15979,7 @@
         <v>959</v>
       </c>
       <c r="C389" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D389" t="s">
         <v>1614</v>
@@ -16005,7 +16005,7 @@
         <v>992</v>
       </c>
       <c r="C390" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D390" t="s">
         <v>1614</v>
@@ -16031,7 +16031,7 @@
         <v>959</v>
       </c>
       <c r="C391" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="D391" t="s">
         <v>1627</v>
@@ -16057,7 +16057,7 @@
         <v>959</v>
       </c>
       <c r="C392" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="D392" t="s">
         <v>1627</v>
@@ -16083,7 +16083,7 @@
         <v>961</v>
       </c>
       <c r="C393" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D393" t="s">
         <v>1615</v>
@@ -16109,7 +16109,7 @@
         <v>959</v>
       </c>
       <c r="C394" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D394" t="s">
         <v>1615</v>
@@ -16135,7 +16135,7 @@
         <v>959</v>
       </c>
       <c r="C395" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D395" t="s">
         <v>1628</v>
@@ -16161,7 +16161,7 @@
         <v>959</v>
       </c>
       <c r="C396" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="D396" t="s">
         <v>1628</v>
@@ -16187,7 +16187,7 @@
         <v>959</v>
       </c>
       <c r="C397" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="D397" t="s">
         <v>1628</v>
@@ -16213,7 +16213,7 @@
         <v>991</v>
       </c>
       <c r="C398" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D398" t="s">
         <v>1616</v>
@@ -16239,7 +16239,7 @@
         <v>959</v>
       </c>
       <c r="C399" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D399" t="s">
         <v>1616</v>
@@ -16291,7 +16291,7 @@
         <v>959</v>
       </c>
       <c r="C401" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="D401" t="s">
         <v>1624</v>
@@ -16317,7 +16317,7 @@
         <v>988</v>
       </c>
       <c r="C402" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D402" t="s">
         <v>1612</v>
@@ -16343,7 +16343,7 @@
         <v>991</v>
       </c>
       <c r="C403" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D403" t="s">
         <v>1612</v>
@@ -16421,7 +16421,7 @@
         <v>959</v>
       </c>
       <c r="C406" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="D406" t="s">
         <v>1625</v>
@@ -16447,7 +16447,7 @@
         <v>961</v>
       </c>
       <c r="C407" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D407" t="s">
         <v>1618</v>
@@ -16473,7 +16473,7 @@
         <v>988</v>
       </c>
       <c r="C408" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D408" t="s">
         <v>1618</v>
@@ -16499,7 +16499,7 @@
         <v>991</v>
       </c>
       <c r="C409" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D409" t="s">
         <v>1618</v>
@@ -16525,7 +16525,7 @@
         <v>961</v>
       </c>
       <c r="C410" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D410" t="s">
         <v>1618</v>
@@ -16551,7 +16551,7 @@
         <v>988</v>
       </c>
       <c r="C411" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D411" t="s">
         <v>1613</v>
@@ -16577,7 +16577,7 @@
         <v>959</v>
       </c>
       <c r="C412" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D412" t="s">
         <v>1613</v>
@@ -16603,7 +16603,7 @@
         <v>991</v>
       </c>
       <c r="C413" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D413" t="s">
         <v>1613</v>
@@ -16655,7 +16655,7 @@
         <v>992</v>
       </c>
       <c r="C415" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D415" t="s">
         <v>1613</v>
@@ -16707,7 +16707,7 @@
         <v>988</v>
       </c>
       <c r="C417" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D417" t="s">
         <v>1614</v>
@@ -16733,7 +16733,7 @@
         <v>959</v>
       </c>
       <c r="C418" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D418" t="s">
         <v>1614</v>
@@ -16759,7 +16759,7 @@
         <v>991</v>
       </c>
       <c r="C419" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D419" t="s">
         <v>1614</v>
@@ -16785,7 +16785,7 @@
         <v>961</v>
       </c>
       <c r="C420" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D420" t="s">
         <v>1614</v>
@@ -16811,7 +16811,7 @@
         <v>992</v>
       </c>
       <c r="C421" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D421" t="s">
         <v>1614</v>
@@ -16863,7 +16863,7 @@
         <v>958</v>
       </c>
       <c r="C423" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D423" t="s">
         <v>1615</v>
@@ -16889,7 +16889,7 @@
         <v>958</v>
       </c>
       <c r="C424" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D424" t="s">
         <v>1615</v>
@@ -16915,7 +16915,7 @@
         <v>990</v>
       </c>
       <c r="C425" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D425" t="s">
         <v>1616</v>
@@ -16941,7 +16941,7 @@
         <v>993</v>
       </c>
       <c r="C426" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D426" t="s">
         <v>1616</v>
@@ -16993,7 +16993,7 @@
         <v>961</v>
       </c>
       <c r="C428" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D428" t="s">
         <v>1612</v>
@@ -17019,7 +17019,7 @@
         <v>959</v>
       </c>
       <c r="C429" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D429" t="s">
         <v>1612</v>
@@ -17045,7 +17045,7 @@
         <v>959</v>
       </c>
       <c r="C430" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D430" t="s">
         <v>1612</v>
@@ -17071,7 +17071,7 @@
         <v>959</v>
       </c>
       <c r="C431" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D431" t="s">
         <v>1612</v>
@@ -17123,7 +17123,7 @@
         <v>961</v>
       </c>
       <c r="C433" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D433" t="s">
         <v>1618</v>
@@ -17149,7 +17149,7 @@
         <v>959</v>
       </c>
       <c r="C434" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D434" t="s">
         <v>1618</v>
@@ -17175,7 +17175,7 @@
         <v>959</v>
       </c>
       <c r="C435" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D435" t="s">
         <v>1618</v>
@@ -17201,7 +17201,7 @@
         <v>959</v>
       </c>
       <c r="C436" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D436" t="s">
         <v>1618</v>
@@ -17253,7 +17253,7 @@
         <v>961</v>
       </c>
       <c r="C438" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D438" t="s">
         <v>1613</v>
@@ -17279,7 +17279,7 @@
         <v>961</v>
       </c>
       <c r="C439" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D439" t="s">
         <v>1613</v>
@@ -17357,7 +17357,7 @@
         <v>961</v>
       </c>
       <c r="C442" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="D442" t="s">
         <v>1615</v>
@@ -17383,7 +17383,7 @@
         <v>961</v>
       </c>
       <c r="C443" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D443" t="s">
         <v>1615</v>
@@ -17409,7 +17409,7 @@
         <v>996</v>
       </c>
       <c r="C444" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D444" t="s">
         <v>1615</v>
@@ -17487,7 +17487,7 @@
         <v>961</v>
       </c>
       <c r="C447" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="D447" t="s">
         <v>1616</v>
@@ -17513,7 +17513,7 @@
         <v>961</v>
       </c>
       <c r="C448" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D448" t="s">
         <v>1616</v>
@@ -17539,7 +17539,7 @@
         <v>996</v>
       </c>
       <c r="C449" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D449" t="s">
         <v>1616</v>
@@ -17617,7 +17617,7 @@
         <v>998</v>
       </c>
       <c r="C452" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D452" t="s">
         <v>1615</v>
@@ -17643,7 +17643,7 @@
         <v>999</v>
       </c>
       <c r="C453" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D453" t="s">
         <v>1616</v>
@@ -17669,7 +17669,7 @@
         <v>1000</v>
       </c>
       <c r="C454" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="D454" t="s">
         <v>1612</v>
@@ -17695,7 +17695,7 @@
         <v>1001</v>
       </c>
       <c r="C455" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="D455" t="s">
         <v>1615</v>
@@ -17721,7 +17721,7 @@
         <v>1000</v>
       </c>
       <c r="C456" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="D456" t="s">
         <v>1616</v>
@@ -17773,7 +17773,7 @@
         <v>1003</v>
       </c>
       <c r="C458" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D458" t="s">
         <v>1613</v>
@@ -17799,7 +17799,7 @@
         <v>1004</v>
       </c>
       <c r="C459" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D459" t="s">
         <v>1614</v>
@@ -17851,7 +17851,7 @@
         <v>1006</v>
       </c>
       <c r="C461" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D461" t="s">
         <v>1612</v>
@@ -17877,7 +17877,7 @@
         <v>1007</v>
       </c>
       <c r="C462" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D462" t="s">
         <v>1612</v>
@@ -17929,7 +17929,7 @@
         <v>1008</v>
       </c>
       <c r="C464" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D464" t="s">
         <v>1613</v>
@@ -17955,7 +17955,7 @@
         <v>1009</v>
       </c>
       <c r="C465" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D465" t="s">
         <v>1614</v>
@@ -18085,7 +18085,7 @@
         <v>1011</v>
       </c>
       <c r="C470" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="D470" t="s">
         <v>1629</v>
@@ -18111,7 +18111,7 @@
         <v>1012</v>
       </c>
       <c r="C471" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D471" t="s">
         <v>1615</v>
@@ -18137,7 +18137,7 @@
         <v>1013</v>
       </c>
       <c r="C472" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D472" t="s">
         <v>1616</v>
@@ -18189,7 +18189,7 @@
         <v>1015</v>
       </c>
       <c r="C474" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="D474" t="s">
         <v>1613</v>
@@ -18215,7 +18215,7 @@
         <v>1015</v>
       </c>
       <c r="C475" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="D475" t="s">
         <v>1614</v>
@@ -18241,7 +18241,7 @@
         <v>1016</v>
       </c>
       <c r="C476" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D476" t="s">
         <v>1615</v>
@@ -18267,7 +18267,7 @@
         <v>1017</v>
       </c>
       <c r="C477" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D477" t="s">
         <v>1616</v>
@@ -18293,7 +18293,7 @@
         <v>1018</v>
       </c>
       <c r="C478" t="s">
-        <v>1315</v>
+        <v>1382</v>
       </c>
       <c r="D478" t="s">
         <v>1612</v>
@@ -18319,7 +18319,7 @@
         <v>1019</v>
       </c>
       <c r="C479" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D479" t="s">
         <v>1618</v>
@@ -18345,7 +18345,7 @@
         <v>1020</v>
       </c>
       <c r="C480" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D480" t="s">
         <v>1618</v>
@@ -18371,7 +18371,7 @@
         <v>1021</v>
       </c>
       <c r="C481" t="s">
-        <v>1315</v>
+        <v>1382</v>
       </c>
       <c r="D481" t="s">
         <v>1615</v>
@@ -18397,7 +18397,7 @@
         <v>1018</v>
       </c>
       <c r="C482" t="s">
-        <v>1315</v>
+        <v>1382</v>
       </c>
       <c r="D482" t="s">
         <v>1616</v>
@@ -18449,7 +18449,7 @@
         <v>1023</v>
       </c>
       <c r="C484" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D484" t="s">
         <v>1613</v>
@@ -18475,7 +18475,7 @@
         <v>1024</v>
       </c>
       <c r="C485" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D485" t="s">
         <v>1614</v>
@@ -18631,7 +18631,7 @@
         <v>1027</v>
       </c>
       <c r="C491" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D491" t="s">
         <v>1613</v>
@@ -18657,7 +18657,7 @@
         <v>1028</v>
       </c>
       <c r="C492" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D492" t="s">
         <v>1614</v>
@@ -18683,7 +18683,7 @@
         <v>1029</v>
       </c>
       <c r="C493" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D493" t="s">
         <v>1615</v>
@@ -18709,7 +18709,7 @@
         <v>1030</v>
       </c>
       <c r="C494" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D494" t="s">
         <v>1616</v>
@@ -18839,7 +18839,7 @@
         <v>961</v>
       </c>
       <c r="C499" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D499" t="s">
         <v>1614</v>
@@ -19307,7 +19307,7 @@
         <v>958</v>
       </c>
       <c r="C517" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="D517" t="s">
         <v>1612</v>
@@ -19333,7 +19333,7 @@
         <v>961</v>
       </c>
       <c r="C518" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D518" t="s">
         <v>1613</v>
@@ -19359,7 +19359,7 @@
         <v>961</v>
       </c>
       <c r="C519" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D519" t="s">
         <v>1614</v>
@@ -19567,7 +19567,7 @@
         <v>961</v>
       </c>
       <c r="C527" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D527" t="s">
         <v>1614</v>
@@ -20347,7 +20347,7 @@
         <v>958</v>
       </c>
       <c r="C557" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D557" t="s">
         <v>1612</v>
@@ -20789,7 +20789,7 @@
         <v>1043</v>
       </c>
       <c r="C574" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D574" t="s">
         <v>1612</v>
@@ -21127,7 +21127,7 @@
         <v>1054</v>
       </c>
       <c r="C587" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D587" t="s">
         <v>1612</v>
@@ -21153,7 +21153,7 @@
         <v>1055</v>
       </c>
       <c r="C588" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D588" t="s">
         <v>1615</v>
@@ -21179,7 +21179,7 @@
         <v>1056</v>
       </c>
       <c r="C589" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D589" t="s">
         <v>1616</v>
@@ -21231,7 +21231,7 @@
         <v>1058</v>
       </c>
       <c r="C591" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D591" t="s">
         <v>1612</v>
@@ -21309,7 +21309,7 @@
         <v>1058</v>
       </c>
       <c r="C594" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D594" t="s">
         <v>1616</v>
@@ -21439,7 +21439,7 @@
         <v>1064</v>
       </c>
       <c r="C599" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D599" t="s">
         <v>1612</v>
@@ -21621,7 +21621,7 @@
         <v>1064</v>
       </c>
       <c r="C606" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D606" t="s">
         <v>1616</v>
@@ -21699,7 +21699,7 @@
         <v>1068</v>
       </c>
       <c r="C609" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D609" t="s">
         <v>1612</v>
@@ -21751,7 +21751,7 @@
         <v>1070</v>
       </c>
       <c r="C611" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D611" t="s">
         <v>1616</v>
@@ -21777,7 +21777,7 @@
         <v>961</v>
       </c>
       <c r="C612" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D612" t="s">
         <v>1612</v>
@@ -21803,7 +21803,7 @@
         <v>961</v>
       </c>
       <c r="C613" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="D613" t="s">
         <v>1612</v>
@@ -21907,7 +21907,7 @@
         <v>959</v>
       </c>
       <c r="C617" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D617" t="s">
         <v>1613</v>
@@ -22063,7 +22063,7 @@
         <v>958</v>
       </c>
       <c r="C623" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D623" t="s">
         <v>1615</v>
@@ -22141,7 +22141,7 @@
         <v>961</v>
       </c>
       <c r="C626" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D626" t="s">
         <v>1616</v>
@@ -22167,7 +22167,7 @@
         <v>961</v>
       </c>
       <c r="C627" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D627" t="s">
         <v>1612</v>
@@ -22271,7 +22271,7 @@
         <v>958</v>
       </c>
       <c r="C631" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D631" t="s">
         <v>1615</v>
@@ -22505,7 +22505,7 @@
         <v>959</v>
       </c>
       <c r="C640" t="s">
-        <v>1332</v>
+        <v>1315</v>
       </c>
       <c r="D640" t="s">
         <v>1614</v>
@@ -22583,7 +22583,7 @@
         <v>958</v>
       </c>
       <c r="C643" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D643" t="s">
         <v>1612</v>
@@ -22661,7 +22661,7 @@
         <v>959</v>
       </c>
       <c r="C646" t="s">
-        <v>1332</v>
+        <v>1315</v>
       </c>
       <c r="D646" t="s">
         <v>1613</v>
@@ -22739,7 +22739,7 @@
         <v>961</v>
       </c>
       <c r="C649" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D649" t="s">
         <v>1616</v>
@@ -25391,7 +25391,7 @@
         <v>1082</v>
       </c>
       <c r="C751" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D751" t="s">
         <v>1615</v>
@@ -25833,7 +25833,7 @@
         <v>1095</v>
       </c>
       <c r="C768" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D768" t="s">
         <v>1619</v>
@@ -25859,7 +25859,7 @@
         <v>959</v>
       </c>
       <c r="C769" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D769" t="s">
         <v>1616</v>
@@ -25911,7 +25911,7 @@
         <v>959</v>
       </c>
       <c r="C771" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D771" t="s">
         <v>1615</v>
@@ -25937,7 +25937,7 @@
         <v>961</v>
       </c>
       <c r="C772" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D772" t="s">
         <v>1612</v>
@@ -26015,7 +26015,7 @@
         <v>1098</v>
       </c>
       <c r="C775" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D775" t="s">
         <v>1620</v>
@@ -26041,7 +26041,7 @@
         <v>961</v>
       </c>
       <c r="C776" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D776" t="s">
         <v>1612</v>
@@ -26067,7 +26067,7 @@
         <v>1099</v>
       </c>
       <c r="C777" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D777" t="s">
         <v>1619</v>
@@ -26119,7 +26119,7 @@
         <v>1100</v>
       </c>
       <c r="C779" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D779" t="s">
         <v>1612</v>
@@ -26327,7 +26327,7 @@
         <v>1107</v>
       </c>
       <c r="C787" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D787" t="s">
         <v>1615</v>
@@ -26665,7 +26665,7 @@
         <v>1115</v>
       </c>
       <c r="C800" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D800" t="s">
         <v>1615</v>
@@ -26717,7 +26717,7 @@
         <v>1115</v>
       </c>
       <c r="C802" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D802" t="s">
         <v>1616</v>
@@ -26899,7 +26899,7 @@
         <v>1120</v>
       </c>
       <c r="C809" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D809" t="s">
         <v>1619</v>
@@ -27029,7 +27029,7 @@
         <v>961</v>
       </c>
       <c r="C814" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D814" t="s">
         <v>1612</v>
@@ -27055,7 +27055,7 @@
         <v>1124</v>
       </c>
       <c r="C815" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D815" t="s">
         <v>1621</v>
@@ -27107,7 +27107,7 @@
         <v>1125</v>
       </c>
       <c r="C817" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D817" t="s">
         <v>1620</v>
@@ -27133,7 +27133,7 @@
         <v>961</v>
       </c>
       <c r="C818" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D818" t="s">
         <v>1612</v>
@@ -27185,7 +27185,7 @@
         <v>1127</v>
       </c>
       <c r="C820" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D820" t="s">
         <v>1619</v>
@@ -28667,7 +28667,7 @@
         <v>961</v>
       </c>
       <c r="C877" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D877" t="s">
         <v>1616</v>
@@ -28719,7 +28719,7 @@
         <v>1132</v>
       </c>
       <c r="C879" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D879" t="s">
         <v>1622</v>
@@ -28745,7 +28745,7 @@
         <v>1132</v>
       </c>
       <c r="C880" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D880" t="s">
         <v>1621</v>
@@ -28823,7 +28823,7 @@
         <v>958</v>
       </c>
       <c r="C883" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="D883" t="s">
         <v>1612</v>
@@ -28901,7 +28901,7 @@
         <v>1135</v>
       </c>
       <c r="C886" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="D886" t="s">
         <v>1619</v>
@@ -28927,7 +28927,7 @@
         <v>1136</v>
       </c>
       <c r="C887" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="D887" t="s">
         <v>1620</v>
@@ -28979,7 +28979,7 @@
         <v>959</v>
       </c>
       <c r="C889" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D889" t="s">
         <v>1613</v>
@@ -29031,7 +29031,7 @@
         <v>959</v>
       </c>
       <c r="C891" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D891" t="s">
         <v>1614</v>
@@ -29109,7 +29109,7 @@
         <v>961</v>
       </c>
       <c r="C894" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D894" t="s">
         <v>1616</v>
@@ -29525,7 +29525,7 @@
         <v>1074</v>
       </c>
       <c r="C910" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D910" t="s">
         <v>1612</v>
@@ -29863,7 +29863,7 @@
         <v>959</v>
       </c>
       <c r="C923" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D923" t="s">
         <v>1616</v>
@@ -29889,7 +29889,7 @@
         <v>1145</v>
       </c>
       <c r="C924" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D924" t="s">
         <v>1613</v>
@@ -29941,7 +29941,7 @@
         <v>961</v>
       </c>
       <c r="C926" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D926" t="s">
         <v>1615</v>
@@ -29967,7 +29967,7 @@
         <v>1146</v>
       </c>
       <c r="C927" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D927" t="s">
         <v>1620</v>
@@ -30019,7 +30019,7 @@
         <v>1148</v>
       </c>
       <c r="C929" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D929" t="s">
         <v>1619</v>
@@ -30045,7 +30045,7 @@
         <v>961</v>
       </c>
       <c r="C930" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D930" t="s">
         <v>1616</v>
@@ -30253,7 +30253,7 @@
         <v>1074</v>
       </c>
       <c r="C938" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D938" t="s">
         <v>1613</v>
@@ -30279,7 +30279,7 @@
         <v>961</v>
       </c>
       <c r="C939" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D939" t="s">
         <v>1614</v>
@@ -30877,7 +30877,7 @@
         <v>959</v>
       </c>
       <c r="C962" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D962" t="s">
         <v>1616</v>
@@ -30929,7 +30929,7 @@
         <v>1155</v>
       </c>
       <c r="C964" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D964" t="s">
         <v>1622</v>
@@ -30981,7 +30981,7 @@
         <v>961</v>
       </c>
       <c r="C966" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D966" t="s">
         <v>1615</v>
@@ -31007,7 +31007,7 @@
         <v>1156</v>
       </c>
       <c r="C967" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D967" t="s">
         <v>1620</v>
@@ -31033,7 +31033,7 @@
         <v>1157</v>
       </c>
       <c r="C968" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D968" t="s">
         <v>1619</v>
@@ -31059,7 +31059,7 @@
         <v>961</v>
       </c>
       <c r="C969" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D969" t="s">
         <v>1616</v>
@@ -31657,7 +31657,7 @@
         <v>958</v>
       </c>
       <c r="C992" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D992" t="s">
         <v>1612</v>
@@ -31683,7 +31683,7 @@
         <v>959</v>
       </c>
       <c r="C993" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D993" t="s">
         <v>1613</v>
@@ -31709,7 +31709,7 @@
         <v>959</v>
       </c>
       <c r="C994" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D994" t="s">
         <v>1614</v>
@@ -31839,7 +31839,7 @@
         <v>958</v>
       </c>
       <c r="C999" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D999" t="s">
         <v>1612</v>
@@ -31865,7 +31865,7 @@
         <v>959</v>
       </c>
       <c r="C1000" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D1000" t="s">
         <v>1613</v>
@@ -31917,7 +31917,7 @@
         <v>959</v>
       </c>
       <c r="C1002" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D1002" t="s">
         <v>1614</v>
@@ -32853,7 +32853,7 @@
         <v>959</v>
       </c>
       <c r="C1038" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1038" t="s">
         <v>1613</v>
@@ -32879,7 +32879,7 @@
         <v>959</v>
       </c>
       <c r="C1039" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D1039" t="s">
         <v>1615</v>
@@ -32931,7 +32931,7 @@
         <v>958</v>
       </c>
       <c r="C1041" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1041" t="s">
         <v>1612</v>
@@ -32957,7 +32957,7 @@
         <v>958</v>
       </c>
       <c r="C1042" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1042" t="s">
         <v>1615</v>
@@ -33243,7 +33243,7 @@
         <v>959</v>
       </c>
       <c r="C1053" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1053" t="s">
         <v>1612</v>
@@ -33451,7 +33451,7 @@
         <v>1183</v>
       </c>
       <c r="C1061" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="D1061" t="s">
         <v>1613</v>
@@ -33841,7 +33841,7 @@
         <v>1193</v>
       </c>
       <c r="C1076" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D1076" t="s">
         <v>1617</v>
@@ -33867,7 +33867,7 @@
         <v>958</v>
       </c>
       <c r="C1077" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1077" t="s">
         <v>1613</v>
@@ -33893,7 +33893,7 @@
         <v>961</v>
       </c>
       <c r="C1078" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1078" t="s">
         <v>1614</v>
@@ -33945,7 +33945,7 @@
         <v>1194</v>
       </c>
       <c r="C1080" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D1080" t="s">
         <v>1620</v>
@@ -33971,7 +33971,7 @@
         <v>958</v>
       </c>
       <c r="C1081" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1081" t="s">
         <v>1612</v>
@@ -33997,7 +33997,7 @@
         <v>958</v>
       </c>
       <c r="C1082" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1082" t="s">
         <v>1615</v>
@@ -34049,7 +34049,7 @@
         <v>959</v>
       </c>
       <c r="C1084" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D1084" t="s">
         <v>1613</v>
@@ -34205,7 +34205,7 @@
         <v>959</v>
       </c>
       <c r="C1090" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1090" t="s">
         <v>1613</v>
@@ -35375,7 +35375,7 @@
         <v>961</v>
       </c>
       <c r="C1135" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="D1135" t="s">
         <v>1612</v>
@@ -35401,7 +35401,7 @@
         <v>958</v>
       </c>
       <c r="C1136" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1136" t="s">
         <v>1615</v>
@@ -35427,7 +35427,7 @@
         <v>1198</v>
       </c>
       <c r="C1137" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="D1137" t="s">
         <v>1616</v>
@@ -35453,7 +35453,7 @@
         <v>958</v>
       </c>
       <c r="C1138" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1138" t="s">
         <v>1612</v>
@@ -35479,7 +35479,7 @@
         <v>958</v>
       </c>
       <c r="C1139" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1139" t="s">
         <v>1615</v>
@@ -35505,7 +35505,7 @@
         <v>1199</v>
       </c>
       <c r="C1140" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1140" t="s">
         <v>1617</v>
@@ -35531,7 +35531,7 @@
         <v>1200</v>
       </c>
       <c r="C1141" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D1141" t="s">
         <v>1613</v>
@@ -35557,7 +35557,7 @@
         <v>1201</v>
       </c>
       <c r="C1142" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D1142" t="s">
         <v>1614</v>
@@ -35609,7 +35609,7 @@
         <v>1203</v>
       </c>
       <c r="C1144" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D1144" t="s">
         <v>1617</v>
@@ -35635,7 +35635,7 @@
         <v>959</v>
       </c>
       <c r="C1145" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1145" t="s">
         <v>1613</v>
@@ -35661,7 +35661,7 @@
         <v>958</v>
       </c>
       <c r="C1146" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1146" t="s">
         <v>1615</v>
@@ -35687,7 +35687,7 @@
         <v>1204</v>
       </c>
       <c r="C1147" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D1147" t="s">
         <v>1620</v>
@@ -35765,7 +35765,7 @@
         <v>1205</v>
       </c>
       <c r="C1150" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1150" t="s">
         <v>1613</v>
@@ -35791,7 +35791,7 @@
         <v>1206</v>
       </c>
       <c r="C1151" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D1151" t="s">
         <v>1613</v>
@@ -35817,7 +35817,7 @@
         <v>1205</v>
       </c>
       <c r="C1152" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1152" t="s">
         <v>1614</v>
@@ -35843,7 +35843,7 @@
         <v>1206</v>
       </c>
       <c r="C1153" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D1153" t="s">
         <v>1614</v>
@@ -36077,7 +36077,7 @@
         <v>958</v>
       </c>
       <c r="C1162" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1162" t="s">
         <v>1612</v>
@@ -36103,7 +36103,7 @@
         <v>958</v>
       </c>
       <c r="C1163" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1163" t="s">
         <v>1615</v>
@@ -36155,7 +36155,7 @@
         <v>1213</v>
       </c>
       <c r="C1165" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D1165" t="s">
         <v>1622</v>
@@ -36181,7 +36181,7 @@
         <v>1214</v>
       </c>
       <c r="C1166" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D1166" t="s">
         <v>1621</v>
@@ -36233,7 +36233,7 @@
         <v>958</v>
       </c>
       <c r="C1168" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D1168" t="s">
         <v>1612</v>
@@ -36259,7 +36259,7 @@
         <v>959</v>
       </c>
       <c r="C1169" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1169" t="s">
         <v>1613</v>
@@ -36337,7 +36337,7 @@
         <v>1218</v>
       </c>
       <c r="C1172" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D1172" t="s">
         <v>1622</v>
@@ -36961,7 +36961,7 @@
         <v>1220</v>
       </c>
       <c r="C1196" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D1196" t="s">
         <v>1622</v>
@@ -36987,7 +36987,7 @@
         <v>958</v>
       </c>
       <c r="C1197" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1197" t="s">
         <v>1615</v>
@@ -37013,7 +37013,7 @@
         <v>1221</v>
       </c>
       <c r="C1198" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1198" t="s">
         <v>1620</v>
@@ -37039,7 +37039,7 @@
         <v>958</v>
       </c>
       <c r="C1199" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1199" t="s">
         <v>1612</v>
@@ -37065,7 +37065,7 @@
         <v>958</v>
       </c>
       <c r="C1200" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1200" t="s">
         <v>1615</v>
@@ -37091,7 +37091,7 @@
         <v>958</v>
       </c>
       <c r="C1201" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1201" t="s">
         <v>1613</v>
@@ -37117,7 +37117,7 @@
         <v>961</v>
       </c>
       <c r="C1202" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1202" t="s">
         <v>1614</v>
@@ -37143,7 +37143,7 @@
         <v>959</v>
       </c>
       <c r="C1203" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1203" t="s">
         <v>1615</v>
@@ -37169,7 +37169,7 @@
         <v>1222</v>
       </c>
       <c r="C1204" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1204" t="s">
         <v>1620</v>
@@ -37195,7 +37195,7 @@
         <v>961</v>
       </c>
       <c r="C1205" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D1205" t="s">
         <v>1612</v>
@@ -37221,7 +37221,7 @@
         <v>961</v>
       </c>
       <c r="C1206" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D1206" t="s">
         <v>1613</v>
@@ -37247,7 +37247,7 @@
         <v>958</v>
       </c>
       <c r="C1207" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D1207" t="s">
         <v>1615</v>
@@ -37273,7 +37273,7 @@
         <v>958</v>
       </c>
       <c r="C1208" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D1208" t="s">
         <v>1616</v>
@@ -37299,7 +37299,7 @@
         <v>1223</v>
       </c>
       <c r="C1209" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D1209" t="s">
         <v>1617</v>
@@ -37325,7 +37325,7 @@
         <v>959</v>
       </c>
       <c r="C1210" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1210" t="s">
         <v>1613</v>
@@ -37351,7 +37351,7 @@
         <v>1224</v>
       </c>
       <c r="C1211" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="D1211" t="s">
         <v>1619</v>
@@ -37377,7 +37377,7 @@
         <v>961</v>
       </c>
       <c r="C1212" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="D1212" t="s">
         <v>1616</v>
@@ -37429,7 +37429,7 @@
         <v>958</v>
       </c>
       <c r="C1214" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D1214" t="s">
         <v>1615</v>
@@ -37455,7 +37455,7 @@
         <v>961</v>
       </c>
       <c r="C1215" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D1215" t="s">
         <v>1616</v>
@@ -42135,7 +42135,7 @@
         <v>958</v>
       </c>
       <c r="C1395" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D1395" t="s">
         <v>1612</v>
@@ -42499,7 +42499,7 @@
         <v>958</v>
       </c>
       <c r="C1409" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D1409" t="s">
         <v>1615</v>
@@ -42603,7 +42603,7 @@
         <v>1225</v>
       </c>
       <c r="C1413" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D1413" t="s">
         <v>1612</v>
@@ -42811,7 +42811,7 @@
         <v>1230</v>
       </c>
       <c r="C1421" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1421" t="s">
         <v>1613</v>
@@ -42915,7 +42915,7 @@
         <v>1230</v>
       </c>
       <c r="C1425" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1425" t="s">
         <v>1614</v>
@@ -43253,7 +43253,7 @@
         <v>1225</v>
       </c>
       <c r="C1438" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D1438" t="s">
         <v>1615</v>
@@ -44969,7 +44969,7 @@
         <v>961</v>
       </c>
       <c r="C1504" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D1504" t="s">
         <v>1612</v>
@@ -45151,7 +45151,7 @@
         <v>961</v>
       </c>
       <c r="C1511" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D1511" t="s">
         <v>1616</v>
@@ -45229,7 +45229,7 @@
         <v>959</v>
       </c>
       <c r="C1514" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1514" t="s">
         <v>1612</v>
@@ -45255,7 +45255,7 @@
         <v>959</v>
       </c>
       <c r="C1515" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D1515" t="s">
         <v>1612</v>
@@ -45281,7 +45281,7 @@
         <v>959</v>
       </c>
       <c r="C1516" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1516" t="s">
         <v>1618</v>
@@ -45307,7 +45307,7 @@
         <v>959</v>
       </c>
       <c r="C1517" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D1517" t="s">
         <v>1613</v>
@@ -45359,7 +45359,7 @@
         <v>959</v>
       </c>
       <c r="C1519" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D1519" t="s">
         <v>1616</v>
@@ -45385,7 +45385,7 @@
         <v>961</v>
       </c>
       <c r="C1520" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D1520" t="s">
         <v>1612</v>
@@ -45515,7 +45515,7 @@
         <v>958</v>
       </c>
       <c r="C1525" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D1525" t="s">
         <v>1613</v>
@@ -45645,7 +45645,7 @@
         <v>959</v>
       </c>
       <c r="C1530" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D1530" t="s">
         <v>1618</v>
@@ -45775,7 +45775,7 @@
         <v>958</v>
       </c>
       <c r="C1535" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D1535" t="s">
         <v>1615</v>
@@ -45905,7 +45905,7 @@
         <v>959</v>
       </c>
       <c r="C1540" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1540" t="s">
         <v>1618</v>
@@ -45957,7 +45957,7 @@
         <v>959</v>
       </c>
       <c r="C1542" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1542" t="s">
         <v>1613</v>
@@ -46087,7 +46087,7 @@
         <v>959</v>
       </c>
       <c r="C1547" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1547" t="s">
         <v>1614</v>
@@ -46243,7 +46243,7 @@
         <v>959</v>
       </c>
       <c r="C1553" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1553" t="s">
         <v>1616</v>
@@ -47361,7 +47361,7 @@
         <v>959</v>
       </c>
       <c r="C1596" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D1596" t="s">
         <v>1634</v>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -13460,7 +13460,7 @@
         <v>1637</v>
       </c>
       <c r="F292" t="s">
-        <v>1679</v>
+        <v>1669</v>
       </c>
       <c r="G292" t="s">
         <v>1795</v>
@@ -25888,7 +25888,7 @@
         <v>1635</v>
       </c>
       <c r="F770" t="s">
-        <v>1669</v>
+        <v>1640</v>
       </c>
       <c r="G770" t="s">
         <v>1810</v>
@@ -30854,7 +30854,7 @@
         <v>1635</v>
       </c>
       <c r="F961" t="s">
-        <v>1669</v>
+        <v>1640</v>
       </c>
       <c r="G961" t="s">
         <v>1819</v>
@@ -36288,7 +36288,7 @@
         <v>1637</v>
       </c>
       <c r="F1170" t="s">
-        <v>1683</v>
+        <v>1688</v>
       </c>
       <c r="G1170" t="s">
         <v>1829</v>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -1246,16 +1246,16 @@
     <t>Cours-EAD-Logiciels de Simulation</t>
   </si>
   <si>
+    <t>TD-Réseaux électriques-G2</t>
+  </si>
+  <si>
+    <t>TP-Systèmes Asservis-SG12</t>
+  </si>
+  <si>
+    <t>TD-Théorie du champ électromagnétique-G1</t>
+  </si>
+  <si>
     <t>TD-Théorie du champ électromagnétique-G2</t>
-  </si>
-  <si>
-    <t>TD-Réseaux électriques-G2</t>
-  </si>
-  <si>
-    <t>TP-Systèmes Asservis-SG12</t>
-  </si>
-  <si>
-    <t>TD-Théorie du champ électromagnétique-G1</t>
   </si>
   <si>
     <t>Cours-Capteurs et Métrologie</t>
@@ -11039,7 +11039,7 @@
         <v>1304</v>
       </c>
       <c r="D199" t="s">
-        <v>1613</v>
+        <v>1618</v>
       </c>
       <c r="E199" t="s">
         <v>1639</v>
@@ -11065,7 +11065,7 @@
         <v>1304</v>
       </c>
       <c r="D200" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="E200" t="s">
         <v>1639</v>
@@ -22190,16 +22190,16 @@
         <v>964</v>
       </c>
       <c r="C628" t="s">
-        <v>1332</v>
+        <v>1346</v>
       </c>
       <c r="D628" t="s">
-        <v>1616</v>
+        <v>1612</v>
       </c>
       <c r="E628" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="F628" t="s">
-        <v>1691</v>
+        <v>1681</v>
       </c>
       <c r="G628" t="s">
         <v>1806</v>
@@ -22210,13 +22210,13 @@
     </row>
     <row r="629" spans="1:8">
       <c r="A629" t="s">
-        <v>411</v>
+        <v>382</v>
       </c>
       <c r="B629" t="s">
         <v>964</v>
       </c>
       <c r="C629" t="s">
-        <v>1346</v>
+        <v>1331</v>
       </c>
       <c r="D629" t="s">
         <v>1612</v>
@@ -22225,7 +22225,7 @@
         <v>1636</v>
       </c>
       <c r="F629" t="s">
-        <v>1681</v>
+        <v>1644</v>
       </c>
       <c r="G629" t="s">
         <v>1806</v>
@@ -22236,22 +22236,22 @@
     </row>
     <row r="630" spans="1:8">
       <c r="A630" t="s">
-        <v>382</v>
+        <v>411</v>
       </c>
       <c r="B630" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="C630" t="s">
-        <v>1331</v>
+        <v>1416</v>
       </c>
       <c r="D630" t="s">
-        <v>1612</v>
+        <v>1618</v>
       </c>
       <c r="E630" t="s">
         <v>1636</v>
       </c>
       <c r="F630" t="s">
-        <v>1644</v>
+        <v>1671</v>
       </c>
       <c r="G630" t="s">
         <v>1806</v>
@@ -22265,19 +22265,19 @@
         <v>412</v>
       </c>
       <c r="B631" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="C631" t="s">
-        <v>1416</v>
+        <v>1305</v>
       </c>
       <c r="D631" t="s">
-        <v>1618</v>
+        <v>1613</v>
       </c>
       <c r="E631" t="s">
         <v>1636</v>
       </c>
       <c r="F631" t="s">
-        <v>1671</v>
+        <v>1646</v>
       </c>
       <c r="G631" t="s">
         <v>1806</v>
@@ -22294,16 +22294,16 @@
         <v>964</v>
       </c>
       <c r="C632" t="s">
-        <v>1305</v>
+        <v>1332</v>
       </c>
       <c r="D632" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="E632" t="s">
         <v>1636</v>
       </c>
       <c r="F632" t="s">
-        <v>1646</v>
+        <v>1691</v>
       </c>
       <c r="G632" t="s">
         <v>1806</v>
@@ -45272,7 +45272,7 @@
     </row>
     <row r="1516" spans="1:8">
       <c r="A1516" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B1516" t="s">
         <v>964</v>
@@ -45402,7 +45402,7 @@
     </row>
     <row r="1521" spans="1:8">
       <c r="A1521" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B1521" t="s">
         <v>964</v>
@@ -46078,7 +46078,7 @@
     </row>
     <row r="1547" spans="1:8">
       <c r="A1547" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B1547" t="s">
         <v>962</v>

--- a/dataEDT-ELT-S1-2027.xlsx
+++ b/dataEDT-ELT-S1-2027.xlsx
@@ -2536,13 +2536,13 @@
     <t>TP-Electrotechnique fondamentale 1-SG22</t>
   </si>
   <si>
+    <t>TP-Electronique fondamentale 1-SG21</t>
+  </si>
+  <si>
     <t>TP-Electrotechnique fondamentale 1-SG21</t>
   </si>
   <si>
     <t>TP-Programmation Python-SG32</t>
-  </si>
-  <si>
-    <t>TP-Electronique fondamentale 1-SG21</t>
   </si>
   <si>
     <t>TP-Electrotechnique fondamentale 1-SG31</t>
@@ -32867,16 +32867,16 @@
     </row>
     <row r="1039" spans="1:8">
       <c r="A1039" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B1039" t="s">
         <v>961</v>
       </c>
       <c r="C1039" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="D1039" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="E1039" t="s">
         <v>1634</v>
@@ -32893,22 +32893,22 @@
     </row>
     <row r="1040" spans="1:8">
       <c r="A1040" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B1040" t="s">
         <v>961</v>
       </c>
       <c r="C1040" t="s">
-        <v>1341</v>
+        <v>1334</v>
       </c>
       <c r="D1040" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="E1040" t="s">
         <v>1634</v>
       </c>
       <c r="F1040" t="s">
-        <v>1679</v>
+        <v>1666</v>
       </c>
       <c r="G1040" t="s">
         <v>1823</v>
@@ -32919,22 +32919,22 @@
     </row>
     <row r="1041" spans="1:8">
       <c r="A1041" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B1041" t="s">
-        <v>961</v>
+        <v>1174</v>
       </c>
       <c r="C1041" t="s">
-        <v>1334</v>
+        <v>1307</v>
       </c>
       <c r="D1041" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="E1041" t="s">
         <v>1634</v>
       </c>
       <c r="F1041" t="s">
-        <v>1666</v>
+        <v>1651</v>
       </c>
       <c r="G1041" t="s">
         <v>1823</v>
@@ -32945,22 +32945,22 @@
     </row>
     <row r="1042" spans="1:8">
       <c r="A1042" t="s">
-        <v>647</v>
+        <v>631</v>
       </c>
       <c r="B1042" t="s">
-        <v>1174</v>
+        <v>960</v>
       </c>
       <c r="C1042" t="s">
-        <v>1307</v>
+        <v>1343</v>
       </c>
       <c r="D1042" t="s">
-        <v>1619</v>
+        <v>1611</v>
       </c>
       <c r="E1042" t="s">
-        <v>1634</v>
+        <v>1638</v>
       </c>
       <c r="F1042" t="s">
-        <v>1651</v>
+        <v>1702</v>
       </c>
       <c r="G1042" t="s">
         <v>1823</v>
@@ -32971,16 +32971,16 @@
     </row>
     <row r="1043" spans="1:8">
       <c r="A1043" t="s">
-        <v>631</v>
+        <v>243</v>
       </c>
       <c r="B1043" t="s">
         <v>960</v>
       </c>
       <c r="C1043" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="D1043" t="s">
-        <v>1611</v>
+        <v>1614</v>
       </c>
       <c r="E1043" t="s">
         <v>1638</v>
@@ -32997,22 +32997,22 @@
     </row>
     <row r="1044" spans="1:8">
       <c r="A1044" t="s">
-        <v>243</v>
+        <v>648</v>
       </c>
       <c r="B1044" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C1044" t="s">
-        <v>1346</v>
+        <v>1307</v>
       </c>
       <c r="D1044" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="E1044" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
       <c r="F1044" t="s">
-        <v>1702</v>
+        <v>1752</v>
       </c>
       <c r="G1044" t="s">
         <v>1823</v>
@@ -33023,22 +33023,22 @@
     </row>
     <row r="1045" spans="1:8">
       <c r="A1045" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B1045" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="C1045" t="s">
         <v>1307</v>
       </c>
       <c r="D1045" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="E1045" t="s">
         <v>1635</v>
       </c>
       <c r="F1045" t="s">
-        <v>1752</v>
+        <v>1642</v>
       </c>
       <c r="G1045" t="s">
         <v>1823</v>
@@ -33049,16 +33049,16 @@
     </row>
     <row r="1046" spans="1:8">
       <c r="A1046" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B1046" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="C1046" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D1046" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="E1046" t="s">
         <v>1635</v>
@@ -33084,7 +33084,7 @@
         <v>1306</v>
       </c>
       <c r="D1047" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="E1047" t="s">
         <v>1635</v>
@@ -33101,22 +33101,22 @@
     </row>
     <row r="1048" spans="1:8">
       <c r="A1048" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B1048" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C1048" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="D1048" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="E1048" t="s">
         <v>1635</v>
       </c>
       <c r="F1048" t="s">
-        <v>1642</v>
+        <v>1752</v>
       </c>
       <c r="G1048" t="s">
         <v>1823</v>
@@ -33127,22 +33127,22 @@
     </row>
     <row r="1049" spans="1:8">
       <c r="A1049" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B1049" t="s">
         <v>961</v>
       </c>
       <c r="C1049" t="s">
-        <v>1307</v>
+        <v>1501</v>
       </c>
       <c r="D1049" t="s">
-        <v>1615</v>
+        <v>1611</v>
       </c>
       <c r="E1049" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="F1049" t="s">
-        <v>1752</v>
+        <v>1762</v>
       </c>
       <c r="G1049" t="s">
         <v>1823</v>
@@ -33153,22 +33153,22 @@
     </row>
     <row r="1050" spans="1:8">
       <c r="A1050" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B1050" t="s">
-        <v>961</v>
+        <v>1175</v>
       </c>
       <c r="C1050" t="s">
-        <v>1501</v>
+        <v>1402</v>
       </c>
       <c r="D1050" t="s">
-        <v>1611</v>
+        <v>1621</v>
       </c>
       <c r="E1050" t="s">
         <v>1636</v>
       </c>
       <c r="F1050" t="s">
-        <v>1762</v>
+        <v>1642</v>
       </c>
       <c r="G1050" t="s">
         <v>1823</v>
@@ -33179,16 +33179,16 @@
     </row>
     <row r="1051" spans="1:8">
       <c r="A1051" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B1051" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="C1051" t="s">
         <v>1402</v>
       </c>
       <c r="D1051" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="E1051" t="s">
         <v>1636</v>
@@ -33205,16 +33205,16 @@
     </row>
     <row r="1052" spans="1:8">
       <c r="A1052" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B1052" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="C1052" t="s">
-        <v>1402</v>
+        <v>1455</v>
       </c>
       <c r="D1052" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="E1052" t="s">
         <v>1636</v>
@@ -33231,16 +33231,16 @@
     </row>
     <row r="1053" spans="1:8">
       <c r="A1053" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B1053" t="s">
-        <v>1177</v>
+        <v>960</v>
       </c>
       <c r="C1053" t="s">
-        <v>1455</v>
+        <v>1501</v>
       </c>
       <c r="D1053" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="E1053" t="s">
         <v>1636</v>
@@ -33257,22 +33257,22 @@
     </row>
     <row r="1054" spans="1:8">
       <c r="A1054" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B1054" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C1054" t="s">
-        <v>1501</v>
+        <v>1343</v>
       </c>
       <c r="D1054" t="s">
-        <v>1615</v>
+        <v>1611</v>
       </c>
       <c r="E1054" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="F1054" t="s">
-        <v>1642</v>
+        <v>1763</v>
       </c>
       <c r="G1054" t="s">
         <v>1823</v>
@@ -33283,22 +33283,22 @@
     </row>
     <row r="1055" spans="1:8">
       <c r="A1055" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B1055" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="C1055" t="s">
-        <v>1343</v>
+        <v>1455</v>
       </c>
       <c r="D1055" t="s">
-        <v>1611</v>
+        <v>1614</v>
       </c>
       <c r="E1055" t="s">
         <v>1637</v>
       </c>
       <c r="F1055" t="s">
-        <v>1763</v>
+        <v>1652</v>
       </c>
       <c r="G1055" t="s">
         <v>1823</v>
@@ -33309,48 +33309,48 @@
     </row>
     <row r="1056" spans="1:8">
       <c r="A1056" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B1056" t="s">
-        <v>960</v>
+        <v>1178</v>
       </c>
       <c r="C1056" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="D1056" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="E1056" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
       <c r="F1056" t="s">
-        <v>1652</v>
+        <v>1663</v>
       </c>
       <c r="G1056" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="H1056" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1057" spans="1:8">
       <c r="A1057" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B1057" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="C1057" t="s">
-        <v>1454</v>
+        <v>1502</v>
       </c>
       <c r="D1057" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="E1057" t="s">
         <v>1634</v>
       </c>
       <c r="F1057" t="s">
-        <v>1663</v>
+        <v>1676</v>
       </c>
       <c r="G1057" t="s">
         <v>1824</v>
@@ -33370,7 +33370,7 @@
         <v>1502</v>
       </c>
       <c r="D1058" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="E1058" t="s">
         <v>1634</v>
@@ -33387,22 +33387,22 @@
     </row>
     <row r="1059" spans="1:8">
       <c r="A1059" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B1059" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="C1059" t="s">
-        <v>1502</v>
+        <v>1405</v>
       </c>
       <c r="D1059" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="E1059" t="s">
         <v>1634</v>
       </c>
       <c r="F1059" t="s">
-        <v>1676</v>
+        <v>1663</v>
       </c>
       <c r="G1059" t="s">
         <v>1824</v>
@@ -33413,16 +33413,16 @@
     </row>
     <row r="1060" spans="1:8">
       <c r="A1060" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B1060" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="C1060" t="s">
         <v>1405</v>
       </c>
       <c r="D1060" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="E1060" t="s">
         <v>1634</v>
@@ -33439,22 +33439,22 @@
     </row>
     <row r="1061" spans="1:8">
       <c r="A1061" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B1061" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="C1061" t="s">
-        <v>1405</v>
+        <v>1412</v>
       </c>
       <c r="D1061" t="s">
-        <v>1615</v>
+        <v>1611</v>
       </c>
       <c r="E1061" t="s">
-        <v>1634</v>
+        <v>1638</v>
       </c>
       <c r="F1061" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="G1061" t="s">
         <v>1824</v>
@@ -33465,22 +33465,22 @@
     </row>
     <row r="1062" spans="1:8">
       <c r="A1062" t="s">
-        <v>661</v>
+        <v>630</v>
       </c>
       <c r="B1062" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C1062" t="s">
-        <v>1412</v>
+        <v>1339</v>
       </c>
       <c r="D1062" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="E1062" t="s">
         <v>1638</v>
       </c>
       <c r="F1062" t="s">
-        <v>1660</v>
+        <v>1663</v>
       </c>
       <c r="G1062" t="s">
         <v>1824</v>
@@ -33491,22 +33491,22 @@
     </row>
     <row r="1063" spans="1:8">
       <c r="A1063" t="s">
-        <v>630</v>
+        <v>661</v>
       </c>
       <c r="B1063" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C1063" t="s">
-        <v>1339</v>
+        <v>1412</v>
       </c>
       <c r="D1063" t="s">
-        <v>1612</v>
+        <v>1615</v>
       </c>
       <c r="E1063" t="s">
         <v>1638</v>
       </c>
       <c r="F1063" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="G1063" t="s">
         <v>1824</v>
@@ -33517,22 +33517,22 @@
     </row>
     <row r="1064" spans="1:8">
       <c r="A1064" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B1064" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="C1064" t="s">
-        <v>1412</v>
+        <v>1312</v>
       </c>
       <c r="D1064" t="s">
-        <v>1615</v>
+        <v>1611</v>
       </c>
       <c r="E1064" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
       <c r="F1064" t="s">
-        <v>1660</v>
+        <v>1663</v>
       </c>
       <c r="G1064" t="s">
         <v>1824</v>
@@ -33543,16 +33543,16 @@
     </row>
     <row r="1065" spans="1:8">
       <c r="A1065" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B1065" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C1065" t="s">
-        <v>1312</v>
+        <v>1449</v>
       </c>
       <c r="D1065" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="E1065" t="s">
         <v>1635</v>
@@ -33569,13 +33569,13 @@
     </row>
     <row r="1066" spans="1:8">
       <c r="A1066" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B1066" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C1066" t="s">
-        <v>1449</v>
+        <v>1503</v>
       </c>
       <c r="D1066" t="s">
         <v>1612</v>
@@ -33584,7 +33584,7 @@
         <v>1635</v>
       </c>
       <c r="F1066" t="s">
-        <v>1663</v>
+        <v>1764</v>
       </c>
       <c r="G1066" t="s">
         <v>1824</v>
@@ -33595,22 +33595,22 @@
     </row>
     <row r="1067" spans="1:8">
       <c r="A1067" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B1067" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C1067" t="s">
-        <v>1503</v>
+        <v>1449</v>
       </c>
       <c r="D1067" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="E1067" t="s">
         <v>1635</v>
       </c>
       <c r="F1067" t="s">
-        <v>1764</v>
+        <v>1663</v>
       </c>
       <c r="G1067" t="s">
         <v>1824</v>
@@ -33621,13 +33621,13 @@
     </row>
     <row r="1068" spans="1:8">
       <c r="A1068" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B1068" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C1068" t="s">
-        <v>1449</v>
+        <v>1503</v>
       </c>
       <c r="D1068" t="s">
         <v>1613</v>
@@ -33636,7 +33636,7 @@
         <v>1635</v>
       </c>
       <c r="F1068" t="s">
-        <v>1663</v>
+        <v>1764</v>
       </c>
       <c r="G1068" t="s">
         <v>1824</v>
@@ -33647,22 +33647,22 @@
     </row>
     <row r="1069" spans="1:8">
       <c r="A1069" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B1069" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="C1069" t="s">
-        <v>1503</v>
+        <v>1312</v>
       </c>
       <c r="D1069" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="E1069" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="F1069" t="s">
-        <v>1764</v>
+        <v>1663</v>
       </c>
       <c r="G1069" t="s">
         <v>1824</v>
@@ -33673,16 +33673,16 @@
     </row>
     <row r="1070" spans="1:8">
       <c r="A1070" t="s">
-        <v>665</v>
+        <v>631</v>
       </c>
       <c r="B1070" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="C1070" t="s">
-        <v>1312</v>
+        <v>1495</v>
       </c>
       <c r="D1070" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="E1070" t="s">
         <v>1636</v>
@@ -33708,7 +33708,7 @@
         <v>1495</v>
       </c>
       <c r="D1071" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="E1071" t="s">
         <v>1636</v>
@@ -33725,16 +33725,16 @@
     </row>
     <row r="1072" spans="1:8">
       <c r="A1072" t="s">
-        <v>631</v>
+        <v>666</v>
       </c>
       <c r="B1072" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="C1072" t="s">
-        <v>1495</v>
+        <v>1449</v>
       </c>
       <c r="D1072" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="E1072" t="s">
         <v>1636</v>
@@ -33751,16 +33751,16 @@
     </row>
     <row r="1073" spans="1:8">
       <c r="A1073" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="B1073" t="s">
-        <v>1189</v>
+        <v>1184</v>
       </c>
       <c r="C1073" t="s">
-        <v>1449</v>
+        <v>1312</v>
       </c>
       <c r="D1073" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="E1073" t="s">
         <v>1636</v>
@@ -33777,19 +33777,19 @@
     </row>
     <row r="1074" spans="1:8">
       <c r="A1074" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="B1074" t="s">
-        <v>1184</v>
+        <v>1190</v>
       </c>
       <c r="C1074" t="s">
-        <v>1312</v>
+        <v>1449</v>
       </c>
       <c r="D1074" t="s">
-        <v>1615</v>
+        <v>1611</v>
       </c>
       <c r="E1074" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="F1074" t="s">
         <v>1663</v>
@@ -33803,16 +33803,16 @@
     </row>
     <row r="1075" spans="1:8">
       <c r="A1075" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B1075" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="C1075" t="s">
-        <v>1449</v>
+        <v>1407</v>
       </c>
       <c r="D1075" t="s">
-        <v>1611</v>
+        <v>1614</v>
       </c>
       <c r="E1075" t="s">
         <v>1637</v>
@@ -33829,16 +33829,16 @@
     </row>
     <row r="1076" spans="1:8">
       <c r="A1076" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B1076" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="C1076" t="s">
         <v>1407</v>
       </c>
       <c r="D1076" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="E1076" t="s">
         <v>1637</v>
@@ -33855,48 +33855,48 @@
     </row>
     <row r="1077" spans="1:8">
       <c r="A1077" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B1077" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="C1077" t="s">
-        <v>1407</v>
+        <v>1334</v>
       </c>
       <c r="D1077" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="E1077" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
       <c r="F1077" t="s">
-        <v>1663</v>
+        <v>1643</v>
       </c>
       <c r="G1077" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="H1077" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="1078" spans="1:8">
       <c r="A1078" t="s">
-        <v>670</v>
+        <v>245</v>
       </c>
       <c r="B1078" t="s">
-        <v>1193</v>
+        <v>960</v>
       </c>
       <c r="C1078" t="s">
-        <v>1334</v>
+        <v>1347</v>
       </c>
       <c r="D1078" t="s">
-        <v>1616</v>
+        <v>1612</v>
       </c>
       <c r="E1078" t="s">
         <v>1634</v>
       </c>
       <c r="F1078" t="s">
-        <v>1643</v>
+        <v>1683</v>
       </c>
       <c r="G1078" t="s">
         <v>1825</v>
@@ -33907,16 +33907,16 @@
     </row>
     <row r="1079" spans="1:8">
       <c r="A1079" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B1079" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="C1079" t="s">
         <v>1347</v>
       </c>
       <c r="D1079" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="E1079" t="s">
         <v>1634</v>
@@ -33933,22 +33933,22 @@
     </row>
     <row r="1080" spans="1:8">
       <c r="A1080" t="s">
-        <v>246</v>
+        <v>671</v>
       </c>
       <c r="B1080" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="C1080" t="s">
-        <v>1347</v>
+        <v>1329</v>
       </c>
       <c r="D1080" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="E1080" t="s">
         <v>1634</v>
       </c>
       <c r="F1080" t="s">
-        <v>1683</v>
+        <v>1643</v>
       </c>
       <c r="G1080" t="s">
         <v>1825</v>
@@ -33959,16 +33959,16 @@
     </row>
     <row r="1081" spans="1:8">
       <c r="A1081" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B1081" t="s">
-        <v>960</v>
+        <v>1194</v>
       </c>
       <c r="C1081" t="s">
-        <v>1329</v>
+        <v>1334</v>
       </c>
       <c r="D1081" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="E1081" t="s">
         <v>1634</v>
@@ -33985,22 +33985,22 @@
     </row>
     <row r="1082" spans="1:8">
       <c r="A1082" t="s">
-        <v>672</v>
+        <v>631</v>
       </c>
       <c r="B1082" t="s">
-        <v>1194</v>
+        <v>960</v>
       </c>
       <c r="C1082" t="s">
-        <v>1334</v>
+        <v>1343</v>
       </c>
       <c r="D1082" t="s">
-        <v>1619</v>
+        <v>1611</v>
       </c>
       <c r="E1082" t="s">
-        <v>1634</v>
+        <v>1638</v>
       </c>
       <c r="F1082" t="s">
-        <v>1643</v>
+        <v>1702</v>
       </c>
       <c r="G1082" t="s">
         <v>1825</v>
@@ -34011,16 +34011,16 @@
     </row>
     <row r="1083" spans="1:8">
       <c r="A1083" t="s">
-        <v>631</v>
+        <v>243</v>
       </c>
       <c r="B1083" t="s">
         <v>960</v>
       </c>
       <c r="C1083" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="D1083" t="s">
-        <v>1611</v>
+        <v>1614</v>
       </c>
       <c r="E1083" t="s">
         <v>1638</v>
@@ -34037,22 +34037,22 @@
     </row>
     <row r="1084" spans="1:8">
       <c r="A1084" t="s">
-        <v>243</v>
+        <v>673</v>
       </c>
       <c r="B1084" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C1084" t="s">
-        <v>1346</v>
+        <v>1335</v>
       </c>
       <c r="D1084" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="E1084" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
       <c r="F1084" t="s">
-        <v>1702</v>
+        <v>1641</v>
       </c>
       <c r="G1084" t="s">
         <v>1825</v>
@@ -34063,22 +34063,22 @@
     </row>
     <row r="1085" spans="1:8">
       <c r="A1085" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B1085" t="s">
         <v>961</v>
       </c>
       <c r="C1085" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D1085" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="E1085" t="s">
         <v>1635</v>
       </c>
       <c r="F1085" t="s">
-        <v>1641</v>
+        <v>1666</v>
       </c>
       <c r="G1085" t="s">
         <v>1825</v>
@@ -34089,22 +34089,22 @@
     </row>
     <row r="1086" spans="1:8">
       <c r="A1086" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B1086" t="s">
-        <v>961</v>
+        <v>1195</v>
       </c>
       <c r="C1086" t="s">
-        <v>1334</v>
+        <v>1303</v>
       </c>
       <c r="D1086" t="s">
-        <v>1612</v>
+        <v>1618</v>
       </c>
       <c r="E1086" t="s">
         <v>1635</v>
       </c>
       <c r="F1086" t="s">
-        <v>1666</v>
+        <v>1643</v>
       </c>
       <c r="G1086" t="s">
         <v>1825</v>
@@ -34115,22 +34115,22 @@
     </row>
     <row r="1087" spans="1:8">
       <c r="A1087" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B1087" t="s">
-        <v>1195</v>
+        <v>961</v>
       </c>
       <c r="C1087" t="s">
         <v>1303</v>
       </c>
       <c r="D1087" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="E1087" t="s">
         <v>1635</v>
       </c>
       <c r="F1087" t="s">
-        <v>1643</v>
+        <v>1724</v>
       </c>
       <c r="G1087" t="s">
         <v>1825</v>
@@ -34141,22 +34141,22 @@
     </row>
     <row r="1088" spans="1:8">
       <c r="A1088" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B1088" t="s">
-        <v>961</v>
+        <v>1196</v>
       </c>
       <c r="C1088" t="s">
-        <v>1303</v>
+        <v>1329</v>
       </c>
       <c r="D1088" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="E1088" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="F1088" t="s">
-        <v>1724</v>
+        <v>1643</v>
       </c>
       <c r="G1088" t="s">
         <v>1825</v>
@@ -34167,16 +34167,16 @@
     </row>
     <row r="1089" spans="1:8">
       <c r="A1089" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B1089" t="s">
-        <v>1196</v>
+        <v>960</v>
       </c>
       <c r="C1089" t="s">
         <v>1329</v>
       </c>
       <c r="D1089" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="E1089" t="s">
         <v>1636</v>
@@ -34193,22 +34193,22 @@
     </row>
     <row r="1090" spans="1:8">
       <c r="A1090" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B1090" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C1090" t="s">
-        <v>1329</v>
+        <v>1500</v>
       </c>
       <c r="D1090" t="s">
-        <v>1615</v>
+        <v>1611</v>
       </c>
       <c r="E1090" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="F1090" t="s">
-        <v>1643</v>
+        <v>1679</v>
       </c>
       <c r="G1090" t="s">
         <v>1825</v>
@@ -34225,7 +34225,7 @@
         <v>961</v>
       </c>
       <c r="C1091" t="s">
-        <v>1500</v>
+        <v>1339</v>
       </c>
       <c r="D1091" t="s">
         <v>1611</v>
@@ -42025,16 +42025,16 @@
         <v>961</v>
       </c>
       <c r="C1391" t="s">
-        <v>1310</v>
+        <v>1568</v>
       </c>
       <c r="D1391" t="s">
-        <v>1617</v>
+        <v>1611</v>
       </c>
       <c r="E1391" t="s">
         <v>1638</v>
       </c>
       <c r="F1391" t="s">
-        <v>1687</v>
+        <v>1778</v>
       </c>
       <c r="G1391" t="s">
         <v>1835</v>
@@ -42048,10 +42048,10 @@
         <v>841</v>
       </c>
       <c r="B1392" t="s">
-        <v>1225</v>
+        <v>961</v>
       </c>
       <c r="C1392" t="s">
-        <v>1567</v>
+        <v>1310</v>
       </c>
       <c r="D1392" t="s">
         <v>1617</v>
@@ -42060,7 +42060,7 @@
         <v>1638</v>
       </c>
       <c r="F1392" t="s">
-        <v>1664</v>
+        <v>1687</v>
       </c>
       <c r="G1392" t="s">
         <v>1835</v>
@@ -42074,19 +42074,19 @@
         <v>842</v>
       </c>
       <c r="B1393" t="s">
-        <v>961</v>
+        <v>1225</v>
       </c>
       <c r="C1393" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="D1393" t="s">
-        <v>1611</v>
+        <v>1617</v>
       </c>
       <c r="E1393" t="s">
         <v>1638</v>
       </c>
       <c r="F1393" t="s">
-        <v>1778</v>
+        <v>1664</v>
       </c>
       <c r="G1393" t="s">
         <v>1835</v>
@@ -42097,7 +42097,7 @@
     </row>
     <row r="1394" spans="1:8">
       <c r="A1394" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B1394" t="s">
         <v>961</v>
